--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2217" uniqueCount="2217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="2218">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87407064437866</t>
+    <t xml:space="preserve">7.87406969070435</t>
   </si>
   <si>
     <t xml:space="preserve">TEN.MI</t>
@@ -47,52 +47,52 @@
     <t xml:space="preserve">7.88865041732788</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6990909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48036670684814</t>
+    <t xml:space="preserve">7.69909143447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48036623001099</t>
   </si>
   <si>
     <t xml:space="preserve">7.19602489471436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11582660675049</t>
+    <t xml:space="preserve">7.11582565307617</t>
   </si>
   <si>
     <t xml:space="preserve">7.07937240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12311887741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07208108901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62734270095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.569016456604</t>
+    <t xml:space="preserve">7.1231164932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07208061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62734365463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56901597976685</t>
   </si>
   <si>
     <t xml:space="preserve">6.77680397033691</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39403772354126</t>
+    <t xml:space="preserve">6.39403676986694</t>
   </si>
   <si>
     <t xml:space="preserve">6.63463354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80596780776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78045034408569</t>
+    <t xml:space="preserve">6.80596685409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78044939041138</t>
   </si>
   <si>
     <t xml:space="preserve">6.88981103897095</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91168403625488</t>
+    <t xml:space="preserve">6.91168308258057</t>
   </si>
   <si>
     <t xml:space="preserve">6.82783889770508</t>
@@ -104,193 +104,193 @@
     <t xml:space="preserve">6.5143346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03562688827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43413686752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29925584793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80232048034668</t>
+    <t xml:space="preserve">7.03562593460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43413543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29925727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.802321434021</t>
   </si>
   <si>
     <t xml:space="preserve">6.95542812347412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74035024642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14863586425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06114530563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148431777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11947250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86064910888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54349899291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55443334579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16686248779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32725954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50224018096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45120573043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61160135269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91781568527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00530529022217</t>
+    <t xml:space="preserve">6.74034976959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14863443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06114625930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8314847946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11947202682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86064863204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54349756240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55443429946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16686344146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3272590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50223684310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45120429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61160039901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91781234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00530433654785</t>
   </si>
   <si>
     <t xml:space="preserve">7.71367263793945</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85948657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58972692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82303285598755</t>
+    <t xml:space="preserve">7.85948848724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58972930908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82303428649902</t>
   </si>
   <si>
     <t xml:space="preserve">7.73554563522339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96155738830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81574249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77929019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95427083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72096300125122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66992855072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98343229293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032464981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53140211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6626353263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6407642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07821369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11466598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17299556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42087841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41358852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45004272460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69793319702148</t>
+    <t xml:space="preserve">7.96155834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81574296951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77928972244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.954270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7209644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66992712020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98343276977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032369613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53140258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66263628005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64076471328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07821273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11466693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17299365997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4208812713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41358947753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45004558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69792938232422</t>
   </si>
   <si>
     <t xml:space="preserve">8.82916450500488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86561965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91665744781494</t>
+    <t xml:space="preserve">8.8656177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91665458679199</t>
   </si>
   <si>
     <t xml:space="preserve">8.63960456848145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80000114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80729293823242</t>
+    <t xml:space="preserve">8.8000020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80729389190674</t>
   </si>
   <si>
     <t xml:space="preserve">8.58856868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47191715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0198860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97614097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39901065826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24589920043945</t>
+    <t xml:space="preserve">8.47191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01988506317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97614002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39900875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2459020614624</t>
   </si>
   <si>
     <t xml:space="preserve">8.21673679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29693698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30422782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45733547210693</t>
+    <t xml:space="preserve">8.29693794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30422878265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4573335647583</t>
   </si>
   <si>
     <t xml:space="preserve">8.64689445495605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67605686187744</t>
+    <t xml:space="preserve">8.67605876922607</t>
   </si>
   <si>
     <t xml:space="preserve">8.3917179107666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56669807434082</t>
+    <t xml:space="preserve">8.56669521331787</t>
   </si>
   <si>
     <t xml:space="preserve">8.62655067443848</t>
@@ -299,49 +299,49 @@
     <t xml:space="preserve">8.73129653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75374412536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.978196144104</t>
+    <t xml:space="preserve">8.75374221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95575141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97819709777832</t>
   </si>
   <si>
     <t xml:space="preserve">8.98567771911621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91086101531982</t>
+    <t xml:space="preserve">8.91086006164551</t>
   </si>
   <si>
     <t xml:space="preserve">8.80611515045166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67892551422119</t>
+    <t xml:space="preserve">8.67892265319824</t>
   </si>
   <si>
     <t xml:space="preserve">8.6489953994751</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08294296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53185176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69645118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52437019348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49444198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28495216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1577615737915</t>
+    <t xml:space="preserve">9.0829439163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53185272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69645214080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52436923980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4944429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28495121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15776062011719</t>
   </si>
   <si>
     <t xml:space="preserve">9.34480667114258</t>
@@ -350,70 +350,70 @@
     <t xml:space="preserve">9.17272567749023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40466213226318</t>
+    <t xml:space="preserve">9.40466117858887</t>
   </si>
   <si>
     <t xml:space="preserve">9.66652488708496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4271068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80119800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30739879608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0455322265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14279747009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61415386199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73386383056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8685359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83112525939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5991907119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32236194610596</t>
+    <t xml:space="preserve">9.42710781097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8011999130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30739688873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04553318023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14279842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61415100097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73386001586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86853504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83112621307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59918785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32236003875732</t>
   </si>
   <si>
     <t xml:space="preserve">9.39718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50940608978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65904426574707</t>
+    <t xml:space="preserve">9.50940799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65904331207275</t>
   </si>
   <si>
     <t xml:space="preserve">9.74882507324219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47947978973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59170532226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21761512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37473201751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18768692016602</t>
+    <t xml:space="preserve">9.4794807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59170627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21761703491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37473392486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18768882751465</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797885894775</t>
@@ -428,10 +428,10 @@
     <t xml:space="preserve">8.8285608291626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94826984405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70885181427002</t>
+    <t xml:space="preserve">8.94826889038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7088508605957</t>
   </si>
   <si>
     <t xml:space="preserve">8.57417774200439</t>
@@ -440,10 +440,10 @@
     <t xml:space="preserve">8.74626064300537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00064373016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19516944885254</t>
+    <t xml:space="preserve">9.00064277648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19517230987549</t>
   </si>
   <si>
     <t xml:space="preserve">9.38969802856445</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">9.36725234985352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48696136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70393562316895</t>
+    <t xml:space="preserve">9.48696231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70393371582031</t>
   </si>
   <si>
     <t xml:space="preserve">9.65156173706055</t>
@@ -464,97 +464,97 @@
     <t xml:space="preserve">9.62911605834961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51688957214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45703411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09042263031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29991436004639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10538864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85848808288574</t>
+    <t xml:space="preserve">9.51689052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45703506469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09042358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22509670257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2999153137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10538768768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85848712921143</t>
   </si>
   <si>
     <t xml:space="preserve">8.66396045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71633243560791</t>
+    <t xml:space="preserve">8.71633148193359</t>
   </si>
   <si>
     <t xml:space="preserve">8.88093376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76870632171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67144298553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69388961791992</t>
+    <t xml:space="preserve">8.76870441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67144393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69388675689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.90337753295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70137023925781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44698810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55921459197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35976982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50192546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64407825469971</t>
+    <t xml:space="preserve">8.7013692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44698715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55921173095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35977077484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50192642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64407920837402</t>
   </si>
   <si>
     <t xml:space="preserve">9.7637882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74134349822998</t>
+    <t xml:space="preserve">9.7413444519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.95083522796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6365966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83860683441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81616401672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94335174560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0406179428101</t>
+    <t xml:space="preserve">9.63660049438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83860874176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81616306304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9433536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0406150817871</t>
   </si>
   <si>
     <t xml:space="preserve">9.99572372436523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0106897354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96579837799072</t>
+    <t xml:space="preserve">10.0106906890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96579742431641</t>
   </si>
   <si>
     <t xml:space="preserve">10.0630617141724</t>
@@ -563,49 +563,49 @@
     <t xml:space="preserve">9.77127075195312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89846229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86105346679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29243278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2800350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6765727996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.616717338562</t>
+    <t xml:space="preserve">9.89846134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86105251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29243183135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2800340652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6765737533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6167192459106</t>
   </si>
   <si>
     <t xml:space="preserve">10.8112459182739</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9384393692017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9309539794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9159908294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7214632034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1216306686401</t>
+    <t xml:space="preserve">10.9384365081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9309558868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9159917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7214622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1216297149658</t>
   </si>
   <si>
     <t xml:space="preserve">10.8045167922974</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0310258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0687808990479</t>
+    <t xml:space="preserve">11.03102684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0687789916992</t>
   </si>
   <si>
     <t xml:space="preserve">10.8347196578979</t>
@@ -614,79 +614,79 @@
     <t xml:space="preserve">10.6761617660522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3783416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464612960815</t>
+    <t xml:space="preserve">11.378342628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464622497559</t>
   </si>
   <si>
     <t xml:space="preserve">11.7407579421997</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0352220535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1937770843506</t>
+    <t xml:space="preserve">12.0352210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1937761306763</t>
   </si>
   <si>
     <t xml:space="preserve">12.0805215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2239789962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5561933517456</t>
+    <t xml:space="preserve">12.2239770889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.556191444397</t>
   </si>
   <si>
     <t xml:space="preserve">12.3749847412109</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2919311523438</t>
+    <t xml:space="preserve">12.2919330596924</t>
   </si>
   <si>
     <t xml:space="preserve">12.4202880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3145809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3674335479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5410919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4504861831665</t>
+    <t xml:space="preserve">12.314582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3674345016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5410928726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4504880905151</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939455032349</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8280029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9790105819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0016641616821</t>
+    <t xml:space="preserve">12.8280038833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9790096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0016632080078</t>
   </si>
   <si>
     <t xml:space="preserve">12.8129043579102</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0243120193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714632034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9488096237183</t>
+    <t xml:space="preserve">13.0243148803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714593887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9488105773926</t>
   </si>
   <si>
     <t xml:space="preserve">12.8808546066284</t>
   </si>
   <si>
-    <t xml:space="preserve">12.865758895874</t>
+    <t xml:space="preserve">12.8657560348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.7751522064209</t>
@@ -695,40 +695,40 @@
     <t xml:space="preserve">12.6769990921021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8204536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7600507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.533540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7676029205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8582048416138</t>
+    <t xml:space="preserve">12.8204545974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7600517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5335426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7676019668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8582077026367</t>
   </si>
   <si>
     <t xml:space="preserve">12.6996488571167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6618986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9865636825562</t>
+    <t xml:space="preserve">12.6618976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9865627288818</t>
   </si>
   <si>
     <t xml:space="preserve">13.0092124938965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8506565093994</t>
+    <t xml:space="preserve">12.8506555557251</t>
   </si>
   <si>
     <t xml:space="preserve">12.2164297103882</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2088794708252</t>
+    <t xml:space="preserve">12.2088785171509</t>
   </si>
   <si>
     <t xml:space="preserve">12.1258239746094</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">12.1182737350464</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1484775543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8766651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0729703903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560258865356</t>
+    <t xml:space="preserve">12.1484756469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8766622543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0729713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.15602684021</t>
   </si>
   <si>
     <t xml:space="preserve">12.2541790008545</t>
@@ -758,28 +758,28 @@
     <t xml:space="preserve">11.974817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8540124893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1862258911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2390785217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7860584259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7256555557251</t>
+    <t xml:space="preserve">11.8540115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1862268447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2390794754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7860593795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7256574630737</t>
   </si>
   <si>
     <t xml:space="preserve">11.9068651199341</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6652536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5142469406128</t>
+    <t xml:space="preserve">11.6652545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5142478942871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5444498062134</t>
@@ -788,118 +788,118 @@
     <t xml:space="preserve">11.4613943099976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0989818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1140804290771</t>
+    <t xml:space="preserve">11.0989809036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1140794754028</t>
   </si>
   <si>
     <t xml:space="preserve">11.1593818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0763292312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3330411911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4085445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4991464614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2952890396118</t>
+    <t xml:space="preserve">11.0763301849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3330402374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.408543586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4991474151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2952909469604</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442823410034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1669321060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2424345016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9932746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8389129638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.763409614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1333742141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0427713394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2013282775879</t>
+    <t xml:space="preserve">11.1669340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2424354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.993275642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8389120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7634077072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1333751678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0427732467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2013263702393</t>
   </si>
   <si>
     <t xml:space="preserve">12.1786756515503</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9370651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3858919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4840478897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2801866531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3481416702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.35569190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3405923843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066976547241</t>
+    <t xml:space="preserve">11.9370679855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3858909606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4840469360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2801885604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3481397628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3556909561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3405914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066986083984</t>
   </si>
   <si>
     <t xml:space="preserve">10.8724708557129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8573684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9026708602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7894153594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949541091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.653510093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6459589004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.661060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.827169418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8800201416016</t>
+    <t xml:space="preserve">10.8573703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9026718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7894172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949550628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6535091400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6459617614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6610612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8271684646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8800191879272</t>
   </si>
   <si>
     <t xml:space="preserve">10.7441139221191</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9781742095947</t>
+    <t xml:space="preserve">10.9781732559204</t>
   </si>
   <si>
     <t xml:space="preserve">10.7139139175415</t>
@@ -908,22 +908,22 @@
     <t xml:space="preserve">10.8951215744019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0183172225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721193313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0260152816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9259195327759</t>
+    <t xml:space="preserve">11.0183162689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721183776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0260162353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9259204864502</t>
   </si>
   <si>
     <t xml:space="preserve">10.7642259597778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6410274505615</t>
+    <t xml:space="preserve">10.6410293579102</t>
   </si>
   <si>
     <t xml:space="preserve">10.6025314331055</t>
@@ -935,67 +935,67 @@
     <t xml:space="preserve">10.4793338775635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4408378601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4177370071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406444549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4023361206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7873229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4947338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5409345626831</t>
+    <t xml:space="preserve">10.4408369064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4177379608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406425476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4023380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7873258590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4947328567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5409336090088</t>
   </si>
   <si>
     <t xml:space="preserve">10.3176412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3715400695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2791433334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2868423461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3330402374268</t>
+    <t xml:space="preserve">10.3715419769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2791423797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2868413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3330392837524</t>
   </si>
   <si>
     <t xml:space="preserve">10.5101346969604</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8335237503052</t>
+    <t xml:space="preserve">10.8335227966309</t>
   </si>
   <si>
     <t xml:space="preserve">10.8566217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7103281021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6179304122925</t>
+    <t xml:space="preserve">10.7103252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6179313659668</t>
   </si>
   <si>
     <t xml:space="preserve">10.3407402038574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4716348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7796258926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9105195999146</t>
+    <t xml:space="preserve">10.4716358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7796239852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9105205535889</t>
   </si>
   <si>
     <t xml:space="preserve">11.0106182098389</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">10.9413204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7565259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5255346298218</t>
+    <t xml:space="preserve">10.7565279006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5255355834961</t>
   </si>
   <si>
     <t xml:space="preserve">10.6256303787231</t>
@@ -1016,25 +1016,25 @@
     <t xml:space="preserve">10.3099403381348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0943508148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9942512512207</t>
+    <t xml:space="preserve">10.0943470001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99425029754639</t>
   </si>
   <si>
     <t xml:space="preserve">9.27047729492188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3474760055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20888137817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29357719421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16267967224121</t>
+    <t xml:space="preserve">9.34747409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2088794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29357528686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16268157958984</t>
   </si>
   <si>
     <t xml:space="preserve">9.22427845001221</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">8.9778881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00868701934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96248912811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92398929595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87779140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80079460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85469245910645</t>
+    <t xml:space="preserve">9.00868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96248817443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92399024963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87779235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80079364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85469150543213</t>
   </si>
   <si>
     <t xml:space="preserve">8.82389354705811</t>
@@ -1067,31 +1067,31 @@
     <t xml:space="preserve">8.7853946685791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72379493713379</t>
+    <t xml:space="preserve">8.72379684448242</t>
   </si>
   <si>
     <t xml:space="preserve">8.63909912109375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52360439300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62370204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64679908752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60830020904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7468957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03178596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11648273468018</t>
+    <t xml:space="preserve">8.52360343933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62369918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6467981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60829925537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74689674377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03178691864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11648368835449</t>
   </si>
   <si>
     <t xml:space="preserve">9.13188171386719</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">8.93169021606445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15498161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37827205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30127429962158</t>
+    <t xml:space="preserve">9.15498065948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37827396392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3012752532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.32437515258789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33207607269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27817821502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26277923583984</t>
+    <t xml:space="preserve">9.33207416534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27817630767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26277828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.2473783493042</t>
@@ -1127,10 +1127,10 @@
     <t xml:space="preserve">9.23967933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20118045806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1087818145752</t>
+    <t xml:space="preserve">9.20117950439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10878276824951</t>
   </si>
   <si>
     <t xml:space="preserve">8.87009239196777</t>
@@ -1139,40 +1139,40 @@
     <t xml:space="preserve">8.84699058532715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9547872543335</t>
+    <t xml:space="preserve">8.95478820800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.73919582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6314001083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65449905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70839595794678</t>
+    <t xml:space="preserve">8.63140106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65449810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70839691162109</t>
   </si>
   <si>
     <t xml:space="preserve">8.79309463500977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00098705291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0471830368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.055850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1328468322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1020479202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.017352104187</t>
+    <t xml:space="preserve">9.00098609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04718399047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0558500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1328477859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1020488739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0173511505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.94035339355469</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">9.82485771179199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70166397094727</t>
+    <t xml:space="preserve">9.70166301727295</t>
   </si>
   <si>
     <t xml:space="preserve">9.45527172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3089771270752</t>
+    <t xml:space="preserve">9.30897521972656</t>
   </si>
   <si>
     <t xml:space="preserve">9.33977508544922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41760635375977</t>
+    <t xml:space="preserve">9.41760730743408</t>
   </si>
   <si>
     <t xml:space="preserve">9.72893333435059</t>
@@ -1202,25 +1202,25 @@
     <t xml:space="preserve">9.6744499206543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44095611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43317317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50322151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69779968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91572666168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80676460266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64331817626953</t>
+    <t xml:space="preserve">9.44095420837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43317222595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5032205581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69779872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91572761535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80676364898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64331912994385</t>
   </si>
   <si>
     <t xml:space="preserve">9.76784801483154</t>
@@ -1229,10 +1229,10 @@
     <t xml:space="preserve">9.86124706268311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.13365650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4371976852417</t>
+    <t xml:space="preserve">10.1336574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.437198638916</t>
   </si>
   <si>
     <t xml:space="preserve">10.1881380081177</t>
@@ -1244,73 +1244,73 @@
     <t xml:space="preserve">9.95464324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1492214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0324764251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1570053100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3126678466797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3905010223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3438005447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.242618560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4294157028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5928602218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6862592697144</t>
+    <t xml:space="preserve">10.1492233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0324754714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.15700340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3126668930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3904991149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3438024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426195144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4294147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6162090301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5928611755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6862573623657</t>
   </si>
   <si>
     <t xml:space="preserve">10.6784763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9508867263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0520648956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.114330291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8886213302612</t>
+    <t xml:space="preserve">10.9508857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0520658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143321990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8886203765869</t>
   </si>
   <si>
     <t xml:space="preserve">10.8341388702393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9975852966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0831985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2933444976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3011302947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1843786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2544288635254</t>
+    <t xml:space="preserve">10.9975843429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.083197593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2933435440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3011283874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.184380531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2544298171997</t>
   </si>
   <si>
     <t xml:space="preserve">11.3166942596436</t>
@@ -1319,31 +1319,31 @@
     <t xml:space="preserve">11.1610317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9586706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9158620834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7018251419067</t>
+    <t xml:space="preserve">10.9586696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9158601760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7018241882324</t>
   </si>
   <si>
     <t xml:space="preserve">10.5850782394409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3048849105835</t>
+    <t xml:space="preserve">10.3048858642578</t>
   </si>
   <si>
     <t xml:space="preserve">10.4566564559937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0519323348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99355983734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90016269683838</t>
+    <t xml:space="preserve">10.0519332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99356079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90016078948975</t>
   </si>
   <si>
     <t xml:space="preserve">10.0636072158813</t>
@@ -1352,64 +1352,64 @@
     <t xml:space="preserve">10.1180896759033</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2620782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5734043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6668014526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5461616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8730535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.347827911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2427539825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9469928741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0909843444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1493558883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3050174713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7175254821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5462961196899</t>
+    <t xml:space="preserve">10.262077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5734024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6667995452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5461626052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8730554580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.347825050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2427549362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9469938278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0909824371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1493549346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0209331512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3050193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7175264358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5462980270386</t>
   </si>
   <si>
     <t xml:space="preserve">11.4645729064941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1999464035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026573181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2777786254883</t>
+    <t xml:space="preserve">11.1999473571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026582717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.277777671814</t>
   </si>
   <si>
     <t xml:space="preserve">11.1376819610596</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3595008850098</t>
+    <t xml:space="preserve">11.3594999313354</t>
   </si>
   <si>
     <t xml:space="preserve">11.7642240524292</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">11.0442838668823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.596752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6239948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7640905380249</t>
+    <t xml:space="preserve">10.5967531204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6239929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7640895843506</t>
   </si>
   <si>
     <t xml:space="preserve">10.6473445892334</t>
@@ -1433,28 +1433,28 @@
     <t xml:space="preserve">10.8574876785278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8964042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8263559341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3244771957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0987663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1298999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451150894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6435852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6708269119263</t>
+    <t xml:space="preserve">10.8964033126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8263540267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3244762420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.09876537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1298990249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4451160430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6435880661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6708250045776</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929956436157</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">11.5813207626343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795355796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8654050827026</t>
+    <t xml:space="preserve">11.7953586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.865406036377</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004306793213</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">12.1611661911011</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8926467895508</t>
+    <t xml:space="preserve">11.8926458358765</t>
   </si>
   <si>
     <t xml:space="preserve">11.9393444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8381643295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183586120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5425367355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5308637619019</t>
+    <t xml:space="preserve">11.8381662368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183576583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.542537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5308656692505</t>
   </si>
   <si>
     <t xml:space="preserve">12.5581073760986</t>
@@ -1502,46 +1502,46 @@
     <t xml:space="preserve">12.8344058990479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5542116165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7604684829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.663179397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7059860229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437215805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7020921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3597707748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3052892684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4556312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4635410308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1549453735352</t>
+    <t xml:space="preserve">12.5542144775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7604675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6631784439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7059869766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437206268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7020931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355878829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3597660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3052854537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4556283950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4635419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1549444198608</t>
   </si>
   <si>
     <t xml:space="preserve">12.8661298751831</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5496187210083</t>
+    <t xml:space="preserve">12.5496196746826</t>
   </si>
   <si>
     <t xml:space="preserve">12.419059753418</t>
@@ -1556,13 +1556,13 @@
     <t xml:space="preserve">12.1460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2964105606079</t>
+    <t xml:space="preserve">12.2964124679565</t>
   </si>
   <si>
     <t xml:space="preserve">12.0392475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9996843338013</t>
+    <t xml:space="preserve">11.9996852874756</t>
   </si>
   <si>
     <t xml:space="preserve">12.3478441238403</t>
@@ -1571,139 +1571,139 @@
     <t xml:space="preserve">12.312237739563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3953189849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230155944824</t>
+    <t xml:space="preserve">12.3953218460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230146408081</t>
   </si>
   <si>
     <t xml:space="preserve">12.2726745605469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4784049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9007730484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205560684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.797908782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8374719619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4111461639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8809928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284687042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5377502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4665355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4348840713501</t>
+    <t xml:space="preserve">12.4784059524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9007759094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205570220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7979097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8374738693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4111480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8809938430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284677505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5377492904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4665365219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.434886932373</t>
   </si>
   <si>
     <t xml:space="preserve">12.3755407333374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5733575820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6089639663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6050100326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6683120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9927339553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520820617676</t>
+    <t xml:space="preserve">12.5733594894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6089677810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6050090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6683111190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9927349090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520801544189</t>
   </si>
   <si>
     <t xml:space="preserve">12.6762237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7355680465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.601053237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5456628799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5575323104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4546680450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4586238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2489356994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3201513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3676261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5961322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.762303352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7702131271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9759454727173</t>
+    <t xml:space="preserve">12.7355699539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6010522842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5456619262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5575313568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4546661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4586248397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2489347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3201503753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3676252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5961332321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7623014450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7702140808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9759464263916</t>
   </si>
   <si>
     <t xml:space="preserve">11.9324254989624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.027379989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8216457366943</t>
+    <t xml:space="preserve">12.0273790359497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.821647644043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5328311920166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4418354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5170068740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6159152984619</t>
+    <t xml:space="preserve">11.4418363571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5170059204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6159162521362</t>
   </si>
   <si>
     <t xml:space="preserve">11.5921764373779</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7148265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086724281311</t>
+    <t xml:space="preserve">11.7148246765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0867233276367</t>
   </si>
   <si>
     <t xml:space="preserve">11.8889036178589</t>
@@ -1715,34 +1715,34 @@
     <t xml:space="preserve">11.2281913757324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4339218139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062271118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3310565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9947633743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9037666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7257318496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228666305542</t>
+    <t xml:space="preserve">11.4339227676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062280654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3310556411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9947643280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.903769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7257328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228647232056</t>
   </si>
   <si>
     <t xml:space="preserve">10.6901245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9433326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9314622879028</t>
+    <t xml:space="preserve">10.9433307647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9314632415771</t>
   </si>
   <si>
     <t xml:space="preserve">10.9354200363159</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">10.9987211227417</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1451053619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1530208587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0857620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1174125671387</t>
+    <t xml:space="preserve">11.1451072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.153018951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0857629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.117413520813</t>
   </si>
   <si>
     <t xml:space="preserve">11.7306499481201</t>
@@ -1772,13 +1772,13 @@
     <t xml:space="preserve">11.6396541595459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5842657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4180974960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7266931533813</t>
+    <t xml:space="preserve">11.584264755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4180965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.726692199707</t>
   </si>
   <si>
     <t xml:space="preserve">11.7820825576782</t>
@@ -1793,37 +1793,37 @@
     <t xml:space="preserve">11.572395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9601192474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6238298416138</t>
+    <t xml:space="preserve">11.9601202011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6238269805908</t>
   </si>
   <si>
     <t xml:space="preserve">11.1332378387451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1411514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.188627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3112764358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2400608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0936727523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0818033218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8325529098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4052648544312</t>
+    <t xml:space="preserve">11.1411504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886281967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3112735748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2400598526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.093674659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.081805229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8325548171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4052639007568</t>
   </si>
   <si>
     <t xml:space="preserve">10.2984428405762</t>
@@ -1832,10 +1832,10 @@
     <t xml:space="preserve">10.2628355026245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.171838760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2034902572632</t>
+    <t xml:space="preserve">10.1718378067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2034912109375</t>
   </si>
   <si>
     <t xml:space="preserve">10.0927114486694</t>
@@ -1844,172 +1844,172 @@
     <t xml:space="preserve">10.3933963775635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5635213851929</t>
+    <t xml:space="preserve">10.5635204315186</t>
   </si>
   <si>
     <t xml:space="preserve">10.6268224716187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6307783126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6189107894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199995040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.484393119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2430534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.159969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85137271881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75641918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87510967254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78015613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68019771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40830516815186</t>
+    <t xml:space="preserve">10.6307792663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6189079284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4843921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2430543899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1599712371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85137176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75641822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8751106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7801570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68019676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40830230712891</t>
   </si>
   <si>
     <t xml:space="preserve">9.58823394775391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45228576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29634857177734</t>
+    <t xml:space="preserve">9.45228672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29634761810303</t>
   </si>
   <si>
     <t xml:space="preserve">9.56024360656738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38031482696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71657466888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66059875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49666118621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78854846954346</t>
+    <t xml:space="preserve">9.38031387329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71657371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66059684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49666213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78854751586914</t>
   </si>
   <si>
     <t xml:space="preserve">8.67259311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50865840911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22876739501953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24875926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9968581199646</t>
+    <t xml:space="preserve">8.50865745544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22876644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24875831604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99685764312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.10881423950195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20077896118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18078422546387</t>
+    <t xml:space="preserve">8.20077800750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1807861328125</t>
   </si>
   <si>
     <t xml:space="preserve">7.8912992477417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71217060089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71376895904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38109970092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39389419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34271430969238</t>
+    <t xml:space="preserve">7.71217012405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71377038955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38110065460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39389562606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34271621704102</t>
   </si>
   <si>
     <t xml:space="preserve">7.54903411865234</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61140871047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59861469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88490295410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01285266876221</t>
+    <t xml:space="preserve">7.61140966415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59861612319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88490152359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01285171508789</t>
   </si>
   <si>
     <t xml:space="preserve">8.05683517456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29673957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31673240661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24076175689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16879177093506</t>
+    <t xml:space="preserve">8.2967414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31673336029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24076271057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16879081726074</t>
   </si>
   <si>
     <t xml:space="preserve">8.22476863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52065277099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45267772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32072925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39670085906982</t>
+    <t xml:space="preserve">8.52065181732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45267963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32073211669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39669990539551</t>
   </si>
   <si>
     <t xml:space="preserve">8.53264808654785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8245325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58862495422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70058345794678</t>
+    <t xml:space="preserve">8.82453346252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58862590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70058250427246</t>
   </si>
   <si>
     <t xml:space="preserve">8.7685546875</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">8.98846912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76455783843994</t>
+    <t xml:space="preserve">8.76455688476562</t>
   </si>
   <si>
     <t xml:space="preserve">8.56463527679443</t>
@@ -2033,34 +2033,34 @@
     <t xml:space="preserve">8.7445650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95248222351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20838260650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22037887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43629169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49227237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55224895477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59622859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75616550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63221454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61622142791748</t>
+    <t xml:space="preserve">8.95248317718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20838165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22037601470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43629360198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49227142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55224704742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59622955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7561674118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63221549987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6162223815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.51626110076904</t>
@@ -2072,37 +2072,37 @@
     <t xml:space="preserve">9.3323335647583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39231109619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3643217086792</t>
+    <t xml:space="preserve">9.39231014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36432075500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.48427391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25236511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11241912841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4202995300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84413146972656</t>
+    <t xml:space="preserve">9.252366065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1124210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42029857635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8441333770752</t>
   </si>
   <si>
     <t xml:space="preserve">9.89611148834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84813022613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86812305450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9840784072876</t>
+    <t xml:space="preserve">9.84813117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86812400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98407649993896</t>
   </si>
   <si>
     <t xml:space="preserve">10.036057472229</t>
@@ -2111,70 +2111,70 @@
     <t xml:space="preserve">10.3079500198364</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2039928436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0680446624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82813739776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0080690383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2759637832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.172004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1440162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95608806610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3199443817139</t>
+    <t xml:space="preserve">10.2039918899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0680437088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82813930511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0080680847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2759628295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1720018386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1440143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95608901977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2559690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3199453353882</t>
   </si>
   <si>
     <t xml:space="preserve">10.0440549850464</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93609523773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0040693283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0560483932495</t>
+    <t xml:space="preserve">9.93609619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0040702819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0560493469238</t>
   </si>
   <si>
     <t xml:space="preserve">10.3959140777588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5278625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4279022216797</t>
+    <t xml:space="preserve">10.5278635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4279041290283</t>
   </si>
   <si>
     <t xml:space="preserve">10.7917613983154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5598516464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3359394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9281005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90011024475098</t>
+    <t xml:space="preserve">10.5598526000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3359413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92809867858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90011119842529</t>
   </si>
   <si>
     <t xml:space="preserve">9.74017238616943</t>
@@ -2183,136 +2183,136 @@
     <t xml:space="preserve">9.60422611236572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44029140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60822582244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41230297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34033107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29235076904297</t>
+    <t xml:space="preserve">9.44029331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60822486877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41230201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34033012390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29234886169434</t>
   </si>
   <si>
     <t xml:space="preserve">9.54025173187256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61222267150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96408557891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0160646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0242462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1755704879761</t>
+    <t xml:space="preserve">9.61222362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96408653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0160655975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.024245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1755695343018</t>
   </si>
   <si>
     <t xml:space="preserve">9.85656070709229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4393949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32487964630127</t>
+    <t xml:space="preserve">9.43939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32487869262695</t>
   </si>
   <si>
     <t xml:space="preserve">9.16128444671631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15310478210449</t>
+    <t xml:space="preserve">9.15310382843018</t>
   </si>
   <si>
     <t xml:space="preserve">9.01404857635498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98541927337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62960147857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87499523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08766651153564</t>
+    <t xml:space="preserve">8.9854211807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62960433959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8749942779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08766555786133</t>
   </si>
   <si>
     <t xml:space="preserve">8.78910732269287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79728698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06312847137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19809246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94452285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83409595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87908554077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.050856590271</t>
+    <t xml:space="preserve">8.79728889465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78092765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06312942504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19809532165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94452381134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83409690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87908458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05085849761963</t>
   </si>
   <si>
     <t xml:space="preserve">9.29624938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39440727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25126075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14901542663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42303466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38213634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65206718444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4271240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44757556915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54573154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54164123535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75431728363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66024780273438</t>
+    <t xml:space="preserve">9.39440536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25126266479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14901351928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42303657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38213729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41485500335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65206909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42712497711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44757461547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54573059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54164218902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75431537628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66024875640869</t>
   </si>
   <si>
     <t xml:space="preserve">9.80748271942139</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">9.98743534088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9424467086792</t>
+    <t xml:space="preserve">9.94244766235352</t>
   </si>
   <si>
     <t xml:space="preserve">9.83202171325684</t>
@@ -2333,115 +2333,115 @@
     <t xml:space="preserve">9.45166492462158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28807163238525</t>
+    <t xml:space="preserve">9.2880687713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.12038612365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24308109283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3126106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59072113037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5089225769043</t>
+    <t xml:space="preserve">9.24308300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31260967254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59071922302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50892162322998</t>
   </si>
   <si>
     <t xml:space="preserve">9.26762104034424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93225193023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71548843383789</t>
+    <t xml:space="preserve">8.93225288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71548938751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.56416606903076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36376190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29423332214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44555950164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787399291992</t>
+    <t xml:space="preserve">8.36376285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29423427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44556045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787494659424</t>
   </si>
   <si>
     <t xml:space="preserve">8.0095796585083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14209270477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71838188171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75764560699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05211448669434</t>
+    <t xml:space="preserve">8.14209175109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71838331222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75764513015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05211544036865</t>
   </si>
   <si>
     <t xml:space="preserve">7.88852024078369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98340511322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08810424804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96377325057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07011032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12409591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21652698516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16335964202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10937213897705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06520175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86070823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00467300415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21243858337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17153930664062</t>
+    <t xml:space="preserve">7.98340654373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08810520172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96377277374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07010936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12409687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21652603149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16335868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10937118530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0652027130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86071062088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00467109680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21243667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17153739929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.41284084320068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51099586486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43737983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31468296051025</t>
+    <t xml:space="preserve">8.51099681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43737888336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31468391418457</t>
   </si>
   <si>
     <t xml:space="preserve">8.3719425201416</t>
@@ -2453,139 +2453,139 @@
     <t xml:space="preserve">8.44146919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31877422332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22061634063721</t>
+    <t xml:space="preserve">8.318772315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22061824798584</t>
   </si>
   <si>
     <t xml:space="preserve">8.20016670227051</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97195291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85743999481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85253047943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72983455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00794410705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96213674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81326723098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48771476745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56296682357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54824495315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63658571243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50898170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54333543777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61531829833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88033962249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67257642745972</t>
+    <t xml:space="preserve">7.97195339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85743761062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85253095626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72983360290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00794506072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96213626861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81326770782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48771333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56296825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54824352264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63658428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50898265838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54333639144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61531734466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88034105300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6725754737854</t>
   </si>
   <si>
     <t xml:space="preserve">7.77400302886963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.742919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64803552627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60713958740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66275930404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68239164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70202350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69220733642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8099946975708</t>
+    <t xml:space="preserve">7.74292135238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64803791046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60713768005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66276025772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68239212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70202398300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858987808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69220638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">7.8852481842041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65785217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40591716766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03739261627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17644596099854</t>
+    <t xml:space="preserve">7.65785360336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40591812133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03739166259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17644691467285</t>
   </si>
   <si>
     <t xml:space="preserve">8.32286357879639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18380641937256</t>
+    <t xml:space="preserve">8.18380832672119</t>
   </si>
   <si>
     <t xml:space="preserve">8.19607830047607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23697662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10446548461914</t>
+    <t xml:space="preserve">8.23697757720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10446357727051</t>
   </si>
   <si>
     <t xml:space="preserve">8.10282897949219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09955883026123</t>
+    <t xml:space="preserve">8.09955596923828</t>
   </si>
   <si>
     <t xml:space="preserve">8.02993392944336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95865154266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08961009979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04153633117676</t>
+    <t xml:space="preserve">7.95865345001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08961200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04153728485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.16918087005615</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">8.15591812133789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08629512786865</t>
+    <t xml:space="preserve">8.08629417419434</t>
   </si>
   <si>
     <t xml:space="preserve">8.09955787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00009441375732</t>
+    <t xml:space="preserve">8.00009346008301</t>
   </si>
   <si>
     <t xml:space="preserve">7.85587453842163</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">7.80116987228394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96694135665894</t>
+    <t xml:space="preserve">7.96693992614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.03987884521484</t>
@@ -2621,172 +2621,172 @@
     <t xml:space="preserve">8.2122802734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24377918243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26864337921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29682445526123</t>
+    <t xml:space="preserve">8.24377822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26864433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2968225479126</t>
   </si>
   <si>
     <t xml:space="preserve">8.53304672241211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44187450408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46259307861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40871906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39214134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37971019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42944049835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49574851989746</t>
+    <t xml:space="preserve">8.44187355041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4625940322876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40872001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3921422958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37970924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42944145202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49574756622314</t>
   </si>
   <si>
     <t xml:space="preserve">8.36313343048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32997703552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37142181396484</t>
+    <t xml:space="preserve">8.32997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37142276763916</t>
   </si>
   <si>
     <t xml:space="preserve">8.48331642150879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7112512588501</t>
+    <t xml:space="preserve">8.71125030517578</t>
   </si>
   <si>
     <t xml:space="preserve">8.69881820678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68224239349365</t>
+    <t xml:space="preserve">8.68224143981934</t>
   </si>
   <si>
     <t xml:space="preserve">8.60764408111572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60350131988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45016193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40043163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45430755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52890300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50403881072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4708833694458</t>
+    <t xml:space="preserve">8.60350036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45016098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40042972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45430564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52890205383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50403785705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47088432312012</t>
   </si>
   <si>
     <t xml:space="preserve">8.41700839996338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37556457519531</t>
+    <t xml:space="preserve">8.37556552886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.05811500549316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18741703033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28687953948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88074111938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73154544830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64203071594238</t>
+    <t xml:space="preserve">8.18741607666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2868766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88074016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73154592514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64202928543091</t>
   </si>
   <si>
     <t xml:space="preserve">7.80282688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90891981124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93212938308716</t>
+    <t xml:space="preserve">7.9089207649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93212795257568</t>
   </si>
   <si>
     <t xml:space="preserve">7.78790807723999</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83598184585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90063333511353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0067253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98186016082764</t>
+    <t xml:space="preserve">7.83598232269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90063190460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00672435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98186063766479</t>
   </si>
   <si>
     <t xml:space="preserve">7.80448627471924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84095525741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13105487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76967191696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37679624557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27733373641968</t>
+    <t xml:space="preserve">7.84095430374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13105392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76967287063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37679672241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27733325958252</t>
   </si>
   <si>
     <t xml:space="preserve">7.29391050338745</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97563076019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77007627487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71868753433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75018310546875</t>
+    <t xml:space="preserve">6.97563171386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77007532119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71868705749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75018405914307</t>
   </si>
   <si>
     <t xml:space="preserve">6.57612419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45511102676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08378505706787</t>
+    <t xml:space="preserve">6.45511198043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08378553390503</t>
   </si>
   <si>
     <t xml:space="preserve">4.78248500823975</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">4.56200981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87903499603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97766757011414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71989440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85085344314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94534397125244</t>
+    <t xml:space="preserve">3.8790340423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97766804695129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71989512443542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85085368156433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94534349441528</t>
   </si>
   <si>
     <t xml:space="preserve">4.15918684005737</t>
@@ -2822,31 +2822,31 @@
     <t xml:space="preserve">4.26362276077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43436670303345</t>
+    <t xml:space="preserve">4.43436622619629</t>
   </si>
   <si>
     <t xml:space="preserve">4.46088981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70788764953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61505699157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59019088745117</t>
+    <t xml:space="preserve">4.70788812637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61505651473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59019136428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.62500286102295</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54543304443359</t>
+    <t xml:space="preserve">4.54543352127075</t>
   </si>
   <si>
     <t xml:space="preserve">4.75430393218994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7874584197998</t>
+    <t xml:space="preserve">4.78745794296265</t>
   </si>
   <si>
     <t xml:space="preserve">4.90681266784668</t>
@@ -2855,61 +2855,61 @@
     <t xml:space="preserve">5.13226127624512</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01456451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97809362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91178560256958</t>
+    <t xml:space="preserve">5.014564037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97809410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9117865562439</t>
   </si>
   <si>
     <t xml:space="preserve">4.69131088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77751207351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80735111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7791690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54045915603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68136501312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86702823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90515470504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686679840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99135589599609</t>
+    <t xml:space="preserve">4.77751159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80735063552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77916860580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54046010971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68136405944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.867027759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90515613555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8968677520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99135637283325</t>
   </si>
   <si>
     <t xml:space="preserve">5.28311252593994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29968976974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00627565383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24664306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0444016456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12065696716309</t>
+    <t xml:space="preserve">5.29968929290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00627517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24664258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04440355300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1206579208374</t>
   </si>
   <si>
     <t xml:space="preserve">5.16375780105591</t>
@@ -2921,22 +2921,22 @@
     <t xml:space="preserve">4.98141050338745</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7642502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79408931732178</t>
+    <t xml:space="preserve">4.76425123214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79408836364746</t>
   </si>
   <si>
     <t xml:space="preserve">5.15878438949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69960069656372</t>
+    <t xml:space="preserve">4.69960021972656</t>
   </si>
   <si>
     <t xml:space="preserve">4.85045099258423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.611741065979</t>
+    <t xml:space="preserve">4.61174058914185</t>
   </si>
   <si>
     <t xml:space="preserve">4.59847974777222</t>
@@ -2945,37 +2945,37 @@
     <t xml:space="preserve">4.64158010482788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71451902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72115087509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83718967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63494920730591</t>
+    <t xml:space="preserve">4.71451997756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72115039825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83718919754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63494873046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.84382009506226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04606008529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2980318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35273694992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63288974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7157735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61465454101562</t>
+    <t xml:space="preserve">5.04606056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29803228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35273599624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63288879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71577453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61465358734131</t>
   </si>
   <si>
     <t xml:space="preserve">5.53508424758911</t>
@@ -2984,19 +2984,19 @@
     <t xml:space="preserve">5.18365049362183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18862342834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1819920539856</t>
+    <t xml:space="preserve">5.18862295150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18199253082275</t>
   </si>
   <si>
     <t xml:space="preserve">5.1306037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12894582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04108667373657</t>
+    <t xml:space="preserve">5.12894630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04108715057373</t>
   </si>
   <si>
     <t xml:space="preserve">5.14220762252808</t>
@@ -3005,25 +3005,25 @@
     <t xml:space="preserve">4.8239278793335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88691997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76093435287476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8139820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70623016357422</t>
+    <t xml:space="preserve">4.88692045211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76093482971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81398105621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70623111724854</t>
   </si>
   <si>
     <t xml:space="preserve">4.85210943222046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76259183883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93002033233643</t>
+    <t xml:space="preserve">4.76259279251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93002128601074</t>
   </si>
   <si>
     <t xml:space="preserve">4.84547805786133</t>
@@ -3032,22 +3032,22 @@
     <t xml:space="preserve">4.76756572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59682178497314</t>
+    <t xml:space="preserve">4.59682130813599</t>
   </si>
   <si>
     <t xml:space="preserve">4.62168836593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67804908752441</t>
+    <t xml:space="preserve">4.67805004119873</t>
   </si>
   <si>
     <t xml:space="preserve">4.75761985778809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76590824127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89355039596558</t>
+    <t xml:space="preserve">4.76590776443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89355134963989</t>
   </si>
   <si>
     <t xml:space="preserve">4.78414297103882</t>
@@ -3062,55 +3062,55 @@
     <t xml:space="preserve">4.58024454116821</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49072885513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27191162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19234132766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0879054069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28185749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29346179962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.485755443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21389102935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2901463508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43602323532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41447401046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32164287567139</t>
+    <t xml:space="preserve">4.4907283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27191114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19234180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08790588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28185701370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29346132278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21389150619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29014587402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43602466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41447448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32164192199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.27688455581665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23875665664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19731426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10448265075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08624744415283</t>
+    <t xml:space="preserve">4.23875761032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19731473922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10448217391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08624887466431</t>
   </si>
   <si>
     <t xml:space="preserve">4.22383832931519</t>
@@ -3119,31 +3119,31 @@
     <t xml:space="preserve">4.1757640838623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13349342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05806636810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08293199539185</t>
+    <t xml:space="preserve">4.1334924697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05806684494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08293342590332</t>
   </si>
   <si>
     <t xml:space="preserve">4.07795906066895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00004720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96192049980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9892725944519</t>
+    <t xml:space="preserve">4.0000467300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96192026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98927211761475</t>
   </si>
   <si>
     <t xml:space="preserve">4.00087642669678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97601008415222</t>
+    <t xml:space="preserve">3.9760103225708</t>
   </si>
   <si>
     <t xml:space="preserve">3.83924984931946</t>
@@ -3152,25 +3152,25 @@
     <t xml:space="preserve">3.84422278404236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82598781585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77957224845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74724698066711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80112171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95943307876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96274900436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85334062576294</t>
+    <t xml:space="preserve">3.82598829269409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77957272529602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74724721908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80112218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95943331718445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96274852752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85334038734436</t>
   </si>
   <si>
     <t xml:space="preserve">3.60053968429565</t>
@@ -3179,34 +3179,34 @@
     <t xml:space="preserve">3.56075501441956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.530916929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45880603790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39747071266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53754734992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399430274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53174495697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44139957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52096962928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55578207969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6535861492157</t>
+    <t xml:space="preserve">3.53091621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45880579948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39747095108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53754663467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399406433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53174543380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44139981269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5209698677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55578184127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65358662605286</t>
   </si>
   <si>
     <t xml:space="preserve">3.58064746856689</t>
@@ -3215,112 +3215,112 @@
     <t xml:space="preserve">3.69005608558655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66436195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60302639007568</t>
+    <t xml:space="preserve">3.66436123847961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60302662849426</t>
   </si>
   <si>
     <t xml:space="preserve">3.51350998878479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60717105865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42730975151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5508086681366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62623405456543</t>
+    <t xml:space="preserve">3.60717129707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42730951309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55080914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62623453140259</t>
   </si>
   <si>
     <t xml:space="preserve">3.710777759552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61877489089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63783884048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67099213600159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57401633262634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47455430030823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37011861801147</t>
+    <t xml:space="preserve">3.61877536773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63783836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67099285125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57401657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47455382347107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3701183795929</t>
   </si>
   <si>
     <t xml:space="preserve">3.17285132408142</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37509155273438</t>
+    <t xml:space="preserve">3.37509202957153</t>
   </si>
   <si>
     <t xml:space="preserve">3.5516369342804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63535189628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19399881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17244815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57029819488525</t>
+    <t xml:space="preserve">3.63535213470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19399929046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17244863510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57029914855957</t>
   </si>
   <si>
     <t xml:space="preserve">4.63660669326782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64655351638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6763916015625</t>
+    <t xml:space="preserve">4.64655303955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67639207839966</t>
   </si>
   <si>
     <t xml:space="preserve">4.74601554870605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11402606964111</t>
+    <t xml:space="preserve">5.11402654647827</t>
   </si>
   <si>
     <t xml:space="preserve">5.21183109283447</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27316665649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19359636306763</t>
+    <t xml:space="preserve">5.27316617965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19359588623047</t>
   </si>
   <si>
     <t xml:space="preserve">5.180335521698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39324903488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73357486724854</t>
+    <t xml:space="preserve">5.39324855804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73357439041138</t>
   </si>
   <si>
     <t xml:space="preserve">5.67825031280518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60113286972046</t>
+    <t xml:space="preserve">5.6011323928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.61957359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43683624267578</t>
+    <t xml:space="preserve">5.43683671951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.52066135406494</t>
@@ -3329,22 +3329,22 @@
     <t xml:space="preserve">5.54748487472534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58101367950439</t>
+    <t xml:space="preserve">5.58101463317871</t>
   </si>
   <si>
     <t xml:space="preserve">5.80901575088501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70339727401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71178007125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71513319015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80231094360352</t>
+    <t xml:space="preserve">5.70339775085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7117805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71513366699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80231046676636</t>
   </si>
   <si>
     <t xml:space="preserve">5.70004463195801</t>
@@ -3359,34 +3359,34 @@
     <t xml:space="preserve">5.6665153503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.721839427948</t>
+    <t xml:space="preserve">5.72183990478516</t>
   </si>
   <si>
     <t xml:space="preserve">5.638014793396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49048471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47539615631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62795639038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58772039413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51227903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55251407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47874879837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67489814758301</t>
+    <t xml:space="preserve">5.4904842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47539567947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6279559135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58772087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51227855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55251502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47874927520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67489719390869</t>
   </si>
   <si>
     <t xml:space="preserve">5.9783411026001</t>
@@ -3401,28 +3401,28 @@
     <t xml:space="preserve">5.82913398742676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99678182601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91295862197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96492910385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65813302993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64304399490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4619836807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27254152297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1786584854126</t>
+    <t xml:space="preserve">5.99678230285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9129581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96492958068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65813255310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64304447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46198320388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27254104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17865896224976</t>
   </si>
   <si>
     <t xml:space="preserve">5.24739456176758</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">5.33792400360107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50054359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38989543914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38151264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60448455810547</t>
+    <t xml:space="preserve">5.50054311752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38989496231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3815131187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60448503494263</t>
   </si>
   <si>
     <t xml:space="preserve">5.6933388710022</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">5.80733966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92972278594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82410430908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89451742172241</t>
+    <t xml:space="preserve">5.92972326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82410478591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89451694488525</t>
   </si>
   <si>
     <t xml:space="preserve">5.90122318267822</t>
@@ -3467,22 +3467,22 @@
     <t xml:space="preserve">6.31196165084839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32202005386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17951917648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03534126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06551885604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29351997375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22813653945923</t>
+    <t xml:space="preserve">6.32201957702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17951965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03534078598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06551790237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29351949691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22813606262207</t>
   </si>
   <si>
     <t xml:space="preserve">6.44440364837646</t>
@@ -3491,16 +3491,16 @@
     <t xml:space="preserve">7.32958745956421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24743938446045</t>
+    <t xml:space="preserve">7.24743890762329</t>
   </si>
   <si>
     <t xml:space="preserve">7.41508722305298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53579378128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51902866363525</t>
+    <t xml:space="preserve">7.53579330444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51903009414673</t>
   </si>
   <si>
     <t xml:space="preserve">7.78559064865112</t>
@@ -3515,52 +3515,52 @@
     <t xml:space="preserve">8.00520992279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11082935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30697727203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31200790405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10579776763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12927055358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09741592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99682855606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81576681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75038433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61961889266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90294551849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69170665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97168159484863</t>
+    <t xml:space="preserve">8.1108283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30697822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31200695037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10579967498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12926864624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09741497039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99682712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81576776504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75038480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61961841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90294313430786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6917085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9716796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.01526927947998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09573936462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05718040466309</t>
+    <t xml:space="preserve">8.09574031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0571813583374</t>
   </si>
   <si>
     <t xml:space="preserve">8.10076904296875</t>
@@ -3578,73 +3578,73 @@
     <t xml:space="preserve">7.69506120681763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63973712921143</t>
+    <t xml:space="preserve">7.63973665237427</t>
   </si>
   <si>
     <t xml:space="preserve">7.62967777252197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99850416183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70679664611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68332576751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73864889144897</t>
+    <t xml:space="preserve">7.99850368499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70679521560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68332481384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73864984512329</t>
   </si>
   <si>
     <t xml:space="preserve">7.39497041702271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47041177749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46370553970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44358777999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70008993148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53914833068848</t>
+    <t xml:space="preserve">7.47041034698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46370601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44358825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70008945465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53914737701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.79229593276978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26420307159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50897169113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57602977752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63805961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98006343841553</t>
+    <t xml:space="preserve">7.26420450210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57603025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63806056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98006248474121</t>
   </si>
   <si>
     <t xml:space="preserve">8.12591648101807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20806407928467</t>
+    <t xml:space="preserve">8.20806503295898</t>
   </si>
   <si>
     <t xml:space="preserve">8.01359272003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28350639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19633007049561</t>
+    <t xml:space="preserve">8.2835054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19632911682129</t>
   </si>
   <si>
     <t xml:space="preserve">8.21477127075195</t>
@@ -3653,31 +3653,31 @@
     <t xml:space="preserve">8.12759399414062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90462064743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85600185394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92976713180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95869731903076</t>
+    <t xml:space="preserve">7.90462160110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85600233078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92976760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9586968421936</t>
   </si>
   <si>
     <t xml:space="preserve">7.80214309692383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82596635818481</t>
+    <t xml:space="preserve">7.82596683502197</t>
   </si>
   <si>
     <t xml:space="preserve">8.04548072814941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96039819717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93827629089355</t>
+    <t xml:space="preserve">7.96039772033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9382758140564</t>
   </si>
   <si>
     <t xml:space="preserve">8.15268611907959</t>
@@ -3686,16 +3686,16 @@
     <t xml:space="preserve">8.24628067016602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31604671478271</t>
+    <t xml:space="preserve">8.31604766845703</t>
   </si>
   <si>
     <t xml:space="preserve">8.1918249130249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20203590393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1714038848877</t>
+    <t xml:space="preserve">8.20203495025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17140579223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.11354827880859</t>
@@ -3704,106 +3704,106 @@
     <t xml:space="preserve">8.12546062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29052066802979</t>
+    <t xml:space="preserve">8.2905216217041</t>
   </si>
   <si>
     <t xml:space="preserve">8.14077663421631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13056468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94848680496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81575679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84468603134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92296266555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97571277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02506256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07100677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80384540557861</t>
+    <t xml:space="preserve">8.13056564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94848585128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81575632095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84468507766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92296171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9757137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02506160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07100772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80384492874146</t>
   </si>
   <si>
     <t xml:space="preserve">7.80554580688477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82086229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97060775756836</t>
+    <t xml:space="preserve">7.82086277008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97060871124268</t>
   </si>
   <si>
     <t xml:space="preserve">7.96550464630127</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02165985107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6438889503479</t>
+    <t xml:space="preserve">8.0216588973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64388751983643</t>
   </si>
   <si>
     <t xml:space="preserve">7.52987718582153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42607450485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65920400619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63197612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46861791610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59964561462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25420618057251</t>
+    <t xml:space="preserve">7.42607402801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65920352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63197660446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46861743927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59964418411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521329879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25420665740967</t>
   </si>
   <si>
     <t xml:space="preserve">7.00235939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12317752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26271533966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18103456497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26441717147827</t>
+    <t xml:space="preserve">7.12317848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26271486282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18103504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26441669464111</t>
   </si>
   <si>
     <t xml:space="preserve">7.47372198104858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40735721588135</t>
+    <t xml:space="preserve">7.40735626220703</t>
   </si>
   <si>
     <t xml:space="preserve">7.47031688690186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46691513061523</t>
+    <t xml:space="preserve">7.46691465377808</t>
   </si>
   <si>
     <t xml:space="preserve">7.29674816131592</t>
@@ -3812,148 +3812,148 @@
     <t xml:space="preserve">7.35800838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40565586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30865955352783</t>
+    <t xml:space="preserve">7.40565538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30865907669067</t>
   </si>
   <si>
     <t xml:space="preserve">7.28313541412354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48222923278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44139099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4856333732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49584245681763</t>
+    <t xml:space="preserve">7.48222970962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44139051437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48563385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49584293365479</t>
   </si>
   <si>
     <t xml:space="preserve">7.30185270309448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3341851234436</t>
+    <t xml:space="preserve">7.33418607711792</t>
   </si>
   <si>
     <t xml:space="preserve">6.99385166168213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93769693374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07042741775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09254884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15550899505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22187471389771</t>
+    <t xml:space="preserve">6.9376974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07042598724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09254837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15551090240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22187423706055</t>
   </si>
   <si>
     <t xml:space="preserve">7.33758783340454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25760936737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34269380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2252779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21166563034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14700078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09424924850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06362009048462</t>
+    <t xml:space="preserve">7.25760889053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34269332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22527885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21166467666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14700174331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0942497253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06361961364746</t>
   </si>
   <si>
     <t xml:space="preserve">7.30695867538452</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25590801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3767261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1401948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87473487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87303352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23038387298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28824090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32567691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57241725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53668308258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59794282913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73577737808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72557020187378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93997955322266</t>
+    <t xml:space="preserve">7.25590896606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37672662734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14019536972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8747353553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87303256988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23038339614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2882399559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32567644119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57241821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53668355941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59794330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73577880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72556734085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93997764587402</t>
   </si>
   <si>
     <t xml:space="preserve">7.67792129516602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79874038696289</t>
+    <t xml:space="preserve">7.79873991012573</t>
   </si>
   <si>
     <t xml:space="preserve">8.15609073638916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35007953643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21054267883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10333919525146</t>
+    <t xml:space="preserve">8.3500804901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21054363250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10333824157715</t>
   </si>
   <si>
     <t xml:space="preserve">8.14758205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40283107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35348415374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45898628234863</t>
+    <t xml:space="preserve">8.40283298492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35348510742188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45898818969727</t>
   </si>
   <si>
     <t xml:space="preserve">8.60618114471436</t>
@@ -3962,34 +3962,34 @@
     <t xml:space="preserve">8.43856716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39091873168945</t>
+    <t xml:space="preserve">8.3909215927124</t>
   </si>
   <si>
     <t xml:space="preserve">8.56363964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55513000488281</t>
+    <t xml:space="preserve">8.55513191223145</t>
   </si>
   <si>
     <t xml:space="preserve">8.42325115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19012546539307</t>
+    <t xml:space="preserve">8.19012260437012</t>
   </si>
   <si>
     <t xml:space="preserve">8.19352722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4147424697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38241195678711</t>
+    <t xml:space="preserve">8.41474342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38241100311279</t>
   </si>
   <si>
     <t xml:space="preserve">8.27520751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79336452484131</t>
+    <t xml:space="preserve">8.79336547851562</t>
   </si>
   <si>
     <t xml:space="preserve">9.03585147857666</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">9.27833938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23154354095459</t>
+    <t xml:space="preserve">9.23154449462891</t>
   </si>
   <si>
     <t xml:space="preserve">8.92524337768555</t>
@@ -4007,25 +4007,25 @@
     <t xml:space="preserve">8.83165264129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73380661010742</t>
+    <t xml:space="preserve">8.73380565643311</t>
   </si>
   <si>
     <t xml:space="preserve">8.71253490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52960586547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28882026672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07611179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26934623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21586036682129</t>
+    <t xml:space="preserve">8.5296049118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28881931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07611083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2693452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21585941314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.31247806549072</t>
@@ -4034,52 +4034,52 @@
     <t xml:space="preserve">8.20895862579346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62753486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69654607772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47225761413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78108549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70689725875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72932767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319543838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0174503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91911029815674</t>
+    <t xml:space="preserve">7.62753343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69654655456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47225713729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78108644485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70689821243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72932815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319639205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01745128631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91911125183105</t>
   </si>
   <si>
     <t xml:space="preserve">7.7603816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69309663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62408351898193</t>
+    <t xml:space="preserve">7.69309520721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62408494949341</t>
   </si>
   <si>
     <t xml:space="preserve">7.87942790985107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63616037368774</t>
+    <t xml:space="preserve">7.63616132736206</t>
   </si>
   <si>
     <t xml:space="preserve">7.85527276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78798675537109</t>
+    <t xml:space="preserve">7.78798723220825</t>
   </si>
   <si>
     <t xml:space="preserve">7.6137318611145</t>
@@ -4088,13 +4088,13 @@
     <t xml:space="preserve">7.86389970779419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86217546463013</t>
+    <t xml:space="preserve">7.86217498779297</t>
   </si>
   <si>
     <t xml:space="preserve">7.87597799301147</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96051645278931</t>
+    <t xml:space="preserve">7.96051549911499</t>
   </si>
   <si>
     <t xml:space="preserve">8.02435207366943</t>
@@ -4103,40 +4103,40 @@
     <t xml:space="preserve">8.0105504989624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94498920440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25899219512939</t>
+    <t xml:space="preserve">7.94498825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25899314880371</t>
   </si>
   <si>
     <t xml:space="preserve">8.37286376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4366979598999</t>
+    <t xml:space="preserve">8.43669700622559</t>
   </si>
   <si>
     <t xml:space="preserve">8.43842315673828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222759246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40909481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58162117004395</t>
+    <t xml:space="preserve">8.45222663879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40909385681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58162307739258</t>
   </si>
   <si>
     <t xml:space="preserve">8.65667343139648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6782398223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85076999664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06211853027344</t>
+    <t xml:space="preserve">8.67824077606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85076904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06211757659912</t>
   </si>
   <si>
     <t xml:space="preserve">9.25190162658691</t>
@@ -4145,13 +4145,13 @@
     <t xml:space="preserve">9.28640747070312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93703460693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49708366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88958930969238</t>
+    <t xml:space="preserve">8.93703365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49708461761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8895902633667</t>
   </si>
   <si>
     <t xml:space="preserve">9.5538272857666</t>
@@ -4160,10 +4160,10 @@
     <t xml:space="preserve">9.37698459625244</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83850193023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78242874145508</t>
+    <t xml:space="preserve">9.83850002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78243064880371</t>
   </si>
   <si>
     <t xml:space="preserve">9.65734577178955</t>
@@ -4172,70 +4172,70 @@
     <t xml:space="preserve">9.85144138336182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86006736755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7738037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87732124328613</t>
+    <t xml:space="preserve">9.86006832122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77380180358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87732028961182</t>
   </si>
   <si>
     <t xml:space="preserve">9.97652530670166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.080041885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92476749420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99809169769287</t>
+    <t xml:space="preserve">10.0800428390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92476654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99809074401855</t>
   </si>
   <si>
     <t xml:space="preserve">10.2266941070557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93770790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75223541259766</t>
+    <t xml:space="preserve">9.93770694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75223731994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.44599628448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52363586425781</t>
+    <t xml:space="preserve">9.5236349105835</t>
   </si>
   <si>
     <t xml:space="preserve">9.42443084716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32091331481934</t>
+    <t xml:space="preserve">9.32091426849365</t>
   </si>
   <si>
     <t xml:space="preserve">9.60990047454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95495891571045</t>
+    <t xml:space="preserve">9.95495986938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.86869430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3560914993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1447410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96358585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2618703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6241827011108</t>
+    <t xml:space="preserve">10.3560905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1447429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96358680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2618713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6241846084595</t>
   </si>
   <si>
     <t xml:space="preserve">10.9815101623535</t>
@@ -4244,88 +4244,88 @@
     <t xml:space="preserve">11.1540403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1497268676758</t>
+    <t xml:space="preserve">11.1497259140015</t>
   </si>
   <si>
     <t xml:space="preserve">10.8736791610718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5113668441772</t>
+    <t xml:space="preserve">10.5113677978516</t>
   </si>
   <si>
     <t xml:space="preserve">10.7356548309326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9081869125366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5724248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6371240615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606161117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9951210021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2927350997925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0123748779297</t>
+    <t xml:space="preserve">10.9081859588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5724239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6371231079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9606151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9951219558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2927360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0123739242554</t>
   </si>
   <si>
     <t xml:space="preserve">11.6845684051514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8829774856567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8657245635986</t>
+    <t xml:space="preserve">11.8829765319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8657236099243</t>
   </si>
   <si>
     <t xml:space="preserve">11.9821834564209</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9735555648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0727596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9390516281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9908084869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5299634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4135055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8146381378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9224681854248</t>
+    <t xml:space="preserve">11.9735546112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0727605819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9390497207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9908075332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5299644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4135074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8146371841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9224691390991</t>
   </si>
   <si>
     <t xml:space="preserve">12.9914808273315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9612865447998</t>
+    <t xml:space="preserve">12.9612874984741</t>
   </si>
   <si>
     <t xml:space="preserve">12.9310941696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5817222595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7233867645264</t>
+    <t xml:space="preserve">12.5817232131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7233877182007</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374578475952</t>
@@ -4334,16 +4334,16 @@
     <t xml:space="preserve">12.0813865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7758188247681</t>
+    <t xml:space="preserve">12.7758197784424</t>
   </si>
   <si>
     <t xml:space="preserve">12.2841091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8448295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6981801986694</t>
+    <t xml:space="preserve">12.8448305130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6981792449951</t>
   </si>
   <si>
     <t xml:space="preserve">12.6377935409546</t>
@@ -4352,79 +4352,79 @@
     <t xml:space="preserve">12.5385894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0598201751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.180591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5989761352539</t>
+    <t xml:space="preserve">12.0598211288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805896759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5989742279053</t>
   </si>
   <si>
     <t xml:space="preserve">12.2668561935425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7283725738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2718410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4486856460571</t>
+    <t xml:space="preserve">12.7283735275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.27184009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4486837387085</t>
   </si>
   <si>
     <t xml:space="preserve">13.3667335510254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0216732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.19420337677</t>
+    <t xml:space="preserve">13.021674156189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1942024230957</t>
   </si>
   <si>
     <t xml:space="preserve">13.4885787963867</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3040447235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5456962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9147653579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0861196517944</t>
+    <t xml:space="preserve">13.3040437698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5456972122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9147644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0861186981201</t>
   </si>
   <si>
     <t xml:space="preserve">14.253077507019</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7302303314209</t>
+    <t xml:space="preserve">13.7302312850952</t>
   </si>
   <si>
     <t xml:space="preserve">13.8356781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.86643409729</t>
+    <t xml:space="preserve">13.8664350509644</t>
   </si>
   <si>
     <t xml:space="preserve">13.8224983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9630966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0641479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0246067047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4094934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.005274772644</t>
+    <t xml:space="preserve">13.963095664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0641498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0246057510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4094924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0052738189697</t>
   </si>
   <si>
     <t xml:space="preserve">12.803165435791</t>
@@ -4433,31 +4433,31 @@
     <t xml:space="preserve">12.693323135376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3154678344727</t>
+    <t xml:space="preserve">12.3154668807983</t>
   </si>
   <si>
     <t xml:space="preserve">11.5641489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3927965164185</t>
+    <t xml:space="preserve">11.3927955627441</t>
   </si>
   <si>
     <t xml:space="preserve">11.6080865859985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6739892959595</t>
+    <t xml:space="preserve">11.6739912033081</t>
   </si>
   <si>
     <t xml:space="preserve">11.072057723999</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7381401062012</t>
+    <t xml:space="preserve">10.7381391525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.9402475357056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9578218460083</t>
+    <t xml:space="preserve">10.9578227996826</t>
   </si>
   <si>
     <t xml:space="preserve">11.2302303314209</t>
@@ -4466,37 +4466,37 @@
     <t xml:space="preserve">11.063271522522</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7820749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5799646377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9666090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0615139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75834846496582</t>
+    <t xml:space="preserve">10.782075881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5799655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9666109085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0615129470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75834941864014</t>
   </si>
   <si>
     <t xml:space="preserve">10.7469253540039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1423568725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2082624435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1116027832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5404243469238</t>
+    <t xml:space="preserve">11.1423559188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2082614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1116018295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.984185218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5404233932495</t>
   </si>
   <si>
     <t xml:space="preserve">10.7117767333984</t>
@@ -4508,13 +4508,13 @@
     <t xml:space="preserve">11.1819000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0676651000977</t>
+    <t xml:space="preserve">11.0676641464233</t>
   </si>
   <si>
     <t xml:space="preserve">10.8523750305176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.975396156311</t>
+    <t xml:space="preserve">10.9753971099854</t>
   </si>
   <si>
     <t xml:space="preserve">11.0940265655518</t>
@@ -4523,22 +4523,22 @@
     <t xml:space="preserve">11.4411268234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5861196517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9551868438721</t>
+    <t xml:space="preserve">11.5861186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9551858901978</t>
   </si>
   <si>
     <t xml:space="preserve">11.6344470977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6608104705811</t>
+    <t xml:space="preserve">11.6608114242554</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0896329879761</t>
+    <t xml:space="preserve">11.0896339416504</t>
   </si>
   <si>
     <t xml:space="preserve">11.3005285263062</t>
@@ -4553,19 +4553,19 @@
     <t xml:space="preserve">11.5685424804688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.542181968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3224973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6827793121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2829542160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2803182601929</t>
+    <t xml:space="preserve">11.5421810150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3224964141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6827783584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2829551696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2803192138672</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704769134521</t>
@@ -4577,19 +4577,19 @@
     <t xml:space="preserve">12.2188062667847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0913896560669</t>
+    <t xml:space="preserve">12.0913906097412</t>
   </si>
   <si>
     <t xml:space="preserve">12.0826034545898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0298776626587</t>
+    <t xml:space="preserve">12.029878616333</t>
   </si>
   <si>
     <t xml:space="preserve">12.4384899139404</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5527257919312</t>
+    <t xml:space="preserve">12.5527267456055</t>
   </si>
   <si>
     <t xml:space="preserve">12.1221466064453</t>
@@ -4604,34 +4604,34 @@
     <t xml:space="preserve">12.3286485671997</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5790872573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5219697952271</t>
+    <t xml:space="preserve">12.5790882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5219688415527</t>
   </si>
   <si>
     <t xml:space="preserve">12.5175762176514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2407751083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9288244247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9024620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7882270812988</t>
+    <t xml:space="preserve">12.2407760620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9288234710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9024629592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7882261276245</t>
   </si>
   <si>
     <t xml:space="preserve">12.126540184021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9622163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1994743347168</t>
+    <t xml:space="preserve">10.9622173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1994733810425</t>
   </si>
   <si>
     <t xml:space="preserve">11.537787437439</t>
@@ -4640,10 +4640,10 @@
     <t xml:space="preserve">11.8761014938354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6564159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4604587554932</t>
+    <t xml:space="preserve">11.6564178466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4604578018188</t>
   </si>
   <si>
     <t xml:space="preserve">12.7504415512085</t>
@@ -4664,16 +4664,16 @@
     <t xml:space="preserve">12.2451696395874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8163461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615148544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217948913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2117776870728</t>
+    <t xml:space="preserve">12.8163452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217939376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2117757797241</t>
   </si>
   <si>
     <t xml:space="preserve">13.1590538024902</t>
@@ -4682,61 +4682,61 @@
     <t xml:space="preserve">13.3216190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2205657958984</t>
+    <t xml:space="preserve">13.2205648422241</t>
   </si>
   <si>
     <t xml:space="preserve">13.5193338394165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8927974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534292221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8005304336548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1564168930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9982452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1959609985352</t>
+    <t xml:space="preserve">13.8927965164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534282684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8005294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1564178466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9982442855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1959600448608</t>
   </si>
   <si>
     <t xml:space="preserve">14.6265411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7539567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4551887512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3585262298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7653789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.055362701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9938526153564</t>
+    <t xml:space="preserve">14.7539577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4551877975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3585271835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7653799057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0553617477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9938516616821</t>
   </si>
   <si>
     <t xml:space="preserve">14.6572952270508</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7275953292847</t>
+    <t xml:space="preserve">14.727596282959</t>
   </si>
   <si>
     <t xml:space="preserve">14.3101949691772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4244327545166</t>
+    <t xml:space="preserve">14.4244337081909</t>
   </si>
   <si>
     <t xml:space="preserve">13.7851209640503</t>
@@ -4745,76 +4745,76 @@
     <t xml:space="preserve">14.6908102035522</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3578367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.446629524231</t>
+    <t xml:space="preserve">14.3578357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4466285705566</t>
   </si>
   <si>
     <t xml:space="preserve">14.5265426635742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1314144134521</t>
+    <t xml:space="preserve">14.1314134597778</t>
   </si>
   <si>
     <t xml:space="preserve">14.54430103302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8417587280273</t>
+    <t xml:space="preserve">14.841757774353</t>
   </si>
   <si>
     <t xml:space="preserve">14.4954652786255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2557239532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.038182258606</t>
+    <t xml:space="preserve">14.2557249069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0381813049316</t>
   </si>
   <si>
     <t xml:space="preserve">13.9138708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6119747161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7806825637817</t>
+    <t xml:space="preserve">13.6119756698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7806816101074</t>
   </si>
   <si>
     <t xml:space="preserve">13.6608104705811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5276193618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9893455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.015983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7451629638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6474924087524</t>
+    <t xml:space="preserve">13.5276203155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9893445968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0159826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7451639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6474914550781</t>
   </si>
   <si>
     <t xml:space="preserve">13.949387550354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1402950286865</t>
+    <t xml:space="preserve">14.1402940750122</t>
   </si>
   <si>
     <t xml:space="preserve">14.4643888473511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.721887588501</t>
+    <t xml:space="preserve">14.7218885421753</t>
   </si>
   <si>
     <t xml:space="preserve">14.7796039581299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6686134338379</t>
+    <t xml:space="preserve">14.6686124801636</t>
   </si>
   <si>
     <t xml:space="preserve">14.7130088806152</t>
@@ -4823,25 +4823,25 @@
     <t xml:space="preserve">14.4599475860596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9349889755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4199924468994</t>
+    <t xml:space="preserve">14.9349908828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4199905395508</t>
   </si>
   <si>
     <t xml:space="preserve">13.4033107757568</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7940006256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0071029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0603799819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0692586898804</t>
+    <t xml:space="preserve">13.793999671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0071039199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0603790283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0692596435547</t>
   </si>
   <si>
     <t xml:space="preserve">14.237964630127</t>
@@ -4850,37 +4850,37 @@
     <t xml:space="preserve">14.4421892166138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3445177078247</t>
+    <t xml:space="preserve">14.3445167541504</t>
   </si>
   <si>
     <t xml:space="preserve">14.2290849685669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6597328186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2679653167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5176630020142</t>
+    <t xml:space="preserve">14.6597318649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2679643630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5176639556885</t>
   </si>
   <si>
     <t xml:space="preserve">14.6952486038208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4244318008423</t>
+    <t xml:space="preserve">14.424430847168</t>
   </si>
   <si>
     <t xml:space="preserve">14.2424049377441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.26904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2956819534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6197748184204</t>
+    <t xml:space="preserve">14.2690439224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2956809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6197757720947</t>
   </si>
   <si>
     <t xml:space="preserve">14.3977928161621</t>
@@ -4889,25 +4889,25 @@
     <t xml:space="preserve">14.4288702011108</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1180944442749</t>
+    <t xml:space="preserve">14.1180953979492</t>
   </si>
   <si>
     <t xml:space="preserve">13.6297330856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5498199462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4388294219971</t>
+    <t xml:space="preserve">13.5498189926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4388284683228</t>
   </si>
   <si>
     <t xml:space="preserve">13.540940284729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8872327804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1225357055664</t>
+    <t xml:space="preserve">13.8872337341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1225337982178</t>
   </si>
   <si>
     <t xml:space="preserve">14.0825777053833</t>
@@ -4916,10 +4916,10 @@
     <t xml:space="preserve">14.3800344467163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4011554718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6641702651978</t>
+    <t xml:space="preserve">15.4011516571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6641712188721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4377508163452</t>
@@ -4928,37 +4928,37 @@
     <t xml:space="preserve">13.971586227417</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2246475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9227504730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2646045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3267593383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3711557388306</t>
+    <t xml:space="preserve">14.2246465682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9227495193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2646036148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3267583847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3711547851562</t>
   </si>
   <si>
     <t xml:space="preserve">14.4732666015625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5487413406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0026636123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7140855789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9105100631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0969762802124</t>
+    <t xml:space="preserve">14.5487403869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.00266456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7140865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9105091094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0969743728638</t>
   </si>
   <si>
     <t xml:space="preserve">11.9249067306519</t>
@@ -4967,16 +4967,16 @@
     <t xml:space="preserve">11.9559841156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7384424209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7695188522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1646480560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0358991622925</t>
+    <t xml:space="preserve">11.7384414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7695178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.164647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0358982086182</t>
   </si>
   <si>
     <t xml:space="preserve">11.7650785446167</t>
@@ -4991,16 +4991,16 @@
     <t xml:space="preserve">11.8361129760742</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7739582061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.609691619873</t>
+    <t xml:space="preserve">11.7739591598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6096906661987</t>
   </si>
   <si>
     <t xml:space="preserve">11.631890296936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9826211929321</t>
+    <t xml:space="preserve">11.9826221466064</t>
   </si>
   <si>
     <t xml:space="preserve">11.6851644515991</t>
@@ -5024,16 +5024,16 @@
     <t xml:space="preserve">11.8405523300171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7828378677368</t>
+    <t xml:space="preserve">11.7828388214111</t>
   </si>
   <si>
     <t xml:space="preserve">11.6540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6363296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5874938964844</t>
+    <t xml:space="preserve">11.6363277435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5874929428101</t>
   </si>
   <si>
     <t xml:space="preserve">11.5031394958496</t>
@@ -5045,22 +5045,22 @@
     <t xml:space="preserve">10.9659423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8949069976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7439603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0280961990356</t>
+    <t xml:space="preserve">10.894907951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7439594268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.02809715271</t>
   </si>
   <si>
     <t xml:space="preserve">11.1168899536133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0991306304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8771476745605</t>
+    <t xml:space="preserve">11.0991315841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8771486282349</t>
   </si>
   <si>
     <t xml:space="preserve">10.7528371810913</t>
@@ -5072,7 +5072,7 @@
     <t xml:space="preserve">10.8460712432861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7705965042114</t>
+    <t xml:space="preserve">10.7705984115601</t>
   </si>
   <si>
     <t xml:space="preserve">10.9171056747437</t>
@@ -5084,7 +5084,7 @@
     <t xml:space="preserve">11.071325302124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2311172485352</t>
+    <t xml:space="preserve">11.2311182022095</t>
   </si>
   <si>
     <t xml:space="preserve">11.2585115432739</t>
@@ -5099,13 +5099,13 @@
     <t xml:space="preserve">11.1489391326904</t>
   </si>
   <si>
-    <t xml:space="preserve">10.847617149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6558666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8795747756958</t>
+    <t xml:space="preserve">10.8476161956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6558656692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8795757293701</t>
   </si>
   <si>
     <t xml:space="preserve">11.2722082138062</t>
@@ -5114,7 +5114,7 @@
     <t xml:space="preserve">11.3452558517456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6054878234863</t>
+    <t xml:space="preserve">11.6054887771606</t>
   </si>
   <si>
     <t xml:space="preserve">11.696798324585</t>
@@ -5126,7 +5126,7 @@
     <t xml:space="preserve">11.7104940414429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6420135498047</t>
+    <t xml:space="preserve">11.6420125961304</t>
   </si>
   <si>
     <t xml:space="preserve">11.9205083847046</t>
@@ -5141,7 +5141,7 @@
     <t xml:space="preserve">11.4274339675903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7972383499146</t>
+    <t xml:space="preserve">11.7972393035889</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374464035034</t>
@@ -5162,10 +5162,10 @@
     <t xml:space="preserve">12.1853075027466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5231533050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5185871124268</t>
+    <t xml:space="preserve">12.523154258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5185880661011</t>
   </si>
   <si>
     <t xml:space="preserve">12.5870704650879</t>
@@ -5174,31 +5174,31 @@
     <t xml:space="preserve">12.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305198669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4501056671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4227123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7696905136108</t>
+    <t xml:space="preserve">12.1305208206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4501066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4227113723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7696895599365</t>
   </si>
   <si>
     <t xml:space="preserve">13.0025300979614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.016227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9568748474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9660062789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1577558517456</t>
+    <t xml:space="preserve">13.0162267684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9568758010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.966007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1577568054199</t>
   </si>
   <si>
     <t xml:space="preserve">13.1668882369995</t>
@@ -5213,25 +5213,25 @@
     <t xml:space="preserve">13.7330093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6553955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6143054962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7010498046875</t>
+    <t xml:space="preserve">13.6553964614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6143064498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7010507583618</t>
   </si>
   <si>
     <t xml:space="preserve">13.6964855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8151874542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7695331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6462650299072</t>
+    <t xml:space="preserve">13.8151893615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7695341110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6462640762329</t>
   </si>
   <si>
     <t xml:space="preserve">13.3632049560547</t>
@@ -5243,16 +5243,16 @@
     <t xml:space="preserve">13.5823488235474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6371335983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0708560943604</t>
+    <t xml:space="preserve">13.637134552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0708570480347</t>
   </si>
   <si>
     <t xml:space="preserve">14.0845527648926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0434637069702</t>
+    <t xml:space="preserve">14.0434627532959</t>
   </si>
   <si>
     <t xml:space="preserve">14.0480289459229</t>
@@ -5264,7 +5264,7 @@
     <t xml:space="preserve">13.9658498764038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9475889205933</t>
+    <t xml:space="preserve">13.9475879669189</t>
   </si>
   <si>
     <t xml:space="preserve">13.9247608184814</t>
@@ -5279,22 +5279,22 @@
     <t xml:space="preserve">13.6736583709717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8380165100098</t>
+    <t xml:space="preserve">13.8380155563354</t>
   </si>
   <si>
     <t xml:space="preserve">13.9612846374512</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9293270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4773416519165</t>
+    <t xml:space="preserve">13.9293251037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4773426055908</t>
   </si>
   <si>
     <t xml:space="preserve">13.6097412109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.550389289856</t>
+    <t xml:space="preserve">13.5503902435303</t>
   </si>
   <si>
     <t xml:space="preserve">13.760401725769</t>
@@ -5306,10 +5306,10 @@
     <t xml:space="preserve">13.7375755310059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8471460342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7421407699585</t>
+    <t xml:space="preserve">13.847146987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7421417236328</t>
   </si>
   <si>
     <t xml:space="preserve">14.0936832427979</t>
@@ -5327,7 +5327,7 @@
     <t xml:space="preserve">13.3951625823975</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3860321044922</t>
+    <t xml:space="preserve">13.3860311508179</t>
   </si>
   <si>
     <t xml:space="preserve">13.4316873550415</t>
@@ -5336,13 +5336,13 @@
     <t xml:space="preserve">13.4362525939941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7740993499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6827878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2125434875488</t>
+    <t xml:space="preserve">13.7740983963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.682788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2125425338745</t>
   </si>
   <si>
     <t xml:space="preserve">13.3084182739258</t>
@@ -5351,31 +5351,31 @@
     <t xml:space="preserve">13.0116605758667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3586397171021</t>
+    <t xml:space="preserve">13.3586387634277</t>
   </si>
   <si>
     <t xml:space="preserve">13.8836708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0069379806519</t>
+    <t xml:space="preserve">14.0069389343262</t>
   </si>
   <si>
     <t xml:space="preserve">13.9567184448242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343332290649</t>
+    <t xml:space="preserve">14.0343322753906</t>
   </si>
   <si>
     <t xml:space="preserve">14.3950071334839</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2945642471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5045776367188</t>
+    <t xml:space="preserve">14.2945652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4954462051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5045785903931</t>
   </si>
   <si>
     <t xml:space="preserve">14.2671728134155</t>
@@ -5384,13 +5384,13 @@
     <t xml:space="preserve">13.9338912963867</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0571594238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0982484817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7969255447388</t>
+    <t xml:space="preserve">14.0571584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0982494354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7969245910645</t>
   </si>
   <si>
     <t xml:space="preserve">14.9383001327515</t>
@@ -5399,13 +5399,13 @@
     <t xml:space="preserve">14.8999509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2542314529419</t>
+    <t xml:space="preserve">15.2542324066162</t>
   </si>
   <si>
     <t xml:space="preserve">14.7830743789673</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3228721618652</t>
+    <t xml:space="preserve">14.3228712081909</t>
   </si>
   <si>
     <t xml:space="preserve">14.585844039917</t>
@@ -5417,7 +5417,7 @@
     <t xml:space="preserve">14.9063415527344</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7008953094482</t>
+    <t xml:space="preserve">14.7008943557739</t>
   </si>
   <si>
     <t xml:space="preserve">14.7191572189331</t>
@@ -5432,13 +5432,13 @@
     <t xml:space="preserve">14.5487966537476</t>
   </si>
   <si>
-    <t xml:space="preserve">14.373064994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1788339614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2620754241943</t>
+    <t xml:space="preserve">14.3730640411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1788349151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2620763778687</t>
   </si>
   <si>
     <t xml:space="preserve">14.3961868286133</t>
@@ -5447,10 +5447,10 @@
     <t xml:space="preserve">14.2990713119507</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1834583282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5672960281372</t>
+    <t xml:space="preserve">14.1834592819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5672950744629</t>
   </si>
   <si>
     <t xml:space="preserve">14.8771381378174</t>
@@ -5462,7 +5462,7 @@
     <t xml:space="preserve">14.6921577453613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4331836700439</t>
+    <t xml:space="preserve">14.4331827163696</t>
   </si>
   <si>
     <t xml:space="preserve">14.5626697540283</t>
@@ -5471,22 +5471,22 @@
     <t xml:space="preserve">14.3453168869019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1094655990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2019557952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.46555519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6274127960205</t>
+    <t xml:space="preserve">14.1094646453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2019567489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4655561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6274137496948</t>
   </si>
   <si>
     <t xml:space="preserve">14.729154586792</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8725156784058</t>
+    <t xml:space="preserve">14.8725147247314</t>
   </si>
   <si>
     <t xml:space="preserve">14.7707748413086</t>
@@ -5495,13 +5495,13 @@
     <t xml:space="preserve">14.8401432037354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7615261077881</t>
+    <t xml:space="preserve">14.7615251541138</t>
   </si>
   <si>
     <t xml:space="preserve">14.7014064788818</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6135416030884</t>
+    <t xml:space="preserve">14.6135406494141</t>
   </si>
   <si>
     <t xml:space="preserve">14.4378070831299</t>
@@ -5519,13 +5519,13 @@
     <t xml:space="preserve">13.6608858108521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6007661819458</t>
+    <t xml:space="preserve">13.6007671356201</t>
   </si>
   <si>
     <t xml:space="preserve">13.6192646026611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4712781906128</t>
+    <t xml:space="preserve">13.4712791442871</t>
   </si>
   <si>
     <t xml:space="preserve">13.4019107818604</t>
@@ -5537,7 +5537,7 @@
     <t xml:space="preserve">13.42041015625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3464164733887</t>
+    <t xml:space="preserve">13.346417427063</t>
   </si>
   <si>
     <t xml:space="preserve">13.6793842315674</t>
@@ -5558,7 +5558,7 @@
     <t xml:space="preserve">13.5822687149048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6100168228149</t>
+    <t xml:space="preserve">13.6100158691406</t>
   </si>
   <si>
     <t xml:space="preserve">13.8921127319336</t>
@@ -5567,7 +5567,7 @@
     <t xml:space="preserve">13.438907623291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6886329650879</t>
+    <t xml:space="preserve">13.6886320114136</t>
   </si>
   <si>
     <t xml:space="preserve">13.4759044647217</t>
@@ -5576,7 +5576,7 @@
     <t xml:space="preserve">13.6377620697021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7903718948364</t>
+    <t xml:space="preserve">13.7903728485107</t>
   </si>
   <si>
     <t xml:space="preserve">13.7071304321289</t>
@@ -5588,40 +5588,40 @@
     <t xml:space="preserve">13.8366174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9522323608398</t>
+    <t xml:space="preserve">13.9522314071655</t>
   </si>
   <si>
     <t xml:space="preserve">13.8042469024658</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8967361450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9095115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1869831085205</t>
+    <t xml:space="preserve">13.8967370986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9095125198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1869840621948</t>
   </si>
   <si>
     <t xml:space="preserve">15.3303451538086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4320831298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3395919799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2378540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731100082397</t>
+    <t xml:space="preserve">15.4320840835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3395929336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2378549575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731109619141</t>
   </si>
   <si>
     <t xml:space="preserve">15.7141799926758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8899145126343</t>
+    <t xml:space="preserve">15.8899126052856</t>
   </si>
   <si>
     <t xml:space="preserve">15.963906288147</t>
@@ -5642,7 +5642,7 @@
     <t xml:space="preserve">16.5281009674072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4078617095947</t>
+    <t xml:space="preserve">16.4078598022461</t>
   </si>
   <si>
     <t xml:space="preserve">16.352367401123</t>
@@ -5657,7 +5657,7 @@
     <t xml:space="preserve">16.78244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8888111114502</t>
+    <t xml:space="preserve">16.8888130187988</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
@@ -5666,7 +5666,7 @@
     <t xml:space="preserve">16.9350566864014</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0182991027832</t>
+    <t xml:space="preserve">17.0183010101318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9396839141846</t>
@@ -5675,7 +5675,7 @@
     <t xml:space="preserve">17.2032814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2402782440186</t>
+    <t xml:space="preserve">17.2402763366699</t>
   </si>
   <si>
     <t xml:space="preserve">17.0599212646484</t>
@@ -5690,7 +5690,7 @@
     <t xml:space="preserve">17.1107902526855</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9766788482666</t>
+    <t xml:space="preserve">16.976676940918</t>
   </si>
   <si>
     <t xml:space="preserve">17.0414218902588</t>
@@ -5699,16 +5699,16 @@
     <t xml:space="preserve">16.5096015930176</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5974674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3708648681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.338493347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2182540893555</t>
+    <t xml:space="preserve">16.597469329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3708667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3384952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2182559967041</t>
   </si>
   <si>
     <t xml:space="preserve">16.1396369934082</t>
@@ -5717,10 +5717,10 @@
     <t xml:space="preserve">16.0471458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7800226211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6967830657959</t>
+    <t xml:space="preserve">14.7800235748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6967821121216</t>
   </si>
   <si>
     <t xml:space="preserve">14.4979267120361</t>
@@ -5729,7 +5729,7 @@
     <t xml:space="preserve">14.4054355621338</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4239349365234</t>
+    <t xml:space="preserve">14.4239339828491</t>
   </si>
   <si>
     <t xml:space="preserve">14.6782836914062</t>
@@ -5750,7 +5750,7 @@
     <t xml:space="preserve">14.9326343536377</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8632650375366</t>
+    <t xml:space="preserve">14.8632659912109</t>
   </si>
   <si>
     <t xml:space="preserve">14.9002618789673</t>
@@ -6663,6 +6663,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.7049999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7550001144409</t>
   </si>
 </sst>
 </file>
@@ -71637,7 +71640,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6500347222</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>3363067</v>
@@ -71658,6 +71661,32 @@
         <v>2216</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6525462963</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>1680929</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>14.8450002670288</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>14.6450004577637</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>14.8199996948242</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>14.7550001144409</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>2217</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2218" uniqueCount="2218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2219" uniqueCount="2219">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,79 +44,79 @@
     <t xml:space="preserve">TEN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88865041732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69909143447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48036623001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19602489471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11582565307617</t>
+    <t xml:space="preserve">7.88865232467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69908952713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48036575317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19602537155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11582660675049</t>
   </si>
   <si>
     <t xml:space="preserve">7.07937240600586</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1231164932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07208061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62734365463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56901597976685</t>
+    <t xml:space="preserve">7.12311744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07208156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62734413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56901502609253</t>
   </si>
   <si>
     <t xml:space="preserve">6.77680397033691</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39403676986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63463354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80596685409546</t>
+    <t xml:space="preserve">6.3940372467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63463306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80596828460693</t>
   </si>
   <si>
     <t xml:space="preserve">6.78044939041138</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88981103897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91168308258057</t>
+    <t xml:space="preserve">6.88981008529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91168260574341</t>
   </si>
   <si>
     <t xml:space="preserve">6.82783889770508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49246168136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5143346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03562593460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43413543701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29925727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.802321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95542812347412</t>
+    <t xml:space="preserve">6.49246215820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51433515548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03562784194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43413591384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29925584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80232191085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95542764663696</t>
   </si>
   <si>
     <t xml:space="preserve">6.74034976959229</t>
@@ -125,241 +125,241 @@
     <t xml:space="preserve">7.14863443374634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06114625930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8314847946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11947202682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86064863204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54349756240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55443429946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16686344146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3272590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50223684310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45120429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61160039901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91781234741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00530433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71367263793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85948848724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58972930908203</t>
+    <t xml:space="preserve">7.0611457824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148431777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11947154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8606481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55443334579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16686201095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32726049423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50223827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45120477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61160087585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91781568527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00530529022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71367120742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85948944091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5897274017334</t>
   </si>
   <si>
     <t xml:space="preserve">7.82303428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73554563522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96155834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81574296951294</t>
+    <t xml:space="preserve">7.73554468154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96156072616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81574392318726</t>
   </si>
   <si>
     <t xml:space="preserve">7.77928972244263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.954270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7209644317627</t>
+    <t xml:space="preserve">7.95426797866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72096300125122</t>
   </si>
   <si>
     <t xml:space="preserve">7.66992712020874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98343276977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032369613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53140258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263628005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64076471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07821273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11466693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17299365997314</t>
+    <t xml:space="preserve">7.98342990875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53140068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66263675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64076519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07821178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11466598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17299270629883</t>
   </si>
   <si>
     <t xml:space="preserve">8.4208812713623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41358947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45004558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69792938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82916450500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8656177520752</t>
+    <t xml:space="preserve">8.41358757019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45004177093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69793033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82916641235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86561870574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.91665458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63960456848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8000020980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80729389190674</t>
+    <t xml:space="preserve">8.63960552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80000114440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80729293823242</t>
   </si>
   <si>
     <t xml:space="preserve">8.58856868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47191524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01988506317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97614002227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39900875091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2459020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21673679351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29693794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30422878265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4573335647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64689445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67605876922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3917179107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56669521331787</t>
+    <t xml:space="preserve">8.47191715240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0198860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97614192962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39900684356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24590301513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21673774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29693603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30422782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45733451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64689636230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67605972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39171600341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56669616699219</t>
   </si>
   <si>
     <t xml:space="preserve">8.62655067443848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73129653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75374221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95575141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97819709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98567771911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91086006164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80611515045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67892265319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6489953994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0829439163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69645214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52436923980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4944429397583</t>
+    <t xml:space="preserve">8.73129749298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75374126434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95575332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97819519042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98567867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91086101531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80611324310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67892551422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64899635314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08294105529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53185081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69645309448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52437019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49444103240967</t>
   </si>
   <si>
     <t xml:space="preserve">9.28495121002197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15776062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34480667114258</t>
+    <t xml:space="preserve">9.1577615737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34480571746826</t>
   </si>
   <si>
     <t xml:space="preserve">9.17272567749023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40466117858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66652488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42710781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8011999130249</t>
+    <t xml:space="preserve">9.40465927124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66652584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42710876464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80119800567627</t>
   </si>
   <si>
     <t xml:space="preserve">9.30739688873291</t>
@@ -371,55 +371,55 @@
     <t xml:space="preserve">9.14279842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61415100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73386001586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86853504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83112621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59918785095215</t>
+    <t xml:space="preserve">9.6141529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73386383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86853408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83112716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59918880462646</t>
   </si>
   <si>
     <t xml:space="preserve">9.32236003875732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39718055725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50940799713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65904331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74882507324219</t>
+    <t xml:space="preserve">9.39717864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50940704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65904426574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74882698059082</t>
   </si>
   <si>
     <t xml:space="preserve">9.4794807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59170627593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21761703491211</t>
+    <t xml:space="preserve">9.59170532226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21761512756348</t>
   </si>
   <si>
     <t xml:space="preserve">9.37473392486572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18768882751465</t>
+    <t xml:space="preserve">9.18768787384033</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16524219512939</t>
+    <t xml:space="preserve">9.16524124145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.0979061126709</t>
@@ -434,133 +434,133 @@
     <t xml:space="preserve">8.7088508605957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57417774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00064277648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19517230987549</t>
+    <t xml:space="preserve">8.57417964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74625968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00064182281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19517135620117</t>
   </si>
   <si>
     <t xml:space="preserve">9.38969802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36725234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48696231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70393371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65156173706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62911605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51689052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45703506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09042358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22509670257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2999153137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10538768768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85848712921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66396045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71633148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88093376159668</t>
+    <t xml:space="preserve">9.36725330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48696136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70393466949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65156078338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62911701202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51688957214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45703411102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09042453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22509574890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29991626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10538959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85848999023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66395950317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71633243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88093280792236</t>
   </si>
   <si>
     <t xml:space="preserve">8.76870441436768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67144393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69388675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90337753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7013692855835</t>
+    <t xml:space="preserve">8.67144203186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69388866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9033784866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70136833190918</t>
   </si>
   <si>
     <t xml:space="preserve">8.44698715209961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55921173095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35977077484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50192642211914</t>
+    <t xml:space="preserve">8.55921268463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35976982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50192356109619</t>
   </si>
   <si>
     <t xml:space="preserve">9.64407920837402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7637882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7413444519043</t>
+    <t xml:space="preserve">9.76379013061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74134349822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.95083522796631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63660049438477</t>
+    <t xml:space="preserve">9.6365966796875</t>
   </si>
   <si>
     <t xml:space="preserve">9.83860874176025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81616306304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9433536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0406150817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99572372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0106906890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96579742431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0630617141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77127075195312</t>
+    <t xml:space="preserve">9.81616115570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94335460662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0406160354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0106887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96579837799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.063060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77127170562744</t>
   </si>
   <si>
     <t xml:space="preserve">9.89846134185791</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">9.86105251312256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29243183135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2800340652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6765737533569</t>
+    <t xml:space="preserve">9.2924337387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2800331115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6765747070312</t>
   </si>
   <si>
     <t xml:space="preserve">10.6167192459106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8112459182739</t>
+    <t xml:space="preserve">10.8112449645996</t>
   </si>
   <si>
     <t xml:space="preserve">10.9384365081787</t>
@@ -590,49 +590,49 @@
     <t xml:space="preserve">10.9309558868408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9159917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7214622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1216297149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8045167922974</t>
+    <t xml:space="preserve">10.9159898757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7214660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1216306686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8045177459717</t>
   </si>
   <si>
     <t xml:space="preserve">11.03102684021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0687789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8347196578979</t>
+    <t xml:space="preserve">11.0687780380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8347187042236</t>
   </si>
   <si>
     <t xml:space="preserve">10.6761617660522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.378342628479</t>
+    <t xml:space="preserve">11.3783407211304</t>
   </si>
   <si>
     <t xml:space="preserve">11.8464622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7407579421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0352210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1937761306763</t>
+    <t xml:space="preserve">11.740758895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0352182388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1937770843506</t>
   </si>
   <si>
     <t xml:space="preserve">12.0805215835571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2239770889282</t>
+    <t xml:space="preserve">12.2239789962769</t>
   </si>
   <si>
     <t xml:space="preserve">12.556191444397</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">12.3749847412109</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2919330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4202880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.314582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3674345016479</t>
+    <t xml:space="preserve">12.2919321060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4202871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3145809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3674335479736</t>
   </si>
   <si>
     <t xml:space="preserve">12.5410928726196</t>
@@ -659,37 +659,37 @@
     <t xml:space="preserve">12.4504880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939455032349</t>
+    <t xml:space="preserve">12.5939435958862</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280038833618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9790096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0016632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8129043579102</t>
+    <t xml:space="preserve">12.9790134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0016622543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8129034042358</t>
   </si>
   <si>
     <t xml:space="preserve">13.0243148803711</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9714593887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9488105773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8808546066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8657560348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7751522064209</t>
+    <t xml:space="preserve">12.9714612960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9488096237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8808555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.865758895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7751541137695</t>
   </si>
   <si>
     <t xml:space="preserve">12.6769990921021</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">12.8204545974731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7600517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5335426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7676019668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8582077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6996488571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6618976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9865627288818</t>
+    <t xml:space="preserve">12.7600507736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.533540725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7676010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8582067489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.699649810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6618967056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9865617752075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0092124938965</t>
@@ -725,31 +725,31 @@
     <t xml:space="preserve">12.8506555557251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2164297103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2088785171509</t>
+    <t xml:space="preserve">12.2164287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2088775634766</t>
   </si>
   <si>
     <t xml:space="preserve">12.1258239746094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2843818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1182737350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1484756469727</t>
+    <t xml:space="preserve">12.2843809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1182727813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.148476600647</t>
   </si>
   <si>
     <t xml:space="preserve">11.8766622543335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0729713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.15602684021</t>
+    <t xml:space="preserve">12.0729703903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560249328613</t>
   </si>
   <si>
     <t xml:space="preserve">12.2541790008545</t>
@@ -758,28 +758,28 @@
     <t xml:space="preserve">11.974817276001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8540115356445</t>
+    <t xml:space="preserve">11.8540134429932</t>
   </si>
   <si>
     <t xml:space="preserve">12.1862268447876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2390794754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7860593795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7256574630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9068651199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6652545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5142478942871</t>
+    <t xml:space="preserve">12.2390785217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.786060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7256565093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9068641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6652536392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5142488479614</t>
   </si>
   <si>
     <t xml:space="preserve">11.5444498062134</t>
@@ -791,37 +791,37 @@
     <t xml:space="preserve">11.0989809036255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1140794754028</t>
+    <t xml:space="preserve">11.1140804290771</t>
   </si>
   <si>
     <t xml:space="preserve">11.1593818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0763301849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3330402374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.408543586731</t>
+    <t xml:space="preserve">11.0763282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3330411911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.408540725708</t>
   </si>
   <si>
     <t xml:space="preserve">11.4991474151611</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2952909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1442823410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1669340133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2424354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.993275642395</t>
+    <t xml:space="preserve">11.2952890396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1442842483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1669330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2424364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9932765960693</t>
   </si>
   <si>
     <t xml:space="preserve">11.8389120101929</t>
@@ -830,22 +830,22 @@
     <t xml:space="preserve">11.7634077072144</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1333751678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0427732467651</t>
+    <t xml:space="preserve">12.1333770751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0427713394165</t>
   </si>
   <si>
     <t xml:space="preserve">12.2013263702393</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1786756515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9370679855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3858909606934</t>
+    <t xml:space="preserve">12.1786766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.937068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.385892868042</t>
   </si>
   <si>
     <t xml:space="preserve">11.4840469360352</t>
@@ -854,49 +854,49 @@
     <t xml:space="preserve">11.2801885604858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3481397628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3556909561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3405914306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8724708557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8573703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9026718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7894172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949550628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6535091400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6459617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6610612869263</t>
+    <t xml:space="preserve">11.3481407165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.35569190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3405904769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066967010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8724718093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8573684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9026699066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7894163131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949541091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6535110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.645959854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6610622406006</t>
   </si>
   <si>
     <t xml:space="preserve">10.8271684646606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8800191879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7441139221191</t>
+    <t xml:space="preserve">10.8800201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7441148757935</t>
   </si>
   <si>
     <t xml:space="preserve">10.9781732559204</t>
@@ -908,19 +908,19 @@
     <t xml:space="preserve">10.8951215744019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0183162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721183776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0260162353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9259204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7642259597778</t>
+    <t xml:space="preserve">11.0183172225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721193313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0260143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9259195327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7642250061035</t>
   </si>
   <si>
     <t xml:space="preserve">10.6410293579102</t>
@@ -929,28 +929,28 @@
     <t xml:space="preserve">10.6025314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3561391830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4793338775635</t>
+    <t xml:space="preserve">10.3561401367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4793357849121</t>
   </si>
   <si>
     <t xml:space="preserve">10.4408369064331</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4177379608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406425476074</t>
+    <t xml:space="preserve">10.4177360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406444549561</t>
   </si>
   <si>
     <t xml:space="preserve">10.4023380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7873258590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4947328567505</t>
+    <t xml:space="preserve">10.7873239517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4947347640991</t>
   </si>
   <si>
     <t xml:space="preserve">10.5409336090088</t>
@@ -959,31 +959,31 @@
     <t xml:space="preserve">10.3176412582397</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3715419769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2791423797607</t>
+    <t xml:space="preserve">10.3715391159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2791433334351</t>
   </si>
   <si>
     <t xml:space="preserve">10.2868413925171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3330392837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5101346969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8335227966309</t>
+    <t xml:space="preserve">10.3330402374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5101356506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8335237503052</t>
   </si>
   <si>
     <t xml:space="preserve">10.8566217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7103252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6179313659668</t>
+    <t xml:space="preserve">10.7103271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6179294586182</t>
   </si>
   <si>
     <t xml:space="preserve">10.3407402038574</t>
@@ -992,55 +992,55 @@
     <t xml:space="preserve">10.4716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7796239852905</t>
+    <t xml:space="preserve">10.7796249389648</t>
   </si>
   <si>
     <t xml:space="preserve">10.9105205535889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0106182098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9413204193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7565279006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5255355834961</t>
+    <t xml:space="preserve">11.0106172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9413185119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7565250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5255327224731</t>
   </si>
   <si>
     <t xml:space="preserve">10.6256303787231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3099403381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0943470001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99425029754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27047729492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34747409820557</t>
+    <t xml:space="preserve">10.3099412918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0943479537964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9942512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27047824859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34747505187988</t>
   </si>
   <si>
     <t xml:space="preserve">9.2088794708252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29357528686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16268157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22427845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9778881072998</t>
+    <t xml:space="preserve">9.29357433319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16267967224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22427940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97788906097412</t>
   </si>
   <si>
     <t xml:space="preserve">9.00868606567383</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">8.87779235839844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80079364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85469150543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82389354705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7853946685791</t>
+    <t xml:space="preserve">8.8007926940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85469245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82389163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78539371490479</t>
   </si>
   <si>
     <t xml:space="preserve">8.72379684448242</t>
@@ -1073,55 +1073,55 @@
     <t xml:space="preserve">8.63909912109375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52360343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62369918823242</t>
+    <t xml:space="preserve">8.52360248565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62370109558105</t>
   </si>
   <si>
     <t xml:space="preserve">8.6467981338501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60829925537109</t>
+    <t xml:space="preserve">8.60830020904541</t>
   </si>
   <si>
     <t xml:space="preserve">8.74689674377441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03178691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11648368835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13188171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93169021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15498065948486</t>
+    <t xml:space="preserve">9.0317850112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11648464202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13188076019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93168926239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1549825668335</t>
   </si>
   <si>
     <t xml:space="preserve">9.37827396392822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3012752532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32437515258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33207416534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27817630767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26277828216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2473783493042</t>
+    <t xml:space="preserve">9.30127716064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32437610626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33207511901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27817821502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26277637481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24737739562988</t>
   </si>
   <si>
     <t xml:space="preserve">9.23967933654785</t>
@@ -1130,28 +1130,28 @@
     <t xml:space="preserve">9.20117950439453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10878276824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87009239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84699058532715</t>
+    <t xml:space="preserve">9.10878467559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87009143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84699153900146</t>
   </si>
   <si>
     <t xml:space="preserve">8.95478820800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73919582366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63140106201172</t>
+    <t xml:space="preserve">8.73919677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6314001083374</t>
   </si>
   <si>
     <t xml:space="preserve">8.65449810028076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70839691162109</t>
+    <t xml:space="preserve">8.70839786529541</t>
   </si>
   <si>
     <t xml:space="preserve">8.79309463500977</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">9.04718399047852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0558500289917</t>
+    <t xml:space="preserve">10.0558490753174</t>
   </si>
   <si>
     <t xml:space="preserve">10.1328477859497</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">10.1020488739014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0173511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94035339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82485771179199</t>
+    <t xml:space="preserve">10.017352104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94035530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82485961914062</t>
   </si>
   <si>
     <t xml:space="preserve">9.70166301727295</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">9.45527172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30897521972656</t>
+    <t xml:space="preserve">9.30897617340088</t>
   </si>
   <si>
     <t xml:space="preserve">9.33977508544922</t>
@@ -1196,13 +1196,13 @@
     <t xml:space="preserve">9.41760730743408</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72893333435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6744499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44095420837402</t>
+    <t xml:space="preserve">9.72893238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67445087432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44095611572266</t>
   </si>
   <si>
     <t xml:space="preserve">9.43317222595215</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">9.69779872894287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91572761535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80676364898682</t>
+    <t xml:space="preserve">9.91572666168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80676460266113</t>
   </si>
   <si>
     <t xml:space="preserve">9.64331912994385</t>
@@ -1226,40 +1226,40 @@
     <t xml:space="preserve">9.76784801483154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86124706268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336574554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.437198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1881380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0480394363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95464324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492233276367</t>
+    <t xml:space="preserve">9.86124420166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4371976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1881370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0480422973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95464515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492204666138</t>
   </si>
   <si>
     <t xml:space="preserve">10.0324754714966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.15700340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3126668930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3904991149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3438024520874</t>
+    <t xml:space="preserve">10.1570062637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3126678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3905000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3438005447388</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426195144653</t>
@@ -1268,40 +1268,40 @@
     <t xml:space="preserve">10.4294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6162090301514</t>
+    <t xml:space="preserve">10.6162118911743</t>
   </si>
   <si>
     <t xml:space="preserve">10.5928611755371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6862573623657</t>
+    <t xml:space="preserve">10.68625831604</t>
   </si>
   <si>
     <t xml:space="preserve">10.6784763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9508857727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0520658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1143321990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8886203765869</t>
+    <t xml:space="preserve">10.9508867263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0520687103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8886194229126</t>
   </si>
   <si>
     <t xml:space="preserve">10.8341388702393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9975843429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.083197593689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2933435440063</t>
+    <t xml:space="preserve">10.9975852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0831985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.293345451355</t>
   </si>
   <si>
     <t xml:space="preserve">11.3011283874512</t>
@@ -1313,76 +1313,76 @@
     <t xml:space="preserve">11.2544298171997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3166942596436</t>
+    <t xml:space="preserve">11.3166933059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610317230225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9586696624756</t>
+    <t xml:space="preserve">10.9586706161499</t>
   </si>
   <si>
     <t xml:space="preserve">10.9158601760864</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7018241882324</t>
+    <t xml:space="preserve">10.7018251419067</t>
   </si>
   <si>
     <t xml:space="preserve">10.5850782394409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3048858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4566564559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0519332885742</t>
+    <t xml:space="preserve">10.3048830032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4566555023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0519313812256</t>
   </si>
   <si>
     <t xml:space="preserve">9.99356079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90016078948975</t>
+    <t xml:space="preserve">9.90016174316406</t>
   </si>
   <si>
     <t xml:space="preserve">10.0636072158813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1180896759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.262077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5734024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667995452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5461626052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8730554580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.347825050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2427549362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9469938278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0909824371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1493549346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209331512451</t>
+    <t xml:space="preserve">10.1180906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2620782852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5734043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668014526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.54616355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8730545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3478260040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2427539825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9469947814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0909833908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1493558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0209341049194</t>
   </si>
   <si>
     <t xml:space="preserve">11.3050193786621</t>
@@ -1400,19 +1400,19 @@
     <t xml:space="preserve">11.1999473571777</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1026582717896</t>
+    <t xml:space="preserve">11.1026592254639</t>
   </si>
   <si>
     <t xml:space="preserve">11.277777671814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1376819610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3594999313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7642240524292</t>
+    <t xml:space="preserve">11.1376829147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3595008850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7642250061035</t>
   </si>
   <si>
     <t xml:space="preserve">11.0442838668823</t>
@@ -1421,97 +1421,97 @@
     <t xml:space="preserve">10.5967531204224</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6239929199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7640895843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6473445892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8574876785278</t>
+    <t xml:space="preserve">10.6239948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7640924453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6473426818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8574886322021</t>
   </si>
   <si>
     <t xml:space="preserve">10.8964033126831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8263540267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3244762420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.09876537323</t>
+    <t xml:space="preserve">10.8263559341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3244781494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0987672805786</t>
   </si>
   <si>
     <t xml:space="preserve">11.1298990249634</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4451160430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6435880661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6708250045776</t>
+    <t xml:space="preserve">11.4451169967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6435861587524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6708269119263</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929956436157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5813207626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.865406036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9004306793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0716600418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1611661911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8926458358765</t>
+    <t xml:space="preserve">11.58131980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953577041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8654069900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.900429725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0716590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1611642837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8926467895508</t>
   </si>
   <si>
     <t xml:space="preserve">11.9393444061279</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8381662368774</t>
+    <t xml:space="preserve">11.8381643295288</t>
   </si>
   <si>
     <t xml:space="preserve">12.1183576583862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.542537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5308656692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5581073760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8344058990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542144775391</t>
+    <t xml:space="preserve">12.5425386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5308637619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.55810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8344078063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542125701904</t>
   </si>
   <si>
     <t xml:space="preserve">12.7604675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6631784439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7059869766235</t>
+    <t xml:space="preserve">12.6631774902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7059850692749</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437206268311</t>
@@ -1520,25 +1520,25 @@
     <t xml:space="preserve">12.7020931243896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9355878829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3597660064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3052854537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4556283950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4635419845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1549444198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661298751831</t>
+    <t xml:space="preserve">12.9355888366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3597688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3052892684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4556274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4635410308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1549463272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661308288574</t>
   </si>
   <si>
     <t xml:space="preserve">12.5496196746826</t>
@@ -1550,10 +1550,10 @@
     <t xml:space="preserve">12.4863176345825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5535755157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1460704803467</t>
+    <t xml:space="preserve">12.5535774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.146068572998</t>
   </si>
   <si>
     <t xml:space="preserve">12.2964124679565</t>
@@ -1562,142 +1562,142 @@
     <t xml:space="preserve">12.0392475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9996852874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3478441238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.312237739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3953218460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230146408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2726745605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4784059524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9007759094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205570220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7979097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8374738693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4111480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8809938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284677505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5377492904663</t>
+    <t xml:space="preserve">11.9996824264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.347843170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3122386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.395320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230165481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2726736068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4784049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9007740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.920557975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7979068756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8374729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4111461639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8809928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5377502441406</t>
   </si>
   <si>
     <t xml:space="preserve">12.4665365219116</t>
   </si>
   <si>
-    <t xml:space="preserve">12.434886932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3755407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5733594894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6089677810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6050090789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6683111190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9927349090576</t>
+    <t xml:space="preserve">12.4348850250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3755397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5733585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6089649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6050081253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6683120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9927358627319</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520801544189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6762237548828</t>
+    <t xml:space="preserve">12.6762247085571</t>
   </si>
   <si>
     <t xml:space="preserve">12.7355699539185</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6010522842407</t>
+    <t xml:space="preserve">12.601053237915</t>
   </si>
   <si>
     <t xml:space="preserve">12.5456619262695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5575313568115</t>
+    <t xml:space="preserve">12.5575332641602</t>
   </si>
   <si>
     <t xml:space="preserve">12.4546661376953</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4586248397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2489347457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3201503753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3676252365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5961332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7623014450073</t>
+    <t xml:space="preserve">12.4586219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2489337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3201494216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3676271438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5961351394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.762300491333</t>
   </si>
   <si>
     <t xml:space="preserve">11.7702140808105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9759464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9324254989624</t>
+    <t xml:space="preserve">11.9759483337402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9324264526367</t>
   </si>
   <si>
     <t xml:space="preserve">12.0273790359497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.821647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5328311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418363571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5170059204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6159162521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5921764373779</t>
+    <t xml:space="preserve">11.8216485977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5328302383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418354034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5170068740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6159152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5921773910522</t>
   </si>
   <si>
     <t xml:space="preserve">11.7148246765137</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">12.0867233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8889036178589</t>
+    <t xml:space="preserve">11.8889045715332</t>
   </si>
   <si>
     <t xml:space="preserve">11.892861366272</t>
@@ -1715,76 +1715,76 @@
     <t xml:space="preserve">11.2281913757324</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4339227676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062280654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3310556411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9947643280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.903769493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7257328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228647232056</t>
+    <t xml:space="preserve">11.4339208602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062261581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9947633743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9037704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7257299423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228656768799</t>
   </si>
   <si>
     <t xml:space="preserve">10.6901245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9433307647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9314632415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9354200363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9987211227417</t>
+    <t xml:space="preserve">10.9433345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9314613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9354190826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.998722076416</t>
   </si>
   <si>
     <t xml:space="preserve">11.1451072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.153018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0857629776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066318511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.117413520813</t>
+    <t xml:space="preserve">11.1530199050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0857610702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066337585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1174125671387</t>
   </si>
   <si>
     <t xml:space="preserve">11.7306499481201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6396541595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.584264755249</t>
+    <t xml:space="preserve">11.6396551132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5842666625977</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180965423584</t>
   </si>
   <si>
-    <t xml:space="preserve">11.726692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820825576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9482507705688</t>
+    <t xml:space="preserve">11.7266931533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9482526779175</t>
   </si>
   <si>
     <t xml:space="preserve">11.6277837753296</t>
@@ -1796,70 +1796,70 @@
     <t xml:space="preserve">11.9601202011108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6238269805908</t>
+    <t xml:space="preserve">11.6238298416138</t>
   </si>
   <si>
     <t xml:space="preserve">11.1332378387451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1411504745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886281967163</t>
+    <t xml:space="preserve">11.141152381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.188627243042</t>
   </si>
   <si>
     <t xml:space="preserve">11.3112735748291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2400598526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.093674659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.081805229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8325548171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4052639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2984428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2628355026245</t>
+    <t xml:space="preserve">11.2400617599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0936737060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0818061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8325538635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4052648544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2984437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2628364562988</t>
   </si>
   <si>
     <t xml:space="preserve">10.1718378067017</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2034912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0927114486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3933963775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5635204315186</t>
+    <t xml:space="preserve">10.2034902572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0927095413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3933954238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5635213851929</t>
   </si>
   <si>
     <t xml:space="preserve">10.6268224716187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6307792663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6189079284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5200004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4843921661377</t>
+    <t xml:space="preserve">10.6307773590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6189098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199995040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.484393119812</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430543899536</t>
@@ -1871,40 +1871,40 @@
     <t xml:space="preserve">9.85137176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75641822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8751106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7801570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68019676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40830230712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58823394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45228672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29634761810303</t>
+    <t xml:space="preserve">9.75642108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87511157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78015804290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68019580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40830516815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58823299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45228576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29634857177734</t>
   </si>
   <si>
     <t xml:space="preserve">9.56024360656738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38031387329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71657371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66059684753418</t>
+    <t xml:space="preserve">9.38031482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71657466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6605978012085</t>
   </si>
   <si>
     <t xml:space="preserve">8.49666213989258</t>
@@ -1913,10 +1913,10 @@
     <t xml:space="preserve">8.78854751586914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67259311676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50865745544434</t>
+    <t xml:space="preserve">8.67259216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50865650177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.22876644134521</t>
@@ -1925,25 +1925,25 @@
     <t xml:space="preserve">8.24875831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99685764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10881423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20077800750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1807861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8912992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71217012405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71377038955688</t>
+    <t xml:space="preserve">7.99685859680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10881519317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20077705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18078517913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89129829406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71217060089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71376848220825</t>
   </si>
   <si>
     <t xml:space="preserve">7.38110065460205</t>
@@ -1952,37 +1952,37 @@
     <t xml:space="preserve">7.39389562606812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34271621704102</t>
+    <t xml:space="preserve">7.34271478652954</t>
   </si>
   <si>
     <t xml:space="preserve">7.54903411865234</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61140966415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59861612319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88490152359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01285171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05683517456055</t>
+    <t xml:space="preserve">7.61140918731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59861469268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8849024772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01285362243652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05683326721191</t>
   </si>
   <si>
     <t xml:space="preserve">8.2967414855957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31673336029053</t>
+    <t xml:space="preserve">8.31673240661621</t>
   </si>
   <si>
     <t xml:space="preserve">8.24076271057129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16879081726074</t>
+    <t xml:space="preserve">8.16879177093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.22476863861084</t>
@@ -1991,25 +1991,25 @@
     <t xml:space="preserve">8.52065181732178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45267963409424</t>
+    <t xml:space="preserve">8.45267772674561</t>
   </si>
   <si>
     <t xml:space="preserve">8.32073211669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39669990539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53264808654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82453346252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70058250427246</t>
+    <t xml:space="preserve">8.39670085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53264904022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82453441619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58862495422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70058059692383</t>
   </si>
   <si>
     <t xml:space="preserve">8.7685546875</t>
@@ -2018,55 +2018,55 @@
     <t xml:space="preserve">8.75655937194824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93249130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98846912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76455688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56463527679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7445650100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95248317718506</t>
+    <t xml:space="preserve">8.9324893951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98846817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76455593109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5646333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74456405639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95248126983643</t>
   </si>
   <si>
     <t xml:space="preserve">9.20838165283203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22037601470947</t>
+    <t xml:space="preserve">9.22037887573242</t>
   </si>
   <si>
     <t xml:space="preserve">9.43629360198975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49227142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55224704742432</t>
+    <t xml:space="preserve">9.49226951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55224514007568</t>
   </si>
   <si>
     <t xml:space="preserve">9.59622955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7561674118042</t>
+    <t xml:space="preserve">9.75616550445557</t>
   </si>
   <si>
     <t xml:space="preserve">9.63221549987793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6162223815918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51626110076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51226329803467</t>
+    <t xml:space="preserve">9.61622142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51626014709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51226234436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.3323335647583</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">9.36432075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48427391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.252366065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1124210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42029857635498</t>
+    <t xml:space="preserve">9.48427295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25236415863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11242008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4202995300293</t>
   </si>
   <si>
     <t xml:space="preserve">9.8441333770752</t>
@@ -2096,10 +2096,10 @@
     <t xml:space="preserve">9.89611148834229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84813117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86812400817871</t>
+    <t xml:space="preserve">9.84812927246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86812210083008</t>
   </si>
   <si>
     <t xml:space="preserve">9.98407649993896</t>
@@ -2114,67 +2114,67 @@
     <t xml:space="preserve">10.2039918899536</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0680437088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82813930511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0080680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1720018386841</t>
+    <t xml:space="preserve">10.0680456161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82813835144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0080690383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2759637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.172004699707</t>
   </si>
   <si>
     <t xml:space="preserve">10.1440143585205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95608901977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2559690475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3199453353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0440549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93609619140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0040702819824</t>
+    <t xml:space="preserve">9.95608806610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.255970954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3199443817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0440559387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93609809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0040693283081</t>
   </si>
   <si>
     <t xml:space="preserve">10.0560493469238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3959140777588</t>
+    <t xml:space="preserve">10.3959150314331</t>
   </si>
   <si>
     <t xml:space="preserve">10.5278635025024</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4279041290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7917613983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5598526000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3359413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92809867858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90011119842529</t>
+    <t xml:space="preserve">10.4279022216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7917604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5598516464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3359384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92810153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90011024475098</t>
   </si>
   <si>
     <t xml:space="preserve">9.74017238616943</t>
@@ -2183,31 +2183,31 @@
     <t xml:space="preserve">9.60422611236572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44029331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60822486877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41230201721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34033012390137</t>
+    <t xml:space="preserve">9.4402904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60822582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41230297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34032917022705</t>
   </si>
   <si>
     <t xml:space="preserve">9.29234886169434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54025173187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61222362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96408653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0160655975342</t>
+    <t xml:space="preserve">9.54025268554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61222267150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96408462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0160646438599</t>
   </si>
   <si>
     <t xml:space="preserve">10.024245262146</t>
@@ -2216,103 +2216,103 @@
     <t xml:space="preserve">10.1755695343018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85656070709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43939590454102</t>
+    <t xml:space="preserve">9.8565616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4393949508667</t>
   </si>
   <si>
     <t xml:space="preserve">9.32487869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16128444671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15310382843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01404857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9854211807251</t>
+    <t xml:space="preserve">9.16128635406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15310573577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0140495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98542022705078</t>
   </si>
   <si>
     <t xml:space="preserve">8.62960433959961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8749942779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08766555786133</t>
+    <t xml:space="preserve">8.87499523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08766651153564</t>
   </si>
   <si>
     <t xml:space="preserve">8.78910732269287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79728889465332</t>
+    <t xml:space="preserve">8.79728698730469</t>
   </si>
   <si>
     <t xml:space="preserve">8.78092765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06312942504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19809532165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94452381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83409690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87908458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05085849761963</t>
+    <t xml:space="preserve">9.0631275177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19809246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9445219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83409595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87908363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05085945129395</t>
   </si>
   <si>
     <t xml:space="preserve">9.29624938964844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39440536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25126266479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14901351928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42303657531738</t>
+    <t xml:space="preserve">9.39440822601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25126171112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14901447296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42303562164307</t>
   </si>
   <si>
     <t xml:space="preserve">9.38213729858398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41485500335693</t>
+    <t xml:space="preserve">9.41485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">9.65206909179688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42712497711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44757461547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54573059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54164218902588</t>
+    <t xml:space="preserve">9.4271240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44757556915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54573154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54164123535156</t>
   </si>
   <si>
     <t xml:space="preserve">9.75431537628174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66024875640869</t>
+    <t xml:space="preserve">9.66024684906006</t>
   </si>
   <si>
     <t xml:space="preserve">9.80748271942139</t>
@@ -2324,22 +2324,22 @@
     <t xml:space="preserve">9.94244766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83202171325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8279333114624</t>
+    <t xml:space="preserve">9.83202075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82793235778809</t>
   </si>
   <si>
     <t xml:space="preserve">9.45166492462158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2880687713623</t>
+    <t xml:space="preserve">9.28806972503662</t>
   </si>
   <si>
     <t xml:space="preserve">9.12038612365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24308300018311</t>
+    <t xml:space="preserve">9.24308204650879</t>
   </si>
   <si>
     <t xml:space="preserve">9.31260967254639</t>
@@ -2348,13 +2348,13 @@
     <t xml:space="preserve">9.59071922302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50892162322998</t>
+    <t xml:space="preserve">9.50892353057861</t>
   </si>
   <si>
     <t xml:space="preserve">9.26762104034424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93225288391113</t>
+    <t xml:space="preserve">8.93225479125977</t>
   </si>
   <si>
     <t xml:space="preserve">8.71548938751221</t>
@@ -2363,100 +2363,100 @@
     <t xml:space="preserve">8.56416606903076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36376285552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29423427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44556045532227</t>
+    <t xml:space="preserve">8.36376094818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29423522949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44555950164795</t>
   </si>
   <si>
     <t xml:space="preserve">8.27787494659424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0095796585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14209175109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71838331222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75764513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05211544036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88852024078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98340654373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08810520172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96377277374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07010936737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12409687042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21652603149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16335868835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10937118530273</t>
+    <t xml:space="preserve">8.00958061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14209270477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71838140487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75764417648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05211448669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88852119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98340463638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08810615539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96377372741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07011032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12409496307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21652889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16335964202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10937213897705</t>
   </si>
   <si>
     <t xml:space="preserve">8.0652027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86071062088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00467109680176</t>
+    <t xml:space="preserve">7.86070871353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00467300415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.21243667602539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17153739929199</t>
+    <t xml:space="preserve">8.17153930664062</t>
   </si>
   <si>
     <t xml:space="preserve">8.41284084320068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51099681854248</t>
+    <t xml:space="preserve">8.5109977722168</t>
   </si>
   <si>
     <t xml:space="preserve">8.43737888336182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31468391418457</t>
+    <t xml:space="preserve">8.31468296051025</t>
   </si>
   <si>
     <t xml:space="preserve">8.3719425201416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60506343841553</t>
+    <t xml:space="preserve">8.60506439208984</t>
   </si>
   <si>
     <t xml:space="preserve">8.44146919250488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.318772315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22061824798584</t>
+    <t xml:space="preserve">8.31877422332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22061634063721</t>
   </si>
   <si>
     <t xml:space="preserve">8.20016670227051</t>
@@ -2465,25 +2465,25 @@
     <t xml:space="preserve">7.97195339202881</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85743761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85253095626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72983360290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00794506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96213626861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81326770782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48771333694458</t>
+    <t xml:space="preserve">7.8574366569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85252904891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72983264923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00794410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96213912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81326723098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48771381378174</t>
   </si>
   <si>
     <t xml:space="preserve">7.56296825408936</t>
@@ -2492,154 +2492,154 @@
     <t xml:space="preserve">7.54824352264404</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63658428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50898265838623</t>
+    <t xml:space="preserve">7.63658618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50898122787476</t>
   </si>
   <si>
     <t xml:space="preserve">7.54333639144897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61531734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88034105300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6725754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77400302886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74292135238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64803791046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60713768005371</t>
+    <t xml:space="preserve">7.61531829833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88033962249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67257595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77400493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74292230606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64803743362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60713815689087</t>
   </si>
   <si>
     <t xml:space="preserve">7.66276025772095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68239212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70202398300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69220638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80999565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8852481842041</t>
+    <t xml:space="preserve">7.68239164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70202255249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61859035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69220685958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80999660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88524913787842</t>
   </si>
   <si>
     <t xml:space="preserve">7.65785360336304</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40591812133789</t>
+    <t xml:space="preserve">7.40591716766357</t>
   </si>
   <si>
     <t xml:space="preserve">8.03739166259766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17644691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32286357879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18380832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19607830047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23697757720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10446357727051</t>
+    <t xml:space="preserve">8.17644596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3228645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18380737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19607925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23697566986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10446643829346</t>
   </si>
   <si>
     <t xml:space="preserve">8.10282897949219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09955596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02993392944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95865345001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08961200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04153728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16918087005615</t>
+    <t xml:space="preserve">8.09955883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02993297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95865201950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0896110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04153919219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16917991638184</t>
   </si>
   <si>
     <t xml:space="preserve">8.15094566345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15591812133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08629417419434</t>
+    <t xml:space="preserve">8.15591907501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08629608154297</t>
   </si>
   <si>
     <t xml:space="preserve">8.09955787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85587453842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80116987228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96693992614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03987884521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2122802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24377822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26864433288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2968225479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53304672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44187355041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4625940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40872001647949</t>
+    <t xml:space="preserve">8.00009536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85587406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80116939544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96694183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03987979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21228218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24377727508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26864242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29682445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53304767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44187450408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46259498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40871810913086</t>
   </si>
   <si>
     <t xml:space="preserve">8.3921422958374</t>
@@ -2648,106 +2648,106 @@
     <t xml:space="preserve">8.37970924377441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42944145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49574756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36313343048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32997894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37142276763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48331642150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71125030517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69881820678711</t>
+    <t xml:space="preserve">8.42944049835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49574851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36313152313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32997798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37142086029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48331546783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71125221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69881916046143</t>
   </si>
   <si>
     <t xml:space="preserve">8.68224143981934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60764408111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60350036621094</t>
+    <t xml:space="preserve">8.60764217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60349941253662</t>
   </si>
   <si>
     <t xml:space="preserve">8.45016098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40042972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45430564880371</t>
+    <t xml:space="preserve">8.40043067932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45430660247803</t>
   </si>
   <si>
     <t xml:space="preserve">8.52890205383301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50403785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47088432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41700839996338</t>
+    <t xml:space="preserve">8.50403690338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47088241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41700744628906</t>
   </si>
   <si>
     <t xml:space="preserve">8.37556552886963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05811500549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18741607666016</t>
+    <t xml:space="preserve">8.05811405181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18741512298584</t>
   </si>
   <si>
     <t xml:space="preserve">8.2868766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88074016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73154592514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64202928543091</t>
+    <t xml:space="preserve">7.88074111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73154735565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64203023910522</t>
   </si>
   <si>
     <t xml:space="preserve">7.80282688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9089207649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93212795257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78790807723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83598232269287</t>
+    <t xml:space="preserve">7.90891981124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93212842941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78790950775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83598184585571</t>
   </si>
   <si>
     <t xml:space="preserve">7.90063190460205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00672435760498</t>
+    <t xml:space="preserve">8.0067253112793</t>
   </si>
   <si>
     <t xml:space="preserve">7.98186063766479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80448627471924</t>
+    <t xml:space="preserve">7.80448484420776</t>
   </si>
   <si>
     <t xml:space="preserve">7.84095430374146</t>
@@ -2759,61 +2759,61 @@
     <t xml:space="preserve">7.76967287063599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37679672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27733325958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29391050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97563171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77007532119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71868705749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75018405914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57612419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45511198043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08378553390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78248500823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65815734863281</t>
+    <t xml:space="preserve">7.37679767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27733421325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29391241073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97563123703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77007579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71868753433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75018310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5761251449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45511150360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08378505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78248405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65815687179565</t>
   </si>
   <si>
     <t xml:space="preserve">4.56200981140137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8790340423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97766804695129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71989512443542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85085368156433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94534349441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15918684005737</t>
+    <t xml:space="preserve">3.87903428077698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97766828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71989417076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85085344314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94534277915955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15918731689453</t>
   </si>
   <si>
     <t xml:space="preserve">4.32661533355713</t>
@@ -2825,22 +2825,22 @@
     <t xml:space="preserve">4.43436622619629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46088981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70788812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61505651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62500286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54543352127075</t>
+    <t xml:space="preserve">4.46088933944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70788860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61505699157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59019041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62500238418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54543304443359</t>
   </si>
   <si>
     <t xml:space="preserve">4.75430393218994</t>
@@ -2849,46 +2849,46 @@
     <t xml:space="preserve">4.78745794296265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90681266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13226127624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.014564037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97809410095215</t>
+    <t xml:space="preserve">4.906813621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13226079940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01456499099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97809457778931</t>
   </si>
   <si>
     <t xml:space="preserve">4.9117865562439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69131088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77751159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80735063552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77916860580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54046010971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68136405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.867027759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90515613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8968677520752</t>
+    <t xml:space="preserve">4.6913104057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77751207351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80735111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7791690826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54045963287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6813645362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86702823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90515470504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686679840088</t>
   </si>
   <si>
     <t xml:space="preserve">4.99135637283325</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">5.28311252593994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29968929290771</t>
+    <t xml:space="preserve">5.29969024658203</t>
   </si>
   <si>
     <t xml:space="preserve">5.00627517700195</t>
@@ -2906,31 +2906,31 @@
     <t xml:space="preserve">5.24664258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04440355300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1206579208374</t>
+    <t xml:space="preserve">5.04440212249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12065744400024</t>
   </si>
   <si>
     <t xml:space="preserve">5.16375780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07092666625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98141050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76425123214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79408836364746</t>
+    <t xml:space="preserve">5.07092618942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98140954971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7642502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79408931732178</t>
   </si>
   <si>
     <t xml:space="preserve">5.15878438949585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69960021972656</t>
+    <t xml:space="preserve">4.69959926605225</t>
   </si>
   <si>
     <t xml:space="preserve">4.85045099258423</t>
@@ -2939,16 +2939,16 @@
     <t xml:space="preserve">4.61174058914185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59847974777222</t>
+    <t xml:space="preserve">4.59847831726074</t>
   </si>
   <si>
     <t xml:space="preserve">4.64158010482788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71451997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72115039825439</t>
+    <t xml:space="preserve">4.71451950073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72114992141724</t>
   </si>
   <si>
     <t xml:space="preserve">4.83718919754028</t>
@@ -2957,43 +2957,43 @@
     <t xml:space="preserve">4.63494873046875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84382009506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04606056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29803228378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35273599624634</t>
+    <t xml:space="preserve">4.84382104873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04606008529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2980318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3527364730835</t>
   </si>
   <si>
     <t xml:space="preserve">5.63288879394531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71577453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61465358734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53508424758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18365049362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18862295150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18199253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1306037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12894630432129</t>
+    <t xml:space="preserve">5.71577405929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61465406417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53508472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18365001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18862342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18199300765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13060331344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12894678115845</t>
   </si>
   <si>
     <t xml:space="preserve">5.04108715057373</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">5.14220762252808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8239278793335</t>
+    <t xml:space="preserve">4.82392835617065</t>
   </si>
   <si>
     <t xml:space="preserve">4.88692045211792</t>
@@ -3011,19 +3011,19 @@
     <t xml:space="preserve">4.76093482971191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81398105621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70623111724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85210943222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76259279251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93002128601074</t>
+    <t xml:space="preserve">4.81398153305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70623016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8521089553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76259231567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93002033233643</t>
   </si>
   <si>
     <t xml:space="preserve">4.84547805786133</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">4.76756572723389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59682130813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62168836593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67805004119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75761985778809</t>
+    <t xml:space="preserve">4.59682273864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62168741226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67804908752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75761890411377</t>
   </si>
   <si>
     <t xml:space="preserve">4.76590776443481</t>
@@ -3050,241 +3050,241 @@
     <t xml:space="preserve">4.89355134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78414297103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70291471481323</t>
+    <t xml:space="preserve">4.78414249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70291519165039</t>
   </si>
   <si>
     <t xml:space="preserve">4.66810321807861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58024454116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4907283782959</t>
+    <t xml:space="preserve">4.58024406433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49072885513306</t>
   </si>
   <si>
     <t xml:space="preserve">4.27191114425659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19234180450439</t>
+    <t xml:space="preserve">4.19234132766724</t>
   </si>
   <si>
     <t xml:space="preserve">4.08790588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28185701370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29346132278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48575592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21389150619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29014587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43602466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41447448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32164192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27688455581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23875761032104</t>
+    <t xml:space="preserve">4.28185749053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29346084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21389102935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29014682769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43602418899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41447401046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32164287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27688407897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23875665664673</t>
   </si>
   <si>
     <t xml:space="preserve">4.19731473922729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10448217391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08624887466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22383832931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1757640838623</t>
+    <t xml:space="preserve">4.10448360443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08624839782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22383737564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17576503753662</t>
   </si>
   <si>
     <t xml:space="preserve">4.1334924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05806684494019</t>
+    <t xml:space="preserve">4.05806732177734</t>
   </si>
   <si>
     <t xml:space="preserve">4.08293342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07795906066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0000467300415</t>
+    <t xml:space="preserve">4.0779595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00004768371582</t>
   </si>
   <si>
     <t xml:space="preserve">3.96192026138306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98927211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00087642669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9760103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83924984931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84422278404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82598829269409</t>
+    <t xml:space="preserve">3.9892725944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00087594985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97601103782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83924961090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84422302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82598805427551</t>
   </si>
   <si>
     <t xml:space="preserve">3.77957272529602</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74724721908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80112218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95943331718445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96274852752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85334038734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60053968429565</t>
+    <t xml:space="preserve">3.74724674224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80112266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95943260192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96274900436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85334014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60054016113281</t>
   </si>
   <si>
     <t xml:space="preserve">3.56075501441956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53091621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45880579948425</t>
+    <t xml:space="preserve">3.53091645240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45880603790283</t>
   </si>
   <si>
     <t xml:space="preserve">3.39747095108032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53754663467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53174543380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44139981269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5209698677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55578184127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65358662605286</t>
+    <t xml:space="preserve">3.53754687309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399430274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53174519538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52096962928772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55578136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65358686447144</t>
   </si>
   <si>
     <t xml:space="preserve">3.58064746856689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69005608558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66436123847961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60302662849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51350998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60717129707336</t>
+    <t xml:space="preserve">3.69005632400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66436171531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6030261516571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51351022720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60717082023621</t>
   </si>
   <si>
     <t xml:space="preserve">3.42730951309204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55080914497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62623453140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.710777759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61877536773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63783836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67099285125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57401657104492</t>
+    <t xml:space="preserve">3.5508086681366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62623405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71077752113342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61877512931824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63783764839172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67099237442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57401633262634</t>
   </si>
   <si>
     <t xml:space="preserve">3.47455382347107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3701183795929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17285132408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37509202957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5516369342804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63535213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19399929046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17244863510132</t>
+    <t xml:space="preserve">3.37011861801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37509155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55163741111755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63535189628601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19399881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17244815826416</t>
   </si>
   <si>
     <t xml:space="preserve">4.57029914855957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63660669326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64655303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67639207839966</t>
+    <t xml:space="preserve">4.63660621643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64655351638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6763916015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.74601554870605</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">5.11402654647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21183109283447</t>
+    <t xml:space="preserve">5.21183061599731</t>
   </si>
   <si>
     <t xml:space="preserve">5.27316617965698</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">5.19359588623047</t>
   </si>
   <si>
-    <t xml:space="preserve">5.180335521698</t>
+    <t xml:space="preserve">5.18033456802368</t>
   </si>
   <si>
     <t xml:space="preserve">5.39324855804443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73357439041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67825031280518</t>
+    <t xml:space="preserve">5.73357391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67825078964233</t>
   </si>
   <si>
     <t xml:space="preserve">5.6011323928833</t>
@@ -3320,37 +3320,37 @@
     <t xml:space="preserve">5.61957359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43683671951294</t>
+    <t xml:space="preserve">5.43683624267578</t>
   </si>
   <si>
     <t xml:space="preserve">5.52066135406494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54748487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58101463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80901575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70339775085449</t>
+    <t xml:space="preserve">5.54748582839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58101415634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80901622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70339727401733</t>
   </si>
   <si>
     <t xml:space="preserve">5.7117805480957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71513366699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80231046676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70004463195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62627983093262</t>
+    <t xml:space="preserve">5.71513319015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8023099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70004510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62627935409546</t>
   </si>
   <si>
     <t xml:space="preserve">5.69501543045044</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">5.6665153503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72183990478516</t>
+    <t xml:space="preserve">5.72183895111084</t>
   </si>
   <si>
     <t xml:space="preserve">5.638014793396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4904842376709</t>
+    <t xml:space="preserve">5.49048471450806</t>
   </si>
   <si>
     <t xml:space="preserve">5.47539567947388</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">5.6279559135437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58772087097168</t>
+    <t xml:space="preserve">5.58771944046021</t>
   </si>
   <si>
     <t xml:space="preserve">5.51227855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55251502990723</t>
+    <t xml:space="preserve">5.55251455307007</t>
   </si>
   <si>
     <t xml:space="preserve">5.47874927520752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67489719390869</t>
+    <t xml:space="preserve">5.67489814758301</t>
   </si>
   <si>
     <t xml:space="preserve">5.9783411026001</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">5.96492958068848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65813255310059</t>
+    <t xml:space="preserve">5.65813302993774</t>
   </si>
   <si>
     <t xml:space="preserve">5.64304447174072</t>
@@ -3419,22 +3419,22 @@
     <t xml:space="preserve">5.46198320388794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27254104614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17865896224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24739456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33792400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50054311752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38989496231079</t>
+    <t xml:space="preserve">5.27254152297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17865800857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24739408493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33792448043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50054264068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38989543914795</t>
   </si>
   <si>
     <t xml:space="preserve">5.3815131187439</t>
@@ -3449,40 +3449,40 @@
     <t xml:space="preserve">5.80733966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92972326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82410478591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89451694488525</t>
+    <t xml:space="preserve">5.92972373962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82410526275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89451742172241</t>
   </si>
   <si>
     <t xml:space="preserve">5.90122318267822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95989942550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31196165084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32201957702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17951965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03534078598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06551790237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29351949691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22813606262207</t>
+    <t xml:space="preserve">5.95989990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31196212768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32202005386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17951917648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03534173965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06551837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29351997375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22813749313354</t>
   </si>
   <si>
     <t xml:space="preserve">6.44440364837646</t>
@@ -3491,76 +3491,76 @@
     <t xml:space="preserve">7.32958745956421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24743890762329</t>
+    <t xml:space="preserve">7.24743843078613</t>
   </si>
   <si>
     <t xml:space="preserve">7.41508722305298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53579330444336</t>
+    <t xml:space="preserve">7.53579425811768</t>
   </si>
   <si>
     <t xml:space="preserve">7.51903009414673</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78559064865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02700424194336</t>
+    <t xml:space="preserve">7.78559112548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02700328826904</t>
   </si>
   <si>
     <t xml:space="preserve">8.14435768127441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00520992279053</t>
+    <t xml:space="preserve">8.00521183013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.1108283996582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30697822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31200695037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10579967498779</t>
+    <t xml:space="preserve">8.30697631835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3120059967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10579872131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.12926864624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09741497039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99682712554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81576776504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75038480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61961841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90294313430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6917085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09574031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0571813583374</t>
+    <t xml:space="preserve">8.09741592407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99682760238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81576728820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75038576126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61961793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90294456481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69170713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97168064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0152702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09573936462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05718231201172</t>
   </si>
   <si>
     <t xml:space="preserve">8.10076904296875</t>
@@ -3569,16 +3569,16 @@
     <t xml:space="preserve">8.10915184020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98173952102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77720785140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69506120681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63973665237427</t>
+    <t xml:space="preserve">7.98173999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77720832824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69506025314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63973617553711</t>
   </si>
   <si>
     <t xml:space="preserve">7.62967777252197</t>
@@ -3587,67 +3587,67 @@
     <t xml:space="preserve">7.99850368499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679521560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68332481384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73864984512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39497041702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47041034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46370601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44358825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70008945465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53914737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79229593276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26420450210571</t>
+    <t xml:space="preserve">7.70679712295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68332624435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73864841461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39496898651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47041082382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46370553970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44358777999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70009088516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53914833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79229640960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26420402526855</t>
   </si>
   <si>
     <t xml:space="preserve">7.50897121429443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57603025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63806056976318</t>
+    <t xml:space="preserve">7.5760293006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63806009292603</t>
   </si>
   <si>
     <t xml:space="preserve">7.98006248474121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12591648101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20806503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01359272003174</t>
+    <t xml:space="preserve">8.12591552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20806407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01359081268311</t>
   </si>
   <si>
     <t xml:space="preserve">8.2835054397583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19632911682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21477127075195</t>
+    <t xml:space="preserve">8.19632816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21477031707764</t>
   </si>
   <si>
     <t xml:space="preserve">8.12759399414062</t>
@@ -3656,82 +3656,82 @@
     <t xml:space="preserve">7.90462160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85600233078003</t>
+    <t xml:space="preserve">7.85600328445435</t>
   </si>
   <si>
     <t xml:space="preserve">7.92976760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9586968421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80214309692383</t>
+    <t xml:space="preserve">7.95869827270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80214405059814</t>
   </si>
   <si>
     <t xml:space="preserve">7.82596683502197</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04548072814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96039772033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9382758140564</t>
+    <t xml:space="preserve">8.04548358917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96039819717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93827724456787</t>
   </si>
   <si>
     <t xml:space="preserve">8.15268611907959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24628067016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31604766845703</t>
+    <t xml:space="preserve">8.2462797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31604671478271</t>
   </si>
   <si>
     <t xml:space="preserve">8.1918249130249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20203495025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17140579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11354827880859</t>
+    <t xml:space="preserve">8.20203685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17140483856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11354923248291</t>
   </si>
   <si>
     <t xml:space="preserve">8.12546062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2905216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14077663421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13056564331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94848585128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81575632095337</t>
+    <t xml:space="preserve">8.29052257537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14077472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13056373596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94848680496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81575727462769</t>
   </si>
   <si>
     <t xml:space="preserve">7.84468507766724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92296171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9757137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02506160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07100772857666</t>
+    <t xml:space="preserve">7.92296123504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97571325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02506256103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07100582122803</t>
   </si>
   <si>
     <t xml:space="preserve">7.80384492874146</t>
@@ -3740,55 +3740,55 @@
     <t xml:space="preserve">7.80554580688477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82086277008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97060871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96550464630127</t>
+    <t xml:space="preserve">7.82086181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97060966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96550416946411</t>
   </si>
   <si>
     <t xml:space="preserve">8.0216588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64388751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52987718582153</t>
+    <t xml:space="preserve">7.64388847351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52987766265869</t>
   </si>
   <si>
     <t xml:space="preserve">7.42607402801514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65920352935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63197660446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46861743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59964418411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25420665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00235939025879</t>
+    <t xml:space="preserve">7.65920448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63197708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46861600875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59964561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521377563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25420618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00235891342163</t>
   </si>
   <si>
     <t xml:space="preserve">7.12317848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26271486282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18103504180908</t>
+    <t xml:space="preserve">7.26271533966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18103456497192</t>
   </si>
   <si>
     <t xml:space="preserve">7.26441669464111</t>
@@ -3797,28 +3797,28 @@
     <t xml:space="preserve">7.47372198104858</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40735626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031688690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46691465377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29674816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35800838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40565538406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30865907669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28313541412354</t>
+    <t xml:space="preserve">7.40735673904419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031784057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46691560745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29674863815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35800743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40565490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30865955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28313493728638</t>
   </si>
   <si>
     <t xml:space="preserve">7.48222970962524</t>
@@ -3830,31 +3830,31 @@
     <t xml:space="preserve">7.48563385009766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49584293365479</t>
+    <t xml:space="preserve">7.49584245681763</t>
   </si>
   <si>
     <t xml:space="preserve">7.30185270309448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33418607711792</t>
+    <t xml:space="preserve">7.3341851234436</t>
   </si>
   <si>
     <t xml:space="preserve">6.99385166168213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9376974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07042598724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09254837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15551090240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22187423706055</t>
+    <t xml:space="preserve">6.93769645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07042694091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09254884719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15551042556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22187519073486</t>
   </si>
   <si>
     <t xml:space="preserve">7.33758783340454</t>
@@ -3866,40 +3866,40 @@
     <t xml:space="preserve">7.34269332885742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22527885437012</t>
+    <t xml:space="preserve">7.22527837753296</t>
   </si>
   <si>
     <t xml:space="preserve">7.21166467666626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14700174331665</t>
+    <t xml:space="preserve">7.14700126647949</t>
   </si>
   <si>
     <t xml:space="preserve">7.0942497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06361961364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30695867538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25590896606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37672662734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14019536972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8747353553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87303256988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23038339614868</t>
+    <t xml:space="preserve">7.0636191368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30695772171021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25590848922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3767261505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1401948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87473440170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87303304672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23038291931152</t>
   </si>
   <si>
     <t xml:space="preserve">7.2882399559021</t>
@@ -3908,28 +3908,28 @@
     <t xml:space="preserve">7.32567644119263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57241821289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53668355941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59794330596924</t>
+    <t xml:space="preserve">7.57241868972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53668403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59794282913208</t>
   </si>
   <si>
     <t xml:space="preserve">7.73577880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72556734085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93997764587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67792129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79873991012573</t>
+    <t xml:space="preserve">7.72556781768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93997812271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67792224884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79874086380005</t>
   </si>
   <si>
     <t xml:space="preserve">8.15609073638916</t>
@@ -3941,64 +3941,64 @@
     <t xml:space="preserve">8.21054363250732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10333824157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14758205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40283298492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35348510742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45898818969727</t>
+    <t xml:space="preserve">8.10333919525146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14758110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35348415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45898532867432</t>
   </si>
   <si>
     <t xml:space="preserve">8.60618114471436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43856716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3909215927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56363964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55513191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42325115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19012260437012</t>
+    <t xml:space="preserve">8.43856620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39092063903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56363868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55513095855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42325305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19012546539307</t>
   </si>
   <si>
     <t xml:space="preserve">8.19352722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41474342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38241100311279</t>
+    <t xml:space="preserve">8.4147424697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38241195678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.27520751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79336547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03585147857666</t>
+    <t xml:space="preserve">8.79336261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03585243225098</t>
   </si>
   <si>
     <t xml:space="preserve">9.27833938598633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23154449462891</t>
+    <t xml:space="preserve">9.23154354095459</t>
   </si>
   <si>
     <t xml:space="preserve">8.92524337768555</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">8.83165264129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73380565643311</t>
+    <t xml:space="preserve">8.73380661010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.71253490447998</t>
@@ -4016,115 +4016,115 @@
     <t xml:space="preserve">8.5296049118042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28881931304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07611083984375</t>
+    <t xml:space="preserve">8.288818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07611179351807</t>
   </si>
   <si>
     <t xml:space="preserve">8.2693452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21585941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247806549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20895862579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62753343582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69654655456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47225713729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78108644485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70689821243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72932815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319639205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01745128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91911125183105</t>
+    <t xml:space="preserve">8.21586132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20895957946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62753486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69654560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47225856781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78108596801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70689868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72932624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01745223999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91910886764526</t>
   </si>
   <si>
     <t xml:space="preserve">7.7603816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69309520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62408494949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87942790985107</t>
+    <t xml:space="preserve">7.69309711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62408447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87942695617676</t>
   </si>
   <si>
     <t xml:space="preserve">7.63616132736206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85527276992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78798723220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6137318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86389970779419</t>
+    <t xml:space="preserve">7.85527324676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78798675537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61373233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86390066146851</t>
   </si>
   <si>
     <t xml:space="preserve">7.86217498779297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87597799301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96051549911499</t>
+    <t xml:space="preserve">7.87597608566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96051692962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.02435207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0105504989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94498825073242</t>
+    <t xml:space="preserve">8.01055145263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94498872756958</t>
   </si>
   <si>
     <t xml:space="preserve">8.25899314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37286376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43669700622559</t>
+    <t xml:space="preserve">8.37286281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4366979598999</t>
   </si>
   <si>
     <t xml:space="preserve">8.43842315673828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.45222568511963</t>
   </si>
   <si>
     <t xml:space="preserve">8.40909385681152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58162307739258</t>
+    <t xml:space="preserve">8.58162212371826</t>
   </si>
   <si>
     <t xml:space="preserve">8.65667343139648</t>
@@ -4133,13 +4133,13 @@
     <t xml:space="preserve">8.67824077606201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85076904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06211757659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25190162658691</t>
+    <t xml:space="preserve">8.85076999664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06211853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2519006729126</t>
   </si>
   <si>
     <t xml:space="preserve">9.28640747070312</t>
@@ -4151,64 +4151,64 @@
     <t xml:space="preserve">8.49708461761475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8895902633667</t>
+    <t xml:space="preserve">8.88958930969238</t>
   </si>
   <si>
     <t xml:space="preserve">9.5538272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37698459625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83850002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78243064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65734577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85144138336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86006832122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77380180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87732028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97652530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0800428390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92476654052734</t>
+    <t xml:space="preserve">9.37698554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8385009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78242969512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65734481811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85144329071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86006736755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77380275726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87732124328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97652435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0800437927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92476558685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.99809074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2266941070557</t>
+    <t xml:space="preserve">10.2266931533813</t>
   </si>
   <si>
     <t xml:space="preserve">9.93770694732666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75223731994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44599628448486</t>
+    <t xml:space="preserve">9.75223636627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44599533081055</t>
   </si>
   <si>
     <t xml:space="preserve">9.5236349105835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42443084716797</t>
+    <t xml:space="preserve">9.42442989349365</t>
   </si>
   <si>
     <t xml:space="preserve">9.32091426849365</t>
@@ -4217,16 +4217,16 @@
     <t xml:space="preserve">9.60990047454834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95495986938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86869430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3560905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1447429656982</t>
+    <t xml:space="preserve">9.95495796203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86869335174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.35608959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1447410583496</t>
   </si>
   <si>
     <t xml:space="preserve">9.96358680725098</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">11.2618713378906</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6241846084595</t>
+    <t xml:space="preserve">11.6241836547852</t>
   </si>
   <si>
     <t xml:space="preserve">10.9815101623535</t>
@@ -4244,10 +4244,10 @@
     <t xml:space="preserve">11.1540403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1497259140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8736791610718</t>
+    <t xml:space="preserve">11.1497268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8736782073975</t>
   </si>
   <si>
     <t xml:space="preserve">10.5113677978516</t>
@@ -4256,22 +4256,22 @@
     <t xml:space="preserve">10.7356548309326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9081859588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5724239349365</t>
+    <t xml:space="preserve">10.908185005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5724248886108</t>
   </si>
   <si>
     <t xml:space="preserve">11.6371231079102</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9606151580811</t>
+    <t xml:space="preserve">11.9606161117554</t>
   </si>
   <si>
     <t xml:space="preserve">11.9951219558716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2927360534668</t>
+    <t xml:space="preserve">12.2927350997925</t>
   </si>
   <si>
     <t xml:space="preserve">12.0123739242554</t>
@@ -4280,16 +4280,16 @@
     <t xml:space="preserve">11.6845684051514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8829765319824</t>
+    <t xml:space="preserve">11.8829774856567</t>
   </si>
   <si>
     <t xml:space="preserve">11.8657236099243</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9821834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9735546112061</t>
+    <t xml:space="preserve">11.9821815490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9735565185547</t>
   </si>
   <si>
     <t xml:space="preserve">12.0727605819702</t>
@@ -4298,13 +4298,13 @@
     <t xml:space="preserve">11.9390497207642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9908075332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5299644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4135074615479</t>
+    <t xml:space="preserve">11.9908084869385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5299634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4135065078735</t>
   </si>
   <si>
     <t xml:space="preserve">12.8146371841431</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">12.9224691390991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9914808273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9612874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9310941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5817232131958</t>
+    <t xml:space="preserve">12.9914817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9612884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.931095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5817222595215</t>
   </si>
   <si>
     <t xml:space="preserve">11.7233877182007</t>
@@ -4334,28 +4334,28 @@
     <t xml:space="preserve">12.0813865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7758197784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2841091156006</t>
+    <t xml:space="preserve">12.7758178710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2841081619263</t>
   </si>
   <si>
     <t xml:space="preserve">12.8448305130005</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6981792449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6377935409546</t>
+    <t xml:space="preserve">12.6981801986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6377944946289</t>
   </si>
   <si>
     <t xml:space="preserve">12.5385894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0598211288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1805896759033</t>
+    <t xml:space="preserve">12.0598201751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805925369263</t>
   </si>
   <si>
     <t xml:space="preserve">12.5989742279053</t>
@@ -4364,7 +4364,7 @@
     <t xml:space="preserve">12.2668561935425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7283735275269</t>
+    <t xml:space="preserve">12.7283725738525</t>
   </si>
   <si>
     <t xml:space="preserve">13.27184009552</t>
@@ -4373,28 +4373,28 @@
     <t xml:space="preserve">13.4486837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3667335510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.021674156189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1942024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4885787963867</t>
+    <t xml:space="preserve">13.3667325973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0216732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.19420337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.488579750061</t>
   </si>
   <si>
     <t xml:space="preserve">13.3040437698364</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5456972122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9147644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0861186981201</t>
+    <t xml:space="preserve">13.5456962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9147653579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0861177444458</t>
   </si>
   <si>
     <t xml:space="preserve">14.253077507019</t>
@@ -4406,25 +4406,25 @@
     <t xml:space="preserve">13.8356781005859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8664350509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8224983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.963095664978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0641498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0246057510376</t>
+    <t xml:space="preserve">13.86643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8224973678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9630947113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0641479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0246067047119</t>
   </si>
   <si>
     <t xml:space="preserve">13.4094924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0052738189697</t>
+    <t xml:space="preserve">13.0052728652954</t>
   </si>
   <si>
     <t xml:space="preserve">12.803165435791</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">12.693323135376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3154668807983</t>
+    <t xml:space="preserve">12.315468788147</t>
   </si>
   <si>
     <t xml:space="preserve">11.5641489028931</t>
@@ -4448,19 +4448,19 @@
     <t xml:space="preserve">11.6739912033081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.072057723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7381391525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9402475357056</t>
+    <t xml:space="preserve">11.0720586776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7381401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9402465820312</t>
   </si>
   <si>
     <t xml:space="preserve">10.9578227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2302303314209</t>
+    <t xml:space="preserve">11.2302293777466</t>
   </si>
   <si>
     <t xml:space="preserve">11.063271522522</t>
@@ -4469,19 +4469,19 @@
     <t xml:space="preserve">10.782075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5799655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9666109085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0615129470825</t>
+    <t xml:space="preserve">10.579966545105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.966609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0615119934082</t>
   </si>
   <si>
     <t xml:space="preserve">9.75834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7469253540039</t>
+    <t xml:space="preserve">10.7469244003296</t>
   </si>
   <si>
     <t xml:space="preserve">11.1423559188843</t>
@@ -4493,22 +4493,22 @@
     <t xml:space="preserve">11.1116018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.984185218811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5404233932495</t>
+    <t xml:space="preserve">10.9841833114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5404243469238</t>
   </si>
   <si>
     <t xml:space="preserve">10.7117767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1467514038086</t>
+    <t xml:space="preserve">11.1467504501343</t>
   </si>
   <si>
     <t xml:space="preserve">11.1819000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0676641464233</t>
+    <t xml:space="preserve">11.067663192749</t>
   </si>
   <si>
     <t xml:space="preserve">10.8523750305176</t>
@@ -4517,28 +4517,28 @@
     <t xml:space="preserve">10.9753971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0940265655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4411268234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5861186981201</t>
+    <t xml:space="preserve">11.0940275192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.441125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5861177444458</t>
   </si>
   <si>
     <t xml:space="preserve">11.9551858901978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6344470977783</t>
+    <t xml:space="preserve">11.6344480514526</t>
   </si>
   <si>
     <t xml:space="preserve">11.6608114242554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5289993286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0896339416504</t>
+    <t xml:space="preserve">11.5290002822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0896329879761</t>
   </si>
   <si>
     <t xml:space="preserve">11.3005285263062</t>
@@ -4547,22 +4547,22 @@
     <t xml:space="preserve">11.4147644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2917413711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5685424804688</t>
+    <t xml:space="preserve">11.2917423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5685434341431</t>
   </si>
   <si>
     <t xml:space="preserve">11.5421810150146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3224964141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6827783584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2829551696777</t>
+    <t xml:space="preserve">11.3224973678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6827793121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2829542160034</t>
   </si>
   <si>
     <t xml:space="preserve">12.2803192138672</t>
@@ -4574,13 +4574,13 @@
     <t xml:space="preserve">12.3945531845093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2188062667847</t>
+    <t xml:space="preserve">12.2188081741333</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913906097412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0826034545898</t>
+    <t xml:space="preserve">12.0826025009155</t>
   </si>
   <si>
     <t xml:space="preserve">12.029878616333</t>
@@ -4595,46 +4595,46 @@
     <t xml:space="preserve">12.1221466064453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7398958206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7442903518677</t>
+    <t xml:space="preserve">11.7398948669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7442893981934</t>
   </si>
   <si>
     <t xml:space="preserve">12.3286485671997</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5790882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5219688415527</t>
+    <t xml:space="preserve">12.5790872573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5219697952271</t>
   </si>
   <si>
     <t xml:space="preserve">12.5175762176514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2407760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9288234710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9024629592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7882261276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.126540184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9622173309326</t>
+    <t xml:space="preserve">12.2407751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9288244247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9024620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7882270812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1265392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9622163772583</t>
   </si>
   <si>
     <t xml:space="preserve">11.1994733810425</t>
   </si>
   <si>
-    <t xml:space="preserve">11.537787437439</t>
+    <t xml:space="preserve">11.5377883911133</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761014938354</t>
@@ -4658,22 +4658,22 @@
     <t xml:space="preserve">12.7328662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.135326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2451696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8163452148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217939376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2117757797241</t>
+    <t xml:space="preserve">12.1353273391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2451686859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8163471221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615129470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2117776870728</t>
   </si>
   <si>
     <t xml:space="preserve">13.1590538024902</t>
@@ -4682,28 +4682,28 @@
     <t xml:space="preserve">13.3216190338135</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2205648422241</t>
+    <t xml:space="preserve">13.2205638885498</t>
   </si>
   <si>
     <t xml:space="preserve">13.5193338394165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8927965164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8005294799805</t>
+    <t xml:space="preserve">13.8927974700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534292221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8005285263062</t>
   </si>
   <si>
     <t xml:space="preserve">14.1564178466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9982442855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1959600448608</t>
+    <t xml:space="preserve">13.9982433319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1959609985352</t>
   </si>
   <si>
     <t xml:space="preserve">14.6265411376953</t>
@@ -4715,16 +4715,16 @@
     <t xml:space="preserve">14.4551877975464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3585271835327</t>
+    <t xml:space="preserve">14.3585262298584</t>
   </si>
   <si>
     <t xml:space="preserve">13.7653799057007</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0553617477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9938516616821</t>
+    <t xml:space="preserve">14.0553636550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9938526153564</t>
   </si>
   <si>
     <t xml:space="preserve">14.6572952270508</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">14.3101949691772</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4244337081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7851209640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6908102035522</t>
+    <t xml:space="preserve">14.4244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.785120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6908092498779</t>
   </si>
   <si>
     <t xml:space="preserve">14.3578357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4466285705566</t>
+    <t xml:space="preserve">14.446629524231</t>
   </si>
   <si>
     <t xml:space="preserve">14.5265426635742</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">14.4954652786255</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2557249069214</t>
+    <t xml:space="preserve">14.2557239532471</t>
   </si>
   <si>
     <t xml:space="preserve">14.0381813049316</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">13.9893445968628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159826278687</t>
+    <t xml:space="preserve">14.015983581543</t>
   </si>
   <si>
     <t xml:space="preserve">13.7451639175415</t>
@@ -4802,13 +4802,13 @@
     <t xml:space="preserve">13.949387550354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1402940750122</t>
+    <t xml:space="preserve">14.1402931213379</t>
   </si>
   <si>
     <t xml:space="preserve">14.4643888473511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7218885421753</t>
+    <t xml:space="preserve">14.721887588501</t>
   </si>
   <si>
     <t xml:space="preserve">14.7796039581299</t>
@@ -4817,7 +4817,7 @@
     <t xml:space="preserve">14.6686124801636</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7130088806152</t>
+    <t xml:space="preserve">14.7130079269409</t>
   </si>
   <si>
     <t xml:space="preserve">14.4599475860596</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">14.9349908828735</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4199905395508</t>
+    <t xml:space="preserve">14.4199914932251</t>
   </si>
   <si>
     <t xml:space="preserve">13.4033107757568</t>
@@ -4838,10 +4838,10 @@
     <t xml:space="preserve">14.0071039199829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0603790283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0692596435547</t>
+    <t xml:space="preserve">14.0603799819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0692586898804</t>
   </si>
   <si>
     <t xml:space="preserve">14.237964630127</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">14.4421892166138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3445167541504</t>
+    <t xml:space="preserve">14.3445177078247</t>
   </si>
   <si>
     <t xml:space="preserve">14.2290849685669</t>
@@ -4865,7 +4865,7 @@
     <t xml:space="preserve">14.5176639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6952486038208</t>
+    <t xml:space="preserve">14.6952495574951</t>
   </si>
   <si>
     <t xml:space="preserve">14.424430847168</t>
@@ -4883,10 +4883,10 @@
     <t xml:space="preserve">14.6197757720947</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3977928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4288702011108</t>
+    <t xml:space="preserve">14.3977937698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4288692474365</t>
   </si>
   <si>
     <t xml:space="preserve">14.1180953979492</t>
@@ -4895,13 +4895,13 @@
     <t xml:space="preserve">13.6297330856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5498189926147</t>
+    <t xml:space="preserve">13.5498199462891</t>
   </si>
   <si>
     <t xml:space="preserve">13.4388284683228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.540940284729</t>
+    <t xml:space="preserve">13.5409393310547</t>
   </si>
   <si>
     <t xml:space="preserve">13.8872337341309</t>
@@ -4916,16 +4916,16 @@
     <t xml:space="preserve">14.3800344467163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4011516571045</t>
+    <t xml:space="preserve">15.4011526107788</t>
   </si>
   <si>
     <t xml:space="preserve">14.6641712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4377508163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.971586227417</t>
+    <t xml:space="preserve">14.4377498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9715852737427</t>
   </si>
   <si>
     <t xml:space="preserve">14.2246465682983</t>
@@ -4943,7 +4943,7 @@
     <t xml:space="preserve">14.3711547851562</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4732666015625</t>
+    <t xml:space="preserve">14.4732656478882</t>
   </si>
   <si>
     <t xml:space="preserve">14.5487403869629</t>
@@ -4967,16 +4967,16 @@
     <t xml:space="preserve">11.9559841156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7384414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7695178985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.164647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0358982086182</t>
+    <t xml:space="preserve">11.7384405136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7695188522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1646480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0358972549438</t>
   </si>
   <si>
     <t xml:space="preserve">11.7650785446167</t>
@@ -4997,7 +4997,7 @@
     <t xml:space="preserve">11.6096906661987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.631890296936</t>
+    <t xml:space="preserve">11.6318893432617</t>
   </si>
   <si>
     <t xml:space="preserve">11.9826221466064</t>
@@ -5009,13 +5009,13 @@
     <t xml:space="preserve">11.5386562347412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5075788497925</t>
+    <t xml:space="preserve">11.5075798034668</t>
   </si>
   <si>
     <t xml:space="preserve">11.8183546066284</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9737424850464</t>
+    <t xml:space="preserve">11.9737434387207</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337854385376</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">11.5031394958496</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2678375244141</t>
+    <t xml:space="preserve">11.2678384780884</t>
   </si>
   <si>
     <t xml:space="preserve">10.9659423828125</t>
@@ -5048,7 +5048,7 @@
     <t xml:space="preserve">10.894907951355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7439594268799</t>
+    <t xml:space="preserve">10.7439584732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.02809715271</t>
@@ -5057,22 +5057,22 @@
     <t xml:space="preserve">11.1168899536133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0991315841675</t>
+    <t xml:space="preserve">11.0991306304932</t>
   </si>
   <si>
     <t xml:space="preserve">10.8771486282349</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7528371810913</t>
+    <t xml:space="preserve">10.7528381347656</t>
   </si>
   <si>
     <t xml:space="preserve">10.8815889358521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8460712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7705984115601</t>
+    <t xml:space="preserve">10.8460702896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7705974578857</t>
   </si>
   <si>
     <t xml:space="preserve">10.9171056747437</t>
@@ -5081,7 +5081,7 @@
     <t xml:space="preserve">10.9526233673096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.071325302124</t>
+    <t xml:space="preserve">11.0713262557983</t>
   </si>
   <si>
     <t xml:space="preserve">11.2311182022095</t>
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">10.8430509567261</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9389266967773</t>
+    <t xml:space="preserve">10.938925743103</t>
   </si>
   <si>
     <t xml:space="preserve">11.1489391326904</t>
@@ -5111,13 +5111,13 @@
     <t xml:space="preserve">11.2722082138062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3452558517456</t>
+    <t xml:space="preserve">11.3452548980713</t>
   </si>
   <si>
     <t xml:space="preserve">11.6054887771606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.696798324585</t>
+    <t xml:space="preserve">11.6967992782593</t>
   </si>
   <si>
     <t xml:space="preserve">11.7561502456665</t>
@@ -5138,10 +5138,10 @@
     <t xml:space="preserve">11.8931140899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4274339675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7972393035889</t>
+    <t xml:space="preserve">11.4274349212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7972402572632</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374464035034</t>
@@ -5153,7 +5153,7 @@
     <t xml:space="preserve">11.829197883606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8337631225586</t>
+    <t xml:space="preserve">11.8337640762329</t>
   </si>
   <si>
     <t xml:space="preserve">11.8657217025757</t>
@@ -5162,19 +5162,19 @@
     <t xml:space="preserve">12.1853075027466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.523154258728</t>
+    <t xml:space="preserve">12.5231533050537</t>
   </si>
   <si>
     <t xml:space="preserve">12.5185880661011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5870704650879</t>
+    <t xml:space="preserve">12.5870695114136</t>
   </si>
   <si>
     <t xml:space="preserve">12.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305208206177</t>
+    <t xml:space="preserve">12.1305198669434</t>
   </si>
   <si>
     <t xml:space="preserve">12.4501066207886</t>
@@ -5186,7 +5186,7 @@
     <t xml:space="preserve">12.7696895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0025300979614</t>
+    <t xml:space="preserve">13.0025291442871</t>
   </si>
   <si>
     <t xml:space="preserve">13.0162267684937</t>
@@ -5201,19 +5201,19 @@
     <t xml:space="preserve">13.1577568054199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1668882369995</t>
+    <t xml:space="preserve">13.1668891906738</t>
   </si>
   <si>
     <t xml:space="preserve">13.5184316635132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5549564361572</t>
+    <t xml:space="preserve">13.5549554824829</t>
   </si>
   <si>
     <t xml:space="preserve">13.7330093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6553964614868</t>
+    <t xml:space="preserve">13.6553955078125</t>
   </si>
   <si>
     <t xml:space="preserve">13.6143064498901</t>
@@ -5225,19 +5225,19 @@
     <t xml:space="preserve">13.6964855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8151893615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7695341110229</t>
+    <t xml:space="preserve">13.8151884078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7695331573486</t>
   </si>
   <si>
     <t xml:space="preserve">13.6462640762329</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3632049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6599617004395</t>
+    <t xml:space="preserve">13.3632040023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6599607467651</t>
   </si>
   <si>
     <t xml:space="preserve">13.5823488235474</t>
@@ -5246,19 +5246,19 @@
     <t xml:space="preserve">13.637134552002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0708570480347</t>
+    <t xml:space="preserve">14.0708560943604</t>
   </si>
   <si>
     <t xml:space="preserve">14.0845527648926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0434627532959</t>
+    <t xml:space="preserve">14.0434637069702</t>
   </si>
   <si>
     <t xml:space="preserve">14.0480289459229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0252017974854</t>
+    <t xml:space="preserve">14.025200843811</t>
   </si>
   <si>
     <t xml:space="preserve">13.9658498764038</t>
@@ -5267,7 +5267,7 @@
     <t xml:space="preserve">13.9475879669189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9247608184814</t>
+    <t xml:space="preserve">13.9247598648071</t>
   </si>
   <si>
     <t xml:space="preserve">13.7877960205078</t>
@@ -5276,13 +5276,13 @@
     <t xml:space="preserve">13.7512722015381</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6736583709717</t>
+    <t xml:space="preserve">13.673659324646</t>
   </si>
   <si>
     <t xml:space="preserve">13.8380155563354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9612846374512</t>
+    <t xml:space="preserve">13.9612836837769</t>
   </si>
   <si>
     <t xml:space="preserve">13.9293251037598</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">13.7421417236328</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0936832427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0891180038452</t>
+    <t xml:space="preserve">14.0936841964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0891189575195</t>
   </si>
   <si>
     <t xml:space="preserve">13.8425817489624</t>
@@ -5336,19 +5336,19 @@
     <t xml:space="preserve">13.4362525939941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7740983963013</t>
+    <t xml:space="preserve">13.7740993499756</t>
   </si>
   <si>
     <t xml:space="preserve">13.682788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2125425338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3084182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0116605758667</t>
+    <t xml:space="preserve">13.2125434875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3084173202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.011661529541</t>
   </si>
   <si>
     <t xml:space="preserve">13.3586387634277</t>
@@ -5372,7 +5372,7 @@
     <t xml:space="preserve">14.2945652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4954462051392</t>
+    <t xml:space="preserve">14.4954471588135</t>
   </si>
   <si>
     <t xml:space="preserve">14.5045785903931</t>
@@ -5381,16 +5381,16 @@
     <t xml:space="preserve">14.2671728134155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9338912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0571584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0982494354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7969245910645</t>
+    <t xml:space="preserve">13.933892250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0571594238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0982484817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7969255447388</t>
   </si>
   <si>
     <t xml:space="preserve">14.9383001327515</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">15.2542324066162</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7830743789673</t>
+    <t xml:space="preserve">14.783073425293</t>
   </si>
   <si>
     <t xml:space="preserve">14.3228712081909</t>
@@ -5411,7 +5411,7 @@
     <t xml:space="preserve">14.585844039917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6917638778687</t>
+    <t xml:space="preserve">14.6917629241943</t>
   </si>
   <si>
     <t xml:space="preserve">14.9063415527344</t>
@@ -5420,7 +5420,7 @@
     <t xml:space="preserve">14.7008943557739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7191572189331</t>
+    <t xml:space="preserve">14.7191581726074</t>
   </si>
   <si>
     <t xml:space="preserve">14.1302080154419</t>
@@ -6666,6 +6666,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.7550001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7650003433228</t>
   </si>
 </sst>
 </file>
@@ -71666,7 +71669,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6525462963</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>1680929</v>
@@ -71687,6 +71690,32 @@
         <v>2217</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6524421296</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>2014141</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>14.7799997329712</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>14.5749998092651</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>14.7049999237061</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>14.7650003433228</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2218</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -38,52 +38,52 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87406969070435</t>
+    <t xml:space="preserve">7.8740701675415</t>
   </si>
   <si>
     <t xml:space="preserve">TEN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88864994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69909238815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48036766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19602584838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11582660675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07937335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12311697006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07208204269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62734317779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.569016456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77680349349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3940372467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63463354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80596828460693</t>
+    <t xml:space="preserve">7.88865089416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69909000396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48036670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19602394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11582851409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07937145233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12311887741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07208061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62734270095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56901597976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77680444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39403629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63463401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80596780776978</t>
   </si>
   <si>
     <t xml:space="preserve">6.78044939041138</t>
@@ -92,301 +92,301 @@
     <t xml:space="preserve">6.88981056213379</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91168212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82783842086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49246215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51433515548706</t>
+    <t xml:space="preserve">6.91168403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82783985137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49246168136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5143346786499</t>
   </si>
   <si>
     <t xml:space="preserve">7.03562831878662</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43413543701172</t>
+    <t xml:space="preserve">6.43413496017456</t>
   </si>
   <si>
     <t xml:space="preserve">6.29925680160522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80232191085815</t>
+    <t xml:space="preserve">6.80232048034668</t>
   </si>
   <si>
     <t xml:space="preserve">6.9554271697998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7403507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1486349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06114625930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8314847946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11947059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86064767837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54349851608276</t>
+    <t xml:space="preserve">6.74034786224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14863443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06114530563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148622512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11947202682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8606481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54349803924561</t>
   </si>
   <si>
     <t xml:space="preserve">6.55443429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16686105728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3272590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50223922729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45120334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61159992218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91781425476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00530433654785</t>
+    <t xml:space="preserve">7.16686201095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32726144790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50223779678345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45120477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61160039901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9178147315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00530529022217</t>
   </si>
   <si>
     <t xml:space="preserve">7.71367216110229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85948753356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58972978591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82303380966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73554420471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9615592956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81574535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77928924560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95426893234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72096347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66992807388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98343086242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032369613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53140115737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263961791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64076471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07821369171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11466693878174</t>
+    <t xml:space="preserve">7.85948801040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5897274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82303333282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7355432510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96156120300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81574392318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77928972244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95426940917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72096395492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66992855072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98343372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53140258789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66263675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6407642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07821178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11466598510742</t>
   </si>
   <si>
     <t xml:space="preserve">8.17299461364746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4208812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41358947753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45004177093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69793128967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82916355133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86561870574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91665458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63960361480713</t>
+    <t xml:space="preserve">8.42088031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41358852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45004558563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69792938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8291654586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86561965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91665554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63960552215576</t>
   </si>
   <si>
     <t xml:space="preserve">8.8000020980835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80729198455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58856964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47191619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01988506317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97614145278931</t>
+    <t xml:space="preserve">8.80729293823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58856868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47191715240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0198860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97614097595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.39900779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24589920043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21673774719238</t>
+    <t xml:space="preserve">8.24590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21673965454102</t>
   </si>
   <si>
     <t xml:space="preserve">8.29693698883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30422782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45733547210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64689540863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67605686187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3917179107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5666971206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62655067443848</t>
+    <t xml:space="preserve">8.30422592163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4573335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64689636230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67605876922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39171695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56669521331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62654972076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.73129653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75374412536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.978196144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98567771911621</t>
+    <t xml:space="preserve">8.75374221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95575141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97819709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98568058013916</t>
   </si>
   <si>
     <t xml:space="preserve">8.91086101531982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80611610412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67892456054688</t>
+    <t xml:space="preserve">8.80611515045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67892169952393</t>
   </si>
   <si>
     <t xml:space="preserve">8.64899730682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08294200897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53185176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69645309448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52437114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49444389343262</t>
+    <t xml:space="preserve">9.0829439163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53185272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69645118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52436923980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4944429397583</t>
   </si>
   <si>
     <t xml:space="preserve">9.28495216369629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1577615737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34480667114258</t>
+    <t xml:space="preserve">9.15775966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34480762481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.17272472381592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40466117858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66652584075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42710781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80119705200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30739784240723</t>
+    <t xml:space="preserve">9.40466213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66652488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4271068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80119895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30739593505859</t>
   </si>
   <si>
     <t xml:space="preserve">9.04553318023682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14279747009277</t>
+    <t xml:space="preserve">9.14279556274414</t>
   </si>
   <si>
     <t xml:space="preserve">9.6141529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73386287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86853504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83112621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59918880462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32235908508301</t>
+    <t xml:space="preserve">9.73386096954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86853408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83112716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59918785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32236099243164</t>
   </si>
   <si>
     <t xml:space="preserve">9.39717960357666</t>
@@ -395,40 +395,40 @@
     <t xml:space="preserve">9.50940704345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65904426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74882507324219</t>
+    <t xml:space="preserve">9.65904140472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74882316589355</t>
   </si>
   <si>
     <t xml:space="preserve">9.47947978973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59170818328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21761417388916</t>
+    <t xml:space="preserve">9.59170627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21761512756348</t>
   </si>
   <si>
     <t xml:space="preserve">9.37473392486572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18768882751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06798076629639</t>
+    <t xml:space="preserve">9.18768978118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06797981262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.16524314880371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0979061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82856178283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94826793670654</t>
+    <t xml:space="preserve">9.09790515899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8285608291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94827079772949</t>
   </si>
   <si>
     <t xml:space="preserve">8.70885181427002</t>
@@ -437,61 +437,61 @@
     <t xml:space="preserve">8.57417869567871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00064182281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19516944885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38969802856445</t>
+    <t xml:space="preserve">8.74626159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00064277648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19516849517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38969707489014</t>
   </si>
   <si>
     <t xml:space="preserve">9.36725234985352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48696136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70393466949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65156269073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62911605834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51688671112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45703506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09042644500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22509574890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29991626739502</t>
+    <t xml:space="preserve">9.48696231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70393562316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65156173706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62911796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51688766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45703411102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09042453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2999153137207</t>
   </si>
   <si>
     <t xml:space="preserve">9.10538768768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85848617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66396045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71633434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88093090057373</t>
+    <t xml:space="preserve">8.85848712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66395950317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71633243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88093376159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.76870536804199</t>
@@ -503,64 +503,64 @@
     <t xml:space="preserve">8.69388771057129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90337657928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7013692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44698619842529</t>
+    <t xml:space="preserve">8.90337944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70136833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44698810577393</t>
   </si>
   <si>
     <t xml:space="preserve">8.55921363830566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35977077484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50192356109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64408206939697</t>
+    <t xml:space="preserve">9.35976982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50192642211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64408016204834</t>
   </si>
   <si>
     <t xml:space="preserve">9.76379013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74134635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95083522796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63659763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83860492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81616115570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94335269927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0406169891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99572467803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0106906890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96579837799072</t>
+    <t xml:space="preserve">9.74134540557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95083618164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6365966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83860683441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.816162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94335174560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0406179428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99572372436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0106887817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96579742431641</t>
   </si>
   <si>
     <t xml:space="preserve">10.0630617141724</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77127361297607</t>
+    <t xml:space="preserve">9.77126979827881</t>
   </si>
   <si>
     <t xml:space="preserve">9.89846134185791</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">9.29243469238281</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2800359725952</t>
+    <t xml:space="preserve">10.2800350189209</t>
   </si>
   <si>
     <t xml:space="preserve">10.6765727996826</t>
@@ -584,97 +584,97 @@
     <t xml:space="preserve">10.8112459182739</t>
   </si>
   <si>
-    <t xml:space="preserve">10.938437461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9309520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9159898757935</t>
+    <t xml:space="preserve">10.9384346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9309549331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9159908294678</t>
   </si>
   <si>
     <t xml:space="preserve">10.7214632034302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1216297149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8045177459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0310249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0687789916992</t>
+    <t xml:space="preserve">11.1216316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8045167922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.03102684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0687780380249</t>
   </si>
   <si>
     <t xml:space="preserve">10.8347187042236</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6761608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3783416748047</t>
+    <t xml:space="preserve">10.6761617660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3783397674561</t>
   </si>
   <si>
     <t xml:space="preserve">11.8464622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7407579421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0352201461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1937761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0805234909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2239789962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.556191444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3749837875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2919321060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4202871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3145818710327</t>
+    <t xml:space="preserve">11.7407569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0352191925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1937780380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0805225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2239770889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5561933517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3749828338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2919311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4202890396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3145837783813</t>
   </si>
   <si>
     <t xml:space="preserve">12.3674345016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5410947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4504871368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5939455032349</t>
+    <t xml:space="preserve">12.5410928726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4504880905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5939464569092</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9790115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0016622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8129034042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0243120193481</t>
+    <t xml:space="preserve">12.9790134429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0016613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8129043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0243139266968</t>
   </si>
   <si>
     <t xml:space="preserve">12.9714612960815</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">12.9488105773926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8808546066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8657560348511</t>
+    <t xml:space="preserve">12.8808574676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8657569885254</t>
   </si>
   <si>
     <t xml:space="preserve">12.7751522064209</t>
@@ -698,70 +698,70 @@
     <t xml:space="preserve">12.8204536437988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7600517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.533543586731</t>
+    <t xml:space="preserve">12.7600507736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5335397720337</t>
   </si>
   <si>
     <t xml:space="preserve">12.7676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6996479034424</t>
+    <t xml:space="preserve">12.8582048416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6996488571167</t>
   </si>
   <si>
     <t xml:space="preserve">12.6618986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9865627288818</t>
+    <t xml:space="preserve">12.9865636825562</t>
   </si>
   <si>
     <t xml:space="preserve">13.0092115402222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8506555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2164306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2088775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1258230209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2843818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1182737350464</t>
+    <t xml:space="preserve">12.8506565093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2164287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2088785171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1258239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2843809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1182727813721</t>
   </si>
   <si>
     <t xml:space="preserve">12.148476600647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8766622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0729722976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560287475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2541799545288</t>
+    <t xml:space="preserve">11.8766632080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0729713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560258865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2541818618774</t>
   </si>
   <si>
     <t xml:space="preserve">11.9748163223267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8540096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1862268447876</t>
+    <t xml:space="preserve">11.8540124893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1862258911133</t>
   </si>
   <si>
     <t xml:space="preserve">12.2390794754028</t>
@@ -770,31 +770,31 @@
     <t xml:space="preserve">11.786060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7256555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9068641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6652555465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5142488479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5444488525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613971710205</t>
+    <t xml:space="preserve">11.7256574630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9068660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6652536392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5142469406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5444498062134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613952636719</t>
   </si>
   <si>
     <t xml:space="preserve">11.0989799499512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1140804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593818664551</t>
+    <t xml:space="preserve">11.1140794754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593837738037</t>
   </si>
   <si>
     <t xml:space="preserve">11.0763292312622</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">11.3330402374268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4085426330566</t>
+    <t xml:space="preserve">11.4085445404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.4991474151611</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2952890396118</t>
+    <t xml:space="preserve">11.2952871322632</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442813873291</t>
@@ -818,25 +818,25 @@
     <t xml:space="preserve">11.1669330596924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2424364089966</t>
+    <t xml:space="preserve">11.2424354553223</t>
   </si>
   <si>
     <t xml:space="preserve">10.993275642395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8389110565186</t>
+    <t xml:space="preserve">11.8389120101929</t>
   </si>
   <si>
     <t xml:space="preserve">11.763409614563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.133373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0427703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2013282775879</t>
+    <t xml:space="preserve">12.1333742141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0427713394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2013273239136</t>
   </si>
   <si>
     <t xml:space="preserve">12.1786756515503</t>
@@ -845,94 +845,94 @@
     <t xml:space="preserve">11.9370670318604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.385892868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4840459823608</t>
+    <t xml:space="preserve">11.3858938217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4840450286865</t>
   </si>
   <si>
     <t xml:space="preserve">11.2801876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3481407165527</t>
+    <t xml:space="preserve">11.3481397628784</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556909561157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3405904769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066995620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8724689483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8573684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9026699066162</t>
+    <t xml:space="preserve">11.3405895233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8724708557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8573703765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9026718139648</t>
   </si>
   <si>
     <t xml:space="preserve">10.7894172668457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4949541091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6535120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6459617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.661060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.827166557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8800210952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7441158294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9781732559204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7139129638672</t>
+    <t xml:space="preserve">10.4949531555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6535110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6459608078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6610622406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8271684646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8800201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7441148757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.978175163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7139139175415</t>
   </si>
   <si>
     <t xml:space="preserve">10.8951206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0183162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721193313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0260181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9259204864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7642259597778</t>
+    <t xml:space="preserve">11.0183153152466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721164703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0260162353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9259195327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7642230987549</t>
   </si>
   <si>
     <t xml:space="preserve">10.6410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6025314331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3561372756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4793357849121</t>
+    <t xml:space="preserve">10.6025304794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3561401367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4793367385864</t>
   </si>
   <si>
     <t xml:space="preserve">10.4408388137817</t>
@@ -944,106 +944,106 @@
     <t xml:space="preserve">10.2406435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4023370742798</t>
+    <t xml:space="preserve">10.4023380279541</t>
   </si>
   <si>
     <t xml:space="preserve">10.7873249053955</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4947347640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5409336090088</t>
+    <t xml:space="preserve">10.4947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5409326553345</t>
   </si>
   <si>
     <t xml:space="preserve">10.3176403045654</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3715410232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2791423797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2868413925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3330392837524</t>
+    <t xml:space="preserve">10.3715400695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2791433334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2868394851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3330421447754</t>
   </si>
   <si>
     <t xml:space="preserve">10.5101337432861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8335218429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8566236495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7103261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6179294586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3407421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4716348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7796239852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9105215072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0106191635132</t>
+    <t xml:space="preserve">10.8335227966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8566226959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7103271484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6179304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3407411575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4716367721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7796258926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9105205535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0106182098389</t>
   </si>
   <si>
     <t xml:space="preserve">10.9413204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7565250396729</t>
+    <t xml:space="preserve">10.7565259933472</t>
   </si>
   <si>
     <t xml:space="preserve">10.5255346298218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6256284713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3099412918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0943479537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99425411224365</t>
+    <t xml:space="preserve">10.6256313323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3099422454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0943470001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9942512512207</t>
   </si>
   <si>
     <t xml:space="preserve">9.27047824859619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34747409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20887756347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29357624053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16267871856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22427845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9778881072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00868892669678</t>
+    <t xml:space="preserve">9.34747505187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2088794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29357528686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16268062591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22427940368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97788619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00868606567383</t>
   </si>
   <si>
     <t xml:space="preserve">8.96248817443848</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">8.92398929595947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87779140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80079364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85469245910645</t>
+    <t xml:space="preserve">8.87778949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80079460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85469150543213</t>
   </si>
   <si>
     <t xml:space="preserve">8.82389354705811</t>
@@ -1067,55 +1067,55 @@
     <t xml:space="preserve">8.7853946685791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72379684448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63909912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52360153198242</t>
+    <t xml:space="preserve">8.72379779815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63909816741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52360343933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.62369918823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6467981338501</t>
+    <t xml:space="preserve">8.64679908752441</t>
   </si>
   <si>
     <t xml:space="preserve">8.60830020904541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7468957901001</t>
+    <t xml:space="preserve">8.74689483642578</t>
   </si>
   <si>
     <t xml:space="preserve">9.03178691864014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11648082733154</t>
+    <t xml:space="preserve">9.11648273468018</t>
   </si>
   <si>
     <t xml:space="preserve">9.13188171386719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93169116973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15498065948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37827301025391</t>
+    <t xml:space="preserve">8.93169021606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15498161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37827205657959</t>
   </si>
   <si>
     <t xml:space="preserve">9.30127620697021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32437324523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33207702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27817630767822</t>
+    <t xml:space="preserve">9.32437515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33207416534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27817821502686</t>
   </si>
   <si>
     <t xml:space="preserve">9.26277732849121</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">9.24737739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23967933654785</t>
+    <t xml:space="preserve">9.23967838287354</t>
   </si>
   <si>
     <t xml:space="preserve">9.20118045806885</t>
@@ -1133,94 +1133,94 @@
     <t xml:space="preserve">9.10878276824951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87009143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84699249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95478916168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73919486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63140106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65449714660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70839500427246</t>
+    <t xml:space="preserve">8.87009239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8469934463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95479011535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73919773101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63139915466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65449810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70839881896973</t>
   </si>
   <si>
     <t xml:space="preserve">8.79309368133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00098609924316</t>
+    <t xml:space="preserve">9.00098705291748</t>
   </si>
   <si>
     <t xml:space="preserve">9.04718589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0558519363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1328477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1020469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0173540115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.940354347229</t>
+    <t xml:space="preserve">10.0558490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1328468322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1020479202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0173511505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94035339355469</t>
   </si>
   <si>
     <t xml:space="preserve">9.82485771179199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70166301727295</t>
+    <t xml:space="preserve">9.70166206359863</t>
   </si>
   <si>
     <t xml:space="preserve">9.45527076721191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30897521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33977508544922</t>
+    <t xml:space="preserve">9.3089771270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3397741317749</t>
   </si>
   <si>
     <t xml:space="preserve">9.41760635375977</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72892951965332</t>
+    <t xml:space="preserve">9.72893333435059</t>
   </si>
   <si>
     <t xml:space="preserve">9.6744499206543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44095516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43317317962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50322151184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69779872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91572666168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80676364898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6433162689209</t>
+    <t xml:space="preserve">9.44095611572266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43317413330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5032205581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69779968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91572761535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80676460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64331722259521</t>
   </si>
   <si>
     <t xml:space="preserve">9.76784801483154</t>
@@ -1229,31 +1229,31 @@
     <t xml:space="preserve">9.86124610900879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4371976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1881380081177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.048041343689</t>
+    <t xml:space="preserve">10.13365650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4372005462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1881370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0480403900146</t>
   </si>
   <si>
     <t xml:space="preserve">9.95464324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1492223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0324745178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1570062637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3126678466797</t>
+    <t xml:space="preserve">10.1492214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0324754714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1570053100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.312668800354</t>
   </si>
   <si>
     <t xml:space="preserve">10.3905000686646</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">10.3438005447388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2426204681396</t>
+    <t xml:space="preserve">10.2426195144653</t>
   </si>
   <si>
     <t xml:space="preserve">10.4294147491455</t>
@@ -1274,103 +1274,103 @@
     <t xml:space="preserve">10.5928621292114</t>
   </si>
   <si>
-    <t xml:space="preserve">10.68625831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6784763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9508848190308</t>
+    <t xml:space="preserve">10.6862573623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6784753799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9508867263794</t>
   </si>
   <si>
     <t xml:space="preserve">11.0520677566528</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1143312454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8886213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8341388702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9975862503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0831995010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2933435440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3011264801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1843786239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2544279098511</t>
+    <t xml:space="preserve">11.1143321990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8886222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8341398239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9975843429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0831985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.293345451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3011274337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1843776702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2544288635254</t>
   </si>
   <si>
     <t xml:space="preserve">11.3166942596436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610288619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9586687088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9158611297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7018260955811</t>
+    <t xml:space="preserve">11.1610317230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.958667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9158601760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7018241882324</t>
   </si>
   <si>
     <t xml:space="preserve">10.5850772857666</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3048839569092</t>
+    <t xml:space="preserve">10.3048830032349</t>
   </si>
   <si>
     <t xml:space="preserve">10.456657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0519323348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99355888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90016174316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0636072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1180896759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2620782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5734052658081</t>
+    <t xml:space="preserve">10.0519332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99355792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90016269683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.063606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.118088722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.262077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5734024047852</t>
   </si>
   <si>
     <t xml:space="preserve">10.6668014526367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5461616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8730535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.347825050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2427539825439</t>
+    <t xml:space="preserve">10.5461626052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8730545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3478288650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2427520751953</t>
   </si>
   <si>
     <t xml:space="preserve">10.9469957351685</t>
@@ -1379,40 +1379,40 @@
     <t xml:space="preserve">11.0909833908081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1493558883667</t>
+    <t xml:space="preserve">11.1493577957153</t>
   </si>
   <si>
     <t xml:space="preserve">11.0209331512451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3050184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7175254821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5462970733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4645719528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1999473571777</t>
+    <t xml:space="preserve">11.3050174713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7175245285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5462980270386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4645748138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1999483108521</t>
   </si>
   <si>
     <t xml:space="preserve">11.1026573181152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2777757644653</t>
+    <t xml:space="preserve">11.277777671814</t>
   </si>
   <si>
     <t xml:space="preserve">11.1376810073853</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3594999313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7642250061035</t>
+    <t xml:space="preserve">11.3595008850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7642240524292</t>
   </si>
   <si>
     <t xml:space="preserve">11.0442838668823</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">10.596752166748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6239948272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7640924453735</t>
+    <t xml:space="preserve">10.6239919662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7640886306763</t>
   </si>
   <si>
     <t xml:space="preserve">10.6473436355591</t>
@@ -1433,25 +1433,25 @@
     <t xml:space="preserve">10.8574876785278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8964023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8263559341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3244752883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0987682342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1298990249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451160430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6435871124268</t>
+    <t xml:space="preserve">10.8964033126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8263549804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3244762420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.09876537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1298980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4451150894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6435852050781</t>
   </si>
   <si>
     <t xml:space="preserve">11.6708269119263</t>
@@ -1460,31 +1460,31 @@
     <t xml:space="preserve">11.5929956436157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5813217163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8654069900513</t>
+    <t xml:space="preserve">11.58131980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8654050827026</t>
   </si>
   <si>
     <t xml:space="preserve">11.9004306793213</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0716590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1611633300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8926458358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9393463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8381643295288</t>
+    <t xml:space="preserve">12.0716600418091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1611642837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8926467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9393453598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8381633758545</t>
   </si>
   <si>
     <t xml:space="preserve">12.1183576583862</t>
@@ -1493,58 +1493,58 @@
     <t xml:space="preserve">12.5425386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5308666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5581073760986</t>
+    <t xml:space="preserve">12.5308637619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5581064224243</t>
   </si>
   <si>
     <t xml:space="preserve">12.8344078063965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5542116165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7604675292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6631803512573</t>
+    <t xml:space="preserve">12.5542125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7604684829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6631784439087</t>
   </si>
   <si>
     <t xml:space="preserve">12.7059860229492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6437206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.702094078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355878829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3597679138184</t>
+    <t xml:space="preserve">12.6437196731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7020931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355897903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3597707748413</t>
   </si>
   <si>
     <t xml:space="preserve">13.3052854537964</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4556293487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4635410308838</t>
+    <t xml:space="preserve">13.4556303024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4635429382324</t>
   </si>
   <si>
     <t xml:space="preserve">13.1549453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8661308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5496187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.419059753418</t>
+    <t xml:space="preserve">12.8661317825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5496206283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4190587997437</t>
   </si>
   <si>
     <t xml:space="preserve">12.4863176345825</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">12.5535764694214</t>
   </si>
   <si>
-    <t xml:space="preserve">12.146071434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2964105606079</t>
+    <t xml:space="preserve">12.1460704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2964115142822</t>
   </si>
   <si>
     <t xml:space="preserve">12.0392475128174</t>
@@ -1565,76 +1565,76 @@
     <t xml:space="preserve">11.9996843338013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3478450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3122367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3953199386597</t>
+    <t xml:space="preserve">12.3478441238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3122386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.395320892334</t>
   </si>
   <si>
     <t xml:space="preserve">12.4230165481567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2726726531982</t>
+    <t xml:space="preserve">12.2726745605469</t>
   </si>
   <si>
     <t xml:space="preserve">12.4784059524536</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9007730484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205570220947</t>
+    <t xml:space="preserve">11.9007749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205560684204</t>
   </si>
   <si>
     <t xml:space="preserve">11.797908782959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8374738693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4111480712891</t>
+    <t xml:space="preserve">11.8374719619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4111471176147</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809938430786</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9284687042236</t>
+    <t xml:space="preserve">11.9284677505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.5377511978149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4665384292603</t>
+    <t xml:space="preserve">12.4665365219116</t>
   </si>
   <si>
     <t xml:space="preserve">12.4348850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755378723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5733575820923</t>
+    <t xml:space="preserve">12.3755397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5733604431152</t>
   </si>
   <si>
     <t xml:space="preserve">12.6089649200439</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6050100326538</t>
+    <t xml:space="preserve">12.6050071716309</t>
   </si>
   <si>
     <t xml:space="preserve">12.6683111190796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9927339553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520811080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6762237548828</t>
+    <t xml:space="preserve">12.992733001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6762256622314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7355690002441</t>
@@ -1643,28 +1643,28 @@
     <t xml:space="preserve">12.6010541915894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5456628799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5575313568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4546680450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4586229324341</t>
+    <t xml:space="preserve">12.5456619262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5575332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4546670913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4586238861084</t>
   </si>
   <si>
     <t xml:space="preserve">12.2489356994629</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3201522827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3676261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.596134185791</t>
+    <t xml:space="preserve">12.3201513290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3676252365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5961332321167</t>
   </si>
   <si>
     <t xml:space="preserve">11.7623014450073</t>
@@ -1673,73 +1673,73 @@
     <t xml:space="preserve">11.7702150344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9759473800659</t>
+    <t xml:space="preserve">11.9759454727173</t>
   </si>
   <si>
     <t xml:space="preserve">11.9324254989624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0273771286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8216466903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5328302383423</t>
+    <t xml:space="preserve">12.027379989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8216457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.532829284668</t>
   </si>
   <si>
     <t xml:space="preserve">11.4418354034424</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5170078277588</t>
+    <t xml:space="preserve">11.5170068740845</t>
   </si>
   <si>
     <t xml:space="preserve">11.6159162521362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5921773910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7148237228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0867252349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8889064788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8928632736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2281904220581</t>
+    <t xml:space="preserve">11.5921754837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7148246765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0867233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8889055252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.892861366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2281913757324</t>
   </si>
   <si>
     <t xml:space="preserve">11.4339227676392</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4062280654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3310565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9947671890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9037675857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7257328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6901245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9433317184448</t>
+    <t xml:space="preserve">11.4062271118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3310556411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9947652816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9037666320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7257318496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6901235580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9433307647705</t>
   </si>
   <si>
     <t xml:space="preserve">10.9314622879028</t>
@@ -1748,94 +1748,94 @@
     <t xml:space="preserve">10.9354190826416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.998722076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1451063156128</t>
+    <t xml:space="preserve">10.9987230300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1451053619385</t>
   </si>
   <si>
     <t xml:space="preserve">11.1530199050903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0857591629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1174125671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7306499481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6396551132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.584264755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4180965423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.726692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9482517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6277828216553</t>
+    <t xml:space="preserve">11.0857610702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066328048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.117413520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7306509017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6396541595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5842628479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4180974960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7266941070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9482507705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6277837753296</t>
   </si>
   <si>
     <t xml:space="preserve">11.572395324707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9601202011108</t>
+    <t xml:space="preserve">11.9601182937622</t>
   </si>
   <si>
     <t xml:space="preserve">11.6238279342651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1332387924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.141149520874</t>
+    <t xml:space="preserve">11.1332406997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1411504745483</t>
   </si>
   <si>
     <t xml:space="preserve">11.1886262893677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3112754821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2400588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0936737060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.081805229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8325538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4052639007568</t>
+    <t xml:space="preserve">11.3112745285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2400608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.093674659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0818042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8325529098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4052648544312</t>
   </si>
   <si>
     <t xml:space="preserve">10.2984428405762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2628345489502</t>
+    <t xml:space="preserve">10.2628364562988</t>
   </si>
   <si>
     <t xml:space="preserve">10.1718378067017</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2034912109375</t>
+    <t xml:space="preserve">10.2034893035889</t>
   </si>
   <si>
     <t xml:space="preserve">10.0927114486694</t>
@@ -1847,19 +1847,19 @@
     <t xml:space="preserve">10.5635204315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6268215179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6307773590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6189079284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.520001411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4843912124634</t>
+    <t xml:space="preserve">10.62682056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6307783126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6189088821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4843940734863</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430543899536</t>
@@ -1871,43 +1871,43 @@
     <t xml:space="preserve">9.85137176513672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75642013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8751106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7801570892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68019771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40830516815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58823204040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45228576660156</t>
+    <t xml:space="preserve">9.75641822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87511157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78015899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68019580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40830421447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58823299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45228481292725</t>
   </si>
   <si>
     <t xml:space="preserve">9.29634761810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5602445602417</t>
+    <t xml:space="preserve">9.56024360656738</t>
   </si>
   <si>
     <t xml:space="preserve">9.38031387329102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71657562255859</t>
+    <t xml:space="preserve">8.71657466888428</t>
   </si>
   <si>
     <t xml:space="preserve">8.66059684753418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49666118621826</t>
+    <t xml:space="preserve">8.49666213989258</t>
   </si>
   <si>
     <t xml:space="preserve">8.78854656219482</t>
@@ -1916,58 +1916,58 @@
     <t xml:space="preserve">8.67259311676025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50865745544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2287654876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24875831604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99685955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10881614685059</t>
+    <t xml:space="preserve">8.50865840911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22876644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24875736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99685716629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10881519317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.20077800750732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1807861328125</t>
+    <t xml:space="preserve">8.18078708648682</t>
   </si>
   <si>
     <t xml:space="preserve">7.89130020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71217060089111</t>
+    <t xml:space="preserve">7.71217012405396</t>
   </si>
   <si>
     <t xml:space="preserve">7.71376943588257</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38109922409058</t>
+    <t xml:space="preserve">7.38110113143921</t>
   </si>
   <si>
     <t xml:space="preserve">7.39389562606812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34271574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5490345954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61140823364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5986156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88490152359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01285171508789</t>
+    <t xml:space="preserve">7.3427152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54903364181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61141014099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59861516952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88490104675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01285266876221</t>
   </si>
   <si>
     <t xml:space="preserve">8.05683326721191</t>
@@ -1979,61 +1979,61 @@
     <t xml:space="preserve">8.31673240661621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24076366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16879177093506</t>
+    <t xml:space="preserve">8.24076175689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878986358643</t>
   </si>
   <si>
     <t xml:space="preserve">8.22476863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52065277099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45268058776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32073211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39670276641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53264713287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82453346252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58862495422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70058345794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75655937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93249130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98846817016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76455688476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5646333694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74456405639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95248413085938</t>
+    <t xml:space="preserve">8.52065181732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45267868041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3207311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39670085906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53264999389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8245325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58862590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70058155059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76855564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75655841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93249034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9884672164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76455593109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56463718414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7445650100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95248222351074</t>
   </si>
   <si>
     <t xml:space="preserve">9.20838260650635</t>
@@ -2042,10 +2042,10 @@
     <t xml:space="preserve">9.22037792205811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43629264831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49227046966553</t>
+    <t xml:space="preserve">9.43629360198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49227142333984</t>
   </si>
   <si>
     <t xml:space="preserve">9.55224704742432</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">9.59622955322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75616836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63221740722656</t>
+    <t xml:space="preserve">9.75616645812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63221645355225</t>
   </si>
   <si>
     <t xml:space="preserve">9.61622142791748</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">9.51226329803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33233547210693</t>
+    <t xml:space="preserve">9.3323335647583</t>
   </si>
   <si>
     <t xml:space="preserve">9.39231014251709</t>
@@ -2078,22 +2078,22 @@
     <t xml:space="preserve">9.36432075500488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48427486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25236415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11242198944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4202995300293</t>
+    <t xml:space="preserve">9.48427295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25236511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11242008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42029857635498</t>
   </si>
   <si>
     <t xml:space="preserve">9.84413242340088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8961124420166</t>
+    <t xml:space="preserve">9.89611053466797</t>
   </si>
   <si>
     <t xml:space="preserve">9.84813022613525</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">9.86812400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9840784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0360565185547</t>
+    <t xml:space="preserve">9.98407649993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.036057472229</t>
   </si>
   <si>
     <t xml:space="preserve">10.3079509735107</t>
@@ -2114,37 +2114,37 @@
     <t xml:space="preserve">10.2039909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0680456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82814025878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0080690383911</t>
+    <t xml:space="preserve">10.0680446624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82813835144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0080680847168</t>
   </si>
   <si>
     <t xml:space="preserve">10.2759637832642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.172004699707</t>
+    <t xml:space="preserve">10.1720027923584</t>
   </si>
   <si>
     <t xml:space="preserve">10.1440143585205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95608711242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.255970954895</t>
+    <t xml:space="preserve">9.95608997344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2559700012207</t>
   </si>
   <si>
     <t xml:space="preserve">10.3199443817139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0440549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93609619140625</t>
+    <t xml:space="preserve">10.0440530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93609714508057</t>
   </si>
   <si>
     <t xml:space="preserve">10.0040693283081</t>
@@ -2153,94 +2153,94 @@
     <t xml:space="preserve">10.0560483932495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3959159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5278644561768</t>
+    <t xml:space="preserve">10.3959150314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5278635025024</t>
   </si>
   <si>
     <t xml:space="preserve">10.427903175354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7917594909668</t>
+    <t xml:space="preserve">10.7917604446411</t>
   </si>
   <si>
     <t xml:space="preserve">10.559850692749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3359403610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92809867858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90010929107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74017429351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60422706604004</t>
+    <t xml:space="preserve">10.3359384536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9281005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90011119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74017333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60422801971436</t>
   </si>
   <si>
     <t xml:space="preserve">9.44029140472412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60822677612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41230201721191</t>
+    <t xml:space="preserve">9.60822582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41230392456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.34033012390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29234790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54025173187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61222553253174</t>
+    <t xml:space="preserve">9.29234886169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54025077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61222362518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.96408462524414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0160655975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0242462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1755685806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85656070709229</t>
+    <t xml:space="preserve">10.0160646438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.024245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1755695343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85655975341797</t>
   </si>
   <si>
     <t xml:space="preserve">9.4393949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32487773895264</t>
+    <t xml:space="preserve">9.32488059997559</t>
   </si>
   <si>
     <t xml:space="preserve">9.16128444671631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15310382843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01405048370361</t>
+    <t xml:space="preserve">9.15310478210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0140495300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.98542022705078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62960433959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87499618530273</t>
+    <t xml:space="preserve">8.62960338592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8749942779541</t>
   </si>
   <si>
     <t xml:space="preserve">9.08766651153564</t>
@@ -2249,49 +2249,49 @@
     <t xml:space="preserve">8.78910732269287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79728603363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06312656402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19809436798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9445219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8340950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87908267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05085754394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29624938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39440631866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25126171112061</t>
+    <t xml:space="preserve">8.79728698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78092861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06312847137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19809341430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94452285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83409595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87908458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05085945129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29624843597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39440536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25126075744629</t>
   </si>
   <si>
     <t xml:space="preserve">9.14901542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4230375289917</t>
+    <t xml:space="preserve">9.42303562164307</t>
   </si>
   <si>
     <t xml:space="preserve">9.38213729858398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41485786437988</t>
+    <t xml:space="preserve">9.41485595703125</t>
   </si>
   <si>
     <t xml:space="preserve">9.65206718444824</t>
@@ -2303,82 +2303,82 @@
     <t xml:space="preserve">9.44757556915283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54573154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5416431427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75431442260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66024780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80748176574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98743629455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94244766235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83202266693115</t>
+    <t xml:space="preserve">9.54573059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54164028167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75431346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66024875640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80748271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98743724822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94244861602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83202171325684</t>
   </si>
   <si>
     <t xml:space="preserve">9.82793235778809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45166492462158</t>
+    <t xml:space="preserve">9.45166397094727</t>
   </si>
   <si>
     <t xml:space="preserve">9.28806972503662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12038421630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24308204650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31260776519775</t>
+    <t xml:space="preserve">9.12038516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24308300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31260967254639</t>
   </si>
   <si>
     <t xml:space="preserve">9.59071922302246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50892353057861</t>
+    <t xml:space="preserve">9.5089225769043</t>
   </si>
   <si>
     <t xml:space="preserve">9.26762199401855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93225288391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71549034118652</t>
+    <t xml:space="preserve">8.93225383758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71548938751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.56416511535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36376285552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2942361831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44555950164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787303924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0095796585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14209079742432</t>
+    <t xml:space="preserve">8.3637638092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29423427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44556140899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787399291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00958156585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14209175109863</t>
   </si>
   <si>
     <t xml:space="preserve">7.71838188171387</t>
@@ -2390,43 +2390,43 @@
     <t xml:space="preserve">8.05211448669434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88852024078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98340654373169</t>
+    <t xml:space="preserve">7.88852119445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98340511322021</t>
   </si>
   <si>
     <t xml:space="preserve">8.08810520172119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96377372741699</t>
+    <t xml:space="preserve">7.96377182006836</t>
   </si>
   <si>
     <t xml:space="preserve">8.07011032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12409496307373</t>
+    <t xml:space="preserve">8.12409687042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.21652698516846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16335773468018</t>
+    <t xml:space="preserve">8.16335678100586</t>
   </si>
   <si>
     <t xml:space="preserve">8.10937309265137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0652027130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86071062088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00467395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21243572235107</t>
+    <t xml:space="preserve">8.06520175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86070871353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00467300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21243858337402</t>
   </si>
   <si>
     <t xml:space="preserve">8.17153739929199</t>
@@ -2438,130 +2438,130 @@
     <t xml:space="preserve">8.51099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43737888336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31468296051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37194061279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60506534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44146919250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31877517700195</t>
+    <t xml:space="preserve">8.43738079071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31468486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37194156646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60506439208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44146633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31877326965332</t>
   </si>
   <si>
     <t xml:space="preserve">8.22061634063721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20016860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97195339202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85743761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85252904891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72983407974243</t>
+    <t xml:space="preserve">8.20016765594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97195386886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85743713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85252952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72983455657959</t>
   </si>
   <si>
     <t xml:space="preserve">8.00794410705566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96213817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81326818466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48771524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56296682357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5482439994812</t>
+    <t xml:space="preserve">7.96213865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81326723098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48771476745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56296825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54824352264404</t>
   </si>
   <si>
     <t xml:space="preserve">7.63658618927002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50898122787476</t>
+    <t xml:space="preserve">7.5089807510376</t>
   </si>
   <si>
     <t xml:space="preserve">7.54333639144897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61531734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88034152984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67257452011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77400541305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74292135238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64803600311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60713720321655</t>
+    <t xml:space="preserve">7.61531829833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88034105300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67257690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77400493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74292182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64803695678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60713911056519</t>
   </si>
   <si>
     <t xml:space="preserve">7.66276073455811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68239116668701</t>
+    <t xml:space="preserve">7.68239164352417</t>
   </si>
   <si>
     <t xml:space="preserve">7.70202398300171</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61859035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69220638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80999565124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8852481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65785217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40591669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03739166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17644596099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32286357879639</t>
+    <t xml:space="preserve">7.61858987808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69220733642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80999517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88524961471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65785264968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40591812133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03739261627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17644691467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3228645324707</t>
   </si>
   <si>
     <t xml:space="preserve">8.18380737304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19607925415039</t>
+    <t xml:space="preserve">8.19607830047607</t>
   </si>
   <si>
     <t xml:space="preserve">8.23697662353516</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">8.0995569229126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02993488311768</t>
+    <t xml:space="preserve">8.02993202209473</t>
   </si>
   <si>
     <t xml:space="preserve">7.95865201950073</t>
@@ -2585,16 +2585,16 @@
     <t xml:space="preserve">8.0896110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04153728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16918087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15094375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591812133789</t>
+    <t xml:space="preserve">8.04153633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16917991638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15094566345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15592002868652</t>
   </si>
   <si>
     <t xml:space="preserve">8.08629608154297</t>
@@ -2603,103 +2603,103 @@
     <t xml:space="preserve">8.00009632110596</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85587406158447</t>
+    <t xml:space="preserve">7.85587358474731</t>
   </si>
   <si>
     <t xml:space="preserve">7.80116939544678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96694087982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03987789154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21228122711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24377822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26864433288574</t>
+    <t xml:space="preserve">7.96694040298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03987884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21227931976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24377727508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26864242553711</t>
   </si>
   <si>
     <t xml:space="preserve">8.29682445526123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53304767608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44187545776367</t>
+    <t xml:space="preserve">8.53304862976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44187259674072</t>
   </si>
   <si>
     <t xml:space="preserve">8.4625940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40871906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3921422958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37970924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42944240570068</t>
+    <t xml:space="preserve">8.40872097015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39214324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3797082901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42944049835205</t>
   </si>
   <si>
     <t xml:space="preserve">8.49575042724609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36313152313232</t>
+    <t xml:space="preserve">8.36313343048096</t>
   </si>
   <si>
     <t xml:space="preserve">8.32997798919678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37142276763916</t>
+    <t xml:space="preserve">8.37142181396484</t>
   </si>
   <si>
     <t xml:space="preserve">8.48331546783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7112512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69881725311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68224239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60764408111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60349941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45016288757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40043163299561</t>
+    <t xml:space="preserve">8.71125221252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69881820678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68224048614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60764503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60350036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45016098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40043067932129</t>
   </si>
   <si>
     <t xml:space="preserve">8.45430755615234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52890205383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50403785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4708833694458</t>
+    <t xml:space="preserve">8.52890300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50403690338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47088432312012</t>
   </si>
   <si>
     <t xml:space="preserve">8.41700744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37556648254395</t>
+    <t xml:space="preserve">8.37556552886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.05811405181885</t>
@@ -2711,118 +2711,118 @@
     <t xml:space="preserve">8.2868766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88074016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73154544830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64203071594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90892171859741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93212842941284</t>
+    <t xml:space="preserve">7.88074111938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73154640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64203023910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90891981124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93212890625</t>
   </si>
   <si>
     <t xml:space="preserve">7.78790950775146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83598279953003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90063285827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0067253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98186063766479</t>
+    <t xml:space="preserve">7.83598136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90063190460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00672435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98186016082764</t>
   </si>
   <si>
     <t xml:space="preserve">7.80448579788208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84095525741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13105487823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76967239379883</t>
+    <t xml:space="preserve">7.84095573425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13105392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76967334747314</t>
   </si>
   <si>
     <t xml:space="preserve">7.37679672241211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27733421325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29391241073608</t>
+    <t xml:space="preserve">7.27733373641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29391145706177</t>
   </si>
   <si>
     <t xml:space="preserve">6.97563219070435</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77007627487183</t>
+    <t xml:space="preserve">6.77007579803467</t>
   </si>
   <si>
     <t xml:space="preserve">6.7186861038208</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75018310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57612371444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45511150360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08378505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78248453140259</t>
+    <t xml:space="preserve">6.75018358230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57612419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45511102676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08378601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78248500823975</t>
   </si>
   <si>
     <t xml:space="preserve">4.65815687179565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56200933456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87903475761414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97766828536987</t>
+    <t xml:space="preserve">4.56201028823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87903523445129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97766804695129</t>
   </si>
   <si>
     <t xml:space="preserve">3.71989488601685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85085391998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9453432559967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15918779373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32661533355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26362276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43436670303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46088981628418</t>
+    <t xml:space="preserve">3.85085344314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94534373283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15918731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32661485671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26362228393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43436574935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46089029312134</t>
   </si>
   <si>
     <t xml:space="preserve">4.70788812637329</t>
@@ -2831,19 +2831,19 @@
     <t xml:space="preserve">4.61505603790283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59019088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62500333786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54543352127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75430488586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7874584197998</t>
+    <t xml:space="preserve">4.59019136428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62500238418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54543399810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7543044090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78745794296265</t>
   </si>
   <si>
     <t xml:space="preserve">4.906813621521</t>
@@ -2855,43 +2855,43 @@
     <t xml:space="preserve">5.01456499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97809410095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91178607940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69131088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77751159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80735158920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77917003631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54046058654785</t>
+    <t xml:space="preserve">4.97809457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91178703308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6913104057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77751064300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80735015869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77916955947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54045963287354</t>
   </si>
   <si>
     <t xml:space="preserve">4.6813645362854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86702871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90515613555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686679840088</t>
+    <t xml:space="preserve">4.86702823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90515518188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686727523804</t>
   </si>
   <si>
     <t xml:space="preserve">4.99135589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2831130027771</t>
+    <t xml:space="preserve">5.28311252593994</t>
   </si>
   <si>
     <t xml:space="preserve">5.29968976974487</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">5.00627565383911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24664354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04440307617188</t>
+    <t xml:space="preserve">5.24664258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04440259933472</t>
   </si>
   <si>
     <t xml:space="preserve">5.12065696716309</t>
@@ -2912,31 +2912,31 @@
     <t xml:space="preserve">5.16375732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07092618942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98140954971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76424980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79408931732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15878486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6995997428894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85045051574707</t>
+    <t xml:space="preserve">5.07092666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98141002655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76425075531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79408836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15878391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69959926605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85045099258423</t>
   </si>
   <si>
     <t xml:space="preserve">4.61174154281616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59847974777222</t>
+    <t xml:space="preserve">4.59847927093506</t>
   </si>
   <si>
     <t xml:space="preserve">4.64157962799072</t>
@@ -2945,13 +2945,13 @@
     <t xml:space="preserve">4.71451902389526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72114944458008</t>
+    <t xml:space="preserve">4.72114992141724</t>
   </si>
   <si>
     <t xml:space="preserve">4.83718919754028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63494920730591</t>
+    <t xml:space="preserve">4.63494968414307</t>
   </si>
   <si>
     <t xml:space="preserve">4.84382009506226</t>
@@ -2960,31 +2960,31 @@
     <t xml:space="preserve">5.04606008529663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2980318069458</t>
+    <t xml:space="preserve">5.29803133010864</t>
   </si>
   <si>
     <t xml:space="preserve">5.3527364730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63288974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71577405929565</t>
+    <t xml:space="preserve">5.63288879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71577453613281</t>
   </si>
   <si>
     <t xml:space="preserve">5.61465454101562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53508329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18365001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18862390518188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18199300765991</t>
+    <t xml:space="preserve">5.53508424758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18365049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18862295150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1819920539856</t>
   </si>
   <si>
     <t xml:space="preserve">5.1306037902832</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">5.12894582748413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04108715057373</t>
+    <t xml:space="preserve">5.04108667373657</t>
   </si>
   <si>
     <t xml:space="preserve">5.14220762252808</t>
@@ -3011,31 +3011,31 @@
     <t xml:space="preserve">4.81398153305054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70622968673706</t>
+    <t xml:space="preserve">4.70623064041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.85210847854614</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76259231567383</t>
+    <t xml:space="preserve">4.76259183883667</t>
   </si>
   <si>
     <t xml:space="preserve">4.93002128601074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84547805786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76756525039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59682178497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62168836593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67805004119873</t>
+    <t xml:space="preserve">4.84547853469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76756620407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5968222618103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62168741226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67804956436157</t>
   </si>
   <si>
     <t xml:space="preserve">4.75761938095093</t>
@@ -3050,145 +3050,145 @@
     <t xml:space="preserve">4.78414297103882</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70291471481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66810369491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58024454116821</t>
+    <t xml:space="preserve">4.70291519165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66810321807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58024501800537</t>
   </si>
   <si>
     <t xml:space="preserve">4.49072885513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27191066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19234180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08790588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28185749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29346084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.485755443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21389245986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29014587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43602418899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41447448730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32164239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27688407897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23875761032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19731426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10448312759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08624839782715</t>
+    <t xml:space="preserve">4.27191114425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19234132766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0879054069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28185701370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29346132278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21389150619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2901463508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43602466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41447401046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32164192199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27688360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23875713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19731473922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10448265075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08624744415283</t>
   </si>
   <si>
     <t xml:space="preserve">4.22383832931519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17576360702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13349199295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05806732177734</t>
+    <t xml:space="preserve">4.17576503753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13349342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05806684494019</t>
   </si>
   <si>
     <t xml:space="preserve">4.082932472229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07795906066895</t>
+    <t xml:space="preserve">4.07796001434326</t>
   </si>
   <si>
     <t xml:space="preserve">4.00004816055298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96192026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98927164077759</t>
+    <t xml:space="preserve">3.9619197845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98927330970764</t>
   </si>
   <si>
     <t xml:space="preserve">4.00087642669678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97600960731506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83924961090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84422278404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82598900794983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77957272529602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74724674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80112266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95943403244019</t>
+    <t xml:space="preserve">3.97601079940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83925008773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8442223072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82598805427551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77957224845886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74724698066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80112195014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95943307876587</t>
   </si>
   <si>
     <t xml:space="preserve">3.96274900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85334086418152</t>
+    <t xml:space="preserve">3.85334014892578</t>
   </si>
   <si>
     <t xml:space="preserve">3.60053968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56075477600098</t>
+    <t xml:space="preserve">3.5607545375824</t>
   </si>
   <si>
     <t xml:space="preserve">3.53091645240784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45880579948425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39747071266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53754711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4239935874939</t>
+    <t xml:space="preserve">3.45880556106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39747142791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53754734992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399406433105</t>
   </si>
   <si>
     <t xml:space="preserve">3.53174519538879</t>
@@ -3200,31 +3200,31 @@
     <t xml:space="preserve">3.5209698677063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55578136444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65358638763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58064675331116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69005656242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66436147689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6030261516571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51351022720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60717058181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42730951309204</t>
+    <t xml:space="preserve">3.5557816028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65358662605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58064794540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69005608558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66436171531677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60302639007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51350998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60717034339905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4273099899292</t>
   </si>
   <si>
     <t xml:space="preserve">3.5508086681366</t>
@@ -3233,52 +3233,52 @@
     <t xml:space="preserve">3.62623429298401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.710777759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6187744140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63783860206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67099189758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57401633262634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47455382347107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37011885643005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37509155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55163741111755</t>
+    <t xml:space="preserve">3.71077799797058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61877489089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63783836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67099213600159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5740168094635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47455430030823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37011861801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17285132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37509179115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55163717269897</t>
   </si>
   <si>
     <t xml:space="preserve">3.63535189628601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19399881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17244815826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57029819488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63660717010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64655351638794</t>
+    <t xml:space="preserve">4.19399833679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17244863510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57029867172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63660669326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64655303955078</t>
   </si>
   <si>
     <t xml:space="preserve">4.6763916015625</t>
@@ -3290,31 +3290,31 @@
     <t xml:space="preserve">5.11402702331543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21183156967163</t>
+    <t xml:space="preserve">5.21183109283447</t>
   </si>
   <si>
     <t xml:space="preserve">5.27316617965698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19359683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18033456802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39324855804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73357439041138</t>
+    <t xml:space="preserve">5.19359636306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18033504486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39324808120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73357486724854</t>
   </si>
   <si>
     <t xml:space="preserve">5.67825078964233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6011323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61957311630249</t>
+    <t xml:space="preserve">5.60113286972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61957359313965</t>
   </si>
   <si>
     <t xml:space="preserve">5.43683671951294</t>
@@ -3323,49 +3323,49 @@
     <t xml:space="preserve">5.52066087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5474853515625</t>
+    <t xml:space="preserve">5.54748439788818</t>
   </si>
   <si>
     <t xml:space="preserve">5.58101415634155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80901622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70339822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7117805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71513271331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80230951309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70004463195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6262788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6950159072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6665153503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72183895111084</t>
+    <t xml:space="preserve">5.80901575088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70339727401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71178007125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71513319015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80231046676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70004415512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62627935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69501543045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66651582717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72183990478516</t>
   </si>
   <si>
     <t xml:space="preserve">5.63801431655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49048376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47539567947388</t>
+    <t xml:space="preserve">5.4904842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47539663314819</t>
   </si>
   <si>
     <t xml:space="preserve">5.6279559135437</t>
@@ -3374,16 +3374,16 @@
     <t xml:space="preserve">5.58772039413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51227903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55251455307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47874879837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67489767074585</t>
+    <t xml:space="preserve">5.51227807998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55251407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47874927520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67489719390869</t>
   </si>
   <si>
     <t xml:space="preserve">5.97834157943726</t>
@@ -3392,10 +3392,10 @@
     <t xml:space="preserve">5.9699592590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93642807006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8291335105896</t>
+    <t xml:space="preserve">5.93642854690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">5.99678230285645</t>
@@ -3404,49 +3404,49 @@
     <t xml:space="preserve">5.9129581451416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96492958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65813207626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64304447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46198463439941</t>
+    <t xml:space="preserve">5.96492910385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65813255310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64304399490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4619836807251</t>
   </si>
   <si>
     <t xml:space="preserve">5.27254152297974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1786584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24739456176758</t>
+    <t xml:space="preserve">5.17865800857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24739408493042</t>
   </si>
   <si>
     <t xml:space="preserve">5.33792400360107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50054311752319</t>
+    <t xml:space="preserve">5.50054359436035</t>
   </si>
   <si>
     <t xml:space="preserve">5.38989496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38151359558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60448503494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6933388710022</t>
+    <t xml:space="preserve">5.3815131187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60448551177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69333791732788</t>
   </si>
   <si>
     <t xml:space="preserve">5.80733966827393</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92972278594971</t>
+    <t xml:space="preserve">5.92972326278687</t>
   </si>
   <si>
     <t xml:space="preserve">5.82410526275635</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">5.89451694488525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90122270584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95989990234375</t>
+    <t xml:space="preserve">5.90122222900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95990037918091</t>
   </si>
   <si>
     <t xml:space="preserve">6.31196117401123</t>
@@ -3470,13 +3470,13 @@
     <t xml:space="preserve">6.17951917648315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03534126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06551790237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29352045059204</t>
+    <t xml:space="preserve">6.03534173965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06551837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29351997375488</t>
   </si>
   <si>
     <t xml:space="preserve">6.22813701629639</t>
@@ -3485,25 +3485,25 @@
     <t xml:space="preserve">6.44440364837646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32958745956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24743890762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41508769989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53579473495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51902961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78559112548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02700424194336</t>
+    <t xml:space="preserve">7.32958650588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24744033813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41508865356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53579568862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51902914047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78559017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02700519561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.14435768127441</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">8.00520992279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11082744598389</t>
+    <t xml:space="preserve">8.1108283996582</t>
   </si>
   <si>
     <t xml:space="preserve">8.30697727203369</t>
@@ -3524,253 +3524,253 @@
     <t xml:space="preserve">8.10579967498779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12926864624023</t>
+    <t xml:space="preserve">8.12926959991455</t>
   </si>
   <si>
     <t xml:space="preserve">8.09741592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99682712554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81576728820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75038433074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61961936950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90294456481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69170808792114</t>
+    <t xml:space="preserve">7.99682664871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81576681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75038480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61961984634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90294361114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69170713424683</t>
   </si>
   <si>
     <t xml:space="preserve">7.97168159484863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01526927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09574031829834</t>
+    <t xml:space="preserve">8.01526832580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09573936462402</t>
   </si>
   <si>
     <t xml:space="preserve">8.0571813583374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10076808929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10915184020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98173809051514</t>
+    <t xml:space="preserve">8.10076904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10915374755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98174142837524</t>
   </si>
   <si>
     <t xml:space="preserve">7.77720785140991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69506072998047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63973617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62967777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99850463867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70679569244385</t>
+    <t xml:space="preserve">7.69506025314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63973569869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62967824935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70679664611816</t>
   </si>
   <si>
     <t xml:space="preserve">7.68332481384277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73865079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39496850967407</t>
+    <t xml:space="preserve">7.73864889144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39496994018555</t>
   </si>
   <si>
     <t xml:space="preserve">7.47041177749634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46370649337769</t>
+    <t xml:space="preserve">7.46370601654053</t>
   </si>
   <si>
     <t xml:space="preserve">7.44358825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70008945465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53914833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79229640960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26420402526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50897121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5760293006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63806056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98006248474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12591743469238</t>
+    <t xml:space="preserve">7.70008993148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53914785385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79229545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26420497894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50897073745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57603025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63806009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98006343841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12591648101807</t>
   </si>
   <si>
     <t xml:space="preserve">8.20806503295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01359272003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2835054397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19632720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21477127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12759304046631</t>
+    <t xml:space="preserve">8.01359176635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28350639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19632816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21477031707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12759208679199</t>
   </si>
   <si>
     <t xml:space="preserve">7.90462160110474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85600137710571</t>
+    <t xml:space="preserve">7.85600328445435</t>
   </si>
   <si>
     <t xml:space="preserve">7.92976951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95869636535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80214309692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82596683502197</t>
+    <t xml:space="preserve">7.9586968421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80214405059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82596588134766</t>
   </si>
   <si>
     <t xml:space="preserve">8.04548263549805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96039724349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93827629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15268707275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24627780914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31604766845703</t>
+    <t xml:space="preserve">7.96039772033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93827772140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15268611907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24627876281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31604671478271</t>
   </si>
   <si>
     <t xml:space="preserve">8.1918249130249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20203590393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17140483856201</t>
+    <t xml:space="preserve">8.20203685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17140579223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.11354923248291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12545967102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29052352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14077472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13056468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94848680496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81575632095337</t>
+    <t xml:space="preserve">8.12545871734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2905216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14077377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13056564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94848728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81575775146484</t>
   </si>
   <si>
     <t xml:space="preserve">7.84468507766724</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92296123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97571325302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02506351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07100677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80384492874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8055477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82086086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97060775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96550369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02165985107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64388799667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52987718582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42607450485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65920209884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63197660446167</t>
+    <t xml:space="preserve">7.92296171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97571277618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02506160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07100772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8038444519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80554628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82086229324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97060918807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96550273895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02165794372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64388847351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52987670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42607355117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65920305252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63197565078735</t>
   </si>
   <si>
     <t xml:space="preserve">7.46861696243286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59964513778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521329879761</t>
+    <t xml:space="preserve">7.59964561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521425247192</t>
   </si>
   <si>
     <t xml:space="preserve">7.25420713424683</t>
@@ -3779,76 +3779,76 @@
     <t xml:space="preserve">7.00235939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12317752838135</t>
+    <t xml:space="preserve">7.12317848205566</t>
   </si>
   <si>
     <t xml:space="preserve">7.26271533966064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18103456497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26441669464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47372245788574</t>
+    <t xml:space="preserve">7.18103408813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26441764831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47372198104858</t>
   </si>
   <si>
     <t xml:space="preserve">7.40735673904419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47031784057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46691608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29674768447876</t>
+    <t xml:space="preserve">7.47031831741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46691513061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29674863815308</t>
   </si>
   <si>
     <t xml:space="preserve">7.35800838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4056544303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30866003036499</t>
+    <t xml:space="preserve">7.40565538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30865955352783</t>
   </si>
   <si>
     <t xml:space="preserve">7.28313446044922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48222970962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44139003753662</t>
+    <t xml:space="preserve">7.48222923278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44139099121094</t>
   </si>
   <si>
     <t xml:space="preserve">7.48563385009766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49584293365479</t>
+    <t xml:space="preserve">7.4958438873291</t>
   </si>
   <si>
     <t xml:space="preserve">7.30185270309448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3341851234436</t>
+    <t xml:space="preserve">7.33418560028076</t>
   </si>
   <si>
     <t xml:space="preserve">6.99385118484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9376974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07042646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09254884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15550994873047</t>
+    <t xml:space="preserve">6.93769645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07042741775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09254837036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15550947189331</t>
   </si>
   <si>
     <t xml:space="preserve">7.22187471389771</t>
@@ -3857,112 +3857,112 @@
     <t xml:space="preserve">7.33758783340454</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25760984420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34269332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22527885437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21166467666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14700174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0942497253418</t>
+    <t xml:space="preserve">7.25761079788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34269380569458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22527837753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2116641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14700126647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09425020217896</t>
   </si>
   <si>
     <t xml:space="preserve">7.0636191368103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30695867538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25590848922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37672710418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14019584655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87473392486572</t>
+    <t xml:space="preserve">7.30695819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25590896606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3767261505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14019536972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87473440170288</t>
   </si>
   <si>
     <t xml:space="preserve">6.87303304672241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23038291931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28823947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32567596435547</t>
+    <t xml:space="preserve">7.23038339614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2882399559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32567691802979</t>
   </si>
   <si>
     <t xml:space="preserve">7.57241821289062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53668260574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59794330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73577928543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72556781768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9399790763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67792129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79873991012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15609073638916</t>
+    <t xml:space="preserve">7.53668355941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59794425964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73577880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7255687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93997812271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67792177200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79874086380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15608978271484</t>
   </si>
   <si>
     <t xml:space="preserve">8.35007953643799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21054172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10334014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14758110046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40283107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35348320007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45898532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60618114471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43856620788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39092063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56363868713379</t>
+    <t xml:space="preserve">8.21054363250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10333824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14758205413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40283298492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35348415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45898723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60618019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43856811523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39091968536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56363964080811</t>
   </si>
   <si>
     <t xml:space="preserve">8.55513095855713</t>
@@ -3971,49 +3971,49 @@
     <t xml:space="preserve">8.42325210571289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19012260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19352626800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41474342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38241100311279</t>
+    <t xml:space="preserve">8.19012355804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19352722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41474437713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38241195678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.27520656585693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79336357116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03585243225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27834033966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23154354095459</t>
+    <t xml:space="preserve">8.79336452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03585147857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27833938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23154449462891</t>
   </si>
   <si>
     <t xml:space="preserve">8.92524337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83165168762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73380661010742</t>
+    <t xml:space="preserve">8.83165264129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73380565643311</t>
   </si>
   <si>
     <t xml:space="preserve">8.71253395080566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5296049118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.288818359375</t>
+    <t xml:space="preserve">8.52960586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28881931304932</t>
   </si>
   <si>
     <t xml:space="preserve">8.07611083984375</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">8.2693452835083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21586227416992</t>
+    <t xml:space="preserve">8.21586132049561</t>
   </si>
   <si>
     <t xml:space="preserve">8.31247711181641</t>
@@ -4031,25 +4031,25 @@
     <t xml:space="preserve">8.20895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62753438949585</t>
+    <t xml:space="preserve">7.62753486633301</t>
   </si>
   <si>
     <t xml:space="preserve">7.69654607772827</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4722580909729</t>
+    <t xml:space="preserve">7.47225761413574</t>
   </si>
   <si>
     <t xml:space="preserve">7.78108596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7068977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7293267250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8431978225708</t>
+    <t xml:space="preserve">7.70689725875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72932624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319686889648</t>
   </si>
   <si>
     <t xml:space="preserve">8.01745128631592</t>
@@ -4058,13 +4058,13 @@
     <t xml:space="preserve">7.91910982131958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76038265228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69309616088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62408351898193</t>
+    <t xml:space="preserve">7.76038217544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69309520721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62408399581909</t>
   </si>
   <si>
     <t xml:space="preserve">7.87942790985107</t>
@@ -4073,46 +4073,46 @@
     <t xml:space="preserve">7.63616132736206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85527420043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78798675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61373281478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86389970779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86217498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87597703933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96051597595215</t>
+    <t xml:space="preserve">7.85527372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78798580169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61373233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86390066146851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86217451095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96051692962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.02435302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01055145263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94498872756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25899410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37286186218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43669986724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43842506408691</t>
+    <t xml:space="preserve">8.01054954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94498777389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25899314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37286281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43669891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4384241104126</t>
   </si>
   <si>
     <t xml:space="preserve">8.45222663879395</t>
@@ -4124,13 +4124,13 @@
     <t xml:space="preserve">8.58162212371826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6566743850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67824077606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85076999664307</t>
+    <t xml:space="preserve">8.65667343139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6782398223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85076904296875</t>
   </si>
   <si>
     <t xml:space="preserve">9.06211853027344</t>
@@ -4139,64 +4139,64 @@
     <t xml:space="preserve">9.2519006729126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28640747070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93703365325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49708366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88958835601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5538272857666</t>
+    <t xml:space="preserve">9.28640556335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93703460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49708461761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8895902633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55382633209229</t>
   </si>
   <si>
     <t xml:space="preserve">9.37698554992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83850193023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78242969512939</t>
+    <t xml:space="preserve">9.8385009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78242874145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.65734577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85144138336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86006641387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77380275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87732028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97652530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0800428390503</t>
+    <t xml:space="preserve">9.85144233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86006832122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77380180358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87732219696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97652435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0800437927246</t>
   </si>
   <si>
     <t xml:space="preserve">9.92476654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99809169769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2266941070557</t>
+    <t xml:space="preserve">9.99808979034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2266931533813</t>
   </si>
   <si>
     <t xml:space="preserve">9.93770694732666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75223636627197</t>
+    <t xml:space="preserve">9.75223731994629</t>
   </si>
   <si>
     <t xml:space="preserve">9.44599628448486</t>
@@ -4211,46 +4211,46 @@
     <t xml:space="preserve">9.32091331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60990142822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95495796203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86869430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.35608959198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1447410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96358585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2618703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6241827011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9815092086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1540393829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1497268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8736801147461</t>
+    <t xml:space="preserve">9.60989952087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95495891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86869335174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3560914993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1447420120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96358680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2618713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6241836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9815111160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1540403366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1497278213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8736791610718</t>
   </si>
   <si>
     <t xml:space="preserve">10.5113677978516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7356538772583</t>
+    <t xml:space="preserve">10.7356557846069</t>
   </si>
   <si>
     <t xml:space="preserve">10.908185005188</t>
@@ -4271,121 +4271,121 @@
     <t xml:space="preserve">12.2927350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0123748779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6845693588257</t>
+    <t xml:space="preserve">12.0123739242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6845684051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.8829765319824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8657236099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9821825027466</t>
+    <t xml:space="preserve">11.8657255172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9821815490723</t>
   </si>
   <si>
     <t xml:space="preserve">11.9735565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0727615356445</t>
+    <t xml:space="preserve">12.0727596282959</t>
   </si>
   <si>
     <t xml:space="preserve">11.9390497207642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9908094406128</t>
+    <t xml:space="preserve">11.9908084869385</t>
   </si>
   <si>
     <t xml:space="preserve">12.5299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4135074615479</t>
+    <t xml:space="preserve">12.4135065078735</t>
   </si>
   <si>
     <t xml:space="preserve">12.8146371841431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9224691390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9914798736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9612884521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9310941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5817222595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.723388671875</t>
+    <t xml:space="preserve">12.9224681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9914808273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9612865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.931095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5817232131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7233877182007</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374588012695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0813865661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7758178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2841081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8448314666748</t>
+    <t xml:space="preserve">12.0813875198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7758188247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2841091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8448295593262</t>
   </si>
   <si>
     <t xml:space="preserve">12.6981801986694</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6377954483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5385894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0598201751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.180591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5989761352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2668571472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7283716201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2718410491943</t>
+    <t xml:space="preserve">12.6377935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5385904312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0598211288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5989751815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2668561935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7283725738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2718420028687</t>
   </si>
   <si>
     <t xml:space="preserve">13.4486837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3667316436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0216722488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.19420337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.488579750061</t>
+    <t xml:space="preserve">13.3667325973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0216732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1942024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4885787963867</t>
   </si>
   <si>
     <t xml:space="preserve">13.3040437698364</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5456972122192</t>
+    <t xml:space="preserve">13.5456953048706</t>
   </si>
   <si>
     <t xml:space="preserve">13.9147653579712</t>
@@ -4406,16 +4406,16 @@
     <t xml:space="preserve">13.86643409729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8224983215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9630966186523</t>
+    <t xml:space="preserve">13.8224964141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.963095664978</t>
   </si>
   <si>
     <t xml:space="preserve">14.0641489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0246067047119</t>
+    <t xml:space="preserve">14.0246076583862</t>
   </si>
   <si>
     <t xml:space="preserve">13.4094924926758</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">11.3927955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6080875396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6739902496338</t>
+    <t xml:space="preserve">11.6080865859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6739912033081</t>
   </si>
   <si>
     <t xml:space="preserve">11.0720586776733</t>
@@ -4460,34 +4460,34 @@
     <t xml:space="preserve">11.2302303314209</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0632705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7820768356323</t>
+    <t xml:space="preserve">11.063271522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7820739746094</t>
   </si>
   <si>
     <t xml:space="preserve">10.579966545105</t>
   </si>
   <si>
-    <t xml:space="preserve">10.966609954834</t>
+    <t xml:space="preserve">10.9666090011597</t>
   </si>
   <si>
     <t xml:space="preserve">10.0615129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75834941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7469253540039</t>
+    <t xml:space="preserve">9.75834846496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7469263076782</t>
   </si>
   <si>
     <t xml:space="preserve">11.1423568725586</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2082614898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1116008758545</t>
+    <t xml:space="preserve">11.2082624435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1115999221802</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841842651367</t>
@@ -4496,16 +4496,16 @@
     <t xml:space="preserve">10.5404233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7117767333984</t>
+    <t xml:space="preserve">10.7117757797241</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1819000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0676641464233</t>
+    <t xml:space="preserve">11.1819009780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.067663192749</t>
   </si>
   <si>
     <t xml:space="preserve">10.8523750305176</t>
@@ -4517,16 +4517,16 @@
     <t xml:space="preserve">11.0940275192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.441125869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5861196517944</t>
+    <t xml:space="preserve">11.4411268234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5861177444458</t>
   </si>
   <si>
     <t xml:space="preserve">11.9551858901978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.634449005127</t>
+    <t xml:space="preserve">11.6344470977783</t>
   </si>
   <si>
     <t xml:space="preserve">11.6608104705811</t>
@@ -4535,13 +4535,13 @@
     <t xml:space="preserve">11.5289993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0896320343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3005294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4147653579712</t>
+    <t xml:space="preserve">11.0896329879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3005285263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4147644042969</t>
   </si>
   <si>
     <t xml:space="preserve">11.2917423248291</t>
@@ -4556,61 +4556,61 @@
     <t xml:space="preserve">11.3224973678589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6827793121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2829542160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2803192138672</t>
+    <t xml:space="preserve">11.6827783584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2829551696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2803182601929</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704759597778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3945531845093</t>
+    <t xml:space="preserve">12.3945541381836</t>
   </si>
   <si>
     <t xml:space="preserve">12.218807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0913896560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0826034545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0298776626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4384908676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5527248382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.122145652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.739896774292</t>
+    <t xml:space="preserve">12.0913906097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0826025009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0298795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4384918212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5527257919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1221466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7398958206177</t>
   </si>
   <si>
     <t xml:space="preserve">11.7442903518677</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3286476135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5790882110596</t>
+    <t xml:space="preserve">12.3286485671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5790872573853</t>
   </si>
   <si>
     <t xml:space="preserve">12.5219697952271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5175762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2407751083374</t>
+    <t xml:space="preserve">12.5175752639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2407760620117</t>
   </si>
   <si>
     <t xml:space="preserve">11.9288244247437</t>
@@ -4622,16 +4622,16 @@
     <t xml:space="preserve">11.7882280349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.126540184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9622173309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1994743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5377883911133</t>
+    <t xml:space="preserve">12.1265392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9622163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1994733810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.537787437439</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761005401611</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">13.1854152679443</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7328672409058</t>
+    <t xml:space="preserve">12.7328662872314</t>
   </si>
   <si>
     <t xml:space="preserve">12.1353273391724</t>
@@ -4661,31 +4661,31 @@
     <t xml:space="preserve">12.2451686859131</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8163461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615129470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217948913574</t>
+    <t xml:space="preserve">12.8163471221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217939376831</t>
   </si>
   <si>
     <t xml:space="preserve">13.2117767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1590547561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3216180801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2205648422241</t>
+    <t xml:space="preserve">13.1590518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3216190338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2205638885498</t>
   </si>
   <si>
     <t xml:space="preserve">13.5193347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8927965164185</t>
+    <t xml:space="preserve">13.8927974700928</t>
   </si>
   <si>
     <t xml:space="preserve">13.4534301757812</t>
@@ -4694,31 +4694,31 @@
     <t xml:space="preserve">13.8005294799805</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1564168930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9982452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1959609985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.626540184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7539567947388</t>
+    <t xml:space="preserve">14.1564178466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9982433319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1959590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6265392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7539577484131</t>
   </si>
   <si>
     <t xml:space="preserve">14.4551877975464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3585252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7653799057007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0553617477417</t>
+    <t xml:space="preserve">14.3585262298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7653789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.055362701416</t>
   </si>
   <si>
     <t xml:space="preserve">13.9938507080078</t>
@@ -4727,10 +4727,10 @@
     <t xml:space="preserve">14.6572961807251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.727593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3101949691772</t>
+    <t xml:space="preserve">14.7275943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3101959228516</t>
   </si>
   <si>
     <t xml:space="preserve">14.4244327545166</t>
@@ -4742,31 +4742,31 @@
     <t xml:space="preserve">14.6908092498779</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3578357696533</t>
+    <t xml:space="preserve">14.3578367233276</t>
   </si>
   <si>
     <t xml:space="preserve">14.4466285705566</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5265426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1314134597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.54430103302</t>
+    <t xml:space="preserve">14.5265436172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1314144134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5443000793457</t>
   </si>
   <si>
     <t xml:space="preserve">14.8417587280273</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4954652786255</t>
+    <t xml:space="preserve">14.4954662322998</t>
   </si>
   <si>
     <t xml:space="preserve">14.2557239532471</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0381813049316</t>
+    <t xml:space="preserve">14.038182258606</t>
   </si>
   <si>
     <t xml:space="preserve">13.9138708114624</t>
@@ -4775,25 +4775,25 @@
     <t xml:space="preserve">13.6119747161865</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7806825637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6608104705811</t>
+    <t xml:space="preserve">13.7806816101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6608114242554</t>
   </si>
   <si>
     <t xml:space="preserve">13.5276203155518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9893445968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7451629638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6474914550781</t>
+    <t xml:space="preserve">13.9893455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0159816741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7451639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6474924087524</t>
   </si>
   <si>
     <t xml:space="preserve">13.949387550354</t>
@@ -4802,28 +4802,28 @@
     <t xml:space="preserve">14.1402940750122</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4643878936768</t>
+    <t xml:space="preserve">14.4643888473511</t>
   </si>
   <si>
     <t xml:space="preserve">14.721887588501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7796039581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6686124801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7130088806152</t>
+    <t xml:space="preserve">14.7796020507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6686134338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7130079269409</t>
   </si>
   <si>
     <t xml:space="preserve">14.4599475860596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9349899291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4199914932251</t>
+    <t xml:space="preserve">14.9349908828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4199905395508</t>
   </si>
   <si>
     <t xml:space="preserve">13.4033117294312</t>
@@ -4832,25 +4832,25 @@
     <t xml:space="preserve">13.7940006256104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0071020126343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0603799819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0692596435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.237964630127</t>
+    <t xml:space="preserve">14.0071029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0603790283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0692586898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2379655838013</t>
   </si>
   <si>
     <t xml:space="preserve">14.4421882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3445177078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2290849685669</t>
+    <t xml:space="preserve">14.3445167541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2290859222412</t>
   </si>
   <si>
     <t xml:space="preserve">14.6597318649292</t>
@@ -4868,34 +4868,34 @@
     <t xml:space="preserve">14.2424058914185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2690439224243</t>
+    <t xml:space="preserve">14.26904296875</t>
   </si>
   <si>
     <t xml:space="preserve">14.2956819534302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6197748184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3977937698364</t>
+    <t xml:space="preserve">14.619776725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3977928161621</t>
   </si>
   <si>
     <t xml:space="preserve">14.4288702011108</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1180934906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6297330856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5498199462891</t>
+    <t xml:space="preserve">14.1180944442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6297340393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5498189926147</t>
   </si>
   <si>
     <t xml:space="preserve">13.4388284683228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.540940284729</t>
+    <t xml:space="preserve">13.5409393310547</t>
   </si>
   <si>
     <t xml:space="preserve">13.8872327804565</t>
@@ -4904,31 +4904,31 @@
     <t xml:space="preserve">14.1225347518921</t>
   </si>
   <si>
-    <t xml:space="preserve">14.082576751709</t>
+    <t xml:space="preserve">14.0825777053833</t>
   </si>
   <si>
     <t xml:space="preserve">14.3800344467163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4011545181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6641712188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4377498626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.971586227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2246475219727</t>
+    <t xml:space="preserve">15.4011535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6641721725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4377489089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9715852737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2246465682983</t>
   </si>
   <si>
     <t xml:space="preserve">13.9227504730225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2646036148071</t>
+    <t xml:space="preserve">14.2646045684814</t>
   </si>
   <si>
     <t xml:space="preserve">14.3267583847046</t>
@@ -4943,10 +4943,10 @@
     <t xml:space="preserve">14.5487413406372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.00266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7140855789185</t>
+    <t xml:space="preserve">14.0026636123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7140865325928</t>
   </si>
   <si>
     <t xml:space="preserve">12.9105091094971</t>
@@ -4955,31 +4955,31 @@
     <t xml:space="preserve">13.0969743728638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9249057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9559841156006</t>
+    <t xml:space="preserve">11.9249067306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9559850692749</t>
   </si>
   <si>
     <t xml:space="preserve">11.7384414672852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7695188522339</t>
+    <t xml:space="preserve">11.7695178985596</t>
   </si>
   <si>
     <t xml:space="preserve">12.1646480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0358982086182</t>
+    <t xml:space="preserve">12.0358972549438</t>
   </si>
   <si>
     <t xml:space="preserve">11.765079498291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3877086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942607879639</t>
+    <t xml:space="preserve">11.3877077102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942598342896</t>
   </si>
   <si>
     <t xml:space="preserve">11.8361139297485</t>
@@ -4991,28 +4991,28 @@
     <t xml:space="preserve">11.6096906661987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6318893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9826231002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6851644515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5386562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5075798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8183565139771</t>
+    <t xml:space="preserve">11.631890296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9826221466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6851654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5386571884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5075788497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8183555603027</t>
   </si>
   <si>
     <t xml:space="preserve">11.9737434387207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337844848633</t>
+    <t xml:space="preserve">11.9337863922119</t>
   </si>
   <si>
     <t xml:space="preserve">11.8405523300171</t>
@@ -5024,10 +5024,10 @@
     <t xml:space="preserve">11.6540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6363286972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5874938964844</t>
+    <t xml:space="preserve">11.6363296508789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5874929428101</t>
   </si>
   <si>
     <t xml:space="preserve">11.5031385421753</t>
@@ -5036,7 +5036,7 @@
     <t xml:space="preserve">11.2678375244141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9659423828125</t>
+    <t xml:space="preserve">10.9659414291382</t>
   </si>
   <si>
     <t xml:space="preserve">10.8949069976807</t>
@@ -5051,19 +5051,19 @@
     <t xml:space="preserve">11.1168909072876</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0991315841675</t>
+    <t xml:space="preserve">11.0991306304932</t>
   </si>
   <si>
     <t xml:space="preserve">10.8771486282349</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7528371810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8815898895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8460702896118</t>
+    <t xml:space="preserve">10.7528381347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8815879821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8460712432861</t>
   </si>
   <si>
     <t xml:space="preserve">10.7705974578857</t>
@@ -5075,16 +5075,16 @@
     <t xml:space="preserve">10.9526224136353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.071325302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2311182022095</t>
+    <t xml:space="preserve">11.0713272094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2311191558838</t>
   </si>
   <si>
     <t xml:space="preserve">11.2585105895996</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8430509567261</t>
+    <t xml:space="preserve">10.8430500030518</t>
   </si>
   <si>
     <t xml:space="preserve">10.9389266967773</t>
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">11.1489400863647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8476161956787</t>
+    <t xml:space="preserve">10.8476152420044</t>
   </si>
   <si>
     <t xml:space="preserve">10.6558666229248</t>
@@ -5108,7 +5108,7 @@
     <t xml:space="preserve">11.3452548980713</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6054878234863</t>
+    <t xml:space="preserve">11.6054887771606</t>
   </si>
   <si>
     <t xml:space="preserve">11.6967992782593</t>
@@ -5120,16 +5120,16 @@
     <t xml:space="preserve">11.7104949951172</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6420125961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205083847046</t>
+    <t xml:space="preserve">11.6420116424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205074310303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8063707351685</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8931131362915</t>
+    <t xml:space="preserve">11.8931140899658</t>
   </si>
   <si>
     <t xml:space="preserve">11.4274339675903</t>
@@ -5144,19 +5144,19 @@
     <t xml:space="preserve">11.6922340393066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8291969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8337640762329</t>
+    <t xml:space="preserve">11.829197883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8337631225586</t>
   </si>
   <si>
     <t xml:space="preserve">11.8657217025757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1853065490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5231533050537</t>
+    <t xml:space="preserve">12.1853075027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5231523513794</t>
   </si>
   <si>
     <t xml:space="preserve">12.5185871124268</t>
@@ -5168,13 +5168,13 @@
     <t xml:space="preserve">12.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305198669434</t>
+    <t xml:space="preserve">12.1305208206177</t>
   </si>
   <si>
     <t xml:space="preserve">12.4501056671143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4227123260498</t>
+    <t xml:space="preserve">12.4227113723755</t>
   </si>
   <si>
     <t xml:space="preserve">12.7696895599365</t>
@@ -5183,13 +5183,13 @@
     <t xml:space="preserve">13.0025300979614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.016227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9568758010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9660053253174</t>
+    <t xml:space="preserve">13.0162258148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9568748474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9660062789917</t>
   </si>
   <si>
     <t xml:space="preserve">13.1577568054199</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">13.1668882369995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184316635132</t>
+    <t xml:space="preserve">13.5184307098389</t>
   </si>
   <si>
     <t xml:space="preserve">13.5549554824829</t>
@@ -5207,19 +5207,19 @@
     <t xml:space="preserve">13.7330083847046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6553955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6143074035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7010507583618</t>
+    <t xml:space="preserve">13.6553964614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6143064498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7010517120361</t>
   </si>
   <si>
     <t xml:space="preserve">13.6964855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8151874542236</t>
+    <t xml:space="preserve">13.8151884078979</t>
   </si>
   <si>
     <t xml:space="preserve">13.7695331573486</t>
@@ -5231,13 +5231,13 @@
     <t xml:space="preserve">13.3632049560547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6599626541138</t>
+    <t xml:space="preserve">13.6599617004395</t>
   </si>
   <si>
     <t xml:space="preserve">13.5823488235474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6371335983276</t>
+    <t xml:space="preserve">13.6371355056763</t>
   </si>
   <si>
     <t xml:space="preserve">14.070855140686</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">14.0845537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0434637069702</t>
+    <t xml:space="preserve">14.0434627532959</t>
   </si>
   <si>
     <t xml:space="preserve">14.0480289459229</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">14.025200843811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9658498764038</t>
+    <t xml:space="preserve">13.9658489227295</t>
   </si>
   <si>
     <t xml:space="preserve">13.9475870132446</t>
@@ -5273,16 +5273,16 @@
     <t xml:space="preserve">13.6736583709717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8380155563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9612855911255</t>
+    <t xml:space="preserve">13.8380146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9612846374512</t>
   </si>
   <si>
     <t xml:space="preserve">13.9293260574341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4773406982422</t>
+    <t xml:space="preserve">13.4773416519165</t>
   </si>
   <si>
     <t xml:space="preserve">13.6097402572632</t>
@@ -5297,10 +5297,10 @@
     <t xml:space="preserve">13.6645269393921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7375755310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8471460342407</t>
+    <t xml:space="preserve">13.7375745773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.847146987915</t>
   </si>
   <si>
     <t xml:space="preserve">13.7421407699585</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">14.0891180038452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8425807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7786636352539</t>
+    <t xml:space="preserve">13.8425817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7786645889282</t>
   </si>
   <si>
     <t xml:space="preserve">13.3951625823975</t>
@@ -5342,7 +5342,7 @@
     <t xml:space="preserve">13.3084182739258</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0116605758667</t>
+    <t xml:space="preserve">13.011661529541</t>
   </si>
   <si>
     <t xml:space="preserve">13.3586387634277</t>
@@ -5351,13 +5351,13 @@
     <t xml:space="preserve">13.8836708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0069389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9567184448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0343322753906</t>
+    <t xml:space="preserve">14.0069398880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9567193984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0343332290649</t>
   </si>
   <si>
     <t xml:space="preserve">14.3950061798096</t>
@@ -5366,7 +5366,7 @@
     <t xml:space="preserve">14.2945652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4954481124878</t>
+    <t xml:space="preserve">14.4954471588135</t>
   </si>
   <si>
     <t xml:space="preserve">14.5045785903931</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">14.2671728134155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.933892250061</t>
+    <t xml:space="preserve">13.9338912963867</t>
   </si>
   <si>
     <t xml:space="preserve">14.0571594238281</t>
@@ -5384,16 +5384,16 @@
     <t xml:space="preserve">14.0982484817505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7969255447388</t>
+    <t xml:space="preserve">13.7969264984131</t>
   </si>
   <si>
     <t xml:space="preserve">14.9383001327515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8999509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2542304992676</t>
+    <t xml:space="preserve">14.8999500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2542314529419</t>
   </si>
   <si>
     <t xml:space="preserve">14.783073425293</t>
@@ -5405,22 +5405,22 @@
     <t xml:space="preserve">14.585844039917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6917638778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9063415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7008953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7191572189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1302080154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3036966323853</t>
+    <t xml:space="preserve">14.6917629241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.906343460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7008943557739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7191562652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1302070617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3036956787109</t>
   </si>
   <si>
     <t xml:space="preserve">14.5487966537476</t>
@@ -71828,7 +71828,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.6512037037</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>1130818</v>
@@ -71849,6 +71849,32 @@
         <v>2193</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.6494791667</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>2005076</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>15.3500003814697</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>15.0200004577637</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>15.2700004577637</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>2180</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="2220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="2221">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,202 +38,202 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8740701675415</t>
+    <t xml:space="preserve">7.87406969070435</t>
   </si>
   <si>
     <t xml:space="preserve">TEN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88865089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69909000396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48036670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19602394104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11582851409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07937145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12311887741089</t>
+    <t xml:space="preserve">7.88865184783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69909143447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48036527633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19602584838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11582660675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07937097549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1231164932251</t>
   </si>
   <si>
     <t xml:space="preserve">7.07208061218262</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62734270095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56901597976685</t>
+    <t xml:space="preserve">6.62734365463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56901693344116</t>
   </si>
   <si>
     <t xml:space="preserve">6.77680444717407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39403629302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63463401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80596780776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78044939041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88981056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91168403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82783985137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49246168136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5143346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03562831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43413496017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29925680160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80232048034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9554271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74034786224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14863443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06114530563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148622512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11947202682495</t>
+    <t xml:space="preserve">6.39403581619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63463258743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80596590042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78044891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88981008529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91168260574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82783937454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49246263504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51433515548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0356273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43413591384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29925632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80232191085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95542764663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74034929275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1486349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06114435195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8314847946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11947154998779</t>
   </si>
   <si>
     <t xml:space="preserve">6.8606481552124</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54349803924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55443429946899</t>
+    <t xml:space="preserve">6.54349851608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55443334579468</t>
   </si>
   <si>
     <t xml:space="preserve">7.16686201095581</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32726144790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50223779678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45120477676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61160039901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9178147315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00530529022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71367216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85948801040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5897274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82303333282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7355432510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96156120300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81574392318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77928972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95426940917969</t>
+    <t xml:space="preserve">7.32726001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50223922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45120286941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61160135269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91781234741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00530338287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71367502212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85948657989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58972787857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82303380966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73554658889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96156024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81574296951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77929019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95426750183105</t>
   </si>
   <si>
     <t xml:space="preserve">7.72096395492554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66992855072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98343372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032464981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53140258789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6407642364502</t>
+    <t xml:space="preserve">7.66992616653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98343086242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53140163421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66263580322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64076471328735</t>
   </si>
   <si>
     <t xml:space="preserve">8.07821178436279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11466598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17299461364746</t>
+    <t xml:space="preserve">8.11466693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17299270629883</t>
   </si>
   <si>
     <t xml:space="preserve">8.42088031768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41358852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45004558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69792938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8291654586792</t>
+    <t xml:space="preserve">8.4135913848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45004463195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69793128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82916450500488</t>
   </si>
   <si>
     <t xml:space="preserve">8.86561965942383</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">8.91665554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63960552215576</t>
+    <t xml:space="preserve">8.63960266113281</t>
   </si>
   <si>
     <t xml:space="preserve">8.8000020980835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80729293823242</t>
+    <t xml:space="preserve">8.80729103088379</t>
   </si>
   <si>
     <t xml:space="preserve">8.58856868743896</t>
@@ -260,133 +260,133 @@
     <t xml:space="preserve">8.0198860168457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97614097595215</t>
+    <t xml:space="preserve">7.97614192962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.39900779724121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24590015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21673965454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29693698883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30422592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4573335647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64689636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67605876922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39171695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56669521331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62654972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73129653930664</t>
+    <t xml:space="preserve">8.24590301513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21673774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29693603515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30422687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45733451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64689540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67605972290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3917179107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56669807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62654876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73129749298096</t>
   </si>
   <si>
     <t xml:space="preserve">8.75374221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95575141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97819709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98568058013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91086101531982</t>
+    <t xml:space="preserve">8.9557523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.978196144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98567771911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91085910797119</t>
   </si>
   <si>
     <t xml:space="preserve">8.80611515045166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67892169952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64899730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0829439163208</t>
+    <t xml:space="preserve">8.67892360687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6489953994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08294105529785</t>
   </si>
   <si>
     <t xml:space="preserve">9.53185272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69645118713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52436923980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4944429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28495216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15775966644287</t>
+    <t xml:space="preserve">9.69645023345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52437019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49444389343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28495121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1577615737915</t>
   </si>
   <si>
     <t xml:space="preserve">9.34480762481689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17272472381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40466213226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66652488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4271068572998</t>
+    <t xml:space="preserve">9.17272281646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40466117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66652393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42710781097412</t>
   </si>
   <si>
     <t xml:space="preserve">9.80119895935059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04553318023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14279556274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6141529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73386096954346</t>
+    <t xml:space="preserve">9.30739784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04553413391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14279651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61415386199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73386287689209</t>
   </si>
   <si>
     <t xml:space="preserve">9.86853408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83112716674805</t>
+    <t xml:space="preserve">9.83112525939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.59918785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32236099243164</t>
+    <t xml:space="preserve">9.32236003875732</t>
   </si>
   <si>
     <t xml:space="preserve">9.39717960357666</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">9.50940704345703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65904140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74882316589355</t>
+    <t xml:space="preserve">9.65904331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74882507324219</t>
   </si>
   <si>
     <t xml:space="preserve">9.47947978973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59170627593994</t>
+    <t xml:space="preserve">9.59170722961426</t>
   </si>
   <si>
     <t xml:space="preserve">9.21761512756348</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">9.37473392486572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18768978118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06797981262207</t>
+    <t xml:space="preserve">9.18768882751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06797790527344</t>
   </si>
   <si>
     <t xml:space="preserve">9.16524314880371</t>
@@ -425,55 +425,55 @@
     <t xml:space="preserve">9.09790515899658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8285608291626</t>
+    <t xml:space="preserve">8.82855987548828</t>
   </si>
   <si>
     <t xml:space="preserve">8.94827079772949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70885181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57417869567871</t>
+    <t xml:space="preserve">8.70885276794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57417774200439</t>
   </si>
   <si>
     <t xml:space="preserve">8.74626159667969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00064277648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19516849517822</t>
+    <t xml:space="preserve">9.00064182281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19517135620117</t>
   </si>
   <si>
     <t xml:space="preserve">9.38969707489014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36725234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48696231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70393562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65156173706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62911796569824</t>
+    <t xml:space="preserve">9.36725330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48696136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70393466949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65156364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62911701202393</t>
   </si>
   <si>
     <t xml:space="preserve">9.51688766479492</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45703411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09042453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22509765625</t>
+    <t xml:space="preserve">9.45703506469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09042549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22509574890137</t>
   </si>
   <si>
     <t xml:space="preserve">9.2999153137207</t>
@@ -488,82 +488,82 @@
     <t xml:space="preserve">8.66395950317383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71633243560791</t>
+    <t xml:space="preserve">8.71633338928223</t>
   </si>
   <si>
     <t xml:space="preserve">8.88093376159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76870536804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67144203186035</t>
+    <t xml:space="preserve">8.76870632171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67144298553467</t>
   </si>
   <si>
     <t xml:space="preserve">8.69388771057129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90337944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70136833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44698810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55921363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35976982116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50192642211914</t>
+    <t xml:space="preserve">8.9033784866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7013692855835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44698715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5592155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35977077484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50192451477051</t>
   </si>
   <si>
     <t xml:space="preserve">9.64408016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76379013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74134540557861</t>
+    <t xml:space="preserve">9.76378917694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7413444519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.95083618164062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6365966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83860683441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.816162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94335174560547</t>
+    <t xml:space="preserve">9.63659858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83860778808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81616115570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94335460662842</t>
   </si>
   <si>
     <t xml:space="preserve">10.0406179428101</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99572372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0106887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96579742431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0630617141724</t>
+    <t xml:space="preserve">9.99572563171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0106897354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96579933166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.063060760498</t>
   </si>
   <si>
     <t xml:space="preserve">9.77126979827881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89846134185791</t>
+    <t xml:space="preserve">9.89846038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.86105251312256</t>
@@ -575,28 +575,28 @@
     <t xml:space="preserve">10.2800350189209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6765727996826</t>
+    <t xml:space="preserve">10.6765737533569</t>
   </si>
   <si>
     <t xml:space="preserve">10.6167182922363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8112459182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9384346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9309549331665</t>
+    <t xml:space="preserve">10.8112440109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.938437461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9309539794922</t>
   </si>
   <si>
     <t xml:space="preserve">10.9159908294678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7214632034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1216316223145</t>
+    <t xml:space="preserve">10.7214641571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1216297149658</t>
   </si>
   <si>
     <t xml:space="preserve">10.8045167922974</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">11.03102684021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0687780380249</t>
+    <t xml:space="preserve">11.0687770843506</t>
   </si>
   <si>
     <t xml:space="preserve">10.8347187042236</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">10.6761617660522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3783397674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7407569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0352191925049</t>
+    <t xml:space="preserve">11.3783416748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464612960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7407579421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0352201461792</t>
   </si>
   <si>
     <t xml:space="preserve">12.1937780380249</t>
@@ -632,31 +632,31 @@
     <t xml:space="preserve">12.0805225372314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2239770889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5561933517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3749828338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2919311523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4202890396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3145837783813</t>
+    <t xml:space="preserve">12.2239780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.556191444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3749837875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2919321060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4202871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3145799636841</t>
   </si>
   <si>
     <t xml:space="preserve">12.3674345016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5410928726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4504880905151</t>
+    <t xml:space="preserve">12.5410938262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4504890441895</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939464569092</t>
@@ -665,31 +665,31 @@
     <t xml:space="preserve">12.8280029296875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9790134429932</t>
+    <t xml:space="preserve">12.9790115356445</t>
   </si>
   <si>
     <t xml:space="preserve">13.0016613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8129043579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0243139266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714612960815</t>
+    <t xml:space="preserve">12.8129024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0243129730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714622497559</t>
   </si>
   <si>
     <t xml:space="preserve">12.9488105773926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8808574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8657569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7751522064209</t>
+    <t xml:space="preserve">12.8808555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8657579421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7751531600952</t>
   </si>
   <si>
     <t xml:space="preserve">12.6769990921021</t>
@@ -698,193 +698,193 @@
     <t xml:space="preserve">12.8204536437988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7600507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5335397720337</t>
+    <t xml:space="preserve">12.7600526809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5335426330566</t>
   </si>
   <si>
     <t xml:space="preserve">12.7676010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8582048416138</t>
+    <t xml:space="preserve">12.8582067489624</t>
   </si>
   <si>
     <t xml:space="preserve">12.6996488571167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6618986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9865636825562</t>
+    <t xml:space="preserve">12.6618957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9865608215332</t>
   </si>
   <si>
     <t xml:space="preserve">13.0092115402222</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8506565093994</t>
+    <t xml:space="preserve">12.8506574630737</t>
   </si>
   <si>
     <t xml:space="preserve">12.2164287567139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2088785171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1258239746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2843809127808</t>
+    <t xml:space="preserve">12.2088756561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1258249282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2843828201294</t>
   </si>
   <si>
     <t xml:space="preserve">12.1182727813721</t>
   </si>
   <si>
-    <t xml:space="preserve">12.148476600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8766632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0729713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2541818618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9748163223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8540124893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1862258911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2390794754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.786060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7256574630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9068660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6652536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5142469406128</t>
+    <t xml:space="preserve">12.1484746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8766622543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0729703903198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560277938843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2541799545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9748182296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8540143966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1862268447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2390775680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7860593795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7256555557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9068641662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6652555465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5142459869385</t>
   </si>
   <si>
     <t xml:space="preserve">11.5444498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4613952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0989799499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1140794754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593837738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0763292312622</t>
+    <t xml:space="preserve">11.4613962173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0989780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1140813827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0763282775879</t>
   </si>
   <si>
     <t xml:space="preserve">11.3330402374268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4085445404053</t>
+    <t xml:space="preserve">11.408543586731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4991474151611</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2952871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1442813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1669330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2424354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.993275642395</t>
+    <t xml:space="preserve">11.2952880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1442823410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1669311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2424373626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9932746887207</t>
   </si>
   <si>
     <t xml:space="preserve">11.8389120101929</t>
   </si>
   <si>
-    <t xml:space="preserve">11.763409614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1333742141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0427713394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2013273239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1786756515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9370670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3858938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4840450286865</t>
+    <t xml:space="preserve">11.7634077072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.133373260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0427703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2013263702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.178674697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.937066078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.385892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4840478897095</t>
   </si>
   <si>
     <t xml:space="preserve">11.2801876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3481397628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3556909561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3405895233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066986083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8724708557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8573703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9026718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7894172668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949531555176</t>
+    <t xml:space="preserve">11.3481416702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3556900024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3405904769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066976547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8724718093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8573684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9026699066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7894163131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949522018433</t>
   </si>
   <si>
     <t xml:space="preserve">10.6535110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6459608078003</t>
+    <t xml:space="preserve">10.6459617614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.6610622406006</t>
@@ -893,67 +893,67 @@
     <t xml:space="preserve">10.8271684646606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8800201416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7441148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.978175163269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7139139175415</t>
+    <t xml:space="preserve">10.8800210952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7441139221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9781742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7139120101929</t>
   </si>
   <si>
     <t xml:space="preserve">10.8951206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0183153152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721164703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0260162353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9259195327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7642230987549</t>
+    <t xml:space="preserve">11.0183162689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721193313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0260171890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9259185791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7642250061035</t>
   </si>
   <si>
     <t xml:space="preserve">10.6410293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6025304794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3561401367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4793367385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4408388137817</t>
+    <t xml:space="preserve">10.6025323867798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3561391830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4793338775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4408369064331</t>
   </si>
   <si>
     <t xml:space="preserve">10.4177370071411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2406435012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4023380279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7873249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4947357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5409326553345</t>
+    <t xml:space="preserve">10.2406463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4023399353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7873239517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4947338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5409336090088</t>
   </si>
   <si>
     <t xml:space="preserve">10.3176403045654</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">10.2791433334351</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2868394851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3330421447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5101337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8335227966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8566226959229</t>
+    <t xml:space="preserve">10.2868423461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3330402374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5101327896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8335247039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8566236495972</t>
   </si>
   <si>
     <t xml:space="preserve">10.7103271484375</t>
@@ -989,97 +989,97 @@
     <t xml:space="preserve">10.3407411575317</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4716367721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7796258926392</t>
+    <t xml:space="preserve">10.4716358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7796230316162</t>
   </si>
   <si>
     <t xml:space="preserve">10.9105205535889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0106182098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9413204193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7565259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5255346298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6256313323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3099422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0943470001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9942512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27047824859619</t>
+    <t xml:space="preserve">11.0106163024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9413166046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7565269470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5255336761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6256294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3099403381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0943489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99425220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27047729492188</t>
   </si>
   <si>
     <t xml:space="preserve">9.34747505187988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2088794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29357528686523</t>
+    <t xml:space="preserve">9.20887851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29357624053955</t>
   </si>
   <si>
     <t xml:space="preserve">9.16268062591553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22427940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97788619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00868606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96248817443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92398929595947</t>
+    <t xml:space="preserve">9.22427845001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9778881072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00868701934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96249008178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92399024963379</t>
   </si>
   <si>
     <t xml:space="preserve">8.87778949737549</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80079460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85469150543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82389354705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7853946685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72379779815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63909816741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52360343933105</t>
+    <t xml:space="preserve">8.80079364776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85469245910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82389259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78539371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72379684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63909912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52360248565674</t>
   </si>
   <si>
     <t xml:space="preserve">8.62369918823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64679908752441</t>
+    <t xml:space="preserve">8.6467981338501</t>
   </si>
   <si>
     <t xml:space="preserve">8.60830020904541</t>
@@ -1088,37 +1088,37 @@
     <t xml:space="preserve">8.74689483642578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03178691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11648273468018</t>
+    <t xml:space="preserve">9.03178596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11648178100586</t>
   </si>
   <si>
     <t xml:space="preserve">9.13188171386719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93169021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15498161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37827205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30127620697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32437515258789</t>
+    <t xml:space="preserve">8.93168926239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15498352050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37827301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3012752532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32437324523926</t>
   </si>
   <si>
     <t xml:space="preserve">9.33207416534424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27817821502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26277732849121</t>
+    <t xml:space="preserve">9.27817726135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26277637481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.24737739562988</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">9.23967838287354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20118045806885</t>
+    <t xml:space="preserve">9.20117950439453</t>
   </si>
   <si>
     <t xml:space="preserve">9.10878276824951</t>
@@ -1136,28 +1136,28 @@
     <t xml:space="preserve">8.87009239196777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8469934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95479011535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73919773101807</t>
+    <t xml:space="preserve">8.84699249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9547872543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73919582366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.63139915466309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65449810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70839881896973</t>
+    <t xml:space="preserve">8.65449905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70839595794678</t>
   </si>
   <si>
     <t xml:space="preserve">8.79309368133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00098705291748</t>
+    <t xml:space="preserve">9.00098609924316</t>
   </si>
   <si>
     <t xml:space="preserve">9.04718589782715</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">10.0558490753174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1328468322754</t>
+    <t xml:space="preserve">10.1328458786011</t>
   </si>
   <si>
     <t xml:space="preserve">10.1020479202271</t>
@@ -1175,22 +1175,22 @@
     <t xml:space="preserve">10.0173511505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94035339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82485771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70166206359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45527076721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3089771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3397741317749</t>
+    <t xml:space="preserve">9.940354347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82485675811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70166301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45527172088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30897617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33977603912354</t>
   </si>
   <si>
     <t xml:space="preserve">9.41760635375977</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">9.44095611572266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43317413330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5032205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69779968261719</t>
+    <t xml:space="preserve">9.43317222595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50322151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6978006362915</t>
   </si>
   <si>
     <t xml:space="preserve">9.91572761535645</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">9.80676460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64331722259521</t>
+    <t xml:space="preserve">9.64332008361816</t>
   </si>
   <si>
     <t xml:space="preserve">9.76784801483154</t>
@@ -1229,28 +1229,28 @@
     <t xml:space="preserve">9.86124610900879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.13365650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4372005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1881370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0480403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95464324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0324754714966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1570053100586</t>
+    <t xml:space="preserve">10.1336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4371976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1881380081177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.048041343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9546422958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0324745178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1570043563843</t>
   </si>
   <si>
     <t xml:space="preserve">10.312668800354</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">10.3905000686646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3438005447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426195144653</t>
+    <t xml:space="preserve">10.3438014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426204681396</t>
   </si>
   <si>
     <t xml:space="preserve">10.4294147491455</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">10.6162109375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5928621292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6862573623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6784753799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9508867263794</t>
+    <t xml:space="preserve">10.5928611755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6862592697144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6784763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9508857727051</t>
   </si>
   <si>
     <t xml:space="preserve">11.0520677566528</t>
@@ -1295,67 +1295,67 @@
     <t xml:space="preserve">10.8341398239136</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9975843429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0831985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.293345451355</t>
+    <t xml:space="preserve">10.9975852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.083197593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2933435440063</t>
   </si>
   <si>
     <t xml:space="preserve">11.3011274337769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1843776702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2544288635254</t>
+    <t xml:space="preserve">11.184380531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2544279098511</t>
   </si>
   <si>
     <t xml:space="preserve">11.3166942596436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1610317230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.958667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9158601760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7018241882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5850772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3048830032349</t>
+    <t xml:space="preserve">11.1610326766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9586687088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9158611297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7018251419067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5850782394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3048858642578</t>
   </si>
   <si>
     <t xml:space="preserve">10.456657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0519332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99355792999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90016269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.063606262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.118088722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.262077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5734024047852</t>
+    <t xml:space="preserve">10.0519323348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99355983734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90016078948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0636072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1180877685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2620782852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5734014511108</t>
   </si>
   <si>
     <t xml:space="preserve">10.6668014526367</t>
@@ -1367,64 +1367,64 @@
     <t xml:space="preserve">10.8730545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3478288650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2427520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9469957351685</t>
+    <t xml:space="preserve">11.3478269577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2427549362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9469938278198</t>
   </si>
   <si>
     <t xml:space="preserve">11.0909833908081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1493577957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209331512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3050174713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7175245285034</t>
+    <t xml:space="preserve">11.149356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0209341049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3050184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7175264358521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5462980270386</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4645748138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1999483108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026573181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.277777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376810073853</t>
+    <t xml:space="preserve">11.4645709991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1999464035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026582717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2777767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376819610596</t>
   </si>
   <si>
     <t xml:space="preserve">11.3595008850098</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7642240524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0442838668823</t>
+    <t xml:space="preserve">11.7642230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.044282913208</t>
   </si>
   <si>
     <t xml:space="preserve">10.596752166748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6239919662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7640886306763</t>
+    <t xml:space="preserve">10.6239929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7640895843506</t>
   </si>
   <si>
     <t xml:space="preserve">10.6473436355591</t>
@@ -1436,34 +1436,34 @@
     <t xml:space="preserve">10.8964033126831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8263549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3244762420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.09876537323</t>
+    <t xml:space="preserve">10.8263540267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3244791030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0987644195557</t>
   </si>
   <si>
     <t xml:space="preserve">11.1298980712891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4451150894165</t>
+    <t xml:space="preserve">11.4451141357422</t>
   </si>
   <si>
     <t xml:space="preserve">11.6435852050781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708269119263</t>
+    <t xml:space="preserve">11.6708278656006</t>
   </si>
   <si>
     <t xml:space="preserve">11.5929956436157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.58131980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953567504883</t>
+    <t xml:space="preserve">11.5813207626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953577041626</t>
   </si>
   <si>
     <t xml:space="preserve">11.8654050827026</t>
@@ -1472,142 +1472,142 @@
     <t xml:space="preserve">11.9004306793213</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0716600418091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1611642837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8926467895508</t>
+    <t xml:space="preserve">12.0716581344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1611652374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8926458358765</t>
   </si>
   <si>
     <t xml:space="preserve">11.9393453598022</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8381633758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183576583862</t>
+    <t xml:space="preserve">11.8381652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183557510376</t>
   </si>
   <si>
     <t xml:space="preserve">12.5425386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5308637619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5581064224243</t>
+    <t xml:space="preserve">12.5308647155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.55810546875</t>
   </si>
   <si>
     <t xml:space="preserve">12.8344078063965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5542125701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7604684829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6631784439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7059860229492</t>
+    <t xml:space="preserve">12.5542135238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7604665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.663179397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7059869766235</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437196731567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7020931243896</t>
+    <t xml:space="preserve">12.702094078064</t>
   </si>
   <si>
     <t xml:space="preserve">12.9355897903442</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3597707748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3052854537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4556303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4635429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1549453735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661317825317</t>
+    <t xml:space="preserve">13.359769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.305287361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4556293487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4635410308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1549444198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661308288574</t>
   </si>
   <si>
     <t xml:space="preserve">12.5496206283569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4190587997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4863176345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5535764694214</t>
+    <t xml:space="preserve">12.419059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4863185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5535774230957</t>
   </si>
   <si>
     <t xml:space="preserve">12.1460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2964115142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0392475128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9996843338013</t>
+    <t xml:space="preserve">12.2964124679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0392484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.999683380127</t>
   </si>
   <si>
     <t xml:space="preserve">12.3478441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3122386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.395320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2726745605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4784059524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9007749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205560684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.797908782959</t>
+    <t xml:space="preserve">12.312237739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953199386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230175018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2726736068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4784049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9007740020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7979097366333</t>
   </si>
   <si>
     <t xml:space="preserve">11.8374719619751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4111471176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8809938430786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284677505493</t>
+    <t xml:space="preserve">12.4111480712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8809928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284687042236</t>
   </si>
   <si>
     <t xml:space="preserve">12.5377511978149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4665365219116</t>
+    <t xml:space="preserve">12.4665374755859</t>
   </si>
   <si>
     <t xml:space="preserve">12.4348850250244</t>
@@ -1616,31 +1616,31 @@
     <t xml:space="preserve">12.3755397796631</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5733604431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6089649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6050071716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6683111190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.992733001709</t>
+    <t xml:space="preserve">12.5733594894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6089668273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6050081253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6683130264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9927339553833</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520801544189</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6762256622314</t>
+    <t xml:space="preserve">12.6762247085571</t>
   </si>
   <si>
     <t xml:space="preserve">12.7355690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6010541915894</t>
+    <t xml:space="preserve">12.6010522842407</t>
   </si>
   <si>
     <t xml:space="preserve">12.5456619262695</t>
@@ -1649,73 +1649,73 @@
     <t xml:space="preserve">12.5575332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4546670913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4586238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2489356994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3201513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3676252365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5961332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7623014450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7702150344849</t>
+    <t xml:space="preserve">12.454665184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4586248397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2489337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3201494216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3676271438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.596134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7623023986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7702131271362</t>
   </si>
   <si>
     <t xml:space="preserve">11.9759454727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9324254989624</t>
+    <t xml:space="preserve">11.9324264526367</t>
   </si>
   <si>
     <t xml:space="preserve">12.027379989624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8216457366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.532829284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5170068740845</t>
+    <t xml:space="preserve">11.821647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5328321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418363571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5170059204102</t>
   </si>
   <si>
     <t xml:space="preserve">11.6159162521362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5921754837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7148246765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0867233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8889055252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.892861366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2281913757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4339227676392</t>
+    <t xml:space="preserve">11.5921773910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.714825630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.086724281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8889064788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8928632736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2281904220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4339218139648</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062271118164</t>
@@ -1724,40 +1724,40 @@
     <t xml:space="preserve">11.3310556411743</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9947652816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9037666320801</t>
+    <t xml:space="preserve">10.9947643280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9037675857544</t>
   </si>
   <si>
     <t xml:space="preserve">10.7257318496704</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6228666305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6901235580444</t>
+    <t xml:space="preserve">10.6228647232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6901245117188</t>
   </si>
   <si>
     <t xml:space="preserve">10.9433307647705</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9314622879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9354190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9987230300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1451053619385</t>
+    <t xml:space="preserve">10.9314632415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9354200363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9987201690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1451072692871</t>
   </si>
   <si>
     <t xml:space="preserve">11.1530199050903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0857610702515</t>
+    <t xml:space="preserve">11.0857620239258</t>
   </si>
   <si>
     <t xml:space="preserve">11.0066328048706</t>
@@ -1766,61 +1766,61 @@
     <t xml:space="preserve">11.117413520813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7306509017944</t>
+    <t xml:space="preserve">11.7306518554688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6396541595459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5842628479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4180974960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7266941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820844650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9482507705688</t>
+    <t xml:space="preserve">11.5842638015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4180955886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.72669506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820854187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9482517242432</t>
   </si>
   <si>
     <t xml:space="preserve">11.6277837753296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.572395324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9601182937622</t>
+    <t xml:space="preserve">11.5723934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9601202011108</t>
   </si>
   <si>
     <t xml:space="preserve">11.6238279342651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1332406997681</t>
+    <t xml:space="preserve">11.1332378387451</t>
   </si>
   <si>
     <t xml:space="preserve">11.1411504745483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886262893677</t>
+    <t xml:space="preserve">11.188627243042</t>
   </si>
   <si>
     <t xml:space="preserve">11.3112745285034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2400608062744</t>
+    <t xml:space="preserve">11.2400598526001</t>
   </si>
   <si>
     <t xml:space="preserve">11.093674659729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0818042755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8325529098511</t>
+    <t xml:space="preserve">11.081805229187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8325538635254</t>
   </si>
   <si>
     <t xml:space="preserve">10.4052648544312</t>
@@ -1829,67 +1829,67 @@
     <t xml:space="preserve">10.2984428405762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2628364562988</t>
+    <t xml:space="preserve">10.2628345489502</t>
   </si>
   <si>
     <t xml:space="preserve">10.1718378067017</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2034893035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0927114486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3933954238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5635204315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.62682056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6307783126831</t>
+    <t xml:space="preserve">10.2034902572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0927104949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3933963775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5635213851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6268224716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6307802200317</t>
   </si>
   <si>
     <t xml:space="preserve">10.6189088821411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5200004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4843940734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2430543899536</t>
+    <t xml:space="preserve">10.5199995040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.484393119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2430534362793</t>
   </si>
   <si>
     <t xml:space="preserve">10.1599702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85137176513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75641822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87511157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78015899658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68019580841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40830421447754</t>
+    <t xml:space="preserve">9.85137271881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75641918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8751106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78015804290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68019485473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40830516815186</t>
   </si>
   <si>
     <t xml:space="preserve">9.58823299407959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45228481292725</t>
+    <t xml:space="preserve">9.45228576660156</t>
   </si>
   <si>
     <t xml:space="preserve">9.29634761810303</t>
@@ -1901,55 +1901,55 @@
     <t xml:space="preserve">9.38031387329102</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71657466888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66059684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49666213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78854656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67259311676025</t>
+    <t xml:space="preserve">8.71657371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6605978012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49666118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78854751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67259120941162</t>
   </si>
   <si>
     <t xml:space="preserve">8.50865840911865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22876644134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24875736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99685716629028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10881519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20077800750732</t>
+    <t xml:space="preserve">8.22876739501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24875926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99685859680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10881423950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20077896118164</t>
   </si>
   <si>
     <t xml:space="preserve">8.18078708648682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89130020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71217012405396</t>
+    <t xml:space="preserve">7.89130115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7121696472168</t>
   </si>
   <si>
     <t xml:space="preserve">7.71376943588257</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38110113143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39389562606812</t>
+    <t xml:space="preserve">7.38109970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39389657974243</t>
   </si>
   <si>
     <t xml:space="preserve">7.3427152633667</t>
@@ -1961,49 +1961,49 @@
     <t xml:space="preserve">7.61141014099121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59861516952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88490104675293</t>
+    <t xml:space="preserve">7.59861421585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88490152359009</t>
   </si>
   <si>
     <t xml:space="preserve">8.01285266876221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05683326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29674053192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31673240661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24076175689697</t>
+    <t xml:space="preserve">8.05683517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29673957824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31673145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24076080322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.16878986358643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22476863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52065181732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45267868041992</t>
+    <t xml:space="preserve">8.22476959228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52065086364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45267963409424</t>
   </si>
   <si>
     <t xml:space="preserve">8.3207311630249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39670085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53264999389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8245325088501</t>
+    <t xml:space="preserve">8.39669990539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53264713287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82453346252441</t>
   </si>
   <si>
     <t xml:space="preserve">8.58862590789795</t>
@@ -2012,43 +2012,43 @@
     <t xml:space="preserve">8.70058155059814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76855564117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75655841827393</t>
+    <t xml:space="preserve">8.76855659484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75656032562256</t>
   </si>
   <si>
     <t xml:space="preserve">8.93249034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9884672164917</t>
+    <t xml:space="preserve">8.98846912384033</t>
   </si>
   <si>
     <t xml:space="preserve">8.76455593109131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56463718414307</t>
+    <t xml:space="preserve">8.56463432312012</t>
   </si>
   <si>
     <t xml:space="preserve">8.7445650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95248222351074</t>
+    <t xml:space="preserve">8.95248317718506</t>
   </si>
   <si>
     <t xml:space="preserve">9.20838260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22037792205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43629360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49227142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55224704742432</t>
+    <t xml:space="preserve">9.22037887573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43629264831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49227046966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55224609375</t>
   </si>
   <si>
     <t xml:space="preserve">9.59622955322266</t>
@@ -2057,22 +2057,22 @@
     <t xml:space="preserve">9.75616645812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63221645355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61622142791748</t>
+    <t xml:space="preserve">9.63221454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6162223815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.51626110076904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51226329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3323335647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39231014251709</t>
+    <t xml:space="preserve">9.51226234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33233261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39230823516846</t>
   </si>
   <si>
     <t xml:space="preserve">9.36432075500488</t>
@@ -2084,7 +2084,7 @@
     <t xml:space="preserve">9.25236511230469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11242008209229</t>
+    <t xml:space="preserve">9.1124210357666</t>
   </si>
   <si>
     <t xml:space="preserve">9.42029857635498</t>
@@ -2093,34 +2093,34 @@
     <t xml:space="preserve">9.84413242340088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89611053466797</t>
+    <t xml:space="preserve">9.8961124420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.84813022613525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86812400817871</t>
+    <t xml:space="preserve">9.86812305450439</t>
   </si>
   <si>
     <t xml:space="preserve">9.98407649993896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.036057472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3079509735107</t>
+    <t xml:space="preserve">10.0360584259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3079519271851</t>
   </si>
   <si>
     <t xml:space="preserve">10.2039909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0680446624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82813835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0080680847168</t>
+    <t xml:space="preserve">10.0680465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82813739776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0080690383911</t>
   </si>
   <si>
     <t xml:space="preserve">10.2759637832642</t>
@@ -2129,25 +2129,25 @@
     <t xml:space="preserve">10.1720027923584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1440143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95608997344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2559700012207</t>
+    <t xml:space="preserve">10.1440162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95608711242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.255970954895</t>
   </si>
   <si>
     <t xml:space="preserve">10.3199443817139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0440530776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93609714508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0040693283081</t>
+    <t xml:space="preserve">10.0440549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93609619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0040702819824</t>
   </si>
   <si>
     <t xml:space="preserve">10.0560483932495</t>
@@ -2168,73 +2168,73 @@
     <t xml:space="preserve">10.559850692749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3359384536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9281005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90011119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74017333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60422801971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44029140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60822582244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41230392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34033012390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54025077819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61222362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96408462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0160646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.024245262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1755695343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85655975341797</t>
+    <t xml:space="preserve">10.3359403610229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92809963226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90010929107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74017429351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60422515869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44028949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60822486877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41230201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34033107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29234790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54025173187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61222171783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96408653259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0160665512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0242443084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1755714416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85656070709229</t>
   </si>
   <si>
     <t xml:space="preserve">9.4393949508667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32488059997559</t>
+    <t xml:space="preserve">9.32487678527832</t>
   </si>
   <si>
     <t xml:space="preserve">9.16128444671631</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15310478210449</t>
+    <t xml:space="preserve">9.15310382843018</t>
   </si>
   <si>
     <t xml:space="preserve">9.0140495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98542022705078</t>
+    <t xml:space="preserve">8.9854211807251</t>
   </si>
   <si>
     <t xml:space="preserve">8.62960338592529</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">8.8749942779541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08766651153564</t>
+    <t xml:space="preserve">9.08766555786133</t>
   </si>
   <si>
     <t xml:space="preserve">8.78910732269287</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">8.79728698730469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78092861175537</t>
+    <t xml:space="preserve">8.78092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">9.06312847137451</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">8.94452285766602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83409595489502</t>
+    <t xml:space="preserve">8.83409690856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.87908458709717</t>
@@ -2273,28 +2273,28 @@
     <t xml:space="preserve">9.05085945129395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29624843597412</t>
+    <t xml:space="preserve">9.29625034332275</t>
   </si>
   <si>
     <t xml:space="preserve">9.39440536499023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25126075744629</t>
+    <t xml:space="preserve">9.25126171112061</t>
   </si>
   <si>
     <t xml:space="preserve">9.14901542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42303562164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38213729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41485595703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65206718444824</t>
+    <t xml:space="preserve">9.42303466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3821382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41485691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65206813812256</t>
   </si>
   <si>
     <t xml:space="preserve">9.42712497711182</t>
@@ -2303,58 +2303,58 @@
     <t xml:space="preserve">9.44757556915283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54573059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54164028167725</t>
+    <t xml:space="preserve">9.54573154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5416431427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.75431346893311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66024875640869</t>
+    <t xml:space="preserve">9.66024780273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.80748271942139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98743724822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94244861602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83202171325684</t>
+    <t xml:space="preserve">9.98743629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94244766235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83202266693115</t>
   </si>
   <si>
     <t xml:space="preserve">9.82793235778809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45166397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28806972503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12038516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24308300018311</t>
+    <t xml:space="preserve">9.45166492462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28807067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12038707733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24308109283447</t>
   </si>
   <si>
     <t xml:space="preserve">9.31260967254639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59071922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5089225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26762199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93225383758545</t>
+    <t xml:space="preserve">9.59072113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50892162322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26762008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93225288391113</t>
   </si>
   <si>
     <t xml:space="preserve">8.71548938751221</t>
@@ -2363,46 +2363,46 @@
     <t xml:space="preserve">8.56416511535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3637638092041</t>
+    <t xml:space="preserve">8.36376190185547</t>
   </si>
   <si>
     <t xml:space="preserve">8.29423427581787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44556140899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787399291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00958156585693</t>
+    <t xml:space="preserve">8.44555854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00958061218262</t>
   </si>
   <si>
     <t xml:space="preserve">8.14209175109863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71838188171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75764560699463</t>
+    <t xml:space="preserve">7.71838235855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75764513015747</t>
   </si>
   <si>
     <t xml:space="preserve">8.05211448669434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88852119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98340511322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08810520172119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96377182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07011032104492</t>
+    <t xml:space="preserve">7.88851976394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98340559005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08810424804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96377468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07011127471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.12409687042236</t>
@@ -2411,37 +2411,37 @@
     <t xml:space="preserve">8.21652698516846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16335678100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10937309265137</t>
+    <t xml:space="preserve">8.16335868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10937404632568</t>
   </si>
   <si>
     <t xml:space="preserve">8.06520175933838</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86070871353149</t>
+    <t xml:space="preserve">7.86071014404297</t>
   </si>
   <si>
     <t xml:space="preserve">8.00467300415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21243858337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17153739929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41284084320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51099681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43738079071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31468486785889</t>
+    <t xml:space="preserve">8.21243667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17154026031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.412841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5109977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43737983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31468296051025</t>
   </si>
   <si>
     <t xml:space="preserve">8.37194156646729</t>
@@ -2450,55 +2450,55 @@
     <t xml:space="preserve">8.60506439208984</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44146633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31877326965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22061634063721</t>
+    <t xml:space="preserve">8.44146823883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.318772315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22061729431152</t>
   </si>
   <si>
     <t xml:space="preserve">8.20016765594482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97195386886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85743713378906</t>
+    <t xml:space="preserve">7.97195339202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85743570327759</t>
   </si>
   <si>
     <t xml:space="preserve">7.85252952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72983455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00794410705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96213865280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81326723098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48771476745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56296825408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54824352264404</t>
+    <t xml:space="preserve">7.72983360290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00794315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96213817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81326627731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48771524429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56296920776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54824447631836</t>
   </si>
   <si>
     <t xml:space="preserve">7.63658618927002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5089807510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54333639144897</t>
+    <t xml:space="preserve">7.50898122787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54333543777466</t>
   </si>
   <si>
     <t xml:space="preserve">7.61531829833984</t>
@@ -2507,25 +2507,25 @@
     <t xml:space="preserve">7.88034105300903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67257690429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77400493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74292182922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64803695678711</t>
+    <t xml:space="preserve">7.67257642745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77400398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74292087554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64803743362427</t>
   </si>
   <si>
     <t xml:space="preserve">7.60713911056519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66276073455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68239164352417</t>
+    <t xml:space="preserve">7.66275930404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68239212036133</t>
   </si>
   <si>
     <t xml:space="preserve">7.70202398300171</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">7.61858987808228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69220733642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80999517440796</t>
+    <t xml:space="preserve">7.69220876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80999612808228</t>
   </si>
   <si>
     <t xml:space="preserve">7.88524961471558</t>
@@ -2546,28 +2546,28 @@
     <t xml:space="preserve">7.65785264968872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40591812133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03739261627197</t>
+    <t xml:space="preserve">7.40591716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03739166259766</t>
   </si>
   <si>
     <t xml:space="preserve">8.17644691467285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3228645324707</t>
+    <t xml:space="preserve">8.32286357879639</t>
   </si>
   <si>
     <t xml:space="preserve">8.18380737304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19607830047607</t>
+    <t xml:space="preserve">8.19607734680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.23697662353516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10446453094482</t>
+    <t xml:space="preserve">8.10446643829346</t>
   </si>
   <si>
     <t xml:space="preserve">8.10282897949219</t>
@@ -2576,52 +2576,52 @@
     <t xml:space="preserve">8.0995569229126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02993202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95865201950073</t>
+    <t xml:space="preserve">8.02993297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95865154266357</t>
   </si>
   <si>
     <t xml:space="preserve">8.0896110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04153633117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16917991638184</t>
+    <t xml:space="preserve">8.04153823852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16918182373047</t>
   </si>
   <si>
     <t xml:space="preserve">8.15094566345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15592002868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08629608154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00009632110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85587358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80116939544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96694040298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03987884521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21227931976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24377727508545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26864242553711</t>
+    <t xml:space="preserve">8.15591907501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08629512786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00009441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85587406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80116987228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96693992614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03987979888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21228218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24377822875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26864433288574</t>
   </si>
   <si>
     <t xml:space="preserve">8.29682445526123</t>
@@ -2630,40 +2630,40 @@
     <t xml:space="preserve">8.53304862976074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44187259674072</t>
+    <t xml:space="preserve">8.44187450408936</t>
   </si>
   <si>
     <t xml:space="preserve">8.4625940322876</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40872097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39214324951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3797082901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42944049835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49575042724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36313343048096</t>
+    <t xml:space="preserve">8.40872001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39214134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37971019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42943859100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49574851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36313247680664</t>
   </si>
   <si>
     <t xml:space="preserve">8.32997798919678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37142181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48331546783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71125221252441</t>
+    <t xml:space="preserve">8.37142276763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48331642150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71125030517578</t>
   </si>
   <si>
     <t xml:space="preserve">8.69881820678711</t>
@@ -2678,40 +2678,40 @@
     <t xml:space="preserve">8.60350036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45016098022461</t>
+    <t xml:space="preserve">8.45016193389893</t>
   </si>
   <si>
     <t xml:space="preserve">8.40043067932129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45430755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52890300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50403690338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47088432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41700744628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37556552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05811405181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18741607666016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2868766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88074111938477</t>
+    <t xml:space="preserve">8.45430660247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52890396118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50403785705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4708833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41700839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37556457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05811500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18741512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28687763214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88073873519897</t>
   </si>
   <si>
     <t xml:space="preserve">7.73154640197754</t>
@@ -2723,55 +2723,55 @@
     <t xml:space="preserve">7.80282688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90891981124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78790950775146</t>
+    <t xml:space="preserve">7.90892028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93212795257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78790712356567</t>
   </si>
   <si>
     <t xml:space="preserve">7.83598136901855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90063190460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00672435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98186016082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80448579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84095573425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13105392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76967334747314</t>
+    <t xml:space="preserve">7.90063142776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00672626495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98186063766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8044867515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8409538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13105297088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76967239379883</t>
   </si>
   <si>
     <t xml:space="preserve">7.37679672241211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27733373641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29391145706177</t>
+    <t xml:space="preserve">7.27733325958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29391098022461</t>
   </si>
   <si>
     <t xml:space="preserve">6.97563219070435</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77007579803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7186861038208</t>
+    <t xml:space="preserve">6.77007627487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71868705749512</t>
   </si>
   <si>
     <t xml:space="preserve">6.75018358230591</t>
@@ -2780,49 +2780,49 @@
     <t xml:space="preserve">6.57612419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45511102676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08378601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78248500823975</t>
+    <t xml:space="preserve">6.45511198043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08378505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78248596191406</t>
   </si>
   <si>
     <t xml:space="preserve">4.65815687179565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56201028823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87903523445129</t>
+    <t xml:space="preserve">4.56200933456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87903451919556</t>
   </si>
   <si>
     <t xml:space="preserve">3.97766804695129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71989488601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85085344314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94534373283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15918731689453</t>
+    <t xml:space="preserve">3.71989417076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85085296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94534301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15918779373169</t>
   </si>
   <si>
     <t xml:space="preserve">4.32661485671997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26362228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43436574935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46089029312134</t>
+    <t xml:space="preserve">4.26362276077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43436670303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46088981628418</t>
   </si>
   <si>
     <t xml:space="preserve">4.70788812637329</t>
@@ -2831,58 +2831,58 @@
     <t xml:space="preserve">4.61505603790283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62500238418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54543399810791</t>
+    <t xml:space="preserve">4.59019041061401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62500333786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54543209075928</t>
   </si>
   <si>
     <t xml:space="preserve">4.7543044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78745794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.906813621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13226127624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01456499099731</t>
+    <t xml:space="preserve">4.7874584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90681266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13226079940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01456451416016</t>
   </si>
   <si>
     <t xml:space="preserve">4.97809457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91178703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6913104057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77751064300537</t>
+    <t xml:space="preserve">4.91178560256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69131135940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77751207351685</t>
   </si>
   <si>
     <t xml:space="preserve">4.80735015869141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77916955947876</t>
+    <t xml:space="preserve">4.77916860580444</t>
   </si>
   <si>
     <t xml:space="preserve">4.54045963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6813645362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86702823638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90515518188477</t>
+    <t xml:space="preserve">4.68136501312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86702728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90515613555908</t>
   </si>
   <si>
     <t xml:space="preserve">4.89686727523804</t>
@@ -2891,19 +2891,19 @@
     <t xml:space="preserve">4.99135589599609</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28311252593994</t>
+    <t xml:space="preserve">5.2831130027771</t>
   </si>
   <si>
     <t xml:space="preserve">5.29968976974487</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00627565383911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24664258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04440259933472</t>
+    <t xml:space="preserve">5.00627517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24664306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04440355300903</t>
   </si>
   <si>
     <t xml:space="preserve">5.12065696716309</t>
@@ -2912,25 +2912,25 @@
     <t xml:space="preserve">5.16375732421875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07092666625977</t>
+    <t xml:space="preserve">5.07092618942261</t>
   </si>
   <si>
     <t xml:space="preserve">4.98141002655029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76425075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79408836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15878391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69959926605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85045099258423</t>
+    <t xml:space="preserve">4.7642502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79408884048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15878486633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6995997428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85045051574707</t>
   </si>
   <si>
     <t xml:space="preserve">4.61174154281616</t>
@@ -2942,49 +2942,49 @@
     <t xml:space="preserve">4.64157962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71451902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72114992141724</t>
+    <t xml:space="preserve">4.71451950073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72114944458008</t>
   </si>
   <si>
     <t xml:space="preserve">4.83718919754028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63494968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84382009506226</t>
+    <t xml:space="preserve">4.63494920730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84382057189941</t>
   </si>
   <si>
     <t xml:space="preserve">5.04606008529663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29803133010864</t>
+    <t xml:space="preserve">5.29803228378296</t>
   </si>
   <si>
     <t xml:space="preserve">5.3527364730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63288879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71577453613281</t>
+    <t xml:space="preserve">5.63288927078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71577405929565</t>
   </si>
   <si>
     <t xml:space="preserve">5.61465454101562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53508424758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18365049362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18862295150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1819920539856</t>
+    <t xml:space="preserve">5.53508377075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18365097045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18862342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18199253082275</t>
   </si>
   <si>
     <t xml:space="preserve">5.1306037902832</t>
@@ -2993,25 +2993,25 @@
     <t xml:space="preserve">5.12894582748413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04108667373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14220762252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8239278793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88692045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76093530654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81398153305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70623064041138</t>
+    <t xml:space="preserve">5.04108715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14220714569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82392740249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88692092895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76093482971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8139820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70622968673706</t>
   </si>
   <si>
     <t xml:space="preserve">4.85210847854614</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">4.76259183883667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93002128601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84547853469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76756620407104</t>
+    <t xml:space="preserve">4.93002080917358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84547805786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76756525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.5968222618103</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">4.62168741226196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67804956436157</t>
+    <t xml:space="preserve">4.67804908752441</t>
   </si>
   <si>
     <t xml:space="preserve">4.75761938095093</t>
@@ -3044,37 +3044,37 @@
     <t xml:space="preserve">4.76590824127197</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89355134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78414297103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70291519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66810321807861</t>
+    <t xml:space="preserve">4.89355087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7841420173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70291566848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66810274124146</t>
   </si>
   <si>
     <t xml:space="preserve">4.58024501800537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49072885513306</t>
+    <t xml:space="preserve">4.49072933197021</t>
   </si>
   <si>
     <t xml:space="preserve">4.27191114425659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19234132766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0879054069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28185701370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29346132278442</t>
+    <t xml:space="preserve">4.19234085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08790588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28185796737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29346084594727</t>
   </si>
   <si>
     <t xml:space="preserve">4.48575592041016</t>
@@ -3086,70 +3086,70 @@
     <t xml:space="preserve">4.2901463508606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43602466583252</t>
+    <t xml:space="preserve">4.43602418899536</t>
   </si>
   <si>
     <t xml:space="preserve">4.41447401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32164192199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27688360214233</t>
+    <t xml:space="preserve">4.32164287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27688407897949</t>
   </si>
   <si>
     <t xml:space="preserve">4.23875713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19731473922729</t>
+    <t xml:space="preserve">4.19731426239014</t>
   </si>
   <si>
     <t xml:space="preserve">4.10448265075684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08624744415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22383832931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17576503753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13349342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05806684494019</t>
+    <t xml:space="preserve">4.08624792098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22383785247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1757640838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1334924697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0580677986145</t>
   </si>
   <si>
     <t xml:space="preserve">4.082932472229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07796001434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00004816055298</t>
+    <t xml:space="preserve">4.0779595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00004720687866</t>
   </si>
   <si>
     <t xml:space="preserve">3.9619197845459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98927330970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00087642669678</t>
+    <t xml:space="preserve">3.9892725944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00087547302246</t>
   </si>
   <si>
     <t xml:space="preserve">3.97601079940796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83925008773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8442223072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82598805427551</t>
+    <t xml:space="preserve">3.83924913406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84422302246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82598853111267</t>
   </si>
   <si>
     <t xml:space="preserve">3.77957224845886</t>
@@ -3158,34 +3158,34 @@
     <t xml:space="preserve">3.74724698066711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80112195014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95943307876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96274900436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85334014892578</t>
+    <t xml:space="preserve">3.80112266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95943379402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96274852752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85334038734436</t>
   </si>
   <si>
     <t xml:space="preserve">3.60053968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5607545375824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53091645240784</t>
+    <t xml:space="preserve">3.56075477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53091621398926</t>
   </si>
   <si>
     <t xml:space="preserve">3.45880556106567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39747142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53754734992981</t>
+    <t xml:space="preserve">3.39747071266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53754758834839</t>
   </si>
   <si>
     <t xml:space="preserve">3.42399406433105</t>
@@ -3194,58 +3194,58 @@
     <t xml:space="preserve">3.53174519538879</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44139981269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5209698677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5557816028595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65358662605286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58064794540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69005608558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66436171531677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60302639007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51350998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60717034339905</t>
+    <t xml:space="preserve">3.44140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52097034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55578184127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65358638763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58064770698547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69005632400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66436123847961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60302662849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51351046562195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60717129707336</t>
   </si>
   <si>
     <t xml:space="preserve">3.4273099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5508086681366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62623429298401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71077799797058</t>
+    <t xml:space="preserve">3.55080890655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62623405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71077728271484</t>
   </si>
   <si>
     <t xml:space="preserve">3.61877489089966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63783836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67099213600159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5740168094635</t>
+    <t xml:space="preserve">3.63783812522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67099261283875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57401585578918</t>
   </si>
   <si>
     <t xml:space="preserve">3.47455430030823</t>
@@ -3260,34 +3260,34 @@
     <t xml:space="preserve">3.37509179115295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55163717269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63535189628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19399833679199</t>
+    <t xml:space="preserve">3.55163741111755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63535213470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19399976730347</t>
   </si>
   <si>
     <t xml:space="preserve">4.17244863510132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57029867172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63660669326782</t>
+    <t xml:space="preserve">4.57029914855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63660621643066</t>
   </si>
   <si>
     <t xml:space="preserve">4.64655303955078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6763916015625</t>
+    <t xml:space="preserve">4.67639207839966</t>
   </si>
   <si>
     <t xml:space="preserve">4.74601554870605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11402702331543</t>
+    <t xml:space="preserve">5.11402654647827</t>
   </si>
   <si>
     <t xml:space="preserve">5.21183109283447</t>
@@ -3302,61 +3302,61 @@
     <t xml:space="preserve">5.18033504486084</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39324808120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73357486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67825078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60113286972046</t>
+    <t xml:space="preserve">5.39324855804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73357439041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67825031280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6011323928833</t>
   </si>
   <si>
     <t xml:space="preserve">5.61957359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43683671951294</t>
+    <t xml:space="preserve">5.4368371963501</t>
   </si>
   <si>
     <t xml:space="preserve">5.52066087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54748439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58101415634155</t>
+    <t xml:space="preserve">5.54748392105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58101367950439</t>
   </si>
   <si>
     <t xml:space="preserve">5.80901575088501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70339727401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71178007125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71513319015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80231046676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70004415512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62627935409546</t>
+    <t xml:space="preserve">5.70339775085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7117805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71513271331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80231094360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70004510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6262788772583</t>
   </si>
   <si>
     <t xml:space="preserve">5.69501543045044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66651582717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72183990478516</t>
+    <t xml:space="preserve">5.6665153503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.721839427948</t>
   </si>
   <si>
     <t xml:space="preserve">5.63801431655884</t>
@@ -3365,43 +3365,43 @@
     <t xml:space="preserve">5.4904842376709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47539663314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6279559135437</t>
+    <t xml:space="preserve">5.47539615631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62795639038086</t>
   </si>
   <si>
     <t xml:space="preserve">5.58772039413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51227807998657</t>
+    <t xml:space="preserve">5.51227855682373</t>
   </si>
   <si>
     <t xml:space="preserve">5.55251407623291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47874927520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67489719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97834157943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9699592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93642854690552</t>
+    <t xml:space="preserve">5.4787483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67489767074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9783411026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96995830535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93642902374268</t>
   </si>
   <si>
     <t xml:space="preserve">5.82913398742676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99678230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9129581451416</t>
+    <t xml:space="preserve">5.9967827796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91295766830444</t>
   </si>
   <si>
     <t xml:space="preserve">5.96492910385132</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">5.65813255310059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64304399490356</t>
+    <t xml:space="preserve">5.64304447174072</t>
   </si>
   <si>
     <t xml:space="preserve">5.4619836807251</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27254152297974</t>
+    <t xml:space="preserve">5.27254104614258</t>
   </si>
   <si>
     <t xml:space="preserve">5.17865800857544</t>
@@ -3425,31 +3425,31 @@
     <t xml:space="preserve">5.24739408493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33792400360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50054359436035</t>
+    <t xml:space="preserve">5.33792495727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50054311752319</t>
   </si>
   <si>
     <t xml:space="preserve">5.38989496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3815131187439</t>
+    <t xml:space="preserve">5.38151264190674</t>
   </si>
   <si>
     <t xml:space="preserve">5.60448551177979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69333791732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80733966827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92972326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82410526275635</t>
+    <t xml:space="preserve">5.6933388710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80733919143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92972278594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82410430908203</t>
   </si>
   <si>
     <t xml:space="preserve">5.89451694488525</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">5.95990037918091</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31196117401123</t>
+    <t xml:space="preserve">6.31196212768555</t>
   </si>
   <si>
     <t xml:space="preserve">6.32202005386353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17951917648315</t>
+    <t xml:space="preserve">6.179518699646</t>
   </si>
   <si>
     <t xml:space="preserve">6.03534173965454</t>
@@ -3482,148 +3482,148 @@
     <t xml:space="preserve">6.22813701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44440364837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32958650588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24744033813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41508865356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53579568862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51902914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78559017181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02700519561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14435768127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00520992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1108283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30697727203369</t>
+    <t xml:space="preserve">6.44440412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32958793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24743938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41508769989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53579425811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51902961730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78559112548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02700328826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1443567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00520896911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11082744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30697631835938</t>
   </si>
   <si>
     <t xml:space="preserve">8.31200695037842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10579967498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12926959991455</t>
+    <t xml:space="preserve">8.10579872131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12927055358887</t>
   </si>
   <si>
     <t xml:space="preserve">8.09741592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99682664871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81576681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75038480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61961984634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90294361114502</t>
+    <t xml:space="preserve">7.99682712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81576776504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75038576126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61961793899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90294456481934</t>
   </si>
   <si>
     <t xml:space="preserve">7.69170713424683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97168159484863</t>
+    <t xml:space="preserve">7.97167873382568</t>
   </si>
   <si>
     <t xml:space="preserve">8.01526832580566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09573936462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0571813583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10076904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10915374755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98174142837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77720785140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69506025314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63973569869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62967824935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99850273132324</t>
+    <t xml:space="preserve">8.09574031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05718040466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10076999664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10915184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98173809051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77720737457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69506120681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63973712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62967729568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99850368499756</t>
   </si>
   <si>
     <t xml:space="preserve">7.70679664611816</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68332481384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73864889144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39496994018555</t>
+    <t xml:space="preserve">7.68332624435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73864936828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39496946334839</t>
   </si>
   <si>
     <t xml:space="preserve">7.47041177749634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46370601654053</t>
+    <t xml:space="preserve">7.46370553970337</t>
   </si>
   <si>
     <t xml:space="preserve">7.44358825683594</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70008993148804</t>
+    <t xml:space="preserve">7.70008945465088</t>
   </si>
   <si>
     <t xml:space="preserve">7.53914785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79229545593262</t>
+    <t xml:space="preserve">7.79229593276978</t>
   </si>
   <si>
     <t xml:space="preserve">7.26420497894287</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50897073745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57603025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63806009292603</t>
+    <t xml:space="preserve">7.50897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5760293006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6380615234375</t>
   </si>
   <si>
     <t xml:space="preserve">7.98006343841553</t>
@@ -3632,13 +3632,13 @@
     <t xml:space="preserve">8.12591648101807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20806503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28350639343262</t>
+    <t xml:space="preserve">8.20806407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01359272003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2835054397583</t>
   </si>
   <si>
     <t xml:space="preserve">8.19632816314697</t>
@@ -3650,31 +3650,31 @@
     <t xml:space="preserve">8.12759208679199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90462160110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85600328445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92976951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9586968421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80214405059814</t>
+    <t xml:space="preserve">7.90462112426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85600185394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92976856231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95869588851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80214309692383</t>
   </si>
   <si>
     <t xml:space="preserve">7.82596588134766</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04548263549805</t>
+    <t xml:space="preserve">8.04548168182373</t>
   </si>
   <si>
     <t xml:space="preserve">7.96039772033691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93827772140503</t>
+    <t xml:space="preserve">7.93827676773071</t>
   </si>
   <si>
     <t xml:space="preserve">8.15268611907959</t>
@@ -3689,49 +3689,49 @@
     <t xml:space="preserve">8.1918249130249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20203685760498</t>
+    <t xml:space="preserve">8.20203495025635</t>
   </si>
   <si>
     <t xml:space="preserve">8.17140579223633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11354923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12545871734619</t>
+    <t xml:space="preserve">8.11354827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12546062469482</t>
   </si>
   <si>
     <t xml:space="preserve">8.2905216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14077377319336</t>
+    <t xml:space="preserve">8.14077568054199</t>
   </si>
   <si>
     <t xml:space="preserve">8.13056564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94848728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81575775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84468507766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92296171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97571277618408</t>
+    <t xml:space="preserve">7.94848680496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81575632095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84468603134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92296266555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9757137298584</t>
   </si>
   <si>
     <t xml:space="preserve">8.02506160736084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07100772857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8038444519043</t>
+    <t xml:space="preserve">8.07100677490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80384492874146</t>
   </si>
   <si>
     <t xml:space="preserve">7.80554628372192</t>
@@ -3740,85 +3740,85 @@
     <t xml:space="preserve">7.82086229324341</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97060918807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96550273895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02165794372559</t>
+    <t xml:space="preserve">7.97060775756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96550369262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0216588973999</t>
   </si>
   <si>
     <t xml:space="preserve">7.64388847351074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52987670898438</t>
+    <t xml:space="preserve">7.52987718582153</t>
   </si>
   <si>
     <t xml:space="preserve">7.42607355117798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65920305252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63197565078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46861696243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59964561462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521425247192</t>
+    <t xml:space="preserve">7.65920352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63197755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4686164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59964466094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521329879761</t>
   </si>
   <si>
     <t xml:space="preserve">7.25420713424683</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00235939025879</t>
+    <t xml:space="preserve">7.00235986709595</t>
   </si>
   <si>
     <t xml:space="preserve">7.12317848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26271533966064</t>
+    <t xml:space="preserve">7.2627158164978</t>
   </si>
   <si>
     <t xml:space="preserve">7.18103408813477</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26441764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47372198104858</t>
+    <t xml:space="preserve">7.26441621780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47372150421143</t>
   </si>
   <si>
     <t xml:space="preserve">7.40735673904419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47031831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46691513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29674863815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35800838470459</t>
+    <t xml:space="preserve">7.47031736373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46691465377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29674768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35800790786743</t>
   </si>
   <si>
     <t xml:space="preserve">7.40565538406372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30865955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28313446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48222923278809</t>
+    <t xml:space="preserve">7.30866003036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28313541412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4822301864624</t>
   </si>
   <si>
     <t xml:space="preserve">7.44139099121094</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">7.30185270309448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33418560028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99385118484497</t>
+    <t xml:space="preserve">7.33418464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99385213851929</t>
   </si>
   <si>
     <t xml:space="preserve">6.93769645690918</t>
@@ -3854,46 +3854,46 @@
     <t xml:space="preserve">7.22187471389771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33758783340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25761079788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34269380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22527837753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2116641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14700126647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09425020217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0636191368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30695819854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25590896606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3767261505127</t>
+    <t xml:space="preserve">7.33758735656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25760984420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34269332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22527742385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21166563034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14700078964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09424924850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06361961364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30695962905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25590848922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37672710418701</t>
   </si>
   <si>
     <t xml:space="preserve">7.14019536972046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87473440170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87303304672241</t>
+    <t xml:space="preserve">6.87473487854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8730320930481</t>
   </si>
   <si>
     <t xml:space="preserve">7.23038339614868</t>
@@ -3902,34 +3902,34 @@
     <t xml:space="preserve">7.2882399559021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32567691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57241821289062</t>
+    <t xml:space="preserve">7.32567644119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57241773605347</t>
   </si>
   <si>
     <t xml:space="preserve">7.53668355941772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59794425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73577880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7255687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93997812271118</t>
+    <t xml:space="preserve">7.59794330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73577785491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72556781768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93997859954834</t>
   </si>
   <si>
     <t xml:space="preserve">7.67792177200317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79874086380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15608978271484</t>
+    <t xml:space="preserve">7.79874134063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15609073638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.35007953643799</t>
@@ -3944,19 +3944,19 @@
     <t xml:space="preserve">8.14758205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40283298492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35348415374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45898723602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60618019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43856811523438</t>
+    <t xml:space="preserve">8.40283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35348224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45898818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60618114471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43856716156006</t>
   </si>
   <si>
     <t xml:space="preserve">8.39091968536377</t>
@@ -3965,22 +3965,22 @@
     <t xml:space="preserve">8.56363964080811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55513095855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42325210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19012355804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19352722167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41474437713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38241195678711</t>
+    <t xml:space="preserve">8.55513191223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42325115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19012451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19352626800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41474342346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38241100311279</t>
   </si>
   <si>
     <t xml:space="preserve">8.27520656585693</t>
@@ -3992,22 +3992,22 @@
     <t xml:space="preserve">9.03585147857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27833938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23154449462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92524337768555</t>
+    <t xml:space="preserve">9.27834033966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23154354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92524433135986</t>
   </si>
   <si>
     <t xml:space="preserve">8.83165264129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73380565643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71253395080566</t>
+    <t xml:space="preserve">8.73380661010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71253490447998</t>
   </si>
   <si>
     <t xml:space="preserve">8.52960586547852</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">8.28881931304932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07611083984375</t>
+    <t xml:space="preserve">8.07611274719238</t>
   </si>
   <si>
     <t xml:space="preserve">8.2693452835083</t>
@@ -4025,49 +4025,49 @@
     <t xml:space="preserve">8.21586132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31247711181641</t>
+    <t xml:space="preserve">8.31247806549072</t>
   </si>
   <si>
     <t xml:space="preserve">8.20895957946777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62753486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69654607772827</t>
+    <t xml:space="preserve">7.62753343582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69654560089111</t>
   </si>
   <si>
     <t xml:space="preserve">7.47225761413574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78108596801758</t>
+    <t xml:space="preserve">7.78108692169189</t>
   </si>
   <si>
     <t xml:space="preserve">7.70689725875854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72932624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01745128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91910982131958</t>
+    <t xml:space="preserve">7.72932767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319639205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0174503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91911029815674</t>
   </si>
   <si>
     <t xml:space="preserve">7.76038217544556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69309520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62408399581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87942790985107</t>
+    <t xml:space="preserve">7.69309616088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62408447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87942695617676</t>
   </si>
   <si>
     <t xml:space="preserve">7.63616132736206</t>
@@ -4076,31 +4076,31 @@
     <t xml:space="preserve">7.85527372360229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78798580169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61373233795166</t>
+    <t xml:space="preserve">7.78798627853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61373281478882</t>
   </si>
   <si>
     <t xml:space="preserve">7.86390066146851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86217451095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96051692962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02435302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01054954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94498777389526</t>
+    <t xml:space="preserve">7.86217594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87597703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96051549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02435207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0105504989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94498920440674</t>
   </si>
   <si>
     <t xml:space="preserve">8.25899314880371</t>
@@ -4112,19 +4112,19 @@
     <t xml:space="preserve">8.43669891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4384241104126</t>
+    <t xml:space="preserve">8.43842506408691</t>
   </si>
   <si>
     <t xml:space="preserve">8.45222663879395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40909385681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58162212371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65667343139648</t>
+    <t xml:space="preserve">8.40909290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58162307739258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65667247772217</t>
   </si>
   <si>
     <t xml:space="preserve">8.6782398223877</t>
@@ -4136,10 +4136,10 @@
     <t xml:space="preserve">9.06211853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2519006729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28640556335449</t>
+    <t xml:space="preserve">9.25190162658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28640747070312</t>
   </si>
   <si>
     <t xml:space="preserve">8.93703460693359</t>
@@ -4148,76 +4148,76 @@
     <t xml:space="preserve">8.49708461761475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8895902633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55382633209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37698554992676</t>
+    <t xml:space="preserve">8.88958835601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5538272857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37698459625244</t>
   </si>
   <si>
     <t xml:space="preserve">9.8385009765625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78242874145508</t>
+    <t xml:space="preserve">9.78243064880371</t>
   </si>
   <si>
     <t xml:space="preserve">9.65734577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85144233703613</t>
+    <t xml:space="preserve">9.85144138336182</t>
   </si>
   <si>
     <t xml:space="preserve">9.86006832122803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77380180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87732219696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97652435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0800437927246</t>
+    <t xml:space="preserve">9.7738037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8773193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97652530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0800447463989</t>
   </si>
   <si>
     <t xml:space="preserve">9.92476654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99808979034424</t>
+    <t xml:space="preserve">9.99809169769287</t>
   </si>
   <si>
     <t xml:space="preserve">10.2266931533813</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93770694732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75223731994629</t>
+    <t xml:space="preserve">9.93770599365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75223827362061</t>
   </si>
   <si>
     <t xml:space="preserve">9.44599628448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52363395690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42443084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60989952087402</t>
+    <t xml:space="preserve">9.5236349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42443180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32091236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60990047454834</t>
   </si>
   <si>
     <t xml:space="preserve">9.95495891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86869335174561</t>
+    <t xml:space="preserve">9.86869430541992</t>
   </si>
   <si>
     <t xml:space="preserve">10.3560914993286</t>
@@ -4229,115 +4229,115 @@
     <t xml:space="preserve">9.96358680725098</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2618713378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6241836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9815111160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1540403366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1497278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8736791610718</t>
+    <t xml:space="preserve">11.2618722915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6241846084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9815101623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1540412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1497268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8736782073975</t>
   </si>
   <si>
     <t xml:space="preserve">10.5113677978516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7356557846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.908185005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5724248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6371221542358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606161117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9951219558716</t>
+    <t xml:space="preserve">10.7356567382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9081859588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5724258422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6371231079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9606151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9951210021973</t>
   </si>
   <si>
     <t xml:space="preserve">12.2927350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0123739242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6845684051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8829765319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8657255172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9821815490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9735565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0727596282959</t>
+    <t xml:space="preserve">12.0123748779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6845674514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8829774856567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8657236099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9821825027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9735555648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0727605819702</t>
   </si>
   <si>
     <t xml:space="preserve">11.9390497207642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9908084869385</t>
+    <t xml:space="preserve">11.9908094406128</t>
   </si>
   <si>
     <t xml:space="preserve">12.5299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4135065078735</t>
+    <t xml:space="preserve">12.4135074615479</t>
   </si>
   <si>
     <t xml:space="preserve">12.8146371841431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9224681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9914808273315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9612865447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.931095123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5817232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7233877182007</t>
+    <t xml:space="preserve">12.9224691390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9914798736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9612874984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9310941696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5817213058472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.723388671875</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374588012695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0813875198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7758188247681</t>
+    <t xml:space="preserve">12.0813865661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7758178710938</t>
   </si>
   <si>
     <t xml:space="preserve">12.2841091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8448295593262</t>
+    <t xml:space="preserve">12.8448314666748</t>
   </si>
   <si>
     <t xml:space="preserve">12.6981801986694</t>
@@ -4346,10 +4346,10 @@
     <t xml:space="preserve">12.6377935409546</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5385904312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0598211288452</t>
+    <t xml:space="preserve">12.5385894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0598192214966</t>
   </si>
   <si>
     <t xml:space="preserve">12.1805906295776</t>
@@ -4358,16 +4358,16 @@
     <t xml:space="preserve">12.5989751815796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2668561935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7283725738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2718420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4486837387085</t>
+    <t xml:space="preserve">12.2668571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7283735275269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2718410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4486846923828</t>
   </si>
   <si>
     <t xml:space="preserve">13.3667325973511</t>
@@ -4379,64 +4379,64 @@
     <t xml:space="preserve">13.1942024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4885787963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3040437698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5456953048706</t>
+    <t xml:space="preserve">13.488579750061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3040447235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5456962585449</t>
   </si>
   <si>
     <t xml:space="preserve">13.9147653579712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0861177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2530765533447</t>
+    <t xml:space="preserve">14.0861186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.253077507019</t>
   </si>
   <si>
     <t xml:space="preserve">13.7302312850952</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8356781005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.86643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8224964141846</t>
+    <t xml:space="preserve">13.8356790542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8664350509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8224973678589</t>
   </si>
   <si>
     <t xml:space="preserve">13.963095664978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0641489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0246076583862</t>
+    <t xml:space="preserve">14.0641498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0246067047119</t>
   </si>
   <si>
     <t xml:space="preserve">13.4094924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.005274772644</t>
+    <t xml:space="preserve">13.0052738189697</t>
   </si>
   <si>
     <t xml:space="preserve">12.803165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6933221817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3154678344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5641498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3927955627441</t>
+    <t xml:space="preserve">12.6933240890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3154668807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5641489028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3927965164185</t>
   </si>
   <si>
     <t xml:space="preserve">11.6080865859985</t>
@@ -4448,13 +4448,13 @@
     <t xml:space="preserve">11.0720586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7381391525269</t>
+    <t xml:space="preserve">10.7381401062012</t>
   </si>
   <si>
     <t xml:space="preserve">10.9402475357056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9578227996826</t>
+    <t xml:space="preserve">10.9578237533569</t>
   </si>
   <si>
     <t xml:space="preserve">11.2302303314209</t>
@@ -4463,22 +4463,22 @@
     <t xml:space="preserve">11.063271522522</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7820739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.579966545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9666090011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0615129470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75834846496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7469263076782</t>
+    <t xml:space="preserve">10.7820749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5799655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.966609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0615119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75834941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7469253540039</t>
   </si>
   <si>
     <t xml:space="preserve">11.1423568725586</t>
@@ -4487,7 +4487,7 @@
     <t xml:space="preserve">11.2082624435425</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1115999221802</t>
+    <t xml:space="preserve">11.1116018295288</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841842651367</t>
@@ -4499,70 +4499,70 @@
     <t xml:space="preserve">10.7117757797241</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1467514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1819009780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.067663192749</t>
+    <t xml:space="preserve">11.1467504501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1818990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0676651000977</t>
   </si>
   <si>
     <t xml:space="preserve">10.8523750305176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9753971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0940275192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4411268234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5861177444458</t>
+    <t xml:space="preserve">10.975396156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0940256118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4411277770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5861186981201</t>
   </si>
   <si>
     <t xml:space="preserve">11.9551858901978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6344470977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6608104705811</t>
+    <t xml:space="preserve">11.6344480514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6608114242554</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0896329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3005285263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4147644042969</t>
+    <t xml:space="preserve">11.0896339416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3005275726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4147634506226</t>
   </si>
   <si>
     <t xml:space="preserve">11.2917423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5685434341431</t>
+    <t xml:space="preserve">11.5685424804688</t>
   </si>
   <si>
     <t xml:space="preserve">11.542181968689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3224973678589</t>
+    <t xml:space="preserve">11.3224964141846</t>
   </si>
   <si>
     <t xml:space="preserve">11.6827783584595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2829551696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2803182601929</t>
+    <t xml:space="preserve">11.2829532623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2803192138672</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704759597778</t>
@@ -4571,70 +4571,70 @@
     <t xml:space="preserve">12.3945541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.218807220459</t>
+    <t xml:space="preserve">12.2188053131104</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913906097412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0826025009155</t>
+    <t xml:space="preserve">12.0826034545898</t>
   </si>
   <si>
     <t xml:space="preserve">12.0298795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4384918212891</t>
+    <t xml:space="preserve">12.4384899139404</t>
   </si>
   <si>
     <t xml:space="preserve">12.5527257919312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1221466064453</t>
+    <t xml:space="preserve">12.1221475601196</t>
   </si>
   <si>
     <t xml:space="preserve">11.7398958206177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7442903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3286485671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5790872573853</t>
+    <t xml:space="preserve">11.7442893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.328649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5790882110596</t>
   </si>
   <si>
     <t xml:space="preserve">12.5219697952271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5175752639771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2407760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9288244247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9024620056152</t>
+    <t xml:space="preserve">12.5175762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2407751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9288234710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9024610519409</t>
   </si>
   <si>
     <t xml:space="preserve">11.7882280349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1265392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9622163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1994733810425</t>
+    <t xml:space="preserve">12.126540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.962215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1994743347168</t>
   </si>
   <si>
     <t xml:space="preserve">11.537787437439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8761005401611</t>
+    <t xml:space="preserve">11.8761014938354</t>
   </si>
   <si>
     <t xml:space="preserve">11.6564168930054</t>
@@ -4643,28 +4643,28 @@
     <t xml:space="preserve">12.4604587554932</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7504415512085</t>
+    <t xml:space="preserve">12.7504405975342</t>
   </si>
   <si>
     <t xml:space="preserve">13.0140619277954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1854152679443</t>
+    <t xml:space="preserve">13.18541431427</t>
   </si>
   <si>
     <t xml:space="preserve">12.7328662872314</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1353273391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2451686859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8163471221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615119934082</t>
+    <t xml:space="preserve">12.135326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2451696395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8163452148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615139007568</t>
   </si>
   <si>
     <t xml:space="preserve">12.9217939376831</t>
@@ -4673,22 +4673,22 @@
     <t xml:space="preserve">13.2117767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1590518951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3216190338135</t>
+    <t xml:space="preserve">13.1590538024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3216180801392</t>
   </si>
   <si>
     <t xml:space="preserve">13.2205638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5193347930908</t>
+    <t xml:space="preserve">13.5193338394165</t>
   </si>
   <si>
     <t xml:space="preserve">13.8927974700928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4534301757812</t>
+    <t xml:space="preserve">13.4534292221069</t>
   </si>
   <si>
     <t xml:space="preserve">13.8005294799805</t>
@@ -4697,16 +4697,16 @@
     <t xml:space="preserve">14.1564178466797</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9982433319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1959590911865</t>
+    <t xml:space="preserve">13.9982452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1959609985352</t>
   </si>
   <si>
     <t xml:space="preserve">14.6265392303467</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7539577484131</t>
+    <t xml:space="preserve">14.7539587020874</t>
   </si>
   <si>
     <t xml:space="preserve">14.4551877975464</t>
@@ -4724,13 +4724,13 @@
     <t xml:space="preserve">13.9938507080078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6572961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7275943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3101959228516</t>
+    <t xml:space="preserve">14.6572952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.727593421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3101949691772</t>
   </si>
   <si>
     <t xml:space="preserve">14.4244327545166</t>
@@ -4745,10 +4745,10 @@
     <t xml:space="preserve">14.3578367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4466285705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5265436172485</t>
+    <t xml:space="preserve">14.4466304779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5265426635742</t>
   </si>
   <si>
     <t xml:space="preserve">14.1314144134521</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">14.5443000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8417587280273</t>
+    <t xml:space="preserve">14.8417596817017</t>
   </si>
   <si>
     <t xml:space="preserve">14.4954662322998</t>
@@ -4769,73 +4769,73 @@
     <t xml:space="preserve">14.038182258606</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9138708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6119747161865</t>
+    <t xml:space="preserve">13.9138717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6119737625122</t>
   </si>
   <si>
     <t xml:space="preserve">13.7806816101074</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6608114242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5276203155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9893455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0159816741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7451639175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6474924087524</t>
+    <t xml:space="preserve">13.6608104705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5276212692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9893445968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0159826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7451629638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6474914550781</t>
   </si>
   <si>
     <t xml:space="preserve">13.949387550354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1402940750122</t>
+    <t xml:space="preserve">14.1402931213379</t>
   </si>
   <si>
     <t xml:space="preserve">14.4643888473511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.721887588501</t>
+    <t xml:space="preserve">14.7218885421753</t>
   </si>
   <si>
     <t xml:space="preserve">14.7796020507812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6686134338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7130079269409</t>
+    <t xml:space="preserve">14.6686124801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7130069732666</t>
   </si>
   <si>
     <t xml:space="preserve">14.4599475860596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9349908828735</t>
+    <t xml:space="preserve">14.9349899291992</t>
   </si>
   <si>
     <t xml:space="preserve">14.4199905395508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4033117294312</t>
+    <t xml:space="preserve">13.4033107757568</t>
   </si>
   <si>
     <t xml:space="preserve">13.7940006256104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0071029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0603790283203</t>
+    <t xml:space="preserve">14.0071039199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0603799819946</t>
   </si>
   <si>
     <t xml:space="preserve">14.0692586898804</t>
@@ -4847,13 +4847,13 @@
     <t xml:space="preserve">14.4421882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3445167541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2290859222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6597318649292</t>
+    <t xml:space="preserve">14.3445177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2290849685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6597309112549</t>
   </si>
   <si>
     <t xml:space="preserve">15.2679653167725</t>
@@ -4862,10 +4862,10 @@
     <t xml:space="preserve">14.5176639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6952486038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2424058914185</t>
+    <t xml:space="preserve">14.6952476501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2424049377441</t>
   </si>
   <si>
     <t xml:space="preserve">14.26904296875</t>
@@ -4877,13 +4877,13 @@
     <t xml:space="preserve">14.619776725769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3977928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4288702011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1180944442749</t>
+    <t xml:space="preserve">14.3977937698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4288692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1180934906006</t>
   </si>
   <si>
     <t xml:space="preserve">13.6297340393066</t>
@@ -4892,10 +4892,10 @@
     <t xml:space="preserve">13.5498189926147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4388284683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5409393310547</t>
+    <t xml:space="preserve">13.4388275146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.540940284729</t>
   </si>
   <si>
     <t xml:space="preserve">13.8872327804565</t>
@@ -4910,31 +4910,31 @@
     <t xml:space="preserve">14.3800344467163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4011535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6641721725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4377489089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9715852737427</t>
+    <t xml:space="preserve">15.4011526107788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6641712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4377498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.971586227417</t>
   </si>
   <si>
     <t xml:space="preserve">14.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9227504730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2646045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3267583847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3711547851562</t>
+    <t xml:space="preserve">13.9227514266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2646036148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3267574310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3711538314819</t>
   </si>
   <si>
     <t xml:space="preserve">14.4732666015625</t>
@@ -4943,28 +4943,28 @@
     <t xml:space="preserve">14.5487413406372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0026636123657</t>
+    <t xml:space="preserve">14.00266456604</t>
   </si>
   <si>
     <t xml:space="preserve">13.7140865325928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9105091094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0969743728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9249067306519</t>
+    <t xml:space="preserve">12.9105100631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0969753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9249057769775</t>
   </si>
   <si>
     <t xml:space="preserve">11.9559850692749</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7384414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7695178985596</t>
+    <t xml:space="preserve">11.7384405136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7695188522339</t>
   </si>
   <si>
     <t xml:space="preserve">12.1646480560303</t>
@@ -4976,7 +4976,7 @@
     <t xml:space="preserve">11.765079498291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3877077102661</t>
+    <t xml:space="preserve">11.3877086639404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942598342896</t>
@@ -4985,10 +4985,10 @@
     <t xml:space="preserve">11.8361139297485</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7739591598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6096906661987</t>
+    <t xml:space="preserve">11.7739582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.609691619873</t>
   </si>
   <si>
     <t xml:space="preserve">11.631890296936</t>
@@ -4997,10 +4997,10 @@
     <t xml:space="preserve">11.9826221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6851654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5386571884155</t>
+    <t xml:space="preserve">11.6851644515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5386581420898</t>
   </si>
   <si>
     <t xml:space="preserve">11.5075788497925</t>
@@ -5009,13 +5009,13 @@
     <t xml:space="preserve">11.8183555603027</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9737434387207</t>
+    <t xml:space="preserve">11.9737424850464</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337863922119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8405523300171</t>
+    <t xml:space="preserve">11.8405532836914</t>
   </si>
   <si>
     <t xml:space="preserve">11.7828388214111</t>
@@ -5024,25 +5024,25 @@
     <t xml:space="preserve">11.6540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6363296508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5874929428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5031385421753</t>
+    <t xml:space="preserve">11.6363286972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5874919891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5031394958496</t>
   </si>
   <si>
     <t xml:space="preserve">11.2678375244141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9659414291382</t>
+    <t xml:space="preserve">10.9659423828125</t>
   </si>
   <si>
     <t xml:space="preserve">10.8949069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7439594268799</t>
+    <t xml:space="preserve">10.7439603805542</t>
   </si>
   <si>
     <t xml:space="preserve">11.0280961990356</t>
@@ -5072,19 +5072,19 @@
     <t xml:space="preserve">10.9171056747437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9526224136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0713272094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2311191558838</t>
+    <t xml:space="preserve">10.9526233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.071325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2311182022095</t>
   </si>
   <si>
     <t xml:space="preserve">11.2585105895996</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8430500030518</t>
+    <t xml:space="preserve">10.8430509567261</t>
   </si>
   <si>
     <t xml:space="preserve">10.9389266967773</t>
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">11.1489400863647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8476152420044</t>
+    <t xml:space="preserve">10.8476161956787</t>
   </si>
   <si>
     <t xml:space="preserve">10.6558666229248</t>
@@ -5108,7 +5108,7 @@
     <t xml:space="preserve">11.3452548980713</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6054887771606</t>
+    <t xml:space="preserve">11.6054878234863</t>
   </si>
   <si>
     <t xml:space="preserve">11.6967992782593</t>
@@ -5120,16 +5120,16 @@
     <t xml:space="preserve">11.7104949951172</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6420116424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205074310303</t>
+    <t xml:space="preserve">11.6420125961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205083847046</t>
   </si>
   <si>
     <t xml:space="preserve">11.8063707351685</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8931140899658</t>
+    <t xml:space="preserve">11.8931131362915</t>
   </si>
   <si>
     <t xml:space="preserve">11.4274339675903</t>
@@ -5144,19 +5144,19 @@
     <t xml:space="preserve">11.6922340393066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.829197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8337631225586</t>
+    <t xml:space="preserve">11.8291969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8337640762329</t>
   </si>
   <si>
     <t xml:space="preserve">11.8657217025757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1853075027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5231523513794</t>
+    <t xml:space="preserve">12.1853065490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5231533050537</t>
   </si>
   <si>
     <t xml:space="preserve">12.5185871124268</t>
@@ -5168,13 +5168,13 @@
     <t xml:space="preserve">12.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305208206177</t>
+    <t xml:space="preserve">12.1305198669434</t>
   </si>
   <si>
     <t xml:space="preserve">12.4501056671143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4227113723755</t>
+    <t xml:space="preserve">12.4227123260498</t>
   </si>
   <si>
     <t xml:space="preserve">12.7696895599365</t>
@@ -5183,13 +5183,13 @@
     <t xml:space="preserve">13.0025300979614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0162258148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9568748474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9660062789917</t>
+    <t xml:space="preserve">13.016227722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9568758010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9660053253174</t>
   </si>
   <si>
     <t xml:space="preserve">13.1577568054199</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">13.1668882369995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184307098389</t>
+    <t xml:space="preserve">13.5184316635132</t>
   </si>
   <si>
     <t xml:space="preserve">13.5549554824829</t>
@@ -5207,19 +5207,19 @@
     <t xml:space="preserve">13.7330083847046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6553964614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6143064498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7010517120361</t>
+    <t xml:space="preserve">13.6553955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6143074035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7010507583618</t>
   </si>
   <si>
     <t xml:space="preserve">13.6964855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8151884078979</t>
+    <t xml:space="preserve">13.8151874542236</t>
   </si>
   <si>
     <t xml:space="preserve">13.7695331573486</t>
@@ -5231,13 +5231,13 @@
     <t xml:space="preserve">13.3632049560547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6599617004395</t>
+    <t xml:space="preserve">13.6599626541138</t>
   </si>
   <si>
     <t xml:space="preserve">13.5823488235474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6371355056763</t>
+    <t xml:space="preserve">13.6371335983276</t>
   </si>
   <si>
     <t xml:space="preserve">14.070855140686</t>
@@ -5246,7 +5246,7 @@
     <t xml:space="preserve">14.0845537185669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0434627532959</t>
+    <t xml:space="preserve">14.0434637069702</t>
   </si>
   <si>
     <t xml:space="preserve">14.0480289459229</t>
@@ -5255,7 +5255,7 @@
     <t xml:space="preserve">14.025200843811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9658489227295</t>
+    <t xml:space="preserve">13.9658498764038</t>
   </si>
   <si>
     <t xml:space="preserve">13.9475870132446</t>
@@ -5273,16 +5273,16 @@
     <t xml:space="preserve">13.6736583709717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8380146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9612846374512</t>
+    <t xml:space="preserve">13.8380155563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9612855911255</t>
   </si>
   <si>
     <t xml:space="preserve">13.9293260574341</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4773416519165</t>
+    <t xml:space="preserve">13.4773406982422</t>
   </si>
   <si>
     <t xml:space="preserve">13.6097402572632</t>
@@ -5297,10 +5297,10 @@
     <t xml:space="preserve">13.6645269393921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7375745773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.847146987915</t>
+    <t xml:space="preserve">13.7375755310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8471460342407</t>
   </si>
   <si>
     <t xml:space="preserve">13.7421407699585</t>
@@ -5312,10 +5312,10 @@
     <t xml:space="preserve">14.0891180038452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8425817489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7786645889282</t>
+    <t xml:space="preserve">13.8425807952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7786636352539</t>
   </si>
   <si>
     <t xml:space="preserve">13.3951625823975</t>
@@ -5342,7 +5342,7 @@
     <t xml:space="preserve">13.3084182739258</t>
   </si>
   <si>
-    <t xml:space="preserve">13.011661529541</t>
+    <t xml:space="preserve">13.0116605758667</t>
   </si>
   <si>
     <t xml:space="preserve">13.3586387634277</t>
@@ -5351,13 +5351,13 @@
     <t xml:space="preserve">13.8836708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0069398880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9567193984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0343332290649</t>
+    <t xml:space="preserve">14.0069389343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9567184448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0343322753906</t>
   </si>
   <si>
     <t xml:space="preserve">14.3950061798096</t>
@@ -5366,7 +5366,7 @@
     <t xml:space="preserve">14.2945652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4954471588135</t>
+    <t xml:space="preserve">14.4954481124878</t>
   </si>
   <si>
     <t xml:space="preserve">14.5045785903931</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">14.2671728134155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9338912963867</t>
+    <t xml:space="preserve">13.933892250061</t>
   </si>
   <si>
     <t xml:space="preserve">14.0571594238281</t>
@@ -5384,16 +5384,16 @@
     <t xml:space="preserve">14.0982484817505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7969264984131</t>
+    <t xml:space="preserve">13.7969255447388</t>
   </si>
   <si>
     <t xml:space="preserve">14.9383001327515</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8999500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2542314529419</t>
+    <t xml:space="preserve">14.8999509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2542304992676</t>
   </si>
   <si>
     <t xml:space="preserve">14.783073425293</t>
@@ -5405,22 +5405,22 @@
     <t xml:space="preserve">14.585844039917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6917629241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.906343460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7008943557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7191562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1302070617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3036956787109</t>
+    <t xml:space="preserve">14.6917638778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9063415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7008953094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7191572189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1302080154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3036966323853</t>
   </si>
   <si>
     <t xml:space="preserve">14.5487966537476</t>
@@ -6672,6 +6672,9 @@
   </si>
   <si>
     <t xml:space="preserve">14.7150001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6949996948242</t>
   </si>
 </sst>
 </file>
@@ -71854,7 +71857,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6494791667</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>2005076</v>
@@ -71875,6 +71878,32 @@
         <v>2180</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6510763889</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>2813818</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>15.6949996948242</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>15.3900003433228</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>15.3999996185303</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>15.6949996948242</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2220</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="2222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="2223">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87406921386719</t>
+    <t xml:space="preserve">7.87407159805298</t>
   </si>
   <si>
     <t xml:space="preserve">TEN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8886513710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69909000396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48036670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1960244178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11582708358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07937288284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12311840057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07208156585693</t>
+    <t xml:space="preserve">7.88865280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69909191131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48036527633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19602537155151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11582612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07937240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12311744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07208108901978</t>
   </si>
   <si>
     <t xml:space="preserve">6.62734222412109</t>
@@ -74,283 +74,283 @@
     <t xml:space="preserve">6.56901597976685</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77680397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39403676986694</t>
+    <t xml:space="preserve">6.7768030166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39403629302979</t>
   </si>
   <si>
     <t xml:space="preserve">6.63463354110718</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80596828460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78044986724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88981151580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91168355941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82783842086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49246215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5143346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03562641143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43413591384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29925584793091</t>
+    <t xml:space="preserve">6.80596733093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78044891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88981103897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91168403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82783794403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49246263504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51433563232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03562498092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43413543701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29925632476807</t>
   </si>
   <si>
     <t xml:space="preserve">6.80232095718384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9554295539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74034976959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1486349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0611457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148288726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11947298049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86064910888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54349946975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55443477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16686010360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32726097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50223731994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45120429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61159992218018</t>
+    <t xml:space="preserve">6.95542764663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7403507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14863395690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06114482879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148384094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11947202682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86064767837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55443334579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16686296463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32726001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50224018096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45120477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61160039901733</t>
   </si>
   <si>
     <t xml:space="preserve">7.91781425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00530624389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71367120742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85948896408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58972835540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82303285598755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73554420471191</t>
+    <t xml:space="preserve">8.00530433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71367073059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85948848724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58972883224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82303380966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73554277420044</t>
   </si>
   <si>
     <t xml:space="preserve">7.9615592956543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81574487686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7792911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95426845550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72096347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6699275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98343324661255</t>
+    <t xml:space="preserve">7.81574058532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77929210662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95426893234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72096157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66992712020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98343276977539</t>
   </si>
   <si>
     <t xml:space="preserve">7.83032464981079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53140163421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6407642364502</t>
+    <t xml:space="preserve">7.53140211105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66263628005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64076280593872</t>
   </si>
   <si>
     <t xml:space="preserve">8.07821178436279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11466789245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17299175262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4208812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41359043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45004558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69793033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8291654586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8656177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91665649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63960647583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80000305175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80729293823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58856868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47191715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01988506317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97614145278931</t>
+    <t xml:space="preserve">8.11466503143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17299365997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42088031768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4135913848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45004272460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69793128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82916450500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86561965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91665554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63960552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8000020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80729198455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58856964111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0198860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97614240646362</t>
   </si>
   <si>
     <t xml:space="preserve">8.39900875091553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24590015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21673965454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29693794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30422973632812</t>
+    <t xml:space="preserve">8.24590110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21673774719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29693698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30422592163086</t>
   </si>
   <si>
     <t xml:space="preserve">8.45733547210693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64689540863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67605876922607</t>
+    <t xml:space="preserve">8.64689445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67605972290039</t>
   </si>
   <si>
     <t xml:space="preserve">8.39171695709229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56669425964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62655258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73129653930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75374031066895</t>
+    <t xml:space="preserve">8.56669616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62655067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73129749298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75374126434326</t>
   </si>
   <si>
     <t xml:space="preserve">8.95575046539307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97819900512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98567962646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91085910797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80611419677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67892551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64899444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08294296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69645214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52437114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4944429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28495216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15776062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34480762481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17272567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40466213226318</t>
+    <t xml:space="preserve">8.97819709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98567771911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91086196899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80611610412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67892360687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64899635314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08294105529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53185081481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69645118713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52436923980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49444389343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28495121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15775966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34480857849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17272472381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40466117858887</t>
   </si>
   <si>
     <t xml:space="preserve">9.66652584075928</t>
@@ -359,40 +359,40 @@
     <t xml:space="preserve">9.4271068572998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8011999130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30739593505859</t>
+    <t xml:space="preserve">9.80119895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30739879608154</t>
   </si>
   <si>
     <t xml:space="preserve">9.04553413391113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14279651641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61415195465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73386383056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8685359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8311243057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59918975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32236289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39717960357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50940704345703</t>
+    <t xml:space="preserve">9.14279842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6141529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73386192321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86853694915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83112621307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59918880462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32236194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39717864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50940608978271</t>
   </si>
   <si>
     <t xml:space="preserve">9.65904331207275</t>
@@ -401,31 +401,31 @@
     <t xml:space="preserve">9.74882507324219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47947788238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59170627593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21761703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37473583221436</t>
+    <t xml:space="preserve">9.47947978973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59170722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21761417388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37473487854004</t>
   </si>
   <si>
     <t xml:space="preserve">9.18768882751465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06797695159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16524410247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09790515899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82855892181396</t>
+    <t xml:space="preserve">9.06797885894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16524314880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09790706634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8285608291626</t>
   </si>
   <si>
     <t xml:space="preserve">8.94826889038086</t>
@@ -434,49 +434,49 @@
     <t xml:space="preserve">8.70885181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57417964935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74625968933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00064182281494</t>
+    <t xml:space="preserve">8.57417869567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74625873565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00064277648926</t>
   </si>
   <si>
     <t xml:space="preserve">9.19517040252686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38969898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36725330352783</t>
+    <t xml:space="preserve">9.38969802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36725234985352</t>
   </si>
   <si>
     <t xml:space="preserve">9.48696041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70393466949463</t>
+    <t xml:space="preserve">9.70393562316895</t>
   </si>
   <si>
     <t xml:space="preserve">9.65156173706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62911605834961</t>
+    <t xml:space="preserve">9.62911796569824</t>
   </si>
   <si>
     <t xml:space="preserve">9.51688957214355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45703506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09042167663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22509670257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29991436004639</t>
+    <t xml:space="preserve">9.45703601837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09042358398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22509574890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29991626739502</t>
   </si>
   <si>
     <t xml:space="preserve">9.10538864135742</t>
@@ -485,49 +485,49 @@
     <t xml:space="preserve">8.85848617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66396141052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71633434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88093185424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76870536804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67144393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69388866424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9033784866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70136833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44698619842529</t>
+    <t xml:space="preserve">8.66396045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71633243560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88093280792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76870441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67144107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69388675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90337944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70136642456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44698810577393</t>
   </si>
   <si>
     <t xml:space="preserve">8.55921459197998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35977077484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50192451477051</t>
+    <t xml:space="preserve">9.35977172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50192642211914</t>
   </si>
   <si>
     <t xml:space="preserve">9.64408016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76379013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7413444519043</t>
+    <t xml:space="preserve">9.7637882232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74134349822998</t>
   </si>
   <si>
     <t xml:space="preserve">9.95083522796631</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">9.83860683441162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81616115570068</t>
+    <t xml:space="preserve">9.816162109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.9433536529541</t>
@@ -548,37 +548,37 @@
     <t xml:space="preserve">10.0406169891357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99572563171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0106916427612</t>
+    <t xml:space="preserve">9.99572467803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0106897354126</t>
   </si>
   <si>
     <t xml:space="preserve">9.96579837799072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.063063621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77127075195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89846134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86105346679688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29243564605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2800340652466</t>
+    <t xml:space="preserve">10.0630617141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77127170562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89846229553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86105442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29243469238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2800369262695</t>
   </si>
   <si>
     <t xml:space="preserve">10.6765727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.616717338562</t>
+    <t xml:space="preserve">10.6167192459106</t>
   </si>
   <si>
     <t xml:space="preserve">10.8112449645996</t>
@@ -587,31 +587,31 @@
     <t xml:space="preserve">10.9384355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9309549331665</t>
+    <t xml:space="preserve">10.9309539794922</t>
   </si>
   <si>
     <t xml:space="preserve">10.9159898757935</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7214641571045</t>
+    <t xml:space="preserve">10.7214651107788</t>
   </si>
   <si>
     <t xml:space="preserve">11.1216316223145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.804515838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0310258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0687780380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.834716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6761617660522</t>
+    <t xml:space="preserve">10.804518699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0310249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0687789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8347196578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6761636734009</t>
   </si>
   <si>
     <t xml:space="preserve">11.3783416748047</t>
@@ -623,175 +623,175 @@
     <t xml:space="preserve">11.7407579421997</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0352210998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1937770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0805215835571</t>
+    <t xml:space="preserve">12.0352191925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1937761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0805225372314</t>
   </si>
   <si>
     <t xml:space="preserve">12.2239780426025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.556191444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3749847412109</t>
+    <t xml:space="preserve">12.5561943054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3749856948853</t>
   </si>
   <si>
     <t xml:space="preserve">12.2919311523438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4202880859375</t>
+    <t xml:space="preserve">12.4202861785889</t>
   </si>
   <si>
     <t xml:space="preserve">12.3145818710327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3674354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5410928726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4504861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5939445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9790077209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0016613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8129024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0243139266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9488105773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8808555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8657579421997</t>
+    <t xml:space="preserve">12.3674335479736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5410957336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4504890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5939435958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280057907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9790115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0016622543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8129053115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0243110656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9488086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8808565139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8657569885254</t>
   </si>
   <si>
     <t xml:space="preserve">12.7751522064209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6769981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8204545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7600507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5335445404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.767599105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8582057952881</t>
+    <t xml:space="preserve">12.6769971847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8204536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7600517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5335416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7676010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8582067489624</t>
   </si>
   <si>
     <t xml:space="preserve">12.699649810791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6618967056274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9865617752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0092134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8506555557251</t>
+    <t xml:space="preserve">12.6618976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9865636825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0092124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8506546020508</t>
   </si>
   <si>
     <t xml:space="preserve">12.2164287567139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2088785171509</t>
+    <t xml:space="preserve">12.2088775634766</t>
   </si>
   <si>
     <t xml:space="preserve">12.1258239746094</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2843828201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1182727813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1484746932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8766632080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0729713439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560249328613</t>
+    <t xml:space="preserve">12.2843809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1182746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.148473739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8766622543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0729722976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560277938843</t>
   </si>
   <si>
     <t xml:space="preserve">12.2541799545288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.974817276001</t>
+    <t xml:space="preserve">11.9748191833496</t>
   </si>
   <si>
     <t xml:space="preserve">11.8540124893188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1862258911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2390785217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.786060333252</t>
+    <t xml:space="preserve">12.1862268447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2390775680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7860584259033</t>
   </si>
   <si>
     <t xml:space="preserve">11.7256565093994</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9068651199341</t>
+    <t xml:space="preserve">11.9068632125854</t>
   </si>
   <si>
     <t xml:space="preserve">11.6652555465698</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5142469406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5444498062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613952636719</t>
+    <t xml:space="preserve">11.5142507553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5444507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613962173462</t>
   </si>
   <si>
     <t xml:space="preserve">11.0989809036255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1140804290771</t>
+    <t xml:space="preserve">11.1140823364258</t>
   </si>
   <si>
     <t xml:space="preserve">11.1593828201294</t>
@@ -800,25 +800,25 @@
     <t xml:space="preserve">11.0763292312622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3330402374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4085426330566</t>
+    <t xml:space="preserve">11.3330421447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4085445404053</t>
   </si>
   <si>
     <t xml:space="preserve">11.4991464614868</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2952909469604</t>
+    <t xml:space="preserve">11.2952899932861</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442832946777</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1669321060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2424364089966</t>
+    <t xml:space="preserve">11.1669330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2424373626709</t>
   </si>
   <si>
     <t xml:space="preserve">10.9932765960693</t>
@@ -827,82 +827,82 @@
     <t xml:space="preserve">11.8389120101929</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7634077072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1333742141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0427694320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2013273239136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1786766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9370670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.385890007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4840469360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2801866531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3481416702271</t>
+    <t xml:space="preserve">11.7634086608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1333751678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0427713394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2013263702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1786756515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9370651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.385892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4840459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2801876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3481407165527</t>
   </si>
   <si>
     <t xml:space="preserve">11.3556909561157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3405895233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066976547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8724708557129</t>
+    <t xml:space="preserve">11.3405904769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066967010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8724689483643</t>
   </si>
   <si>
     <t xml:space="preserve">10.8573703765869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9026708602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7894163131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949541091919</t>
+    <t xml:space="preserve">10.9026718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7894144058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949531555176</t>
   </si>
   <si>
     <t xml:space="preserve">10.6535110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.645959854126</t>
+    <t xml:space="preserve">10.6459617614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.6610612869263</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8271684646606</t>
+    <t xml:space="preserve">10.827169418335</t>
   </si>
   <si>
     <t xml:space="preserve">10.8800210952759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7441158294678</t>
+    <t xml:space="preserve">10.7441129684448</t>
   </si>
   <si>
     <t xml:space="preserve">10.9781742095947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7139120101929</t>
+    <t xml:space="preserve">10.7139139175415</t>
   </si>
   <si>
     <t xml:space="preserve">10.8951206207275</t>
@@ -911,28 +911,28 @@
     <t xml:space="preserve">11.0183162689209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9721164703369</t>
+    <t xml:space="preserve">10.9721183776855</t>
   </si>
   <si>
     <t xml:space="preserve">11.0260162353516</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9259195327759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7642240524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6410284042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6025304794312</t>
+    <t xml:space="preserve">10.9259204864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7642250061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6410293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6025333404541</t>
   </si>
   <si>
     <t xml:space="preserve">10.3561401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4793357849121</t>
+    <t xml:space="preserve">10.4793348312378</t>
   </si>
   <si>
     <t xml:space="preserve">10.4408378601074</t>
@@ -941,73 +941,73 @@
     <t xml:space="preserve">10.4177379608154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2406425476074</t>
+    <t xml:space="preserve">10.2406435012817</t>
   </si>
   <si>
     <t xml:space="preserve">10.4023389816284</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7873258590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4947347640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5409326553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3176403045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3715410232544</t>
+    <t xml:space="preserve">10.7873268127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5409336090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3176393508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3715381622314</t>
   </si>
   <si>
     <t xml:space="preserve">10.2791433334351</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2868423461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3330392837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5101327896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8335218429565</t>
+    <t xml:space="preserve">10.2868413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3330421447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5101346969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8335227966309</t>
   </si>
   <si>
     <t xml:space="preserve">10.8566226959229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7103290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6179294586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3407382965088</t>
+    <t xml:space="preserve">10.7103252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6179313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3407411575317</t>
   </si>
   <si>
     <t xml:space="preserve">10.4716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7796239852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9105205535889</t>
+    <t xml:space="preserve">10.7796249389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9105195999146</t>
   </si>
   <si>
     <t xml:space="preserve">11.0106172561646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9413175582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7565250396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5255336761475</t>
+    <t xml:space="preserve">10.9413185119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7565279006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5255317687988</t>
   </si>
   <si>
     <t xml:space="preserve">10.6256294250488</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">9.99425220489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27047824859619</t>
+    <t xml:space="preserve">9.27047634124756</t>
   </si>
   <si>
     <t xml:space="preserve">9.34747505187988</t>
@@ -1034,34 +1034,34 @@
     <t xml:space="preserve">9.29357624053955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16268062591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22427940368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97789001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00868797302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96248912811279</t>
+    <t xml:space="preserve">9.16268157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22427845001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97788715362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00868701934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96248722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.92399024963379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87778949737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80079174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85469245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82389163970947</t>
+    <t xml:space="preserve">8.87779140472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80079555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85469150543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82389354705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.7853946685791</t>
@@ -1070,28 +1070,28 @@
     <t xml:space="preserve">8.72379684448242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63910007476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52360343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62370204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64680004119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60829925537109</t>
+    <t xml:space="preserve">8.63909912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52360248565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62370014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6467981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60830020904541</t>
   </si>
   <si>
     <t xml:space="preserve">8.74689483642578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0317850112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11648273468018</t>
+    <t xml:space="preserve">9.03178596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11648368835449</t>
   </si>
   <si>
     <t xml:space="preserve">9.13188171386719</t>
@@ -1100,76 +1100,76 @@
     <t xml:space="preserve">8.93168926239014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1549825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37827396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30127716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32437419891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33207416534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27817630767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26277923583984</t>
+    <t xml:space="preserve">9.15498352050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37827491760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3012752532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32437515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33207511901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27817535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26277732849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.24737739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23967742919922</t>
+    <t xml:space="preserve">9.23967933654785</t>
   </si>
   <si>
     <t xml:space="preserve">9.20117950439453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1087818145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87009239196777</t>
+    <t xml:space="preserve">9.10878086090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87009143829346</t>
   </si>
   <si>
     <t xml:space="preserve">8.84699153900146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95478916168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73919486999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63139820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65449810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79309368133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0009880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04718399047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.055850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1328468322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1020498275757</t>
+    <t xml:space="preserve">8.95478820800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73919582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63140106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65449905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70839595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79309463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00098514556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04718589782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0558490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1328458786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1020488739014</t>
   </si>
   <si>
     <t xml:space="preserve">10.0173530578613</t>
@@ -1178,178 +1178,178 @@
     <t xml:space="preserve">9.940354347229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82485771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70166301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45526885986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3089771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33977794647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4176082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72892951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6744499206543</t>
+    <t xml:space="preserve">9.82485866546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70166397094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45527076721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30897521972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33977699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41760540008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72893238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67445087432861</t>
   </si>
   <si>
     <t xml:space="preserve">9.44095706939697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43317127227783</t>
+    <t xml:space="preserve">9.43317317962646</t>
   </si>
   <si>
     <t xml:space="preserve">9.50322151184082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6978006362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91572761535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80676364898682</t>
+    <t xml:space="preserve">9.69779872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91572570800781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80676555633545</t>
   </si>
   <si>
     <t xml:space="preserve">9.64331722259521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76784610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86124610900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4371995925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1881370544434</t>
+    <t xml:space="preserve">9.76784706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86124515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.13365650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.437198638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1881380081177</t>
   </si>
   <si>
     <t xml:space="preserve">10.048041343689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95464515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0324745178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1570043563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.312668800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3905010223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3438005447388</t>
+    <t xml:space="preserve">9.95464324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0324754714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1570053100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3126678466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3905000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3437995910645</t>
   </si>
   <si>
     <t xml:space="preserve">10.242618560791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4294157028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5928611755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6862592697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6784772872925</t>
+    <t xml:space="preserve">10.4294147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6162099838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5928602218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6862573623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6784782409668</t>
   </si>
   <si>
     <t xml:space="preserve">10.9508867263794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0520658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1143321990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8886203765869</t>
+    <t xml:space="preserve">11.0520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.114330291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8886194229126</t>
   </si>
   <si>
     <t xml:space="preserve">10.8341388702393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9975852966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0831995010376</t>
+    <t xml:space="preserve">10.9975843429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0831985473633</t>
   </si>
   <si>
     <t xml:space="preserve">11.2933435440063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3011283874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.184380531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2544288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3166933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1610317230225</t>
+    <t xml:space="preserve">11.3011293411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1843795776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2544279098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3166942596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1610307693481</t>
   </si>
   <si>
     <t xml:space="preserve">10.9586687088013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9158620834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7018260955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5850791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3048839569092</t>
+    <t xml:space="preserve">10.9158611297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7018280029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5850782394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3048849105835</t>
   </si>
   <si>
     <t xml:space="preserve">10.4566564559937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0519313812256</t>
+    <t xml:space="preserve">10.0519323348999</t>
   </si>
   <si>
     <t xml:space="preserve">9.99355983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90016269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0636072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1180896759033</t>
+    <t xml:space="preserve">9.90016078948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.063606262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1180877685547</t>
   </si>
   <si>
     <t xml:space="preserve">10.262077331543</t>
@@ -1358,16 +1358,16 @@
     <t xml:space="preserve">10.5734043121338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6667995452881</t>
+    <t xml:space="preserve">10.6668004989624</t>
   </si>
   <si>
     <t xml:space="preserve">10.5461626052856</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8730554580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3478260040283</t>
+    <t xml:space="preserve">10.8730564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3478240966797</t>
   </si>
   <si>
     <t xml:space="preserve">11.2427539825439</t>
@@ -1382,13 +1382,13 @@
     <t xml:space="preserve">11.149356842041</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0209350585938</t>
+    <t xml:space="preserve">11.0209341049194</t>
   </si>
   <si>
     <t xml:space="preserve">11.3050193786621</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7175245285034</t>
+    <t xml:space="preserve">11.7175254821777</t>
   </si>
   <si>
     <t xml:space="preserve">11.5462951660156</t>
@@ -1397,22 +1397,22 @@
     <t xml:space="preserve">11.4645729064941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1999483108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026582717896</t>
+    <t xml:space="preserve">11.1999464035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026573181152</t>
   </si>
   <si>
     <t xml:space="preserve">11.277777671814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1376800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3595018386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7642250061035</t>
+    <t xml:space="preserve">11.1376819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3595027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7642240524292</t>
   </si>
   <si>
     <t xml:space="preserve">11.0442838668823</t>
@@ -1421,25 +1421,25 @@
     <t xml:space="preserve">10.596752166748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6239938735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7640905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6473445892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8574876785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8964033126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8263559341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3244771957397</t>
+    <t xml:space="preserve">10.6239948272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7640914916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6473436355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8574867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8964052200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8263530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3244762420654</t>
   </si>
   <si>
     <t xml:space="preserve">11.09876537323</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">11.6435871124268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6708269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5929946899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813207626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953577041626</t>
+    <t xml:space="preserve">11.6708278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5929956436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.58131980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.795355796814</t>
   </si>
   <si>
     <t xml:space="preserve">11.8654069900513</t>
@@ -1475,7 +1475,7 @@
     <t xml:space="preserve">12.0716600418091</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1611633300781</t>
+    <t xml:space="preserve">12.1611652374268</t>
   </si>
   <si>
     <t xml:space="preserve">11.8926467895508</t>
@@ -1484,52 +1484,52 @@
     <t xml:space="preserve">11.9393463134766</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8381652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183576583862</t>
+    <t xml:space="preserve">11.8381643295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183567047119</t>
   </si>
   <si>
     <t xml:space="preserve">12.5425395965576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5308637619019</t>
+    <t xml:space="preserve">12.5308656692505</t>
   </si>
   <si>
     <t xml:space="preserve">12.55810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8344058990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542125701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7604675292969</t>
+    <t xml:space="preserve">12.8344078063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542135238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7604684829712</t>
   </si>
   <si>
     <t xml:space="preserve">12.6631784439087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7059850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437215805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7020931243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355878829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3597688674927</t>
+    <t xml:space="preserve">12.7059860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437196731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.702094078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355897903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3597717285156</t>
   </si>
   <si>
     <t xml:space="preserve">13.3052854537964</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4556283950806</t>
+    <t xml:space="preserve">13.4556303024292</t>
   </si>
   <si>
     <t xml:space="preserve">13.4635419845581</t>
@@ -1538,25 +1538,25 @@
     <t xml:space="preserve">13.1549453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8661317825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5496187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4190587997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4863185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5535774230957</t>
+    <t xml:space="preserve">12.8661308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5496196746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4190616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4863166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5535764694214</t>
   </si>
   <si>
     <t xml:space="preserve">12.1460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2964115142822</t>
+    <t xml:space="preserve">12.2964105606079</t>
   </si>
   <si>
     <t xml:space="preserve">12.0392484664917</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">12.3478441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.312237739563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.395320892334</t>
+    <t xml:space="preserve">12.3122386932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953218460083</t>
   </si>
   <si>
     <t xml:space="preserve">12.4230155944824</t>
@@ -1580,55 +1580,55 @@
     <t xml:space="preserve">12.2726736068726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4784078598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9007730484009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205541610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.797908782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8374738693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4111490249634</t>
+    <t xml:space="preserve">12.4784049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9007749557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205570220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7979078292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8374729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4111471176147</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809928894043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9284696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5377521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4665365219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4348859786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3755407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5733585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6089658737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6050081253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6683120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.992733001709</t>
+    <t xml:space="preserve">11.9284687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5377511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4665374755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4348840713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3755397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5733575820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6089649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6050090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6683101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9927339553833</t>
   </si>
   <si>
     <t xml:space="preserve">13.0520811080933</t>
@@ -1640,58 +1640,58 @@
     <t xml:space="preserve">12.7355690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6010541915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5456628799438</t>
+    <t xml:space="preserve">12.601053237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5456638336182</t>
   </si>
   <si>
     <t xml:space="preserve">12.5575332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.454665184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4586238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2489356994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3201494216919</t>
+    <t xml:space="preserve">12.4546661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4586219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2489347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3201503753662</t>
   </si>
   <si>
     <t xml:space="preserve">12.3676271438599</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5961332321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.762303352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7702140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9759454727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9324235916138</t>
+    <t xml:space="preserve">11.5961351394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7623014450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7702150344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9759435653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9324264526367</t>
   </si>
   <si>
     <t xml:space="preserve">12.0273790359497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8216466903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5328302383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5170078277588</t>
+    <t xml:space="preserve">11.8216457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5328311920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418344497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5170068740845</t>
   </si>
   <si>
     <t xml:space="preserve">11.6159152984619</t>
@@ -1706,46 +1706,46 @@
     <t xml:space="preserve">12.086724281311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8889064788818</t>
+    <t xml:space="preserve">11.8889045715332</t>
   </si>
   <si>
     <t xml:space="preserve">11.8928632736206</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2281904220581</t>
+    <t xml:space="preserve">11.2281923294067</t>
   </si>
   <si>
     <t xml:space="preserve">11.4339218139648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4062280654907</t>
+    <t xml:space="preserve">11.4062271118164</t>
   </si>
   <si>
     <t xml:space="preserve">11.3310565948486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9947662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9037685394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7257308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228647232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6901245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9433326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9314622879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9354181289673</t>
+    <t xml:space="preserve">10.9947652816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9037675857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7257328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228666305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6901235580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9433336257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9314613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9354190826416</t>
   </si>
   <si>
     <t xml:space="preserve">10.9987201690674</t>
@@ -1754,40 +1754,40 @@
     <t xml:space="preserve">11.1451082229614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.153018951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0857629776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066347122192</t>
+    <t xml:space="preserve">11.1530199050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0857610702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066328048706</t>
   </si>
   <si>
     <t xml:space="preserve">11.1174125671387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7306499481201</t>
+    <t xml:space="preserve">11.7306489944458</t>
   </si>
   <si>
     <t xml:space="preserve">11.6396532058716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5842657089233</t>
+    <t xml:space="preserve">11.5842666625977</t>
   </si>
   <si>
     <t xml:space="preserve">11.4180974960327</t>
   </si>
   <si>
-    <t xml:space="preserve">11.72669506073</t>
+    <t xml:space="preserve">11.7266941070557</t>
   </si>
   <si>
     <t xml:space="preserve">11.7820835113525</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9482526779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6277837753296</t>
+    <t xml:space="preserve">11.9482507705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6277847290039</t>
   </si>
   <si>
     <t xml:space="preserve">11.5723962783813</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">11.1332378387451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1411504745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886281967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3112735748291</t>
+    <t xml:space="preserve">11.141152381897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.188627243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3112754821777</t>
   </si>
   <si>
     <t xml:space="preserve">11.2400598526001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.093674659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.081805229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8325538635254</t>
+    <t xml:space="preserve">11.0936756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0818061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8325519561768</t>
   </si>
   <si>
     <t xml:space="preserve">10.4052648544312</t>
@@ -1829,40 +1829,40 @@
     <t xml:space="preserve">10.2984437942505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2628355026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.171838760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2034893035889</t>
+    <t xml:space="preserve">10.2628364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1718397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2034921646118</t>
   </si>
   <si>
     <t xml:space="preserve">10.0927124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3933954238892</t>
+    <t xml:space="preserve">10.3933963775635</t>
   </si>
   <si>
     <t xml:space="preserve">10.5635204315186</t>
   </si>
   <si>
-    <t xml:space="preserve">10.62682056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6307792663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6189088821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5200004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.484393119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2430553436279</t>
+    <t xml:space="preserve">10.6268224716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6307783126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6189098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199995040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4843902587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.243052482605</t>
   </si>
   <si>
     <t xml:space="preserve">10.1599712371826</t>
@@ -1871,25 +1871,25 @@
     <t xml:space="preserve">9.85137271881104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75641822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8751106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78015804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68019676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40830230712891</t>
+    <t xml:space="preserve">9.75641918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87510871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7801570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68019771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40830421447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.58823299407959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45228672027588</t>
+    <t xml:space="preserve">9.45228576660156</t>
   </si>
   <si>
     <t xml:space="preserve">9.29634761810303</t>
@@ -1901,88 +1901,88 @@
     <t xml:space="preserve">9.38031482696533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71657657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66059684753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49666023254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78854656219482</t>
+    <t xml:space="preserve">8.71657466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66059589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49666213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78854846954346</t>
   </si>
   <si>
     <t xml:space="preserve">8.67259407043457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50865745544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22876834869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24875736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99685764312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10881519317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20077800750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18078517913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89130020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71216821670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71376800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3810977935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39389514923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34271574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54903507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61140918731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59861469268799</t>
+    <t xml:space="preserve">8.50865840911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22876644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24875926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99685955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10881328582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20077705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1807861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89129972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71217060089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71377038955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38110017776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39389562606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34271621704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54903364181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61141014099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59861612319946</t>
   </si>
   <si>
     <t xml:space="preserve">7.8849024772644</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01285171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05683612823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29674053192139</t>
+    <t xml:space="preserve">8.01285266876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05683326721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2967414855957</t>
   </si>
   <si>
     <t xml:space="preserve">8.31673145294189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24076175689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878890991211</t>
+    <t xml:space="preserve">8.24076080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16879177093506</t>
   </si>
   <si>
     <t xml:space="preserve">8.22476863861084</t>
@@ -1991,40 +1991,40 @@
     <t xml:space="preserve">8.52065277099609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45267772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32073211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39670181274414</t>
+    <t xml:space="preserve">8.45267963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3207311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39670085906982</t>
   </si>
   <si>
     <t xml:space="preserve">8.53264808654785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8245325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58862495422363</t>
+    <t xml:space="preserve">8.82453441619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58862686157227</t>
   </si>
   <si>
     <t xml:space="preserve">8.70058250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76855564117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75656032562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93249130249023</t>
+    <t xml:space="preserve">8.76855373382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75655937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93249034881592</t>
   </si>
   <si>
     <t xml:space="preserve">8.98846912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76455688476562</t>
+    <t xml:space="preserve">8.76455593109131</t>
   </si>
   <si>
     <t xml:space="preserve">8.56463432312012</t>
@@ -2033,13 +2033,13 @@
     <t xml:space="preserve">8.7445650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95248413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20838260650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22037696838379</t>
+    <t xml:space="preserve">8.95248317718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20838165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22037792205811</t>
   </si>
   <si>
     <t xml:space="preserve">9.43629360198975</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">9.55224704742432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59622859954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75616645812988</t>
+    <t xml:space="preserve">9.59622955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75616836547852</t>
   </si>
   <si>
     <t xml:space="preserve">9.63221645355225</t>
@@ -2063,70 +2063,70 @@
     <t xml:space="preserve">9.6162223815918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51626110076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51226329803467</t>
+    <t xml:space="preserve">9.51626300811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51226234436035</t>
   </si>
   <si>
     <t xml:space="preserve">9.3323335647583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39230918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3643217086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48427391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25236415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11242198944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42029762268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84413242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89611339569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84812927246094</t>
+    <t xml:space="preserve">9.39230823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36432075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48427295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25236511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1124210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42029857635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8441333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89611148834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84813117980957</t>
   </si>
   <si>
     <t xml:space="preserve">9.86812400817871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98407745361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0360555648804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3079490661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2039909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0680465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82813739776611</t>
+    <t xml:space="preserve">9.9840784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.036057472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3079509735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2039918899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0680437088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82813835144043</t>
   </si>
   <si>
     <t xml:space="preserve">10.0080680847168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.172004699707</t>
+    <t xml:space="preserve">10.2759618759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1720037460327</t>
   </si>
   <si>
     <t xml:space="preserve">10.1440162658691</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">9.95608806610107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3199462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0440540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93609714508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0040693283081</t>
+    <t xml:space="preserve">10.2559690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3199453353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0440549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93609619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0040702819824</t>
   </si>
   <si>
     <t xml:space="preserve">10.0560483932495</t>
@@ -2156,79 +2156,79 @@
     <t xml:space="preserve">10.3959150314331</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5278654098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4279012680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7917585372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5598516464233</t>
+    <t xml:space="preserve">10.5278644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4279022216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7917604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.559850692749</t>
   </si>
   <si>
     <t xml:space="preserve">10.3359394073486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92809963226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90011024475098</t>
+    <t xml:space="preserve">9.92809867858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">9.74017429351807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60422706604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44028949737549</t>
+    <t xml:space="preserve">9.60422611236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44029140472412</t>
   </si>
   <si>
     <t xml:space="preserve">9.60822582244873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41230297088623</t>
+    <t xml:space="preserve">9.41230201721191</t>
   </si>
   <si>
     <t xml:space="preserve">9.34033012390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54025363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61222267150879</t>
+    <t xml:space="preserve">9.29234790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54025173187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61222362518311</t>
   </si>
   <si>
     <t xml:space="preserve">9.96408557891846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0160646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0242443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1755695343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85655975341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43939590454102</t>
+    <t xml:space="preserve">10.0160655975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0242462158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1755704879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8565616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43939685821533</t>
   </si>
   <si>
     <t xml:space="preserve">9.32487869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16128349304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15310573577881</t>
+    <t xml:space="preserve">9.16128540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15310382843018</t>
   </si>
   <si>
     <t xml:space="preserve">9.0140495300293</t>
@@ -2237,109 +2237,109 @@
     <t xml:space="preserve">8.98542022705078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62960338592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8749942779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08766555786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78910636901855</t>
+    <t xml:space="preserve">8.62960243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87499523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08766746520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78910827636719</t>
   </si>
   <si>
     <t xml:space="preserve">8.79728698730469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78092575073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06312847137451</t>
+    <t xml:space="preserve">8.78092861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0631275177002</t>
   </si>
   <si>
     <t xml:space="preserve">9.19809341430664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94452381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83409690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87908458709717</t>
+    <t xml:space="preserve">8.9445219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83409404754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87908363342285</t>
   </si>
   <si>
     <t xml:space="preserve">9.05085849761963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29624938964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39440631866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25126266479492</t>
+    <t xml:space="preserve">9.29625034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39440536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25126075744629</t>
   </si>
   <si>
     <t xml:space="preserve">9.14901542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42303562164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3821382522583</t>
+    <t xml:space="preserve">9.42303657531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38213634490967</t>
   </si>
   <si>
     <t xml:space="preserve">9.41485595703125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65206718444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4271240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44757556915283</t>
+    <t xml:space="preserve">9.65206909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42712497711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44757461547852</t>
   </si>
   <si>
     <t xml:space="preserve">9.54573154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54164123535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75431537628174</t>
+    <t xml:space="preserve">9.5416431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75431632995605</t>
   </si>
   <si>
     <t xml:space="preserve">9.66024780273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8074836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98743438720703</t>
+    <t xml:space="preserve">9.80748271942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98743629455566</t>
   </si>
   <si>
     <t xml:space="preserve">9.94244575500488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83202075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82793426513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45166397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28806972503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12038612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24308204650879</t>
+    <t xml:space="preserve">9.83202266693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82793140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45166492462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2880687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12038516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24308109283447</t>
   </si>
   <si>
     <t xml:space="preserve">9.31260967254639</t>
@@ -2351,280 +2351,280 @@
     <t xml:space="preserve">9.5089225769043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26762104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93225288391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71548938751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56416416168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36376285552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29423522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44556045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00958061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14209365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71838188171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75764465332031</t>
+    <t xml:space="preserve">9.26762008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93225193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71549034118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56416511535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36376190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29423332214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44555950164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787399291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0095796585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14209270477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71838140487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75764513015747</t>
   </si>
   <si>
     <t xml:space="preserve">8.05211448669434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88851976394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98340702056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08810615539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96377420425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07011127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12409687042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21652603149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16335964202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10937118530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06520366668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86071062088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00467491149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21243858337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17153930664062</t>
+    <t xml:space="preserve">7.88852024078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98340559005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08810520172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96377372741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07011032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12409591674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21652698516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16335868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10937309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0652027130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86070871353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00467300415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21243667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17153739929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.41283988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5109977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43737888336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31468296051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3719425201416</t>
+    <t xml:space="preserve">8.51099681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43737983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31468391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37194156646729</t>
   </si>
   <si>
     <t xml:space="preserve">8.60506343841553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44146823883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31877613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22061824798584</t>
+    <t xml:space="preserve">8.4414701461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31877422332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22061634063721</t>
   </si>
   <si>
     <t xml:space="preserve">8.20016765594482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97195291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85743761062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85253047943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72983455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00794506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96213912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81326770782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4877142906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5629677772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54824447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63658571243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50898170471191</t>
+    <t xml:space="preserve">7.97195148468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85743618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85252809524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72983551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00794315338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96213817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81326723098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48771524429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56296873092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54824495315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63658475875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50898027420044</t>
   </si>
   <si>
     <t xml:space="preserve">7.54333639144897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61531829833984</t>
+    <t xml:space="preserve">7.615318775177</t>
   </si>
   <si>
     <t xml:space="preserve">7.88034152984619</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67257642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77400398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74292325973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64803791046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60713863372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66275978088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68239402770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70202350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61859083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69220685958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80999517440796</t>
+    <t xml:space="preserve">7.67257595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77400302886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74292039871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64803552627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60713720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66276216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68239164352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70202255249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61858940124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69220781326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80999565124512</t>
   </si>
   <si>
     <t xml:space="preserve">7.8852481842041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65785264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40591764450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03739166259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17644691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32286262512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18380737304688</t>
+    <t xml:space="preserve">7.65785312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40591716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03739070892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17644596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32286357879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18380832672119</t>
   </si>
   <si>
     <t xml:space="preserve">8.19607734680176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23697662353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10446453094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10282897949219</t>
+    <t xml:space="preserve">8.23697471618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10446643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10282802581787</t>
   </si>
   <si>
     <t xml:space="preserve">8.09955787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02993392944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95865249633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08961200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04153728485107</t>
+    <t xml:space="preserve">8.02993297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95865297317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0896110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04153823852539</t>
   </si>
   <si>
     <t xml:space="preserve">8.16918087005615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15094566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591812133789</t>
+    <t xml:space="preserve">8.15094661712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591907501221</t>
   </si>
   <si>
     <t xml:space="preserve">8.08629512786865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85587406158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80116891860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96694040298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03987979888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2122802734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24377822875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26864337921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2968225479126</t>
+    <t xml:space="preserve">8.00009632110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85587310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80116939544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96694183349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03987884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21228218078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24377632141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26864242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29682445526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.53304767608643</t>
@@ -2639,28 +2639,28 @@
     <t xml:space="preserve">8.40871906280518</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3921422958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3797082901001</t>
+    <t xml:space="preserve">8.39214134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37970924377441</t>
   </si>
   <si>
     <t xml:space="preserve">8.42944049835205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49574756622314</t>
+    <t xml:space="preserve">8.49574947357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.36313247680664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32997989654541</t>
+    <t xml:space="preserve">8.32997798919678</t>
   </si>
   <si>
     <t xml:space="preserve">8.37141990661621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48331737518311</t>
+    <t xml:space="preserve">8.48331546783447</t>
   </si>
   <si>
     <t xml:space="preserve">8.71125221252441</t>
@@ -2669,13 +2669,13 @@
     <t xml:space="preserve">8.69881820678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68224143981934</t>
+    <t xml:space="preserve">8.68224048614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.60764503479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60350036621094</t>
+    <t xml:space="preserve">8.60349941253662</t>
   </si>
   <si>
     <t xml:space="preserve">8.45016098022461</t>
@@ -2687,169 +2687,169 @@
     <t xml:space="preserve">8.45430660247803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52890300750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50403785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47088432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41700839996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37556457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05811309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18741703033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28687858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88073968887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73154592514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64202976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282735824585</t>
+    <t xml:space="preserve">8.52890205383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50403594970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47088241577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41700744628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37556552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05811500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18741512298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28687763214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88074016571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73154640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64203023910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282688140869</t>
   </si>
   <si>
     <t xml:space="preserve">7.90891981124878</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93212842941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78790998458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83598136901855</t>
+    <t xml:space="preserve">7.93212795257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78790807723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83598184585571</t>
   </si>
   <si>
     <t xml:space="preserve">7.90063190460205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00672626495361</t>
+    <t xml:space="preserve">8.0067253112793</t>
   </si>
   <si>
     <t xml:space="preserve">7.98185968399048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80448627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84095478057861</t>
+    <t xml:space="preserve">7.80448484420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84095525741577</t>
   </si>
   <si>
     <t xml:space="preserve">8.13105392456055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76967239379883</t>
+    <t xml:space="preserve">7.76967430114746</t>
   </si>
   <si>
     <t xml:space="preserve">7.37679624557495</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27733325958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29391050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97563219070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77007532119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71868705749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75018310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57612371444702</t>
+    <t xml:space="preserve">7.27733421325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29391145706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97563123703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77007579803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71868658065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75018358230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57612419128418</t>
   </si>
   <si>
     <t xml:space="preserve">6.45511150360107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08378553390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7824854850769</t>
+    <t xml:space="preserve">6.08378505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78248500823975</t>
   </si>
   <si>
     <t xml:space="preserve">4.65815687179565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56201028823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8790340423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97766780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71989417076111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85085368156433</t>
+    <t xml:space="preserve">4.56200981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87903428077698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97766828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71989464759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85085344314575</t>
   </si>
   <si>
     <t xml:space="preserve">3.9453432559967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15918779373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32661581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26362276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43436717987061</t>
+    <t xml:space="preserve">4.15918731689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32661485671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26362323760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43436670303345</t>
   </si>
   <si>
     <t xml:space="preserve">4.46088981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70788908004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61505651473999</t>
+    <t xml:space="preserve">4.70788812637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61505699157715</t>
   </si>
   <si>
     <t xml:space="preserve">4.59019088745117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62500333786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54543399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75430345535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78745937347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90681314468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13226127624512</t>
+    <t xml:space="preserve">4.62500286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54543304443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75430393218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78745794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.906813621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13226079940796</t>
   </si>
   <si>
     <t xml:space="preserve">5.01456451416016</t>
@@ -2858,34 +2858,34 @@
     <t xml:space="preserve">4.97809457778931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91178560256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6913104057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77751159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80735111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7791690826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54045963287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68136405944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86702919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90515518188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686679840088</t>
+    <t xml:space="preserve">4.91178607940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69131135940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77751207351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80735158920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77916860580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54045915603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68136548995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86702823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90515565872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686632156372</t>
   </si>
   <si>
     <t xml:space="preserve">4.99135541915894</t>
@@ -2894,97 +2894,97 @@
     <t xml:space="preserve">5.2831130027771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29968929290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00627613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24664306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04440307617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12065696716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16375780105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07092571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98141002655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76424980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79408836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15878438949585</t>
+    <t xml:space="preserve">5.29969024658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00627517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24664354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04440259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12065744400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16375732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07092618942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98141050338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7642502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79408931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15878486633301</t>
   </si>
   <si>
     <t xml:space="preserve">4.69959926605225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85045051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.611741065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59847927093506</t>
+    <t xml:space="preserve">4.85045146942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61174154281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5984787940979</t>
   </si>
   <si>
     <t xml:space="preserve">4.64157962799072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71451950073242</t>
+    <t xml:space="preserve">4.71451902389526</t>
   </si>
   <si>
     <t xml:space="preserve">4.72114992141724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83718872070312</t>
+    <t xml:space="preserve">4.83718919754028</t>
   </si>
   <si>
     <t xml:space="preserve">4.63494920730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8438196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04606008529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2980318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3527364730835</t>
+    <t xml:space="preserve">4.84382009506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04605913162231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29803228378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35273694992065</t>
   </si>
   <si>
     <t xml:space="preserve">5.63288879394531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71577453613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53508329391479</t>
+    <t xml:space="preserve">5.71577405929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61465406417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53508424758911</t>
   </si>
   <si>
     <t xml:space="preserve">5.18365001678467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18862342834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1819920539856</t>
+    <t xml:space="preserve">5.18862390518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18199253082275</t>
   </si>
   <si>
     <t xml:space="preserve">5.1306037902832</t>
@@ -2996,16 +2996,16 @@
     <t xml:space="preserve">5.04108762741089</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14220666885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8239278793335</t>
+    <t xml:space="preserve">5.14220809936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82392835617065</t>
   </si>
   <si>
     <t xml:space="preserve">4.88692092895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7609338760376</t>
+    <t xml:space="preserve">4.76093482971191</t>
   </si>
   <si>
     <t xml:space="preserve">4.81398153305054</t>
@@ -3017,37 +3017,37 @@
     <t xml:space="preserve">4.85210943222046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76259231567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93002080917358</t>
+    <t xml:space="preserve">4.76259183883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93002033233643</t>
   </si>
   <si>
     <t xml:space="preserve">4.84547805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76756620407104</t>
+    <t xml:space="preserve">4.76756525039673</t>
   </si>
   <si>
     <t xml:space="preserve">4.5968222618103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62168741226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67804956436157</t>
+    <t xml:space="preserve">4.62168788909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67804908752441</t>
   </si>
   <si>
     <t xml:space="preserve">4.75761890411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76590824127197</t>
+    <t xml:space="preserve">4.76590776443481</t>
   </si>
   <si>
     <t xml:space="preserve">4.89355134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78414344787598</t>
+    <t xml:space="preserve">4.78414249420166</t>
   </si>
   <si>
     <t xml:space="preserve">4.70291471481323</t>
@@ -3056,85 +3056,85 @@
     <t xml:space="preserve">4.66810321807861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58024406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49072885513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27191114425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19234085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08790636062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28185749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29346132278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48575592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21389198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29014539718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43602514266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41447496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32164287567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27688360214233</t>
+    <t xml:space="preserve">4.58024454116821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4907283782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27191162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19234180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08790588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28185701370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29346084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21389102935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29014587402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4360237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41447305679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32164335250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27688455581665</t>
   </si>
   <si>
     <t xml:space="preserve">4.23875713348389</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19731426239014</t>
+    <t xml:space="preserve">4.19731473922729</t>
   </si>
   <si>
     <t xml:space="preserve">4.10448312759399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08624887466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22383832931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17576551437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13349342346191</t>
+    <t xml:space="preserve">4.08624792098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22383880615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17576503753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13349294662476</t>
   </si>
   <si>
     <t xml:space="preserve">4.05806684494019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08293294906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07795906066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00004720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96192049980164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98927235603333</t>
+    <t xml:space="preserve">4.08293342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0779595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00004816055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96192026138306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98927211761475</t>
   </si>
   <si>
     <t xml:space="preserve">4.00087642669678</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">3.97601008415222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8392493724823</t>
+    <t xml:space="preserve">3.83924913406372</t>
   </si>
   <si>
     <t xml:space="preserve">3.84422302246094</t>
@@ -3152,16 +3152,16 @@
     <t xml:space="preserve">3.82598853111267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7795717716217</t>
+    <t xml:space="preserve">3.77957201004028</t>
   </si>
   <si>
     <t xml:space="preserve">3.74724674224854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80112218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95943331718445</t>
+    <t xml:space="preserve">3.80112171173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95943355560303</t>
   </si>
   <si>
     <t xml:space="preserve">3.96274900436401</t>
@@ -3176,31 +3176,31 @@
     <t xml:space="preserve">3.56075477600098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53091669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45880627632141</t>
+    <t xml:space="preserve">3.53091621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45880603790283</t>
   </si>
   <si>
     <t xml:space="preserve">3.39747047424316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53754711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399406433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53174543380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44140005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52096962928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5557816028595</t>
+    <t xml:space="preserve">3.53754734992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399382591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53174495697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44139981269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5209698677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55578207969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.65358638763428</t>
@@ -3209,16 +3209,16 @@
     <t xml:space="preserve">3.58064746856689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69005608558655</t>
+    <t xml:space="preserve">3.69005632400513</t>
   </si>
   <si>
     <t xml:space="preserve">3.66436147689819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6030261516571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51350975036621</t>
+    <t xml:space="preserve">3.60302639007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51351022720337</t>
   </si>
   <si>
     <t xml:space="preserve">3.60717058181763</t>
@@ -3230,10 +3230,10 @@
     <t xml:space="preserve">3.5508086681366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62623357772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71077823638916</t>
+    <t xml:space="preserve">3.62623405456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71077752113342</t>
   </si>
   <si>
     <t xml:space="preserve">3.61877465248108</t>
@@ -3242,115 +3242,115 @@
     <t xml:space="preserve">3.63783812522888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67099237442017</t>
+    <t xml:space="preserve">3.67099213600159</t>
   </si>
   <si>
     <t xml:space="preserve">3.57401609420776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47455382347107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37011861801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1728515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37509155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55163741111755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63535237312317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19399881362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17244911193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57029867172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63660717010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64655351638794</t>
+    <t xml:space="preserve">3.47455358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3701183795929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17285132408142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37509179115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55163788795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63535189628601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19399833679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17244863510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57029819488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63660764694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64655256271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.67639207839966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74601554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11402654647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21183109283447</t>
+    <t xml:space="preserve">4.74601602554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11402702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21183204650879</t>
   </si>
   <si>
     <t xml:space="preserve">5.27316617965698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19359636306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18033409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39324760437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73357391357422</t>
+    <t xml:space="preserve">5.19359588623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18033456802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39324808120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73357486724854</t>
   </si>
   <si>
     <t xml:space="preserve">5.67825078964233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60113143920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61957311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43683624267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52066040039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54748487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58101463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80901575088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70339822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71178102493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71513271331787</t>
+    <t xml:space="preserve">5.6011323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61957406997681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43683671951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52066087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5474853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58101367950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80901622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70339775085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71178007125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71513319015503</t>
   </si>
   <si>
     <t xml:space="preserve">5.8023099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70004463195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62627983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69501495361328</t>
+    <t xml:space="preserve">5.70004510879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62627935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69501543045044</t>
   </si>
   <si>
     <t xml:space="preserve">5.66651582717896</t>
@@ -3365,13 +3365,13 @@
     <t xml:space="preserve">5.49048471450806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47539520263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62795639038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58772039413452</t>
+    <t xml:space="preserve">5.47539567947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6279559135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58771991729736</t>
   </si>
   <si>
     <t xml:space="preserve">5.51227807998657</t>
@@ -3383,19 +3383,19 @@
     <t xml:space="preserve">5.47874879837036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67489719390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9783411026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96995830535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93642950057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82913446426392</t>
+    <t xml:space="preserve">5.67489814758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97834062576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96995878219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93642854690552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82913398742676</t>
   </si>
   <si>
     <t xml:space="preserve">5.99678230285645</t>
@@ -3410,13 +3410,13 @@
     <t xml:space="preserve">5.65813302993774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64304447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46198415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27254104614258</t>
+    <t xml:space="preserve">5.64304399490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4619836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27254152297974</t>
   </si>
   <si>
     <t xml:space="preserve">5.17865800857544</t>
@@ -3425,43 +3425,43 @@
     <t xml:space="preserve">5.24739503860474</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33792448043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50054264068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38989496231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38151216506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60448551177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69333934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80733966827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92972373962402</t>
+    <t xml:space="preserve">5.33792352676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50054311752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38989543914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38151359558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60448503494263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69333839416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80734014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92972326278687</t>
   </si>
   <si>
     <t xml:space="preserve">5.82410478591919</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89451694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90122270584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95989942550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31196117401123</t>
+    <t xml:space="preserve">5.89451742172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90122318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95990037918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31196212768555</t>
   </si>
   <si>
     <t xml:space="preserve">6.32202005386353</t>
@@ -3470,58 +3470,58 @@
     <t xml:space="preserve">6.17951917648315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03534126281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06551742553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29351949691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22813653945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44440364837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32958793640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24743986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41508674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53579330444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51902914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78559112548828</t>
+    <t xml:space="preserve">6.03534078598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06551837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29352045059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22813749313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44440317153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32958745956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24743890762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41508722305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53579473495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51903009414673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7855920791626</t>
   </si>
   <si>
     <t xml:space="preserve">8.02700424194336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14435768127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00521087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1108283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30697727203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31200695037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10579967498779</t>
+    <t xml:space="preserve">8.14435863494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00520992279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11082744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30697631835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31200790405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10579872131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.12926959991455</t>
@@ -3530,154 +3530,154 @@
     <t xml:space="preserve">8.09741592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99682855606079</t>
+    <t xml:space="preserve">7.99682712554932</t>
   </si>
   <si>
     <t xml:space="preserve">7.81576728820801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75038480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61961841583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90294599533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69170665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97168016433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526927947998</t>
+    <t xml:space="preserve">7.75038576126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61961889266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90294456481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69170808792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97168159484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0152702331543</t>
   </si>
   <si>
     <t xml:space="preserve">8.09574031829834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0571813583374</t>
+    <t xml:space="preserve">8.05718231201172</t>
   </si>
   <si>
     <t xml:space="preserve">8.10076904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10915088653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98174047470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7772102355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69506120681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63973760604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62967729568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99850368499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70679569244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68332576751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73864984512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39496898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47041130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46370649337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44358968734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7000904083252</t>
+    <t xml:space="preserve">8.10915279388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98174095153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77720785140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69506025314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63973617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62967681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99850463867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70679616928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68332529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73865032196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39496946334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4704122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46370601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44358682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70008993148804</t>
   </si>
   <si>
     <t xml:space="preserve">7.53914737701416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79229593276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26420545578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50897073745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57603025436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63806056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98006391525269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12591552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20806407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01359367370605</t>
+    <t xml:space="preserve">7.79229640960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26420450210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5760293006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63806009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98006248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1259183883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20806312561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01359081268311</t>
   </si>
   <si>
     <t xml:space="preserve">8.28350639343262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19633007049561</t>
+    <t xml:space="preserve">8.19632816314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.21477031707764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12759208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90462112426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85600280761719</t>
+    <t xml:space="preserve">8.12759304046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90462255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85600233078003</t>
   </si>
   <si>
     <t xml:space="preserve">7.92976760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95869636535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80214214324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82596588134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04548168182373</t>
+    <t xml:space="preserve">7.95869731903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80214405059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82596683502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04548263549805</t>
   </si>
   <si>
     <t xml:space="preserve">7.96039819717407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93827533721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15268611907959</t>
+    <t xml:space="preserve">7.93827629089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15268802642822</t>
   </si>
   <si>
     <t xml:space="preserve">8.24627876281738</t>
@@ -3686,34 +3686,34 @@
     <t xml:space="preserve">8.31604862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1918249130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20203495025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17140483856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11354923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12546062469482</t>
+    <t xml:space="preserve">8.19182586669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20203590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17140579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11354827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12545967102051</t>
   </si>
   <si>
     <t xml:space="preserve">8.29052352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14077377319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13056564331055</t>
+    <t xml:space="preserve">8.14077568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13056468963623</t>
   </si>
   <si>
     <t xml:space="preserve">7.94848585128784</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81575727462769</t>
+    <t xml:space="preserve">7.81575632095337</t>
   </si>
   <si>
     <t xml:space="preserve">7.84468507766724</t>
@@ -3722,67 +3722,67 @@
     <t xml:space="preserve">7.92296123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97571325302124</t>
+    <t xml:space="preserve">7.97571516036987</t>
   </si>
   <si>
     <t xml:space="preserve">8.02506160736084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07100772857666</t>
+    <t xml:space="preserve">8.07100677490234</t>
   </si>
   <si>
     <t xml:space="preserve">7.80384397506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80554580688477</t>
+    <t xml:space="preserve">7.8055477142334</t>
   </si>
   <si>
     <t xml:space="preserve">7.82086181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97060775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96550273895264</t>
+    <t xml:space="preserve">7.97060966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96550369262695</t>
   </si>
   <si>
     <t xml:space="preserve">8.02165985107422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6438889503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52987623214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42607402801514</t>
+    <t xml:space="preserve">7.64388847351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52987766265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42607545852661</t>
   </si>
   <si>
     <t xml:space="preserve">7.65920352935791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63197612762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46861743927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59964370727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521377563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25420665740967</t>
+    <t xml:space="preserve">7.63197708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4686164855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59964609146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521282196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25420618057251</t>
   </si>
   <si>
     <t xml:space="preserve">7.00235986709595</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12317752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26271533966064</t>
+    <t xml:space="preserve">7.12317800521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2627158164978</t>
   </si>
   <si>
     <t xml:space="preserve">7.18103456497192</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">7.26441621780396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47372102737427</t>
+    <t xml:space="preserve">7.4737229347229</t>
   </si>
   <si>
     <t xml:space="preserve">7.40735721588135</t>
@@ -3800,85 +3800,85 @@
     <t xml:space="preserve">7.47031831741333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46691513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2967472076416</t>
+    <t xml:space="preserve">7.46691608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29674863815308</t>
   </si>
   <si>
     <t xml:space="preserve">7.35800838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40565490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30865955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28313446044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48222827911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44139051437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48563480377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49584293365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30185222625732</t>
+    <t xml:space="preserve">7.4056544303894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30865907669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28313493728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48222875595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4413890838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48563385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4958438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30185270309448</t>
   </si>
   <si>
     <t xml:space="preserve">7.3341851234436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99385213851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93769693374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07042646408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09254884719849</t>
+    <t xml:space="preserve">6.99385118484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93769645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07042741775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0925498008728</t>
   </si>
   <si>
     <t xml:space="preserve">7.15550994873047</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22187519073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33758878707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25761032104492</t>
+    <t xml:space="preserve">7.22187471389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33758735656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25760936737061</t>
   </si>
   <si>
     <t xml:space="preserve">7.34269380569458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22527885437012</t>
+    <t xml:space="preserve">7.2252779006958</t>
   </si>
   <si>
     <t xml:space="preserve">7.21166515350342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14700174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09425067901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0636191368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30695819854736</t>
+    <t xml:space="preserve">7.14700222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0942497253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06361961364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30695867538452</t>
   </si>
   <si>
     <t xml:space="preserve">7.25590848922729</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">7.37672710418701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1401948928833</t>
+    <t xml:space="preserve">7.14019536972046</t>
   </si>
   <si>
     <t xml:space="preserve">6.87473487854004</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">7.23038291931152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28823900222778</t>
+    <t xml:space="preserve">7.28824043273926</t>
   </si>
   <si>
     <t xml:space="preserve">7.32567644119263</t>
@@ -3908,28 +3908,28 @@
     <t xml:space="preserve">7.57241773605347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53668260574341</t>
+    <t xml:space="preserve">7.53668308258057</t>
   </si>
   <si>
     <t xml:space="preserve">7.59794330596924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73577737808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72556686401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9399790763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67792129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79874086380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15608978271484</t>
+    <t xml:space="preserve">7.73577880859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7255687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93997812271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67792224884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79873991012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15609073638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.35007953643799</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">8.40283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35348415374756</t>
+    <t xml:space="preserve">8.35348320007324</t>
   </si>
   <si>
     <t xml:space="preserve">8.45898628234863</t>
@@ -3959,16 +3959,16 @@
     <t xml:space="preserve">8.43856620788574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39092063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56363868713379</t>
+    <t xml:space="preserve">8.3909215927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56364059448242</t>
   </si>
   <si>
     <t xml:space="preserve">8.55513095855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42325305938721</t>
+    <t xml:space="preserve">8.42325210571289</t>
   </si>
   <si>
     <t xml:space="preserve">8.19012355804443</t>
@@ -3977,19 +3977,19 @@
     <t xml:space="preserve">8.19352626800537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41474342346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38241100311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27520656585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79336452484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03585243225098</t>
+    <t xml:space="preserve">8.4147424697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38241195678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27520561218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79336357116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03585147857666</t>
   </si>
   <si>
     <t xml:space="preserve">9.27833938598633</t>
@@ -3998,43 +3998,43 @@
     <t xml:space="preserve">9.23154354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92524147033691</t>
+    <t xml:space="preserve">8.92524242401123</t>
   </si>
   <si>
     <t xml:space="preserve">8.83165264129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73380565643311</t>
+    <t xml:space="preserve">8.73380661010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.71253395080566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5296049118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28882026672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07611083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26934432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21586036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31247615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20895957946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62753486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69654560089111</t>
+    <t xml:space="preserve">8.52960586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.288818359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07611179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2693452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21586132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31247520446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20896053314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62753438949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69654655456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.4722580909729</t>
@@ -4043,37 +4043,37 @@
     <t xml:space="preserve">7.78108692169189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70689821243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72932720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319591522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01745223999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91910982131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76038265228271</t>
+    <t xml:space="preserve">7.7068977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72932624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319686889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0174503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91910886764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7603816986084</t>
   </si>
   <si>
     <t xml:space="preserve">7.69309616088867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62408399581909</t>
+    <t xml:space="preserve">7.62408351898193</t>
   </si>
   <si>
     <t xml:space="preserve">7.87942790985107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63616132736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85527229309082</t>
+    <t xml:space="preserve">7.63616037368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85527324676514</t>
   </si>
   <si>
     <t xml:space="preserve">7.78798675537109</t>
@@ -4082,82 +4082,82 @@
     <t xml:space="preserve">7.61373233795166</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86389970779419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86217594146729</t>
+    <t xml:space="preserve">7.86389875411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86217498779297</t>
   </si>
   <si>
     <t xml:space="preserve">7.87597703933716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96051597595215</t>
+    <t xml:space="preserve">7.96051692962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.02435302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01054954528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9449896812439</t>
+    <t xml:space="preserve">8.0105504989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94498872756958</t>
   </si>
   <si>
     <t xml:space="preserve">8.25899410247803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37286281585693</t>
+    <t xml:space="preserve">8.37286186218262</t>
   </si>
   <si>
     <t xml:space="preserve">8.43669891357422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43842506408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.4384241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45222568511963</t>
   </si>
   <si>
     <t xml:space="preserve">8.40909290313721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58162307739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65667343139648</t>
+    <t xml:space="preserve">8.58162212371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65667533874512</t>
   </si>
   <si>
     <t xml:space="preserve">8.67824077606201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85076999664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06211757659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25190162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28640556335449</t>
+    <t xml:space="preserve">8.85076904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06211853027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2519006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28640747070312</t>
   </si>
   <si>
     <t xml:space="preserve">8.93703460693359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49708461761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88958930969238</t>
+    <t xml:space="preserve">8.49708366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88958835601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.5538272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37698650360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83850002288818</t>
+    <t xml:space="preserve">9.37698459625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8385009765625</t>
   </si>
   <si>
     <t xml:space="preserve">9.78242969512939</t>
@@ -4166,10 +4166,10 @@
     <t xml:space="preserve">9.65734577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85144233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86006736755371</t>
+    <t xml:space="preserve">9.85144138336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86006832122803</t>
   </si>
   <si>
     <t xml:space="preserve">9.77380275726318</t>
@@ -4190,40 +4190,40 @@
     <t xml:space="preserve">9.99809169769287</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2266941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93770694732666</t>
+    <t xml:space="preserve">10.2266931533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93770599365234</t>
   </si>
   <si>
     <t xml:space="preserve">9.75223636627197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44599533081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52363681793213</t>
+    <t xml:space="preserve">9.44599628448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5236349105835</t>
   </si>
   <si>
     <t xml:space="preserve">9.42442989349365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60989952087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95495986938477</t>
+    <t xml:space="preserve">9.32091236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60990047454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95495891571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.86869335174561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3560914993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1447420120239</t>
+    <t xml:space="preserve">10.3560905456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1447410583496</t>
   </si>
   <si>
     <t xml:space="preserve">9.96358680725098</t>
@@ -4235,34 +4235,34 @@
     <t xml:space="preserve">11.6241846084595</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9815111160278</t>
+    <t xml:space="preserve">10.9815092086792</t>
   </si>
   <si>
     <t xml:space="preserve">11.1540403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1497259140015</t>
+    <t xml:space="preserve">11.1497278213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.8736791610718</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5113668441772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7356538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9081859588623</t>
+    <t xml:space="preserve">10.5113677978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7356548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.908185005188</t>
   </si>
   <si>
     <t xml:space="preserve">11.5724248886108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6371231079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606161117554</t>
+    <t xml:space="preserve">11.6371221542358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9606151580811</t>
   </si>
   <si>
     <t xml:space="preserve">11.9951219558716</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">12.2927350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0123748779297</t>
+    <t xml:space="preserve">12.0123739242554</t>
   </si>
   <si>
     <t xml:space="preserve">11.6845684051514</t>
@@ -4280,16 +4280,16 @@
     <t xml:space="preserve">11.8829774856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8657245635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9821834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9735546112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0727605819702</t>
+    <t xml:space="preserve">11.8657236099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9821815490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9735555648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0727586746216</t>
   </si>
   <si>
     <t xml:space="preserve">11.9390497207642</t>
@@ -4298,40 +4298,40 @@
     <t xml:space="preserve">11.9908075332642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5299634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4135055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8146362304688</t>
+    <t xml:space="preserve">12.5299644470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4135074615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8146371841431</t>
   </si>
   <si>
     <t xml:space="preserve">12.9224691390991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9914798736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9612874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9310941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5817222595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.723388671875</t>
+    <t xml:space="preserve">12.9914817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9612884521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9310960769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5817232131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7233877182007</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374597549438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0813865661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7758188247681</t>
+    <t xml:space="preserve">12.0813875198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7758178710938</t>
   </si>
   <si>
     <t xml:space="preserve">12.2841100692749</t>
@@ -4340,43 +4340,43 @@
     <t xml:space="preserve">12.8448305130005</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6981801986694</t>
+    <t xml:space="preserve">12.6981811523438</t>
   </si>
   <si>
     <t xml:space="preserve">12.6377954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5385904312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0598192214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.180591583252</t>
+    <t xml:space="preserve">12.5385894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0598201751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805925369263</t>
   </si>
   <si>
     <t xml:space="preserve">12.598973274231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2668561935425</t>
+    <t xml:space="preserve">12.2668571472168</t>
   </si>
   <si>
     <t xml:space="preserve">12.7283725738525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.27184009552</t>
+    <t xml:space="preserve">13.2718410491943</t>
   </si>
   <si>
     <t xml:space="preserve">13.4486837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3667325973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0216732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.19420337677</t>
+    <t xml:space="preserve">13.3667316436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.021674156189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1942043304443</t>
   </si>
   <si>
     <t xml:space="preserve">13.4885807037354</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">13.3040447235107</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5456972122192</t>
+    <t xml:space="preserve">13.5456962585449</t>
   </si>
   <si>
     <t xml:space="preserve">13.9147634506226</t>
@@ -4394,16 +4394,16 @@
     <t xml:space="preserve">14.0861177444458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2530765533447</t>
+    <t xml:space="preserve">14.2530784606934</t>
   </si>
   <si>
     <t xml:space="preserve">13.7302303314209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8356771469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8664350509644</t>
+    <t xml:space="preserve">13.8356781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.86643409729</t>
   </si>
   <si>
     <t xml:space="preserve">13.8224973678589</t>
@@ -4415,40 +4415,40 @@
     <t xml:space="preserve">14.0641479492188</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0246057510376</t>
+    <t xml:space="preserve">14.0246076583862</t>
   </si>
   <si>
     <t xml:space="preserve">13.4094924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.005274772644</t>
+    <t xml:space="preserve">13.0052738189697</t>
   </si>
   <si>
     <t xml:space="preserve">12.8031644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.693323135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3154678344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5641498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3927965164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6080865859985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6739912033081</t>
+    <t xml:space="preserve">12.6933221817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.315468788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5641508102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3927955627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6080875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6739902496338</t>
   </si>
   <si>
     <t xml:space="preserve">11.0720586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7381391525269</t>
+    <t xml:space="preserve">10.7381401062012</t>
   </si>
   <si>
     <t xml:space="preserve">10.9402475357056</t>
@@ -4460,13 +4460,13 @@
     <t xml:space="preserve">11.2302293777466</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0632705688477</t>
+    <t xml:space="preserve">11.063271522522</t>
   </si>
   <si>
     <t xml:space="preserve">10.782075881958</t>
   </si>
   <si>
-    <t xml:space="preserve">10.579966545105</t>
+    <t xml:space="preserve">10.5799655914307</t>
   </si>
   <si>
     <t xml:space="preserve">10.966609954834</t>
@@ -4493,10 +4493,10 @@
     <t xml:space="preserve">10.9841842651367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5404243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117757797241</t>
+    <t xml:space="preserve">10.5404233932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117767333984</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467514038086</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">11.1819000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0676641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8523740768433</t>
+    <t xml:space="preserve">11.067663192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8523750305176</t>
   </si>
   <si>
     <t xml:space="preserve">10.9753971099854</t>
@@ -4517,16 +4517,16 @@
     <t xml:space="preserve">11.0940265655518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4411268234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5861177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9551858901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.634449005127</t>
+    <t xml:space="preserve">11.441125869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5861186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9551849365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6344480514526</t>
   </si>
   <si>
     <t xml:space="preserve">11.6608114242554</t>
@@ -4541,79 +4541,79 @@
     <t xml:space="preserve">11.3005294799805</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4147653579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2917404174805</t>
+    <t xml:space="preserve">11.4147644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2917423248291</t>
   </si>
   <si>
     <t xml:space="preserve">11.5685443878174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5421810150146</t>
+    <t xml:space="preserve">11.542181968689</t>
   </si>
   <si>
     <t xml:space="preserve">11.3224973678589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6827783584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2829551696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2803182601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1704759597778</t>
+    <t xml:space="preserve">11.6827793121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2829542160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2803192138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1704769134521</t>
   </si>
   <si>
     <t xml:space="preserve">12.3945531845093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2188062667847</t>
+    <t xml:space="preserve">12.218807220459</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913896560669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0826025009155</t>
+    <t xml:space="preserve">12.0826034545898</t>
   </si>
   <si>
     <t xml:space="preserve">12.029878616333</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4384908676147</t>
+    <t xml:space="preserve">12.4384899139404</t>
   </si>
   <si>
     <t xml:space="preserve">12.5527248382568</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1221466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.739896774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7442903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3286485671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5790882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5219707489014</t>
+    <t xml:space="preserve">12.1221475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7398958206177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7442893981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.328649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5790872573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5219697952271</t>
   </si>
   <si>
     <t xml:space="preserve">12.5175762176514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2407760620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9288244247437</t>
+    <t xml:space="preserve">12.2407751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9288234710693</t>
   </si>
   <si>
     <t xml:space="preserve">11.9024620056152</t>
@@ -4622,22 +4622,22 @@
     <t xml:space="preserve">11.7882280349731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1265392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9622163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1994743347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5377883911133</t>
+    <t xml:space="preserve">12.126540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9622173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1994733810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.537787437439</t>
   </si>
   <si>
     <t xml:space="preserve">11.8761014938354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6564178466797</t>
+    <t xml:space="preserve">11.6564168930054</t>
   </si>
   <si>
     <t xml:space="preserve">12.4604587554932</t>
@@ -4646,10 +4646,10 @@
     <t xml:space="preserve">12.7504415512085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0140609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.18541431427</t>
+    <t xml:space="preserve">13.0140619277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1854152679443</t>
   </si>
   <si>
     <t xml:space="preserve">12.7328662872314</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">12.9217948913574</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2117767333984</t>
+    <t xml:space="preserve">13.2117776870728</t>
   </si>
   <si>
     <t xml:space="preserve">13.1590538024902</t>
@@ -4682,40 +4682,40 @@
     <t xml:space="preserve">13.2205638885498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5193338394165</t>
+    <t xml:space="preserve">13.5193347930908</t>
   </si>
   <si>
     <t xml:space="preserve">13.8927965164185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4534282684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8005304336548</t>
+    <t xml:space="preserve">13.4534292221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8005294799805</t>
   </si>
   <si>
     <t xml:space="preserve">14.1564168930054</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9982442855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1959609985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.626540184021</t>
+    <t xml:space="preserve">13.9982452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1959600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6265411376953</t>
   </si>
   <si>
     <t xml:space="preserve">14.7539577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4551877975464</t>
+    <t xml:space="preserve">14.4551868438721</t>
   </si>
   <si>
     <t xml:space="preserve">14.3585252761841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7653799057007</t>
+    <t xml:space="preserve">13.765380859375</t>
   </si>
   <si>
     <t xml:space="preserve">14.055362701416</t>
@@ -4727,19 +4727,19 @@
     <t xml:space="preserve">14.6572961807251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7275953292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3101959228516</t>
+    <t xml:space="preserve">14.7275943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3101949691772</t>
   </si>
   <si>
     <t xml:space="preserve">14.424430847168</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7851219177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6908102035522</t>
+    <t xml:space="preserve">13.785120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6908092498779</t>
   </si>
   <si>
     <t xml:space="preserve">14.3578357696533</t>
@@ -4748,31 +4748,31 @@
     <t xml:space="preserve">14.446629524231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5265436172485</t>
+    <t xml:space="preserve">14.5265426635742</t>
   </si>
   <si>
     <t xml:space="preserve">14.1314134597778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5443000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8417568206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954662322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2557229995728</t>
+    <t xml:space="preserve">14.54430103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.841757774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4954652786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2557239532471</t>
   </si>
   <si>
     <t xml:space="preserve">14.0381813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9138717651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6119737625122</t>
+    <t xml:space="preserve">13.9138708114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6119756698608</t>
   </si>
   <si>
     <t xml:space="preserve">13.7806816101074</t>
@@ -4784,31 +4784,31 @@
     <t xml:space="preserve">13.5276203155518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9893455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0159826278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7451629638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6474905014038</t>
+    <t xml:space="preserve">13.9893445968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.015983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7451639175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6474914550781</t>
   </si>
   <si>
     <t xml:space="preserve">13.949387550354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1402940750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643878936768</t>
+    <t xml:space="preserve">14.1402931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643888473511</t>
   </si>
   <si>
     <t xml:space="preserve">14.721887588501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7796049118042</t>
+    <t xml:space="preserve">14.7796039581299</t>
   </si>
   <si>
     <t xml:space="preserve">14.6686124801636</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">14.4599475860596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9349918365479</t>
+    <t xml:space="preserve">14.9349908828735</t>
   </si>
   <si>
     <t xml:space="preserve">14.4199914932251</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">14.0071039199829</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0603790283203</t>
+    <t xml:space="preserve">14.0603799819946</t>
   </si>
   <si>
     <t xml:space="preserve">14.0692586898804</t>
@@ -4850,22 +4850,22 @@
     <t xml:space="preserve">14.3445177078247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2290859222412</t>
+    <t xml:space="preserve">14.2290849685669</t>
   </si>
   <si>
     <t xml:space="preserve">14.6597318649292</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2679653167725</t>
+    <t xml:space="preserve">15.2679643630981</t>
   </si>
   <si>
     <t xml:space="preserve">14.5176639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6952486038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2424058914185</t>
+    <t xml:space="preserve">14.6952495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2424049377441</t>
   </si>
   <si>
     <t xml:space="preserve">14.2690439224243</t>
@@ -4880,7 +4880,7 @@
     <t xml:space="preserve">14.3977937698364</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4288711547852</t>
+    <t xml:space="preserve">14.4288692474365</t>
   </si>
   <si>
     <t xml:space="preserve">14.1180953979492</t>
@@ -4889,13 +4889,13 @@
     <t xml:space="preserve">13.6297330856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5498189926147</t>
+    <t xml:space="preserve">13.5498199462891</t>
   </si>
   <si>
     <t xml:space="preserve">13.4388284683228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.540940284729</t>
+    <t xml:space="preserve">13.5409393310547</t>
   </si>
   <si>
     <t xml:space="preserve">13.8872337341309</t>
@@ -4910,7 +4910,7 @@
     <t xml:space="preserve">14.3800344467163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4011545181274</t>
+    <t xml:space="preserve">15.4011526107788</t>
   </si>
   <si>
     <t xml:space="preserve">14.6641712188721</t>
@@ -4919,13 +4919,13 @@
     <t xml:space="preserve">14.4377498626709</t>
   </si>
   <si>
-    <t xml:space="preserve">13.971586227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.224645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9227504730225</t>
+    <t xml:space="preserve">13.9715852737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2246465682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9227495193481</t>
   </si>
   <si>
     <t xml:space="preserve">14.2646036148071</t>
@@ -4937,13 +4937,13 @@
     <t xml:space="preserve">14.3711547851562</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4732666015625</t>
+    <t xml:space="preserve">14.4732656478882</t>
   </si>
   <si>
     <t xml:space="preserve">14.5487403869629</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0026636123657</t>
+    <t xml:space="preserve">14.00266456604</t>
   </si>
   <si>
     <t xml:space="preserve">13.7140865325928</t>
@@ -4961,13 +4961,13 @@
     <t xml:space="preserve">11.9559841156006</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7384414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7695198059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.164647102356</t>
+    <t xml:space="preserve">11.7384405136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7695188522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1646480560303</t>
   </si>
   <si>
     <t xml:space="preserve">12.0358972549438</t>
@@ -4976,28 +4976,28 @@
     <t xml:space="preserve">11.7650785446167</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3877086639404</t>
+    <t xml:space="preserve">11.3877077102661</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942598342896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8361139297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7739582061768</t>
+    <t xml:space="preserve">11.8361129760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7739591598511</t>
   </si>
   <si>
     <t xml:space="preserve">11.6096906661987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.631890296936</t>
+    <t xml:space="preserve">11.6318893432617</t>
   </si>
   <si>
     <t xml:space="preserve">11.9826221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6851654052734</t>
+    <t xml:space="preserve">11.6851644515991</t>
   </si>
   <si>
     <t xml:space="preserve">11.5386562347412</t>
@@ -5006,10 +5006,10 @@
     <t xml:space="preserve">11.5075798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8183555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9737424850464</t>
+    <t xml:space="preserve">11.8183546066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9737434387207</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337854385376</t>
@@ -5042,7 +5042,7 @@
     <t xml:space="preserve">10.894907951355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7439594268799</t>
+    <t xml:space="preserve">10.7439584732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.02809715271</t>
@@ -5051,7 +5051,7 @@
     <t xml:space="preserve">11.1168899536133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0991315841675</t>
+    <t xml:space="preserve">11.0991306304932</t>
   </si>
   <si>
     <t xml:space="preserve">10.8771486282349</t>
@@ -5060,10 +5060,10 @@
     <t xml:space="preserve">10.7528381347656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8815879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8460712432861</t>
+    <t xml:space="preserve">10.8815889358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8460702896118</t>
   </si>
   <si>
     <t xml:space="preserve">10.7705974578857</t>
@@ -5072,10 +5072,10 @@
     <t xml:space="preserve">10.9171056747437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9526214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.071325302124</t>
+    <t xml:space="preserve">10.9526233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0713262557983</t>
   </si>
   <si>
     <t xml:space="preserve">11.2311182022095</t>
@@ -5093,16 +5093,16 @@
     <t xml:space="preserve">11.1489391326904</t>
   </si>
   <si>
-    <t xml:space="preserve">10.847617149353</t>
+    <t xml:space="preserve">10.8476161956787</t>
   </si>
   <si>
     <t xml:space="preserve">10.6558656692505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8795747756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2722072601318</t>
+    <t xml:space="preserve">10.8795757293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2722082138062</t>
   </si>
   <si>
     <t xml:space="preserve">11.3452548980713</t>
@@ -5114,10 +5114,10 @@
     <t xml:space="preserve">11.6967992782593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7561511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7104949951172</t>
+    <t xml:space="preserve">11.7561502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7104940414429</t>
   </si>
   <si>
     <t xml:space="preserve">11.6420125961304</t>
@@ -5126,13 +5126,13 @@
     <t xml:space="preserve">11.9205083847046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8063716888428</t>
+    <t xml:space="preserve">11.8063707351685</t>
   </si>
   <si>
     <t xml:space="preserve">11.8931140899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4274339675903</t>
+    <t xml:space="preserve">11.4274349212646</t>
   </si>
   <si>
     <t xml:space="preserve">11.7972402572632</t>
@@ -5153,7 +5153,7 @@
     <t xml:space="preserve">11.8657217025757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1853065490723</t>
+    <t xml:space="preserve">12.1853075027466</t>
   </si>
   <si>
     <t xml:space="preserve">12.5231533050537</t>
@@ -5162,13 +5162,13 @@
     <t xml:space="preserve">12.5185880661011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5870685577393</t>
+    <t xml:space="preserve">12.5870695114136</t>
   </si>
   <si>
     <t xml:space="preserve">12.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305208206177</t>
+    <t xml:space="preserve">12.1305198669434</t>
   </si>
   <si>
     <t xml:space="preserve">12.4501066207886</t>
@@ -5177,16 +5177,16 @@
     <t xml:space="preserve">12.4227113723755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7696886062622</t>
+    <t xml:space="preserve">12.7696895599365</t>
   </si>
   <si>
     <t xml:space="preserve">13.0025291442871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.016227722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9568748474121</t>
+    <t xml:space="preserve">13.0162267684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9568758010864</t>
   </si>
   <si>
     <t xml:space="preserve">12.966007232666</t>
@@ -5195,10 +5195,10 @@
     <t xml:space="preserve">13.1577568054199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1668882369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184307098389</t>
+    <t xml:space="preserve">13.1668891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184316635132</t>
   </si>
   <si>
     <t xml:space="preserve">13.5549554824829</t>
@@ -5207,7 +5207,7 @@
     <t xml:space="preserve">13.7330093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6553964614868</t>
+    <t xml:space="preserve">13.6553955078125</t>
   </si>
   <si>
     <t xml:space="preserve">13.6143064498901</t>
@@ -5222,16 +5222,16 @@
     <t xml:space="preserve">13.8151884078979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7695341110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6462650299072</t>
+    <t xml:space="preserve">13.7695331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6462640762329</t>
   </si>
   <si>
     <t xml:space="preserve">13.3632040023804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6599617004395</t>
+    <t xml:space="preserve">13.6599607467651</t>
   </si>
   <si>
     <t xml:space="preserve">13.5823488235474</t>
@@ -5243,7 +5243,7 @@
     <t xml:space="preserve">14.0708560943604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0845518112183</t>
+    <t xml:space="preserve">14.0845527648926</t>
   </si>
   <si>
     <t xml:space="preserve">14.0434637069702</t>
@@ -5258,46 +5258,46 @@
     <t xml:space="preserve">13.9658498764038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9475870132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9247608184814</t>
+    <t xml:space="preserve">13.9475879669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9247598648071</t>
   </si>
   <si>
     <t xml:space="preserve">13.7877960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7512712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6736583709717</t>
+    <t xml:space="preserve">13.7512722015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.673659324646</t>
   </si>
   <si>
     <t xml:space="preserve">13.8380155563354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9612846374512</t>
+    <t xml:space="preserve">13.9612836837769</t>
   </si>
   <si>
     <t xml:space="preserve">13.9293251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4773416519165</t>
+    <t xml:space="preserve">13.4773426055908</t>
   </si>
   <si>
     <t xml:space="preserve">13.6097412109375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.550389289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7604026794434</t>
+    <t xml:space="preserve">13.5503902435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.760401725769</t>
   </si>
   <si>
     <t xml:space="preserve">13.6645269393921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7375745773315</t>
+    <t xml:space="preserve">13.7375755310059</t>
   </si>
   <si>
     <t xml:space="preserve">13.847146987915</t>
@@ -5318,7 +5318,7 @@
     <t xml:space="preserve">13.7786645889282</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3951635360718</t>
+    <t xml:space="preserve">13.3951625823975</t>
   </si>
   <si>
     <t xml:space="preserve">13.3860311508179</t>
@@ -5327,7 +5327,7 @@
     <t xml:space="preserve">13.4316873550415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4362516403198</t>
+    <t xml:space="preserve">13.4362525939941</t>
   </si>
   <si>
     <t xml:space="preserve">13.7740993499756</t>
@@ -5339,7 +5339,7 @@
     <t xml:space="preserve">13.2125434875488</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3084182739258</t>
+    <t xml:space="preserve">13.3084173202515</t>
   </si>
   <si>
     <t xml:space="preserve">13.011661529541</t>
@@ -5357,28 +5357,28 @@
     <t xml:space="preserve">13.9567184448242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343313217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3950061798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2945642471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954462051392</t>
+    <t xml:space="preserve">14.0343322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3950071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2945652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4954471588135</t>
   </si>
   <si>
     <t xml:space="preserve">14.5045785903931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2671718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9338912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0571603775024</t>
+    <t xml:space="preserve">14.2671728134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.933892250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0571594238281</t>
   </si>
   <si>
     <t xml:space="preserve">14.0982484817505</t>
@@ -5387,13 +5387,13 @@
     <t xml:space="preserve">13.7969255447388</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9383010864258</t>
+    <t xml:space="preserve">14.9383001327515</t>
   </si>
   <si>
     <t xml:space="preserve">14.8999509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2542333602905</t>
+    <t xml:space="preserve">15.2542324066162</t>
   </si>
   <si>
     <t xml:space="preserve">14.783073425293</t>
@@ -5405,16 +5405,16 @@
     <t xml:space="preserve">14.585844039917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6917638778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9063425064087</t>
+    <t xml:space="preserve">14.6917629241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9063415527344</t>
   </si>
   <si>
     <t xml:space="preserve">14.7008943557739</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7191572189331</t>
+    <t xml:space="preserve">14.7191581726074</t>
   </si>
   <si>
     <t xml:space="preserve">14.1302080154419</t>
@@ -5429,7 +5429,7 @@
     <t xml:space="preserve">14.3730640411377</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1788339614868</t>
+    <t xml:space="preserve">14.1788349151611</t>
   </si>
   <si>
     <t xml:space="preserve">14.2620763778687</t>
@@ -5438,7 +5438,7 @@
     <t xml:space="preserve">14.3961868286133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.299072265625</t>
+    <t xml:space="preserve">14.2990713119507</t>
   </si>
   <si>
     <t xml:space="preserve">14.1834592819214</t>
@@ -5459,13 +5459,13 @@
     <t xml:space="preserve">14.4331827163696</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5626707077026</t>
+    <t xml:space="preserve">14.5626697540283</t>
   </si>
   <si>
     <t xml:space="preserve">14.3453168869019</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1094655990601</t>
+    <t xml:space="preserve">14.1094646453857</t>
   </si>
   <si>
     <t xml:space="preserve">14.2019567489624</t>
@@ -5477,22 +5477,22 @@
     <t xml:space="preserve">14.6274137496948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7291536331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8725137710571</t>
+    <t xml:space="preserve">14.729154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8725147247314</t>
   </si>
   <si>
     <t xml:space="preserve">14.7707748413086</t>
   </si>
   <si>
-    <t xml:space="preserve">14.840142250061</t>
+    <t xml:space="preserve">14.8401432037354</t>
   </si>
   <si>
     <t xml:space="preserve">14.7615251541138</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7014074325562</t>
+    <t xml:space="preserve">14.7014064788818</t>
   </si>
   <si>
     <t xml:space="preserve">14.6135406494141</t>
@@ -5504,7 +5504,7 @@
     <t xml:space="preserve">14.3869390487671</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0863428115845</t>
+    <t xml:space="preserve">14.0863418579102</t>
   </si>
   <si>
     <t xml:space="preserve">13.8736143112183</t>
@@ -5522,10 +5522,10 @@
     <t xml:space="preserve">13.4712791442871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4019117355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065351486206</t>
+    <t xml:space="preserve">13.4019107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065361022949</t>
   </si>
   <si>
     <t xml:space="preserve">13.42041015625</t>
@@ -5540,28 +5540,28 @@
     <t xml:space="preserve">13.8551158905029</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8504915237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9291086196899</t>
+    <t xml:space="preserve">13.850492477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9291095733643</t>
   </si>
   <si>
     <t xml:space="preserve">13.8597402572632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5822696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6100149154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8921136856079</t>
+    <t xml:space="preserve">13.5822687149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6100158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8921127319336</t>
   </si>
   <si>
     <t xml:space="preserve">13.438907623291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6886329650879</t>
+    <t xml:space="preserve">13.6886320114136</t>
   </si>
   <si>
     <t xml:space="preserve">13.4759044647217</t>
@@ -5573,13 +5573,13 @@
     <t xml:space="preserve">13.7903728485107</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7071313858032</t>
+    <t xml:space="preserve">13.7071304321289</t>
   </si>
   <si>
     <t xml:space="preserve">13.6331386566162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8366184234619</t>
+    <t xml:space="preserve">13.8366174697876</t>
   </si>
   <si>
     <t xml:space="preserve">13.9522314071655</t>
@@ -5600,31 +5600,31 @@
     <t xml:space="preserve">15.3303451538086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4320831298828</t>
+    <t xml:space="preserve">15.4320840835571</t>
   </si>
   <si>
     <t xml:space="preserve">15.3395929336548</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2378540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731100082397</t>
+    <t xml:space="preserve">15.2378549575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731109619141</t>
   </si>
   <si>
     <t xml:space="preserve">15.7141799926758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.88991355896</t>
+    <t xml:space="preserve">15.8899126052856</t>
   </si>
   <si>
     <t xml:space="preserve">15.963906288147</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0101490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0009021759033</t>
+    <t xml:space="preserve">16.0101509094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0009002685547</t>
   </si>
   <si>
     <t xml:space="preserve">16.2275047302246</t>
@@ -5636,7 +5636,7 @@
     <t xml:space="preserve">16.5281009674072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4078617095947</t>
+    <t xml:space="preserve">16.4078598022461</t>
   </si>
   <si>
     <t xml:space="preserve">16.352367401123</t>
@@ -5654,19 +5654,19 @@
     <t xml:space="preserve">16.8888130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">16.911937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.93505859375</t>
+    <t xml:space="preserve">16.9119358062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9350566864014</t>
   </si>
   <si>
     <t xml:space="preserve">17.0183010101318</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9396820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2032833099365</t>
+    <t xml:space="preserve">16.9396839141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2032814025879</t>
   </si>
   <si>
     <t xml:space="preserve">17.2402763366699</t>
@@ -5675,13 +5675,13 @@
     <t xml:space="preserve">17.0599212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1894054412842</t>
+    <t xml:space="preserve">17.1894073486328</t>
   </si>
   <si>
     <t xml:space="preserve">16.9489326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1107921600342</t>
+    <t xml:space="preserve">17.1107902526855</t>
   </si>
   <si>
     <t xml:space="preserve">16.976676940918</t>
@@ -5693,40 +5693,40 @@
     <t xml:space="preserve">16.5096015930176</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5974674224854</t>
+    <t xml:space="preserve">16.597469329834</t>
   </si>
   <si>
     <t xml:space="preserve">16.3708667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.338493347168</t>
+    <t xml:space="preserve">16.3384952545166</t>
   </si>
   <si>
     <t xml:space="preserve">16.2182559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1396389007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0471477508545</t>
+    <t xml:space="preserve">16.1396369934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0471458435059</t>
   </si>
   <si>
     <t xml:space="preserve">14.7800235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6967830657959</t>
+    <t xml:space="preserve">14.6967821121216</t>
   </si>
   <si>
     <t xml:space="preserve">14.4979267120361</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4054365158081</t>
+    <t xml:space="preserve">14.4054355621338</t>
   </si>
   <si>
     <t xml:space="preserve">14.4239339828491</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6782846450806</t>
+    <t xml:space="preserve">14.6782836914062</t>
   </si>
   <si>
     <t xml:space="preserve">14.6690349578857</t>
@@ -5741,19 +5741,19 @@
     <t xml:space="preserve">14.9465065002441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9326333999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8632650375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9002628326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9808807373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1421175003052</t>
+    <t xml:space="preserve">14.9326343536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8632659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9002618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9808797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1421184539795</t>
   </si>
   <si>
     <t xml:space="preserve">14.8338689804077</t>
@@ -5780,13 +5780,13 @@
     <t xml:space="preserve">14.3169603347778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1699485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0845890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9755144119263</t>
+    <t xml:space="preserve">14.1699495315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0845880508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9755153656006</t>
   </si>
   <si>
     <t xml:space="preserve">14.056134223938</t>
@@ -5810,13 +5810,13 @@
     <t xml:space="preserve">13.5771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6577816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8617010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6198434829712</t>
+    <t xml:space="preserve">13.6577825546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8617000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6198444366455</t>
   </si>
   <si>
     <t xml:space="preserve">13.7621126174927</t>
@@ -5825,7 +5825,7 @@
     <t xml:space="preserve">13.6008749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.752628326416</t>
+    <t xml:space="preserve">13.7526273727417</t>
   </si>
   <si>
     <t xml:space="preserve">13.6625242233276</t>
@@ -5834,7 +5834,7 @@
     <t xml:space="preserve">13.3590183258057</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2973699569702</t>
+    <t xml:space="preserve">13.2973690032959</t>
   </si>
   <si>
     <t xml:space="preserve">13.6103601455688</t>
@@ -5852,13 +5852,13 @@
     <t xml:space="preserve">13.5534524917603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4159269332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5202560424805</t>
+    <t xml:space="preserve">13.3969564437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4159259796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5202569961548</t>
   </si>
   <si>
     <t xml:space="preserve">13.8047943115234</t>
@@ -5867,25 +5867,25 @@
     <t xml:space="preserve">13.7953090667725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7336587905884</t>
+    <t xml:space="preserve">13.7336578369141</t>
   </si>
   <si>
     <t xml:space="preserve">13.9470615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6340713500977</t>
+    <t xml:space="preserve">13.6340703964233</t>
   </si>
   <si>
     <t xml:space="preserve">13.6672668457031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6862373352051</t>
+    <t xml:space="preserve">13.6862363815308</t>
   </si>
   <si>
     <t xml:space="preserve">13.8285045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8854131698608</t>
+    <t xml:space="preserve">13.8854122161865</t>
   </si>
   <si>
     <t xml:space="preserve">12.6761293411255</t>
@@ -5897,7 +5897,7 @@
     <t xml:space="preserve">12.0548896789551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0311794281006</t>
+    <t xml:space="preserve">12.0311784744263</t>
   </si>
   <si>
     <t xml:space="preserve">12.1639623641968</t>
@@ -5906,7 +5906,7 @@
     <t xml:space="preserve">12.0833435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1687049865723</t>
+    <t xml:space="preserve">12.1687040328979</t>
   </si>
   <si>
     <t xml:space="preserve">12.102313041687</t>
@@ -5915,22 +5915,22 @@
     <t xml:space="preserve">12.0406627655029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.140251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1876745223999</t>
+    <t xml:space="preserve">12.1402521133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1876735687256</t>
   </si>
   <si>
     <t xml:space="preserve">11.8557138442993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.95530128479</t>
+    <t xml:space="preserve">11.9553022384644</t>
   </si>
   <si>
     <t xml:space="preserve">11.9837560653687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1829328536987</t>
+    <t xml:space="preserve">12.1829319000244</t>
   </si>
   <si>
     <t xml:space="preserve">11.8414869308472</t>
@@ -5957,7 +5957,7 @@
     <t xml:space="preserve">12.3299427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0691175460815</t>
+    <t xml:space="preserve">12.0691165924072</t>
   </si>
   <si>
     <t xml:space="preserve">12.0359201431274</t>
@@ -5972,7 +5972,7 @@
     <t xml:space="preserve">12.5291185379028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196342468262</t>
+    <t xml:space="preserve">12.5196332931519</t>
   </si>
   <si>
     <t xml:space="preserve">12.6856136322021</t>
@@ -5993,7 +5993,7 @@
     <t xml:space="preserve">13.0365428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4348955154419</t>
+    <t xml:space="preserve">13.4348945617676</t>
   </si>
   <si>
     <t xml:space="preserve">13.4064416885376</t>
@@ -6014,13 +6014,13 @@
     <t xml:space="preserve">13.6909790039062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9565458297729</t>
+    <t xml:space="preserve">13.9565467834473</t>
   </si>
   <si>
     <t xml:space="preserve">14.0087118148804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7384004592896</t>
+    <t xml:space="preserve">13.7384014129639</t>
   </si>
   <si>
     <t xml:space="preserve">13.8000507354736</t>
@@ -6029,7 +6029,7 @@
     <t xml:space="preserve">13.781081199646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9186086654663</t>
+    <t xml:space="preserve">13.918607711792</t>
   </si>
   <si>
     <t xml:space="preserve">14.0798463821411</t>
@@ -6047,10 +6047,10 @@
     <t xml:space="preserve">14.3217029571533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2363414764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3643827438354</t>
+    <t xml:space="preserve">14.2363424301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3643836975098</t>
   </si>
   <si>
     <t xml:space="preserve">14.5777854919434</t>
@@ -6059,13 +6059,13 @@
     <t xml:space="preserve">14.4781980514526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6678895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6590280532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4177932739258</t>
+    <t xml:space="preserve">14.6678886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6590270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4177913665771</t>
   </si>
   <si>
     <t xml:space="preserve">16.346658706665</t>
@@ -6077,7 +6077,7 @@
     <t xml:space="preserve">16.4130516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5078964233398</t>
+    <t xml:space="preserve">16.5078983306885</t>
   </si>
   <si>
     <t xml:space="preserve">16.5553188323975</t>
@@ -6678,6 +6678,9 @@
   </si>
   <si>
     <t xml:space="preserve">15.9449996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1499996185303</t>
   </si>
 </sst>
 </file>
@@ -71938,7 +71941,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6940625</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>1672299</v>
@@ -71959,6 +71962,32 @@
         <v>2221</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6928240741</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>1785992</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>16.2049999237061</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>15.8599996566772</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>15.8850002288818</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>16.1499996185303</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>2222</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2226" uniqueCount="2226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2227" uniqueCount="2227">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,118 +38,118 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87406969070435</t>
+    <t xml:space="preserve">7.8740701675415</t>
   </si>
   <si>
     <t xml:space="preserve">TEN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88865041732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6990909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48036575317383</t>
+    <t xml:space="preserve">7.88864994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69909143447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48036766052246</t>
   </si>
   <si>
     <t xml:space="preserve">7.19602489471436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11582660675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0793719291687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12311792373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07208156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62734270095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56901597976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77680397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39403629302979</t>
+    <t xml:space="preserve">7.11582565307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07937288284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12311697006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07208013534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62734222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56901550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77680253982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39403676986694</t>
   </si>
   <si>
     <t xml:space="preserve">6.63463306427002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80596685409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78044939041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88981246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91168451309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82783937454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49246215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51433563232422</t>
+    <t xml:space="preserve">6.80596780776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78044986724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88981151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91168308258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8278374671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49246311187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51433515548706</t>
   </si>
   <si>
     <t xml:space="preserve">7.03562879562378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43413496017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29925632476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80232095718384</t>
+    <t xml:space="preserve">6.43413591384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29925584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80232048034668</t>
   </si>
   <si>
     <t xml:space="preserve">6.95542812347412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74035024642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14863538742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0611457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8314847946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11947250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86064863204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54349803924561</t>
+    <t xml:space="preserve">6.74034881591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14863443374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06114530563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148431777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11947154998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8606481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54349899291992</t>
   </si>
   <si>
     <t xml:space="preserve">6.55443382263184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16686248779297</t>
+    <t xml:space="preserve">7.16686153411865</t>
   </si>
   <si>
     <t xml:space="preserve">7.32726144790649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50223922729492</t>
+    <t xml:space="preserve">7.50223827362061</t>
   </si>
   <si>
     <t xml:space="preserve">7.45120429992676</t>
@@ -158,40 +158,40 @@
     <t xml:space="preserve">7.61159944534302</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91781520843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00530338287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71367120742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85948705673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58972692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82303333282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73554372787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9615592956543</t>
+    <t xml:space="preserve">7.91781377792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0053014755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71367168426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85948848724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58972787857056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82303476333618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73554515838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96155881881714</t>
   </si>
   <si>
     <t xml:space="preserve">7.81574249267578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7792911529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95426845550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72096252441406</t>
+    <t xml:space="preserve">7.77928924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95426893234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72096300125122</t>
   </si>
   <si>
     <t xml:space="preserve">7.66992807388306</t>
@@ -200,124 +200,124 @@
     <t xml:space="preserve">7.98343181610107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83032417297363</t>
+    <t xml:space="preserve">7.83032608032227</t>
   </si>
   <si>
     <t xml:space="preserve">7.53140163421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66263675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64076471328735</t>
+    <t xml:space="preserve">7.66263628005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64076328277588</t>
   </si>
   <si>
     <t xml:space="preserve">8.07821273803711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11466598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17299175262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4208812713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41358852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45004367828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69793033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82916450500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86561965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91665363311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63960456848145</t>
+    <t xml:space="preserve">8.11466693878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17299270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42087936401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41358947753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45004463195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69793224334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82916736602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86561870574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91665554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63960647583008</t>
   </si>
   <si>
     <t xml:space="preserve">8.80000114440918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80729484558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58856964111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47191524505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01988697052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97614145278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39900875091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2459020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21673679351807</t>
+    <t xml:space="preserve">8.80729389190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58856773376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47191715240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01988506317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97614002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39900779724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21673774719238</t>
   </si>
   <si>
     <t xml:space="preserve">8.29693603515625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30422687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45733451843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64689445495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67605876922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39171695709229</t>
+    <t xml:space="preserve">8.30422782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45733261108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64689350128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67605781555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3917179107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.56669616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62654972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73129749298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75374031066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95575332641602</t>
+    <t xml:space="preserve">8.62655162811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73129653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75374221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95575046539307</t>
   </si>
   <si>
     <t xml:space="preserve">8.97819805145264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98568248748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91086101531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80611610412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67892360687256</t>
+    <t xml:space="preserve">8.98567867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91086006164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80611515045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67892169952393</t>
   </si>
   <si>
     <t xml:space="preserve">8.6489953994751</t>
@@ -329,55 +329,55 @@
     <t xml:space="preserve">9.53185176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69645214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52436923980713</t>
+    <t xml:space="preserve">9.69645404815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52437019348145</t>
   </si>
   <si>
     <t xml:space="preserve">9.4944429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28495121002197</t>
+    <t xml:space="preserve">9.28495311737061</t>
   </si>
   <si>
     <t xml:space="preserve">9.15775966644287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34480667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17272472381592</t>
+    <t xml:space="preserve">9.34480857849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1727237701416</t>
   </si>
   <si>
     <t xml:space="preserve">9.40466117858887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66652488708496</t>
+    <t xml:space="preserve">9.66652584075928</t>
   </si>
   <si>
     <t xml:space="preserve">9.4271068572998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8011999130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30739688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04553508758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14279747009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61415386199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73386192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86853504180908</t>
+    <t xml:space="preserve">9.80119705200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30739784240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0455322265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14279651641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61415195465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73386096954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8685359954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.83112525939941</t>
@@ -386,160 +386,160 @@
     <t xml:space="preserve">9.59918880462646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32236289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39718151092529</t>
+    <t xml:space="preserve">9.32236194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39717960357666</t>
   </si>
   <si>
     <t xml:space="preserve">9.50940608978271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65904331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74882698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47947883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59170722961426</t>
+    <t xml:space="preserve">9.65904426574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7488260269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47948169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59170818328857</t>
   </si>
   <si>
     <t xml:space="preserve">9.21761608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37473201751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18768787384033</t>
+    <t xml:space="preserve">9.37473392486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18768882751465</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16524219512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0979061126709</t>
+    <t xml:space="preserve">9.16524410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09790706634521</t>
   </si>
   <si>
     <t xml:space="preserve">8.82855892181396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94827079772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70884990692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57417774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74625873565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00064182281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19516849517822</t>
+    <t xml:space="preserve">8.94826984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70885181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57417678833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74626159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00064373016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19517040252686</t>
   </si>
   <si>
     <t xml:space="preserve">9.38969707489014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36725044250488</t>
+    <t xml:space="preserve">9.36725425720215</t>
   </si>
   <si>
     <t xml:space="preserve">9.48696041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70393562316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65156173706055</t>
+    <t xml:space="preserve">9.70393466949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65156269073486</t>
   </si>
   <si>
     <t xml:space="preserve">9.62911701202393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51688861846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45703411102295</t>
+    <t xml:space="preserve">9.51688766479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45703506469727</t>
   </si>
   <si>
     <t xml:space="preserve">9.09042453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22509670257568</t>
+    <t xml:space="preserve">9.22509765625</t>
   </si>
   <si>
     <t xml:space="preserve">9.2999153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10538768768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85848903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66395854949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71633338928223</t>
+    <t xml:space="preserve">9.10538864135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85848617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66396141052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71633434295654</t>
   </si>
   <si>
     <t xml:space="preserve">8.88093280792236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76870632171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67144203186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69388675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90337944030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7013692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44698715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55921363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35976982116699</t>
+    <t xml:space="preserve">8.76870441436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67144107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69388771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90338039398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70136833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44698619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55921459197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35977077484131</t>
   </si>
   <si>
     <t xml:space="preserve">9.50192546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64408111572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76379013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74134254455566</t>
+    <t xml:space="preserve">9.64407920837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7637882232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7413444519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.95083427429199</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63659858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83860874176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.816162109375</t>
+    <t xml:space="preserve">9.63659954071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83860778808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81616401672363</t>
   </si>
   <si>
     <t xml:space="preserve">9.94335269927979</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">10.0406169891357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99572467803955</t>
+    <t xml:space="preserve">9.99572563171387</t>
   </si>
   <si>
     <t xml:space="preserve">10.0106887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96579837799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0630598068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77127170562744</t>
+    <t xml:space="preserve">9.96579742431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0630617141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77127075195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.89846134185791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86105537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29243183135986</t>
+    <t xml:space="preserve">9.86105251312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29243278503418</t>
   </si>
   <si>
     <t xml:space="preserve">10.2800359725952</t>
@@ -578,34 +578,34 @@
     <t xml:space="preserve">10.6765737533569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.616717338562</t>
+    <t xml:space="preserve">10.6167182922363</t>
   </si>
   <si>
     <t xml:space="preserve">10.8112440109253</t>
   </si>
   <si>
-    <t xml:space="preserve">10.938437461853</t>
+    <t xml:space="preserve">10.9384365081787</t>
   </si>
   <si>
     <t xml:space="preserve">10.9309549331665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9159908294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7214622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1216306686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8045167922974</t>
+    <t xml:space="preserve">10.9159917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7214632034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1216297149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.804518699646</t>
   </si>
   <si>
     <t xml:space="preserve">11.03102684021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0687799453735</t>
+    <t xml:space="preserve">11.0687789916992</t>
   </si>
   <si>
     <t xml:space="preserve">10.8347187042236</t>
@@ -617,31 +617,31 @@
     <t xml:space="preserve">11.3783416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8464622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7407560348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0352191925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1937770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0805225372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2239789962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.556191444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3749847412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2919330596924</t>
+    <t xml:space="preserve">11.8464641571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.740758895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0352210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1937789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0805244445801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2239799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5561923980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3749837875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2919321060181</t>
   </si>
   <si>
     <t xml:space="preserve">12.4202871322632</t>
@@ -650,10 +650,10 @@
     <t xml:space="preserve">12.314582824707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3674335479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5410928726196</t>
+    <t xml:space="preserve">12.3674354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.541090965271</t>
   </si>
   <si>
     <t xml:space="preserve">12.4504880905151</t>
@@ -662,100 +662,100 @@
     <t xml:space="preserve">12.5939435958862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8280038833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9790086746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0016641616821</t>
+    <t xml:space="preserve">12.8280067443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9790143966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0016622543335</t>
   </si>
   <si>
     <t xml:space="preserve">12.8129034042358</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0243148803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714612960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9488067626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8808584213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8657550811768</t>
+    <t xml:space="preserve">13.0243167877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9488086700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8808555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8657579421997</t>
   </si>
   <si>
     <t xml:space="preserve">12.7751531600952</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6769981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8204545974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7600507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.533540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7676029205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8582077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6996488571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6618976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9865598678589</t>
+    <t xml:space="preserve">12.6770000457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8204555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7600498199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5335426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7676010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.858208656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.699649810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6618967056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9865617752075</t>
   </si>
   <si>
     <t xml:space="preserve">13.0092124938965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8506555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2164278030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2088785171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1258230209351</t>
+    <t xml:space="preserve">12.8506565093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2164287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2088775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1258239746094</t>
   </si>
   <si>
     <t xml:space="preserve">12.2843818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1182737350464</t>
+    <t xml:space="preserve">12.1182727813721</t>
   </si>
   <si>
     <t xml:space="preserve">12.1484756469727</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8766632080078</t>
+    <t xml:space="preserve">11.8766651153564</t>
   </si>
   <si>
     <t xml:space="preserve">12.0729713439941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.156023979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2541790008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9748163223267</t>
+    <t xml:space="preserve">12.15602684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2541799545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9748182296753</t>
   </si>
   <si>
     <t xml:space="preserve">11.8540134429932</t>
@@ -764,52 +764,52 @@
     <t xml:space="preserve">12.1862268447876</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2390785217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7860593795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7256555557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9068632125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6652555465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5142478942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5444498062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4613971710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0989799499512</t>
+    <t xml:space="preserve">12.2390775680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7860584259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7256574630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9068651199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6652545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5142488479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5444488525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4613952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0989809036255</t>
   </si>
   <si>
     <t xml:space="preserve">11.1140804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1593809127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0763301849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3330411911011</t>
+    <t xml:space="preserve">11.1593828201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0763273239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3330383300781</t>
   </si>
   <si>
     <t xml:space="preserve">11.4085426330566</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4991483688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2952890396118</t>
+    <t xml:space="preserve">11.4991464614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2952899932861</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442832946777</t>
@@ -818,190 +818,190 @@
     <t xml:space="preserve">11.1669330596924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2424364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9932765960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8389110565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7634086608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.133373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0427713394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2013263702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1786766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9370651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3858909606934</t>
+    <t xml:space="preserve">11.2424373626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9932746887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8389120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.763409614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1333751678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0427722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2013273239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1786756515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.937066078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.385892868042</t>
   </si>
   <si>
     <t xml:space="preserve">11.4840478897095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2801866531372</t>
+    <t xml:space="preserve">11.2801876068115</t>
   </si>
   <si>
     <t xml:space="preserve">11.3481397628784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3556909561157</t>
+    <t xml:space="preserve">11.35569190979</t>
   </si>
   <si>
     <t xml:space="preserve">11.3405904769897</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5066976547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8724718093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8573703765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9026708602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7894163131714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4949531555176</t>
+    <t xml:space="preserve">11.5066986083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8724699020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8573694229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9026727676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7894172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949541091919</t>
   </si>
   <si>
     <t xml:space="preserve">10.653510093689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6459608078003</t>
+    <t xml:space="preserve">10.6459627151489</t>
   </si>
   <si>
     <t xml:space="preserve">10.6610612869263</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8271675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8800201416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7441148757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9781742095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7139129638672</t>
+    <t xml:space="preserve">10.8271684646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8800220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7441139221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.978175163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7139139175415</t>
   </si>
   <si>
     <t xml:space="preserve">10.8951206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0183162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721202850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0260143280029</t>
+    <t xml:space="preserve">11.0183181762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721174240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0260162353516</t>
   </si>
   <si>
     <t xml:space="preserve">10.9259195327759</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7642250061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6410312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6025323867798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3561401367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4793348312378</t>
+    <t xml:space="preserve">10.7642259597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6410303115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6025314331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3561372756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4793367385864</t>
   </si>
   <si>
     <t xml:space="preserve">10.4408359527588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4177379608154</t>
+    <t xml:space="preserve">10.4177370071411</t>
   </si>
   <si>
     <t xml:space="preserve">10.2406425476074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4023389816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7873249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4947328567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5409345626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3176393508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3715391159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2791423797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2868423461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3330402374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5101346969604</t>
+    <t xml:space="preserve">10.4023370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7873239517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4947338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5409317016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3176412582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3715372085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2791414260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2868394851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3330421447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5101327896118</t>
   </si>
   <si>
     <t xml:space="preserve">10.8335218429565</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8566236495972</t>
+    <t xml:space="preserve">10.8566226959229</t>
   </si>
   <si>
     <t xml:space="preserve">10.7103261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6179313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3407392501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4716367721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7796239852905</t>
+    <t xml:space="preserve">10.6179294586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3407411575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4716358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7796249389648</t>
   </si>
   <si>
     <t xml:space="preserve">10.9105195999146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0106172561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9413185119629</t>
+    <t xml:space="preserve">11.0106182098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9413223266602</t>
   </si>
   <si>
     <t xml:space="preserve">10.7565269470215</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">10.5255336761475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6256303787231</t>
+    <t xml:space="preserve">10.6256294250488</t>
   </si>
   <si>
     <t xml:space="preserve">10.3099403381348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.094349861145</t>
+    <t xml:space="preserve">10.0943489074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.99425220489502</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">9.34747505187988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20887851715088</t>
+    <t xml:space="preserve">9.2088794708252</t>
   </si>
   <si>
     <t xml:space="preserve">9.29357719421387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16268157958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22427845001221</t>
+    <t xml:space="preserve">9.16268062591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22428035736084</t>
   </si>
   <si>
     <t xml:space="preserve">8.9778881072998</t>
@@ -1046,40 +1046,40 @@
     <t xml:space="preserve">9.00868511199951</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96248817443848</t>
+    <t xml:space="preserve">8.96248722076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.92399024963379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8777904510498</t>
+    <t xml:space="preserve">8.87779140472412</t>
   </si>
   <si>
     <t xml:space="preserve">8.80079460144043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85469245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82389163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78539276123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72379684448242</t>
+    <t xml:space="preserve">8.85469055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82389259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7853946685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72379493713379</t>
   </si>
   <si>
     <t xml:space="preserve">8.63909912109375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52360439300537</t>
+    <t xml:space="preserve">8.52360343933105</t>
   </si>
   <si>
     <t xml:space="preserve">8.62370014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6467981338501</t>
+    <t xml:space="preserve">8.64680004119873</t>
   </si>
   <si>
     <t xml:space="preserve">8.60830116271973</t>
@@ -1088,160 +1088,160 @@
     <t xml:space="preserve">8.74689483642578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03178596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11648464202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13188171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93169021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15498352050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37827301025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30127811431885</t>
+    <t xml:space="preserve">9.0317850112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11648178100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1318826675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93168830871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1549825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37827491760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30127716064453</t>
   </si>
   <si>
     <t xml:space="preserve">9.32437515258789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33207702636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27817916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26277828216553</t>
+    <t xml:space="preserve">9.33207416534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27817630767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26277732849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.2473783493042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23967933654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20118141174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10878467559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87009239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84699249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95478820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73919677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63139915466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65449810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70839595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79309272766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00098609924316</t>
+    <t xml:space="preserve">9.2396764755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20118045806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1087818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87009143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84699153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95478916168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73919582366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6314001083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65449905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70839691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79309463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0009880065918</t>
   </si>
   <si>
     <t xml:space="preserve">9.04718589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.055850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1328477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1020469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0173511505127</t>
+    <t xml:space="preserve">10.0558500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1328468322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1020479202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0173501968384</t>
   </si>
   <si>
     <t xml:space="preserve">9.940354347229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82485866546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70166206359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45527076721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30897617340088</t>
+    <t xml:space="preserve">9.82485771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70166397094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4552698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30897521972656</t>
   </si>
   <si>
     <t xml:space="preserve">9.33977508544922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41760635375977</t>
+    <t xml:space="preserve">9.4176082611084</t>
   </si>
   <si>
     <t xml:space="preserve">9.72893238067627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6744499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44095611572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43317413330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5032205581665</t>
+    <t xml:space="preserve">9.67444896697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44095516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43317317962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50322246551514</t>
   </si>
   <si>
     <t xml:space="preserve">9.69779968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91572761535645</t>
+    <t xml:space="preserve">9.91572952270508</t>
   </si>
   <si>
     <t xml:space="preserve">9.80676364898682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6433162689209</t>
+    <t xml:space="preserve">9.64331912994385</t>
   </si>
   <si>
     <t xml:space="preserve">9.76784801483154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86124610900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.13365650177</t>
+    <t xml:space="preserve">9.86124515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1336545944214</t>
   </si>
   <si>
     <t xml:space="preserve">10.4371976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1881380081177</t>
+    <t xml:space="preserve">10.1881370544434</t>
   </si>
   <si>
     <t xml:space="preserve">10.048041343689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95464324951172</t>
+    <t xml:space="preserve">9.9546422958374</t>
   </si>
   <si>
     <t xml:space="preserve">10.1492223739624</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">10.0324754714966</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1570062637329</t>
+    <t xml:space="preserve">10.1570072174072</t>
   </si>
   <si>
     <t xml:space="preserve">10.3126668930054</t>
@@ -1259,19 +1259,19 @@
     <t xml:space="preserve">10.3904991149902</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3437986373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426204681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4294137954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5928611755371</t>
+    <t xml:space="preserve">10.3438014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.242618560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4294128417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6162118911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5928630828857</t>
   </si>
   <si>
     <t xml:space="preserve">10.6862592697144</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">10.6784772872925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9508848190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0520677566528</t>
+    <t xml:space="preserve">10.9508857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0520668029785</t>
   </si>
   <si>
     <t xml:space="preserve">11.114333152771</t>
@@ -1295,34 +1295,34 @@
     <t xml:space="preserve">10.8341388702393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9975843429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0832004547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2933435440063</t>
+    <t xml:space="preserve">10.9975852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0831985473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2933444976807</t>
   </si>
   <si>
     <t xml:space="preserve">11.3011274337769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1843786239624</t>
+    <t xml:space="preserve">11.1843814849854</t>
   </si>
   <si>
     <t xml:space="preserve">11.2544279098511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3166933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1610298156738</t>
+    <t xml:space="preserve">11.3166952133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1610317230225</t>
   </si>
   <si>
     <t xml:space="preserve">10.9586687088013</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9158592224121</t>
+    <t xml:space="preserve">10.9158620834351</t>
   </si>
   <si>
     <t xml:space="preserve">10.7018260955811</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">10.5850791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3048830032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4566555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0519332885742</t>
+    <t xml:space="preserve">10.3048858642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.456657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0519342422485</t>
   </si>
   <si>
     <t xml:space="preserve">9.99355792999268</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">9.90016174316406</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0636072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1180896759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.262077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5734024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667995452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5461616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8730554580688</t>
+    <t xml:space="preserve">10.0636081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.118088722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2620782852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5734033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668014526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5461626052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8730535507202</t>
   </si>
   <si>
     <t xml:space="preserve">11.3478260040283</t>
@@ -1376,16 +1376,16 @@
     <t xml:space="preserve">10.9469938278198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0909843444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1493558883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209341049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3050193786621</t>
+    <t xml:space="preserve">11.0909833908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1493549346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0209350585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3050184249878</t>
   </si>
   <si>
     <t xml:space="preserve">11.7175254821777</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">11.5462961196899</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4645738601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1999473571777</t>
+    <t xml:space="preserve">11.4645719528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1999483108521</t>
   </si>
   <si>
     <t xml:space="preserve">11.1026573181152</t>
@@ -1406,40 +1406,40 @@
     <t xml:space="preserve">11.277777671814</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1376810073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3595008850098</t>
+    <t xml:space="preserve">11.1376829147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3595018386841</t>
   </si>
   <si>
     <t xml:space="preserve">11.7642250061035</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0442838668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5967512130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6239938735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7640924453735</t>
+    <t xml:space="preserve">11.044282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.596752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6239919662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7640914916992</t>
   </si>
   <si>
     <t xml:space="preserve">10.6473445892334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8574867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8964033126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8263549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3244771957397</t>
+    <t xml:space="preserve">10.8574886322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8964042663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8263559341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3244791030884</t>
   </si>
   <si>
     <t xml:space="preserve">11.0987663269043</t>
@@ -1451,94 +1451,94 @@
     <t xml:space="preserve">11.4451160430908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6435842514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6708250045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.59299659729</t>
+    <t xml:space="preserve">11.6435852050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6708288192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5929975509644</t>
   </si>
   <si>
     <t xml:space="preserve">11.5813217163086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8654050827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9004316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0716590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1611661911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8926448822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9393463134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8381662368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183576583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5425395965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5308647155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5581064224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8344068527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542154312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7604694366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.663179397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7059860229492</t>
+    <t xml:space="preserve">11.795355796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8654069900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9004287719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0716581344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1611652374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8926467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9393444061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8381643295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183567047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5425386428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5308637619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5581045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8344078063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7604665756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6631784439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7059850692749</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437196731567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.702094078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355878829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.359769821167</t>
+    <t xml:space="preserve">12.7020931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355888366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3597688674927</t>
   </si>
   <si>
     <t xml:space="preserve">13.3052864074707</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4556303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4635438919067</t>
+    <t xml:space="preserve">13.4556283950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4635410308838</t>
   </si>
   <si>
     <t xml:space="preserve">13.1549453735352</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8661317825317</t>
+    <t xml:space="preserve">12.8661308288574</t>
   </si>
   <si>
     <t xml:space="preserve">12.5496206283569</t>
@@ -1547,100 +1547,100 @@
     <t xml:space="preserve">12.419059753418</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4863176345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5535764694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.146071434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2964134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0392484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9996843338013</t>
+    <t xml:space="preserve">12.4863166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5535774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1460704803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2964115142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.039249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.999683380127</t>
   </si>
   <si>
     <t xml:space="preserve">12.3478441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.312237739563</t>
+    <t xml:space="preserve">12.3122396469116</t>
   </si>
   <si>
     <t xml:space="preserve">12.3953218460083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4230165481567</t>
+    <t xml:space="preserve">12.4230175018311</t>
   </si>
   <si>
     <t xml:space="preserve">12.2726736068726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.478404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9007749557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205551147461</t>
+    <t xml:space="preserve">12.4784059524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9007759094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205570220947</t>
   </si>
   <si>
     <t xml:space="preserve">11.7979078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8374710083008</t>
+    <t xml:space="preserve">11.8374719619751</t>
   </si>
   <si>
     <t xml:space="preserve">12.4111461639404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8809938430786</t>
+    <t xml:space="preserve">11.88099193573</t>
   </si>
   <si>
     <t xml:space="preserve">11.9284687042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5377521514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4665384292603</t>
+    <t xml:space="preserve">12.5377511978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4665355682373</t>
   </si>
   <si>
     <t xml:space="preserve">12.4348850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3755397796631</t>
+    <t xml:space="preserve">12.3755388259888</t>
   </si>
   <si>
     <t xml:space="preserve">12.5733594894409</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6089649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6050081253052</t>
+    <t xml:space="preserve">12.6089668273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6050100326538</t>
   </si>
   <si>
     <t xml:space="preserve">12.6683111190796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.992733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520801544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6762247085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7355690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6010522842407</t>
+    <t xml:space="preserve">12.9927320480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520792007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6762228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7355680465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.601053237915</t>
   </si>
   <si>
     <t xml:space="preserve">12.5456638336182</t>
@@ -1649,13 +1649,13 @@
     <t xml:space="preserve">12.5575332641602</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4546661376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4586229324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2489366531372</t>
+    <t xml:space="preserve">12.4546680450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4586219787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2489356994629</t>
   </si>
   <si>
     <t xml:space="preserve">12.3201503753662</t>
@@ -1664,58 +1664,58 @@
     <t xml:space="preserve">12.3676271438599</t>
   </si>
   <si>
-    <t xml:space="preserve">11.596134185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7623014450073</t>
+    <t xml:space="preserve">11.5961332321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7623023986816</t>
   </si>
   <si>
     <t xml:space="preserve">11.7702150344849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9759464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9324264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0273780822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.82164478302</t>
+    <t xml:space="preserve">11.9759454727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9324254989624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0273771286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.821647644043</t>
   </si>
   <si>
     <t xml:space="preserve">11.5328311920166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4418354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5170068740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6159152984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5921783447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.714825630188</t>
+    <t xml:space="preserve">11.4418344497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5170078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6159162521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5921773910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7148237228394</t>
   </si>
   <si>
     <t xml:space="preserve">12.0867223739624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8889055252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8928623199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2281913757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4339208602905</t>
+    <t xml:space="preserve">11.8889064788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8928632736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2281904220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4339218139648</t>
   </si>
   <si>
     <t xml:space="preserve">11.4062280654907</t>
@@ -1727,70 +1727,70 @@
     <t xml:space="preserve">10.9947652816772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9037675857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7257318496704</t>
+    <t xml:space="preserve">10.9037704467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7257328033447</t>
   </si>
   <si>
     <t xml:space="preserve">10.6228666305542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6901245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9433336257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9314622879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9354200363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9987201690674</t>
+    <t xml:space="preserve">10.6901235580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9433326721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9314632415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9354181289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.998722076416</t>
   </si>
   <si>
     <t xml:space="preserve">11.1451072692871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1530208587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0857620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066337585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.117413520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7306499481201</t>
+    <t xml:space="preserve">11.1530199050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0857629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066328048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1174125671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7306509017944</t>
   </si>
   <si>
     <t xml:space="preserve">11.6396551132202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5842657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4180974960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7266941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9482498168945</t>
+    <t xml:space="preserve">11.584264755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4180965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7266931533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9482507705688</t>
   </si>
   <si>
     <t xml:space="preserve">11.6277847290039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.572395324707</t>
+    <t xml:space="preserve">11.5723962783813</t>
   </si>
   <si>
     <t xml:space="preserve">11.9601202011108</t>
@@ -1799,28 +1799,28 @@
     <t xml:space="preserve">11.6238269805908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1332378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1411514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1886291503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3112754821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2400617599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0936737060547</t>
+    <t xml:space="preserve">11.1332387924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.141149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886262893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3112745285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2400579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.093674659729</t>
   </si>
   <si>
     <t xml:space="preserve">11.0818042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8325538635254</t>
+    <t xml:space="preserve">10.8325519561768</t>
   </si>
   <si>
     <t xml:space="preserve">10.4052658081055</t>
@@ -1832,31 +1832,31 @@
     <t xml:space="preserve">10.2628355026245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1718378067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2034893035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0927114486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3933944702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5635185241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6268215179443</t>
+    <t xml:space="preserve">10.1718397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2034902572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0927133560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3933963775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5635194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6268224716187</t>
   </si>
   <si>
     <t xml:space="preserve">10.6307783126831</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6189098358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.519998550415</t>
+    <t xml:space="preserve">10.6189088821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5199995040894</t>
   </si>
   <si>
     <t xml:space="preserve">10.4843912124634</t>
@@ -1865,7 +1865,7 @@
     <t xml:space="preserve">10.2430534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1599683761597</t>
+    <t xml:space="preserve">10.1599702835083</t>
   </si>
   <si>
     <t xml:space="preserve">9.85137271881104</t>
@@ -1874,13 +1874,13 @@
     <t xml:space="preserve">9.75641822814941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8751106262207</t>
+    <t xml:space="preserve">9.87510967254639</t>
   </si>
   <si>
     <t xml:space="preserve">9.7801570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68019676208496</t>
+    <t xml:space="preserve">9.68019771575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.40830326080322</t>
@@ -1898,46 +1898,46 @@
     <t xml:space="preserve">9.56024265289307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38031673431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71657562255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66059875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49666309356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78854751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67259502410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50865745544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22876834869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24875831604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9968581199646</t>
+    <t xml:space="preserve">9.38031482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71657466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66059684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49666118621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78854465484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67259120941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50865650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22876644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24876022338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99685716629028</t>
   </si>
   <si>
     <t xml:space="preserve">8.10881519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20077705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18078517913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89130020141602</t>
+    <t xml:space="preserve">8.20077896118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1807861328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89129972457886</t>
   </si>
   <si>
     <t xml:space="preserve">7.71217012405396</t>
@@ -1946,67 +1946,67 @@
     <t xml:space="preserve">7.71376848220825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38110065460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39389514923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34271574020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54903364181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61140871047974</t>
+    <t xml:space="preserve">7.38109922409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39389610290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3427152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54903316497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61140966415405</t>
   </si>
   <si>
     <t xml:space="preserve">7.59861469268799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88490104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01285171508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05683422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29673957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31673336029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24076080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16879177093506</t>
+    <t xml:space="preserve">7.88490152359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01285266876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05683517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2967414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31673431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24076366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16879081726074</t>
   </si>
   <si>
     <t xml:space="preserve">8.22476768493652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52065181732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45267963409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3207311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39670085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53264713287354</t>
+    <t xml:space="preserve">8.52065086364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45267772674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32073020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39670181274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53264808654785</t>
   </si>
   <si>
     <t xml:space="preserve">8.8245325088501</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58862495422363</t>
+    <t xml:space="preserve">8.58862590789795</t>
   </si>
   <si>
     <t xml:space="preserve">8.70058155059814</t>
@@ -2015,100 +2015,100 @@
     <t xml:space="preserve">8.7685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75655937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93249130249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98847007751465</t>
+    <t xml:space="preserve">8.75655841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93249034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98846626281738</t>
   </si>
   <si>
     <t xml:space="preserve">8.76455593109131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56463432312012</t>
+    <t xml:space="preserve">8.56463527679443</t>
   </si>
   <si>
     <t xml:space="preserve">8.7445650100708</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95248126983643</t>
+    <t xml:space="preserve">8.95248317718506</t>
   </si>
   <si>
     <t xml:space="preserve">9.20838260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22037887573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43629169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49227142333984</t>
+    <t xml:space="preserve">9.22037792205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43629360198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49226951599121</t>
   </si>
   <si>
     <t xml:space="preserve">9.55224609375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59622955322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7561674118042</t>
+    <t xml:space="preserve">9.59623146057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75616645812988</t>
   </si>
   <si>
     <t xml:space="preserve">9.63221549987793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61622142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51626110076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51226425170898</t>
+    <t xml:space="preserve">9.6162223815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51626014709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51226329803467</t>
   </si>
   <si>
     <t xml:space="preserve">9.3323335647583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39231014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36432075500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48427200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25236511230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11242008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42029857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84413242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8961124420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84813117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86812305450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98407649993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0360584259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3079509735107</t>
+    <t xml:space="preserve">9.39230823516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3643217086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48427391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25236701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11241912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42030048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84413433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89611148834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84813213348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86812400817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98408031463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.036057472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3079500198364</t>
   </si>
   <si>
     <t xml:space="preserve">10.2039909362793</t>
@@ -2126,22 +2126,22 @@
     <t xml:space="preserve">10.2759637832642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.172004699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1440153121948</t>
+    <t xml:space="preserve">10.1720027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1440134048462</t>
   </si>
   <si>
     <t xml:space="preserve">9.95608806610107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2559680938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3199462890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0440549850464</t>
+    <t xml:space="preserve">10.2559700012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3199453353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0440540313721</t>
   </si>
   <si>
     <t xml:space="preserve">9.93609428405762</t>
@@ -2150,91 +2150,91 @@
     <t xml:space="preserve">10.0040702819824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0560493469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3959159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5278635025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4279041290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7917613983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5598516464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3359394073486</t>
+    <t xml:space="preserve">10.0560483932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3959150314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5278644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.427903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7917594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.559850692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3359384536743</t>
   </si>
   <si>
     <t xml:space="preserve">9.92809963226318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90011024475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74017333984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60422611236572</t>
+    <t xml:space="preserve">9.90011119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74017429351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60422801971436</t>
   </si>
   <si>
     <t xml:space="preserve">9.44029235839844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60822582244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4123010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34033012390137</t>
+    <t xml:space="preserve">9.60822486877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41230392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34032917022705</t>
   </si>
   <si>
     <t xml:space="preserve">9.29234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54025268554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61222362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96408653259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0160636901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0242443084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1755704879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8565616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4393949508667</t>
+    <t xml:space="preserve">9.54025077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61222457885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96408462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0160655975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.024245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1755685806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85656070709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43939399719238</t>
   </si>
   <si>
     <t xml:space="preserve">9.32487869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16128540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15310478210449</t>
+    <t xml:space="preserve">9.16128444671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15310573577881</t>
   </si>
   <si>
     <t xml:space="preserve">9.0140495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98542022705078</t>
+    <t xml:space="preserve">8.9854211807251</t>
   </si>
   <si>
     <t xml:space="preserve">8.62960338592529</t>
@@ -2246,43 +2246,43 @@
     <t xml:space="preserve">9.08766651153564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78910636901855</t>
+    <t xml:space="preserve">8.78910732269287</t>
   </si>
   <si>
     <t xml:space="preserve">8.79728603363037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78092765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06312847137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19809436798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94452285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8340950012207</t>
+    <t xml:space="preserve">8.78092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0631275177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19809246063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94452095031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83409690856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.87908363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05085849761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29624843597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39440727233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25126075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14901638031006</t>
+    <t xml:space="preserve">9.05085754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29624938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39440536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25126266479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14901351928711</t>
   </si>
   <si>
     <t xml:space="preserve">9.42303562164307</t>
@@ -2291,46 +2291,46 @@
     <t xml:space="preserve">9.38213634490967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41485500335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65206718444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42712593078613</t>
+    <t xml:space="preserve">9.41485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65206909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42712497711182</t>
   </si>
   <si>
     <t xml:space="preserve">9.44757461547852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54573154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54164218902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75431442260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66024875640869</t>
+    <t xml:space="preserve">9.54573059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54164123535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75431346893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66024780273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.80748176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98743724822998</t>
+    <t xml:space="preserve">9.98743629455566</t>
   </si>
   <si>
     <t xml:space="preserve">9.94244861602783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83202171325684</t>
+    <t xml:space="preserve">9.83202362060547</t>
   </si>
   <si>
     <t xml:space="preserve">9.82793140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4516658782959</t>
+    <t xml:space="preserve">9.45166492462158</t>
   </si>
   <si>
     <t xml:space="preserve">9.28806972503662</t>
@@ -2339,91 +2339,91 @@
     <t xml:space="preserve">9.12038516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24308300018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31260776519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59072017669678</t>
+    <t xml:space="preserve">9.24308204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31260871887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59071922302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.5089225769043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26762104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93225193023682</t>
+    <t xml:space="preserve">9.26762008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93225288391113</t>
   </si>
   <si>
     <t xml:space="preserve">8.71549034118652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56416511535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36376190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29423522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44555854797363</t>
+    <t xml:space="preserve">8.56416606903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36376285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29423427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44556045532227</t>
   </si>
   <si>
     <t xml:space="preserve">8.27787685394287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00958061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14209270477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71838235855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75764513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05211353302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88852119445801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98340606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08810615539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96377372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07011032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12409591674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21652889251709</t>
+    <t xml:space="preserve">8.0095796585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14209365844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71838188171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75764560699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05211639404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88851976394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98340559005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08810520172119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96377468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07011127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12409687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21652603149414</t>
   </si>
   <si>
     <t xml:space="preserve">8.16335868835449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10937213897705</t>
+    <t xml:space="preserve">8.10937309265137</t>
   </si>
   <si>
     <t xml:space="preserve">8.0652027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86070871353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00467300415039</t>
+    <t xml:space="preserve">7.86071014404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00467205047607</t>
   </si>
   <si>
     <t xml:space="preserve">8.21243762969971</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">8.41283988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51099681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43737888336182</t>
+    <t xml:space="preserve">8.51099586486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43737983703613</t>
   </si>
   <si>
     <t xml:space="preserve">8.31468391418457</t>
@@ -2447,10 +2447,10 @@
     <t xml:space="preserve">8.37194156646729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60506343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44146823883057</t>
+    <t xml:space="preserve">8.60506439208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44146919250488</t>
   </si>
   <si>
     <t xml:space="preserve">8.31877326965332</t>
@@ -2459,121 +2459,121 @@
     <t xml:space="preserve">8.22061729431152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20016860961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97195386886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85743808746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85252952575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72983312606812</t>
+    <t xml:space="preserve">8.20016574859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97195434570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85743618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85253047943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72983264923096</t>
   </si>
   <si>
     <t xml:space="preserve">8.00794410705566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9621376991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81326770782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4877142906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56296730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5482439994812</t>
+    <t xml:space="preserve">7.96213912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81326723098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48771333694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5629677772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54824352264404</t>
   </si>
   <si>
     <t xml:space="preserve">7.63658618927002</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50898265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54333686828613</t>
+    <t xml:space="preserve">7.5089807510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54333591461182</t>
   </si>
   <si>
     <t xml:space="preserve">7.61531734466553</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88034009933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6725754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77400350570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74292039871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64803695678711</t>
+    <t xml:space="preserve">7.88034105300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67257595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77400398254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74292182922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64803743362427</t>
   </si>
   <si>
     <t xml:space="preserve">7.60713768005371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66275882720947</t>
+    <t xml:space="preserve">7.66276073455811</t>
   </si>
   <si>
     <t xml:space="preserve">7.68239164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70202445983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61859035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69220876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80999612808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88524866104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6578516960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40591621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03739261627197</t>
+    <t xml:space="preserve">7.70202493667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61859083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69220733642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80999517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88525056838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65785312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40591716766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03739166259766</t>
   </si>
   <si>
     <t xml:space="preserve">8.17644691467285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32286262512207</t>
+    <t xml:space="preserve">8.32286357879639</t>
   </si>
   <si>
     <t xml:space="preserve">8.18380737304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19607734680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23697566986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10446643829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10282802581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09955883026123</t>
+    <t xml:space="preserve">8.19607925415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23697662353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10446548461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10282897949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0995569229126</t>
   </si>
   <si>
     <t xml:space="preserve">8.02993297576904</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">7.95865106582642</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08961009979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04153537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16918087005615</t>
+    <t xml:space="preserve">8.0896110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04153823852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16917991638184</t>
   </si>
   <si>
     <t xml:space="preserve">8.15094566345215</t>
@@ -2603,16 +2603,16 @@
     <t xml:space="preserve">8.09955787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85587358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80116939544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96694135665894</t>
+    <t xml:space="preserve">8.00009441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85587406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80116844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96693992614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.03987884521484</t>
@@ -2627,28 +2627,28 @@
     <t xml:space="preserve">8.26864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29682350158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53304672241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44187259674072</t>
+    <t xml:space="preserve">8.29682445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53304767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44187355041504</t>
   </si>
   <si>
     <t xml:space="preserve">8.46259498596191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40872001647949</t>
+    <t xml:space="preserve">8.40871906280518</t>
   </si>
   <si>
     <t xml:space="preserve">8.39214324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37970924377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42944049835205</t>
+    <t xml:space="preserve">8.37971019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42944145202637</t>
   </si>
   <si>
     <t xml:space="preserve">8.49574851989746</t>
@@ -2660,139 +2660,139 @@
     <t xml:space="preserve">8.32997798919678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37142181396484</t>
+    <t xml:space="preserve">8.37142086029053</t>
   </si>
   <si>
     <t xml:space="preserve">8.48331546783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7112512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69881820678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68224048614502</t>
+    <t xml:space="preserve">8.71125030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69881916046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68224239349365</t>
   </si>
   <si>
     <t xml:space="preserve">8.60764503479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60350036621094</t>
+    <t xml:space="preserve">8.60349941253662</t>
   </si>
   <si>
     <t xml:space="preserve">8.45016193389893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40043163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45430755615234</t>
+    <t xml:space="preserve">8.40043067932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45430564880371</t>
   </si>
   <si>
     <t xml:space="preserve">8.52890300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50403785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47088432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41700744628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37556552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05811309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18741416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28687858581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88074207305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73154592514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64203023910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90891981124878</t>
+    <t xml:space="preserve">8.50403690338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4708833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41700839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37556457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05811500549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18741703033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28687953948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88073825836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73154497146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64202928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282688140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90892124176025</t>
   </si>
   <si>
     <t xml:space="preserve">7.93212795257568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78790807723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83598232269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90063238143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00672435760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98186111450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8044867515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8409538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13105392456055</t>
+    <t xml:space="preserve">7.78790903091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83598136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90063333511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0067253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98186016082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80448627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84095430374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13105201721191</t>
   </si>
   <si>
     <t xml:space="preserve">7.76967239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37679576873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27733373641968</t>
+    <t xml:space="preserve">7.37679767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27733469009399</t>
   </si>
   <si>
     <t xml:space="preserve">7.29391098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9756326675415</t>
+    <t xml:space="preserve">6.97563219070435</t>
   </si>
   <si>
     <t xml:space="preserve">6.77007579803467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71868705749512</t>
+    <t xml:space="preserve">6.71868753433228</t>
   </si>
   <si>
     <t xml:space="preserve">6.75018358230591</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57612466812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45511150360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08378458023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7824854850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65815734863281</t>
+    <t xml:space="preserve">6.57612419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45511245727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08378601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78248500823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65815687179565</t>
   </si>
   <si>
     <t xml:space="preserve">4.56201028823853</t>
@@ -2801,37 +2801,37 @@
     <t xml:space="preserve">3.87903475761414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97766804695129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71989440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85085344314575</t>
+    <t xml:space="preserve">3.97766828536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71989488601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85085368156433</t>
   </si>
   <si>
     <t xml:space="preserve">3.9453432559967</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15918731689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32661581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26362228393555</t>
+    <t xml:space="preserve">4.15918636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32661533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26362371444702</t>
   </si>
   <si>
     <t xml:space="preserve">4.43436622619629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46088981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70788812637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61505651473999</t>
+    <t xml:space="preserve">4.46088933944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70788764953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61505794525146</t>
   </si>
   <si>
     <t xml:space="preserve">4.59019136428833</t>
@@ -2840,70 +2840,70 @@
     <t xml:space="preserve">4.62500333786011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54543352127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75430536270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78745889663696</t>
+    <t xml:space="preserve">4.54543256759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7543044090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78745794296265</t>
   </si>
   <si>
     <t xml:space="preserve">4.90681314468384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13226127624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01456499099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97809410095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91178703308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69131135940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77751159667969</t>
+    <t xml:space="preserve">5.13226079940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.014564037323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97809457778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91178560256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69131088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.777512550354</t>
   </si>
   <si>
     <t xml:space="preserve">4.80735063552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77917003631592</t>
+    <t xml:space="preserve">4.77916955947876</t>
   </si>
   <si>
     <t xml:space="preserve">4.54045963287354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68136405944824</t>
+    <t xml:space="preserve">4.6813645362854</t>
   </si>
   <si>
     <t xml:space="preserve">4.86702823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90515565872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686632156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99135589599609</t>
+    <t xml:space="preserve">4.90515613555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99135637283325</t>
   </si>
   <si>
     <t xml:space="preserve">5.28311252593994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29968976974487</t>
+    <t xml:space="preserve">5.29969024658203</t>
   </si>
   <si>
     <t xml:space="preserve">5.00627517700195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24664354324341</t>
+    <t xml:space="preserve">5.24664211273193</t>
   </si>
   <si>
     <t xml:space="preserve">5.04440307617188</t>
@@ -2915,43 +2915,43 @@
     <t xml:space="preserve">5.16375780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07092666625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98141002655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76425075531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79408836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15878486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69960021972656</t>
+    <t xml:space="preserve">5.07092571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98141050338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7642502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79408884048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15878438949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6995997428894</t>
   </si>
   <si>
     <t xml:space="preserve">4.85045099258423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61174058914185</t>
+    <t xml:space="preserve">4.61174154281616</t>
   </si>
   <si>
     <t xml:space="preserve">4.59847974777222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64158010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71451950073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72114992141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83718872070312</t>
+    <t xml:space="preserve">4.64157962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71451997756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72115039825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83718919754028</t>
   </si>
   <si>
     <t xml:space="preserve">4.63494920730591</t>
@@ -2966,37 +2966,37 @@
     <t xml:space="preserve">5.2980318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35273551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63288831710815</t>
+    <t xml:space="preserve">5.3527364730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63288879394531</t>
   </si>
   <si>
     <t xml:space="preserve">5.71577405929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61465358734131</t>
+    <t xml:space="preserve">5.61465406417847</t>
   </si>
   <si>
     <t xml:space="preserve">5.53508424758911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18365001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18862295150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18199253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13060331344604</t>
+    <t xml:space="preserve">5.18365049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18862342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18199157714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1306037902832</t>
   </si>
   <si>
     <t xml:space="preserve">5.12894630432129</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04108715057373</t>
+    <t xml:space="preserve">5.04108667373657</t>
   </si>
   <si>
     <t xml:space="preserve">5.14220762252808</t>
@@ -3005,37 +3005,37 @@
     <t xml:space="preserve">4.8239278793335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88692045211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76093482971191</t>
+    <t xml:space="preserve">4.88691997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76093530654907</t>
   </si>
   <si>
     <t xml:space="preserve">4.8139820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70623111724854</t>
+    <t xml:space="preserve">4.70623064041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.8521089553833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76259279251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93002033233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84547805786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76756477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5968222618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62168788909912</t>
+    <t xml:space="preserve">4.76259231567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93002128601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84547853469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76756572723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59682178497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62168836593628</t>
   </si>
   <si>
     <t xml:space="preserve">4.67804956436157</t>
@@ -3044,121 +3044,121 @@
     <t xml:space="preserve">4.75761938095093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76590824127197</t>
+    <t xml:space="preserve">4.76590728759766</t>
   </si>
   <si>
     <t xml:space="preserve">4.89355134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78414249420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70291519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66810274124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58024454116821</t>
+    <t xml:space="preserve">4.78414344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70291423797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66810321807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58024501800537</t>
   </si>
   <si>
     <t xml:space="preserve">4.4907283782959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27191162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19234132766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0879054069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28185749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29346179962158</t>
+    <t xml:space="preserve">4.27191019058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19234180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08790588378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28185701370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29346227645874</t>
   </si>
   <si>
     <t xml:space="preserve">4.48575592041016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21389102935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29014587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43602466583252</t>
+    <t xml:space="preserve">4.21389150619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29014539718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4360237121582</t>
   </si>
   <si>
     <t xml:space="preserve">4.41447401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32164239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27688360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23875665664673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19731426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10448265075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08624744415283</t>
+    <t xml:space="preserve">4.32164144515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27688407897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23875713348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19731521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10448360443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08624792098999</t>
   </si>
   <si>
     <t xml:space="preserve">4.22383832931519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17576503753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1334924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05806732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.082932472229</t>
+    <t xml:space="preserve">4.17576360702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13349294662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05806684494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08293199539185</t>
   </si>
   <si>
     <t xml:space="preserve">4.0779595375061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0000467300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9619197845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98927283287048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00087690353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9760103225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8392493724823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84422326087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82598853111267</t>
+    <t xml:space="preserve">4.00004720687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96192002296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98927211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00087642669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97601056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83924913406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8442223072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82598805427551</t>
   </si>
   <si>
     <t xml:space="preserve">3.77957248687744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74724674224854</t>
+    <t xml:space="preserve">3.74724721908569</t>
   </si>
   <si>
     <t xml:space="preserve">3.80112218856812</t>
@@ -3167,97 +3167,97 @@
     <t xml:space="preserve">3.95943355560303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96274900436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85334062576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6005392074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56075549125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5309157371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45880532264709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39747071266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53754687309265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399382591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53174543380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44140005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52096962928772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5557816028595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6535861492157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58064723014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69005680084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66436195373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6030261516571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51350975036621</t>
+    <t xml:space="preserve">3.96274971961975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8533399105072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60053992271423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5607545375824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53091645240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45880579948425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39747047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53754711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42399430274963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53174519538879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44139981269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52097010612488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55578136444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65358662605286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58064794540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69005584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66436147689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60302710533142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51350998878479</t>
   </si>
   <si>
     <t xml:space="preserve">3.60717082023621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42730951309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55080890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62623405456543</t>
+    <t xml:space="preserve">3.4273099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5508086681366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62623453140259</t>
   </si>
   <si>
     <t xml:space="preserve">3.71077752113342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61877465248108</t>
+    <t xml:space="preserve">3.61877536773682</t>
   </si>
   <si>
     <t xml:space="preserve">3.63783836364746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67099213600159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57401609420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47455430030823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3701183795929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17285132408142</t>
+    <t xml:space="preserve">3.67099237442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57401657104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47455406188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37011861801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1728515625</t>
   </si>
   <si>
     <t xml:space="preserve">3.37509179115295</t>
@@ -3266,31 +3266,31 @@
     <t xml:space="preserve">3.55163764953613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63535189628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19399976730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17244958877563</t>
+    <t xml:space="preserve">3.63535165786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19399929046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17244863510132</t>
   </si>
   <si>
     <t xml:space="preserve">4.57029867172241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63660669326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64655303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67639207839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74601554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11402702331543</t>
+    <t xml:space="preserve">4.63660621643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64655351638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67639255523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74601602554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11402606964111</t>
   </si>
   <si>
     <t xml:space="preserve">5.21183109283447</t>
@@ -3299,37 +3299,37 @@
     <t xml:space="preserve">5.27316617965698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19359683990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18033504486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39324855804443</t>
+    <t xml:space="preserve">5.19359636306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18033456802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39324760437012</t>
   </si>
   <si>
     <t xml:space="preserve">5.73357486724854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67825078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60113191604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61957311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4368371963501</t>
+    <t xml:space="preserve">5.67825031280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6011323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61957359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43683671951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.52066087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54748487472534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58101367950439</t>
+    <t xml:space="preserve">5.54748392105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58101415634155</t>
   </si>
   <si>
     <t xml:space="preserve">5.80901622772217</t>
@@ -3338,16 +3338,16 @@
     <t xml:space="preserve">5.70339727401733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71178007125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71513366699219</t>
+    <t xml:space="preserve">5.7117805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71513319015503</t>
   </si>
   <si>
     <t xml:space="preserve">5.8023099899292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70004558563232</t>
+    <t xml:space="preserve">5.70004510879517</t>
   </si>
   <si>
     <t xml:space="preserve">5.62627935409546</t>
@@ -3359,28 +3359,28 @@
     <t xml:space="preserve">5.6665153503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72183990478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63801431655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4904842376709</t>
+    <t xml:space="preserve">5.72183895111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.638014793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49048471450806</t>
   </si>
   <si>
     <t xml:space="preserve">5.47539615631104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62795686721802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58772039413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51227807998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55251407623291</t>
+    <t xml:space="preserve">5.62795639038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58772087097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51227903366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55251455307007</t>
   </si>
   <si>
     <t xml:space="preserve">5.47874927520752</t>
@@ -3392,25 +3392,25 @@
     <t xml:space="preserve">5.97834157943726</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9699592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93642807006836</t>
+    <t xml:space="preserve">5.96995830535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93642902374268</t>
   </si>
   <si>
     <t xml:space="preserve">5.82913446426392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9967827796936</t>
+    <t xml:space="preserve">5.99678230285645</t>
   </si>
   <si>
     <t xml:space="preserve">5.9129581451416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96492862701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65813302993774</t>
+    <t xml:space="preserve">5.96492910385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65813207626343</t>
   </si>
   <si>
     <t xml:space="preserve">5.64304447174072</t>
@@ -3422,16 +3422,16 @@
     <t xml:space="preserve">5.27254104614258</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1786584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24739408493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33792495727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50054264068604</t>
+    <t xml:space="preserve">5.17865800857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24739503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33792400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50054311752319</t>
   </si>
   <si>
     <t xml:space="preserve">5.38989496231079</t>
@@ -3446,13 +3446,13 @@
     <t xml:space="preserve">5.69333839416504</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80734014511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92972373962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82410478591919</t>
+    <t xml:space="preserve">5.80733966827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92972326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82410430908203</t>
   </si>
   <si>
     <t xml:space="preserve">5.89451694488525</t>
@@ -3461,19 +3461,19 @@
     <t xml:space="preserve">5.90122270584106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95990037918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31196117401123</t>
+    <t xml:space="preserve">5.95989942550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31196165084839</t>
   </si>
   <si>
     <t xml:space="preserve">6.32202005386353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17951965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03534173965454</t>
+    <t xml:space="preserve">6.179518699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03534078598022</t>
   </si>
   <si>
     <t xml:space="preserve">6.06551790237427</t>
@@ -3485,43 +3485,43 @@
     <t xml:space="preserve">6.22813653945923</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44440317153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32958698272705</t>
+    <t xml:space="preserve">6.44440412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32958793640137</t>
   </si>
   <si>
     <t xml:space="preserve">7.24743938446045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41508769989014</t>
+    <t xml:space="preserve">7.41508722305298</t>
   </si>
   <si>
     <t xml:space="preserve">7.53579473495483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51902914047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78558969497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02700424194336</t>
+    <t xml:space="preserve">7.51903057098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78559064865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02700328826904</t>
   </si>
   <si>
     <t xml:space="preserve">8.14435768127441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00520992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11082935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30697536468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31200790405273</t>
+    <t xml:space="preserve">8.00521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1108283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30697727203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31200695037842</t>
   </si>
   <si>
     <t xml:space="preserve">8.10579967498779</t>
@@ -3533,67 +3533,67 @@
     <t xml:space="preserve">8.09741687774658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99682760238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81576776504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75038385391235</t>
+    <t xml:space="preserve">7.99682712554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81576728820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75038480758667</t>
   </si>
   <si>
     <t xml:space="preserve">7.61961841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90294551849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69170713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97168064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09574222564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05718231201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10076999664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10915279388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98173856735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77720785140991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69506168365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63973569869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62967824935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99850273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70679616928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68332433700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73864984512329</t>
+    <t xml:space="preserve">7.90294456481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6917085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01527118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09574127197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05718040466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10076904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10915088653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98174047470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77720880508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69506025314331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63973712921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62967729568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99850416183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70679664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68332529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73864889144897</t>
   </si>
   <si>
     <t xml:space="preserve">7.39496946334839</t>
@@ -3602,10 +3602,10 @@
     <t xml:space="preserve">7.47041130065918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.463707447052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4435887336731</t>
+    <t xml:space="preserve">7.46370553970337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44358921051025</t>
   </si>
   <si>
     <t xml:space="preserve">7.70008945465088</t>
@@ -3614,25 +3614,25 @@
     <t xml:space="preserve">7.539146900177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79229640960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26420545578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50897169113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57603073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63806056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98006343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12591648101807</t>
+    <t xml:space="preserve">7.79229593276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26420497894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50897073745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57603025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63806009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98006248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12591743469238</t>
   </si>
   <si>
     <t xml:space="preserve">8.20806407928467</t>
@@ -3641,46 +3641,46 @@
     <t xml:space="preserve">8.01359272003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28350734710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19632911682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21477031707764</t>
+    <t xml:space="preserve">8.2835054397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19633007049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21477127075195</t>
   </si>
   <si>
     <t xml:space="preserve">8.12759304046631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90462160110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85600328445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92976856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95869779586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80214405059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82596683502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04548263549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96039867401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93827676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15268611907959</t>
+    <t xml:space="preserve">7.90462064743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85600280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92976808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95869731903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80214357376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82596492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04548168182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96039915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9382758140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15268707275391</t>
   </si>
   <si>
     <t xml:space="preserve">8.2462797164917</t>
@@ -3689,91 +3689,91 @@
     <t xml:space="preserve">8.31604671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1918249130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20203399658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17140483856201</t>
+    <t xml:space="preserve">8.19182682037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20203685760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17140579223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.11354732513428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12545967102051</t>
+    <t xml:space="preserve">8.12546157836914</t>
   </si>
   <si>
     <t xml:space="preserve">8.2905216217041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14077472686768</t>
+    <t xml:space="preserve">8.14077568054199</t>
   </si>
   <si>
     <t xml:space="preserve">8.13056564331055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.948486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81575679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84468603134155</t>
+    <t xml:space="preserve">7.94848680496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81575632095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84468412399292</t>
   </si>
   <si>
     <t xml:space="preserve">7.92296171188354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97571277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02506256103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07100677490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80384540557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80554628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82086133956909</t>
+    <t xml:space="preserve">7.97571325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02506351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07100772857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80384492874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80554580688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82086229324341</t>
   </si>
   <si>
     <t xml:space="preserve">7.97060823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96550273895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02165985107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64388942718506</t>
+    <t xml:space="preserve">7.96550369262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02165794372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64388847351074</t>
   </si>
   <si>
     <t xml:space="preserve">7.52987670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42607402801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65920400619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63197660446167</t>
+    <t xml:space="preserve">7.42607355117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65920352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63197708129883</t>
   </si>
   <si>
     <t xml:space="preserve">7.46861696243286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59964466094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521234512329</t>
+    <t xml:space="preserve">7.59964418411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521377563477</t>
   </si>
   <si>
     <t xml:space="preserve">7.25420618057251</t>
@@ -3782,16 +3782,16 @@
     <t xml:space="preserve">7.00235891342163</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12317848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26271390914917</t>
+    <t xml:space="preserve">7.12317752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26271533966064</t>
   </si>
   <si>
     <t xml:space="preserve">7.18103504180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26441669464111</t>
+    <t xml:space="preserve">7.26441621780396</t>
   </si>
   <si>
     <t xml:space="preserve">7.47372198104858</t>
@@ -3800,25 +3800,25 @@
     <t xml:space="preserve">7.40735769271851</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47031831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46691465377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29674816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35800886154175</t>
+    <t xml:space="preserve">7.47031879425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46691417694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29674863815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35800790786743</t>
   </si>
   <si>
     <t xml:space="preserve">7.40565538406372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30865955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28313446044922</t>
+    <t xml:space="preserve">7.30866003036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28313493728638</t>
   </si>
   <si>
     <t xml:space="preserve">7.48222970962524</t>
@@ -3827,52 +3827,52 @@
     <t xml:space="preserve">7.44139003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4856333732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49584341049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30185270309448</t>
+    <t xml:space="preserve">7.48563385009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49584436416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30185317993164</t>
   </si>
   <si>
     <t xml:space="preserve">7.3341851234436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99385213851929</t>
+    <t xml:space="preserve">6.99385166168213</t>
   </si>
   <si>
     <t xml:space="preserve">6.93769693374634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07042789459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09254884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15550947189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22187519073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33758735656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25761032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34269380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2252779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21166467666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14700126647949</t>
+    <t xml:space="preserve">7.07042646408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09254789352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15550994873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22187471389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3375883102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25760984420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34269428253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22527885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21166515350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14700174331665</t>
   </si>
   <si>
     <t xml:space="preserve">7.09425067901611</t>
@@ -3881,13 +3881,13 @@
     <t xml:space="preserve">7.06362009048462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30695819854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25590801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3767261505127</t>
+    <t xml:space="preserve">7.30695867538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25590848922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37672710418701</t>
   </si>
   <si>
     <t xml:space="preserve">7.1401948928833</t>
@@ -3899,22 +3899,22 @@
     <t xml:space="preserve">6.87303304672241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23038339614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28824043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32567691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57241725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53668308258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59794330596924</t>
+    <t xml:space="preserve">7.23038387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28823947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32567644119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57241916656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53668355941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59794425964355</t>
   </si>
   <si>
     <t xml:space="preserve">7.73577833175659</t>
@@ -3926,34 +3926,34 @@
     <t xml:space="preserve">7.9399790763855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67792224884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79873943328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15608882904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3500804901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21054458618164</t>
+    <t xml:space="preserve">7.67792129516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79874038696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15609073638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35008144378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21054267883301</t>
   </si>
   <si>
     <t xml:space="preserve">8.10333824157715</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14758205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40283107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35348224639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45898723602295</t>
+    <t xml:space="preserve">8.14758110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35348415374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45898818969727</t>
   </si>
   <si>
     <t xml:space="preserve">8.60618019104004</t>
@@ -3962,25 +3962,25 @@
     <t xml:space="preserve">8.43856716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3909215927124</t>
+    <t xml:space="preserve">8.39091968536377</t>
   </si>
   <si>
     <t xml:space="preserve">8.56364059448242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55513191223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42325115203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19012451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.193528175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41474342346191</t>
+    <t xml:space="preserve">8.55513000488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42325210571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19012260437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19352626800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41474437713623</t>
   </si>
   <si>
     <t xml:space="preserve">8.38241100311279</t>
@@ -3989,37 +3989,37 @@
     <t xml:space="preserve">8.27520656585693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79336452484131</t>
+    <t xml:space="preserve">8.79336547851562</t>
   </si>
   <si>
     <t xml:space="preserve">9.03585147857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2783374786377</t>
+    <t xml:space="preserve">9.27833843231201</t>
   </si>
   <si>
     <t xml:space="preserve">9.23154449462891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92524337768555</t>
+    <t xml:space="preserve">8.92524433135986</t>
   </si>
   <si>
     <t xml:space="preserve">8.83165168762207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73380470275879</t>
+    <t xml:space="preserve">8.73380565643311</t>
   </si>
   <si>
     <t xml:space="preserve">8.71253490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52960586547852</t>
+    <t xml:space="preserve">8.52960395812988</t>
   </si>
   <si>
     <t xml:space="preserve">8.28882026672363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07611274719238</t>
+    <t xml:space="preserve">8.07611179351807</t>
   </si>
   <si>
     <t xml:space="preserve">8.2693452835083</t>
@@ -4031,13 +4031,13 @@
     <t xml:space="preserve">8.31247711181641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20895957946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62753534317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69654703140259</t>
+    <t xml:space="preserve">8.20895862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62753391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69654607772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.47225713729858</t>
@@ -4046,85 +4046,85 @@
     <t xml:space="preserve">7.78108644485474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70689725875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72932767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319686889648</t>
+    <t xml:space="preserve">7.70689821243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72932720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319639205933</t>
   </si>
   <si>
     <t xml:space="preserve">8.01745128631592</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9191107749939</t>
+    <t xml:space="preserve">7.91910934448242</t>
   </si>
   <si>
     <t xml:space="preserve">7.76038265228271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69309520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62408304214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87942886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6361608505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85527324676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78798627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61373233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86390066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86217451095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96051597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02435207366943</t>
+    <t xml:space="preserve">7.69309568405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62408447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87942790985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63616180419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85527372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78798723220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61373281478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86389970779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86217498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87597799301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96051549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02435302734375</t>
   </si>
   <si>
     <t xml:space="preserve">8.0105504989624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94498777389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25899314880371</t>
+    <t xml:space="preserve">7.94498825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25899410247803</t>
   </si>
   <si>
     <t xml:space="preserve">8.37286281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43669891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43842315673828</t>
+    <t xml:space="preserve">8.43669700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43842506408691</t>
   </si>
   <si>
     <t xml:space="preserve">8.45222568511963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40909385681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58162403106689</t>
+    <t xml:space="preserve">8.40909481048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58162307739258</t>
   </si>
   <si>
     <t xml:space="preserve">8.65667343139648</t>
@@ -4133,7 +4133,7 @@
     <t xml:space="preserve">8.6782398223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85076999664307</t>
+    <t xml:space="preserve">8.85076904296875</t>
   </si>
   <si>
     <t xml:space="preserve">9.06211853027344</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">9.25190162658691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28640842437744</t>
+    <t xml:space="preserve">9.28640747070312</t>
   </si>
   <si>
     <t xml:space="preserve">8.93703460693359</t>
@@ -4151,40 +4151,40 @@
     <t xml:space="preserve">8.49708461761475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88958835601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55382633209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37698554992676</t>
+    <t xml:space="preserve">8.88958930969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55382823944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37698459625244</t>
   </si>
   <si>
     <t xml:space="preserve">9.8385009765625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78243064880371</t>
+    <t xml:space="preserve">9.78242969512939</t>
   </si>
   <si>
     <t xml:space="preserve">9.65734481811523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85144233703613</t>
+    <t xml:space="preserve">9.85144138336182</t>
   </si>
   <si>
     <t xml:space="preserve">9.86006832122803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77380275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87732124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97652530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0800428390503</t>
+    <t xml:space="preserve">9.77380180358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8773193359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97652435302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0800437927246</t>
   </si>
   <si>
     <t xml:space="preserve">9.92476654052734</t>
@@ -4193,61 +4193,61 @@
     <t xml:space="preserve">9.99809074401855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.226692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93770599365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75223541259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44599628448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5236349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42443180084229</t>
+    <t xml:space="preserve">10.2266931533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93770694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75223731994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44599533081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52363586425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42443084716797</t>
   </si>
   <si>
     <t xml:space="preserve">9.32091426849365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60989856719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95495986938477</t>
+    <t xml:space="preserve">9.60989952087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95495891571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.86869430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3560905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1447420120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96358489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2618703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6241827011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9815101623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1540393829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1497278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8736801147461</t>
+    <t xml:space="preserve">10.3560914993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1447429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96358680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2618713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6241836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9815092086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1540403366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1497268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8736791610718</t>
   </si>
   <si>
     <t xml:space="preserve">10.5113677978516</t>
@@ -4256,34 +4256,34 @@
     <t xml:space="preserve">10.7356557846069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.908185005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5724248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6371240615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606142044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9951210021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2927360534668</t>
+    <t xml:space="preserve">10.9081840515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5724239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6371231079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9606161117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9951219558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2927350997925</t>
   </si>
   <si>
     <t xml:space="preserve">12.0123739242554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6845674514771</t>
+    <t xml:space="preserve">11.6845684051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.8829774856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8657255172729</t>
+    <t xml:space="preserve">11.8657245635986</t>
   </si>
   <si>
     <t xml:space="preserve">11.9821834564209</t>
@@ -4301,40 +4301,40 @@
     <t xml:space="preserve">11.9908084869385</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5299644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4135055541992</t>
+    <t xml:space="preserve">12.5299634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4135065078735</t>
   </si>
   <si>
     <t xml:space="preserve">12.8146381378174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9224672317505</t>
+    <t xml:space="preserve">12.9224681854248</t>
   </si>
   <si>
     <t xml:space="preserve">12.9914808273315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9612874984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9310941696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5817222595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.723388671875</t>
+    <t xml:space="preserve">12.9612865447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.931095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5817232131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7233867645264</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374588012695</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0813875198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7758188247681</t>
+    <t xml:space="preserve">12.0813865661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7758197784424</t>
   </si>
   <si>
     <t xml:space="preserve">12.2841091156006</t>
@@ -4343,49 +4343,49 @@
     <t xml:space="preserve">12.8448305130005</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6981811523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6377954483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5385904312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0598192214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.180591583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5989742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2668561935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7283716201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2718410491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4486827850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3667306900024</t>
+    <t xml:space="preserve">12.6981801986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6377944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5385894775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0598211288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1805906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5989751815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2668552398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7283725738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.27184009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4486837387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3667325973511</t>
   </si>
   <si>
     <t xml:space="preserve">13.0216732025146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.19420337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.488579750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3040437698364</t>
+    <t xml:space="preserve">13.1942024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4885787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3040447235107</t>
   </si>
   <si>
     <t xml:space="preserve">13.5456962585449</t>
@@ -4394,40 +4394,40 @@
     <t xml:space="preserve">13.9147644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0861196517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2530765533447</t>
+    <t xml:space="preserve">14.0861186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.253077507019</t>
   </si>
   <si>
     <t xml:space="preserve">13.7302312850952</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8356790542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.86643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8224973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9630947113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0641489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0246067047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4094924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0052757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.803165435791</t>
+    <t xml:space="preserve">13.8356781005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8664350509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8224983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.963095664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0641498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0246076583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4094934463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0052738189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8031644821167</t>
   </si>
   <si>
     <t xml:space="preserve">12.693323135376</t>
@@ -4436,22 +4436,22 @@
     <t xml:space="preserve">12.3154668807983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5641489028931</t>
+    <t xml:space="preserve">11.5641508102417</t>
   </si>
   <si>
     <t xml:space="preserve">11.3927965164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6080856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6739912033081</t>
+    <t xml:space="preserve">11.6080865859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6739902496338</t>
   </si>
   <si>
     <t xml:space="preserve">11.0720586776733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7381381988525</t>
+    <t xml:space="preserve">10.7381391525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.9402475357056</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">11.2302293777466</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0632705688477</t>
+    <t xml:space="preserve">11.063271522522</t>
   </si>
   <si>
     <t xml:space="preserve">10.7820749282837</t>
@@ -4478,25 +4478,25 @@
     <t xml:space="preserve">10.0615129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75835037231445</t>
+    <t xml:space="preserve">9.75834941864014</t>
   </si>
   <si>
     <t xml:space="preserve">10.7469253540039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1423559188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2082624435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1116008758545</t>
+    <t xml:space="preserve">11.1423568725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2082614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1116018295288</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841842651367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5404233932495</t>
+    <t xml:space="preserve">10.5404224395752</t>
   </si>
   <si>
     <t xml:space="preserve">10.7117757797241</t>
@@ -4508,16 +4508,16 @@
     <t xml:space="preserve">11.1819000244141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.067663192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8523731231689</t>
+    <t xml:space="preserve">11.0676651000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8523759841919</t>
   </si>
   <si>
     <t xml:space="preserve">10.9753971099854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0940265655518</t>
+    <t xml:space="preserve">11.0940256118774</t>
   </si>
   <si>
     <t xml:space="preserve">11.4411277770996</t>
@@ -4526,19 +4526,19 @@
     <t xml:space="preserve">11.5861186981201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9551858901978</t>
+    <t xml:space="preserve">11.9551868438721</t>
   </si>
   <si>
     <t xml:space="preserve">11.6344480514526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6608104705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5290002822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0896339416504</t>
+    <t xml:space="preserve">11.6608114242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5289993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0896329879761</t>
   </si>
   <si>
     <t xml:space="preserve">11.3005275726318</t>
@@ -4547,73 +4547,73 @@
     <t xml:space="preserve">11.4147644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2917432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5685434341431</t>
+    <t xml:space="preserve">11.2917423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5685424804688</t>
   </si>
   <si>
     <t xml:space="preserve">11.542181968689</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3224973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6827783584595</t>
+    <t xml:space="preserve">11.3224964141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6827793121338</t>
   </si>
   <si>
     <t xml:space="preserve">11.2829542160034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2803192138672</t>
+    <t xml:space="preserve">12.2803182601929</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704769134521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3945531845093</t>
+    <t xml:space="preserve">12.3945541381836</t>
   </si>
   <si>
     <t xml:space="preserve">12.2188062667847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0913906097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0826025009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0298776626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4384899139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5527276992798</t>
+    <t xml:space="preserve">12.0913896560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0826034545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.029878616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4384908676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5527248382568</t>
   </si>
   <si>
     <t xml:space="preserve">12.1221466064453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.739896774292</t>
+    <t xml:space="preserve">11.7398958206177</t>
   </si>
   <si>
     <t xml:space="preserve">11.7442903518677</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3286476135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5790872573853</t>
+    <t xml:space="preserve">12.328649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5790882110596</t>
   </si>
   <si>
     <t xml:space="preserve">12.5219707489014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5175762176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2407751083374</t>
+    <t xml:space="preserve">12.5175771713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2407760620117</t>
   </si>
   <si>
     <t xml:space="preserve">11.9288244247437</t>
@@ -4622,163 +4622,163 @@
     <t xml:space="preserve">11.9024620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7882280349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1265382766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9622163772583</t>
+    <t xml:space="preserve">11.7882270812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1265411376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9622173309326</t>
   </si>
   <si>
     <t xml:space="preserve">11.1994733810425</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5377883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761005401611</t>
+    <t xml:space="preserve">11.537787437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8761014938354</t>
   </si>
   <si>
     <t xml:space="preserve">11.6564178466797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4604587554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7504396438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0140619277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1854162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7328653335571</t>
+    <t xml:space="preserve">12.4604578018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7504405975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0140628814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1854152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7328672409058</t>
   </si>
   <si>
     <t xml:space="preserve">12.1353273391724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2451696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8163461685181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5615139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217948913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2117767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1590528488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3216199874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2205648422241</t>
+    <t xml:space="preserve">12.2451705932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8163471221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5615129470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217939376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2117776870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1590547561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3216180801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2205638885498</t>
   </si>
   <si>
     <t xml:space="preserve">13.5193338394165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8927974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534301757812</t>
+    <t xml:space="preserve">13.8927965164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534292221069</t>
   </si>
   <si>
     <t xml:space="preserve">13.8005294799805</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1564168930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9982442855835</t>
+    <t xml:space="preserve">14.156418800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9982452392578</t>
   </si>
   <si>
     <t xml:space="preserve">14.1959609985352</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6265420913696</t>
+    <t xml:space="preserve">14.626540184021</t>
   </si>
   <si>
     <t xml:space="preserve">14.7539577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4551868438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3585252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7653789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.055362701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9938507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6572961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7275953292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3101949691772</t>
+    <t xml:space="preserve">14.4551887512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3585271835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7653799057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0553617477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9938497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6572971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7275943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3101940155029</t>
   </si>
   <si>
     <t xml:space="preserve">14.4244318008423</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7851209640503</t>
+    <t xml:space="preserve">13.785120010376</t>
   </si>
   <si>
     <t xml:space="preserve">14.6908102035522</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3578367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4466304779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5265426635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1314144134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5443000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8417587280273</t>
+    <t xml:space="preserve">14.3578357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4466285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5265436172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1314134597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.54430103302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.841757774353</t>
   </si>
   <si>
     <t xml:space="preserve">14.4954671859741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2557249069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.038182258606</t>
+    <t xml:space="preserve">14.2557239532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0381813049316</t>
   </si>
   <si>
     <t xml:space="preserve">13.9138708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6119756698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7806825637817</t>
+    <t xml:space="preserve">13.6119747161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7806816101074</t>
   </si>
   <si>
     <t xml:space="preserve">13.6608104705811</t>
@@ -4787,13 +4787,13 @@
     <t xml:space="preserve">13.5276203155518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9893455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0159816741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7451639175415</t>
+    <t xml:space="preserve">13.9893445968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0159826278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7451648712158</t>
   </si>
   <si>
     <t xml:space="preserve">13.6474924087524</t>
@@ -4802,46 +4802,46 @@
     <t xml:space="preserve">13.949387550354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1402931213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643888473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7218885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7796049118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6686115264893</t>
+    <t xml:space="preserve">14.1402921676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643878936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7218866348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7796030044556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6686124801636</t>
   </si>
   <si>
     <t xml:space="preserve">14.7130088806152</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4599475860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9349908828735</t>
+    <t xml:space="preserve">14.4599466323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9349889755249</t>
   </si>
   <si>
     <t xml:space="preserve">14.4199914932251</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4033126831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.793999671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0071039199829</t>
+    <t xml:space="preserve">13.4033107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7940006256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0071029663086</t>
   </si>
   <si>
     <t xml:space="preserve">14.0603790283203</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0692577362061</t>
+    <t xml:space="preserve">14.0692596435547</t>
   </si>
   <si>
     <t xml:space="preserve">14.237964630127</t>
@@ -4850,22 +4850,22 @@
     <t xml:space="preserve">14.4421882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">14.344518661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2290849685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6597309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2679634094238</t>
+    <t xml:space="preserve">14.3445177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2290859222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6597328186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2679653167725</t>
   </si>
   <si>
     <t xml:space="preserve">14.5176639556885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6952486038208</t>
+    <t xml:space="preserve">14.6952495574951</t>
   </si>
   <si>
     <t xml:space="preserve">14.2424049377441</t>
@@ -4874,31 +4874,31 @@
     <t xml:space="preserve">14.26904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2956800460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6197748184204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3977928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4288721084595</t>
+    <t xml:space="preserve">14.2956819534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.619776725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3977937698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4288702011108</t>
   </si>
   <si>
     <t xml:space="preserve">14.1180953979492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.629734992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5498189926147</t>
+    <t xml:space="preserve">13.6297330856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5498199462891</t>
   </si>
   <si>
     <t xml:space="preserve">13.4388275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.540940284729</t>
+    <t xml:space="preserve">13.5409393310547</t>
   </si>
   <si>
     <t xml:space="preserve">13.8872327804565</t>
@@ -4907,16 +4907,16 @@
     <t xml:space="preserve">14.1225347518921</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0825777053833</t>
+    <t xml:space="preserve">14.082576751709</t>
   </si>
   <si>
     <t xml:space="preserve">14.380033493042</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4011526107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6641721725464</t>
+    <t xml:space="preserve">15.4011545181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6641712188721</t>
   </si>
   <si>
     <t xml:space="preserve">14.4377498626709</t>
@@ -4928,16 +4928,16 @@
     <t xml:space="preserve">14.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9227514266968</t>
+    <t xml:space="preserve">13.9227504730225</t>
   </si>
   <si>
     <t xml:space="preserve">14.2646036148071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3267593383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3711538314819</t>
+    <t xml:space="preserve">14.3267583847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3711547851562</t>
   </si>
   <si>
     <t xml:space="preserve">14.4732666015625</t>
@@ -4946,25 +4946,25 @@
     <t xml:space="preserve">14.5487413406372</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0026636123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7140874862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9105100631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0969734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9249076843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9559850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7384414672852</t>
+    <t xml:space="preserve">14.00266456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7140865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9105091094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0969753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9249067306519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9559841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7384405136108</t>
   </si>
   <si>
     <t xml:space="preserve">11.7695188522339</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">12.1646480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0358972549438</t>
+    <t xml:space="preserve">12.0358982086182</t>
   </si>
   <si>
     <t xml:space="preserve">11.765079498291</t>
@@ -4991,37 +4991,37 @@
     <t xml:space="preserve">11.7739591598511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6096897125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.631890296936</t>
+    <t xml:space="preserve">11.609691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6318893432617</t>
   </si>
   <si>
     <t xml:space="preserve">11.9826231002808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6851654052734</t>
+    <t xml:space="preserve">11.6851663589478</t>
   </si>
   <si>
     <t xml:space="preserve">11.5386562347412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5075788497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8183536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9737424850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9337863922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8405542373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7828378677368</t>
+    <t xml:space="preserve">11.5075798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8183546066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9737434387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9337854385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8405523300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7828388214111</t>
   </si>
   <si>
     <t xml:space="preserve">11.6540880203247</t>
@@ -5039,13 +5039,13 @@
     <t xml:space="preserve">11.2678375244141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9659414291382</t>
+    <t xml:space="preserve">10.9659433364868</t>
   </si>
   <si>
     <t xml:space="preserve">10.8949069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7439594268799</t>
+    <t xml:space="preserve">10.7439584732056</t>
   </si>
   <si>
     <t xml:space="preserve">11.0280961990356</t>
@@ -5057,16 +5057,16 @@
     <t xml:space="preserve">11.0991306304932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8771476745605</t>
+    <t xml:space="preserve">10.8771486282349</t>
   </si>
   <si>
     <t xml:space="preserve">10.7528381347656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8815879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8460712432861</t>
+    <t xml:space="preserve">10.8815889358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8460702896118</t>
   </si>
   <si>
     <t xml:space="preserve">10.7705974578857</t>
@@ -5078,28 +5078,28 @@
     <t xml:space="preserve">10.9526224136353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0713272094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2311191558838</t>
+    <t xml:space="preserve">11.0713262557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2311172485352</t>
   </si>
   <si>
     <t xml:space="preserve">11.2585105895996</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8430500030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9389266967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1489400863647</t>
+    <t xml:space="preserve">10.8430509567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.938925743103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1489391326904</t>
   </si>
   <si>
     <t xml:space="preserve">10.8476152420044</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6558666229248</t>
+    <t xml:space="preserve">10.6558656692505</t>
   </si>
   <si>
     <t xml:space="preserve">10.8795747756958</t>
@@ -5108,7 +5108,7 @@
     <t xml:space="preserve">11.2722082138062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3452548980713</t>
+    <t xml:space="preserve">11.3452558517456</t>
   </si>
   <si>
     <t xml:space="preserve">11.6054887771606</t>
@@ -5123,10 +5123,10 @@
     <t xml:space="preserve">11.7104949951172</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6420116424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205074310303</t>
+    <t xml:space="preserve">11.6420125961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205083847046</t>
   </si>
   <si>
     <t xml:space="preserve">11.8063707351685</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">11.8931140899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4274339675903</t>
+    <t xml:space="preserve">11.4274349212646</t>
   </si>
   <si>
     <t xml:space="preserve">11.7972393035889</t>
@@ -5144,13 +5144,13 @@
     <t xml:space="preserve">11.6374464035034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6922340393066</t>
+    <t xml:space="preserve">11.6922330856323</t>
   </si>
   <si>
     <t xml:space="preserve">11.829197883606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8337631225586</t>
+    <t xml:space="preserve">11.8337640762329</t>
   </si>
   <si>
     <t xml:space="preserve">11.8657217025757</t>
@@ -5159,10 +5159,10 @@
     <t xml:space="preserve">12.1853075027466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5231523513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5185871124268</t>
+    <t xml:space="preserve">12.523154258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5185880661011</t>
   </si>
   <si>
     <t xml:space="preserve">12.5870695114136</t>
@@ -5171,13 +5171,13 @@
     <t xml:space="preserve">12.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305208206177</t>
+    <t xml:space="preserve">12.1305198669434</t>
   </si>
   <si>
     <t xml:space="preserve">12.4501056671143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4227113723755</t>
+    <t xml:space="preserve">12.4227123260498</t>
   </si>
   <si>
     <t xml:space="preserve">12.7696895599365</t>
@@ -5186,31 +5186,31 @@
     <t xml:space="preserve">13.0025300979614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0162258148193</t>
+    <t xml:space="preserve">13.016227722168</t>
   </si>
   <si>
     <t xml:space="preserve">12.9568748474121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9660062789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1577568054199</t>
+    <t xml:space="preserve">12.9660053253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1577558517456</t>
   </si>
   <si>
     <t xml:space="preserve">13.1668882369995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184307098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5549554824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7330083847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6553964614868</t>
+    <t xml:space="preserve">13.5184326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5549545288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7330093383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6553955078125</t>
   </si>
   <si>
     <t xml:space="preserve">13.6143064498901</t>
@@ -5231,16 +5231,16 @@
     <t xml:space="preserve">13.6462640762329</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3632049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6599617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5823488235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6371355056763</t>
+    <t xml:space="preserve">13.3632040023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6599607467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.582347869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6371335983276</t>
   </si>
   <si>
     <t xml:space="preserve">14.070855140686</t>
@@ -5264,25 +5264,25 @@
     <t xml:space="preserve">13.9475870132446</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9247608184814</t>
+    <t xml:space="preserve">13.9247598648071</t>
   </si>
   <si>
     <t xml:space="preserve">13.7877960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7512712478638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6736583709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380146026611</t>
+    <t xml:space="preserve">13.7512722015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.673659324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380155563354</t>
   </si>
   <si>
     <t xml:space="preserve">13.9612846374512</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9293260574341</t>
+    <t xml:space="preserve">13.9293270111084</t>
   </si>
   <si>
     <t xml:space="preserve">13.4773416519165</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">13.6097402572632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5503902435303</t>
+    <t xml:space="preserve">13.550389289856</t>
   </si>
   <si>
     <t xml:space="preserve">13.760401725769</t>
@@ -5306,70 +5306,70 @@
     <t xml:space="preserve">13.847146987915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7421407699585</t>
+    <t xml:space="preserve">13.7421398162842</t>
   </si>
   <si>
     <t xml:space="preserve">14.0936841964722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0891180038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8425817489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7786645889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3951625823975</t>
+    <t xml:space="preserve">14.0891189575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8425807952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7786655426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3951635360718</t>
   </si>
   <si>
     <t xml:space="preserve">13.3860321044922</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4316864013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4362525939941</t>
+    <t xml:space="preserve">13.4316873550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4362516403198</t>
   </si>
   <si>
     <t xml:space="preserve">13.7740993499756</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6827878952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2125434875488</t>
+    <t xml:space="preserve">13.682788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2125444412231</t>
   </si>
   <si>
     <t xml:space="preserve">13.3084182739258</t>
   </si>
   <si>
-    <t xml:space="preserve">13.011661529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3586387634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8836708068848</t>
+    <t xml:space="preserve">13.0116624832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3586378097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8836717605591</t>
   </si>
   <si>
     <t xml:space="preserve">14.0069398880005</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9567193984985</t>
+    <t xml:space="preserve">13.9567184448242</t>
   </si>
   <si>
     <t xml:space="preserve">14.0343332290649</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3950061798096</t>
+    <t xml:space="preserve">14.3950071334839</t>
   </si>
   <si>
     <t xml:space="preserve">14.2945652008057</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4954471588135</t>
+    <t xml:space="preserve">14.4954481124878</t>
   </si>
   <si>
     <t xml:space="preserve">14.5045785903931</t>
@@ -5378,10 +5378,10 @@
     <t xml:space="preserve">14.2671728134155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9338912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0571594238281</t>
+    <t xml:space="preserve">13.933892250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0571603775024</t>
   </si>
   <si>
     <t xml:space="preserve">14.0982484817505</t>
@@ -5390,10 +5390,10 @@
     <t xml:space="preserve">13.7969264984131</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9383001327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8999500274658</t>
+    <t xml:space="preserve">14.9383010864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999509811401</t>
   </si>
   <si>
     <t xml:space="preserve">15.2542314529419</t>
@@ -5402,7 +5402,7 @@
     <t xml:space="preserve">14.783073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3228712081909</t>
+    <t xml:space="preserve">14.3228721618652</t>
   </si>
   <si>
     <t xml:space="preserve">14.585844039917</t>
@@ -5414,16 +5414,16 @@
     <t xml:space="preserve">14.906343460083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7008943557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7191562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1302070617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3036956787109</t>
+    <t xml:space="preserve">14.7008953094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7191581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1302080154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3036966323853</t>
   </si>
   <si>
     <t xml:space="preserve">14.5487966537476</t>
@@ -5459,7 +5459,7 @@
     <t xml:space="preserve">14.6921577453613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4331836700439</t>
+    <t xml:space="preserve">14.4331827163696</t>
   </si>
   <si>
     <t xml:space="preserve">14.5626697540283</t>
@@ -5477,13 +5477,13 @@
     <t xml:space="preserve">14.46555519104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6274127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.729154586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8725156784058</t>
+    <t xml:space="preserve">14.6274137496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7291536331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8725137710571</t>
   </si>
   <si>
     <t xml:space="preserve">14.7707748413086</t>
@@ -5498,13 +5498,13 @@
     <t xml:space="preserve">14.7014074325562</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6135416030884</t>
+    <t xml:space="preserve">14.6135406494141</t>
   </si>
   <si>
     <t xml:space="preserve">14.4378070831299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3869390487671</t>
+    <t xml:space="preserve">14.3869380950928</t>
   </si>
   <si>
     <t xml:space="preserve">14.0863428115845</t>
@@ -5525,10 +5525,10 @@
     <t xml:space="preserve">13.4712791442871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4019107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065361022949</t>
+    <t xml:space="preserve">13.4019117355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065351486206</t>
   </si>
   <si>
     <t xml:space="preserve">13.4204092025757</t>
@@ -5546,7 +5546,7 @@
     <t xml:space="preserve">13.850492477417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9291086196899</t>
+    <t xml:space="preserve">13.9291095733643</t>
   </si>
   <si>
     <t xml:space="preserve">13.8597402572632</t>
@@ -5555,22 +5555,22 @@
     <t xml:space="preserve">13.5822687149048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6100158691406</t>
+    <t xml:space="preserve">13.6100149154663</t>
   </si>
   <si>
     <t xml:space="preserve">13.8921127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4389066696167</t>
+    <t xml:space="preserve">13.438907623291</t>
   </si>
   <si>
     <t xml:space="preserve">13.6886329650879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4759044647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6377620697021</t>
+    <t xml:space="preserve">13.4759035110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6377630233765</t>
   </si>
   <si>
     <t xml:space="preserve">13.7903728485107</t>
@@ -5579,64 +5579,64 @@
     <t xml:space="preserve">13.7071304321289</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6331386566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8366184234619</t>
+    <t xml:space="preserve">13.6331377029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8366174697876</t>
   </si>
   <si>
     <t xml:space="preserve">13.9522314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8042459487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8967361450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9095115661621</t>
+    <t xml:space="preserve">13.8042469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8967370986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9095125198364</t>
   </si>
   <si>
     <t xml:space="preserve">15.1869831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3303442001343</t>
+    <t xml:space="preserve">15.3303461074829</t>
   </si>
   <si>
     <t xml:space="preserve">15.4320831298828</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3395910263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2378540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731100082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7141809463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8899145126343</t>
+    <t xml:space="preserve">15.3395919799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2378530502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731109619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7141799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.88991355896</t>
   </si>
   <si>
     <t xml:space="preserve">15.963906288147</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0101490020752</t>
+    <t xml:space="preserve">16.0101509094238</t>
   </si>
   <si>
     <t xml:space="preserve">16.0009021759033</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2275047302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3801136016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5280990600586</t>
+    <t xml:space="preserve">16.227502822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3801155090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5281009674072</t>
   </si>
   <si>
     <t xml:space="preserve">16.4078617095947</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">16.6067161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6390895843506</t>
+    <t xml:space="preserve">16.639087677002</t>
   </si>
   <si>
     <t xml:space="preserve">16.78244972229</t>
@@ -5663,13 +5663,13 @@
     <t xml:space="preserve">16.93505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0182991027832</t>
+    <t xml:space="preserve">17.0183010101318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9396839141846</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2032814025879</t>
+    <t xml:space="preserve">17.2032833099365</t>
   </si>
   <si>
     <t xml:space="preserve">17.2402763366699</t>
@@ -5696,22 +5696,22 @@
     <t xml:space="preserve">16.5096015930176</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5974674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3708648681641</t>
+    <t xml:space="preserve">16.5974655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3708667755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.338493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2182540893555</t>
+    <t xml:space="preserve">16.2182559967041</t>
   </si>
   <si>
     <t xml:space="preserve">16.1396389007568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0471458435059</t>
+    <t xml:space="preserve">16.0471477508545</t>
   </si>
   <si>
     <t xml:space="preserve">14.7800235748291</t>
@@ -5720,10 +5720,10 @@
     <t xml:space="preserve">14.6967821121216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4979267120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4054365158081</t>
+    <t xml:space="preserve">14.4979276657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4054355621338</t>
   </si>
   <si>
     <t xml:space="preserve">14.4239349365234</t>
@@ -5753,10 +5753,10 @@
     <t xml:space="preserve">14.9002628326416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9808797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1421184539795</t>
+    <t xml:space="preserve">14.9808807373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1421175003052</t>
   </si>
   <si>
     <t xml:space="preserve">14.8338689804077</t>
@@ -5783,13 +5783,13 @@
     <t xml:space="preserve">14.3169603347778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1699495315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0845880508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9755153656006</t>
+    <t xml:space="preserve">14.1699485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0845890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9755144119263</t>
   </si>
   <si>
     <t xml:space="preserve">14.056134223938</t>
@@ -5813,13 +5813,13 @@
     <t xml:space="preserve">13.5771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6577825546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8617000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6198444366455</t>
+    <t xml:space="preserve">13.6577816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8617010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6198434829712</t>
   </si>
   <si>
     <t xml:space="preserve">13.7621126174927</t>
@@ -5828,7 +5828,7 @@
     <t xml:space="preserve">13.6008749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7526273727417</t>
+    <t xml:space="preserve">13.752628326416</t>
   </si>
   <si>
     <t xml:space="preserve">13.6625242233276</t>
@@ -5837,7 +5837,7 @@
     <t xml:space="preserve">13.3590183258057</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2973690032959</t>
+    <t xml:space="preserve">13.2973699569702</t>
   </si>
   <si>
     <t xml:space="preserve">13.6103601455688</t>
@@ -5855,13 +5855,13 @@
     <t xml:space="preserve">13.5534524917603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3969564437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4159259796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5202569961548</t>
+    <t xml:space="preserve">13.3969573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4159269332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5202560424805</t>
   </si>
   <si>
     <t xml:space="preserve">13.8047943115234</t>
@@ -5870,25 +5870,25 @@
     <t xml:space="preserve">13.7953090667725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7336578369141</t>
+    <t xml:space="preserve">13.7336587905884</t>
   </si>
   <si>
     <t xml:space="preserve">13.9470615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6340703964233</t>
+    <t xml:space="preserve">13.6340713500977</t>
   </si>
   <si>
     <t xml:space="preserve">13.6672668457031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6862363815308</t>
+    <t xml:space="preserve">13.6862373352051</t>
   </si>
   <si>
     <t xml:space="preserve">13.8285045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8854122161865</t>
+    <t xml:space="preserve">13.8854131698608</t>
   </si>
   <si>
     <t xml:space="preserve">12.6761293411255</t>
@@ -5900,7 +5900,7 @@
     <t xml:space="preserve">12.0548896789551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0311784744263</t>
+    <t xml:space="preserve">12.0311794281006</t>
   </si>
   <si>
     <t xml:space="preserve">12.1639623641968</t>
@@ -5909,7 +5909,7 @@
     <t xml:space="preserve">12.0833435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1687040328979</t>
+    <t xml:space="preserve">12.1687049865723</t>
   </si>
   <si>
     <t xml:space="preserve">12.102313041687</t>
@@ -5918,22 +5918,22 @@
     <t xml:space="preserve">12.0406627655029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1402521133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1876735687256</t>
+    <t xml:space="preserve">12.140251159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1876745223999</t>
   </si>
   <si>
     <t xml:space="preserve">11.8557138442993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9553022384644</t>
+    <t xml:space="preserve">11.95530128479</t>
   </si>
   <si>
     <t xml:space="preserve">11.9837560653687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1829319000244</t>
+    <t xml:space="preserve">12.1829328536987</t>
   </si>
   <si>
     <t xml:space="preserve">11.8414869308472</t>
@@ -5960,7 +5960,7 @@
     <t xml:space="preserve">12.3299427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0691165924072</t>
+    <t xml:space="preserve">12.0691175460815</t>
   </si>
   <si>
     <t xml:space="preserve">12.0359201431274</t>
@@ -5975,7 +5975,7 @@
     <t xml:space="preserve">12.5291185379028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196332931519</t>
+    <t xml:space="preserve">12.5196342468262</t>
   </si>
   <si>
     <t xml:space="preserve">12.6856136322021</t>
@@ -5996,7 +5996,7 @@
     <t xml:space="preserve">13.0365428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4348945617676</t>
+    <t xml:space="preserve">13.4348955154419</t>
   </si>
   <si>
     <t xml:space="preserve">13.4064416885376</t>
@@ -6017,13 +6017,13 @@
     <t xml:space="preserve">13.6909790039062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9565467834473</t>
+    <t xml:space="preserve">13.9565458297729</t>
   </si>
   <si>
     <t xml:space="preserve">14.0087118148804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7384014129639</t>
+    <t xml:space="preserve">13.7384004592896</t>
   </si>
   <si>
     <t xml:space="preserve">13.8000507354736</t>
@@ -6032,7 +6032,7 @@
     <t xml:space="preserve">13.781081199646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.918607711792</t>
+    <t xml:space="preserve">13.9186086654663</t>
   </si>
   <si>
     <t xml:space="preserve">14.0798463821411</t>
@@ -6050,10 +6050,10 @@
     <t xml:space="preserve">14.3217029571533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2363424301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3643836975098</t>
+    <t xml:space="preserve">14.2363414764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3643827438354</t>
   </si>
   <si>
     <t xml:space="preserve">14.5777854919434</t>
@@ -6062,13 +6062,13 @@
     <t xml:space="preserve">14.4781980514526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6678886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6590270996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4177913665771</t>
+    <t xml:space="preserve">14.6678895950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6590280532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4177932739258</t>
   </si>
   <si>
     <t xml:space="preserve">16.346658706665</t>
@@ -6080,7 +6080,7 @@
     <t xml:space="preserve">16.4130516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5078983306885</t>
+    <t xml:space="preserve">16.5078964233398</t>
   </si>
   <si>
     <t xml:space="preserve">16.5553188323975</t>
@@ -6690,6 +6690,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.2999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2849998474121</t>
   </si>
 </sst>
 </file>
@@ -72028,7 +72031,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6926041667</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>5749554</v>
@@ -72049,6 +72052,32 @@
         <v>2225</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6910763889</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>2372414</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>17.4599990844727</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>17.1149997711182</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>17.1499996185303</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>17.2849998474121</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>2226</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2229" uniqueCount="2229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2230" uniqueCount="2230">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87407112121582</t>
+    <t xml:space="preserve">7.8740701675415</t>
   </si>
   <si>
     <t xml:space="preserve">TEN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88865089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69908952713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48036575317383</t>
+    <t xml:space="preserve">7.88865232467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69909143447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48036623001099</t>
   </si>
   <si>
     <t xml:space="preserve">7.19602489471436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1158242225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07937145233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12311697006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07208061218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62734174728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56901693344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77680444717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39403676986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63463354110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80596685409546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78045034408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88981008529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91168308258057</t>
+    <t xml:space="preserve">7.11582708358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07937049865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12311744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07208299636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62734079360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56901597976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77680349349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39403629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63463401794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8059663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7804479598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88981103897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91168260574341</t>
   </si>
   <si>
     <t xml:space="preserve">6.82783889770508</t>
@@ -107,166 +107,166 @@
     <t xml:space="preserve">7.0356273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43413543701172</t>
+    <t xml:space="preserve">6.43413639068604</t>
   </si>
   <si>
     <t xml:space="preserve">6.29925584793091</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80232286453247</t>
+    <t xml:space="preserve">6.80232048034668</t>
   </si>
   <si>
     <t xml:space="preserve">6.95542764663696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74034976959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14863538742065</t>
+    <t xml:space="preserve">6.7403507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14863634109497</t>
   </si>
   <si>
     <t xml:space="preserve">7.0611457824707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83148431777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11947250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8606481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54349851608276</t>
+    <t xml:space="preserve">6.83148527145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11947202682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86064910888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54349803924561</t>
   </si>
   <si>
     <t xml:space="preserve">6.55443429946899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16686153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32726001739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50223779678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45120334625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61160087585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91781568527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00530433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71367073059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85948801040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58972835540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82303333282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73554468154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96156072616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8157434463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77928972244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95426893234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72096347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66992807388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98343276977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53140115737915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263723373413</t>
+    <t xml:space="preserve">7.16686201095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32726049423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50223922729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4512038230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61160135269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91781282424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00530242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71367120742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85948991775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58972883224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82303285598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73554658889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96156024932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81574296951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77929019927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95426988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72096395492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66992616653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98343086242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032608032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53140068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66263484954834</t>
   </si>
   <si>
     <t xml:space="preserve">7.64076375961304</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07821273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11466598510742</t>
+    <t xml:space="preserve">8.07821083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11466693878174</t>
   </si>
   <si>
     <t xml:space="preserve">8.17299270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42088222503662</t>
+    <t xml:space="preserve">8.4208812713623</t>
   </si>
   <si>
     <t xml:space="preserve">8.41358947753906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45004463195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69793224334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82916736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86562061309814</t>
+    <t xml:space="preserve">8.45004367828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69793128967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8291654586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86561965942383</t>
   </si>
   <si>
     <t xml:space="preserve">8.91665458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63960552215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80000114440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80729198455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58856773376465</t>
+    <t xml:space="preserve">8.63960647583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8000020980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80729389190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58856964111328</t>
   </si>
   <si>
     <t xml:space="preserve">8.47191524505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01988506317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97614097595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39900779724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24590301513672</t>
+    <t xml:space="preserve">8.0198860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97614145278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39900875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2459020614624</t>
   </si>
   <si>
     <t xml:space="preserve">8.21673679351807</t>
@@ -275,34 +275,34 @@
     <t xml:space="preserve">8.29693794250488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30422687530518</t>
+    <t xml:space="preserve">8.30422782897949</t>
   </si>
   <si>
     <t xml:space="preserve">8.45733547210693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64689636230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67605686187744</t>
+    <t xml:space="preserve">8.64689445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67605781555176</t>
   </si>
   <si>
     <t xml:space="preserve">8.39171695709229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56669521331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62655067443848</t>
+    <t xml:space="preserve">8.5666971206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62655162811279</t>
   </si>
   <si>
     <t xml:space="preserve">8.73129653930664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75374317169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9557523727417</t>
+    <t xml:space="preserve">8.75374221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95575332641602</t>
   </si>
   <si>
     <t xml:space="preserve">8.97819709777832</t>
@@ -311,52 +311,52 @@
     <t xml:space="preserve">8.98567867279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91085815429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80611801147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67892360687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6489953994751</t>
+    <t xml:space="preserve">8.91086101531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80611419677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67892456054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64899635314941</t>
   </si>
   <si>
     <t xml:space="preserve">9.08294296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53185272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69645404815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52436923980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49444103240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28495025634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15776252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34480667114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17272567749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40466117858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66652297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42710876464844</t>
+    <t xml:space="preserve">9.53185176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69645214080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52437114715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4944429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28495121002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15776062011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34480571746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17272472381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40466022491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66652584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42710781097412</t>
   </si>
   <si>
     <t xml:space="preserve">9.80119800567627</t>
@@ -374,16 +374,16 @@
     <t xml:space="preserve">9.6141529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73386096954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86853408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83112525939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59918880462646</t>
+    <t xml:space="preserve">9.73386287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86853504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83112907409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59918689727783</t>
   </si>
   <si>
     <t xml:space="preserve">9.32236194610596</t>
@@ -392,70 +392,70 @@
     <t xml:space="preserve">9.39718055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50940608978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65904235839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74882411956787</t>
+    <t xml:space="preserve">9.50940799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65904521942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74882507324219</t>
   </si>
   <si>
     <t xml:space="preserve">9.47947978973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59170532226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21761608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37473487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18768787384033</t>
+    <t xml:space="preserve">9.59170627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21761703491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37473297119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18768882751465</t>
   </si>
   <si>
     <t xml:space="preserve">9.06797885894775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16524124145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09790706634521</t>
+    <t xml:space="preserve">9.16524410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0979061126709</t>
   </si>
   <si>
     <t xml:space="preserve">8.82855987548828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94826889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70885181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57417774200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74626064300537</t>
+    <t xml:space="preserve">8.94826984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70885276794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57417964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74625968933105</t>
   </si>
   <si>
     <t xml:space="preserve">9.00064373016357</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19517040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38969802856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3672513961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48696041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70393562316895</t>
+    <t xml:space="preserve">9.19516754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38969898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36725425720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48696136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70393466949463</t>
   </si>
   <si>
     <t xml:space="preserve">9.65156173706055</t>
@@ -464,55 +464,55 @@
     <t xml:space="preserve">9.62911701202393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51688861846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45703411102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09042358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22509765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29991626739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10538768768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85848617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6639575958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71633338928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88093280792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76870441436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67144107818604</t>
+    <t xml:space="preserve">9.51688957214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45703315734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09042549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22509860992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29991436004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10538959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85848808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66396045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71633148193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88093376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76870536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67144298553467</t>
   </si>
   <si>
     <t xml:space="preserve">8.69388675689697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9033784866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70137023925781</t>
+    <t xml:space="preserve">8.90337753295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7013692855835</t>
   </si>
   <si>
     <t xml:space="preserve">8.44698619842529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55921173095703</t>
+    <t xml:space="preserve">8.55921459197998</t>
   </si>
   <si>
     <t xml:space="preserve">9.35976982116699</t>
@@ -521,10 +521,10 @@
     <t xml:space="preserve">9.50192546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64408111572266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76378726959229</t>
+    <t xml:space="preserve">9.64408016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7637882232666</t>
   </si>
   <si>
     <t xml:space="preserve">9.7413444519043</t>
@@ -539,193 +539,193 @@
     <t xml:space="preserve">9.83860683441162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81616306304932</t>
+    <t xml:space="preserve">9.81616401672363</t>
   </si>
   <si>
     <t xml:space="preserve">9.9433536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0406150817871</t>
+    <t xml:space="preserve">10.0406169891357</t>
   </si>
   <si>
     <t xml:space="preserve">9.99572563171387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0106887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96580028533936</t>
+    <t xml:space="preserve">10.0106897354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96579933166504</t>
   </si>
   <si>
     <t xml:space="preserve">10.0630626678467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77127170562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89846229553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86105346679688</t>
+    <t xml:space="preserve">9.77126979827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89846038818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86105060577393</t>
   </si>
   <si>
     <t xml:space="preserve">9.2924337387085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2800331115723</t>
+    <t xml:space="preserve">10.2800340652466</t>
   </si>
   <si>
     <t xml:space="preserve">10.6765727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6167192459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8112468719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9384355545044</t>
+    <t xml:space="preserve">10.616717338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8112459182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9384365081787</t>
   </si>
   <si>
     <t xml:space="preserve">10.9309539794922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9159917831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7214622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1216306686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8045177459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0310258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0687780380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8347187042236</t>
+    <t xml:space="preserve">10.9159908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7214641571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1216316223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8045167922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0310249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0687770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8347177505493</t>
   </si>
   <si>
     <t xml:space="preserve">10.6761617660522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3783445358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464622497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7407598495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0352191925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1937770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0805225372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2239789962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5561904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3749847412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2919311523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4202890396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3145818710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3674335479736</t>
+    <t xml:space="preserve">11.3783407211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464632034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7407579421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0352210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1937780380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0805234909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2239780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5561923980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3749837875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2919330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4202871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.314582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3674345016479</t>
   </si>
   <si>
     <t xml:space="preserve">12.5410928726196</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5939464569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280038833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9790086746216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0016622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8129034042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0243148803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714593887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9488086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8808574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8657579421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7751531600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6769981384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8204545974731</t>
+    <t xml:space="preserve">12.4504871368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5939445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9790105819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0016603469849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8129043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0243158340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9488105773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8808565139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8657560348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7751522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6769990921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8204526901245</t>
   </si>
   <si>
     <t xml:space="preserve">12.7600517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">12.533540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7676029205322</t>
+    <t xml:space="preserve">12.5335426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.767599105835</t>
   </si>
   <si>
     <t xml:space="preserve">12.8582057952881</t>
   </si>
   <si>
-    <t xml:space="preserve">12.699649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6618976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9865627288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0092096328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8506546020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2164297103882</t>
+    <t xml:space="preserve">12.6996517181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6618967056274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9865608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0092124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8506565093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2164278030396</t>
   </si>
   <si>
     <t xml:space="preserve">12.2088775634766</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">12.2843818664551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1182727813721</t>
+    <t xml:space="preserve">12.1182737350464</t>
   </si>
   <si>
     <t xml:space="preserve">12.1484746932983</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">12.0729722976685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.156023979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2541780471802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9748163223267</t>
+    <t xml:space="preserve">12.1560258865356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2541790008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9748182296753</t>
   </si>
   <si>
     <t xml:space="preserve">11.8540134429932</t>
@@ -767,112 +767,112 @@
     <t xml:space="preserve">12.2390775680542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.786060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7256593704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9068651199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6652536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5142469406128</t>
+    <t xml:space="preserve">11.786057472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7256574630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9068670272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6652545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5142478942871</t>
   </si>
   <si>
     <t xml:space="preserve">11.5444498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4613952636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0989789962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1140804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0763282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3330402374268</t>
+    <t xml:space="preserve">11.4613971710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0989799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1140813827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593828201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0763292312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3330411911011</t>
   </si>
   <si>
     <t xml:space="preserve">11.4085426330566</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4991474151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2952890396118</t>
+    <t xml:space="preserve">11.4991464614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2952880859375</t>
   </si>
   <si>
     <t xml:space="preserve">11.1442813873291</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1669340133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2424354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9932746887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8389139175415</t>
+    <t xml:space="preserve">11.1669330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2424364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9932765960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8389120101929</t>
   </si>
   <si>
     <t xml:space="preserve">11.7634086608887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1333723068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0427703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2013292312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1786756515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9370670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3858938217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4840459823608</t>
+    <t xml:space="preserve">12.1333742141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0427713394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2013282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1786766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9370641708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3858919143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4840488433838</t>
   </si>
   <si>
     <t xml:space="preserve">11.2801876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3481407165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3556900024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3405895233154</t>
+    <t xml:space="preserve">11.3481397628784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3556909561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3405904769897</t>
   </si>
   <si>
     <t xml:space="preserve">11.5066967010498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8724689483643</t>
+    <t xml:space="preserve">10.8724718093872</t>
   </si>
   <si>
     <t xml:space="preserve">10.8573684692383</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9026718139648</t>
+    <t xml:space="preserve">10.9026708602905</t>
   </si>
   <si>
     <t xml:space="preserve">10.7894172668457</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">10.6459608078003</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6610622406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8271684646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8800172805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7441158294678</t>
+    <t xml:space="preserve">10.6610612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8271675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8800220489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7441139221191</t>
   </si>
   <si>
     <t xml:space="preserve">10.9781732559204</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7139139175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8951215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0183162689209</t>
+    <t xml:space="preserve">10.7139129638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8951225280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0183172225952</t>
   </si>
   <si>
     <t xml:space="preserve">10.9721183776855</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">11.0260152816772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9259204864502</t>
+    <t xml:space="preserve">10.9259214401245</t>
   </si>
   <si>
     <t xml:space="preserve">10.7642240524292</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">10.6410303115845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6025304794312</t>
+    <t xml:space="preserve">10.6025314331055</t>
   </si>
   <si>
     <t xml:space="preserve">10.3561391830444</t>
@@ -938,10 +938,10 @@
     <t xml:space="preserve">10.4408359527588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4177360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406425476074</t>
+    <t xml:space="preserve">10.4177389144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406454086304</t>
   </si>
   <si>
     <t xml:space="preserve">10.4023389816284</t>
@@ -950,103 +950,103 @@
     <t xml:space="preserve">10.7873258590698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4947338104248</t>
+    <t xml:space="preserve">10.4947347640991</t>
   </si>
   <si>
     <t xml:space="preserve">10.5409307479858</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3176403045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3715362548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2791423797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2868413925171</t>
+    <t xml:space="preserve">10.3176422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3715372085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2791442871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2868404388428</t>
   </si>
   <si>
     <t xml:space="preserve">10.3330411911011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5101337432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8335237503052</t>
+    <t xml:space="preserve">10.5101327896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8335218429565</t>
   </si>
   <si>
     <t xml:space="preserve">10.8566226959229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7103261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6179313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3407411575317</t>
+    <t xml:space="preserve">10.7103281021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6179304122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3407392501831</t>
   </si>
   <si>
     <t xml:space="preserve">10.4716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7796258926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9105215072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0106163024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9413204193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7565250396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5255336761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6256303787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3099422454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0943479537964</t>
+    <t xml:space="preserve">10.7796230316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9105195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0106191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9413194656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7565269470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5255327224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6256294250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3099403381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0943489074707</t>
   </si>
   <si>
     <t xml:space="preserve">9.9942512512207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27047634124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34747505187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2088794708252</t>
+    <t xml:space="preserve">9.27047729492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34747314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20887851715088</t>
   </si>
   <si>
     <t xml:space="preserve">9.29357624053955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16268253326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22427845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97788715362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00868701934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96248722076416</t>
+    <t xml:space="preserve">9.16268062591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22427749633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97788619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96248817443848</t>
   </si>
   <si>
     <t xml:space="preserve">8.92398929595947</t>
@@ -1058,142 +1058,142 @@
     <t xml:space="preserve">8.80079460144043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85469245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82389259338379</t>
+    <t xml:space="preserve">8.85469150543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82389354705811</t>
   </si>
   <si>
     <t xml:space="preserve">8.7853946685791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72379589080811</t>
+    <t xml:space="preserve">8.72379493713379</t>
   </si>
   <si>
     <t xml:space="preserve">8.63909912109375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52360343933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62369918823242</t>
+    <t xml:space="preserve">8.52360153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62370109558105</t>
   </si>
   <si>
     <t xml:space="preserve">8.64679908752441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60830116271973</t>
+    <t xml:space="preserve">8.60829925537109</t>
   </si>
   <si>
     <t xml:space="preserve">8.7468957901001</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0317850112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11648273468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13188171386719</t>
+    <t xml:space="preserve">9.03178596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11648178100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1318826675415</t>
   </si>
   <si>
     <t xml:space="preserve">8.93168926239014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1549825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37827396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3012752532959</t>
+    <t xml:space="preserve">9.15498161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37827301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30127620697021</t>
   </si>
   <si>
     <t xml:space="preserve">9.32437515258789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33207607269287</t>
+    <t xml:space="preserve">9.33207416534424</t>
   </si>
   <si>
     <t xml:space="preserve">9.27817726135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26277732849121</t>
+    <t xml:space="preserve">9.26277828216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.24737739562988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23967742919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2011775970459</t>
+    <t xml:space="preserve">9.23967933654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20118045806885</t>
   </si>
   <si>
     <t xml:space="preserve">9.10878372192383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87009143829346</t>
+    <t xml:space="preserve">8.87009239196777</t>
   </si>
   <si>
     <t xml:space="preserve">8.84699249267578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95479011535645</t>
+    <t xml:space="preserve">8.95478820800781</t>
   </si>
   <si>
     <t xml:space="preserve">8.73919582366943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63140106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65449810028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79309368133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00098609924316</t>
+    <t xml:space="preserve">8.6314001083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65449905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70839881896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79309463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00098705291748</t>
   </si>
   <si>
     <t xml:space="preserve">9.04718589782715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.055850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.132848739624</t>
+    <t xml:space="preserve">10.0558500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1328449249268</t>
   </si>
   <si>
     <t xml:space="preserve">10.1020498275757</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0173501968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94035243988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82485866546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70166492462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4552698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30897617340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33977508544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41760730743408</t>
+    <t xml:space="preserve">10.017352104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.940354347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82485771179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70166301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45527172088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30897521972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33977794647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41760635375977</t>
   </si>
   <si>
     <t xml:space="preserve">9.72893142700195</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">9.67445087432861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44095706939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43317317962646</t>
+    <t xml:space="preserve">9.44095802307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43317127227783</t>
   </si>
   <si>
     <t xml:space="preserve">9.5032205581665</t>
@@ -1217,31 +1217,31 @@
     <t xml:space="preserve">9.91572856903076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80676555633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64331817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76784801483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86124515533447</t>
+    <t xml:space="preserve">9.80676364898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64331912994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76784706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86124420166016</t>
   </si>
   <si>
     <t xml:space="preserve">10.1336574554443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.437198638916</t>
+    <t xml:space="preserve">10.4371976852417</t>
   </si>
   <si>
     <t xml:space="preserve">10.1881380081177</t>
   </si>
   <si>
-    <t xml:space="preserve">10.048038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9546422958374</t>
+    <t xml:space="preserve">10.048041343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95464420318604</t>
   </si>
   <si>
     <t xml:space="preserve">10.1492233276367</t>
@@ -1253,52 +1253,52 @@
     <t xml:space="preserve">10.1570043563843</t>
   </si>
   <si>
-    <t xml:space="preserve">10.312668800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3904991149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3438024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426195144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4294147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6162109375</t>
+    <t xml:space="preserve">10.3126697540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3905010223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3438005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426176071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4294166564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6162118911743</t>
   </si>
   <si>
     <t xml:space="preserve">10.5928611755371</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6862592697144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6784753799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9508876800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0520658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1143321990967</t>
+    <t xml:space="preserve">10.68625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6784763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9508848190308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0520677566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143312454224</t>
   </si>
   <si>
     <t xml:space="preserve">10.8886203765869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8341388702393</t>
+    <t xml:space="preserve">10.8341398239136</t>
   </si>
   <si>
     <t xml:space="preserve">10.9975852966309</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0832004547119</t>
+    <t xml:space="preserve">11.0831985473633</t>
   </si>
   <si>
     <t xml:space="preserve">11.2933444976807</t>
@@ -1307,16 +1307,16 @@
     <t xml:space="preserve">11.3011283874512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1843786239624</t>
+    <t xml:space="preserve">11.1843795776367</t>
   </si>
   <si>
     <t xml:space="preserve">11.2544298171997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3166933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1610317230225</t>
+    <t xml:space="preserve">11.3166923522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1610307693481</t>
   </si>
   <si>
     <t xml:space="preserve">10.9586696624756</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">10.9158620834351</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7018251419067</t>
+    <t xml:space="preserve">10.7018260955811</t>
   </si>
   <si>
     <t xml:space="preserve">10.5850782394409</t>
@@ -1334,58 +1334,58 @@
     <t xml:space="preserve">10.3048849105835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4566555023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0519332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99355888366699</t>
+    <t xml:space="preserve">10.456657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0519342422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99356174468994</t>
   </si>
   <si>
     <t xml:space="preserve">9.90016078948975</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0636072158813</t>
+    <t xml:space="preserve">10.0636081695557</t>
   </si>
   <si>
     <t xml:space="preserve">10.1180896759033</t>
   </si>
   <si>
-    <t xml:space="preserve">10.262077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5734043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6668014526367</t>
+    <t xml:space="preserve">10.2620782852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5734033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668004989624</t>
   </si>
   <si>
     <t xml:space="preserve">10.5461616516113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8730545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.347827911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2427549362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9469938278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0909833908081</t>
+    <t xml:space="preserve">10.8730554580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3478269577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2427539825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9469947814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0909824371338</t>
   </si>
   <si>
     <t xml:space="preserve">11.1493577957153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0209341049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3050193786621</t>
+    <t xml:space="preserve">11.0209331512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3050174713135</t>
   </si>
   <si>
     <t xml:space="preserve">11.7175264358521</t>
@@ -1394,22 +1394,22 @@
     <t xml:space="preserve">11.5462980270386</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4645738601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1999464035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026563644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.277777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376810073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3595018386841</t>
+    <t xml:space="preserve">11.4645729064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1999444961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2777767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376819610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3595008850098</t>
   </si>
   <si>
     <t xml:space="preserve">11.7642240524292</t>
@@ -1418,13 +1418,13 @@
     <t xml:space="preserve">11.0442848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5967531204224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6239938735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7640895843506</t>
+    <t xml:space="preserve">10.596752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6239929199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7640905380249</t>
   </si>
   <si>
     <t xml:space="preserve">10.6473436355591</t>
@@ -1433,157 +1433,157 @@
     <t xml:space="preserve">10.8574876785278</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8964042663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8263549804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3244762420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.09876537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1298980712891</t>
+    <t xml:space="preserve">10.8964023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8263559341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3244771957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0987663269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1298999786377</t>
   </si>
   <si>
     <t xml:space="preserve">11.4451141357422</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6435852050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6708269119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5929956436157</t>
+    <t xml:space="preserve">11.6435871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.670825958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5929937362671</t>
   </si>
   <si>
     <t xml:space="preserve">11.58131980896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7953567504883</t>
+    <t xml:space="preserve">11.795355796814</t>
   </si>
   <si>
     <t xml:space="preserve">11.8654069900513</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9004306793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0716600418091</t>
+    <t xml:space="preserve">11.900429725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0716590881348</t>
   </si>
   <si>
     <t xml:space="preserve">12.1611652374268</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8926467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9393453598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8381624221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183586120605</t>
+    <t xml:space="preserve">11.8926458358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9393463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8381652832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183576583862</t>
   </si>
   <si>
     <t xml:space="preserve">12.5425386428833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5308628082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5581064224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8344087600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542125701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7604656219482</t>
+    <t xml:space="preserve">12.5308647155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.55810546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8344068527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542135238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7604684829712</t>
   </si>
   <si>
     <t xml:space="preserve">12.663179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7059879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6437215805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.702094078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3597717285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3052864074707</t>
+    <t xml:space="preserve">12.7059860229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6437196731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7020931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355897903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.359769821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.305287361145</t>
   </si>
   <si>
     <t xml:space="preserve">13.4556293487549</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4635429382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1549472808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5496187210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4190587997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4863185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5535764694214</t>
+    <t xml:space="preserve">13.4635410308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1549463272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661298751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5496196746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.419059753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4863176345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5535755157471</t>
   </si>
   <si>
     <t xml:space="preserve">12.1460704803467</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2964115142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0392484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9996852874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.347843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3122386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.395320892334</t>
+    <t xml:space="preserve">12.2964105606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0392475128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9996843338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.347846031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.312237739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953218460083</t>
   </si>
   <si>
     <t xml:space="preserve">12.4230165481567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2726755142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4784049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9007740020752</t>
+    <t xml:space="preserve">12.2726745605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4784069061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9007749557495</t>
   </si>
   <si>
     <t xml:space="preserve">11.9205570220947</t>
@@ -1592,31 +1592,31 @@
     <t xml:space="preserve">11.797908782959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8374710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4111480712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8809928894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9284687042236</t>
+    <t xml:space="preserve">11.8374729156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4111471176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.88099193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9284696578979</t>
   </si>
   <si>
     <t xml:space="preserve">12.5377521514893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4665355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4348850250244</t>
+    <t xml:space="preserve">12.4665374755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4348840713501</t>
   </si>
   <si>
     <t xml:space="preserve">12.3755407333374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5733585357666</t>
+    <t xml:space="preserve">12.573356628418</t>
   </si>
   <si>
     <t xml:space="preserve">12.6089658737183</t>
@@ -1625,46 +1625,46 @@
     <t xml:space="preserve">12.6050100326538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6683111190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9927339553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520782470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6762228012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7355699539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6010522842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5456619262695</t>
+    <t xml:space="preserve">12.6683120727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9927310943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6762237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7355690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.601053237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5456638336182</t>
   </si>
   <si>
     <t xml:space="preserve">12.5575323104858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4546680450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4586238861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2489366531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3201503753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3676261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5961322784424</t>
+    <t xml:space="preserve">12.4546670913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.458625793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2489347457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3201484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3676280975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.596134185791</t>
   </si>
   <si>
     <t xml:space="preserve">11.7623014450073</t>
@@ -1676,19 +1676,19 @@
     <t xml:space="preserve">11.9759454727173</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9324264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0273790359497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8216466903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5328330993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418363571167</t>
+    <t xml:space="preserve">11.9324245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0273780822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.821647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5328321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418354034424</t>
   </si>
   <si>
     <t xml:space="preserve">11.5170068740845</t>
@@ -1700,139 +1700,139 @@
     <t xml:space="preserve">11.5921773910522</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7148246765137</t>
+    <t xml:space="preserve">11.7148265838623</t>
   </si>
   <si>
     <t xml:space="preserve">12.086724281311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8889064788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8928623199463</t>
+    <t xml:space="preserve">11.8889055252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.892861366272</t>
   </si>
   <si>
     <t xml:space="preserve">11.2281923294067</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4339218139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.406229019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3310556411743</t>
+    <t xml:space="preserve">11.4339227676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062252044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3310565948486</t>
   </si>
   <si>
     <t xml:space="preserve">10.9947652816772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9037666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7257328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228647232056</t>
+    <t xml:space="preserve">10.903769493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7257318496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228666305542</t>
   </si>
   <si>
     <t xml:space="preserve">10.6901235580444</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9433326721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9314622879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9354190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.998722076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1451072692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1530179977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0857629776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0066328048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1174116134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7306499481201</t>
+    <t xml:space="preserve">10.9433317184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9314613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9354209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9987201690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1451063156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1530208587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0857620239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0066347122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.117413520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7306509017944</t>
   </si>
   <si>
     <t xml:space="preserve">11.6396551132202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5842657089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4180974960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7266931533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820825576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9482507705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6277856826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5723962783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9601192474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6238279342651</t>
+    <t xml:space="preserve">11.584264755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4180965423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7266941070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9482517242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6277837753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.572395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9601202011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6238288879395</t>
   </si>
   <si>
     <t xml:space="preserve">11.1332387924194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1411514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.188627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3112745285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2400598526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0936737060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0818042755127</t>
+    <t xml:space="preserve">11.1411504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886281967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3112754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2400579452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.093674659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0818033218384</t>
   </si>
   <si>
     <t xml:space="preserve">10.8325519561768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4052648544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2984428405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2628364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.171838760376</t>
+    <t xml:space="preserve">10.4052639007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2984437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2628345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1718378067017</t>
   </si>
   <si>
     <t xml:space="preserve">10.2034902572632</t>
@@ -1844,259 +1844,259 @@
     <t xml:space="preserve">10.3933944702148</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5635204315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6268224716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6307773590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6189088821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5199975967407</t>
+    <t xml:space="preserve">10.5635213851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.626823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6307783126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6189079284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.519998550415</t>
   </si>
   <si>
     <t xml:space="preserve">10.484393119812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2430534362793</t>
+    <t xml:space="preserve">10.2430543899536</t>
   </si>
   <si>
     <t xml:space="preserve">10.1599702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85137367248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75641822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8751106262207</t>
+    <t xml:space="preserve">9.85137176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75641918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87511157989502</t>
   </si>
   <si>
     <t xml:space="preserve">9.7801570892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68019676208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40830326080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58823299407959</t>
+    <t xml:space="preserve">9.68019580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40830421447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58823204040527</t>
   </si>
   <si>
     <t xml:space="preserve">9.45228672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29634666442871</t>
+    <t xml:space="preserve">9.29634571075439</t>
   </si>
   <si>
     <t xml:space="preserve">9.5602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38031578063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71657657623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6605978012085</t>
+    <t xml:space="preserve">9.38031387329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71657371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66059684753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.49666118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78854751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67259120941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50865745544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2287654876709</t>
+    <t xml:space="preserve">8.78854656219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67259311676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50865650177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22876739501953</t>
   </si>
   <si>
     <t xml:space="preserve">8.24876022338867</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9968581199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10881423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20077705383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1807861328125</t>
+    <t xml:space="preserve">7.99685716629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10881519317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20077896118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18078422546387</t>
   </si>
   <si>
     <t xml:space="preserve">7.89129972457886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71216869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71377038955688</t>
+    <t xml:space="preserve">7.71217012405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71376943588257</t>
   </si>
   <si>
     <t xml:space="preserve">7.38109922409058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39389562606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3427152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5490345954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61140775680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59861516952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8849024772644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01285457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05683422088623</t>
+    <t xml:space="preserve">7.39389514923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34271478652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54903411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61140871047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59861373901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88490152359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01285266876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05683326721191</t>
   </si>
   <si>
     <t xml:space="preserve">8.29674053192139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31673336029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24076271057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878986358643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22476863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52065086364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45267772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32073211669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39670276641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53264713287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8245325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58862495422363</t>
+    <t xml:space="preserve">8.31673145294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24076366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16879081726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22476768493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52065181732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45267963409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3207311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39670181274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53264808654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82453346252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58862590789795</t>
   </si>
   <si>
     <t xml:space="preserve">8.70058250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76855373382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75656032562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9324893951416</t>
+    <t xml:space="preserve">8.76855564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75655841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93249034881592</t>
   </si>
   <si>
     <t xml:space="preserve">8.9884672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76455593109131</t>
+    <t xml:space="preserve">8.76455688476562</t>
   </si>
   <si>
     <t xml:space="preserve">8.56463527679443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74456405639648</t>
+    <t xml:space="preserve">8.7445650100708</t>
   </si>
   <si>
     <t xml:space="preserve">8.95248317718506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20838260650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22037696838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43629455566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49226951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55224514007568</t>
+    <t xml:space="preserve">9.20838165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22037601470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43629264831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49227142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55224704742432</t>
   </si>
   <si>
     <t xml:space="preserve">9.59623050689697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75616645812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63221549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61622333526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51626110076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51226329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33233261108398</t>
+    <t xml:space="preserve">9.75616550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63221740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61622047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51626300811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51226234436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3323335647583</t>
   </si>
   <si>
     <t xml:space="preserve">9.39230918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3643217086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48427295684814</t>
+    <t xml:space="preserve">9.36432075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48427200317383</t>
   </si>
   <si>
     <t xml:space="preserve">9.25236415863037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1124210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4202995300293</t>
+    <t xml:space="preserve">9.11242008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42029762268066</t>
   </si>
   <si>
     <t xml:space="preserve">9.84413242340088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89611148834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84813022613525</t>
+    <t xml:space="preserve">9.8961124420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84813117980957</t>
   </si>
   <si>
     <t xml:space="preserve">9.86812305450439</t>
@@ -2105,46 +2105,46 @@
     <t xml:space="preserve">9.98407745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0360584259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3079500198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2039909362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0680446624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82813739776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0080671310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2759628295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1720027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1440143585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95608711242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2559700012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3199453353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0440559387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93609714508057</t>
+    <t xml:space="preserve">10.036057472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3079509735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.203989982605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.068042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82814025878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0080690383911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2759637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.172004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1440153121948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95609092712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2559690475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3199462890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0440549850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93609428405762</t>
   </si>
   <si>
     <t xml:space="preserve">10.0040702819824</t>
@@ -2165,22 +2165,22 @@
     <t xml:space="preserve">10.7917604446411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5598497390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3359403610229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92809867858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90011119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74017429351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60422515869141</t>
+    <t xml:space="preserve">10.5598516464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3359394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92809963226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90011215209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74017333984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60422801971436</t>
   </si>
   <si>
     <t xml:space="preserve">9.44029235839844</t>
@@ -2189,70 +2189,70 @@
     <t xml:space="preserve">9.60822486877441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41230392456055</t>
+    <t xml:space="preserve">9.4123010635376</t>
   </si>
   <si>
     <t xml:space="preserve">9.34033107757568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29234886169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54025363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61222362518311</t>
+    <t xml:space="preserve">9.29234981536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54025077819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61222457885742</t>
   </si>
   <si>
     <t xml:space="preserve">9.96408557891846</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0160636901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0242462158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1755695343018</t>
+    <t xml:space="preserve">10.0160646438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.024245262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1755685806274</t>
   </si>
   <si>
     <t xml:space="preserve">9.8565616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43939590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32487773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16128540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15310287475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01405048370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9854211807251</t>
+    <t xml:space="preserve">9.4393949508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32487869262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16128444671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15310382843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0140495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98541927337646</t>
   </si>
   <si>
     <t xml:space="preserve">8.62960338592529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87499618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08766651153564</t>
+    <t xml:space="preserve">8.87499332427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08766746520996</t>
   </si>
   <si>
     <t xml:space="preserve">8.78910732269287</t>
   </si>
   <si>
-    <t xml:space="preserve">8.797287940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78092765808105</t>
+    <t xml:space="preserve">8.79728698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78092670440674</t>
   </si>
   <si>
     <t xml:space="preserve">9.06312942504883</t>
@@ -2261,25 +2261,25 @@
     <t xml:space="preserve">9.19809341430664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9445219039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83409690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87908458709717</t>
+    <t xml:space="preserve">8.94452285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83409595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87908363342285</t>
   </si>
   <si>
     <t xml:space="preserve">9.05085849761963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29625129699707</t>
+    <t xml:space="preserve">9.29625034332275</t>
   </si>
   <si>
     <t xml:space="preserve">9.39440631866455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25126361846924</t>
+    <t xml:space="preserve">9.25126266479492</t>
   </si>
   <si>
     <t xml:space="preserve">9.14901542663574</t>
@@ -2288,25 +2288,25 @@
     <t xml:space="preserve">9.42303657531738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38213634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41485691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65206909179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42712497711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44757461547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54573059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5416431427002</t>
+    <t xml:space="preserve">9.38213920593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65206813812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42712306976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44757556915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54573154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54164218902588</t>
   </si>
   <si>
     <t xml:space="preserve">9.75431442260742</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">9.66024780273438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80748271942139</t>
+    <t xml:space="preserve">9.80748176574707</t>
   </si>
   <si>
     <t xml:space="preserve">9.98743724822998</t>
@@ -2324,13 +2324,13 @@
     <t xml:space="preserve">9.94244766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83202075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82793045043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45166301727295</t>
+    <t xml:space="preserve">9.83202171325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82793140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4516658782959</t>
   </si>
   <si>
     <t xml:space="preserve">9.28806972503662</t>
@@ -2345,61 +2345,61 @@
     <t xml:space="preserve">9.31260967254639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59072017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5089225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26762104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93225383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71548843383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56416511535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36376285552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29423427581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44555854797363</t>
+    <t xml:space="preserve">9.59072113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50892162322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26762199401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93225288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71548938751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56416702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36376190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2942361831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44555950164795</t>
   </si>
   <si>
     <t xml:space="preserve">8.27787590026855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0095796585083</t>
+    <t xml:space="preserve">8.00958061218262</t>
   </si>
   <si>
     <t xml:space="preserve">8.14209270477295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71838092803955</t>
+    <t xml:space="preserve">7.71838235855103</t>
   </si>
   <si>
     <t xml:space="preserve">7.75764513015747</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05211448669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88851928710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98340368270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08810615539551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96377372741699</t>
+    <t xml:space="preserve">8.05211544036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88852071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98340654373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08810424804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96377325057983</t>
   </si>
   <si>
     <t xml:space="preserve">8.07011127471924</t>
@@ -2408,127 +2408,127 @@
     <t xml:space="preserve">8.12409591674805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21652698516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16335773468018</t>
+    <t xml:space="preserve">8.21652889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16335868835449</t>
   </si>
   <si>
     <t xml:space="preserve">8.10937118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0652027130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86070823669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00467395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21243762969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17153644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41284084320068</t>
+    <t xml:space="preserve">8.06520175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86070919036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00467205047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21243667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17153739929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41283893585205</t>
   </si>
   <si>
     <t xml:space="preserve">8.51099681854248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43737983703613</t>
+    <t xml:space="preserve">8.43738079071045</t>
   </si>
   <si>
     <t xml:space="preserve">8.31468391418457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37194156646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60506248474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44146919250488</t>
+    <t xml:space="preserve">8.3719425201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60506439208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44146823883057</t>
   </si>
   <si>
     <t xml:space="preserve">8.31877422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22061729431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20016765594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97195434570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8574366569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85253000259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72983407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00794506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96213912963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81326532363892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48771524429321</t>
+    <t xml:space="preserve">8.22061824798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20016670227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97195482254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85743713378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85252904891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72983312606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00794410705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96213817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81326675415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48771476745605</t>
   </si>
   <si>
     <t xml:space="preserve">7.5629677772522</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54824304580688</t>
+    <t xml:space="preserve">7.54824352264404</t>
   </si>
   <si>
     <t xml:space="preserve">7.6365852355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50898313522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54333639144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61531782150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88034009933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6725754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7740044593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74292230606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64803838729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60713863372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66276025772095</t>
+    <t xml:space="preserve">7.50898122787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54333734512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61531829833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88034105300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67257499694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77400350570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74292039871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64803695678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60713815689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66275978088379</t>
   </si>
   <si>
     <t xml:space="preserve">7.68239116668701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70202302932739</t>
+    <t xml:space="preserve">7.70202255249023</t>
   </si>
   <si>
     <t xml:space="preserve">7.61859035491943</t>
@@ -2537,43 +2537,43 @@
     <t xml:space="preserve">7.69220781326294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80999517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88524770736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65785312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40591812133789</t>
+    <t xml:space="preserve">7.80999565124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88524723052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65785360336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40591764450073</t>
   </si>
   <si>
     <t xml:space="preserve">8.03739070892334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17644691467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3228645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18380832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19608020782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23697566986084</t>
+    <t xml:space="preserve">8.17644596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32286262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18380737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19607734680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23697662353516</t>
   </si>
   <si>
     <t xml:space="preserve">8.10446548461914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10282897949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09955787658691</t>
+    <t xml:space="preserve">8.10282802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0995569229126</t>
   </si>
   <si>
     <t xml:space="preserve">8.02993392944336</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">7.95865106582642</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0896110534668</t>
+    <t xml:space="preserve">8.08961009979248</t>
   </si>
   <si>
     <t xml:space="preserve">8.04153728485107</t>
@@ -2594,28 +2594,28 @@
     <t xml:space="preserve">8.15094566345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15591812133789</t>
+    <t xml:space="preserve">8.15591907501221</t>
   </si>
   <si>
     <t xml:space="preserve">8.08629512786865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0995569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85587406158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80117034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96693897247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03987884521484</t>
+    <t xml:space="preserve">8.09955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00009536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85587453842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80116844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96694087982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03987979888916</t>
   </si>
   <si>
     <t xml:space="preserve">8.21228122711182</t>
@@ -2624,37 +2624,37 @@
     <t xml:space="preserve">8.24377727508545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26864242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29682540893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53304576873779</t>
+    <t xml:space="preserve">8.26864433288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29682445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53304862976074</t>
   </si>
   <si>
     <t xml:space="preserve">8.44187259674072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4625940322876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40872097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3921422958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37971019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42944145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49574947357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36313343048096</t>
+    <t xml:space="preserve">8.46259498596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40872001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39214324951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37970924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.429443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49574851989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36313247680664</t>
   </si>
   <si>
     <t xml:space="preserve">8.32997894287109</t>
@@ -2663,106 +2663,106 @@
     <t xml:space="preserve">8.37142086029053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48331546783447</t>
+    <t xml:space="preserve">8.48331737518311</t>
   </si>
   <si>
     <t xml:space="preserve">8.71125221252441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69881820678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68224143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60764408111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6034984588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45016193389893</t>
+    <t xml:space="preserve">8.69881629943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68224239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60764503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60350036621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45016288757324</t>
   </si>
   <si>
     <t xml:space="preserve">8.40043163299561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45430660247803</t>
+    <t xml:space="preserve">8.45430564880371</t>
   </si>
   <si>
     <t xml:space="preserve">8.52890300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50403785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47088432312012</t>
+    <t xml:space="preserve">8.50403881072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4708833694458</t>
   </si>
   <si>
     <t xml:space="preserve">8.41700744628906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37556457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05811405181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18741512298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28687953948975</t>
+    <t xml:space="preserve">8.37556648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05811309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18741607666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28687858581543</t>
   </si>
   <si>
     <t xml:space="preserve">7.88073968887329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73154544830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64202976226807</t>
+    <t xml:space="preserve">7.73154735565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64203071594238</t>
   </si>
   <si>
     <t xml:space="preserve">7.80282688140869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90892124176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93212604522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78790760040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83598184585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90063238143921</t>
+    <t xml:space="preserve">7.90892028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93213033676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78790903091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83598232269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90063142776489</t>
   </si>
   <si>
     <t xml:space="preserve">8.00672626495361</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98185920715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80448532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8409538269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13105297088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76967144012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37679624557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27733469009399</t>
+    <t xml:space="preserve">7.98186111450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80448484420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84095478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13105392456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76967239379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37679672241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27733278274536</t>
   </si>
   <si>
     <t xml:space="preserve">7.29391193389893</t>
@@ -2771,22 +2771,22 @@
     <t xml:space="preserve">6.97563171386719</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77007627487183</t>
+    <t xml:space="preserve">6.77007579803467</t>
   </si>
   <si>
     <t xml:space="preserve">6.71868705749512</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75018262863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57612419128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45511198043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08378553390503</t>
+    <t xml:space="preserve">6.75018358230591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57612371444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45511054992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08378505706787</t>
   </si>
   <si>
     <t xml:space="preserve">4.78248500823975</t>
@@ -2795,31 +2795,31 @@
     <t xml:space="preserve">4.65815734863281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56200981140137</t>
+    <t xml:space="preserve">4.56201028823853</t>
   </si>
   <si>
     <t xml:space="preserve">3.87903451919556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97766828536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71989488601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85085415840149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94534277915955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15918731689453</t>
+    <t xml:space="preserve">3.97766780853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71989464759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85085320472717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94534301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15918779373169</t>
   </si>
   <si>
     <t xml:space="preserve">4.32661533355713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26362228393555</t>
+    <t xml:space="preserve">4.26362276077271</t>
   </si>
   <si>
     <t xml:space="preserve">4.43436670303345</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">4.46088981628418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70788812637329</t>
+    <t xml:space="preserve">4.70788860321045</t>
   </si>
   <si>
     <t xml:space="preserve">4.61505651473999</t>
@@ -2837,64 +2837,64 @@
     <t xml:space="preserve">4.59019136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62500286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54543256759644</t>
+    <t xml:space="preserve">4.62500238418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54543352127075</t>
   </si>
   <si>
     <t xml:space="preserve">4.75430393218994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78745889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90681314468384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13226127624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.014564037323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97809457778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9117865562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69131088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.777512550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80735015869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77917003631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54045963287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68136548995972</t>
+    <t xml:space="preserve">4.78745794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90681409835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01456451416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97809410095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91178607940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69131135940552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77751159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80735111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77916955947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54046010971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68136501312256</t>
   </si>
   <si>
     <t xml:space="preserve">4.86702823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90515518188477</t>
+    <t xml:space="preserve">4.90515565872192</t>
   </si>
   <si>
     <t xml:space="preserve">4.89686679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99135637283325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2831130027771</t>
+    <t xml:space="preserve">4.99135589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28311252593994</t>
   </si>
   <si>
     <t xml:space="preserve">5.29968976974487</t>
@@ -2903,31 +2903,31 @@
     <t xml:space="preserve">5.00627565383911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24664258956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04440307617188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12065696716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16375780105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07092618942261</t>
+    <t xml:space="preserve">5.24664306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04440259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12065744400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16375684738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07092571258545</t>
   </si>
   <si>
     <t xml:space="preserve">4.98141002655029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76425075531006</t>
+    <t xml:space="preserve">4.7642502784729</t>
   </si>
   <si>
     <t xml:space="preserve">4.79408884048462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15878486633301</t>
+    <t xml:space="preserve">5.15878391265869</t>
   </si>
   <si>
     <t xml:space="preserve">4.6995997428894</t>
@@ -2936,34 +2936,34 @@
     <t xml:space="preserve">4.85045146942139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61174058914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5984787940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64158010482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71451902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72115039825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83718967437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63494968414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84382057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04606056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2980318069458</t>
+    <t xml:space="preserve">4.611741065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59847974777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64157962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71451950073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72114992141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83718919754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63494920730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8438196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04605960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29803228378296</t>
   </si>
   <si>
     <t xml:space="preserve">5.35273694992065</t>
@@ -2975,7 +2975,7 @@
     <t xml:space="preserve">5.71577405929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61465406417847</t>
+    <t xml:space="preserve">5.61465454101562</t>
   </si>
   <si>
     <t xml:space="preserve">5.53508424758911</t>
@@ -2984,22 +2984,22 @@
     <t xml:space="preserve">5.18365049362183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18862295150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18199253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1306037902832</t>
+    <t xml:space="preserve">5.18862390518188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1819920539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13060331344604</t>
   </si>
   <si>
     <t xml:space="preserve">5.12894582748413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04108762741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14220762252808</t>
+    <t xml:space="preserve">5.04108715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14220714569092</t>
   </si>
   <si>
     <t xml:space="preserve">4.82392740249634</t>
@@ -3008,103 +3008,103 @@
     <t xml:space="preserve">4.88692045211792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76093482971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81398153305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70623064041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8521089553833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76259279251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93002080917358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84547853469849</t>
+    <t xml:space="preserve">4.76093530654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81398248672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70623016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85210847854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76259231567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93002128601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84547805786133</t>
   </si>
   <si>
     <t xml:space="preserve">4.76756525039673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5968222618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62168788909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67804908752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75761890411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76590871810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89355182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7841420173645</t>
+    <t xml:space="preserve">4.59682178497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62168741226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67805004119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75761938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76590824127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89355134963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78414297103882</t>
   </si>
   <si>
     <t xml:space="preserve">4.70291423797607</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66810274124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58024454116821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4907283782959</t>
+    <t xml:space="preserve">4.66810321807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58024406433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49072790145874</t>
   </si>
   <si>
     <t xml:space="preserve">4.27191114425659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19234085083008</t>
+    <t xml:space="preserve">4.19234132766724</t>
   </si>
   <si>
     <t xml:space="preserve">4.08790588378906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28185796737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29346132278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48575496673584</t>
+    <t xml:space="preserve">4.28185749053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29346179962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575592041016</t>
   </si>
   <si>
     <t xml:space="preserve">4.21389150619507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29014587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4360237121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41447496414185</t>
+    <t xml:space="preserve">4.2901463508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43602466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41447448730469</t>
   </si>
   <si>
     <t xml:space="preserve">4.32164239883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27688455581665</t>
+    <t xml:space="preserve">4.27688407897949</t>
   </si>
   <si>
     <t xml:space="preserve">4.23875617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19731473922729</t>
+    <t xml:space="preserve">4.19731426239014</t>
   </si>
   <si>
     <t xml:space="preserve">4.10448265075684</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">4.08624792098999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22383785247803</t>
+    <t xml:space="preserve">4.22383832931519</t>
   </si>
   <si>
     <t xml:space="preserve">4.1757640838623</t>
@@ -3122,43 +3122,43 @@
     <t xml:space="preserve">4.1334924697876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05806684494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08293342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07795906066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00004720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96192002296448</t>
+    <t xml:space="preserve">4.05806636810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08293199539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0779595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00004768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96192026138306</t>
   </si>
   <si>
     <t xml:space="preserve">3.98927211761475</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00087642669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97601056098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83925008773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84422278404236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82598876953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77957224845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74724674224854</t>
+    <t xml:space="preserve">4.00087594985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97600984573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83924984931946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84422254562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82598853111267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77957248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74724698066711</t>
   </si>
   <si>
     <t xml:space="preserve">3.80112242698669</t>
@@ -3167,64 +3167,64 @@
     <t xml:space="preserve">3.95943355560303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96274876594543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8533399105072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60053968429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56075525283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53091621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45880579948425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39747047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53754663467407</t>
+    <t xml:space="preserve">3.96274900436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85334014892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60053944587708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56075477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53091645240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45880603790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39747071266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53754711151123</t>
   </si>
   <si>
     <t xml:space="preserve">3.42399406433105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53174495697021</t>
+    <t xml:space="preserve">3.53174543380737</t>
   </si>
   <si>
     <t xml:space="preserve">3.44139981269836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52097010612488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55578136444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65358686447144</t>
+    <t xml:space="preserve">3.52097034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5557816028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65358638763428</t>
   </si>
   <si>
     <t xml:space="preserve">3.58064746856689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69005584716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66436147689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60302686691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51350975036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60717082023621</t>
+    <t xml:space="preserve">3.69005656242371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66436123847961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60302591323853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51350998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60717153549194</t>
   </si>
   <si>
     <t xml:space="preserve">3.42730951309204</t>
@@ -3239,43 +3239,43 @@
     <t xml:space="preserve">3.71077728271484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61877465248108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63783836364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67099237442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57401657104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47455382347107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3701183795929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17285132408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3750913143158</t>
+    <t xml:space="preserve">3.61877512931824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63783812522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67099213600159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57401609420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47455430030823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37011885643005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37509179115295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55163764953613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63535118103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19399833679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17244863510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57029819488525</t>
+    <t xml:space="preserve">3.63535141944885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19399881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17244911193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57029867172241</t>
   </si>
   <si>
     <t xml:space="preserve">4.63660669326782</t>
@@ -3284,22 +3284,22 @@
     <t xml:space="preserve">4.64655303955078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6763916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74601554870605</t>
+    <t xml:space="preserve">4.67639207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7460150718689</t>
   </si>
   <si>
     <t xml:space="preserve">5.11402654647827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21183061599731</t>
+    <t xml:space="preserve">5.21183109283447</t>
   </si>
   <si>
     <t xml:space="preserve">5.27316665649414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19359588623047</t>
+    <t xml:space="preserve">5.19359683990479</t>
   </si>
   <si>
     <t xml:space="preserve">5.18033409118652</t>
@@ -3308,49 +3308,49 @@
     <t xml:space="preserve">5.39324808120728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73357486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67825031280518</t>
+    <t xml:space="preserve">5.73357439041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67825078964233</t>
   </si>
   <si>
     <t xml:space="preserve">5.6011323928833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61957359313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43683671951294</t>
+    <t xml:space="preserve">5.61957263946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43683624267578</t>
   </si>
   <si>
     <t xml:space="preserve">5.52066135406494</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54748439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58101463317871</t>
+    <t xml:space="preserve">5.5474853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58101415634155</t>
   </si>
   <si>
     <t xml:space="preserve">5.80901622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70339727401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71177959442139</t>
+    <t xml:space="preserve">5.70339775085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71177911758423</t>
   </si>
   <si>
     <t xml:space="preserve">5.71513223648071</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80230951309204</t>
+    <t xml:space="preserve">5.80231046676636</t>
   </si>
   <si>
     <t xml:space="preserve">5.70004510879517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62627983093262</t>
+    <t xml:space="preserve">5.6262788772583</t>
   </si>
   <si>
     <t xml:space="preserve">5.69501543045044</t>
@@ -3359,85 +3359,85 @@
     <t xml:space="preserve">5.6665153503418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72183895111084</t>
+    <t xml:space="preserve">5.721839427948</t>
   </si>
   <si>
     <t xml:space="preserve">5.638014793396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49048471450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47539615631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6279559135437</t>
+    <t xml:space="preserve">5.4904842376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47539663314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62795639038086</t>
   </si>
   <si>
     <t xml:space="preserve">5.58772039413452</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51227903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55251407623291</t>
+    <t xml:space="preserve">5.51227855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55251455307007</t>
   </si>
   <si>
     <t xml:space="preserve">5.47874879837036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67489671707153</t>
+    <t xml:space="preserve">5.67489862442017</t>
   </si>
   <si>
     <t xml:space="preserve">5.97834157943726</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9699592590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93642854690552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82913398742676</t>
+    <t xml:space="preserve">5.96995878219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93642902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82913446426392</t>
   </si>
   <si>
     <t xml:space="preserve">5.99678182601929</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91295862197876</t>
+    <t xml:space="preserve">5.9129581451416</t>
   </si>
   <si>
     <t xml:space="preserve">5.96492910385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65813255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64304447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46198463439941</t>
+    <t xml:space="preserve">5.65813207626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64304399490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46198415756226</t>
   </si>
   <si>
     <t xml:space="preserve">5.27254152297974</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17865800857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24739408493042</t>
+    <t xml:space="preserve">5.1786584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24739456176758</t>
   </si>
   <si>
     <t xml:space="preserve">5.33792448043823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50054311752319</t>
+    <t xml:space="preserve">5.50054359436035</t>
   </si>
   <si>
     <t xml:space="preserve">5.38989496231079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3815131187439</t>
+    <t xml:space="preserve">5.38151359558105</t>
   </si>
   <si>
     <t xml:space="preserve">5.60448503494263</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">5.6933388710022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80733919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92972278594971</t>
+    <t xml:space="preserve">5.80734014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92972230911255</t>
   </si>
   <si>
     <t xml:space="preserve">5.82410478591919</t>
@@ -3461,85 +3461,85 @@
     <t xml:space="preserve">5.90122270584106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95989990234375</t>
+    <t xml:space="preserve">5.95990037918091</t>
   </si>
   <si>
     <t xml:space="preserve">6.31196165084839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32202005386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.179518699646</t>
+    <t xml:space="preserve">6.32202053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17951917648315</t>
   </si>
   <si>
     <t xml:space="preserve">6.03534173965454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06551837921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29351949691772</t>
+    <t xml:space="preserve">6.06551885604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29351997375488</t>
   </si>
   <si>
     <t xml:space="preserve">6.22813701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44440460205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32958745956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24743890762329</t>
+    <t xml:space="preserve">6.44440412521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32958698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24743938446045</t>
   </si>
   <si>
     <t xml:space="preserve">7.41508722305298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53579473495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51903009414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78559064865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02700519561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14435863494873</t>
+    <t xml:space="preserve">7.53579425811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51902914047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78559112548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02700328826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14435768127441</t>
   </si>
   <si>
     <t xml:space="preserve">8.00520992279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11082935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30697727203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3120059967041</t>
+    <t xml:space="preserve">8.1108283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30697631835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31200695037842</t>
   </si>
   <si>
     <t xml:space="preserve">8.10579872131348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12926864624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09741592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99682807922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81576776504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75038433074951</t>
+    <t xml:space="preserve">8.12926959991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0974178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99682903289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81576824188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75038480758667</t>
   </si>
   <si>
     <t xml:space="preserve">7.61961889266968</t>
@@ -3548,94 +3548,94 @@
     <t xml:space="preserve">7.90294551849365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69170713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01526832580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09574127197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05717945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10076904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10915184020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98174047470093</t>
+    <t xml:space="preserve">7.69170618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97168159484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01526927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09574031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0571813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10076999664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10915088653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98174142837524</t>
   </si>
   <si>
     <t xml:space="preserve">7.77720737457275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69506025314331</t>
+    <t xml:space="preserve">7.69505977630615</t>
   </si>
   <si>
     <t xml:space="preserve">7.63973712921143</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62967729568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99850416183472</t>
+    <t xml:space="preserve">7.62967872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99850368499756</t>
   </si>
   <si>
     <t xml:space="preserve">7.70679616928101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68332576751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73865079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39496898651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47041130065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46370601654053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44358730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7000904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53914785385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79229545593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26420450210571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50897169113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57603073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63805961608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98006343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12591743469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20806407928467</t>
+    <t xml:space="preserve">7.68332529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73864984512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39496994018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47041273117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46370649337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44358682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70008993148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53914833068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7922945022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26420402526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50897073745728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5760293006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63806009292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98006296157837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12591648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20806312561035</t>
   </si>
   <si>
     <t xml:space="preserve">8.01359272003174</t>
@@ -3653,10 +3653,10 @@
     <t xml:space="preserve">8.12759399414062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90462064743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85600328445435</t>
+    <t xml:space="preserve">7.90462160110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85600280761719</t>
   </si>
   <si>
     <t xml:space="preserve">7.92976808547974</t>
@@ -3665,25 +3665,25 @@
     <t xml:space="preserve">7.95869731903076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80214357376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82596731185913</t>
+    <t xml:space="preserve">7.80214405059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82596588134766</t>
   </si>
   <si>
     <t xml:space="preserve">8.04548072814941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96039915084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93827676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15268611907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2462797164917</t>
+    <t xml:space="preserve">7.96039867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93827724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15268707275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24627780914307</t>
   </si>
   <si>
     <t xml:space="preserve">8.31604671478271</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">8.20203495025635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17140483856201</t>
+    <t xml:space="preserve">8.17140579223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.11354827880859</t>
@@ -3716,16 +3716,16 @@
     <t xml:space="preserve">7.94848680496216</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81575727462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84468555450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92296171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97571229934692</t>
+    <t xml:space="preserve">7.81575679779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84468603134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92296266555786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97571325302124</t>
   </si>
   <si>
     <t xml:space="preserve">8.02506160736084</t>
@@ -3734,52 +3734,52 @@
     <t xml:space="preserve">8.07100677490234</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8038444519043</t>
+    <t xml:space="preserve">7.80384540557861</t>
   </si>
   <si>
     <t xml:space="preserve">7.80554628372192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82086181640625</t>
+    <t xml:space="preserve">7.82086133956909</t>
   </si>
   <si>
     <t xml:space="preserve">7.97060823440552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96550464630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0216588973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64388799667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52987718582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42607498168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65920305252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63197708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4686164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59964561462402</t>
+    <t xml:space="preserve">7.96550416946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02165985107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64388751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52987623214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42607450485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65920257568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63197612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46861696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59964513778687</t>
   </si>
   <si>
     <t xml:space="preserve">7.46521329879761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25420618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00235939025879</t>
+    <t xml:space="preserve">7.25420713424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00235891342163</t>
   </si>
   <si>
     <t xml:space="preserve">7.12317800521851</t>
@@ -3794,49 +3794,49 @@
     <t xml:space="preserve">7.26441669464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47372198104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40735769271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031831741333</t>
+    <t xml:space="preserve">7.47372150421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40735816955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031736373901</t>
   </si>
   <si>
     <t xml:space="preserve">7.46691465377808</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29674816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35800790786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40565490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30865955352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28313541412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48222923278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4413914680481</t>
+    <t xml:space="preserve">7.29674768447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35800838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4056568145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30866003036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28313493728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48222875595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44138956069946</t>
   </si>
   <si>
     <t xml:space="preserve">7.4856333732605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4958438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30185317993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33418464660645</t>
+    <t xml:space="preserve">7.49584436416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30185222625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3341851234436</t>
   </si>
   <si>
     <t xml:space="preserve">6.99385213851929</t>
@@ -3845,130 +3845,130 @@
     <t xml:space="preserve">6.93769693374634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07042598724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09254837036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15550994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22187519073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33758878707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25761032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34269285202026</t>
+    <t xml:space="preserve">7.07042646408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09254884719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15550947189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22187423706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33758783340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25760936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34269332885742</t>
   </si>
   <si>
     <t xml:space="preserve">7.22527837753296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21166467666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14700126647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09425163269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06362009048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30695819854736</t>
+    <t xml:space="preserve">7.21166563034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14700078964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0942497253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06361961364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30695867538452</t>
   </si>
   <si>
     <t xml:space="preserve">7.25590848922729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3767261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14019584655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87473487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87303304672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23038339614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2882399559021</t>
+    <t xml:space="preserve">7.37672662734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1401948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87473440170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87303352355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23038482666016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28824090957642</t>
   </si>
   <si>
     <t xml:space="preserve">7.32567644119263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57241773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53668308258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59794235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73577880859375</t>
+    <t xml:space="preserve">7.57241821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53668260574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59794473648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73577785491943</t>
   </si>
   <si>
     <t xml:space="preserve">7.72556781768799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93997716903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67792129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79873895645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15609073638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35007953643799</t>
+    <t xml:space="preserve">7.93997859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67792272567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79873991012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15608978271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3500804901123</t>
   </si>
   <si>
     <t xml:space="preserve">8.21054363250732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10333919525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14758205413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40283107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35348415374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45898723602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60618019104004</t>
+    <t xml:space="preserve">8.10333824157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14758110046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40283203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35348224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45898818969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60618114471436</t>
   </si>
   <si>
     <t xml:space="preserve">8.43856716156006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39092063903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56363964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55513191223145</t>
+    <t xml:space="preserve">8.3909215927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56363868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55513095855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.42325115203857</t>
@@ -3977,34 +3977,34 @@
     <t xml:space="preserve">8.19012355804443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19352722167969</t>
+    <t xml:space="preserve">8.193528175354</t>
   </si>
   <si>
     <t xml:space="preserve">8.41474437713623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38241291046143</t>
+    <t xml:space="preserve">8.38241100311279</t>
   </si>
   <si>
     <t xml:space="preserve">8.27520751953125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79336547851562</t>
+    <t xml:space="preserve">8.79336357116699</t>
   </si>
   <si>
     <t xml:space="preserve">9.03585243225098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27834033966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23154449462891</t>
+    <t xml:space="preserve">9.27833938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23154258728027</t>
   </si>
   <si>
     <t xml:space="preserve">8.92524337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83165073394775</t>
+    <t xml:space="preserve">8.83165168762207</t>
   </si>
   <si>
     <t xml:space="preserve">8.73380661010742</t>
@@ -4013,52 +4013,52 @@
     <t xml:space="preserve">8.7125358581543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52960395812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.288818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07611179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2693452835083</t>
+    <t xml:space="preserve">8.52960586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28881931304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07611274719238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26934432983398</t>
   </si>
   <si>
     <t xml:space="preserve">8.21586132049561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31247615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20895957946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62753486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69654512405396</t>
+    <t xml:space="preserve">8.31247806549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20895767211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62753438949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69654607772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.4722580909729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78108692169189</t>
+    <t xml:space="preserve">7.78108644485474</t>
   </si>
   <si>
     <t xml:space="preserve">7.7068977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72932720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84319686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01745223999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91910982131958</t>
+    <t xml:space="preserve">7.72932815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84319639205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0174503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91911029815674</t>
   </si>
   <si>
     <t xml:space="preserve">7.76038265228271</t>
@@ -4070,16 +4070,16 @@
     <t xml:space="preserve">7.62408447265625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87942695617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63616037368774</t>
+    <t xml:space="preserve">7.87942743301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63616180419922</t>
   </si>
   <si>
     <t xml:space="preserve">7.85527324676514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78798675537109</t>
+    <t xml:space="preserve">7.78798723220825</t>
   </si>
   <si>
     <t xml:space="preserve">7.61373233795166</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">7.86217498779297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87597608566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96051692962646</t>
+    <t xml:space="preserve">7.87597703933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96051645278931</t>
   </si>
   <si>
     <t xml:space="preserve">8.02435302734375</t>
@@ -4103,22 +4103,22 @@
     <t xml:space="preserve">8.01055145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9449896812439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25899314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37286186218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43669700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43842315673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45222759246826</t>
+    <t xml:space="preserve">7.94498920440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25899410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37286281585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4366979598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4384241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45222568511963</t>
   </si>
   <si>
     <t xml:space="preserve">8.40909385681152</t>
@@ -4127,46 +4127,46 @@
     <t xml:space="preserve">8.58162307739258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6566743850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67824077606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85076904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06211853027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25189971923828</t>
+    <t xml:space="preserve">8.65667343139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6782398223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85076999664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06211948394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2519006729126</t>
   </si>
   <si>
     <t xml:space="preserve">9.28640747070312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93703269958496</t>
+    <t xml:space="preserve">8.93703460693359</t>
   </si>
   <si>
     <t xml:space="preserve">8.49708366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8895902633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5538272857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37698650360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8385009765625</t>
+    <t xml:space="preserve">8.88958930969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55382633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37698459625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83850193023682</t>
   </si>
   <si>
     <t xml:space="preserve">9.78242969512939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65734577178955</t>
+    <t xml:space="preserve">9.65734481811523</t>
   </si>
   <si>
     <t xml:space="preserve">9.85144138336182</t>
@@ -4175,31 +4175,31 @@
     <t xml:space="preserve">9.86006736755371</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77380275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87732124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97652339935303</t>
+    <t xml:space="preserve">9.7738037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87732028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97652530670166</t>
   </si>
   <si>
     <t xml:space="preserve">10.0800428390503</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92476558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99809169769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2266931533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93770790100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75223731994629</t>
+    <t xml:space="preserve">9.92476749420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99809265136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.22669506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93770694732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75223636627197</t>
   </si>
   <si>
     <t xml:space="preserve">9.44599628448486</t>
@@ -4208,37 +4208,37 @@
     <t xml:space="preserve">9.52363395690918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42442893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60989952087402</t>
+    <t xml:space="preserve">9.4244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32091236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60990047454834</t>
   </si>
   <si>
     <t xml:space="preserve">9.95495891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86869335174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3560905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1447410583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96358680725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2618713378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6241836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9815092086792</t>
+    <t xml:space="preserve">9.86869430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.35608959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1447420120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96358585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2618703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6241827011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9815101623535</t>
   </si>
   <si>
     <t xml:space="preserve">11.1540403366089</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">11.1497268676758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8736772537231</t>
+    <t xml:space="preserve">10.8736791610718</t>
   </si>
   <si>
     <t xml:space="preserve">10.5113677978516</t>
@@ -4256,31 +4256,31 @@
     <t xml:space="preserve">10.7356548309326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9081859588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5724239349365</t>
+    <t xml:space="preserve">10.908185005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5724248886108</t>
   </si>
   <si>
     <t xml:space="preserve">11.6371221542358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9606161117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9951219558716</t>
+    <t xml:space="preserve">11.9606142044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9951229095459</t>
   </si>
   <si>
     <t xml:space="preserve">12.2927350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0123748779297</t>
+    <t xml:space="preserve">12.012375831604</t>
   </si>
   <si>
     <t xml:space="preserve">11.6845684051514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8829774856567</t>
+    <t xml:space="preserve">11.8829765319824</t>
   </si>
   <si>
     <t xml:space="preserve">11.8657245635986</t>
@@ -4289,34 +4289,34 @@
     <t xml:space="preserve">11.9821825027466</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9735565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0727605819702</t>
+    <t xml:space="preserve">11.9735555648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0727596282959</t>
   </si>
   <si>
     <t xml:space="preserve">11.9390497207642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9908084869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5299644470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4135065078735</t>
+    <t xml:space="preserve">11.9908075332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5299634933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4135055541992</t>
   </si>
   <si>
     <t xml:space="preserve">12.8146371841431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9224691390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9914817810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9612874984741</t>
+    <t xml:space="preserve">12.9224681854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9914798736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9612884521484</t>
   </si>
   <si>
     <t xml:space="preserve">12.931095123291</t>
@@ -4325,19 +4325,19 @@
     <t xml:space="preserve">12.5817222595215</t>
   </si>
   <si>
-    <t xml:space="preserve">11.723388671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1374588012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0813856124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7758178710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2841100692749</t>
+    <t xml:space="preserve">11.7233867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1374578475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0813865661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7758188247681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2841091156006</t>
   </si>
   <si>
     <t xml:space="preserve">12.8448314666748</t>
@@ -4346,16 +4346,16 @@
     <t xml:space="preserve">12.6981811523438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6377954483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5385894775391</t>
+    <t xml:space="preserve">12.6377944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5385913848877</t>
   </si>
   <si>
     <t xml:space="preserve">12.0598201751709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1805925369263</t>
+    <t xml:space="preserve">12.180591583252</t>
   </si>
   <si>
     <t xml:space="preserve">12.5989751815796</t>
@@ -4373,61 +4373,61 @@
     <t xml:space="preserve">13.4486837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3667335510254</t>
+    <t xml:space="preserve">13.3667316436768</t>
   </si>
   <si>
     <t xml:space="preserve">13.0216732025146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.19420337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.488579750061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3040437698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5456962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9147644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0861177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.253077507019</t>
+    <t xml:space="preserve">13.1942024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4885787963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3040447235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5456972122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9147663116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0861196517944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2530765533447</t>
   </si>
   <si>
     <t xml:space="preserve">13.7302312850952</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8356790542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.86643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8224973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9630947113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0641489028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0246076583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4094915390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0052738189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8031644821167</t>
+    <t xml:space="preserve">13.8356771469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8664331436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8224983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9630966186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0641479492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0246067047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4094934463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.005274772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.803165435791</t>
   </si>
   <si>
     <t xml:space="preserve">12.6933221817017</t>
@@ -4439,43 +4439,43 @@
     <t xml:space="preserve">11.5641498565674</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3927965164185</t>
+    <t xml:space="preserve">11.3927955627441</t>
   </si>
   <si>
     <t xml:space="preserve">11.6080865859985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6739921569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0720596313477</t>
+    <t xml:space="preserve">11.6739902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0720586776733</t>
   </si>
   <si>
     <t xml:space="preserve">10.7381391525269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9402465820312</t>
+    <t xml:space="preserve">10.9402484893799</t>
   </si>
   <si>
     <t xml:space="preserve">10.9578227996826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2302293777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.063271522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.782075881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.579966545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.966609954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0615119934082</t>
+    <t xml:space="preserve">11.2302303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0632705688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7820749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5799655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9666090011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0615139007568</t>
   </si>
   <si>
     <t xml:space="preserve">9.75834941864014</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">10.7469253540039</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1423568725586</t>
+    <t xml:space="preserve">11.1423578262329</t>
   </si>
   <si>
     <t xml:space="preserve">11.2082614898682</t>
@@ -4493,22 +4493,22 @@
     <t xml:space="preserve">11.1116018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841833114624</t>
+    <t xml:space="preserve">10.984185218811</t>
   </si>
   <si>
     <t xml:space="preserve">10.5404233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7117767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1467514038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1819000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.067663192749</t>
+    <t xml:space="preserve">10.7117757797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1467504501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1818990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0676641464233</t>
   </si>
   <si>
     <t xml:space="preserve">10.8523750305176</t>
@@ -4523,31 +4523,31 @@
     <t xml:space="preserve">11.441125869751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5861177444458</t>
+    <t xml:space="preserve">11.5861186981201</t>
   </si>
   <si>
     <t xml:space="preserve">11.9551868438721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6344480514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6608104705811</t>
+    <t xml:space="preserve">11.634449005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6608095169067</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0896329879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3005275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4147653579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2917423248291</t>
+    <t xml:space="preserve">11.0896320343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3005285263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4147644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2917432785034</t>
   </si>
   <si>
     <t xml:space="preserve">11.5685434341431</t>
@@ -4562,40 +4562,40 @@
     <t xml:space="preserve">11.6827793121338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2829532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2803182601929</t>
+    <t xml:space="preserve">11.2829542160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2803192138672</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704769134521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3945541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2188081741333</t>
+    <t xml:space="preserve">12.3945531845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.218807220459</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913896560669</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0826025009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.029878616333</t>
+    <t xml:space="preserve">12.0826034545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0298776626587</t>
   </si>
   <si>
     <t xml:space="preserve">12.4384899139404</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5527257919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1221466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7398958206177</t>
+    <t xml:space="preserve">12.5527248382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.122145652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.739896774292</t>
   </si>
   <si>
     <t xml:space="preserve">11.7442893981934</t>
@@ -4607,13 +4607,13 @@
     <t xml:space="preserve">12.5790872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5219707489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5175771713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2407741546631</t>
+    <t xml:space="preserve">12.5219697952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5175762176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2407751083374</t>
   </si>
   <si>
     <t xml:space="preserve">11.9288244247437</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">11.9024620056152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7882270812988</t>
+    <t xml:space="preserve">11.7882261276245</t>
   </si>
   <si>
     <t xml:space="preserve">12.126540184021</t>
@@ -4634,13 +4634,13 @@
     <t xml:space="preserve">11.1994743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5377864837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761014938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6564178466797</t>
+    <t xml:space="preserve">11.537787437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8760995864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6564168930054</t>
   </si>
   <si>
     <t xml:space="preserve">12.4604578018188</t>
@@ -4652,52 +4652,52 @@
     <t xml:space="preserve">13.0140619277954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1854152679443</t>
+    <t xml:space="preserve">13.18541431427</t>
   </si>
   <si>
     <t xml:space="preserve">12.7328672409058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1353282928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2451696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8163471221924</t>
+    <t xml:space="preserve">12.135326385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2451686859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8163452148438</t>
   </si>
   <si>
     <t xml:space="preserve">12.5615129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9217939376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2117776870728</t>
+    <t xml:space="preserve">12.9217948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2117767333984</t>
   </si>
   <si>
     <t xml:space="preserve">13.1590538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3216190338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2205638885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5193338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8927974700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4534292221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8005294799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.156418800354</t>
+    <t xml:space="preserve">13.3216171264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2205657958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5193347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8927965164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4534301757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8005285263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1564178466797</t>
   </si>
   <si>
     <t xml:space="preserve">13.9982452392578</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">14.1959609985352</t>
   </si>
   <si>
-    <t xml:space="preserve">14.626540184021</t>
+    <t xml:space="preserve">14.6265411376953</t>
   </si>
   <si>
     <t xml:space="preserve">14.7539567947388</t>
@@ -4724,19 +4724,19 @@
     <t xml:space="preserve">14.055362701416</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9938516616821</t>
+    <t xml:space="preserve">13.9938526153564</t>
   </si>
   <si>
     <t xml:space="preserve">14.6572961807251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7275953292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3101940155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.424430847168</t>
+    <t xml:space="preserve">14.7275943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3101949691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4244337081909</t>
   </si>
   <si>
     <t xml:space="preserve">13.785120010376</t>
@@ -4745,7 +4745,7 @@
     <t xml:space="preserve">14.6908092498779</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3578357696533</t>
+    <t xml:space="preserve">14.3578367233276</t>
   </si>
   <si>
     <t xml:space="preserve">14.446629524231</t>
@@ -4757,16 +4757,16 @@
     <t xml:space="preserve">14.1314134597778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.54430103302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8417587280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954681396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2557249069214</t>
+    <t xml:space="preserve">14.5443019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.841757774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4954652786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2557239532471</t>
   </si>
   <si>
     <t xml:space="preserve">14.0381813049316</t>
@@ -4781,37 +4781,37 @@
     <t xml:space="preserve">13.7806825637817</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6608104705811</t>
+    <t xml:space="preserve">13.6608114242554</t>
   </si>
   <si>
     <t xml:space="preserve">13.5276203155518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9893445968628</t>
+    <t xml:space="preserve">13.9893455505371</t>
   </si>
   <si>
     <t xml:space="preserve">14.0159826278687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7451648712158</t>
+    <t xml:space="preserve">13.7451639175415</t>
   </si>
   <si>
     <t xml:space="preserve">13.6474914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9493885040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1402921676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643878936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7218866348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7796030044556</t>
+    <t xml:space="preserve">13.949387550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1402940750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643888473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7796039581299</t>
   </si>
   <si>
     <t xml:space="preserve">14.6686115264893</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">13.4033117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.793999671936</t>
+    <t xml:space="preserve">13.7940006256104</t>
   </si>
   <si>
     <t xml:space="preserve">14.0071029663086</t>
@@ -4844,13 +4844,13 @@
     <t xml:space="preserve">14.0692586898804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2379655838013</t>
+    <t xml:space="preserve">14.237964630127</t>
   </si>
   <si>
     <t xml:space="preserve">14.4421882629395</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3445177078247</t>
+    <t xml:space="preserve">14.344518661499</t>
   </si>
   <si>
     <t xml:space="preserve">14.2290859222412</t>
@@ -4859,22 +4859,22 @@
     <t xml:space="preserve">14.6597328186035</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2679643630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5176630020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6952505111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4244318008423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2424049377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2690420150757</t>
+    <t xml:space="preserve">15.2679662704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5176639556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6952486038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4244327545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2424058914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.26904296875</t>
   </si>
   <si>
     <t xml:space="preserve">14.2956819534302</t>
@@ -4889,79 +4889,79 @@
     <t xml:space="preserve">14.4288702011108</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1180944442749</t>
+    <t xml:space="preserve">14.1180934906006</t>
   </si>
   <si>
     <t xml:space="preserve">13.6297330856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5498189926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4388275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5409383773804</t>
+    <t xml:space="preserve">13.5498199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4388294219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5409393310547</t>
   </si>
   <si>
     <t xml:space="preserve">13.8872327804565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1225337982178</t>
+    <t xml:space="preserve">14.1225347518921</t>
   </si>
   <si>
     <t xml:space="preserve">14.082576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">14.380033493042</t>
+    <t xml:space="preserve">14.3800344467163</t>
   </si>
   <si>
     <t xml:space="preserve">15.4011545181274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6641712188721</t>
+    <t xml:space="preserve">14.6641721725464</t>
   </si>
   <si>
     <t xml:space="preserve">14.4377508163452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.971586227417</t>
+    <t xml:space="preserve">13.9715852737427</t>
   </si>
   <si>
     <t xml:space="preserve">14.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9227495193481</t>
+    <t xml:space="preserve">13.9227504730225</t>
   </si>
   <si>
     <t xml:space="preserve">14.2646036148071</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3267574310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3711547851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4732675552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5487422943115</t>
+    <t xml:space="preserve">14.3267583847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3711557388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4732656478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5487413406372</t>
   </si>
   <si>
     <t xml:space="preserve">14.00266456604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7140865325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9105091094971</t>
+    <t xml:space="preserve">13.7140855789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9105081558228</t>
   </si>
   <si>
     <t xml:space="preserve">13.0969753265381</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9249067306519</t>
+    <t xml:space="preserve">11.9249057769775</t>
   </si>
   <si>
     <t xml:space="preserve">11.9559841156006</t>
@@ -4976,25 +4976,25 @@
     <t xml:space="preserve">12.1646480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0358972549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.765079498291</t>
+    <t xml:space="preserve">12.0358982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7650785446167</t>
   </si>
   <si>
     <t xml:space="preserve">11.3877086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942588806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8361129760742</t>
+    <t xml:space="preserve">11.4942607879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8361139297485</t>
   </si>
   <si>
     <t xml:space="preserve">11.7739591598511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.609691619873</t>
+    <t xml:space="preserve">11.6096897125244</t>
   </si>
   <si>
     <t xml:space="preserve">11.6318893432617</t>
@@ -5003,25 +5003,25 @@
     <t xml:space="preserve">11.9826221466064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6851654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5386562347412</t>
+    <t xml:space="preserve">11.6851644515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5386571884155</t>
   </si>
   <si>
     <t xml:space="preserve">11.5075798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8183546066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9737434387207</t>
+    <t xml:space="preserve">11.8183555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9737424850464</t>
   </si>
   <si>
     <t xml:space="preserve">11.9337844848633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8405523300171</t>
+    <t xml:space="preserve">11.8405532836914</t>
   </si>
   <si>
     <t xml:space="preserve">11.7828378677368</t>
@@ -5033,46 +5033,46 @@
     <t xml:space="preserve">11.6363286972046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5874929428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5031404495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2678375244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9659423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.894907951355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7439575195312</t>
+    <t xml:space="preserve">11.5874938964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5031385421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2678365707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9659414291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8949069976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7439594268799</t>
   </si>
   <si>
     <t xml:space="preserve">11.02809715271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1168899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0991306304932</t>
+    <t xml:space="preserve">11.1168909072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0991315841675</t>
   </si>
   <si>
     <t xml:space="preserve">10.8771486282349</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7528381347656</t>
+    <t xml:space="preserve">10.7528371810913</t>
   </si>
   <si>
     <t xml:space="preserve">10.8815889358521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8460712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7705984115601</t>
+    <t xml:space="preserve">10.8460702896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7705974578857</t>
   </si>
   <si>
     <t xml:space="preserve">10.9171056747437</t>
@@ -5081,7 +5081,7 @@
     <t xml:space="preserve">10.9526224136353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0713262557983</t>
+    <t xml:space="preserve">11.071325302124</t>
   </si>
   <si>
     <t xml:space="preserve">11.2311182022095</t>
@@ -5093,7 +5093,7 @@
     <t xml:space="preserve">10.8430500030518</t>
   </si>
   <si>
-    <t xml:space="preserve">10.938925743103</t>
+    <t xml:space="preserve">10.9389266967773</t>
   </si>
   <si>
     <t xml:space="preserve">11.1489391326904</t>
@@ -5102,16 +5102,16 @@
     <t xml:space="preserve">10.8476161956787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6558656692505</t>
+    <t xml:space="preserve">10.6558666229248</t>
   </si>
   <si>
     <t xml:space="preserve">10.8795747756958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2722082138062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3452558517456</t>
+    <t xml:space="preserve">11.2722091674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3452548980713</t>
   </si>
   <si>
     <t xml:space="preserve">11.6054878234863</t>
@@ -5129,7 +5129,7 @@
     <t xml:space="preserve">11.6420135498047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9205083847046</t>
+    <t xml:space="preserve">11.9205074310303</t>
   </si>
   <si>
     <t xml:space="preserve">11.8063707351685</t>
@@ -5144,13 +5144,13 @@
     <t xml:space="preserve">11.7972393035889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6374473571777</t>
+    <t xml:space="preserve">11.6374464035034</t>
   </si>
   <si>
     <t xml:space="preserve">11.6922340393066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8291988372803</t>
+    <t xml:space="preserve">11.829197883606</t>
   </si>
   <si>
     <t xml:space="preserve">11.8337640762329</t>
@@ -5165,16 +5165,16 @@
     <t xml:space="preserve">12.5231533050537</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5185880661011</t>
+    <t xml:space="preserve">12.5185871124268</t>
   </si>
   <si>
     <t xml:space="preserve">12.5870695114136</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4820642471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1305208206177</t>
+    <t xml:space="preserve">12.482063293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1305198669434</t>
   </si>
   <si>
     <t xml:space="preserve">12.4501056671143</t>
@@ -5189,10 +5189,10 @@
     <t xml:space="preserve">13.0025291442871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0162267684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9568748474121</t>
+    <t xml:space="preserve">13.016227722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9568758010864</t>
   </si>
   <si>
     <t xml:space="preserve">12.9660053253174</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">13.1577568054199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1668882369995</t>
+    <t xml:space="preserve">13.1668891906738</t>
   </si>
   <si>
     <t xml:space="preserve">13.5184326171875</t>
@@ -5213,19 +5213,19 @@
     <t xml:space="preserve">13.7330093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6553964614868</t>
+    <t xml:space="preserve">13.6553955078125</t>
   </si>
   <si>
     <t xml:space="preserve">13.6143064498901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7010517120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6964845657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8151884078979</t>
+    <t xml:space="preserve">13.7010507583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6964855194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8151874542236</t>
   </si>
   <si>
     <t xml:space="preserve">13.7695331573486</t>
@@ -5234,13 +5234,13 @@
     <t xml:space="preserve">13.6462650299072</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3632049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6599607467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.582347869873</t>
+    <t xml:space="preserve">13.3632040023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6599617004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5823488235474</t>
   </si>
   <si>
     <t xml:space="preserve">13.637134552002</t>
@@ -5267,13 +5267,13 @@
     <t xml:space="preserve">13.9475879669189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9247589111328</t>
+    <t xml:space="preserve">13.9247598648071</t>
   </si>
   <si>
     <t xml:space="preserve">13.7877960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7512722015381</t>
+    <t xml:space="preserve">13.7512712478638</t>
   </si>
   <si>
     <t xml:space="preserve">13.673659324646</t>
@@ -5282,13 +5282,13 @@
     <t xml:space="preserve">13.8380155563354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9612836837769</t>
+    <t xml:space="preserve">13.9612846374512</t>
   </si>
   <si>
     <t xml:space="preserve">13.9293270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4773426055908</t>
+    <t xml:space="preserve">13.4773416519165</t>
   </si>
   <si>
     <t xml:space="preserve">13.6097402572632</t>
@@ -5297,16 +5297,16 @@
     <t xml:space="preserve">13.550389289856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7604026794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6645278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7375745773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.847146987915</t>
+    <t xml:space="preserve">13.760401725769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6645269393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7375755310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8471460342407</t>
   </si>
   <si>
     <t xml:space="preserve">13.7421407699585</t>
@@ -5321,7 +5321,7 @@
     <t xml:space="preserve">13.8425817489624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7786655426025</t>
+    <t xml:space="preserve">13.7786645889282</t>
   </si>
   <si>
     <t xml:space="preserve">13.3951625823975</t>
@@ -5333,31 +5333,31 @@
     <t xml:space="preserve">13.4316873550415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4362516403198</t>
+    <t xml:space="preserve">13.4362525939941</t>
   </si>
   <si>
     <t xml:space="preserve">13.7740993499756</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6827898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2125444412231</t>
+    <t xml:space="preserve">13.682788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2125434875488</t>
   </si>
   <si>
     <t xml:space="preserve">13.3084182739258</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0116624832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3586378097534</t>
+    <t xml:space="preserve">13.011661529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3586387634277</t>
   </si>
   <si>
     <t xml:space="preserve">13.8836708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0069398880005</t>
+    <t xml:space="preserve">14.0069389343262</t>
   </si>
   <si>
     <t xml:space="preserve">13.9567184448242</t>
@@ -5381,7 +5381,7 @@
     <t xml:space="preserve">14.2671728134155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9338912963867</t>
+    <t xml:space="preserve">13.933892250061</t>
   </si>
   <si>
     <t xml:space="preserve">14.0571603775024</t>
@@ -5390,7 +5390,7 @@
     <t xml:space="preserve">14.0982484817505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7969264984131</t>
+    <t xml:space="preserve">13.7969255447388</t>
   </si>
   <si>
     <t xml:space="preserve">14.9383001327515</t>
@@ -5411,16 +5411,16 @@
     <t xml:space="preserve">14.585844039917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6917629241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9063444137573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7008953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7191581726074</t>
+    <t xml:space="preserve">14.6917638778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9063425064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7008962631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7191572189331</t>
   </si>
   <si>
     <t xml:space="preserve">14.1302070617676</t>
@@ -5465,7 +5465,7 @@
     <t xml:space="preserve">14.4331836700439</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5626707077026</t>
+    <t xml:space="preserve">14.5626697540283</t>
   </si>
   <si>
     <t xml:space="preserve">14.3453178405762</t>
@@ -5480,13 +5480,13 @@
     <t xml:space="preserve">14.46555519104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6274137496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7291536331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8725147247314</t>
+    <t xml:space="preserve">14.6274127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.729154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8725156784058</t>
   </si>
   <si>
     <t xml:space="preserve">14.7707748413086</t>
@@ -5501,19 +5501,19 @@
     <t xml:space="preserve">14.7014074325562</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6135406494141</t>
+    <t xml:space="preserve">14.6135416030884</t>
   </si>
   <si>
     <t xml:space="preserve">14.4378070831299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3869380950928</t>
+    <t xml:space="preserve">14.3869390487671</t>
   </si>
   <si>
     <t xml:space="preserve">14.0863428115845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8736133575439</t>
+    <t xml:space="preserve">13.8736143112183</t>
   </si>
   <si>
     <t xml:space="preserve">13.6608858108521</t>
@@ -5528,7 +5528,7 @@
     <t xml:space="preserve">13.4712791442871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4019117355347</t>
+    <t xml:space="preserve">13.4019107818604</t>
   </si>
   <si>
     <t xml:space="preserve">13.4065361022949</t>
@@ -5537,28 +5537,28 @@
     <t xml:space="preserve">13.4204092025757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3464183807373</t>
+    <t xml:space="preserve">13.346417427063</t>
   </si>
   <si>
     <t xml:space="preserve">13.6793832778931</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8551149368286</t>
+    <t xml:space="preserve">13.8551158905029</t>
   </si>
   <si>
     <t xml:space="preserve">13.850492477417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9291095733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8597412109375</t>
+    <t xml:space="preserve">13.9291086196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8597402572632</t>
   </si>
   <si>
     <t xml:space="preserve">13.5822687149048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6100149154663</t>
+    <t xml:space="preserve">13.6100158691406</t>
   </si>
   <si>
     <t xml:space="preserve">13.8921127319336</t>
@@ -5570,10 +5570,10 @@
     <t xml:space="preserve">13.6886329650879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4759035110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6377630233765</t>
+    <t xml:space="preserve">13.4759044647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6377620697021</t>
   </si>
   <si>
     <t xml:space="preserve">13.7903728485107</t>
@@ -5585,7 +5585,7 @@
     <t xml:space="preserve">13.6331386566162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8366174697876</t>
+    <t xml:space="preserve">13.8366184234619</t>
   </si>
   <si>
     <t xml:space="preserve">13.9522314071655</t>
@@ -5594,28 +5594,28 @@
     <t xml:space="preserve">13.8042459487915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8967370986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9095125198364</t>
+    <t xml:space="preserve">13.8967361450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9095115661621</t>
   </si>
   <si>
     <t xml:space="preserve">15.1869831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3303451538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4320821762085</t>
+    <t xml:space="preserve">15.3303442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4320831298828</t>
   </si>
   <si>
     <t xml:space="preserve">15.3395910263062</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2378530502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1731109619141</t>
+    <t xml:space="preserve">15.2378540039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1731100082397</t>
   </si>
   <si>
     <t xml:space="preserve">15.7141809463501</t>
@@ -5627,7 +5627,7 @@
     <t xml:space="preserve">15.963906288147</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0101509094238</t>
+    <t xml:space="preserve">16.0101490020752</t>
   </si>
   <si>
     <t xml:space="preserve">16.0009021759033</t>
@@ -5636,13 +5636,13 @@
     <t xml:space="preserve">16.2275047302246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3801155090332</t>
+    <t xml:space="preserve">16.3801136016846</t>
   </si>
   <si>
     <t xml:space="preserve">16.5280990600586</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4078598022461</t>
+    <t xml:space="preserve">16.4078617095947</t>
   </si>
   <si>
     <t xml:space="preserve">16.352367401123</t>
@@ -5651,7 +5651,7 @@
     <t xml:space="preserve">16.6067161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.639087677002</t>
+    <t xml:space="preserve">16.6390895843506</t>
   </si>
   <si>
     <t xml:space="preserve">16.78244972229</t>
@@ -5684,10 +5684,10 @@
     <t xml:space="preserve">17.1894073486328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9489307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1107921600342</t>
+    <t xml:space="preserve">16.9489326477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1107902526855</t>
   </si>
   <si>
     <t xml:space="preserve">16.9766788482666</t>
@@ -5699,7 +5699,7 @@
     <t xml:space="preserve">16.5096015930176</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5974655151367</t>
+    <t xml:space="preserve">16.5974674224854</t>
   </si>
   <si>
     <t xml:space="preserve">16.3708648681641</t>
@@ -5714,7 +5714,7 @@
     <t xml:space="preserve">16.1396389007568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0471477508545</t>
+    <t xml:space="preserve">16.0471458435059</t>
   </si>
   <si>
     <t xml:space="preserve">14.7800235748291</t>
@@ -5726,7 +5726,7 @@
     <t xml:space="preserve">14.4979267120361</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4054355621338</t>
+    <t xml:space="preserve">14.4054365158081</t>
   </si>
   <si>
     <t xml:space="preserve">14.4239349365234</t>
@@ -5744,22 +5744,22 @@
     <t xml:space="preserve">14.8170204162598</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9465074539185</t>
+    <t xml:space="preserve">14.9465065002441</t>
   </si>
   <si>
     <t xml:space="preserve">14.9326333999634</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8632640838623</t>
+    <t xml:space="preserve">14.8632650375366</t>
   </si>
   <si>
     <t xml:space="preserve">14.9002628326416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9808807373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1421175003052</t>
+    <t xml:space="preserve">14.9808797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1421184539795</t>
   </si>
   <si>
     <t xml:space="preserve">14.8338689804077</t>
@@ -5786,13 +5786,13 @@
     <t xml:space="preserve">14.3169603347778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1699485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0845890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9755144119263</t>
+    <t xml:space="preserve">14.1699495315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0845880508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9755153656006</t>
   </si>
   <si>
     <t xml:space="preserve">14.056134223938</t>
@@ -5816,13 +5816,13 @@
     <t xml:space="preserve">13.5771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6577816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8617010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6198434829712</t>
+    <t xml:space="preserve">13.6577825546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8617000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6198444366455</t>
   </si>
   <si>
     <t xml:space="preserve">13.7621126174927</t>
@@ -5831,7 +5831,7 @@
     <t xml:space="preserve">13.6008749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.752628326416</t>
+    <t xml:space="preserve">13.7526273727417</t>
   </si>
   <si>
     <t xml:space="preserve">13.6625242233276</t>
@@ -5840,7 +5840,7 @@
     <t xml:space="preserve">13.3590183258057</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2973699569702</t>
+    <t xml:space="preserve">13.2973690032959</t>
   </si>
   <si>
     <t xml:space="preserve">13.6103601455688</t>
@@ -5858,13 +5858,13 @@
     <t xml:space="preserve">13.5534524917603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4159269332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5202560424805</t>
+    <t xml:space="preserve">13.3969564437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4159259796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5202569961548</t>
   </si>
   <si>
     <t xml:space="preserve">13.8047943115234</t>
@@ -5873,25 +5873,25 @@
     <t xml:space="preserve">13.7953090667725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7336587905884</t>
+    <t xml:space="preserve">13.7336578369141</t>
   </si>
   <si>
     <t xml:space="preserve">13.9470615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6340713500977</t>
+    <t xml:space="preserve">13.6340703964233</t>
   </si>
   <si>
     <t xml:space="preserve">13.6672668457031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6862373352051</t>
+    <t xml:space="preserve">13.6862363815308</t>
   </si>
   <si>
     <t xml:space="preserve">13.8285045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8854131698608</t>
+    <t xml:space="preserve">13.8854122161865</t>
   </si>
   <si>
     <t xml:space="preserve">12.6761293411255</t>
@@ -5903,7 +5903,7 @@
     <t xml:space="preserve">12.0548896789551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0311794281006</t>
+    <t xml:space="preserve">12.0311784744263</t>
   </si>
   <si>
     <t xml:space="preserve">12.1639623641968</t>
@@ -5912,7 +5912,7 @@
     <t xml:space="preserve">12.0833435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1687049865723</t>
+    <t xml:space="preserve">12.1687040328979</t>
   </si>
   <si>
     <t xml:space="preserve">12.102313041687</t>
@@ -5921,22 +5921,22 @@
     <t xml:space="preserve">12.0406627655029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.140251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1876745223999</t>
+    <t xml:space="preserve">12.1402521133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1876735687256</t>
   </si>
   <si>
     <t xml:space="preserve">11.8557138442993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.95530128479</t>
+    <t xml:space="preserve">11.9553022384644</t>
   </si>
   <si>
     <t xml:space="preserve">11.9837560653687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1829328536987</t>
+    <t xml:space="preserve">12.1829319000244</t>
   </si>
   <si>
     <t xml:space="preserve">11.8414869308472</t>
@@ -5963,7 +5963,7 @@
     <t xml:space="preserve">12.3299427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0691175460815</t>
+    <t xml:space="preserve">12.0691165924072</t>
   </si>
   <si>
     <t xml:space="preserve">12.0359201431274</t>
@@ -5978,7 +5978,7 @@
     <t xml:space="preserve">12.5291185379028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196342468262</t>
+    <t xml:space="preserve">12.5196332931519</t>
   </si>
   <si>
     <t xml:space="preserve">12.6856136322021</t>
@@ -5999,7 +5999,7 @@
     <t xml:space="preserve">13.0365428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4348955154419</t>
+    <t xml:space="preserve">13.4348945617676</t>
   </si>
   <si>
     <t xml:space="preserve">13.4064416885376</t>
@@ -6020,13 +6020,13 @@
     <t xml:space="preserve">13.6909790039062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9565458297729</t>
+    <t xml:space="preserve">13.9565467834473</t>
   </si>
   <si>
     <t xml:space="preserve">14.0087118148804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7384004592896</t>
+    <t xml:space="preserve">13.7384014129639</t>
   </si>
   <si>
     <t xml:space="preserve">13.8000507354736</t>
@@ -6035,7 +6035,7 @@
     <t xml:space="preserve">13.781081199646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9186086654663</t>
+    <t xml:space="preserve">13.918607711792</t>
   </si>
   <si>
     <t xml:space="preserve">14.0798463821411</t>
@@ -6053,10 +6053,10 @@
     <t xml:space="preserve">14.3217029571533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2363414764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3643827438354</t>
+    <t xml:space="preserve">14.2363424301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3643836975098</t>
   </si>
   <si>
     <t xml:space="preserve">14.5777854919434</t>
@@ -6065,13 +6065,13 @@
     <t xml:space="preserve">14.4781980514526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6678895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6590280532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4177932739258</t>
+    <t xml:space="preserve">14.6678886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6590270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4177913665771</t>
   </si>
   <si>
     <t xml:space="preserve">16.346658706665</t>
@@ -6083,7 +6083,7 @@
     <t xml:space="preserve">16.4130516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5078964233398</t>
+    <t xml:space="preserve">16.5078983306885</t>
   </si>
   <si>
     <t xml:space="preserve">16.5553188323975</t>
@@ -6699,6 +6699,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.6550006866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3549995422363</t>
   </si>
 </sst>
 </file>
@@ -72089,7 +72092,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6937731481</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>1736287</v>
@@ -72110,6 +72113,32 @@
         <v>2228</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6925115741</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>1338061</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>17.2700004577637</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>17.4950008392334</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>17.3549995422363</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>2229</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="2233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2234" uniqueCount="2234">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,175 +38,175 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87407064437866</t>
+    <t xml:space="preserve">7.87407159805298</t>
   </si>
   <si>
     <t xml:space="preserve">TEN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88864946365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6990909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48036575317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1960244178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11582708358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07937335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1231164932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07208108901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62734270095825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56901693344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77680349349976</t>
+    <t xml:space="preserve">7.88865041732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69909143447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48036766052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19602680206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11582612991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07937240600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12311697006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07208013534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62734222412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56901550292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77680397033691</t>
   </si>
   <si>
     <t xml:space="preserve">6.3940372467041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6346321105957</t>
+    <t xml:space="preserve">6.63463354110718</t>
   </si>
   <si>
     <t xml:space="preserve">6.80596685409546</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78044939041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88981056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91168403625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82783937454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49246168136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51433420181274</t>
+    <t xml:space="preserve">6.78044891357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88981103897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91168355941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82783889770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49246311187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51433563232422</t>
   </si>
   <si>
     <t xml:space="preserve">7.03562688827515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43413639068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29925584793091</t>
+    <t xml:space="preserve">6.43413591384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29925537109375</t>
   </si>
   <si>
     <t xml:space="preserve">6.80232095718384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95542860031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74034833908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14863443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06114625930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148527145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11947154998779</t>
+    <t xml:space="preserve">6.95542764663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74034976959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14863538742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0611457824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148574829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11947107315063</t>
   </si>
   <si>
     <t xml:space="preserve">6.86064672470093</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54349803924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55443429946899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16686248779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32726049423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50223922729492</t>
+    <t xml:space="preserve">6.54349660873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55443382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16686153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32726001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50223827362061</t>
   </si>
   <si>
     <t xml:space="preserve">7.45120286941528</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61160135269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91781568527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00530242919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71367216110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85948657989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58972835540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82303333282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73554563522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96155977249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81574392318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77929019927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9542670249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7209620475769</t>
+    <t xml:space="preserve">7.61159944534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91781377792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00530433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71367263793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85948753356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58972883224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82303285598755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73554468154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9615592956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8157434463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77928924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95426893234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7209644317627</t>
   </si>
   <si>
     <t xml:space="preserve">7.6699275970459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98342990875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53140211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66263723373413</t>
+    <t xml:space="preserve">7.98343276977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53140020370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6626353263855</t>
   </si>
   <si>
     <t xml:space="preserve">7.64076471328735</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">8.07821273803711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11466693878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17299365997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42088031768799</t>
+    <t xml:space="preserve">8.11466598510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17299461364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42087841033936</t>
   </si>
   <si>
     <t xml:space="preserve">8.41358852386475</t>
@@ -245,49 +245,49 @@
     <t xml:space="preserve">8.63960552215576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80000305175781</t>
+    <t xml:space="preserve">8.8000020980835</t>
   </si>
   <si>
     <t xml:space="preserve">8.80729293823242</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58857154846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47191715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01988697052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97614002227783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39900779724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2459020614624</t>
+    <t xml:space="preserve">8.58856868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47191524505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01988506317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97614097595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39900970458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24590301513672</t>
   </si>
   <si>
     <t xml:space="preserve">8.21673679351807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29693508148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30422782897949</t>
+    <t xml:space="preserve">8.29693698883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30422687530518</t>
   </si>
   <si>
     <t xml:space="preserve">8.45733451843262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64689540863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67605876922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39171886444092</t>
+    <t xml:space="preserve">8.64689350128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67605781555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39171600341797</t>
   </si>
   <si>
     <t xml:space="preserve">8.5666971206665</t>
@@ -296,73 +296,73 @@
     <t xml:space="preserve">8.62655162811279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73129558563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75374126434326</t>
+    <t xml:space="preserve">8.73129653930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75374221801758</t>
   </si>
   <si>
     <t xml:space="preserve">8.9557523727417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.978196144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98567962646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91086101531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80611610412598</t>
+    <t xml:space="preserve">8.97819709777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98567867279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91085815429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80611515045166</t>
   </si>
   <si>
     <t xml:space="preserve">8.67892456054688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64899826049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08294296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53185081481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69645214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52437114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49444389343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28495121002197</t>
+    <t xml:space="preserve">8.64899635314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0829439163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53185272216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69645404815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52436828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49444484710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28495216369629</t>
   </si>
   <si>
     <t xml:space="preserve">9.15776062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34480571746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17272567749023</t>
+    <t xml:space="preserve">9.34480667114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17272472381592</t>
   </si>
   <si>
     <t xml:space="preserve">9.40466022491455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66652488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42710781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80119895935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30739593505859</t>
+    <t xml:space="preserve">9.66652679443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4271068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80119800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30739688873291</t>
   </si>
   <si>
     <t xml:space="preserve">9.04553318023682</t>
@@ -371,181 +371,181 @@
     <t xml:space="preserve">9.14279747009277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61415100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73386192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86853408813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83112621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59918975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32236289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39718151092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50940418243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65904426574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7488260269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47947788238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59170532226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21761608123779</t>
+    <t xml:space="preserve">9.61415195465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73386287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86853504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83112716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59918880462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32236194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39717864990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50940608978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65904521942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74882411956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47947978973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59170722961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21761417388916</t>
   </si>
   <si>
     <t xml:space="preserve">9.37473392486572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18768787384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06798076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16524314880371</t>
+    <t xml:space="preserve">9.18768692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06797885894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16524410247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.0979061126709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82855987548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94826889038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70885276794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57417869567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74625873565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00064182281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19517040252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38969707489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36725425720215</t>
+    <t xml:space="preserve">8.82856178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94827079772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70885181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57417964935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74625968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00064277648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19516944885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38969802856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36725234985352</t>
   </si>
   <si>
     <t xml:space="preserve">9.48696041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70393562316895</t>
+    <t xml:space="preserve">9.70393657684326</t>
   </si>
   <si>
     <t xml:space="preserve">9.65156078338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62911701202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51688957214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45703315734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09042263031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22509765625</t>
+    <t xml:space="preserve">9.62911605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51688861846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45703601837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09042549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22509574890137</t>
   </si>
   <si>
     <t xml:space="preserve">9.2999153137207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10538673400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85848903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66396141052246</t>
+    <t xml:space="preserve">9.10539054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85848617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66395950317383</t>
   </si>
   <si>
     <t xml:space="preserve">8.71633243560791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88093185424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76870536804199</t>
+    <t xml:space="preserve">8.880934715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76870441436768</t>
   </si>
   <si>
     <t xml:space="preserve">8.67144203186035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69388771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90337753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7013692855835</t>
+    <t xml:space="preserve">8.69388866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90337944030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70137119293213</t>
   </si>
   <si>
     <t xml:space="preserve">8.44698715209961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55921363830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35976791381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50192546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64408016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7637882232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74134254455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95083618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63659572601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83860683441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.816162109375</t>
+    <t xml:space="preserve">8.5592155456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35976982116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50192451477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64407730102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76378726959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74134349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95083522796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63659763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83860492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81616115570068</t>
   </si>
   <si>
     <t xml:space="preserve">9.9433536529541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0406150817871</t>
+    <t xml:space="preserve">10.0406169891357</t>
   </si>
   <si>
     <t xml:space="preserve">9.99572467803955</t>
@@ -554,46 +554,46 @@
     <t xml:space="preserve">10.0106897354126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96579647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.063060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77127265930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89846324920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86105442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29243469238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2800369262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6765747070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.616717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8112440109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.938437461853</t>
+    <t xml:space="preserve">9.96579837799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0630617141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77126979827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89846134185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86105537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29243659973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2800350189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6765727996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6167163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8112459182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9384384155273</t>
   </si>
   <si>
     <t xml:space="preserve">10.9309539794922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9159898757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7214651107788</t>
+    <t xml:space="preserve">10.9159908294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7214632034302</t>
   </si>
   <si>
     <t xml:space="preserve">11.1216306686401</t>
@@ -602,40 +602,40 @@
     <t xml:space="preserve">10.8045177459717</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0310258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0687770843506</t>
+    <t xml:space="preserve">11.0310249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0687780380249</t>
   </si>
   <si>
     <t xml:space="preserve">10.8347196578979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6761627197266</t>
+    <t xml:space="preserve">10.6761617660522</t>
   </si>
   <si>
     <t xml:space="preserve">11.3783416748047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8464612960815</t>
+    <t xml:space="preserve">11.8464603424072</t>
   </si>
   <si>
     <t xml:space="preserve">11.740758895874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0352191925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1937761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0805225372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2239780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5561943054199</t>
+    <t xml:space="preserve">12.0352210998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1937770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0805215835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2239799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5561923980713</t>
   </si>
   <si>
     <t xml:space="preserve">12.3749847412109</t>
@@ -647,43 +647,43 @@
     <t xml:space="preserve">12.4202880859375</t>
   </si>
   <si>
-    <t xml:space="preserve">12.314582824707</t>
+    <t xml:space="preserve">12.3145809173584</t>
   </si>
   <si>
     <t xml:space="preserve">12.3674345016479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5410928726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4504880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5939435958862</t>
+    <t xml:space="preserve">12.5410919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4504890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5939426422119</t>
   </si>
   <si>
     <t xml:space="preserve">12.8280038833618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9790096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0016622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8129053115845</t>
+    <t xml:space="preserve">12.9790105819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0016613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8129034042358</t>
   </si>
   <si>
     <t xml:space="preserve">13.0243139266968</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9714593887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9488096237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8808536529541</t>
+    <t xml:space="preserve">12.9714622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9488105773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8808574676514</t>
   </si>
   <si>
     <t xml:space="preserve">12.8657569885254</t>
@@ -698,46 +698,46 @@
     <t xml:space="preserve">12.8204545974731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7600498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5335426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7676019668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6996488571167</t>
+    <t xml:space="preserve">12.7600517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5335416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7676010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.858208656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6996507644653</t>
   </si>
   <si>
     <t xml:space="preserve">12.6618976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9865636825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0092134475708</t>
+    <t xml:space="preserve">12.9865646362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0092115402222</t>
   </si>
   <si>
     <t xml:space="preserve">12.8506546020508</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2164287567139</t>
+    <t xml:space="preserve">12.2164297103882</t>
   </si>
   <si>
     <t xml:space="preserve">12.2088785171509</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1258239746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2843790054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1182737350464</t>
+    <t xml:space="preserve">12.1258230209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2843828201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1182746887207</t>
   </si>
   <si>
     <t xml:space="preserve">12.1484756469727</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">11.8766632080078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0729722976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2541809082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.974817276001</t>
+    <t xml:space="preserve">12.0729713439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.15602684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2541799545288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9748182296753</t>
   </si>
   <si>
     <t xml:space="preserve">11.8540124893188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1862268447876</t>
+    <t xml:space="preserve">12.1862258911133</t>
   </si>
   <si>
     <t xml:space="preserve">12.2390785217285</t>
@@ -770,145 +770,145 @@
     <t xml:space="preserve">11.7860593795776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.725658416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9068641662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6652545928955</t>
+    <t xml:space="preserve">11.7256574630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9068660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6652536392212</t>
   </si>
   <si>
     <t xml:space="preserve">11.5142488479614</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5444488525391</t>
+    <t xml:space="preserve">11.5444507598877</t>
   </si>
   <si>
     <t xml:space="preserve">11.4613962173462</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0989809036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1140804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593809127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0763292312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3330402374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4085426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4991483688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2952909469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1442832946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1669330596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2424354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9932765960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8389110565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7634105682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1333751678467</t>
+    <t xml:space="preserve">11.0989789962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1140794754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593828201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0763282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3330411911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.408543586731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4991474151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2952890396118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1442823410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1669340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2424364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.993275642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8389129638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7634086608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1333742141724</t>
   </si>
   <si>
     <t xml:space="preserve">12.0427703857422</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2013282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1786766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9370670318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.385892868042</t>
+    <t xml:space="preserve">12.2013273239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1786756515503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9370651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3858919143677</t>
   </si>
   <si>
     <t xml:space="preserve">11.4840459823608</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2801866531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3481397628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3556928634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3405923843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066986083984</t>
+    <t xml:space="preserve">11.2801876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3481416702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.35569190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3405914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066967010498</t>
   </si>
   <si>
     <t xml:space="preserve">10.8724708557129</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8573684692383</t>
+    <t xml:space="preserve">10.857367515564</t>
   </si>
   <si>
     <t xml:space="preserve">10.9026718139648</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7894153594971</t>
+    <t xml:space="preserve">10.7894172668457</t>
   </si>
   <si>
     <t xml:space="preserve">10.4949531555176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6535120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.645959854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.661060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8271684646606</t>
+    <t xml:space="preserve">10.6535110473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6459608078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6610612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.827169418335</t>
   </si>
   <si>
     <t xml:space="preserve">10.8800201416016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7441158294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9781742095947</t>
+    <t xml:space="preserve">10.7441139221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.978175163269</t>
   </si>
   <si>
     <t xml:space="preserve">10.7139129638672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8951234817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0183181762695</t>
+    <t xml:space="preserve">10.8951196670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0183191299438</t>
   </si>
   <si>
     <t xml:space="preserve">10.9721183776855</t>
@@ -920,247 +920,247 @@
     <t xml:space="preserve">10.9259185791016</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7642230987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6410312652588</t>
+    <t xml:space="preserve">10.7642250061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6410284042358</t>
   </si>
   <si>
     <t xml:space="preserve">10.6025304794312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3561372756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4793338775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4408359527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4177370071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406444549561</t>
+    <t xml:space="preserve">10.3561401367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4793348312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4408378601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4177389144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406435012817</t>
   </si>
   <si>
     <t xml:space="preserve">10.4023380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7873239517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4947357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5409326553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3176412582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3715391159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2791442871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2868404388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3330392837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5101346969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8335218429565</t>
+    <t xml:space="preserve">10.7873249053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4947366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5409336090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3176403045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3715400695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2791423797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2868413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3330402374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5101337432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8335247039795</t>
   </si>
   <si>
     <t xml:space="preserve">10.8566217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7103290557861</t>
+    <t xml:space="preserve">10.7103261947632</t>
   </si>
   <si>
     <t xml:space="preserve">10.6179304122925</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3407392501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4716367721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7796239852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9105205535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0106163024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9413185119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7565259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5255336761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6256294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3099403381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0943479537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99425220489502</t>
+    <t xml:space="preserve">10.3407411575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4716358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7796258926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9105195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0106172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9413175582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7565269470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5255327224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6256303787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3099412918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0943470001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99425315856934</t>
   </si>
   <si>
     <t xml:space="preserve">9.27047634124756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34747409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2088794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29357624053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16268062591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22427940368652</t>
+    <t xml:space="preserve">9.3474760055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20888137817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29357528686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16268157958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22428035736084</t>
   </si>
   <si>
     <t xml:space="preserve">8.9778881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00868511199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96248912811279</t>
+    <t xml:space="preserve">9.00868701934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96249008178711</t>
   </si>
   <si>
     <t xml:space="preserve">8.92399024963379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87779140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80079364776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85469245910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82389259338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78539371490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72379589080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63909912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52360343933105</t>
+    <t xml:space="preserve">8.87779235839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80079650878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85469055175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82389354705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78539562225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72379493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63909816741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52360439300537</t>
   </si>
   <si>
     <t xml:space="preserve">8.62370014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6467981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60830116271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7468957901001</t>
+    <t xml:space="preserve">8.64679908752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60830020904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74689483642578</t>
   </si>
   <si>
     <t xml:space="preserve">9.0317850112915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11648368835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13188076019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93169021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15498161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37827682495117</t>
+    <t xml:space="preserve">9.11648178100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1318826675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93168926239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15497970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37827396392822</t>
   </si>
   <si>
     <t xml:space="preserve">9.30127620697021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32437515258789</t>
+    <t xml:space="preserve">9.32437610626221</t>
   </si>
   <si>
     <t xml:space="preserve">9.33207511901855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27817821502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26277637481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24737930297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23967933654785</t>
+    <t xml:space="preserve">9.27817535400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26277732849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24737739562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23967838287354</t>
   </si>
   <si>
     <t xml:space="preserve">9.20117950439453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10878467559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87008953094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84699153900146</t>
+    <t xml:space="preserve">9.1087818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87009143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84699058532715</t>
   </si>
   <si>
     <t xml:space="preserve">8.95478820800781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7391939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6314001083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65449905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70839595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79309558868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00098609924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04718399047852</t>
+    <t xml:space="preserve">8.73919677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63140106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65449810028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70839786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79309272766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00098705291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04718494415283</t>
   </si>
   <si>
     <t xml:space="preserve">10.0558500289917</t>
@@ -1175,34 +1175,34 @@
     <t xml:space="preserve">10.0173511505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94035339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82486057281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70166301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45526885986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30897521972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33977603912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41760635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7289342880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6744499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44095802307129</t>
+    <t xml:space="preserve">9.94035625457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82485866546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70166110992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4552698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30897617340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33977699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4176082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72893238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67444801330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44095611572266</t>
   </si>
   <si>
     <t xml:space="preserve">9.43317222595215</t>
@@ -1214,160 +1214,160 @@
     <t xml:space="preserve">9.69779968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91572666168213</t>
+    <t xml:space="preserve">9.91572856903076</t>
   </si>
   <si>
     <t xml:space="preserve">9.8067626953125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64331912994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76784801483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86124610900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.437198638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1881370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0480394363403</t>
+    <t xml:space="preserve">9.64331817626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76784706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86124801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1336574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4371976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.188138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.048041343689</t>
   </si>
   <si>
     <t xml:space="preserve">9.95464324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1492223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0324773788452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1570043563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3126668930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3905000686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3438014984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.242618560791</t>
+    <t xml:space="preserve">10.1492214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0324745178223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1570062637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.312668800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3905010223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3438005447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426195144653</t>
   </si>
   <si>
     <t xml:space="preserve">10.4294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6162099838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5928611755371</t>
+    <t xml:space="preserve">10.6162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5928621292114</t>
   </si>
   <si>
     <t xml:space="preserve">10.6862592697144</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6784753799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9508848190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0520677566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.114333152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8886213302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8341379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9975843429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0831985473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2933435440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3011274337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.184380531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2544298171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3166952133179</t>
+    <t xml:space="preserve">10.6784772872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9508867263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0520668029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143321990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8886203765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8341388702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9975852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0832004547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2933444976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3011293411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1843776702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2544288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3166933059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.1610307693481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9586706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9158601760864</t>
+    <t xml:space="preserve">10.9586696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9158620834351</t>
   </si>
   <si>
     <t xml:space="preserve">10.7018260955811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5850801467896</t>
+    <t xml:space="preserve">10.5850791931152</t>
   </si>
   <si>
     <t xml:space="preserve">10.3048849105835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.456657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0519323348999</t>
+    <t xml:space="preserve">10.4566564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0519342422485</t>
   </si>
   <si>
     <t xml:space="preserve">9.99355983734131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90016078948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0636081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1180906295776</t>
+    <t xml:space="preserve">9.90016269683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0636072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1180896759033</t>
   </si>
   <si>
     <t xml:space="preserve">10.262077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5734033584595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6667995452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.546160697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8730564117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3478269577026</t>
+    <t xml:space="preserve">10.5734014511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668014526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.54616355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8730545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3478260040283</t>
   </si>
   <si>
     <t xml:space="preserve">11.2427530288696</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">11.0909833908081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1493539810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0209341049194</t>
+    <t xml:space="preserve">11.1493558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0209331512451</t>
   </si>
   <si>
     <t xml:space="preserve">11.3050184249878</t>
@@ -1391,43 +1391,43 @@
     <t xml:space="preserve">11.7175254821777</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5462961196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4645738601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1999473571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1026573181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2777786254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376838684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3595027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7642240524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.044282913208</t>
+    <t xml:space="preserve">11.5462970733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4645729064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1999454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1026563644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.277777671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376810073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3594999313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7642230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0442838668823</t>
   </si>
   <si>
     <t xml:space="preserve">10.5967531204224</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6239938735962</t>
+    <t xml:space="preserve">10.6239948272705</t>
   </si>
   <si>
     <t xml:space="preserve">10.7640905380249</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6473445892334</t>
+    <t xml:space="preserve">10.6473436355591</t>
   </si>
   <si>
     <t xml:space="preserve">10.8574886322021</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">10.8964042663574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8263559341431</t>
+    <t xml:space="preserve">10.8263540267944</t>
   </si>
   <si>
     <t xml:space="preserve">11.3244771957397</t>
@@ -1445,109 +1445,109 @@
     <t xml:space="preserve">11.09876537323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1298971176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451150894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6435890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.670825958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5929956436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5813217163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8654069900513</t>
+    <t xml:space="preserve">11.1298999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4451169967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6435871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6708269119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5929946899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.58131980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8654050827026</t>
   </si>
   <si>
     <t xml:space="preserve">11.900429725647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0716581344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1611642837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8926458358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9393444061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8381643295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183576583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5425395965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5308647155762</t>
+    <t xml:space="preserve">12.0716609954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1611652374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8926467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9393453598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8381633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183595657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.542537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5308637619019</t>
   </si>
   <si>
     <t xml:space="preserve">12.5581064224243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8344058990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5542135238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7604656219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6631774902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7059869766235</t>
+    <t xml:space="preserve">12.8344078063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5542125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7604675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6631784439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7059860229492</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.702094078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3597688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.305287361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4556293487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4635438919067</t>
+    <t xml:space="preserve">12.7020931243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355878829956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3597707748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3052864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4556312561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4635400772095</t>
   </si>
   <si>
     <t xml:space="preserve">13.1549444198608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8661308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.549617767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.419059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4863166809082</t>
+    <t xml:space="preserve">12.8661298751831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5496206283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4190587997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4863185882568</t>
   </si>
   <si>
     <t xml:space="preserve">12.5535764694214</t>
@@ -1559,31 +1559,31 @@
     <t xml:space="preserve">12.2964105606079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0392484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9996852874756</t>
+    <t xml:space="preserve">12.0392475128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9996824264526</t>
   </si>
   <si>
     <t xml:space="preserve">12.3478441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3122386932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.395320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4230175018311</t>
+    <t xml:space="preserve">12.312237739563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953218460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4230146408081</t>
   </si>
   <si>
     <t xml:space="preserve">12.2726736068726</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4784059524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9007768630981</t>
+    <t xml:space="preserve">12.4784049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9007730484009</t>
   </si>
   <si>
     <t xml:space="preserve">11.9205551147461</t>
@@ -1607,85 +1607,85 @@
     <t xml:space="preserve">12.5377511978149</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4665374755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4348850250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3755397796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5733585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6089658737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6050081253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6683111190796</t>
+    <t xml:space="preserve">12.4665355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4348840713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3755388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5733575820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6089668273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6050090789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6683120727539</t>
   </si>
   <si>
     <t xml:space="preserve">12.9927349090576</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0520792007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6762247085571</t>
+    <t xml:space="preserve">13.0520801544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6762256622314</t>
   </si>
   <si>
     <t xml:space="preserve">12.7355690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">12.601053237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5456638336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5575313568115</t>
+    <t xml:space="preserve">12.6010522842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5456619262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5575332641602</t>
   </si>
   <si>
     <t xml:space="preserve">12.4546670913696</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4586219787598</t>
+    <t xml:space="preserve">12.4586238861084</t>
   </si>
   <si>
     <t xml:space="preserve">12.2489337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3201503753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3676271438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.596134185791</t>
+    <t xml:space="preserve">12.3201494216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3676261901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5961332321167</t>
   </si>
   <si>
     <t xml:space="preserve">11.762300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7702140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9759464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9324264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0273761749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.821647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5328311920166</t>
+    <t xml:space="preserve">11.7702150344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9759454727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9324245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0273780822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8216466903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5328321456909</t>
   </si>
   <si>
     <t xml:space="preserve">11.4418344497681</t>
@@ -1700,49 +1700,49 @@
     <t xml:space="preserve">11.5921754837036</t>
   </si>
   <si>
-    <t xml:space="preserve">11.714825630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.086724281311</t>
+    <t xml:space="preserve">11.7148237228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0867233276367</t>
   </si>
   <si>
     <t xml:space="preserve">11.8889055252075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8928623199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2281904220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4339227676392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062280654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3310546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9947652816772</t>
+    <t xml:space="preserve">11.8928632736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2281913757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4339218139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062261581421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3310556411743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9947643280029</t>
   </si>
   <si>
     <t xml:space="preserve">10.9037685394287</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7257308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228666305542</t>
+    <t xml:space="preserve">10.7257318496704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228656768799</t>
   </si>
   <si>
     <t xml:space="preserve">10.6901245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9433307647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9314622879028</t>
+    <t xml:space="preserve">10.9433317184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9314632415771</t>
   </si>
   <si>
     <t xml:space="preserve">10.9354190826416</t>
@@ -1751,85 +1751,85 @@
     <t xml:space="preserve">10.9987230300903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1451082229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1530208587646</t>
+    <t xml:space="preserve">11.1451072692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.153018951416</t>
   </si>
   <si>
     <t xml:space="preserve">11.0857620239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0066347122192</t>
+    <t xml:space="preserve">11.0066337585449</t>
   </si>
   <si>
     <t xml:space="preserve">11.1174125671387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7306518554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6396541595459</t>
+    <t xml:space="preserve">11.7306509017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6396532058716</t>
   </si>
   <si>
     <t xml:space="preserve">11.5842657089233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4180974960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.72669506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7820835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9482517242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6277847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5723972320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9601182937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6238288879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1332368850708</t>
+    <t xml:space="preserve">11.4180955886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.726692199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7820816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9482498168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6277837753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5723934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9601211547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6238279342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1332378387451</t>
   </si>
   <si>
     <t xml:space="preserve">11.1411514282227</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1886281967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3112754821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2400598526001</t>
+    <t xml:space="preserve">11.188627243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3112726211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2400617599487</t>
   </si>
   <si>
     <t xml:space="preserve">11.0936737060547</t>
   </si>
   <si>
-    <t xml:space="preserve">11.081805229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8325519561768</t>
+    <t xml:space="preserve">11.0818042755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8325548171997</t>
   </si>
   <si>
     <t xml:space="preserve">10.4052648544312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2984447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2628345489502</t>
+    <t xml:space="preserve">10.2984437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2628355026245</t>
   </si>
   <si>
     <t xml:space="preserve">10.171838760376</t>
@@ -1838,16 +1838,16 @@
     <t xml:space="preserve">10.2034902572632</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0927104949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3933954238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5635213851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6268224716187</t>
+    <t xml:space="preserve">10.0927124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3933973312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5635223388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.626823425293</t>
   </si>
   <si>
     <t xml:space="preserve">10.6307792663574</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">10.6189088821411</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5199995040894</t>
+    <t xml:space="preserve">10.520001411438</t>
   </si>
   <si>
     <t xml:space="preserve">10.484393119812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2430534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1599702835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85137462615967</t>
+    <t xml:space="preserve">10.243052482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1599712371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85137176513672</t>
   </si>
   <si>
     <t xml:space="preserve">9.75641918182373</t>
@@ -1877,115 +1877,115 @@
     <t xml:space="preserve">9.87511157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78015804290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68019485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40830612182617</t>
+    <t xml:space="preserve">9.7801570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68019676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40830421447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.58823299407959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45228576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29634761810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5602445602417</t>
+    <t xml:space="preserve">9.45228672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29634857177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56024360656738</t>
   </si>
   <si>
     <t xml:space="preserve">9.38031482696533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71657371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66059875488281</t>
+    <t xml:space="preserve">8.71657466888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66059684753418</t>
   </si>
   <si>
     <t xml:space="preserve">8.49666213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78854846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67259216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50866031646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22876930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24875736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99685764312744</t>
+    <t xml:space="preserve">8.78854560852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67259311676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50865745544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22876644134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24875926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99685668945312</t>
   </si>
   <si>
     <t xml:space="preserve">8.10881519317627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20077896118164</t>
+    <t xml:space="preserve">8.20077705383301</t>
   </si>
   <si>
     <t xml:space="preserve">8.18078517913818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89130020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7121696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71376991271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38110113143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39389562606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3427152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5490345954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61140966415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59861469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88490152359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01285362243652</t>
+    <t xml:space="preserve">7.8912992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71217012405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71376943588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38109827041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39389657974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34271574020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54903364181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61140918731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59861516952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88490200042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01285266876221</t>
   </si>
   <si>
     <t xml:space="preserve">8.05683517456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29673957824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31673145294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24076271057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16879081726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22476768493652</t>
+    <t xml:space="preserve">8.29674053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31673336029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24076080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878890991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22476959228516</t>
   </si>
   <si>
     <t xml:space="preserve">8.52065277099609</t>
@@ -1994,19 +1994,19 @@
     <t xml:space="preserve">8.45267963409424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3207311630249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39670085906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53264904022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82453346252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58862495422363</t>
+    <t xml:space="preserve">8.32073020935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39669990539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53264617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8245325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58862590789795</t>
   </si>
   <si>
     <t xml:space="preserve">8.70058155059814</t>
@@ -2015,13 +2015,13 @@
     <t xml:space="preserve">8.7685546875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75655841827393</t>
+    <t xml:space="preserve">8.75655937194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.93249130249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98846912384033</t>
+    <t xml:space="preserve">8.98846817016602</t>
   </si>
   <si>
     <t xml:space="preserve">8.76455593109131</t>
@@ -2033,22 +2033,22 @@
     <t xml:space="preserve">8.74456405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95248222351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20838260650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22037792205811</t>
+    <t xml:space="preserve">8.95248413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20838356018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22037601470947</t>
   </si>
   <si>
     <t xml:space="preserve">9.43629360198975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49226951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55224609375</t>
+    <t xml:space="preserve">9.49227046966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55224704742432</t>
   </si>
   <si>
     <t xml:space="preserve">9.59623050689697</t>
@@ -2057,112 +2057,112 @@
     <t xml:space="preserve">9.75616645812988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63221549987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61622047424316</t>
+    <t xml:space="preserve">9.63221645355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61622142791748</t>
   </si>
   <si>
     <t xml:space="preserve">9.51626110076904</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51226425170898</t>
+    <t xml:space="preserve">9.51226329803467</t>
   </si>
   <si>
     <t xml:space="preserve">9.3323335647583</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39231014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3643217086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48427295684814</t>
+    <t xml:space="preserve">9.39230918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36432075500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48427391052246</t>
   </si>
   <si>
     <t xml:space="preserve">9.25236511230469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11242008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42029857635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84413242340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89611148834229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84813117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86812305450439</t>
+    <t xml:space="preserve">9.1124210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4202995300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8441333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8961124420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84813022613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86812400817871</t>
   </si>
   <si>
     <t xml:space="preserve">9.98407745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.036057472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3079500198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.203989982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0680456161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82813739776611</t>
+    <t xml:space="preserve">10.0360584259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3079509735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2039918899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0680446624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82813835144043</t>
   </si>
   <si>
     <t xml:space="preserve">10.0080671310425</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2759618759155</t>
+    <t xml:space="preserve">10.2759637832642</t>
   </si>
   <si>
     <t xml:space="preserve">10.1720037460327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1440153121948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95608997344971</t>
+    <t xml:space="preserve">10.1440143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95608711242676</t>
   </si>
   <si>
     <t xml:space="preserve">10.255970954895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3199453353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0440549850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93609523773193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0040683746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0560464859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3959150314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5278635025024</t>
+    <t xml:space="preserve">10.3199443817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0440540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93609619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0040702819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0560493469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3959169387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5278644561768</t>
   </si>
   <si>
     <t xml:space="preserve">10.4279022216797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7917604446411</t>
+    <t xml:space="preserve">10.7917613983154</t>
   </si>
   <si>
     <t xml:space="preserve">10.559850692749</t>
@@ -2174,7 +2174,7 @@
     <t xml:space="preserve">9.92809867858887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90011024475098</t>
+    <t xml:space="preserve">9.90011119842529</t>
   </si>
   <si>
     <t xml:space="preserve">9.74017333984375</t>
@@ -2183,25 +2183,25 @@
     <t xml:space="preserve">9.60422611236572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4402904510498</t>
+    <t xml:space="preserve">9.44029140472412</t>
   </si>
   <si>
     <t xml:space="preserve">9.60822582244873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41230392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34032917022705</t>
+    <t xml:space="preserve">9.41230201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34033012390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.29234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54025268554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61222362518311</t>
+    <t xml:space="preserve">9.54025459289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61222457885742</t>
   </si>
   <si>
     <t xml:space="preserve">9.96408653259277</t>
@@ -2213,67 +2213,67 @@
     <t xml:space="preserve">10.0242462158203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1755695343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8565616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43939399719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32488059997559</t>
+    <t xml:space="preserve">10.1755704879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85655975341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32487964630127</t>
   </si>
   <si>
     <t xml:space="preserve">9.16128540039062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15310478210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01405048370361</t>
+    <t xml:space="preserve">9.15310382843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01405143737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.98542022705078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62960338592529</t>
+    <t xml:space="preserve">8.62960243225098</t>
   </si>
   <si>
     <t xml:space="preserve">8.8749942779541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08766651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78910636901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79728698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78092765808105</t>
+    <t xml:space="preserve">9.08766555786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78910732269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.797287940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78092575073242</t>
   </si>
   <si>
     <t xml:space="preserve">9.0631275177002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19809436798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9445219039917</t>
+    <t xml:space="preserve">9.19809150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94452285766602</t>
   </si>
   <si>
     <t xml:space="preserve">8.83409595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87908554077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.050856590271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29624938964844</t>
+    <t xml:space="preserve">8.87908458709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05085754394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29625034332275</t>
   </si>
   <si>
     <t xml:space="preserve">9.39440631866455</t>
@@ -2282,22 +2282,22 @@
     <t xml:space="preserve">9.25126171112061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14901638031006</t>
+    <t xml:space="preserve">9.14901542663574</t>
   </si>
   <si>
     <t xml:space="preserve">9.42303466796875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38213634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41485691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65206909179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42712593078613</t>
+    <t xml:space="preserve">9.3821382522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41485595703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65206813812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42712497711182</t>
   </si>
   <si>
     <t xml:space="preserve">9.44757556915283</t>
@@ -2309,40 +2309,40 @@
     <t xml:space="preserve">9.54164218902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75431442260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66024684906006</t>
+    <t xml:space="preserve">9.75431537628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66024780273438</t>
   </si>
   <si>
     <t xml:space="preserve">9.80748271942139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98743534088135</t>
+    <t xml:space="preserve">9.98743438720703</t>
   </si>
   <si>
     <t xml:space="preserve">9.94244766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83202171325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82793235778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45166492462158</t>
+    <t xml:space="preserve">9.83202075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82793140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4516658782959</t>
   </si>
   <si>
     <t xml:space="preserve">9.28806972503662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12038516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24308300018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3126106262207</t>
+    <t xml:space="preserve">9.12038612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24308204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31260967254639</t>
   </si>
   <si>
     <t xml:space="preserve">9.59072017669678</t>
@@ -2354,46 +2354,46 @@
     <t xml:space="preserve">9.26762008666992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93225288391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71549034118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56416606903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36376190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29423522949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44556045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787494659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00958156585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14209175109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71838188171387</t>
+    <t xml:space="preserve">8.93225193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71548843383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56416511535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36376285552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29423427581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44555950164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787399291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00958061218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14209079742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71838283538818</t>
   </si>
   <si>
     <t xml:space="preserve">7.75764513015747</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05211353302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88852024078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98340606689453</t>
+    <t xml:space="preserve">8.05211448669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88852214813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98340511322021</t>
   </si>
   <si>
     <t xml:space="preserve">8.08810424804688</t>
@@ -2402,16 +2402,16 @@
     <t xml:space="preserve">7.96377325057983</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07010936737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12409687042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21652698516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16335964202881</t>
+    <t xml:space="preserve">8.07011032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12409782409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21652603149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16335868835449</t>
   </si>
   <si>
     <t xml:space="preserve">8.10937213897705</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">7.86070919036865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00467395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21243762969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17153835296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41283893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51099681854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4373779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3146858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37194156646729</t>
+    <t xml:space="preserve">8.00467205047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21243572235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17153930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41283988952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5109977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43738079071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31468391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3719425201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.60506439208984</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">8.22061634063721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20016670227051</t>
+    <t xml:space="preserve">8.20016765594482</t>
   </si>
   <si>
     <t xml:space="preserve">7.97195291519165</t>
@@ -2468,22 +2468,22 @@
     <t xml:space="preserve">7.85743713378906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85253047943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72983360290527</t>
+    <t xml:space="preserve">7.85253143310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72983312606812</t>
   </si>
   <si>
     <t xml:space="preserve">8.00794410705566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96213674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81326770782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48771476745605</t>
+    <t xml:space="preserve">7.96213865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81326675415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48771572113037</t>
   </si>
   <si>
     <t xml:space="preserve">7.56296825408936</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">7.5482439994812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63658475875854</t>
+    <t xml:space="preserve">7.63658571243286</t>
   </si>
   <si>
     <t xml:space="preserve">7.50898122787476</t>
@@ -2501,19 +2501,19 @@
     <t xml:space="preserve">7.54333639144897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.615318775177</t>
+    <t xml:space="preserve">7.61531829833984</t>
   </si>
   <si>
     <t xml:space="preserve">7.88033962249756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67257642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77400398254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74292135238647</t>
+    <t xml:space="preserve">7.67257690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77400302886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74292087554932</t>
   </si>
   <si>
     <t xml:space="preserve">7.64803743362427</t>
@@ -2522,34 +2522,34 @@
     <t xml:space="preserve">7.60713768005371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66276121139526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68239164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70202302932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858940124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69220781326294</t>
+    <t xml:space="preserve">7.66275978088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68239116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70202398300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61859035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69220733642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.80999565124512</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8852481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65785074234009</t>
+    <t xml:space="preserve">7.88524913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65785264968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.40591716766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03739166259766</t>
+    <t xml:space="preserve">8.03739070892334</t>
   </si>
   <si>
     <t xml:space="preserve">8.17644691467285</t>
@@ -2558,64 +2558,64 @@
     <t xml:space="preserve">8.32286357879639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18380737304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19607925415039</t>
+    <t xml:space="preserve">8.18380832672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19607734680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.23697566986084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10446548461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10283088684082</t>
+    <t xml:space="preserve">8.10446643829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10282802581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09955883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02993297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95865249633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0896110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04153728485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16918087005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15094661712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591812133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08629608154297</t>
   </si>
   <si>
     <t xml:space="preserve">8.09955787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02993297576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95865154266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08961200714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04153728485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16917991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15094661712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591907501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08629512786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0995569229126</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.00009536743164</t>
   </si>
   <si>
     <t xml:space="preserve">7.85587358474731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80116987228394</t>
+    <t xml:space="preserve">7.80116891860962</t>
   </si>
   <si>
     <t xml:space="preserve">7.96694040298462</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03987979888916</t>
+    <t xml:space="preserve">8.03987884521484</t>
   </si>
   <si>
     <t xml:space="preserve">8.21228122711182</t>
@@ -2624,10 +2624,10 @@
     <t xml:space="preserve">8.24377727508545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26864242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29682445526123</t>
+    <t xml:space="preserve">8.26864337921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29682350158691</t>
   </si>
   <si>
     <t xml:space="preserve">8.53304767608643</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">8.44187450408936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4625940322876</t>
+    <t xml:space="preserve">8.46259593963623</t>
   </si>
   <si>
     <t xml:space="preserve">8.40872001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39214134216309</t>
+    <t xml:space="preserve">8.3921422958374</t>
   </si>
   <si>
     <t xml:space="preserve">8.37970924377441</t>
@@ -2651,58 +2651,58 @@
     <t xml:space="preserve">8.42944049835205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49574756622314</t>
+    <t xml:space="preserve">8.49574851989746</t>
   </si>
   <si>
     <t xml:space="preserve">8.36313343048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32997798919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37142181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48331642150879</t>
+    <t xml:space="preserve">8.32997894287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37142086029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48331737518311</t>
   </si>
   <si>
     <t xml:space="preserve">8.71125221252441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69881820678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68224143981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60764503479004</t>
+    <t xml:space="preserve">8.69882011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68224239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60764408111572</t>
   </si>
   <si>
     <t xml:space="preserve">8.60350036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45016193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40043163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45430755615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52890396118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50403881072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47088241577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41700744628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37556743621826</t>
+    <t xml:space="preserve">8.45016098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40043067932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45430564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52890300750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50403785705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4708833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41700839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37556552886963</t>
   </si>
   <si>
     <t xml:space="preserve">8.05811405181885</t>
@@ -2714,52 +2714,52 @@
     <t xml:space="preserve">8.28687858581543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88073968887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73154735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6420316696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90891981124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93212938308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78790807723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83598232269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90063238143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00672626495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98186016082764</t>
+    <t xml:space="preserve">7.88073873519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73154640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90892028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93212747573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78790760040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83598136901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90063142776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00672721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98185920715332</t>
   </si>
   <si>
     <t xml:space="preserve">7.80448627471924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84095335006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13105297088623</t>
+    <t xml:space="preserve">7.8409538269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13105487823486</t>
   </si>
   <si>
     <t xml:space="preserve">7.76967287063599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37679767608643</t>
+    <t xml:space="preserve">7.37679672241211</t>
   </si>
   <si>
     <t xml:space="preserve">7.27733325958252</t>
@@ -2768,16 +2768,16 @@
     <t xml:space="preserve">7.29391145706177</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97563171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77007627487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71868753433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75018310546875</t>
+    <t xml:space="preserve">6.97563123703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77007532119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71868705749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75018405914307</t>
   </si>
   <si>
     <t xml:space="preserve">6.57612419128418</t>
@@ -2786,10 +2786,10 @@
     <t xml:space="preserve">6.45511198043823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08378553390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78248453140259</t>
+    <t xml:space="preserve">6.08378505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7824854850769</t>
   </si>
   <si>
     <t xml:space="preserve">4.65815687179565</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">3.97766804695129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71989440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85085320472717</t>
+    <t xml:space="preserve">3.71989464759827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85085344314575</t>
   </si>
   <si>
     <t xml:space="preserve">3.94534301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15918731689453</t>
+    <t xml:space="preserve">4.15918779373169</t>
   </si>
   <si>
     <t xml:space="preserve">4.32661533355713</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">4.43436670303345</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46089029312134</t>
+    <t xml:space="preserve">4.46088981628418</t>
   </si>
   <si>
     <t xml:space="preserve">4.70788812637329</t>
@@ -2834,31 +2834,31 @@
     <t xml:space="preserve">4.61505699157715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59019088745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62500238418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54543399810791</t>
+    <t xml:space="preserve">4.59019184112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62500286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54543352127075</t>
   </si>
   <si>
     <t xml:space="preserve">4.7543044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7874584197998</t>
+    <t xml:space="preserve">4.78745794296265</t>
   </si>
   <si>
     <t xml:space="preserve">4.90681314468384</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13226175308228</t>
+    <t xml:space="preserve">5.13226127624512</t>
   </si>
   <si>
     <t xml:space="preserve">5.01456451416016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97809410095215</t>
+    <t xml:space="preserve">4.97809457778931</t>
   </si>
   <si>
     <t xml:space="preserve">4.9117865562439</t>
@@ -2867,79 +2867,79 @@
     <t xml:space="preserve">4.69131088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77751159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80735063552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77917003631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54045963287354</t>
+    <t xml:space="preserve">4.77751207351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80735111236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77916955947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54046010971069</t>
   </si>
   <si>
     <t xml:space="preserve">4.6813645362854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86702871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90515518188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686679840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99135589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2831130027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29968976974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00627613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24664306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04440212249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1206579208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16375875473022</t>
+    <t xml:space="preserve">4.86702823638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90515613555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686727523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99135637283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28311252593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29968929290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00627517700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24664258956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04440259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12065696716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16375732421875</t>
   </si>
   <si>
     <t xml:space="preserve">5.07092571258545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98141050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76424980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79408884048462</t>
+    <t xml:space="preserve">4.98141002655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7642502784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79408931732178</t>
   </si>
   <si>
     <t xml:space="preserve">5.15878486633301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69960021972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85045051574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.611741065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59847927093506</t>
+    <t xml:space="preserve">4.6995997428894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85045099258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61174154281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59848022460938</t>
   </si>
   <si>
     <t xml:space="preserve">4.64158058166504</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">4.71451950073242</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72114992141724</t>
+    <t xml:space="preserve">4.72115039825439</t>
   </si>
   <si>
     <t xml:space="preserve">4.83718919754028</t>
@@ -2957,37 +2957,37 @@
     <t xml:space="preserve">4.63494920730591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84382057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04605960845947</t>
+    <t xml:space="preserve">4.84382009506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04606056213379</t>
   </si>
   <si>
     <t xml:space="preserve">5.29803228378296</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35273599624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63288879394531</t>
+    <t xml:space="preserve">5.3527364730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63288927078247</t>
   </si>
   <si>
     <t xml:space="preserve">5.7157735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61465454101562</t>
+    <t xml:space="preserve">5.61465406417847</t>
   </si>
   <si>
     <t xml:space="preserve">5.53508424758911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18365049362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18862438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1819920539856</t>
+    <t xml:space="preserve">5.18365001678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18862295150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18199253082275</t>
   </si>
   <si>
     <t xml:space="preserve">5.1306037902832</t>
@@ -2996,31 +2996,31 @@
     <t xml:space="preserve">5.12894582748413</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04108762741089</t>
+    <t xml:space="preserve">5.04108715057373</t>
   </si>
   <si>
     <t xml:space="preserve">5.14220762252808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8239278793335</t>
+    <t xml:space="preserve">4.82392740249634</t>
   </si>
   <si>
     <t xml:space="preserve">4.88692092895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76093530654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81398153305054</t>
+    <t xml:space="preserve">4.76093482971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81398057937622</t>
   </si>
   <si>
     <t xml:space="preserve">4.70623064041138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85210847854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76259231567383</t>
+    <t xml:space="preserve">4.85210943222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76259279251099</t>
   </si>
   <si>
     <t xml:space="preserve">4.93002080917358</t>
@@ -3029,34 +3029,34 @@
     <t xml:space="preserve">4.84547853469849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76756572723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5968222618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6216869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67805004119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75762033462524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7659068107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89355134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78414249420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70291519165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66810274124146</t>
+    <t xml:space="preserve">4.76756525039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59682178497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62168788909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67804908752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75761985778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76590776443481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89355182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7841420173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70291471481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66810321807861</t>
   </si>
   <si>
     <t xml:space="preserve">4.58024454116821</t>
@@ -3071,43 +3071,43 @@
     <t xml:space="preserve">4.19234085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08790588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28185749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29346179962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.485755443573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21389102935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2901463508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43602418899536</t>
+    <t xml:space="preserve">4.0879054069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28185701370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29346132278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48575592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21389150619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29014539718628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43602466583252</t>
   </si>
   <si>
     <t xml:space="preserve">4.41447401046753</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32164335250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27688455581665</t>
+    <t xml:space="preserve">4.32164287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27688407897949</t>
   </si>
   <si>
     <t xml:space="preserve">4.23875665664673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19731473922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10448312759399</t>
+    <t xml:space="preserve">4.19731521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10448265075684</t>
   </si>
   <si>
     <t xml:space="preserve">4.08624744415283</t>
@@ -3116,73 +3116,73 @@
     <t xml:space="preserve">4.22383785247803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17576456069946</t>
+    <t xml:space="preserve">4.1757640838623</t>
   </si>
   <si>
     <t xml:space="preserve">4.13349294662476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05806684494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08293199539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0779595375061</t>
+    <t xml:space="preserve">4.05806732177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08293294906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07795906066895</t>
   </si>
   <si>
     <t xml:space="preserve">4.00004768371582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96192002296448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98927211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00087547302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97601008415222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83924984931946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84422326087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82598733901978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77957105636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74724674224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80112242698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95943307876587</t>
+    <t xml:space="preserve">3.96192097663879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9892725944519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00087690353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97601056098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83925032615662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84422254562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82598781585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7795717716217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74724698066711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80112218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95943331718445</t>
   </si>
   <si>
     <t xml:space="preserve">3.96274900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85334014892578</t>
+    <t xml:space="preserve">3.85334062576294</t>
   </si>
   <si>
     <t xml:space="preserve">3.60053968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56075525283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53091645240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45880603790283</t>
+    <t xml:space="preserve">3.56075477600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53091621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45880556106567</t>
   </si>
   <si>
     <t xml:space="preserve">3.39747095108032</t>
@@ -3191,22 +3191,22 @@
     <t xml:space="preserve">3.53754687309265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42399430274963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53174543380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44139981269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5209698677063</t>
+    <t xml:space="preserve">3.42399382591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53174495697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44140005111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52097058296204</t>
   </si>
   <si>
     <t xml:space="preserve">3.55578136444092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65358638763428</t>
+    <t xml:space="preserve">3.65358662605286</t>
   </si>
   <si>
     <t xml:space="preserve">3.58064723014832</t>
@@ -3221,31 +3221,31 @@
     <t xml:space="preserve">3.60302662849426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51351022720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60717082023621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42730951309204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55080819129944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62623405456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71077704429626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61877489089966</t>
+    <t xml:space="preserve">3.51350998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60717105865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4273099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55080842971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62623429298401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71077799797058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61877417564392</t>
   </si>
   <si>
     <t xml:space="preserve">3.63783812522888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67099285125732</t>
+    <t xml:space="preserve">3.67099165916443</t>
   </si>
   <si>
     <t xml:space="preserve">3.57401633262634</t>
@@ -3257,19 +3257,19 @@
     <t xml:space="preserve">3.3701183795929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17285132408142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37509155273438</t>
+    <t xml:space="preserve">3.1728515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37509202957153</t>
   </si>
   <si>
     <t xml:space="preserve">3.55163764953613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63535189628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19399881362915</t>
+    <t xml:space="preserve">3.63535213470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19399785995483</t>
   </si>
   <si>
     <t xml:space="preserve">4.17244863510132</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">4.57029819488525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63660669326782</t>
+    <t xml:space="preserve">4.63660621643066</t>
   </si>
   <si>
     <t xml:space="preserve">4.64655256271362</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">4.6763916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7460150718689</t>
+    <t xml:space="preserve">4.74601602554321</t>
   </si>
   <si>
     <t xml:space="preserve">5.11402654647827</t>
@@ -3296,13 +3296,13 @@
     <t xml:space="preserve">5.21183156967163</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27316665649414</t>
+    <t xml:space="preserve">5.27316617965698</t>
   </si>
   <si>
     <t xml:space="preserve">5.19359636306763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18033456802368</t>
+    <t xml:space="preserve">5.18033504486084</t>
   </si>
   <si>
     <t xml:space="preserve">5.39324855804443</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">5.73357439041138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67825031280518</t>
+    <t xml:space="preserve">5.67825078964233</t>
   </si>
   <si>
     <t xml:space="preserve">5.6011323928833</t>
@@ -3320,31 +3320,31 @@
     <t xml:space="preserve">5.61957406997681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43683671951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52066087722778</t>
+    <t xml:space="preserve">5.4368371963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52066135406494</t>
   </si>
   <si>
     <t xml:space="preserve">5.54748487472534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58101463317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80901575088501</t>
+    <t xml:space="preserve">5.58101367950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80901622772217</t>
   </si>
   <si>
     <t xml:space="preserve">5.70339775085449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7117805480957</t>
+    <t xml:space="preserve">5.71178102493286</t>
   </si>
   <si>
     <t xml:space="preserve">5.71513319015503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8023099899292</t>
+    <t xml:space="preserve">5.80231046676636</t>
   </si>
   <si>
     <t xml:space="preserve">5.70004510879517</t>
@@ -3359,88 +3359,88 @@
     <t xml:space="preserve">5.66651582717896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72183895111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63801431655884</t>
+    <t xml:space="preserve">5.721839427948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.638014793396</t>
   </si>
   <si>
     <t xml:space="preserve">5.49048471450806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47539615631104</t>
+    <t xml:space="preserve">5.47539567947388</t>
   </si>
   <si>
     <t xml:space="preserve">5.62795543670654</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58771991729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51227903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55251407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47874879837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67489767074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9783411026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96995830535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93642902374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82913446426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99678230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91295862197876</t>
+    <t xml:space="preserve">5.58772039413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51227855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55251455307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4787483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67489719390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97834062576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9699592590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93642807006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8291335105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9967827796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9129581451416</t>
   </si>
   <si>
     <t xml:space="preserve">5.96492958068848</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65813302993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64304494857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4619836807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27254152297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17865896224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24739456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33792448043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50054359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38989543914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38151264190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60448503494263</t>
+    <t xml:space="preserve">5.6581335067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64304399490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46198415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27254104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1786584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24739408493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33792400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50054311752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38989496231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3815131187439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60448551177979</t>
   </si>
   <si>
     <t xml:space="preserve">5.6933388710022</t>
@@ -3449,115 +3449,115 @@
     <t xml:space="preserve">5.80733919143677</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92972326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82410478591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8945164680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90122270584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95989990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31196117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32201957702637</t>
+    <t xml:space="preserve">5.92972230911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82410526275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89451694488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90122318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95990037918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31196165084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32202005386353</t>
   </si>
   <si>
     <t xml:space="preserve">6.17951917648315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03534173965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06551790237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29351949691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22813653945923</t>
+    <t xml:space="preserve">6.03534126281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06551837921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29352045059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22813701629639</t>
   </si>
   <si>
     <t xml:space="preserve">6.44440364837646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32958745956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24743986129761</t>
+    <t xml:space="preserve">7.32958793640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24743843078613</t>
   </si>
   <si>
     <t xml:space="preserve">7.41508722305298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53579425811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51903009414673</t>
+    <t xml:space="preserve">7.53579473495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51902961730957</t>
   </si>
   <si>
     <t xml:space="preserve">7.78559064865112</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02700328826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14435863494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00521087646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1108283996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30697631835938</t>
+    <t xml:space="preserve">8.02700424194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1443567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00520992279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11082744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30697727203369</t>
   </si>
   <si>
     <t xml:space="preserve">8.31200695037842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10579967498779</t>
+    <t xml:space="preserve">8.10579872131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.12926959991455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09741592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99682760238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81576681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75038480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61961889266968</t>
+    <t xml:space="preserve">8.0974178314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99682950973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81576871871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75038385391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61961793899536</t>
   </si>
   <si>
     <t xml:space="preserve">7.90294551849365</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69170618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97168064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0152702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09574031829834</t>
+    <t xml:space="preserve">7.6917085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01526927947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09573936462402</t>
   </si>
   <si>
     <t xml:space="preserve">8.05718040466309</t>
@@ -3569,178 +3569,178 @@
     <t xml:space="preserve">8.10915184020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98174047470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77720785140991</t>
+    <t xml:space="preserve">7.98173952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77720832824707</t>
   </si>
   <si>
     <t xml:space="preserve">7.69506025314331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6397385597229</t>
+    <t xml:space="preserve">7.63973712921143</t>
   </si>
   <si>
     <t xml:space="preserve">7.62967777252197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9985032081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70679426193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68332529067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73864889144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39496946334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47041082382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46370506286621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4435887336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70008850097656</t>
+    <t xml:space="preserve">7.99850416183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70679569244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68332481384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73864793777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39497041702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47041177749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46370601654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44358825683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70008945465088</t>
   </si>
   <si>
     <t xml:space="preserve">7.53914785385132</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79229497909546</t>
+    <t xml:space="preserve">7.79229593276978</t>
   </si>
   <si>
     <t xml:space="preserve">7.2642035484314</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50897073745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5760293006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63806104660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98006343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12591743469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20806407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01359272003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2835054397583</t>
+    <t xml:space="preserve">7.50897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57603120803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63806056976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98006248474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12591648101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20806503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01359367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28350734710693</t>
   </si>
   <si>
     <t xml:space="preserve">8.19632816314697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21477031707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12759304046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90462160110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85600280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92976808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95869827270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8021445274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82596683502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04548168182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96039724349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93827533721924</t>
+    <t xml:space="preserve">8.21477127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12759208679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90462255477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8560037612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92976713180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95869636535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80214405059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82596731185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04548263549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96039915084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93827724456787</t>
   </si>
   <si>
     <t xml:space="preserve">8.15268707275391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2462797164917</t>
+    <t xml:space="preserve">8.24627876281738</t>
   </si>
   <si>
     <t xml:space="preserve">8.31604671478271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19182395935059</t>
+    <t xml:space="preserve">8.1918249130249</t>
   </si>
   <si>
     <t xml:space="preserve">8.20203590393066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17140674591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11354923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12545967102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29052066802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14077568054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13056373596191</t>
+    <t xml:space="preserve">8.17140483856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11354827880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12546062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29052257537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14077472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1305627822876</t>
   </si>
   <si>
     <t xml:space="preserve">7.94848680496216</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81575584411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84468555450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92296266555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97571277618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02506065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07100582122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80384683609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80554628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82086277008057</t>
+    <t xml:space="preserve">7.81575679779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84468650817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92296075820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97571182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02506160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07100677490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80384492874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80554723739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82086229324341</t>
   </si>
   <si>
     <t xml:space="preserve">7.97060871124268</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">8.0216588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64388799667358</t>
+    <t xml:space="preserve">7.64388847351074</t>
   </si>
   <si>
     <t xml:space="preserve">7.52987670898438</t>
@@ -3761,31 +3761,31 @@
     <t xml:space="preserve">7.42607450485229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65920257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63197708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4686164855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59964513778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521377563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25420618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00235939025879</t>
+    <t xml:space="preserve">7.65920352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63197660446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46861553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59964561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521329879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25420665740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00235986709595</t>
   </si>
   <si>
     <t xml:space="preserve">7.12317848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26271533966064</t>
+    <t xml:space="preserve">7.26271629333496</t>
   </si>
   <si>
     <t xml:space="preserve">7.18103361129761</t>
@@ -3797,22 +3797,22 @@
     <t xml:space="preserve">7.47372102737427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40735673904419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031736373901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46691465377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29674911499023</t>
+    <t xml:space="preserve">7.40735626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031688690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46691513061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29674816131592</t>
   </si>
   <si>
     <t xml:space="preserve">7.35800743103027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40565586090088</t>
+    <t xml:space="preserve">7.40565538406372</t>
   </si>
   <si>
     <t xml:space="preserve">7.30865955352783</t>
@@ -3821,118 +3821,118 @@
     <t xml:space="preserve">7.28313493728638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48223066329956</t>
+    <t xml:space="preserve">7.48222875595093</t>
   </si>
   <si>
     <t xml:space="preserve">7.44139003753662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48563385009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4958438873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30185222625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33418464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99385166168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93769645690918</t>
+    <t xml:space="preserve">7.4856333732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49584436416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30185270309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3341851234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99385261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93769693374634</t>
   </si>
   <si>
     <t xml:space="preserve">7.07042694091797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09254932403564</t>
+    <t xml:space="preserve">7.09254884719849</t>
   </si>
   <si>
     <t xml:space="preserve">7.15551042556763</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22187423706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33758783340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25760889053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34269380569458</t>
+    <t xml:space="preserve">7.22187566757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3375883102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25760984420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34269285202026</t>
   </si>
   <si>
     <t xml:space="preserve">7.2252779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2116641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14700126647949</t>
+    <t xml:space="preserve">7.21166515350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14700174331665</t>
   </si>
   <si>
     <t xml:space="preserve">7.0942497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0636191368103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30695867538452</t>
+    <t xml:space="preserve">7.06361961364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30695819854736</t>
   </si>
   <si>
     <t xml:space="preserve">7.25590801239014</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3767261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14019584655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87473487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87303352355957</t>
+    <t xml:space="preserve">7.37672662734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1401948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8747353553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87303400039673</t>
   </si>
   <si>
     <t xml:space="preserve">7.23038291931152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28823947906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32567644119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57241773605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53668308258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59794235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73577785491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72556924819946</t>
+    <t xml:space="preserve">7.2882399559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32567691802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57241678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53668355941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59794282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73577928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72556829452515</t>
   </si>
   <si>
     <t xml:space="preserve">7.93997859954834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67792129516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79874038696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15609073638916</t>
+    <t xml:space="preserve">7.67792081832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79873991012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15608978271484</t>
   </si>
   <si>
     <t xml:space="preserve">8.3500804901123</t>
@@ -3950,22 +3950,22 @@
     <t xml:space="preserve">8.40283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35348320007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45898723602295</t>
+    <t xml:space="preserve">8.35348224639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45898818969727</t>
   </si>
   <si>
     <t xml:space="preserve">8.60618019104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43856716156006</t>
+    <t xml:space="preserve">8.43856906890869</t>
   </si>
   <si>
     <t xml:space="preserve">8.39091968536377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56363868713379</t>
+    <t xml:space="preserve">8.56363964080811</t>
   </si>
   <si>
     <t xml:space="preserve">8.55513095855713</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">8.42325115203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19012355804443</t>
+    <t xml:space="preserve">8.19012451171875</t>
   </si>
   <si>
     <t xml:space="preserve">8.19352722167969</t>
@@ -3983,19 +3983,19 @@
     <t xml:space="preserve">8.41474342346191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38241100311279</t>
+    <t xml:space="preserve">8.38241195678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.27520656585693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79336547851562</t>
+    <t xml:space="preserve">8.79336452484131</t>
   </si>
   <si>
     <t xml:space="preserve">9.03585052490234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27833843231201</t>
+    <t xml:space="preserve">9.27833938598633</t>
   </si>
   <si>
     <t xml:space="preserve">9.23154449462891</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">8.92524337768555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83165264129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73380661010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7125358581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52960395812988</t>
+    <t xml:space="preserve">8.83165168762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73380565643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71253395080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52960586547852</t>
   </si>
   <si>
     <t xml:space="preserve">8.28881931304932</t>
@@ -4022,10 +4022,10 @@
     <t xml:space="preserve">8.07611083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26934623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21585941314697</t>
+    <t xml:space="preserve">8.2693452835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21586036682129</t>
   </si>
   <si>
     <t xml:space="preserve">8.31247711181641</t>
@@ -4037,40 +4037,40 @@
     <t xml:space="preserve">7.62753534317017</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69654655456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47225761413574</t>
+    <t xml:space="preserve">7.69654560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47225856781006</t>
   </si>
   <si>
     <t xml:space="preserve">7.78108692169189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70689916610718</t>
+    <t xml:space="preserve">7.70689821243286</t>
   </si>
   <si>
     <t xml:space="preserve">7.72932767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84319591522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0174503326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91910934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76038312911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69309711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62408304214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87942886352539</t>
+    <t xml:space="preserve">7.84319734573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01744937896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91911029815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76038217544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69309663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62408399581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87942695617676</t>
   </si>
   <si>
     <t xml:space="preserve">7.63616132736206</t>
@@ -4079,46 +4079,46 @@
     <t xml:space="preserve">7.85527324676514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78798675537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61373329162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86390161514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86217451095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87597608566284</t>
+    <t xml:space="preserve">7.78798723220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61373233795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86389970779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86217546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87597799301147</t>
   </si>
   <si>
     <t xml:space="preserve">7.96051645278931</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02435302734375</t>
+    <t xml:space="preserve">8.02435207366943</t>
   </si>
   <si>
     <t xml:space="preserve">8.0105504989624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94498920440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25899410247803</t>
+    <t xml:space="preserve">7.94499015808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25899219512939</t>
   </si>
   <si>
     <t xml:space="preserve">8.37286281585693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43669700622559</t>
+    <t xml:space="preserve">8.43669891357422</t>
   </si>
   <si>
     <t xml:space="preserve">8.43842315673828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45222663879395</t>
+    <t xml:space="preserve">8.45222568511963</t>
   </si>
   <si>
     <t xml:space="preserve">8.40909385681152</t>
@@ -4130,25 +4130,25 @@
     <t xml:space="preserve">8.65667343139648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67824077606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85076904296875</t>
+    <t xml:space="preserve">8.67823886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85076999664307</t>
   </si>
   <si>
     <t xml:space="preserve">9.06211853027344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25190162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28640747070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93703556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49708461761475</t>
+    <t xml:space="preserve">9.25190258026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28640651702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93703460693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49708366394043</t>
   </si>
   <si>
     <t xml:space="preserve">8.88958835601807</t>
@@ -4157,22 +4157,22 @@
     <t xml:space="preserve">9.5538272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37698459625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83850288391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78242969512939</t>
+    <t xml:space="preserve">9.37698554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83850193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78242874145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.65734577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8514404296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86006832122803</t>
+    <t xml:space="preserve">9.85144138336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86006736755371</t>
   </si>
   <si>
     <t xml:space="preserve">9.77380275726318</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">9.87732028961182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97652435302734</t>
+    <t xml:space="preserve">9.97652530670166</t>
   </si>
   <si>
     <t xml:space="preserve">10.0800428390503</t>
@@ -4205,25 +4205,25 @@
     <t xml:space="preserve">9.44599628448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5236349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42443084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32091331481934</t>
+    <t xml:space="preserve">9.52363395690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42443180084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32091236114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.60990142822266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95495891571045</t>
+    <t xml:space="preserve">9.95495796203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.86869335174561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3560914993286</t>
+    <t xml:space="preserve">10.3560905456543</t>
   </si>
   <si>
     <t xml:space="preserve">10.1447410583496</t>
@@ -4238,31 +4238,31 @@
     <t xml:space="preserve">11.6241836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9815092086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1540403366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1497278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8736782073975</t>
+    <t xml:space="preserve">10.9815111160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1540412902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1497268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8736791610718</t>
   </si>
   <si>
     <t xml:space="preserve">10.5113668441772</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7356557846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9081859588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5724239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6371231079102</t>
+    <t xml:space="preserve">10.7356548309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9081869125366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5724248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6371221542358</t>
   </si>
   <si>
     <t xml:space="preserve">11.9606161117554</t>
@@ -4274,10 +4274,10 @@
     <t xml:space="preserve">12.2927350997925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0123739242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6845693588257</t>
+    <t xml:space="preserve">12.012375831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6845674514771</t>
   </si>
   <si>
     <t xml:space="preserve">11.8829765319824</t>
@@ -4286,13 +4286,13 @@
     <t xml:space="preserve">11.8657255172729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9821815490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9735565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0727596282959</t>
+    <t xml:space="preserve">11.9821834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9735555648804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0727605819702</t>
   </si>
   <si>
     <t xml:space="preserve">11.9390506744385</t>
@@ -4304,19 +4304,19 @@
     <t xml:space="preserve">12.5299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4135055541992</t>
+    <t xml:space="preserve">12.4135065078735</t>
   </si>
   <si>
     <t xml:space="preserve">12.8146381378174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9224672317505</t>
+    <t xml:space="preserve">12.9224681854248</t>
   </si>
   <si>
     <t xml:space="preserve">12.9914808273315</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9612874984741</t>
+    <t xml:space="preserve">12.9612865447998</t>
   </si>
   <si>
     <t xml:space="preserve">12.9310941696167</t>
@@ -4325,13 +4325,13 @@
     <t xml:space="preserve">12.5817232131958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7233877182007</t>
+    <t xml:space="preserve">11.723388671875</t>
   </si>
   <si>
     <t xml:space="preserve">12.1374578475952</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0813865661621</t>
+    <t xml:space="preserve">12.0813875198364</t>
   </si>
   <si>
     <t xml:space="preserve">12.7758188247681</t>
@@ -4343,16 +4343,16 @@
     <t xml:space="preserve">12.8448305130005</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6981792449951</t>
+    <t xml:space="preserve">12.6981801986694</t>
   </si>
   <si>
     <t xml:space="preserve">12.6377954483032</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5385894775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0598182678223</t>
+    <t xml:space="preserve">12.5385904312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0598201751709</t>
   </si>
   <si>
     <t xml:space="preserve">12.180591583252</t>
@@ -4370,10 +4370,10 @@
     <t xml:space="preserve">13.2718420028687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4486837387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3667325973511</t>
+    <t xml:space="preserve">13.4486846923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3667316436768</t>
   </si>
   <si>
     <t xml:space="preserve">13.0216732025146</t>
@@ -4382,37 +4382,37 @@
     <t xml:space="preserve">13.19420337677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.488579750061</t>
+    <t xml:space="preserve">13.4885778427124</t>
   </si>
   <si>
     <t xml:space="preserve">13.3040437698364</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5456962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9147653579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0861196517944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2530755996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7302303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8356790542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8664350509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8224973678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9630947113037</t>
+    <t xml:space="preserve">13.5456972122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9147644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0861186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.253077507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7302312850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8356771469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.86643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8224983215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.963095664978</t>
   </si>
   <si>
     <t xml:space="preserve">14.0641489028931</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">14.0246067047119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4094915390015</t>
+    <t xml:space="preserve">13.4094934463501</t>
   </si>
   <si>
     <t xml:space="preserve">13.0052738189697</t>
@@ -4433,25 +4433,25 @@
     <t xml:space="preserve">12.693323135376</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3154668807983</t>
+    <t xml:space="preserve">12.315468788147</t>
   </si>
   <si>
     <t xml:space="preserve">11.5641489028931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3927955627441</t>
+    <t xml:space="preserve">11.3927946090698</t>
   </si>
   <si>
     <t xml:space="preserve">11.6080865859985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6739912033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0720586776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7381391525269</t>
+    <t xml:space="preserve">11.6739902496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.072057723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7381401062012</t>
   </si>
   <si>
     <t xml:space="preserve">10.9402484893799</t>
@@ -4466,13 +4466,13 @@
     <t xml:space="preserve">11.063271522522</t>
   </si>
   <si>
-    <t xml:space="preserve">10.782075881958</t>
+    <t xml:space="preserve">10.7820749282837</t>
   </si>
   <si>
     <t xml:space="preserve">10.5799655914307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9666090011597</t>
+    <t xml:space="preserve">10.966609954834</t>
   </si>
   <si>
     <t xml:space="preserve">10.0615129470825</t>
@@ -4481,64 +4481,64 @@
     <t xml:space="preserve">9.75834941864014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7469253540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1423568725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2082624435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1116018295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5404243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7117767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1467504501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1819009780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0676651000977</t>
+    <t xml:space="preserve">10.7469263076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1423578262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2082614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1116027832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.984185218811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5404233932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7117776870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.14674949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1818990707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0676641464233</t>
   </si>
   <si>
     <t xml:space="preserve">10.8523750305176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.975396156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0940256118774</t>
+    <t xml:space="preserve">10.9753980636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0940265655518</t>
   </si>
   <si>
     <t xml:space="preserve">11.4411268234253</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5861177444458</t>
+    <t xml:space="preserve">11.5861186981201</t>
   </si>
   <si>
     <t xml:space="preserve">11.9551858901978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6344470977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6608114242554</t>
+    <t xml:space="preserve">11.634449005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6608104705811</t>
   </si>
   <si>
     <t xml:space="preserve">11.5289993286133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0896339416504</t>
+    <t xml:space="preserve">11.0896329879761</t>
   </si>
   <si>
     <t xml:space="preserve">11.3005294799805</t>
@@ -4547,10 +4547,10 @@
     <t xml:space="preserve">11.4147644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2917404174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5685434341431</t>
+    <t xml:space="preserve">11.2917413711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5685424804688</t>
   </si>
   <si>
     <t xml:space="preserve">11.5421810150146</t>
@@ -4559,13 +4559,13 @@
     <t xml:space="preserve">11.3224983215332</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6827793121338</t>
+    <t xml:space="preserve">11.6827783584595</t>
   </si>
   <si>
     <t xml:space="preserve">11.2829542160034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2803192138672</t>
+    <t xml:space="preserve">12.2803201675415</t>
   </si>
   <si>
     <t xml:space="preserve">12.1704769134521</t>
@@ -4577,28 +4577,28 @@
     <t xml:space="preserve">12.218807220459</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0913896560669</t>
+    <t xml:space="preserve">12.0913906097412</t>
   </si>
   <si>
     <t xml:space="preserve">12.0826034545898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0298795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4384908676147</t>
+    <t xml:space="preserve">12.0298776626587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4384899139404</t>
   </si>
   <si>
     <t xml:space="preserve">12.5527267456055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.122145652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7398948669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7442893981934</t>
+    <t xml:space="preserve">12.1221446990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7398977279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7442903518677</t>
   </si>
   <si>
     <t xml:space="preserve">12.328649520874</t>
@@ -4610,37 +4610,37 @@
     <t xml:space="preserve">12.5219697952271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5175762176514</t>
+    <t xml:space="preserve">12.5175771713257</t>
   </si>
   <si>
     <t xml:space="preserve">12.2407751083374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9288244247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9024629592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7882261276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.126540184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9622173309326</t>
+    <t xml:space="preserve">11.9288234710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9024610519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7882270812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1265392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9622163772583</t>
   </si>
   <si>
     <t xml:space="preserve">11.1994743347168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5377883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6564168930054</t>
+    <t xml:space="preserve">11.5377864837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8760995864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6564159393311</t>
   </si>
   <si>
     <t xml:space="preserve">12.4604587554932</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">13.0140619277954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.18541431427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7328662872314</t>
+    <t xml:space="preserve">13.1854152679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7328653335571</t>
   </si>
   <si>
     <t xml:space="preserve">12.1353273391724</t>
@@ -4667,10 +4667,10 @@
     <t xml:space="preserve">12.8163471221924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5615129470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217948913574</t>
+    <t xml:space="preserve">12.5615139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217939376831</t>
   </si>
   <si>
     <t xml:space="preserve">13.2117776870728</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">13.1590538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3216190338135</t>
+    <t xml:space="preserve">13.3216180801392</t>
   </si>
   <si>
     <t xml:space="preserve">13.2205648422241</t>
@@ -4688,31 +4688,31 @@
     <t xml:space="preserve">13.5193347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8927965164185</t>
+    <t xml:space="preserve">13.8927974700928</t>
   </si>
   <si>
     <t xml:space="preserve">13.4534292221069</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8005285263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.156418800354</t>
+    <t xml:space="preserve">13.8005294799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1564178466797</t>
   </si>
   <si>
     <t xml:space="preserve">13.9982452392578</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1959600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6265420913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7539577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4551868438721</t>
+    <t xml:space="preserve">14.1959609985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.626540184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7539567947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4551877975464</t>
   </si>
   <si>
     <t xml:space="preserve">14.3585262298584</t>
@@ -4724,19 +4724,19 @@
     <t xml:space="preserve">14.0553617477417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9938516616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6572961807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.727596282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3101959228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4244318008423</t>
+    <t xml:space="preserve">13.9938526153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6572952270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7275953292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3101949691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4244327545166</t>
   </si>
   <si>
     <t xml:space="preserve">13.785120010376</t>
@@ -4748,7 +4748,7 @@
     <t xml:space="preserve">14.3578367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4466285705566</t>
+    <t xml:space="preserve">14.446629524231</t>
   </si>
   <si>
     <t xml:space="preserve">14.5265436172485</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">14.841757774353</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4954652786255</t>
+    <t xml:space="preserve">14.4954643249512</t>
   </si>
   <si>
     <t xml:space="preserve">14.2557239532471</t>
@@ -4787,7 +4787,7 @@
     <t xml:space="preserve">13.5276203155518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9893455505371</t>
+    <t xml:space="preserve">13.9893445968628</t>
   </si>
   <si>
     <t xml:space="preserve">14.0159826278687</t>
@@ -4796,34 +4796,34 @@
     <t xml:space="preserve">13.7451639175415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6474914550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9493885040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1402931213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643878936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7218885421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7796049118042</t>
+    <t xml:space="preserve">13.6474905014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.949387550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1402940750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643888473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7796030044556</t>
   </si>
   <si>
     <t xml:space="preserve">14.6686124801636</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7130088806152</t>
+    <t xml:space="preserve">14.7130079269409</t>
   </si>
   <si>
     <t xml:space="preserve">14.4599475860596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9349908828735</t>
+    <t xml:space="preserve">14.9349899291992</t>
   </si>
   <si>
     <t xml:space="preserve">14.4199914932251</t>
@@ -4832,31 +4832,31 @@
     <t xml:space="preserve">13.4033117294312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.793999671936</t>
+    <t xml:space="preserve">13.7940006256104</t>
   </si>
   <si>
     <t xml:space="preserve">14.0071029663086</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0603799819946</t>
+    <t xml:space="preserve">14.0603790283203</t>
   </si>
   <si>
     <t xml:space="preserve">14.0692586898804</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2379665374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4421892166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3445167541504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2290859222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6597318649292</t>
+    <t xml:space="preserve">14.237964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4421882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3445177078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2290849685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6597328186035</t>
   </si>
   <si>
     <t xml:space="preserve">15.2679662704468</t>
@@ -4871,37 +4871,37 @@
     <t xml:space="preserve">14.2424058914185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2690420150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2956800460815</t>
+    <t xml:space="preserve">14.26904296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2956819534302</t>
   </si>
   <si>
     <t xml:space="preserve">14.6197757720947</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3977928161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4288702011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1180953979492</t>
+    <t xml:space="preserve">14.3977937698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4288692474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1180944442749</t>
   </si>
   <si>
     <t xml:space="preserve">13.6297330856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5498189926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4388275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5409393310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8872337341309</t>
+    <t xml:space="preserve">13.5498199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4388284683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.540940284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8872318267822</t>
   </si>
   <si>
     <t xml:space="preserve">14.1225347518921</t>
@@ -4910,10 +4910,10 @@
     <t xml:space="preserve">14.082576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">14.380033493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4011526107788</t>
+    <t xml:space="preserve">14.3800344467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4011545181274</t>
   </si>
   <si>
     <t xml:space="preserve">14.6641721725464</t>
@@ -4928,16 +4928,16 @@
     <t xml:space="preserve">14.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9227495193481</t>
+    <t xml:space="preserve">13.9227504730225</t>
   </si>
   <si>
     <t xml:space="preserve">14.2646045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3267583847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3711538314819</t>
+    <t xml:space="preserve">14.3267593383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3711547851562</t>
   </si>
   <si>
     <t xml:space="preserve">14.4732666015625</t>
@@ -4949,43 +4949,43 @@
     <t xml:space="preserve">14.00266456604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7140865325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9105100631714</t>
+    <t xml:space="preserve">13.7140846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9105091094971</t>
   </si>
   <si>
     <t xml:space="preserve">13.0969743728638</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9249067306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9559850692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7384405136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7695178985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.164647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0358982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7650775909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3877067565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942598342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8361129760742</t>
+    <t xml:space="preserve">11.9249057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9559841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7384414672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7695188522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1646480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0358991622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.765079498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3877077102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942607879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8361139297485</t>
   </si>
   <si>
     <t xml:space="preserve">11.7739591598511</t>
@@ -4994,85 +4994,85 @@
     <t xml:space="preserve">11.6096906661987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.631890296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9826231002808</t>
+    <t xml:space="preserve">11.6318893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9826221466064</t>
   </si>
   <si>
     <t xml:space="preserve">11.6851654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5386562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5075798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8183546066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9737424850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9337863922119</t>
+    <t xml:space="preserve">11.5386571884155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5075788497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8183565139771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9737434387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9337844848633</t>
   </si>
   <si>
     <t xml:space="preserve">11.8405532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7828388214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.654088973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6363277435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5874919891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5031404495239</t>
+    <t xml:space="preserve">11.7828369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6540870666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6363286972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5874929428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5031385421753</t>
   </si>
   <si>
     <t xml:space="preserve">11.2678375244141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9659423828125</t>
+    <t xml:space="preserve">10.9659414291382</t>
   </si>
   <si>
     <t xml:space="preserve">10.8949069976807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7439584732056</t>
+    <t xml:space="preserve">10.7439594268799</t>
   </si>
   <si>
     <t xml:space="preserve">11.02809715271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1168899536133</t>
+    <t xml:space="preserve">11.1168909072876</t>
   </si>
   <si>
     <t xml:space="preserve">11.0991315841675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8771495819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7528390884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8815879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8460712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7705974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9171047210693</t>
+    <t xml:space="preserve">10.8771486282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7528381347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8815889358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8460702896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7705965042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9171056747437</t>
   </si>
   <si>
     <t xml:space="preserve">10.9526233673096</t>
@@ -5084,67 +5084,67 @@
     <t xml:space="preserve">11.2311182022095</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2585115432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8430509567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.938925743103</t>
+    <t xml:space="preserve">11.2585105895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8430500030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9389266967773</t>
   </si>
   <si>
     <t xml:space="preserve">11.1489391326904</t>
   </si>
   <si>
-    <t xml:space="preserve">10.847617149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6558656692505</t>
+    <t xml:space="preserve">10.8476161956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6558666229248</t>
   </si>
   <si>
     <t xml:space="preserve">10.8795747756958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2722072601318</t>
+    <t xml:space="preserve">11.2722091674805</t>
   </si>
   <si>
     <t xml:space="preserve">11.3452548980713</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6054887771606</t>
+    <t xml:space="preserve">11.6054878234863</t>
   </si>
   <si>
     <t xml:space="preserve">11.6967992782593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7561511993408</t>
+    <t xml:space="preserve">11.7561502456665</t>
   </si>
   <si>
     <t xml:space="preserve">11.7104949951172</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6420125961304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205083847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8063716888428</t>
+    <t xml:space="preserve">11.6420135498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8063707351685</t>
   </si>
   <si>
     <t xml:space="preserve">11.8931140899658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4274339675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7972402572632</t>
+    <t xml:space="preserve">11.4274349212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7972393035889</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374464035034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6922330856323</t>
+    <t xml:space="preserve">11.6922340393066</t>
   </si>
   <si>
     <t xml:space="preserve">11.829197883606</t>
@@ -5156,31 +5156,31 @@
     <t xml:space="preserve">11.8657217025757</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1853065490723</t>
+    <t xml:space="preserve">12.1853075027466</t>
   </si>
   <si>
     <t xml:space="preserve">12.5231533050537</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5185880661011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5870685577393</t>
+    <t xml:space="preserve">12.5185871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5870695114136</t>
   </si>
   <si>
     <t xml:space="preserve">12.482063293457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1305208206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4501066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4227113723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7696886062622</t>
+    <t xml:space="preserve">12.1305198669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4501056671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4227123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7696895599365</t>
   </si>
   <si>
     <t xml:space="preserve">13.0025291442871</t>
@@ -5189,19 +5189,19 @@
     <t xml:space="preserve">13.016227722168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568748474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.966007232666</t>
+    <t xml:space="preserve">12.9568758010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9660053253174</t>
   </si>
   <si>
     <t xml:space="preserve">13.1577568054199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1668882369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5184307098389</t>
+    <t xml:space="preserve">13.1668891906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5184326171875</t>
   </si>
   <si>
     <t xml:space="preserve">13.5549554824829</t>
@@ -5210,7 +5210,7 @@
     <t xml:space="preserve">13.7330093383789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6553964614868</t>
+    <t xml:space="preserve">13.6553955078125</t>
   </si>
   <si>
     <t xml:space="preserve">13.6143064498901</t>
@@ -5222,10 +5222,10 @@
     <t xml:space="preserve">13.6964855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8151884078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7695341110229</t>
+    <t xml:space="preserve">13.8151874542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7695331573486</t>
   </si>
   <si>
     <t xml:space="preserve">13.6462650299072</t>
@@ -5243,10 +5243,10 @@
     <t xml:space="preserve">13.637134552002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0708560943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0845518112183</t>
+    <t xml:space="preserve">14.070855140686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0845537185669</t>
   </si>
   <si>
     <t xml:space="preserve">14.0434637069702</t>
@@ -5261,10 +5261,10 @@
     <t xml:space="preserve">13.9658498764038</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9475870132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9247608184814</t>
+    <t xml:space="preserve">13.9475879669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9247598648071</t>
   </si>
   <si>
     <t xml:space="preserve">13.7877960205078</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">13.7512712478638</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6736583709717</t>
+    <t xml:space="preserve">13.673659324646</t>
   </si>
   <si>
     <t xml:space="preserve">13.8380155563354</t>
@@ -5282,37 +5282,37 @@
     <t xml:space="preserve">13.9612846374512</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9293251037598</t>
+    <t xml:space="preserve">13.9293270111084</t>
   </si>
   <si>
     <t xml:space="preserve">13.4773416519165</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6097412109375</t>
+    <t xml:space="preserve">13.6097402572632</t>
   </si>
   <si>
     <t xml:space="preserve">13.550389289856</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7604026794434</t>
+    <t xml:space="preserve">13.760401725769</t>
   </si>
   <si>
     <t xml:space="preserve">13.6645269393921</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7375745773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.847146987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7421417236328</t>
+    <t xml:space="preserve">13.7375755310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8471460342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7421407699585</t>
   </si>
   <si>
     <t xml:space="preserve">14.0936841964722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0891189575195</t>
+    <t xml:space="preserve">14.0891180038452</t>
   </si>
   <si>
     <t xml:space="preserve">13.8425817489624</t>
@@ -5321,16 +5321,16 @@
     <t xml:space="preserve">13.7786645889282</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3951635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3860311508179</t>
+    <t xml:space="preserve">13.3951625823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3860321044922</t>
   </si>
   <si>
     <t xml:space="preserve">13.4316873550415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4362516403198</t>
+    <t xml:space="preserve">13.4362525939941</t>
   </si>
   <si>
     <t xml:space="preserve">13.7740993499756</t>
@@ -5360,25 +5360,25 @@
     <t xml:space="preserve">13.9567184448242</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0343313217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3950061798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2945642471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4954462051392</t>
+    <t xml:space="preserve">14.0343322753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3950071334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2945652008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4954481124878</t>
   </si>
   <si>
     <t xml:space="preserve">14.5045785903931</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2671718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9338912963867</t>
+    <t xml:space="preserve">14.2671728134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.933892250061</t>
   </si>
   <si>
     <t xml:space="preserve">14.0571603775024</t>
@@ -5390,19 +5390,19 @@
     <t xml:space="preserve">13.7969255447388</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9383010864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8999509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2542333602905</t>
+    <t xml:space="preserve">14.9383001327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8999500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2542304992676</t>
   </si>
   <si>
     <t xml:space="preserve">14.783073425293</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3228712081909</t>
+    <t xml:space="preserve">14.3228721618652</t>
   </si>
   <si>
     <t xml:space="preserve">14.585844039917</t>
@@ -5414,13 +5414,13 @@
     <t xml:space="preserve">14.9063425064087</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7008943557739</t>
+    <t xml:space="preserve">14.7008962631226</t>
   </si>
   <si>
     <t xml:space="preserve">14.7191572189331</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1302080154419</t>
+    <t xml:space="preserve">14.1302070617676</t>
   </si>
   <si>
     <t xml:space="preserve">14.3036966323853</t>
@@ -5429,22 +5429,22 @@
     <t xml:space="preserve">14.5487966537476</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3730640411377</t>
+    <t xml:space="preserve">14.373064994812</t>
   </si>
   <si>
     <t xml:space="preserve">14.1788339614868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2620763778687</t>
+    <t xml:space="preserve">14.2620754241943</t>
   </si>
   <si>
     <t xml:space="preserve">14.3961868286133</t>
   </si>
   <si>
-    <t xml:space="preserve">14.299072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1834592819214</t>
+    <t xml:space="preserve">14.2990713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1834583282471</t>
   </si>
   <si>
     <t xml:space="preserve">14.5672950744629</t>
@@ -5459,46 +5459,46 @@
     <t xml:space="preserve">14.6921577453613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4331827163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5626707077026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3453168869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1094655990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2019567489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4655561447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6274137496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7291536331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8725137710571</t>
+    <t xml:space="preserve">14.4331836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5626697540283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3453178405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1094665527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2019557952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.46555519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6274127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.729154586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8725156784058</t>
   </si>
   <si>
     <t xml:space="preserve">14.7707748413086</t>
   </si>
   <si>
-    <t xml:space="preserve">14.840142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7615251541138</t>
+    <t xml:space="preserve">14.8401432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7615261077881</t>
   </si>
   <si>
     <t xml:space="preserve">14.7014074325562</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6135406494141</t>
+    <t xml:space="preserve">14.6135416030884</t>
   </si>
   <si>
     <t xml:space="preserve">14.4378070831299</t>
@@ -5516,7 +5516,7 @@
     <t xml:space="preserve">13.6608858108521</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6007671356201</t>
+    <t xml:space="preserve">13.6007661819458</t>
   </si>
   <si>
     <t xml:space="preserve">13.6192646026611</t>
@@ -5525,25 +5525,25 @@
     <t xml:space="preserve">13.4712791442871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4019117355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4065351486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.42041015625</t>
+    <t xml:space="preserve">13.4019107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4065361022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4204092025757</t>
   </si>
   <si>
     <t xml:space="preserve">13.346417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6793842315674</t>
+    <t xml:space="preserve">13.6793832778931</t>
   </si>
   <si>
     <t xml:space="preserve">13.8551158905029</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8504915237427</t>
+    <t xml:space="preserve">13.850492477417</t>
   </si>
   <si>
     <t xml:space="preserve">13.9291086196899</t>
@@ -5552,16 +5552,16 @@
     <t xml:space="preserve">13.8597402572632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5822696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6100149154663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8921136856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.438907623291</t>
+    <t xml:space="preserve">13.5822687149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6100158691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8921127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4389066696167</t>
   </si>
   <si>
     <t xml:space="preserve">13.6886329650879</t>
@@ -5576,7 +5576,7 @@
     <t xml:space="preserve">13.7903728485107</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7071313858032</t>
+    <t xml:space="preserve">13.7071304321289</t>
   </si>
   <si>
     <t xml:space="preserve">13.6331386566162</t>
@@ -5588,25 +5588,25 @@
     <t xml:space="preserve">13.9522314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8042469024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8967370986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9095125198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1869840621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303451538086</t>
+    <t xml:space="preserve">13.8042459487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8967361450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9095115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1869831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303442001343</t>
   </si>
   <si>
     <t xml:space="preserve">15.4320831298828</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3395929336548</t>
+    <t xml:space="preserve">15.3395910263062</t>
   </si>
   <si>
     <t xml:space="preserve">15.2378540039062</t>
@@ -5615,10 +5615,10 @@
     <t xml:space="preserve">15.1731100082397</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7141799926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.88991355896</t>
+    <t xml:space="preserve">15.7141809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8899145126343</t>
   </si>
   <si>
     <t xml:space="preserve">15.963906288147</t>
@@ -5636,7 +5636,7 @@
     <t xml:space="preserve">16.3801136016846</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5281009674072</t>
+    <t xml:space="preserve">16.5280990600586</t>
   </si>
   <si>
     <t xml:space="preserve">16.4078617095947</t>
@@ -5648,7 +5648,7 @@
     <t xml:space="preserve">16.6067161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.639087677002</t>
+    <t xml:space="preserve">16.6390895843506</t>
   </si>
   <si>
     <t xml:space="preserve">16.78244972229</t>
@@ -5657,19 +5657,19 @@
     <t xml:space="preserve">16.8888130187988</t>
   </si>
   <si>
-    <t xml:space="preserve">16.911937713623</t>
+    <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
     <t xml:space="preserve">16.93505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0183010101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9396820068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2032833099365</t>
+    <t xml:space="preserve">17.0182991027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9396839141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2032814025879</t>
   </si>
   <si>
     <t xml:space="preserve">17.2402763366699</t>
@@ -5678,19 +5678,19 @@
     <t xml:space="preserve">17.0599212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1894054412842</t>
+    <t xml:space="preserve">17.1894073486328</t>
   </si>
   <si>
     <t xml:space="preserve">16.9489326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1107921600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.976676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0414218902588</t>
+    <t xml:space="preserve">17.1107902526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9766788482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0414237976074</t>
   </si>
   <si>
     <t xml:space="preserve">16.5096015930176</t>
@@ -5699,25 +5699,25 @@
     <t xml:space="preserve">16.5974674224854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3708667755127</t>
+    <t xml:space="preserve">16.3708648681641</t>
   </si>
   <si>
     <t xml:space="preserve">16.338493347168</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2182559967041</t>
+    <t xml:space="preserve">16.2182540893555</t>
   </si>
   <si>
     <t xml:space="preserve">16.1396389007568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0471477508545</t>
+    <t xml:space="preserve">16.0471458435059</t>
   </si>
   <si>
     <t xml:space="preserve">14.7800235748291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6967830657959</t>
+    <t xml:space="preserve">14.6967821121216</t>
   </si>
   <si>
     <t xml:space="preserve">14.4979267120361</t>
@@ -5726,13 +5726,13 @@
     <t xml:space="preserve">14.4054365158081</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4239339828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6782846450806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6690349578857</t>
+    <t xml:space="preserve">14.4239349365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6782836914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6690340042114</t>
   </si>
   <si>
     <t xml:space="preserve">14.4886779785156</t>
@@ -5753,10 +5753,10 @@
     <t xml:space="preserve">14.9002628326416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9808807373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1421175003052</t>
+    <t xml:space="preserve">14.9808797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1421184539795</t>
   </si>
   <si>
     <t xml:space="preserve">14.8338689804077</t>
@@ -5783,13 +5783,13 @@
     <t xml:space="preserve">14.3169603347778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1699485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0845890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9755144119263</t>
+    <t xml:space="preserve">14.1699495315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0845880508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9755153656006</t>
   </si>
   <si>
     <t xml:space="preserve">14.056134223938</t>
@@ -5813,13 +5813,13 @@
     <t xml:space="preserve">13.5771636962891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6577816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8617010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6198434829712</t>
+    <t xml:space="preserve">13.6577825546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8617000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6198444366455</t>
   </si>
   <si>
     <t xml:space="preserve">13.7621126174927</t>
@@ -5828,7 +5828,7 @@
     <t xml:space="preserve">13.6008749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.752628326416</t>
+    <t xml:space="preserve">13.7526273727417</t>
   </si>
   <si>
     <t xml:space="preserve">13.6625242233276</t>
@@ -5837,7 +5837,7 @@
     <t xml:space="preserve">13.3590183258057</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2973699569702</t>
+    <t xml:space="preserve">13.2973690032959</t>
   </si>
   <si>
     <t xml:space="preserve">13.6103601455688</t>
@@ -5855,13 +5855,13 @@
     <t xml:space="preserve">13.5534524917603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3969573974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4159269332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5202560424805</t>
+    <t xml:space="preserve">13.3969564437866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4159259796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5202569961548</t>
   </si>
   <si>
     <t xml:space="preserve">13.8047943115234</t>
@@ -5870,25 +5870,25 @@
     <t xml:space="preserve">13.7953090667725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7336587905884</t>
+    <t xml:space="preserve">13.7336578369141</t>
   </si>
   <si>
     <t xml:space="preserve">13.9470615386963</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6340713500977</t>
+    <t xml:space="preserve">13.6340703964233</t>
   </si>
   <si>
     <t xml:space="preserve">13.6672668457031</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6862373352051</t>
+    <t xml:space="preserve">13.6862363815308</t>
   </si>
   <si>
     <t xml:space="preserve">13.8285045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8854131698608</t>
+    <t xml:space="preserve">13.8854122161865</t>
   </si>
   <si>
     <t xml:space="preserve">12.6761293411255</t>
@@ -5900,7 +5900,7 @@
     <t xml:space="preserve">12.0548896789551</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0311794281006</t>
+    <t xml:space="preserve">12.0311784744263</t>
   </si>
   <si>
     <t xml:space="preserve">12.1639623641968</t>
@@ -5909,7 +5909,7 @@
     <t xml:space="preserve">12.0833435058594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1687049865723</t>
+    <t xml:space="preserve">12.1687040328979</t>
   </si>
   <si>
     <t xml:space="preserve">12.102313041687</t>
@@ -5918,22 +5918,22 @@
     <t xml:space="preserve">12.0406627655029</t>
   </si>
   <si>
-    <t xml:space="preserve">12.140251159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1876745223999</t>
+    <t xml:space="preserve">12.1402521133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1876735687256</t>
   </si>
   <si>
     <t xml:space="preserve">11.8557138442993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.95530128479</t>
+    <t xml:space="preserve">11.9553022384644</t>
   </si>
   <si>
     <t xml:space="preserve">11.9837560653687</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1829328536987</t>
+    <t xml:space="preserve">12.1829319000244</t>
   </si>
   <si>
     <t xml:space="preserve">11.8414869308472</t>
@@ -5960,7 +5960,7 @@
     <t xml:space="preserve">12.3299427032471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0691175460815</t>
+    <t xml:space="preserve">12.0691165924072</t>
   </si>
   <si>
     <t xml:space="preserve">12.0359201431274</t>
@@ -5975,7 +5975,7 @@
     <t xml:space="preserve">12.5291185379028</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5196342468262</t>
+    <t xml:space="preserve">12.5196332931519</t>
   </si>
   <si>
     <t xml:space="preserve">12.6856136322021</t>
@@ -5996,7 +5996,7 @@
     <t xml:space="preserve">13.0365428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4348955154419</t>
+    <t xml:space="preserve">13.4348945617676</t>
   </si>
   <si>
     <t xml:space="preserve">13.4064416885376</t>
@@ -6017,13 +6017,13 @@
     <t xml:space="preserve">13.6909790039062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9565458297729</t>
+    <t xml:space="preserve">13.9565467834473</t>
   </si>
   <si>
     <t xml:space="preserve">14.0087118148804</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7384004592896</t>
+    <t xml:space="preserve">13.7384014129639</t>
   </si>
   <si>
     <t xml:space="preserve">13.8000507354736</t>
@@ -6032,7 +6032,7 @@
     <t xml:space="preserve">13.781081199646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9186086654663</t>
+    <t xml:space="preserve">13.918607711792</t>
   </si>
   <si>
     <t xml:space="preserve">14.0798463821411</t>
@@ -6050,10 +6050,10 @@
     <t xml:space="preserve">14.3217029571533</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2363414764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3643827438354</t>
+    <t xml:space="preserve">14.2363424301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3643836975098</t>
   </si>
   <si>
     <t xml:space="preserve">14.5777854919434</t>
@@ -6062,13 +6062,13 @@
     <t xml:space="preserve">14.4781980514526</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6678895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6590280532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4177932739258</t>
+    <t xml:space="preserve">14.6678886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6590270996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4177913665771</t>
   </si>
   <si>
     <t xml:space="preserve">16.346658706665</t>
@@ -6080,7 +6080,7 @@
     <t xml:space="preserve">16.4130516052246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5078964233398</t>
+    <t xml:space="preserve">16.5078983306885</t>
   </si>
   <si>
     <t xml:space="preserve">16.5553188323975</t>
@@ -6711,6 +6711,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8899993896484</t>
   </si>
 </sst>
 </file>
@@ -72231,7 +72234,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6928240741</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>1166051</v>
@@ -72252,6 +72255,32 @@
         <v>2232</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6912731481</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>1417694</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>18</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>17.6299991607666</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>17.6499996185303</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>17.8899993896484</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>2233</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="2237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="2238">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87407159805298</t>
+    <t xml:space="preserve">7.87406921386719</t>
   </si>
   <si>
     <t xml:space="preserve">TEN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8886513710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69909000396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48036766052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19602489471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11582708358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07937335968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12311744689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07208061218262</t>
+    <t xml:space="preserve">7.88865232467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69909048080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4803671836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19602394104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11582660675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07937097549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12311601638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07208108901978</t>
   </si>
   <si>
     <t xml:space="preserve">6.62734222412109</t>
@@ -74,160 +74,160 @@
     <t xml:space="preserve">6.56901597976685</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77680444717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3940372467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63463401794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80596828460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78044843673706</t>
+    <t xml:space="preserve">6.77680397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39403676986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63463354110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8059663772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78044891357422</t>
   </si>
   <si>
     <t xml:space="preserve">6.88981103897095</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91168451309204</t>
+    <t xml:space="preserve">6.91168355941772</t>
   </si>
   <si>
     <t xml:space="preserve">6.82783889770508</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49246215820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51433563232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03562688827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43413686752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29925727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80232238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9554271697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74034929275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1486349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06114530563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83148574829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11947059631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8606481552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54349946975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55443477630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16686153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32726097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50223875045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45120286941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61160039901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91781282424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00530529022217</t>
+    <t xml:space="preserve">6.49246120452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51433610916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03562593460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43413400650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29925584793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.802321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95542907714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74035024642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14863634109497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06114482879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83148527145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11947202682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86064624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54349803924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55443429946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16686248779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32726001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50223827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4512038230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61160182952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91781616210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00530338287354</t>
   </si>
   <si>
     <t xml:space="preserve">7.71367120742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85948753356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5897274017334</t>
+    <t xml:space="preserve">7.85948991775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58972787857056</t>
   </si>
   <si>
     <t xml:space="preserve">7.82303380966187</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73554468154907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96156024932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81574392318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77928829193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95426893234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72096300125122</t>
+    <t xml:space="preserve">7.73554563522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9615592956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8157434463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77928924560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95426845550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72096395492554</t>
   </si>
   <si>
     <t xml:space="preserve">7.6699275970459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98343324661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83032560348511</t>
+    <t xml:space="preserve">7.98343229293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83032417297363</t>
   </si>
   <si>
     <t xml:space="preserve">7.53140163421631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66263866424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64076280593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07821273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11466598510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17299270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42087936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41358852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45004367828369</t>
+    <t xml:space="preserve">7.66263675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64076328277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07821369171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11466789245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17299365997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42088222503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41358947753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45004463195801</t>
   </si>
   <si>
     <t xml:space="preserve">8.69793033599854</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">8.8291654586792</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86562061309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91665458679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63960456848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80000400543213</t>
+    <t xml:space="preserve">8.86561870574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91665554046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63960552215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80000114440918</t>
   </si>
   <si>
     <t xml:space="preserve">8.80729389190674</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">8.58856868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47191715240479</t>
+    <t xml:space="preserve">8.47191524505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.0198860168457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97614049911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39900779724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24590110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21673774719238</t>
+    <t xml:space="preserve">7.97614336013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39900970458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24590015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2167387008667</t>
   </si>
   <si>
     <t xml:space="preserve">8.29693698883057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30422878265381</t>
+    <t xml:space="preserve">8.30422687530518</t>
   </si>
   <si>
     <t xml:space="preserve">8.45733547210693</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">8.67605686187744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39171695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56669616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62654972076416</t>
+    <t xml:space="preserve">8.39171886444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5666971206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62655353546143</t>
   </si>
   <si>
     <t xml:space="preserve">8.73129653930664</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">8.75374317169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9557523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97819709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98567676544189</t>
+    <t xml:space="preserve">8.95575141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.978196144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98567867279053</t>
   </si>
   <si>
     <t xml:space="preserve">8.91086006164551</t>
@@ -317,34 +317,34 @@
     <t xml:space="preserve">8.80611419677734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67892360687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64899730682373</t>
+    <t xml:space="preserve">8.67892456054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6489953994751</t>
   </si>
   <si>
     <t xml:space="preserve">9.08294296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53185176849365</t>
+    <t xml:space="preserve">9.53184986114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.69645404815674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52436923980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49444198608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28495407104492</t>
+    <t xml:space="preserve">9.52437019348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49444389343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28495216369629</t>
   </si>
   <si>
     <t xml:space="preserve">9.15776062011719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34480857849121</t>
+    <t xml:space="preserve">9.34480476379395</t>
   </si>
   <si>
     <t xml:space="preserve">9.17272472381592</t>
@@ -362,10 +362,10 @@
     <t xml:space="preserve">9.8011999130249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30739593505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04553604125977</t>
+    <t xml:space="preserve">9.30739879608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0455322265625</t>
   </si>
   <si>
     <t xml:space="preserve">9.14279651641846</t>
@@ -374,22 +374,22 @@
     <t xml:space="preserve">9.6141529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73386192321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8685359954834</t>
+    <t xml:space="preserve">9.73386383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86853504180908</t>
   </si>
   <si>
     <t xml:space="preserve">9.83112525939941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59918975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32236003875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39717960357666</t>
+    <t xml:space="preserve">9.59918785095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32236289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39718055725098</t>
   </si>
   <si>
     <t xml:space="preserve">9.50940704345703</t>
@@ -404,43 +404,43 @@
     <t xml:space="preserve">9.47947978973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59170722961426</t>
+    <t xml:space="preserve">9.59170627593994</t>
   </si>
   <si>
     <t xml:space="preserve">9.21761512756348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37473487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18768692016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0679817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16524314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09790706634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8285608291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94826984405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70884990692139</t>
+    <t xml:space="preserve">9.37473583221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18768882751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06797981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16524410247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09790515899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82856178283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94826889038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7088508605957</t>
   </si>
   <si>
     <t xml:space="preserve">8.57417774200439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74626159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00064277648926</t>
+    <t xml:space="preserve">8.74625968933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00064086914062</t>
   </si>
   <si>
     <t xml:space="preserve">9.19517040252686</t>
@@ -449,121 +449,121 @@
     <t xml:space="preserve">9.38969802856445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36725330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48695945739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70393562316895</t>
+    <t xml:space="preserve">9.36725234985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48696041107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70393466949463</t>
   </si>
   <si>
     <t xml:space="preserve">9.65156078338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62911701202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51689052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45703506469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09042453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22509670257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29991626739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10538864135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85848903656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66396045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71633148193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88093376159668</t>
+    <t xml:space="preserve">9.62911605834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51688861846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45703411102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09042167663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29991436004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10538768768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85848617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66396141052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71633338928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88093280792236</t>
   </si>
   <si>
     <t xml:space="preserve">8.76870632171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67144107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69388866424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9033784866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70136833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44698619842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5592155456543</t>
+    <t xml:space="preserve">8.67144298553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69388771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90337657928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70136737823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44698715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55921268463135</t>
   </si>
   <si>
     <t xml:space="preserve">9.35976982116699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50192260742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64408111572266</t>
+    <t xml:space="preserve">9.50192546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64407920837402</t>
   </si>
   <si>
     <t xml:space="preserve">9.76379013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7413444519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95083618164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63659954071045</t>
+    <t xml:space="preserve">9.74134254455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95083522796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63659763336182</t>
   </si>
   <si>
     <t xml:space="preserve">9.83860683441162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.816162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94335269927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0406150817871</t>
+    <t xml:space="preserve">9.81616306304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94335460662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0406179428101</t>
   </si>
   <si>
     <t xml:space="preserve">9.99572563171387</t>
   </si>
   <si>
-    <t xml:space="preserve">10.010687828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96579933166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0630617141724</t>
+    <t xml:space="preserve">10.0106906890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96579837799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0630626678467</t>
   </si>
   <si>
     <t xml:space="preserve">9.77127075195312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89846229553223</t>
+    <t xml:space="preserve">9.89846038818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.86105346679688</t>
@@ -572,76 +572,76 @@
     <t xml:space="preserve">9.29243564605713</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2800350189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6765727996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.616717338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8112449645996</t>
+    <t xml:space="preserve">10.2800359725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6765737533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6167163848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8112440109253</t>
   </si>
   <si>
     <t xml:space="preserve">10.9384355545044</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9309530258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9159898757935</t>
+    <t xml:space="preserve">10.9309539794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9159908294678</t>
   </si>
   <si>
     <t xml:space="preserve">10.7214641571045</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1216297149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8045196533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0310249328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0687770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8347187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6761617660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3783416748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464612960815</t>
+    <t xml:space="preserve">11.1216306686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8045177459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.03102684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0687789916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8347206115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6761627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.378342628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464622497559</t>
   </si>
   <si>
     <t xml:space="preserve">11.740758895874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0352191925049</t>
+    <t xml:space="preserve">12.0352201461792</t>
   </si>
   <si>
     <t xml:space="preserve">12.1937770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0805225372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2239799499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5561904907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3749837875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.291934967041</t>
+    <t xml:space="preserve">12.0805234909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2239789962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.556191444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3749856948853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2919330596924</t>
   </si>
   <si>
     <t xml:space="preserve">12.4202871322632</t>
@@ -650,151 +650,151 @@
     <t xml:space="preserve">12.3145818710327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3674345016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5410919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4504899978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5939464569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8280057907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9790115356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0016613006592</t>
+    <t xml:space="preserve">12.3674325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5410928726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4504880905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5939445495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8280048370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9790105819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0016632080078</t>
   </si>
   <si>
     <t xml:space="preserve">12.8129024505615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0243129730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714612960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9488096237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8808574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8657560348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7751502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6769971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8204555511475</t>
+    <t xml:space="preserve">13.0243139266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714593887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9488077163696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8808555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8657550811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7751522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6769981384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8204545974731</t>
   </si>
   <si>
     <t xml:space="preserve">12.7600517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">12.533543586731</t>
+    <t xml:space="preserve">12.5335416793823</t>
   </si>
   <si>
     <t xml:space="preserve">12.7676019668579</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.699649810791</t>
+    <t xml:space="preserve">12.8582067489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6996488571167</t>
   </si>
   <si>
     <t xml:space="preserve">12.6618986129761</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9865636825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0092134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8506555557251</t>
+    <t xml:space="preserve">12.9865617752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0092124938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8506526947021</t>
   </si>
   <si>
     <t xml:space="preserve">12.2164297103882</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2088785171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1258220672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2843818664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1182718276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.148476600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8766651153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0729703903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1560258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2541799545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9748182296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8540124893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1862258911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2390785217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7860584259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7256574630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9068660736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6652555465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5142478942871</t>
+    <t xml:space="preserve">12.2088775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1258239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2843809127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1182737350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.148473739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8766641616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0729722976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1560249328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2541780471802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.974817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8540115356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1862277984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2390766143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.786060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7256555557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9068651199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6652536392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5142469406128</t>
   </si>
   <si>
     <t xml:space="preserve">11.5444498062134</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4613962173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0989809036255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1140823364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1593809127808</t>
+    <t xml:space="preserve">11.4613952636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0989799499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1140804290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1593818664551</t>
   </si>
   <si>
     <t xml:space="preserve">11.0763282775879</t>
@@ -806,22 +806,22 @@
     <t xml:space="preserve">11.408543586731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4991464614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2952890396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1442813873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1669330596924</t>
+    <t xml:space="preserve">11.4991483688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2952871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1442823410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1669340133667</t>
   </si>
   <si>
     <t xml:space="preserve">11.2424373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.993275642395</t>
+    <t xml:space="preserve">10.9932746887207</t>
   </si>
   <si>
     <t xml:space="preserve">11.8389120101929</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">12.0427694320679</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2013282775879</t>
+    <t xml:space="preserve">12.2013273239136</t>
   </si>
   <si>
     <t xml:space="preserve">12.1786756515503</t>
@@ -848,22 +848,22 @@
     <t xml:space="preserve">11.385892868042</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4840459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2801866531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3481407165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.35569190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3405895233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5066967010498</t>
+    <t xml:space="preserve">11.4840478897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2801885604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3481426239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3556909561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3405914306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5066986083984</t>
   </si>
   <si>
     <t xml:space="preserve">10.8724708557129</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">10.8573703765869</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9026718139648</t>
+    <t xml:space="preserve">10.9026708602905</t>
   </si>
   <si>
     <t xml:space="preserve">10.7894153594971</t>
@@ -881,37 +881,37 @@
     <t xml:space="preserve">10.4949541091919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.653510093689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.645959854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6610622406006</t>
+    <t xml:space="preserve">10.6535091400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6459608078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.661060333252</t>
   </si>
   <si>
     <t xml:space="preserve">10.8271675109863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8800201416016</t>
+    <t xml:space="preserve">10.8800220489502</t>
   </si>
   <si>
     <t xml:space="preserve">10.7441139221191</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9781742095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7139129638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8951215744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0183162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9721193313599</t>
+    <t xml:space="preserve">10.978175163269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7139120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8951225280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0183172225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9721183776855</t>
   </si>
   <si>
     <t xml:space="preserve">11.0260162353516</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">10.6410303115845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6025304794312</t>
+    <t xml:space="preserve">10.6025323867798</t>
   </si>
   <si>
     <t xml:space="preserve">10.3561401367188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4793338775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4408349990845</t>
+    <t xml:space="preserve">10.4793348312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4408359527588</t>
   </si>
   <si>
     <t xml:space="preserve">10.4177370071411</t>
@@ -947,31 +947,31 @@
     <t xml:space="preserve">10.4023380279541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7873249053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4947328567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5409317016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3176422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3715391159058</t>
+    <t xml:space="preserve">10.7873258590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5409326553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3176412582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3715381622314</t>
   </si>
   <si>
     <t xml:space="preserve">10.2791433334351</t>
   </si>
   <si>
-    <t xml:space="preserve">10.28684425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3330392837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5101356506348</t>
+    <t xml:space="preserve">10.2868404388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3330411911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5101346969604</t>
   </si>
   <si>
     <t xml:space="preserve">10.8335227966309</t>
@@ -980,46 +980,46 @@
     <t xml:space="preserve">10.8566236495972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7103271484375</t>
+    <t xml:space="preserve">10.7103281021118</t>
   </si>
   <si>
     <t xml:space="preserve">10.6179294586182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3407411575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4716358184814</t>
+    <t xml:space="preserve">10.3407402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4716348648071</t>
   </si>
   <si>
     <t xml:space="preserve">10.7796239852905</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9105205535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0106182098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9413213729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7565259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5255346298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6256303787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3099412918091</t>
+    <t xml:space="preserve">10.9105186462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0106163024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9413204193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7565250396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5255355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6256284713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3099422454834</t>
   </si>
   <si>
     <t xml:space="preserve">10.0943489074707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9942512512207</t>
+    <t xml:space="preserve">9.99425220489502</t>
   </si>
   <si>
     <t xml:space="preserve">9.27047634124756</t>
@@ -1028,28 +1028,28 @@
     <t xml:space="preserve">9.34747505187988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2088794708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29357719421387</t>
+    <t xml:space="preserve">9.20887851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29357528686523</t>
   </si>
   <si>
     <t xml:space="preserve">9.16268157958984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22427845001221</t>
+    <t xml:space="preserve">9.22427940368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.9778881072998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00868606567383</t>
+    <t xml:space="preserve">9.00868701934814</t>
   </si>
   <si>
     <t xml:space="preserve">8.96248817443848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92398834228516</t>
+    <t xml:space="preserve">8.92399024963379</t>
   </si>
   <si>
     <t xml:space="preserve">8.87779140472412</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">8.85469055175781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82389354705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7853946685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72379589080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63910007476807</t>
+    <t xml:space="preserve">8.82389259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78539371490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72379684448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63909912109375</t>
   </si>
   <si>
     <t xml:space="preserve">8.52360248565674</t>
@@ -1079,46 +1079,46 @@
     <t xml:space="preserve">8.62370014190674</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64679908752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60830211639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7468957901001</t>
+    <t xml:space="preserve">8.64680004119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60829925537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74689483642578</t>
   </si>
   <si>
     <t xml:space="preserve">9.03178596496582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11648082733154</t>
+    <t xml:space="preserve">9.11648273468018</t>
   </si>
   <si>
     <t xml:space="preserve">9.1318826675415</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93169021606445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15498352050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37827396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30127716064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32437419891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33207511901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27817821502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26277828216553</t>
+    <t xml:space="preserve">8.93168926239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15498161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37827205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30127429962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32437515258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33207702636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27817726135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26277732849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.2473783493042</t>
@@ -1127,25 +1127,25 @@
     <t xml:space="preserve">9.23967838287354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20117855072021</t>
+    <t xml:space="preserve">9.20118045806885</t>
   </si>
   <si>
     <t xml:space="preserve">9.1087818145752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87009048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84699249267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95478820800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73919677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63139915466309</t>
+    <t xml:space="preserve">8.87009239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84699153900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95478916168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73919486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6314001083374</t>
   </si>
   <si>
     <t xml:space="preserve">8.65449905395508</t>
@@ -1154,43 +1154,43 @@
     <t xml:space="preserve">8.70839691162109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79309368133545</t>
+    <t xml:space="preserve">8.79309463500977</t>
   </si>
   <si>
     <t xml:space="preserve">9.00098609924316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04718589782715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0558490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1328477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1020469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0173511505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94035530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82485771179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70166301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4552698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3089771270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33977508544922</t>
+    <t xml:space="preserve">9.04718494415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.055850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1328468322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1020488739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0173540115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94035339355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82485675811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70166206359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45527076721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30897808074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3397741317749</t>
   </si>
   <si>
     <t xml:space="preserve">9.41760635375977</t>
@@ -1202,163 +1202,163 @@
     <t xml:space="preserve">9.67445087432861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44095611572266</t>
+    <t xml:space="preserve">9.44095516204834</t>
   </si>
   <si>
     <t xml:space="preserve">9.43317317962646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5032205581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69779968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91572666168213</t>
+    <t xml:space="preserve">9.50322151184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69779872894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91572856903076</t>
   </si>
   <si>
     <t xml:space="preserve">9.80676364898682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64331817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76784706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86124420166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4371995925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.188138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.048041343689</t>
+    <t xml:space="preserve">9.64331722259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76784896850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86124515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.13365650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4371976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1881370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0480422973633</t>
   </si>
   <si>
     <t xml:space="preserve">9.95464324951172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1492214202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0324745178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1570062637329</t>
+    <t xml:space="preserve">10.1492223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0324754714966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1570053100586</t>
   </si>
   <si>
     <t xml:space="preserve">10.3126678466797</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3904991149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3437995910645</t>
+    <t xml:space="preserve">10.3905000686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3438005447388</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426204681396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4294166564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6162118911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5928602218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6862592697144</t>
+    <t xml:space="preserve">10.4294137954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6162099838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5928621292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6862573623657</t>
   </si>
   <si>
     <t xml:space="preserve">10.6784763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9508848190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0520658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.114333152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8886203765869</t>
+    <t xml:space="preserve">10.9508857727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0520668029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1143321990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8886222839355</t>
   </si>
   <si>
     <t xml:space="preserve">10.8341388702393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9975852966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0831995010376</t>
+    <t xml:space="preserve">10.9975843429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0831985473633</t>
   </si>
   <si>
     <t xml:space="preserve">11.2933435440063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3011293411255</t>
+    <t xml:space="preserve">11.3011274337769</t>
   </si>
   <si>
     <t xml:space="preserve">11.184380531311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2544279098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3166933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1610298156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9586696624756</t>
+    <t xml:space="preserve">11.2544298171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3166942596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1610317230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9586687088013</t>
   </si>
   <si>
     <t xml:space="preserve">10.9158611297607</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7018241882324</t>
+    <t xml:space="preserve">10.7018260955811</t>
   </si>
   <si>
     <t xml:space="preserve">10.5850782394409</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3048868179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.456657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0519323348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99355888366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90016078948975</t>
+    <t xml:space="preserve">10.3048839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4566564559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0519313812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99355792999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90016269683838</t>
   </si>
   <si>
     <t xml:space="preserve">10.06360912323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1180896759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2620782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5734052658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.666802406311</t>
+    <t xml:space="preserve">10.1180906295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2620763778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5734043121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6668004989624</t>
   </si>
   <si>
     <t xml:space="preserve">10.5461626052856</t>
@@ -1367,16 +1367,16 @@
     <t xml:space="preserve">10.8730545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3478260040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2427530288696</t>
+    <t xml:space="preserve">11.3478269577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2427539825439</t>
   </si>
   <si>
     <t xml:space="preserve">10.9469947814941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0909833908081</t>
+    <t xml:space="preserve">11.0909824371338</t>
   </si>
   <si>
     <t xml:space="preserve">11.149356842041</t>
@@ -1385,52 +1385,52 @@
     <t xml:space="preserve">11.0209341049194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3050193786621</t>
+    <t xml:space="preserve">11.3050203323364</t>
   </si>
   <si>
     <t xml:space="preserve">11.7175254821777</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5462970733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4645719528198</t>
+    <t xml:space="preserve">11.5462961196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4645757675171</t>
   </si>
   <si>
     <t xml:space="preserve">11.1999464035034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1026582717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.277777671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1376800537109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3595018386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7642250061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0442819595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.596752166748</t>
+    <t xml:space="preserve">11.1026554107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2777786254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1376829147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3595008850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7642230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.044282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5967540740967</t>
   </si>
   <si>
     <t xml:space="preserve">10.6239957809448</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7640895843506</t>
+    <t xml:space="preserve">10.7640914916992</t>
   </si>
   <si>
     <t xml:space="preserve">10.6473436355591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8574886322021</t>
+    <t xml:space="preserve">10.8574876785278</t>
   </si>
   <si>
     <t xml:space="preserve">10.8964052200317</t>
@@ -1439,58 +1439,58 @@
     <t xml:space="preserve">10.8263549804688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3244781494141</t>
+    <t xml:space="preserve">11.3244762420654</t>
   </si>
   <si>
     <t xml:space="preserve">11.09876537323</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1298990249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4451160430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6435861587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6708269119263</t>
+    <t xml:space="preserve">11.1298980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4451169967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6435871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.670825958252</t>
   </si>
   <si>
     <t xml:space="preserve">11.59299659729</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5813217163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.865406036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9004316329956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0716590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1611652374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8926477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9393453598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8381652832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1183595657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5425405502319</t>
+    <t xml:space="preserve">11.5813207626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.795355796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8654050827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.900429725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0716581344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1611642837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8926467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9393463134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8381624221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1183576583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5425395965576</t>
   </si>
   <si>
     <t xml:space="preserve">12.5308647155762</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">12.5581064224243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8344078063965</t>
+    <t xml:space="preserve">12.8344068527222</t>
   </si>
   <si>
     <t xml:space="preserve">12.5542135238647</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7604665756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6631784439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7059850692749</t>
+    <t xml:space="preserve">12.7604675292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6631774902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7059860229492</t>
   </si>
   <si>
     <t xml:space="preserve">12.6437206268311</t>
@@ -1520,55 +1520,55 @@
     <t xml:space="preserve">12.7020931243896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9355897903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3597707748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3052864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4556293487549</t>
+    <t xml:space="preserve">12.9355888366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3597717285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3052883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4556283950806</t>
   </si>
   <si>
     <t xml:space="preserve">13.4635419845581</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1549444198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8661298751831</t>
+    <t xml:space="preserve">13.1549434661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8661308288574</t>
   </si>
   <si>
     <t xml:space="preserve">12.5496187210083</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4190587997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4863185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5535764694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1460704803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2964115142822</t>
+    <t xml:space="preserve">12.4190578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4863166809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5535774230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.146071434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2964124679565</t>
   </si>
   <si>
     <t xml:space="preserve">12.0392475128174</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9996843338013</t>
+    <t xml:space="preserve">11.999683380127</t>
   </si>
   <si>
     <t xml:space="preserve">12.3478450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">12.312237739563</t>
+    <t xml:space="preserve">12.3122367858887</t>
   </si>
   <si>
     <t xml:space="preserve">12.3953218460083</t>
@@ -1577,67 +1577,67 @@
     <t xml:space="preserve">12.4230155944824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2726745605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4784049987793</t>
+    <t xml:space="preserve">12.2726736068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4784059524536</t>
   </si>
   <si>
     <t xml:space="preserve">11.9007749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.920557975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7979078292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8374729156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4111471176147</t>
+    <t xml:space="preserve">11.9205551147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.797908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8374719619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4111480712891</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809928894043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9284696578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5377511978149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4665365219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4348840713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3755388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5733585357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6089658737183</t>
+    <t xml:space="preserve">11.9284687042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5377521514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4665355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4348850250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3755397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5733594894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6089649200439</t>
   </si>
   <si>
     <t xml:space="preserve">12.6050090789795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6683120727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9927349090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0520820617676</t>
+    <t xml:space="preserve">12.6683101654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9927339553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0520811080933</t>
   </si>
   <si>
     <t xml:space="preserve">12.6762237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7355680465698</t>
+    <t xml:space="preserve">12.7355690002441</t>
   </si>
   <si>
     <t xml:space="preserve">12.601053237915</t>
@@ -1646,22 +1646,22 @@
     <t xml:space="preserve">12.5456628799438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5575323104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4546661376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4586248397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2489337921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3201513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3676261901855</t>
+    <t xml:space="preserve">12.5575332641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4546670913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4586229324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2489356994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3201503753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3676242828369</t>
   </si>
   <si>
     <t xml:space="preserve">11.5961332321167</t>
@@ -1670,61 +1670,61 @@
     <t xml:space="preserve">11.762300491333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7702140808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9759464263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9324254989624</t>
+    <t xml:space="preserve">11.7702131271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9759454727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9324264526367</t>
   </si>
   <si>
     <t xml:space="preserve">12.0273780822754</t>
   </si>
   <si>
-    <t xml:space="preserve">11.821647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5328311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4418354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5170040130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6159162521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5921764373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7148275375366</t>
+    <t xml:space="preserve">11.8216457366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5328302383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4418363571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5170068740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6159152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5921773910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7148265838623</t>
   </si>
   <si>
     <t xml:space="preserve">12.0867233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8889045715332</t>
+    <t xml:space="preserve">11.8889055252075</t>
   </si>
   <si>
     <t xml:space="preserve">11.892861366272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2281913757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4339237213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4062261581421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3310565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9947662353516</t>
+    <t xml:space="preserve">11.2281894683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4339227676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4062271118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3310575485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9947652816772</t>
   </si>
   <si>
     <t xml:space="preserve">10.9037675857544</t>
@@ -1736,31 +1736,31 @@
     <t xml:space="preserve">10.6228647232056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6901254653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9433307647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9314641952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9354190826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9987201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1451053619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.153018951416</t>
+    <t xml:space="preserve">10.6901235580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9433326721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9314622879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9354181289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9987211227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1451082229614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.153021812439</t>
   </si>
   <si>
     <t xml:space="preserve">11.0857620239258</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0066337585449</t>
+    <t xml:space="preserve">11.0066328048706</t>
   </si>
   <si>
     <t xml:space="preserve">11.1174125671387</t>
@@ -1769,79 +1769,79 @@
     <t xml:space="preserve">11.7306499481201</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6396532058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.584264755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.418098449707</t>
+    <t xml:space="preserve">11.6396551132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5842657089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4180965423584</t>
   </si>
   <si>
     <t xml:space="preserve">11.7266931533813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7820835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9482507705688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6277837753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5723962783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9601192474365</t>
+    <t xml:space="preserve">11.7820825576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9482526779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6277847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.572395324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9601202011108</t>
   </si>
   <si>
     <t xml:space="preserve">11.6238279342651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1332378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1411514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.188627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3112745285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2400588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0936756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.081805229187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8325519561768</t>
+    <t xml:space="preserve">11.1332387924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1411504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1886281967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3112754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2400608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.093674659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0818061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8325538635254</t>
   </si>
   <si>
     <t xml:space="preserve">10.4052639007568</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2984428405762</t>
+    <t xml:space="preserve">10.2984437942505</t>
   </si>
   <si>
     <t xml:space="preserve">10.2628355026245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.171838760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2034921646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0927104949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3933944702148</t>
+    <t xml:space="preserve">10.1718378067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2034902572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0927114486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3933973312378</t>
   </si>
   <si>
     <t xml:space="preserve">10.5635204315186</t>
@@ -1853,25 +1853,25 @@
     <t xml:space="preserve">10.6307792663574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6189088821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.520001411438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4843921661377</t>
+    <t xml:space="preserve">10.6189098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4843940734863</t>
   </si>
   <si>
     <t xml:space="preserve">10.2430534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1599702835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85137271881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75642013549805</t>
+    <t xml:space="preserve">10.159969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85137176513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75641918182373</t>
   </si>
   <si>
     <t xml:space="preserve">9.87510967254639</t>
@@ -1880,121 +1880,121 @@
     <t xml:space="preserve">9.78015804290771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68019580841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40830421447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58823299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45228672027588</t>
+    <t xml:space="preserve">9.68019676208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40830516815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58823394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45228576660156</t>
   </si>
   <si>
     <t xml:space="preserve">9.29634761810303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5602445602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38031578063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71657371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66059684753418</t>
+    <t xml:space="preserve">9.56024551391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38031387329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71657562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6605978012085</t>
   </si>
   <si>
     <t xml:space="preserve">8.49666213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78854846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67259311676025</t>
+    <t xml:space="preserve">8.78854751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67259407043457</t>
   </si>
   <si>
     <t xml:space="preserve">8.50865745544434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22876644134521</t>
+    <t xml:space="preserve">8.22876739501953</t>
   </si>
   <si>
     <t xml:space="preserve">8.24875831604004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9968581199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10881423950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20077800750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18078422546387</t>
+    <t xml:space="preserve">7.99685764312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10881519317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20077896118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18078708648682</t>
   </si>
   <si>
     <t xml:space="preserve">7.89130020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71217107772827</t>
+    <t xml:space="preserve">7.71217012405396</t>
   </si>
   <si>
     <t xml:space="preserve">7.71376943588257</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38109922409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39389562606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34271669387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54903507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61140966415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59861469268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88490104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01285362243652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05683422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29674243927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31673336029053</t>
+    <t xml:space="preserve">7.38109970092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39389419555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3427152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54903411865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61140918731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59861516952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88490152359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01285076141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05683517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29674053192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31673240661621</t>
   </si>
   <si>
     <t xml:space="preserve">8.24076366424561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16878986358643</t>
+    <t xml:space="preserve">8.16879081726074</t>
   </si>
   <si>
     <t xml:space="preserve">8.22476768493652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52065181732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45267677307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3207311630249</t>
+    <t xml:space="preserve">8.52065086364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45267868041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32073020935059</t>
   </si>
   <si>
     <t xml:space="preserve">8.39670085906982</t>
@@ -2003,34 +2003,34 @@
     <t xml:space="preserve">8.53264713287354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8245325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58862495422363</t>
+    <t xml:space="preserve">8.82453155517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58862400054932</t>
   </si>
   <si>
     <t xml:space="preserve">8.70058250427246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75656032562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93249034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9884672164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76455783843994</t>
+    <t xml:space="preserve">8.76855564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75655841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93249130249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98846817016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76455593109131</t>
   </si>
   <si>
     <t xml:space="preserve">8.56463432312012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74456405639648</t>
+    <t xml:space="preserve">8.74456596374512</t>
   </si>
   <si>
     <t xml:space="preserve">8.95248317718506</t>
@@ -2039,73 +2039,73 @@
     <t xml:space="preserve">9.20838260650635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22037792205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43629360198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49227142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55224704742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59623050689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75616836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63221549987793</t>
+    <t xml:space="preserve">9.22037601470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43629264831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49226951599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59622955322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7561674118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63221645355225</t>
   </si>
   <si>
     <t xml:space="preserve">9.61622142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51626110076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51226234436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33233451843262</t>
+    <t xml:space="preserve">9.51626205444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51226329803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3323335647583</t>
   </si>
   <si>
     <t xml:space="preserve">9.39231109619141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36431980133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48427200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25236415863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1124210357666</t>
+    <t xml:space="preserve">9.3643217086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48427391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25236511230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11241912841797</t>
   </si>
   <si>
     <t xml:space="preserve">9.42029857635498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8441333770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89611148834229</t>
+    <t xml:space="preserve">9.84413146972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89611339569092</t>
   </si>
   <si>
     <t xml:space="preserve">9.84813022613525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86812496185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9840784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.036057472229</t>
+    <t xml:space="preserve">9.86812305450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98407745361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0360565185547</t>
   </si>
   <si>
     <t xml:space="preserve">10.3079509735107</t>
@@ -2114,37 +2114,37 @@
     <t xml:space="preserve">10.2039909362793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0680437088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82814121246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0080680847168</t>
+    <t xml:space="preserve">10.0680446624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82814025878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0080661773682</t>
   </si>
   <si>
     <t xml:space="preserve">10.2759637832642</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1720037460327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1440162658691</t>
+    <t xml:space="preserve">10.172004699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1440143585205</t>
   </si>
   <si>
     <t xml:space="preserve">9.95608901977539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2559719085693</t>
+    <t xml:space="preserve">10.255970954895</t>
   </si>
   <si>
     <t xml:space="preserve">10.3199453353882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0440540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93609714508057</t>
+    <t xml:space="preserve">10.0440530776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93609523773193</t>
   </si>
   <si>
     <t xml:space="preserve">10.0040702819824</t>
@@ -2153,25 +2153,25 @@
     <t xml:space="preserve">10.0560483932495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3959159851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5278644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4279022216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7917613983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5598497390747</t>
+    <t xml:space="preserve">10.3959140777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5278635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.427903175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7917594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5598526000977</t>
   </si>
   <si>
     <t xml:space="preserve">10.3359403610229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9281005859375</t>
+    <t xml:space="preserve">9.92809963226318</t>
   </si>
   <si>
     <t xml:space="preserve">9.90011119842529</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">9.74017333984375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60422801971436</t>
+    <t xml:space="preserve">9.60422706604004</t>
   </si>
   <si>
     <t xml:space="preserve">9.44029235839844</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">9.60822582244873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41230392456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34032917022705</t>
+    <t xml:space="preserve">9.41230201721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34033203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.29234886169434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54025173187256</t>
+    <t xml:space="preserve">9.54025077819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.61222362518311</t>
@@ -2213,85 +2213,85 @@
     <t xml:space="preserve">10.0242443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1755714416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85656070709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43939399719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32488059997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16128540039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15310573577881</t>
+    <t xml:space="preserve">10.1755704879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8565616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43939590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32487964630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16128349304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15310478210449</t>
   </si>
   <si>
     <t xml:space="preserve">9.0140495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98542022705078</t>
+    <t xml:space="preserve">8.98541927337646</t>
   </si>
   <si>
     <t xml:space="preserve">8.62960338592529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87499523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08766746520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7891092300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.797287940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78092765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06312942504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19809246063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94452285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8340950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87908458709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05085754394531</t>
+    <t xml:space="preserve">8.8749942779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08766651153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78910636901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79728603363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78092575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0631275177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19809341430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9445219039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83409595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87908363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05085849761963</t>
   </si>
   <si>
     <t xml:space="preserve">9.29625034332275</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39440822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25126171112061</t>
+    <t xml:space="preserve">9.39440727233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25125980377197</t>
   </si>
   <si>
     <t xml:space="preserve">9.14901542663574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42303371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38213539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41485500335693</t>
+    <t xml:space="preserve">9.4230375289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38213729858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41485691070557</t>
   </si>
   <si>
     <t xml:space="preserve">9.65206813812256</t>
@@ -2300,10 +2300,10 @@
     <t xml:space="preserve">9.42712593078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4475736618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54573249816895</t>
+    <t xml:space="preserve">9.44757556915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54573345184326</t>
   </si>
   <si>
     <t xml:space="preserve">9.5416431427002</t>
@@ -2312,46 +2312,46 @@
     <t xml:space="preserve">9.75431442260742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66024780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80748271942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9874382019043</t>
+    <t xml:space="preserve">9.66024875640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80748176574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98743629455566</t>
   </si>
   <si>
     <t xml:space="preserve">9.94244766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83202266693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82793140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45166397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2880687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12038516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24308300018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31260871887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59072017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50892353057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26762294769287</t>
+    <t xml:space="preserve">9.83202075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82793235778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4516658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28806972503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12038612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24308204650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31260967254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59072113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50892162322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26762104034424</t>
   </si>
   <si>
     <t xml:space="preserve">8.93225288391113</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">8.56416511535645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36376190185547</t>
+    <t xml:space="preserve">8.36376285552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.29423522949219</t>
@@ -2372,25 +2372,25 @@
     <t xml:space="preserve">8.44555950164795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27787685394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00958061218262</t>
+    <t xml:space="preserve">8.27787590026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0095796585083</t>
   </si>
   <si>
     <t xml:space="preserve">8.14209270477295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71838331222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75764608383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0521125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88852024078369</t>
+    <t xml:space="preserve">7.71838283538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75764417648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05211544036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88851976394653</t>
   </si>
   <si>
     <t xml:space="preserve">7.98340511322021</t>
@@ -2399,31 +2399,31 @@
     <t xml:space="preserve">8.08810520172119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96377372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07010936737061</t>
+    <t xml:space="preserve">7.96377325057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.12409687042236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21652793884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16335868835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10937309265137</t>
+    <t xml:space="preserve">8.21652889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16336059570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10937213897705</t>
   </si>
   <si>
     <t xml:space="preserve">8.06520175933838</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86070775985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00467395782471</t>
+    <t xml:space="preserve">7.86070823669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00467300415039</t>
   </si>
   <si>
     <t xml:space="preserve">8.21243858337402</t>
@@ -2450,19 +2450,19 @@
     <t xml:space="preserve">8.60506343841553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44146919250488</t>
+    <t xml:space="preserve">8.4414701461792</t>
   </si>
   <si>
     <t xml:space="preserve">8.31877422332764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22061824798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20016670227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97195482254028</t>
+    <t xml:space="preserve">8.22061634063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20016765594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97195291519165</t>
   </si>
   <si>
     <t xml:space="preserve">7.85743808746338</t>
@@ -2474,82 +2474,82 @@
     <t xml:space="preserve">7.72983360290527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00794506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96213674545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81326770782471</t>
+    <t xml:space="preserve">8.0079460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96213912963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81326627731323</t>
   </si>
   <si>
     <t xml:space="preserve">7.4877142906189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56296730041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54824304580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6365852355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50898170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54333639144897</t>
+    <t xml:space="preserve">7.56296825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54824447631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63658475875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50898218154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54333591461182</t>
   </si>
   <si>
     <t xml:space="preserve">7.61531782150269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88034105300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67257642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77400493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74292039871216</t>
+    <t xml:space="preserve">7.88034152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67257499694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7740044593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74292230606079</t>
   </si>
   <si>
     <t xml:space="preserve">7.64803695678711</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60713768005371</t>
+    <t xml:space="preserve">7.60713815689087</t>
   </si>
   <si>
     <t xml:space="preserve">7.66275978088379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68239307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70202302932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61858987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69220781326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80999612808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88524866104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65785312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40591716766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03739166259766</t>
+    <t xml:space="preserve">7.68239259719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70202350616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61859035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69220733642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80999422073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88524913787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6578516960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40591764450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03739070892334</t>
   </si>
   <si>
     <t xml:space="preserve">8.17644596099854</t>
@@ -2558,61 +2558,61 @@
     <t xml:space="preserve">8.32286357879639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18380832672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19607925415039</t>
+    <t xml:space="preserve">8.18380737304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19607830047607</t>
   </si>
   <si>
     <t xml:space="preserve">8.23697662353516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10446548461914</t>
+    <t xml:space="preserve">8.10446453094482</t>
   </si>
   <si>
     <t xml:space="preserve">8.10282897949219</t>
   </si>
   <si>
+    <t xml:space="preserve">8.09955883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02993297576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95865249633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08961200714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04153633117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16918087005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15094470977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15592098236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08629608154297</t>
+  </si>
+  <si>
     <t xml:space="preserve">8.09955787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02993392944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95865106582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08961009979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04153537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16918087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15094566345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591907501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08629608154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0995569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00009441375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85587310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80116987228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96694040298462</t>
+    <t xml:space="preserve">8.00009536743164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85587406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80116939544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96694135665894</t>
   </si>
   <si>
     <t xml:space="preserve">8.03987979888916</t>
@@ -2627,49 +2627,49 @@
     <t xml:space="preserve">8.26864337921143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29682350158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53304767608643</t>
+    <t xml:space="preserve">8.29682445526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53304862976074</t>
   </si>
   <si>
     <t xml:space="preserve">8.44187450408936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46259593963623</t>
+    <t xml:space="preserve">8.46259498596191</t>
   </si>
   <si>
     <t xml:space="preserve">8.40872001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39214134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37970924377441</t>
+    <t xml:space="preserve">8.39214420318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3797082901001</t>
   </si>
   <si>
     <t xml:space="preserve">8.42944049835205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49574947357178</t>
+    <t xml:space="preserve">8.49574851989746</t>
   </si>
   <si>
     <t xml:space="preserve">8.36313343048096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32997894287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37142181396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48331546783447</t>
+    <t xml:space="preserve">8.32997798919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37142086029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48331737518311</t>
   </si>
   <si>
     <t xml:space="preserve">8.71125030517578</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69881916046143</t>
+    <t xml:space="preserve">8.69881725311279</t>
   </si>
   <si>
     <t xml:space="preserve">8.68224143981934</t>
@@ -2678,13 +2678,13 @@
     <t xml:space="preserve">8.60764503479004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60349941253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45016098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40043163299561</t>
+    <t xml:space="preserve">8.60350131988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45016193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40043067932129</t>
   </si>
   <si>
     <t xml:space="preserve">8.45430755615234</t>
@@ -2693,64 +2693,64 @@
     <t xml:space="preserve">8.52890300750732</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50403785705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4708833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41700649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37556552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05811500549316</t>
+    <t xml:space="preserve">8.50403690338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47088432312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41700839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.375563621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05811405181885</t>
   </si>
   <si>
     <t xml:space="preserve">8.18741607666016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28687953948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88074016571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73154592514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64202880859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80282878875732</t>
+    <t xml:space="preserve">8.28687858581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88073873519897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73154497146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64203023910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80282831192017</t>
   </si>
   <si>
     <t xml:space="preserve">7.90891981124878</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93212890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78790855407715</t>
+    <t xml:space="preserve">7.93212747573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78790950775146</t>
   </si>
   <si>
     <t xml:space="preserve">7.83598136901855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90063095092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0067253112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98185920715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80448484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8409538269043</t>
+    <t xml:space="preserve">7.90063190460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00672721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98185968399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80448532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84095430374146</t>
   </si>
   <si>
     <t xml:space="preserve">8.13105392456055</t>
@@ -2759,31 +2759,31 @@
     <t xml:space="preserve">7.7696738243103</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37679719924927</t>
+    <t xml:space="preserve">7.37679672241211</t>
   </si>
   <si>
     <t xml:space="preserve">7.27733469009399</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29391145706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97563219070435</t>
+    <t xml:space="preserve">7.29391193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97563171386719</t>
   </si>
   <si>
     <t xml:space="preserve">6.77007627487183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71868658065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75018358230591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5761251449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45511102676392</t>
+    <t xml:space="preserve">6.71868705749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75018310546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57612419128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45511150360107</t>
   </si>
   <si>
     <t xml:space="preserve">6.08378505706787</t>
@@ -2792,52 +2792,52 @@
     <t xml:space="preserve">4.78248500823975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65815687179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56200933456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8790340423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97766804695129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71989488601685</t>
+    <t xml:space="preserve">4.65815734863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56200981140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87903451919556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97766876220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71989464759827</t>
   </si>
   <si>
     <t xml:space="preserve">3.85085320472717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9453432559967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15918684005737</t>
+    <t xml:space="preserve">3.94534277915955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15918731689453</t>
   </si>
   <si>
     <t xml:space="preserve">4.32661581039429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26362276077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43436574935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46088981628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70788860321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61505651473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62500333786011</t>
+    <t xml:space="preserve">4.26362323760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43436670303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4608907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70788812637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61505603790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59019088745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62500381469727</t>
   </si>
   <si>
     <t xml:space="preserve">4.54543352127075</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">4.7874584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90681266784668</t>
+    <t xml:space="preserve">4.90681314468384</t>
   </si>
   <si>
     <t xml:space="preserve">5.13226079940796</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">4.97809410095215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91178607940674</t>
+    <t xml:space="preserve">4.91178560256958</t>
   </si>
   <si>
     <t xml:space="preserve">4.69131183624268</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">4.77751207351685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80735063552856</t>
+    <t xml:space="preserve">4.80735111236572</t>
   </si>
   <si>
     <t xml:space="preserve">4.77916955947876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046058654785</t>
+    <t xml:space="preserve">4.54046010971069</t>
   </si>
   <si>
     <t xml:space="preserve">4.68136501312256</t>
@@ -2885,19 +2885,19 @@
     <t xml:space="preserve">4.86702823638916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90515661239624</t>
+    <t xml:space="preserve">4.90515613555908</t>
   </si>
   <si>
     <t xml:space="preserve">4.89686632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99135589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28311252593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29969024658203</t>
+    <t xml:space="preserve">4.99135637283325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28311204910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29968929290771</t>
   </si>
   <si>
     <t xml:space="preserve">5.00627517700195</t>
@@ -2906,52 +2906,52 @@
     <t xml:space="preserve">5.24664258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04440259933472</t>
+    <t xml:space="preserve">5.04440212249756</t>
   </si>
   <si>
     <t xml:space="preserve">5.12065744400024</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16375780105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07092618942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98141050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7642502784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79408884048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15878486633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6995997428894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85045194625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61174201965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5984787940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64158058166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71451902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72115039825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83718919754028</t>
+    <t xml:space="preserve">5.16375827789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07092666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98141002655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76424980163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79408931732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15878391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69960069656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85045146942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61174154281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59847927093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64157962799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71451950073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72115087509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83718872070312</t>
   </si>
   <si>
     <t xml:space="preserve">4.63494873046875</t>
@@ -2960,70 +2960,70 @@
     <t xml:space="preserve">4.84382009506226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04606008529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2980318069458</t>
+    <t xml:space="preserve">5.04606056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29803228378296</t>
   </si>
   <si>
     <t xml:space="preserve">5.3527364730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63288879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71577405929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61465406417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53508377075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18365001678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18862295150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18199253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13060331344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12894582748413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04108715057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14220809936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82392692565918</t>
+    <t xml:space="preserve">5.63288974761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71577453613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61465454101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53508424758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18365049362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18862342834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18199300765991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1306037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12894630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04108667373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14220714569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82392740249634</t>
   </si>
   <si>
     <t xml:space="preserve">4.88692092895508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76093482971191</t>
+    <t xml:space="preserve">4.76093435287476</t>
   </si>
   <si>
     <t xml:space="preserve">4.8139820098877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70623111724854</t>
+    <t xml:space="preserve">4.70623064041138</t>
   </si>
   <si>
     <t xml:space="preserve">4.8521089553833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76259279251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93002080917358</t>
+    <t xml:space="preserve">4.76259183883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93002033233643</t>
   </si>
   <si>
     <t xml:space="preserve">4.84547805786133</t>
@@ -3032,25 +3032,25 @@
     <t xml:space="preserve">4.76756525039673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5968222618103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62168836593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67804956436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75761985778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76590776443481</t>
+    <t xml:space="preserve">4.59682178497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62168741226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67805004119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75761938095093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76590871810913</t>
   </si>
   <si>
     <t xml:space="preserve">4.89355087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78414249420166</t>
+    <t xml:space="preserve">4.78414154052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.70291471481323</t>
@@ -3065,88 +3065,88 @@
     <t xml:space="preserve">4.49072933197021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27191114425659</t>
+    <t xml:space="preserve">4.27191162109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.19234132766724</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08790588378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28185844421387</t>
+    <t xml:space="preserve">4.08790636062622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28185749053955</t>
   </si>
   <si>
     <t xml:space="preserve">4.29346179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48575592041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21389150619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29014682769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43602466583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41447353363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32164239883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27688455581665</t>
+    <t xml:space="preserve">4.48575496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21389245986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2901463508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43602514266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41447448730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32164287567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27688503265381</t>
   </si>
   <si>
     <t xml:space="preserve">4.23875665664673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19731426239014</t>
+    <t xml:space="preserve">4.19731473922729</t>
   </si>
   <si>
     <t xml:space="preserve">4.10448265075684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08624744415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22383880615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17576456069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1334924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05806732177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.082932472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0779595375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00004720687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96192026138306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98927235603333</t>
+    <t xml:space="preserve">4.08624839782715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22383785247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17576503753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13349199295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0580677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08293294906616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07796049118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00004768371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96192002296448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98927187919617</t>
   </si>
   <si>
     <t xml:space="preserve">4.00087594985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97601079940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83924913406372</t>
+    <t xml:space="preserve">3.97601103782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83924984931946</t>
   </si>
   <si>
     <t xml:space="preserve">3.84422302246094</t>
@@ -3155,64 +3155,64 @@
     <t xml:space="preserve">3.82598829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77957248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74724745750427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80112338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95943355560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96274852752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85334038734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60053944587708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56075525283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53091597557068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45880579948425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39747071266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53754734992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42399382591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53174519538879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44140005111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52097034454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55578207969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65358591079712</t>
+    <t xml:space="preserve">3.77957224845886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74724650382996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80112314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95943379402161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96274948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85334086418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60053968429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56075501441956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53091621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45880532264709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39747047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53754687309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4239935874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53174567222595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44139981269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5209698677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5557816028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65358662605286</t>
   </si>
   <si>
     <t xml:space="preserve">3.58064770698547</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69005632400513</t>
+    <t xml:space="preserve">3.69005608558655</t>
   </si>
   <si>
     <t xml:space="preserve">3.66436171531677</t>
@@ -3221,19 +3221,19 @@
     <t xml:space="preserve">3.60302662849426</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51351022720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60717105865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42730927467346</t>
+    <t xml:space="preserve">3.51350998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60717082023621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42730951309204</t>
   </si>
   <si>
     <t xml:space="preserve">3.5508086681366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62623405456543</t>
+    <t xml:space="preserve">3.62623429298401</t>
   </si>
   <si>
     <t xml:space="preserve">3.71077728271484</t>
@@ -3242,34 +3242,34 @@
     <t xml:space="preserve">3.61877465248108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63783931732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67099237442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57401633262634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47455430030823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37011885643005</t>
+    <t xml:space="preserve">3.63783836364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67099285125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57401609420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47455406188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37011861801147</t>
   </si>
   <si>
     <t xml:space="preserve">3.1728515625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37509179115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55163764953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63535213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19399976730347</t>
+    <t xml:space="preserve">3.37509155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55163717269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63535165786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19399929046631</t>
   </si>
   <si>
     <t xml:space="preserve">4.17244863510132</t>
@@ -3278,55 +3278,55 @@
     <t xml:space="preserve">4.57029914855957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63660621643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64655303955078</t>
+    <t xml:space="preserve">4.63660669326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64655351638794</t>
   </si>
   <si>
     <t xml:space="preserve">4.6763916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74601554870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11402750015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21183156967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27316617965698</t>
+    <t xml:space="preserve">4.7460150718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11402654647827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21183109283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27316570281982</t>
   </si>
   <si>
     <t xml:space="preserve">5.19359636306763</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18033456802368</t>
+    <t xml:space="preserve">5.18033361434937</t>
   </si>
   <si>
     <t xml:space="preserve">5.39324903488159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73357486724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67825078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60113191604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61957359313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4368371963501</t>
+    <t xml:space="preserve">5.73357439041138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67825126647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60113143920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61957311630249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43683671951294</t>
   </si>
   <si>
     <t xml:space="preserve">5.52066087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54748439788818</t>
+    <t xml:space="preserve">5.54748487472534</t>
   </si>
   <si>
     <t xml:space="preserve">5.58101463317871</t>
@@ -3338,88 +3338,88 @@
     <t xml:space="preserve">5.70339775085449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71178007125854</t>
+    <t xml:space="preserve">5.71178102493286</t>
   </si>
   <si>
     <t xml:space="preserve">5.71513319015503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80231046676636</t>
+    <t xml:space="preserve">5.8023099899292</t>
   </si>
   <si>
     <t xml:space="preserve">5.70004510879517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6262788772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69501543045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66651487350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72183895111084</t>
+    <t xml:space="preserve">5.62627935409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6950159072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66651582717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.721839427948</t>
   </si>
   <si>
     <t xml:space="preserve">5.63801431655884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49048519134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47539615631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62795639038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58772134780884</t>
+    <t xml:space="preserve">5.49048471450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47539663314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6279559135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58772039413452</t>
   </si>
   <si>
     <t xml:space="preserve">5.51227903366089</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55251407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47874927520752</t>
+    <t xml:space="preserve">5.55251359939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47874975204468</t>
   </si>
   <si>
     <t xml:space="preserve">5.67489719390869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97834062576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9699592590332</t>
+    <t xml:space="preserve">5.97834157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96995830535889</t>
   </si>
   <si>
     <t xml:space="preserve">5.93642902374268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82913398742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99678230285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9129581451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96492910385132</t>
+    <t xml:space="preserve">5.82913494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99678182601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91295766830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96492958068848</t>
   </si>
   <si>
     <t xml:space="preserve">5.65813302993774</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64304447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4619836807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27254104614258</t>
+    <t xml:space="preserve">5.64304399490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46198415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27254152297974</t>
   </si>
   <si>
     <t xml:space="preserve">5.1786584854126</t>
@@ -3428,31 +3428,31 @@
     <t xml:space="preserve">5.24739408493042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33792448043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50054311752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38989496231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3815131187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60448503494263</t>
+    <t xml:space="preserve">5.33792400360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50054264068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38989543914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38151216506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60448551177979</t>
   </si>
   <si>
     <t xml:space="preserve">5.6933388710022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80733919143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92972373962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82410430908203</t>
+    <t xml:space="preserve">5.80733966827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92972326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82410478591919</t>
   </si>
   <si>
     <t xml:space="preserve">5.89451694488525</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">5.90122318267822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95989990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31196212768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32201957702637</t>
+    <t xml:space="preserve">5.95990037918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31196117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32202005386353</t>
   </si>
   <si>
     <t xml:space="preserve">6.17952013015747</t>
@@ -3476,88 +3476,88 @@
     <t xml:space="preserve">6.0353422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06551742553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29351997375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22813749313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44440364837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32958841323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24743986129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41508817672729</t>
+    <t xml:space="preserve">6.06551885604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29351949691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22813653945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44440317153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32958698272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24743938446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41508722305298</t>
   </si>
   <si>
     <t xml:space="preserve">7.53579425811768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51903009414673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78559064865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02700519561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14435863494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00520992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11082744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30697727203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31200885772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10579967498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12926959991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09741592407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99682664871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81576776504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75038385391235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61961984634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90294456481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69170665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97168064117432</t>
+    <t xml:space="preserve">7.51902914047241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78558969497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02700424194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14435768127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00521087646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1108283996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30697631835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31200790405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10579872131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12927055358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09741687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99682855606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81576633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75038433074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61961889266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90294504165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69170761108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97168016433716</t>
   </si>
   <si>
     <t xml:space="preserve">8.01526832580566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09573936462402</t>
+    <t xml:space="preserve">8.09574127197266</t>
   </si>
   <si>
     <t xml:space="preserve">8.05718040466309</t>
@@ -3572,67 +3572,67 @@
     <t xml:space="preserve">7.98173952102661</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77720832824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69506025314331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63973569869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62967729568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99850368499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70679569244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68332529067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73864889144897</t>
+    <t xml:space="preserve">7.7772068977356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69506120681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63973665237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62967777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99850273132324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70679521560669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68332481384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73864936828613</t>
   </si>
   <si>
     <t xml:space="preserve">7.39496850967407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4704122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46370697021484</t>
+    <t xml:space="preserve">7.47041130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46370553970337</t>
   </si>
   <si>
     <t xml:space="preserve">7.44358777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7000904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.539146900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79229640960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26420402526855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50897169113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57602977752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6380615234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98006343841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12591743469238</t>
+    <t xml:space="preserve">7.70008993148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53914737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79229593276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26420545578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50897121429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5760293006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63806104660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98006391525269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1259183883667</t>
   </si>
   <si>
     <t xml:space="preserve">8.20806407928467</t>
@@ -3641,106 +3641,106 @@
     <t xml:space="preserve">8.01359272003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28350639343262</t>
+    <t xml:space="preserve">8.2835054397583</t>
   </si>
   <si>
     <t xml:space="preserve">8.19632816314697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21477031707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12759208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90462064743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85600233078003</t>
+    <t xml:space="preserve">8.21476936340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12759304046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90462207794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85600280761719</t>
   </si>
   <si>
     <t xml:space="preserve">7.92976760864258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9586968421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80214405059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82596683502197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04548263549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96039772033691</t>
+    <t xml:space="preserve">7.95869636535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80214357376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82596635818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04548168182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96039819717407</t>
   </si>
   <si>
     <t xml:space="preserve">7.93827676773071</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15268802642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24627780914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31604766845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1918249130249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20203495025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17140483856201</t>
+    <t xml:space="preserve">8.15268611907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24627876281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31604671478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19182586669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20203590393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17140579223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.11354827880859</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12545871734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29052257537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14077472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13056373596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.948486328125</t>
+    <t xml:space="preserve">8.12546062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29052352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14077377319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13056468963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94848680496216</t>
   </si>
   <si>
     <t xml:space="preserve">7.81575679779053</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84468507766724</t>
+    <t xml:space="preserve">7.84468460083008</t>
   </si>
   <si>
     <t xml:space="preserve">7.92296266555786</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9757137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02506160736084</t>
+    <t xml:space="preserve">7.97571325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02506256103516</t>
   </si>
   <si>
     <t xml:space="preserve">8.07100677490234</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80384635925293</t>
+    <t xml:space="preserve">7.80384540557861</t>
   </si>
   <si>
     <t xml:space="preserve">7.80554628372192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82086133956909</t>
+    <t xml:space="preserve">7.82086181640625</t>
   </si>
   <si>
     <t xml:space="preserve">7.97060823440552</t>
@@ -3752,85 +3752,85 @@
     <t xml:space="preserve">8.0216588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64388704299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52987670898438</t>
+    <t xml:space="preserve">7.6438889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52987766265869</t>
   </si>
   <si>
     <t xml:space="preserve">7.42607450485229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65920448303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63197660446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46861791610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59964466094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46521282196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25420570373535</t>
+    <t xml:space="preserve">7.65920305252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63197612762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46861696243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59964513778687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46521377563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25420665740967</t>
   </si>
   <si>
     <t xml:space="preserve">7.00235939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12317800521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26271533966064</t>
+    <t xml:space="preserve">7.12317848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26271438598633</t>
   </si>
   <si>
     <t xml:space="preserve">7.18103504180908</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26441669464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47372102737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40735626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031831741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46691513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29674863815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35800933837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40565586090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30866003036499</t>
+    <t xml:space="preserve">7.26441717147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47372150421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40735721588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031784057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46691465377808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29674816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35800886154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40565490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30865955352783</t>
   </si>
   <si>
     <t xml:space="preserve">7.28313493728638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4822301864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44138956069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4856333732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49584436416626</t>
+    <t xml:space="preserve">7.48222875595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44139003753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48563289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49584341049194</t>
   </si>
   <si>
     <t xml:space="preserve">7.30185270309448</t>
@@ -3839,94 +3839,94 @@
     <t xml:space="preserve">7.3341851234436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99385166168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93769598007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07042694091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09254884719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15550947189331</t>
+    <t xml:space="preserve">6.99385261535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93769645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07042646408081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09254789352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15550994873047</t>
   </si>
   <si>
     <t xml:space="preserve">7.22187519073486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33758783340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25761032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34269380569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22527694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21166515350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14700174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09425020217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06361961364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30695772171021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25590801239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37672710418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14019441604614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87473487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87303352355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23038339614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28824043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32567644119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57241725921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53668308258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5979437828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73577833175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7255687713623</t>
+    <t xml:space="preserve">7.33758735656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25760936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34269332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22527742385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21166563034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14700126647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09425067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06362009048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30695819854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25590705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37672662734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14019536972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87473440170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87303400039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23038387298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28823947906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32567691802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57241821289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53668403625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59794330596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73577928543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72556829452515</t>
   </si>
   <si>
     <t xml:space="preserve">7.93997812271118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67792177200317</t>
+    <t xml:space="preserve">7.67792272567749</t>
   </si>
   <si>
     <t xml:space="preserve">7.79873991012573</t>
@@ -3935,76 +3935,76 @@
     <t xml:space="preserve">8.15609073638916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35008144378662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21054458618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10333824157715</t>
+    <t xml:space="preserve">8.35007953643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21054363250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10333728790283</t>
   </si>
   <si>
     <t xml:space="preserve">8.14758205413818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35348415374756</t>
+    <t xml:space="preserve">8.40283107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35348320007324</t>
   </si>
   <si>
     <t xml:space="preserve">8.45898723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60618114471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43856716156006</t>
+    <t xml:space="preserve">8.60618019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43856525421143</t>
   </si>
   <si>
     <t xml:space="preserve">8.39092063903809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56363964080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55513286590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42325210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19012355804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19352626800537</t>
+    <t xml:space="preserve">8.56363868713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55513095855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42325115203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19012451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.193528175354</t>
   </si>
   <si>
     <t xml:space="preserve">8.41474342346191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38241291046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27520561218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79336357116699</t>
+    <t xml:space="preserve">8.38241195678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27520847320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79336452484131</t>
   </si>
   <si>
     <t xml:space="preserve">9.03585147857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27833843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23154544830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92524242401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83165264129639</t>
+    <t xml:space="preserve">9.27833938598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23154354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92524337768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83165168762207</t>
   </si>
   <si>
     <t xml:space="preserve">8.73380565643311</t>
@@ -4019,10 +4019,10 @@
     <t xml:space="preserve">8.28881931304932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07611179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26934432983398</t>
+    <t xml:space="preserve">8.07610988616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2693452835083</t>
   </si>
   <si>
     <t xml:space="preserve">8.21585941314697</t>
@@ -4031,67 +4031,67 @@
     <t xml:space="preserve">8.31247615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20895957946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62753534317017</t>
+    <t xml:space="preserve">8.20895862579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62753486633301</t>
   </si>
   <si>
     <t xml:space="preserve">7.69654703140259</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47225713729858</t>
+    <t xml:space="preserve">7.47225761413574</t>
   </si>
   <si>
     <t xml:space="preserve">7.78108596801758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70689725875854</t>
+    <t xml:space="preserve">7.70689821243286</t>
   </si>
   <si>
     <t xml:space="preserve">7.72932767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84319686889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01745128631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9191107749939</t>
+    <t xml:space="preserve">7.84319734573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0174503326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91911029815674</t>
   </si>
   <si>
     <t xml:space="preserve">7.76038217544556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69309520721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62408351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87942886352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6361608505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85527324676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78798627853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61373233795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86390066146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86217451095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8759765625</t>
+    <t xml:space="preserve">7.69309568405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62408447265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87942743301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63616180419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85527372360229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78798818588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6137318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86390018463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86217498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87597703933716</t>
   </si>
   <si>
     <t xml:space="preserve">7.96051692962646</t>
@@ -4103,37 +4103,37 @@
     <t xml:space="preserve">8.0105504989624</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94498872756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25899314880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37286281585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43669891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43842315673828</t>
+    <t xml:space="preserve">7.94498825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25899219512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37286376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43669700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43842220306396</t>
   </si>
   <si>
     <t xml:space="preserve">8.45222568511963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40909481048584</t>
+    <t xml:space="preserve">8.40909576416016</t>
   </si>
   <si>
     <t xml:space="preserve">8.58162307739258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65667343139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6782398223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85076999664307</t>
+    <t xml:space="preserve">8.6566743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67824077606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85077095031738</t>
   </si>
   <si>
     <t xml:space="preserve">9.06211757659912</t>
@@ -4142,61 +4142,61 @@
     <t xml:space="preserve">9.25190162658691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28640842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93703556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49708461761475</t>
+    <t xml:space="preserve">9.28640747070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93703365325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49708271026611</t>
   </si>
   <si>
     <t xml:space="preserve">8.88958835601807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55382633209229</t>
+    <t xml:space="preserve">9.55382823944092</t>
   </si>
   <si>
     <t xml:space="preserve">9.37698554992676</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8385009765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78243064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65734481811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85144233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86006927490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77380180358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87732124328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97652435302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0800428390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92476749420166</t>
+    <t xml:space="preserve">9.83850193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78242969512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65734577178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85144329071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86006832122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77380275726318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87732028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97652626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0800447463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92476558685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.99809169769287</t>
   </si>
   <si>
-    <t xml:space="preserve">10.226692199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93770599365234</t>
+    <t xml:space="preserve">10.2266931533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93770503997803</t>
   </si>
   <si>
     <t xml:space="preserve">9.75223541259766</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">9.44599628448486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5236349105835</t>
+    <t xml:space="preserve">9.52363395690918</t>
   </si>
   <si>
     <t xml:space="preserve">9.42443084716797</t>
@@ -4214,25 +4214,25 @@
     <t xml:space="preserve">9.32091331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60989856719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95495986938477</t>
+    <t xml:space="preserve">9.60989952087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95495891571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.86869430541992</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3560905456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1447420120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96358489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2618703842163</t>
+    <t xml:space="preserve">10.3560914993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1447410583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96358585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2618713378906</t>
   </si>
   <si>
     <t xml:space="preserve">11.6241817474365</t>
@@ -4244,34 +4244,34 @@
     <t xml:space="preserve">11.1540403366089</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1497278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8736801147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5113687515259</t>
+    <t xml:space="preserve">11.1497268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8736791610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5113668441772</t>
   </si>
   <si>
     <t xml:space="preserve">10.7356557846069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.908185005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5724248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6371240615845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9606142044067</t>
+    <t xml:space="preserve">10.9081859588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5724239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6371231079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9606151580811</t>
   </si>
   <si>
     <t xml:space="preserve">11.9951219558716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2927360534668</t>
+    <t xml:space="preserve">12.2927350997925</t>
   </si>
   <si>
     <t xml:space="preserve">12.0123748779297</t>
@@ -4283,10 +4283,10 @@
     <t xml:space="preserve">11.8829774856567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8657264709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9821825027466</t>
+    <t xml:space="preserve">11.8657255172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9821815490723</t>
   </si>
   <si>
     <t xml:space="preserve">11.9735546112061</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">12.0727605819702</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9390497207642</t>
+    <t xml:space="preserve">11.9390487670898</t>
   </si>
   <si>
     <t xml:space="preserve">11.9908084869385</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">12.8146381378174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9224672317505</t>
+    <t xml:space="preserve">12.9224681854248</t>
   </si>
   <si>
     <t xml:space="preserve">12.9914808273315</t>
@@ -4322,88 +4322,88 @@
     <t xml:space="preserve">12.9310941696167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5817222595215</t>
+    <t xml:space="preserve">12.5817213058472</t>
   </si>
   <si>
     <t xml:space="preserve">11.723388671875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1374588012695</t>
+    <t xml:space="preserve">12.1374578475952</t>
   </si>
   <si>
     <t xml:space="preserve">12.0813865661621</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7758188247681</t>
+    <t xml:space="preserve">12.7758169174194</t>
   </si>
   <si>
     <t xml:space="preserve">12.2841091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8448314666748</t>
+    <t xml:space="preserve">12.8448295593262</t>
   </si>
   <si>
     <t xml:space="preserve">12.6981811523438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6377954483032</t>
+    <t xml:space="preserve">12.6377935409546</t>
   </si>
   <si>
     <t xml:space="preserve">12.5385894775391</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0598201751709</t>
+    <t xml:space="preserve">12.0598192214966</t>
   </si>
   <si>
     <t xml:space="preserve">12.180591583252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5989742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2668561935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7283716201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2718420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4486827850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3667316436768</t>
+    <t xml:space="preserve">12.5989751815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2668571472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7283725738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2718410491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4486846923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3667325973511</t>
   </si>
   <si>
     <t xml:space="preserve">13.021674156189</t>
   </si>
   <si>
-    <t xml:space="preserve">13.19420337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.488579750061</t>
+    <t xml:space="preserve">13.1942024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4885787963867</t>
   </si>
   <si>
     <t xml:space="preserve">13.3040437698364</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5456962585449</t>
+    <t xml:space="preserve">13.5456972122192</t>
   </si>
   <si>
     <t xml:space="preserve">13.9147644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0861196517944</t>
+    <t xml:space="preserve">14.0861186981201</t>
   </si>
   <si>
     <t xml:space="preserve">14.2530765533447</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7302312850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8356790542603</t>
+    <t xml:space="preserve">13.7302303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8356781005859</t>
   </si>
   <si>
     <t xml:space="preserve">13.86643409729</t>
@@ -4412,7 +4412,7 @@
     <t xml:space="preserve">13.8224973678589</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9630947113037</t>
+    <t xml:space="preserve">13.963095664978</t>
   </si>
   <si>
     <t xml:space="preserve">14.0641489028931</t>
@@ -4421,52 +4421,52 @@
     <t xml:space="preserve">14.0246067047119</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4094924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0052757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.803165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.693323135376</t>
+    <t xml:space="preserve">13.4094934463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.005274772644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8031644821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6933240890503</t>
   </si>
   <si>
     <t xml:space="preserve">12.3154668807983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5641489028931</t>
+    <t xml:space="preserve">11.5641498565674</t>
   </si>
   <si>
     <t xml:space="preserve">11.3927965164185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6080856323242</t>
+    <t xml:space="preserve">11.6080846786499</t>
   </si>
   <si>
     <t xml:space="preserve">11.6739912033081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0720586776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7381381988525</t>
+    <t xml:space="preserve">11.0720567703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7381391525269</t>
   </si>
   <si>
     <t xml:space="preserve">10.9402475357056</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9578227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2302293777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0632705688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7820749282837</t>
+    <t xml:space="preserve">10.9578237533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2302303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0632696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.782075881958</t>
   </si>
   <si>
     <t xml:space="preserve">10.579966545105</t>
@@ -4475,103 +4475,103 @@
     <t xml:space="preserve">10.966609954834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0615129470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75835037231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7469253540039</t>
+    <t xml:space="preserve">10.0615119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75834941864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7469263076782</t>
   </si>
   <si>
     <t xml:space="preserve">11.1423559188843</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2082624435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1116008758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841842651367</t>
+    <t xml:space="preserve">11.2082614898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1116018295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.984185218811</t>
   </si>
   <si>
     <t xml:space="preserve">10.5404233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7117757797241</t>
+    <t xml:space="preserve">10.7117767333984</t>
   </si>
   <si>
     <t xml:space="preserve">11.1467514038086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1819000244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.067663192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8523731231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9753971099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0940265655518</t>
+    <t xml:space="preserve">11.1819009780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0676641464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8523740768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.975396156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0940256118774</t>
   </si>
   <si>
     <t xml:space="preserve">11.4411277770996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5861186981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9551858901978</t>
+    <t xml:space="preserve">11.5861177444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9551868438721</t>
   </si>
   <si>
     <t xml:space="preserve">11.6344480514526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6608104705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5290002822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0896339416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3005275726318</t>
+    <t xml:space="preserve">11.6608114242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5289993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0896329879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3005294799805</t>
   </si>
   <si>
     <t xml:space="preserve">11.4147644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2917432785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5685434341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.542181968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3224973678589</t>
+    <t xml:space="preserve">11.2917423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5685443878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5421810150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3224983215332</t>
   </si>
   <si>
     <t xml:space="preserve">11.6827783584595</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2829542160034</t>
+    <t xml:space="preserve">11.2829532623291</t>
   </si>
   <si>
     <t xml:space="preserve">12.2803192138672</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1704769134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3945531845093</t>
+    <t xml:space="preserve">12.1704759597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.394552230835</t>
   </si>
   <si>
     <t xml:space="preserve">12.2188062667847</t>
@@ -4586,13 +4586,13 @@
     <t xml:space="preserve">12.0298776626587</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4384899139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5527276992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1221466064453</t>
+    <t xml:space="preserve">12.4384889602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5527257919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.122145652771</t>
   </si>
   <si>
     <t xml:space="preserve">11.739896774292</t>
@@ -4601,100 +4601,100 @@
     <t xml:space="preserve">11.7442903518677</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3286476135254</t>
+    <t xml:space="preserve">12.3286485671997</t>
   </si>
   <si>
     <t xml:space="preserve">12.5790872573853</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5219707489014</t>
+    <t xml:space="preserve">12.5219697952271</t>
   </si>
   <si>
     <t xml:space="preserve">12.5175762176514</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2407751083374</t>
+    <t xml:space="preserve">12.2407741546631</t>
   </si>
   <si>
     <t xml:space="preserve">11.9288244247437</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9024620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7882280349731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1265382766724</t>
+    <t xml:space="preserve">11.9024610519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7882270812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.126540184021</t>
   </si>
   <si>
     <t xml:space="preserve">10.9622163772583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1994733810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5377883911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8761005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6564178466797</t>
+    <t xml:space="preserve">11.1994752883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.537787437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8760995864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6564168930054</t>
   </si>
   <si>
     <t xml:space="preserve">12.4604587554932</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7504396438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0140619277954</t>
+    <t xml:space="preserve">12.7504405975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0140609741211</t>
   </si>
   <si>
     <t xml:space="preserve">13.1854162216187</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7328653335571</t>
+    <t xml:space="preserve">12.7328662872314</t>
   </si>
   <si>
     <t xml:space="preserve">12.1353273391724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2451696395874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8163461685181</t>
+    <t xml:space="preserve">12.2451705932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8163452148438</t>
   </si>
   <si>
     <t xml:space="preserve">12.5615139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9217948913574</t>
+    <t xml:space="preserve">12.9217939376831</t>
   </si>
   <si>
     <t xml:space="preserve">13.2117767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1590528488159</t>
+    <t xml:space="preserve">13.1590538024902</t>
   </si>
   <si>
     <t xml:space="preserve">13.3216199874878</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2205648422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5193338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8927974700928</t>
+    <t xml:space="preserve">13.2205657958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5193347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8927965164185</t>
   </si>
   <si>
     <t xml:space="preserve">13.4534301757812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8005294799805</t>
+    <t xml:space="preserve">13.8005275726318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1564168930054</t>
@@ -4703,10 +4703,10 @@
     <t xml:space="preserve">13.9982442855835</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1959609985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6265420913696</t>
+    <t xml:space="preserve">14.1959619522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6265411376953</t>
   </si>
   <si>
     <t xml:space="preserve">14.7539577484131</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">14.3585252761841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7653789520264</t>
+    <t xml:space="preserve">13.7653799057007</t>
   </si>
   <si>
     <t xml:space="preserve">14.055362701416</t>
@@ -4727,13 +4727,13 @@
     <t xml:space="preserve">13.9938507080078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6572961807251</t>
+    <t xml:space="preserve">14.6572971343994</t>
   </si>
   <si>
     <t xml:space="preserve">14.7275953292847</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3101949691772</t>
+    <t xml:space="preserve">14.3101940155029</t>
   </si>
   <si>
     <t xml:space="preserve">14.4244318008423</t>
@@ -4742,7 +4742,7 @@
     <t xml:space="preserve">13.7851209640503</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6908102035522</t>
+    <t xml:space="preserve">14.6908111572266</t>
   </si>
   <si>
     <t xml:space="preserve">14.3578367233276</t>
@@ -4784,13 +4784,13 @@
     <t xml:space="preserve">13.6608104705811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5276203155518</t>
+    <t xml:space="preserve">13.5276193618774</t>
   </si>
   <si>
     <t xml:space="preserve">13.9893455505371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0159816741943</t>
+    <t xml:space="preserve">14.0159826278687</t>
   </si>
   <si>
     <t xml:space="preserve">13.7451639175415</t>
@@ -4802,10 +4802,10 @@
     <t xml:space="preserve">13.949387550354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1402931213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643888473511</t>
+    <t xml:space="preserve">14.1402940750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643898010254</t>
   </si>
   <si>
     <t xml:space="preserve">14.7218885421753</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">14.7796049118042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6686115264893</t>
+    <t xml:space="preserve">14.6686124801636</t>
   </si>
   <si>
     <t xml:space="preserve">14.7130088806152</t>
@@ -4823,46 +4823,46 @@
     <t xml:space="preserve">14.4599475860596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9349908828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4199914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4033126831055</t>
+    <t xml:space="preserve">14.9349899291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4199924468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4033117294312</t>
   </si>
   <si>
     <t xml:space="preserve">13.793999671936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0071039199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0603790283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0692577362061</t>
+    <t xml:space="preserve">14.0071029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0603799819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0692586898804</t>
   </si>
   <si>
     <t xml:space="preserve">14.237964630127</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4421882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.344518661499</t>
+    <t xml:space="preserve">14.4421892166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3445177078247</t>
   </si>
   <si>
     <t xml:space="preserve">14.2290849685669</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6597309112549</t>
+    <t xml:space="preserve">14.6597318649292</t>
   </si>
   <si>
     <t xml:space="preserve">15.2679634094238</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5176639556885</t>
+    <t xml:space="preserve">14.5176630020142</t>
   </si>
   <si>
     <t xml:space="preserve">14.6952486038208</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">14.26904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2956800460815</t>
+    <t xml:space="preserve">14.2956809997559</t>
   </si>
   <si>
     <t xml:space="preserve">14.6197748184204</t>
@@ -4883,19 +4883,19 @@
     <t xml:space="preserve">14.3977928161621</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4288721084595</t>
+    <t xml:space="preserve">14.4288711547852</t>
   </si>
   <si>
     <t xml:space="preserve">14.1180953979492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.629734992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5498189926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4388275146484</t>
+    <t xml:space="preserve">13.6297340393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5498199462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4388284683228</t>
   </si>
   <si>
     <t xml:space="preserve">13.540940284729</t>
@@ -4910,16 +4910,16 @@
     <t xml:space="preserve">14.0825777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">14.380033493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4011526107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6641721725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4377498626709</t>
+    <t xml:space="preserve">14.3800344467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4011535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6641712188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4377508163452</t>
   </si>
   <si>
     <t xml:space="preserve">13.971586227417</t>
@@ -4928,16 +4928,16 @@
     <t xml:space="preserve">14.2246465682983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9227514266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2646036148071</t>
+    <t xml:space="preserve">13.9227504730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2646045684814</t>
   </si>
   <si>
     <t xml:space="preserve">14.3267593383789</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3711538314819</t>
+    <t xml:space="preserve">14.3711547851562</t>
   </si>
   <si>
     <t xml:space="preserve">14.4732666015625</t>
@@ -4949,16 +4949,16 @@
     <t xml:space="preserve">14.0026636123657</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7140874862671</t>
+    <t xml:space="preserve">13.7140865325928</t>
   </si>
   <si>
     <t xml:space="preserve">12.9105100631714</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0969734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9249076843262</t>
+    <t xml:space="preserve">13.0969753265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9249067306519</t>
   </si>
   <si>
     <t xml:space="preserve">11.9559850692749</t>
@@ -4973,13 +4973,13 @@
     <t xml:space="preserve">12.1646480560303</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0358972549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.765079498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3877086639404</t>
+    <t xml:space="preserve">12.0358982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7650785446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3877077102661</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942598342896</t>
@@ -4988,22 +4988,22 @@
     <t xml:space="preserve">11.8361129760742</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7739591598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6096897125244</t>
+    <t xml:space="preserve">11.7739582061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6096906661987</t>
   </si>
   <si>
     <t xml:space="preserve">11.631890296936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9826231002808</t>
+    <t xml:space="preserve">11.9826221466064</t>
   </si>
   <si>
     <t xml:space="preserve">11.6851654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5386562347412</t>
+    <t xml:space="preserve">11.5386552810669</t>
   </si>
   <si>
     <t xml:space="preserve">11.5075788497925</t>
@@ -5015,10 +5015,10 @@
     <t xml:space="preserve">11.9737424850464</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9337863922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8405542373657</t>
+    <t xml:space="preserve">11.9337854385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8405523300171</t>
   </si>
   <si>
     <t xml:space="preserve">11.7828378677368</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">11.6540880203247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6363286972046</t>
+    <t xml:space="preserve">11.6363296508789</t>
   </si>
   <si>
     <t xml:space="preserve">11.5874938964844</t>
@@ -5054,13 +5054,13 @@
     <t xml:space="preserve">11.1168899536133</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0991306304932</t>
+    <t xml:space="preserve">11.0991315841675</t>
   </si>
   <si>
     <t xml:space="preserve">10.8771476745605</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7528381347656</t>
+    <t xml:space="preserve">10.7528371810913</t>
   </si>
   <si>
     <t xml:space="preserve">10.8815879821777</t>
@@ -5069,19 +5069,19 @@
     <t xml:space="preserve">10.8460712432861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7705974578857</t>
+    <t xml:space="preserve">10.7705965042114</t>
   </si>
   <si>
     <t xml:space="preserve">10.9171056747437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9526224136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0713272094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2311191558838</t>
+    <t xml:space="preserve">10.9526233673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0713262557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2311182022095</t>
   </si>
   <si>
     <t xml:space="preserve">11.2585105895996</t>
@@ -5093,10 +5093,10 @@
     <t xml:space="preserve">10.9389266967773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1489400863647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8476152420044</t>
+    <t xml:space="preserve">11.1489391326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8476161956787</t>
   </si>
   <si>
     <t xml:space="preserve">10.6558666229248</t>
@@ -5114,19 +5114,19 @@
     <t xml:space="preserve">11.6054887771606</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6967992782593</t>
+    <t xml:space="preserve">11.696798324585</t>
   </si>
   <si>
     <t xml:space="preserve">11.7561502456665</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7104949951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6420116424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205074310303</t>
+    <t xml:space="preserve">11.7104940414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6420125961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205083847046</t>
   </si>
   <si>
     <t xml:space="preserve">11.8063707351685</t>
@@ -5138,13 +5138,13 @@
     <t xml:space="preserve">11.4274339675903</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7972393035889</t>
+    <t xml:space="preserve">11.7972383499146</t>
   </si>
   <si>
     <t xml:space="preserve">11.6374464035034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6922340393066</t>
+    <t xml:space="preserve">11.6922330856323</t>
   </si>
   <si>
     <t xml:space="preserve">11.829197883606</t>
@@ -5153,13 +5153,13 @@
     <t xml:space="preserve">11.8337631225586</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8657217025757</t>
+    <t xml:space="preserve">11.8657207489014</t>
   </si>
   <si>
     <t xml:space="preserve">12.1853075027466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5231523513794</t>
+    <t xml:space="preserve">12.5231533050537</t>
   </si>
   <si>
     <t xml:space="preserve">12.5185871124268</t>
@@ -5180,43 +5180,43 @@
     <t xml:space="preserve">12.4227113723755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7696895599365</t>
+    <t xml:space="preserve">12.7696905136108</t>
   </si>
   <si>
     <t xml:space="preserve">13.0025300979614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0162258148193</t>
+    <t xml:space="preserve">13.0162267684937</t>
   </si>
   <si>
     <t xml:space="preserve">12.9568748474121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9660062789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1577568054199</t>
+    <t xml:space="preserve">12.966007232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1577558517456</t>
   </si>
   <si>
     <t xml:space="preserve">13.1668882369995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5184307098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5549554824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7330083847046</t>
+    <t xml:space="preserve">13.5184316635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5549564361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7330093383789</t>
   </si>
   <si>
     <t xml:space="preserve">13.6553964614868</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6143064498901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7010517120361</t>
+    <t xml:space="preserve">13.6143054962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7010507583618</t>
   </si>
   <si>
     <t xml:space="preserve">13.6964855194092</t>
@@ -5228,22 +5228,22 @@
     <t xml:space="preserve">13.7695331573486</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6462640762329</t>
+    <t xml:space="preserve">13.6462650299072</t>
   </si>
   <si>
     <t xml:space="preserve">13.3632049560547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6599617004395</t>
+    <t xml:space="preserve">13.6599607467651</t>
   </si>
   <si>
     <t xml:space="preserve">13.5823488235474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6371355056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.070855140686</t>
+    <t xml:space="preserve">13.637134552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0708560943604</t>
   </si>
   <si>
     <t xml:space="preserve">14.0845537185669</t>
@@ -5261,7 +5261,7 @@
     <t xml:space="preserve">13.9658489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9475870132446</t>
+    <t xml:space="preserve">13.9475879669189</t>
   </si>
   <si>
     <t xml:space="preserve">13.9247608184814</t>
@@ -5270,13 +5270,13 @@
     <t xml:space="preserve">13.7877960205078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7512712478638</t>
+    <t xml:space="preserve">13.7512722015381</t>
   </si>
   <si>
     <t xml:space="preserve">13.6736583709717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8380146026611</t>
+    <t xml:space="preserve">13.8380155563354</t>
   </si>
   <si>
     <t xml:space="preserve">13.9612846374512</t>
@@ -5291,7 +5291,7 @@
     <t xml:space="preserve">13.6097402572632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5503902435303</t>
+    <t xml:space="preserve">13.550389289856</t>
   </si>
   <si>
     <t xml:space="preserve">13.760401725769</t>
@@ -5309,7 +5309,7 @@
     <t xml:space="preserve">13.7421407699585</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0936841964722</t>
+    <t xml:space="preserve">14.0936832427979</t>
   </si>
   <si>
     <t xml:space="preserve">14.0891180038452</t>
@@ -5318,7 +5318,7 @@
     <t xml:space="preserve">13.8425817489624</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7786645889282</t>
+    <t xml:space="preserve">13.7786655426025</t>
   </si>
   <si>
     <t xml:space="preserve">13.3951625823975</t>
@@ -5327,7 +5327,7 @@
     <t xml:space="preserve">13.3860321044922</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4316864013672</t>
+    <t xml:space="preserve">13.4316873550415</t>
   </si>
   <si>
     <t xml:space="preserve">13.4362525939941</t>
@@ -5348,16 +5348,16 @@
     <t xml:space="preserve">13.011661529541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3586387634277</t>
+    <t xml:space="preserve">13.3586397171021</t>
   </si>
   <si>
     <t xml:space="preserve">13.8836708068848</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0069398880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9567193984985</t>
+    <t xml:space="preserve">14.0069389343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9567184448242</t>
   </si>
   <si>
     <t xml:space="preserve">14.0343332290649</t>
@@ -5396,10 +5396,10 @@
     <t xml:space="preserve">14.8999500274658</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2542314529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.783073425293</t>
+    <t xml:space="preserve">15.2542324066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7830743789673</t>
   </si>
   <si>
     <t xml:space="preserve">14.3228712081909</t>
@@ -5408,7 +5408,7 @@
     <t xml:space="preserve">14.585844039917</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6917629241943</t>
+    <t xml:space="preserve">14.6917638778687</t>
   </si>
   <si>
     <t xml:space="preserve">14.906343460083</t>
@@ -5423,7 +5423,7 @@
     <t xml:space="preserve">14.1302070617676</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3036956787109</t>
+    <t xml:space="preserve">14.3036966323853</t>
   </si>
   <si>
     <t xml:space="preserve">14.5487966537476</t>
@@ -5447,7 +5447,7 @@
     <t xml:space="preserve">14.1834583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5672950744629</t>
+    <t xml:space="preserve">14.5672960281372</t>
   </si>
   <si>
     <t xml:space="preserve">14.8771381378174</t>
@@ -5465,10 +5465,10 @@
     <t xml:space="preserve">14.5626697540283</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3453178405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1094665527344</t>
+    <t xml:space="preserve">14.3453168869019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1094655990601</t>
   </si>
   <si>
     <t xml:space="preserve">14.2019557952881</t>
@@ -5495,7 +5495,7 @@
     <t xml:space="preserve">14.7615261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7014074325562</t>
+    <t xml:space="preserve">14.7014064788818</t>
   </si>
   <si>
     <t xml:space="preserve">14.6135416030884</t>
@@ -5507,7 +5507,7 @@
     <t xml:space="preserve">14.3869390487671</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0863428115845</t>
+    <t xml:space="preserve">14.0863418579102</t>
   </si>
   <si>
     <t xml:space="preserve">13.8736143112183</t>
@@ -5522,7 +5522,7 @@
     <t xml:space="preserve">13.6192646026611</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4712791442871</t>
+    <t xml:space="preserve">13.4712781906128</t>
   </si>
   <si>
     <t xml:space="preserve">13.4019107818604</t>
@@ -5531,13 +5531,13 @@
     <t xml:space="preserve">13.4065361022949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4204092025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.346417427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6793832778931</t>
+    <t xml:space="preserve">13.42041015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3464164733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6793842315674</t>
   </si>
   <si>
     <t xml:space="preserve">13.8551158905029</t>
@@ -5546,7 +5546,7 @@
     <t xml:space="preserve">13.850492477417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9291086196899</t>
+    <t xml:space="preserve">13.9291095733643</t>
   </si>
   <si>
     <t xml:space="preserve">13.8597402572632</t>
@@ -5555,13 +5555,13 @@
     <t xml:space="preserve">13.5822687149048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6100158691406</t>
+    <t xml:space="preserve">13.6100168228149</t>
   </si>
   <si>
     <t xml:space="preserve">13.8921127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4389066696167</t>
+    <t xml:space="preserve">13.438907623291</t>
   </si>
   <si>
     <t xml:space="preserve">13.6886329650879</t>
@@ -5573,7 +5573,7 @@
     <t xml:space="preserve">13.6377620697021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7903728485107</t>
+    <t xml:space="preserve">13.7903718948364</t>
   </si>
   <si>
     <t xml:space="preserve">13.7071304321289</t>
@@ -5582,13 +5582,13 @@
     <t xml:space="preserve">13.6331386566162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8366184234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9522314071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8042459487915</t>
+    <t xml:space="preserve">13.8366174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9522323608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8042469024658</t>
   </si>
   <si>
     <t xml:space="preserve">13.8967361450195</t>
@@ -5600,13 +5600,13 @@
     <t xml:space="preserve">15.1869831085205</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3303442001343</t>
+    <t xml:space="preserve">15.3303451538086</t>
   </si>
   <si>
     <t xml:space="preserve">15.4320831298828</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3395910263062</t>
+    <t xml:space="preserve">15.3395919799805</t>
   </si>
   <si>
     <t xml:space="preserve">15.2378540039062</t>
@@ -5615,7 +5615,7 @@
     <t xml:space="preserve">15.1731100082397</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7141809463501</t>
+    <t xml:space="preserve">15.7141799926758</t>
   </si>
   <si>
     <t xml:space="preserve">15.8899145126343</t>
@@ -5624,10 +5624,10 @@
     <t xml:space="preserve">15.963906288147</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0101490020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0009021759033</t>
+    <t xml:space="preserve">16.0101509094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0009002685547</t>
   </si>
   <si>
     <t xml:space="preserve">16.2275047302246</t>
@@ -5636,7 +5636,7 @@
     <t xml:space="preserve">16.3801136016846</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5280990600586</t>
+    <t xml:space="preserve">16.5281009674072</t>
   </si>
   <si>
     <t xml:space="preserve">16.4078617095947</t>
@@ -5648,19 +5648,19 @@
     <t xml:space="preserve">16.6067161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6390895843506</t>
+    <t xml:space="preserve">16.639087677002</t>
   </si>
   <si>
     <t xml:space="preserve">16.78244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8888130187988</t>
+    <t xml:space="preserve">16.8888111114502</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">16.93505859375</t>
+    <t xml:space="preserve">16.9350566864014</t>
   </si>
   <si>
     <t xml:space="preserve">17.0182991027832</t>
@@ -5672,7 +5672,7 @@
     <t xml:space="preserve">17.2032814025879</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2402763366699</t>
+    <t xml:space="preserve">17.2402782440186</t>
   </si>
   <si>
     <t xml:space="preserve">17.0599212646484</t>
@@ -5690,7 +5690,7 @@
     <t xml:space="preserve">16.9766788482666</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0414237976074</t>
+    <t xml:space="preserve">17.0414218902588</t>
   </si>
   <si>
     <t xml:space="preserve">16.5096015930176</t>
@@ -5708,22 +5708,22 @@
     <t xml:space="preserve">16.2182540893555</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1396389007568</t>
+    <t xml:space="preserve">16.1396369934082</t>
   </si>
   <si>
     <t xml:space="preserve">16.0471458435059</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7800235748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6967821121216</t>
+    <t xml:space="preserve">14.7800226211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6967830657959</t>
   </si>
   <si>
     <t xml:space="preserve">14.4979267120361</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4054365158081</t>
+    <t xml:space="preserve">14.4054355621338</t>
   </si>
   <si>
     <t xml:space="preserve">14.4239349365234</t>
@@ -5732,7 +5732,7 @@
     <t xml:space="preserve">14.6782836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6690340042114</t>
+    <t xml:space="preserve">14.6690349578857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4886779785156</t>
@@ -5744,13 +5744,13 @@
     <t xml:space="preserve">14.9465065002441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9326333999634</t>
+    <t xml:space="preserve">14.9326343536377</t>
   </si>
   <si>
     <t xml:space="preserve">14.8632650375366</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9002628326416</t>
+    <t xml:space="preserve">14.9002618789673</t>
   </si>
   <si>
     <t xml:space="preserve">14.9808797836304</t>
@@ -6723,6 +6723,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.6049995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4950008392334</t>
   </si>
 </sst>
 </file>
@@ -72347,7 +72350,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6911226852</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>1976928</v>
@@ -72368,6 +72371,32 @@
         <v>2236</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6913078704</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>1693388</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>17.6299991607666</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>17.4699993133545</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>17.5550003051758</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>17.4950008392334</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>2237</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/TEN.MI.xlsx
+++ b/data/TEN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2245" uniqueCount="2245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="2246">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,88 +38,88 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74111652374268</t>
+    <t xml:space="preserve">7.74111700057983</t>
   </si>
   <si>
     <t xml:space="preserve">TEN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75545072555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56909132003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35406112670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07452011108398</t>
+    <t xml:space="preserve">7.75545215606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.569091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35405969619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07451963424683</t>
   </si>
   <si>
     <t xml:space="preserve">6.99567604064941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95983695983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00284337997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95266914367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51544046401978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45809936523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66237735748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28607368469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52260780334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69104719161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66596221923828</t>
+    <t xml:space="preserve">6.95983648300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00284433364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9526686668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51543951034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45809841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66237783432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28607416152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52260684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69104862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66596269607544</t>
   </si>
   <si>
     <t xml:space="preserve">6.77347660064697</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79497957229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7125506401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38283729553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40433883666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91682958602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32549524307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19289255142212</t>
+    <t xml:space="preserve">6.7949800491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71255111694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38283586502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40434122085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91683149337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32549571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19289350509644</t>
   </si>
   <si>
     <t xml:space="preserve">6.68746471405029</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83798599243164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62653923034668</t>
+    <t xml:space="preserve">6.83798503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62653875350952</t>
   </si>
   <si>
     <t xml:space="preserve">7.02793073654175</t>
@@ -131,187 +131,187 @@
     <t xml:space="preserve">6.71613550186157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99925994873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74480438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43301010131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44376182556152</t>
+    <t xml:space="preserve">6.99926042556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7448034286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43301105499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44376087188721</t>
   </si>
   <si>
     <t xml:space="preserve">7.04584980010986</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20353937149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37556457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32538890838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.483078956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7841215133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87013387680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58342599868774</t>
+    <t xml:space="preserve">7.20353746414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37556409835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32539033889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48307800292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78412199020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87013530731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5834264755249</t>
   </si>
   <si>
     <t xml:space="preserve">7.72678184509277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46157550811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60492944717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82712888717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68377447128296</t>
+    <t xml:space="preserve">7.46157693862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69094276428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60493040084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82712841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68377494812012</t>
   </si>
   <si>
     <t xml:space="preserve">7.64793491363525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81996011734009</t>
+    <t xml:space="preserve">7.81996202468872</t>
   </si>
   <si>
     <t xml:space="preserve">7.59059429168701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54042053222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84863185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69810914993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40423345565796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53325223922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51174879074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94181060791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97765016555786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03499126434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2786922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27152442932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30736541748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55106830596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68008708953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71592426300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76609706878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49372482299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65141487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65858268737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4435510635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3288688659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88447046279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84146356582642</t>
+    <t xml:space="preserve">7.54042100906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84863328933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69810962677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40423488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53325462341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51174974441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94181156158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97765064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03499221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27869510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27152729034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30736446380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55106735229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68008422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71592235565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76609802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49372673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6514139175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6585807800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44354820251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32886695861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88447141647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84146213531494</t>
   </si>
   <si>
     <t xml:space="preserve">8.2571907043457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10667037963867</t>
+    <t xml:space="preserve">8.10666942596436</t>
   </si>
   <si>
     <t xml:space="preserve">8.07799911499023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1568431854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16401100158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31453227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50089263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52956199645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25002384185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4220495223999</t>
+    <t xml:space="preserve">8.15684223175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1640100479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31453418731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50089168548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52956390380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25002193450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42204856872559</t>
   </si>
   <si>
     <t xml:space="preserve">8.48089218139648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58387088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60593414306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80453491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82660293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83395767211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76040172576904</t>
+    <t xml:space="preserve">8.58386898040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60593605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80453300476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82660102844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83395671844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76039886474609</t>
   </si>
   <si>
     <t xml:space="preserve">8.6574239730835</t>
@@ -320,49 +320,49 @@
     <t xml:space="preserve">8.53238010406494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50295829772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92957782745361</t>
+    <t xml:space="preserve">8.50295639038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92957878112793</t>
   </si>
   <si>
     <t xml:space="preserve">9.37090682983398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53272724151611</t>
+    <t xml:space="preserve">9.53272819519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.36355113983154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33413028717041</t>
+    <t xml:space="preserve">9.33412742614746</t>
   </si>
   <si>
     <t xml:space="preserve">9.12817668914795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00312995910645</t>
+    <t xml:space="preserve">9.00313377380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.18701934814453</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01784324645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24586296081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50330829620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26793098449707</t>
+    <t xml:space="preserve">9.01784133911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24586391448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50330543518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26792812347412</t>
   </si>
   <si>
     <t xml:space="preserve">9.63570594787598</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15024280548096</t>
+    <t xml:space="preserve">9.15023994445801</t>
   </si>
   <si>
     <t xml:space="preserve">8.89279937744141</t>
@@ -371,169 +371,169 @@
     <t xml:space="preserve">8.98842144012451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45181655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56950569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70190334320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66512870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43710708618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16495323181152</t>
+    <t xml:space="preserve">9.45181941986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56950664520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70190525054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66512584686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43710613250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16495227813721</t>
   </si>
   <si>
     <t xml:space="preserve">9.23850917816162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34884071350098</t>
+    <t xml:space="preserve">9.34884166717529</t>
   </si>
   <si>
     <t xml:space="preserve">9.49595069885254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58421802520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31942081451416</t>
+    <t xml:space="preserve">9.5842170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31941890716553</t>
   </si>
   <si>
     <t xml:space="preserve">9.42975234985352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06197357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21644115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03255462646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91486644744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01048851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94428539276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67949104309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79717922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56180381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42940521240234</t>
+    <t xml:space="preserve">9.06197547912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2164421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03255367279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9148645401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01048755645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94428730010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67948913574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79717826843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56180095672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42940235137939</t>
   </si>
   <si>
     <t xml:space="preserve">8.59857845306396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84866619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03990840911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2311544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20908641815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32677459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54008483886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48859405517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46652889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35619735717773</t>
+    <t xml:space="preserve">8.84866523742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03991031646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23115158081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20908737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32677555084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54008388519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4885950088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46652793884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35619831085205</t>
   </si>
   <si>
     <t xml:space="preserve">9.2973518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93693161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06933403015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14288520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95164203643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70891094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51766967773438</t>
+    <t xml:space="preserve">8.93693256378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06933212280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14288711547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95164394378662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70891284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51767063140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.56915760040283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73097896575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62064647674561</t>
+    <t xml:space="preserve">8.73097705841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62064552307129</t>
   </si>
   <si>
     <t xml:space="preserve">8.52502536773682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54708957672119</t>
+    <t xml:space="preserve">8.54709053039551</t>
   </si>
   <si>
     <t xml:space="preserve">8.75304508209229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55444717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30435943603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4146900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2017297744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34148693084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48124122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59892654418945</t>
+    <t xml:space="preserve">8.55444526672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30435752868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41469097137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20173072814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34148406982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48124027252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59892845153809</t>
   </si>
   <si>
     <t xml:space="preserve">9.57686233520508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78281688690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47388458251953</t>
+    <t xml:space="preserve">9.78281593322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47388362884521</t>
   </si>
   <si>
     <t xml:space="preserve">9.67248249053955</t>
@@ -542,25 +542,25 @@
     <t xml:space="preserve">9.65041542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77545928955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87108135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82694721221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84165859222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79752731323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89314746856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60628414154053</t>
+    <t xml:space="preserve">9.77546119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87108039855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82694625854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84165954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79752540588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89314651489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60628509521484</t>
   </si>
   <si>
     <t xml:space="preserve">9.73132705688477</t>
@@ -572,124 +572,124 @@
     <t xml:space="preserve">9.13553237915039</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1064577102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4962978363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4374551773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.628698348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7537422180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7463855743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7316761016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5404319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9338407516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6220827102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8447694778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8818826675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6517763137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4958944320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1862201690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6464366912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5425157546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8320055007935</t>
+    <t xml:space="preserve">10.1064567565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.496298789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4374532699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6286973953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7537412643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7463865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7316751480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.540431022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9338426589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6220836639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8447685241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8818817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6517744064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4958934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1862182617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6464347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.542516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8320045471191</t>
   </si>
   <si>
     <t xml:space="preserve">11.9878854751587</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8765411376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0175771713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3441820144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1660318374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0843830108643</t>
+    <t xml:space="preserve">11.8765430450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.344181060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1660346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0843849182129</t>
   </si>
   <si>
     <t xml:space="preserve">12.2105712890625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1066493988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1586112976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3293380737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2402610778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3812980651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6114025115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7598600387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7821283340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5965595245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8043975830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7524366378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7301692962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6633634567261</t>
+    <t xml:space="preserve">12.106650352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1586093902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3293371200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2402591705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3812952041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6114053726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7598609924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7821311950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5965576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8043956756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7524356842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7301683425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6633653640747</t>
   </si>
   <si>
     <t xml:space="preserve">12.6485185623169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5594425201416</t>
+    <t xml:space="preserve">12.5594444274902</t>
   </si>
   <si>
     <t xml:space="preserve">12.4629459381104</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">12.6039819717407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5445976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3219127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5520210266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6410970687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4852161407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4481039047241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7672843933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7895536422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6336727142334</t>
+    <t xml:space="preserve">12.5445995330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3219146728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.55202293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6410932540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4852132797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4481019973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7672834396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7895526885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.633674621582</t>
   </si>
   <si>
     <t xml:space="preserve">12.0101556777954</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">12.0027313232422</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9210796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0769605636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9136571884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9433479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6761264801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8691205978394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9507703781128</t>
+    <t xml:space="preserve">11.9210786819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.076961517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9136552810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9433488845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6761245727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.869119644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9507713317871</t>
   </si>
   <si>
     <t xml:space="preserve">12.047266960144</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">11.7726240158081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6538572311401</t>
+    <t xml:space="preserve">11.6538553237915</t>
   </si>
   <si>
     <t xml:space="preserve">11.9804630279541</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0324201583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5870485305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5276708602905</t>
+    <t xml:space="preserve">12.0324211120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5276699066162</t>
   </si>
   <si>
     <t xml:space="preserve">11.7058172225952</t>
@@ -779,31 +779,31 @@
     <t xml:space="preserve">11.4682865142822</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3198289871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3495216369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2678718566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9115743637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.926420211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9709568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8893060684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1416807174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159070968628</t>
+    <t xml:space="preserve">11.3198299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3495206832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2678709030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9115724563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9264192581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9709548950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8893041610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1416816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159109115601</t>
   </si>
   <si>
     <t xml:space="preserve">11.3049831390381</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">11.104567527771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9561109542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9783802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0526094436646</t>
+    <t xml:space="preserve">10.9561100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9783773422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0526084899902</t>
   </si>
   <si>
     <t xml:space="preserve">10.8076543807983</t>
@@ -827,28 +827,28 @@
     <t xml:space="preserve">11.639012336731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5647840499878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9285011291504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.839427947998</t>
+    <t xml:space="preserve">11.5647850036621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9285001754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8394269943237</t>
   </si>
   <si>
     <t xml:space="preserve">11.9953079223633</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9730396270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7355089187622</t>
+    <t xml:space="preserve">11.9730405807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7355098724365</t>
   </si>
   <si>
     <t xml:space="preserve">11.1936435699463</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2901391983032</t>
+    <t xml:space="preserve">11.2901372909546</t>
   </si>
   <si>
     <t xml:space="preserve">11.0897216796875</t>
@@ -857,49 +857,49 @@
     <t xml:space="preserve">11.1565275192261</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1639518737793</t>
+    <t xml:space="preserve">11.1639499664307</t>
   </si>
   <si>
     <t xml:space="preserve">11.1491060256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3124074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6888885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6740427017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.718578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6072368621826</t>
+    <t xml:space="preserve">11.312406539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6888875961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6740446090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.718581199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6072378158569</t>
   </si>
   <si>
     <t xml:space="preserve">10.3177461624146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4736261367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4662027359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4810495376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6443500518799</t>
+    <t xml:space="preserve">10.4736270904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4662036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.481050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6443519592285</t>
   </si>
   <si>
     <t xml:space="preserve">10.6963109970093</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5626983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7928085327148</t>
+    <t xml:space="preserve">10.5627002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7928094863892</t>
   </si>
   <si>
     <t xml:space="preserve">10.5330076217651</t>
@@ -911,28 +911,28 @@
     <t xml:space="preserve">10.8322725296021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7868528366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8398408889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7414331436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5824699401855</t>
+    <t xml:space="preserve">10.7868537902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8398427963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.74143409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5824708938599</t>
   </si>
   <si>
     <t xml:space="preserve">10.4613552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">10.423508644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1812763214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3023910522461</t>
+    <t xml:space="preserve">10.4235076904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812744140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3023900985718</t>
   </si>
   <si>
     <t xml:space="preserve">10.2645435333252</t>
@@ -941,40 +941,40 @@
     <t xml:space="preserve">10.2418346405029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0677299499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.22669506073</t>
+    <t xml:space="preserve">10.0677318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2266941070557</t>
   </si>
   <si>
     <t xml:space="preserve">10.6051807403564</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3175315856934</t>
+    <t xml:space="preserve">10.317530632019</t>
   </si>
   <si>
     <t xml:space="preserve">10.3629493713379</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1434278488159</t>
+    <t xml:space="preserve">10.1434288024902</t>
   </si>
   <si>
     <t xml:space="preserve">10.1964159011841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1055812835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1131477355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1585674285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.332670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6506013870239</t>
+    <t xml:space="preserve">10.1055793762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1131467819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1585664749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3326711654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6506004333496</t>
   </si>
   <si>
     <t xml:space="preserve">10.6733083724976</t>
@@ -983,31 +983,31 @@
     <t xml:space="preserve">10.529483795166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4386463165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1661367416382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2948226928711</t>
+    <t xml:space="preserve">10.4386472702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1661357879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2948236465454</t>
   </si>
   <si>
     <t xml:space="preserve">10.5976095199585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7262964248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8247022628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.756573677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5749015808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478107452393</t>
+    <t xml:space="preserve">10.7262945175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8247041702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7565746307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5749034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478097915649</t>
   </si>
   <si>
     <t xml:space="preserve">10.446216583252</t>
@@ -1016,46 +1016,46 @@
     <t xml:space="preserve">10.135856628418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92390441894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82549953460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1139440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18964290618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05338859558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1366548538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00796890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06852722167969</t>
+    <t xml:space="preserve">9.92390537261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8254976272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11394596099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18964195251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05338764190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13665580749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00797080993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06852626800537</t>
   </si>
   <si>
     <t xml:space="preserve">8.82629680633545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85657596588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81115627288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77330684661865</t>
+    <t xml:space="preserve">8.85657405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81115531921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77330875396729</t>
   </si>
   <si>
     <t xml:space="preserve">8.72789001464844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65219211578369</t>
+    <t xml:space="preserve">8.65219306945801</t>
   </si>
   <si>
     <t xml:space="preserve">8.70518016815186</t>
@@ -1064,118 +1064,118 @@
     <t xml:space="preserve">8.67490196228027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63705158233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57649421691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49322700500488</t>
+    <t xml:space="preserve">8.63705253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57649612426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4932279586792</t>
   </si>
   <si>
     <t xml:space="preserve">8.37968254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47808837890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50079822540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46295070648193</t>
+    <t xml:space="preserve">8.47808933258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50079727172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46294975280762</t>
   </si>
   <si>
     <t xml:space="preserve">8.59920310974121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8792839050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96255016326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97768878936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7808780670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00040054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21992301940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1442232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1669340133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17450428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12151527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10637474060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09123706817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08366870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04581737518311</t>
+    <t xml:space="preserve">8.87928485870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96255111694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97769069671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78087711334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00039958953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21992206573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14422225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16693210601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17450141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12151622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1063756942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09123611450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08366966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04581642150879</t>
   </si>
   <si>
     <t xml:space="preserve">8.95498085021973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7203197479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69760990142822</t>
+    <t xml:space="preserve">8.72032165527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69761180877686</t>
   </si>
   <si>
     <t xml:space="preserve">8.80358695983887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59163475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48565578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50836658477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56135654449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64462280273438</t>
+    <t xml:space="preserve">8.59163570404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48565864562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5083703994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.561354637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64462375640869</t>
   </si>
   <si>
     <t xml:space="preserve">8.8490047454834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89442157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88605690002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96175289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93147563934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84820938110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77251148223877</t>
+    <t xml:space="preserve">8.89442348480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88605785369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96175479888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93147468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84821033477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77251243591309</t>
   </si>
   <si>
     <t xml:space="preserve">9.65896606445312</t>
@@ -1184,19 +1184,19 @@
     <t xml:space="preserve">9.53785037994385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29561901092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15179538726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18207454681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25858879089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56465911865234</t>
+    <t xml:space="preserve">9.29561996459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15179347991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18207359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2585916519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56465816497803</t>
   </si>
   <si>
     <t xml:space="preserve">9.51109790802002</t>
@@ -1205,70 +1205,70 @@
     <t xml:space="preserve">9.28154563903809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27389335632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34275913238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53405284881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74830150604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64117622375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48049163818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60291862487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69474029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96254920959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.260968208313</t>
+    <t xml:space="preserve">9.27389240264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34276103973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5340518951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74830055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6411771774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48049068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60291767120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69473838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96255016326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2609672546387</t>
   </si>
   <si>
     <t xml:space="preserve">10.0161104202271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87837886810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78656005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97785186767578</t>
+    <t xml:space="preserve">9.87838077545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78655910491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9778528213501</t>
   </si>
   <si>
     <t xml:space="preserve">9.86307716369629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98550415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.13853931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2150564193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1691465377808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0696716308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2533140182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4369564056396</t>
+    <t xml:space="preserve">9.98550510406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1385383605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2150573730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1691455841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0696744918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2533159255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.436954498291</t>
   </si>
   <si>
     <t xml:space="preserve">10.4140014648438</t>
@@ -1277,10 +1277,10 @@
     <t xml:space="preserve">10.5058212280273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4981708526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7659816741943</t>
+    <t xml:space="preserve">10.4981689453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.76598072052</t>
   </si>
   <si>
     <t xml:space="preserve">10.8654518127441</t>
@@ -1292,160 +1292,160 @@
     <t xml:space="preserve">10.7047672271729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6512041091919</t>
+    <t xml:space="preserve">10.6512050628662</t>
   </si>
   <si>
     <t xml:space="preserve">10.8118915557861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8960599899292</t>
+    <t xml:space="preserve">10.8960590362549</t>
   </si>
   <si>
     <t xml:space="preserve">11.1026554107666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1103086471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.995532989502</t>
+    <t xml:space="preserve">11.1103067398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9955320358276</t>
   </si>
   <si>
     <t xml:space="preserve">11.0643978118896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1256132125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9725780487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7736330032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7315473556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.521125793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4063510894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1308879852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2800951004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88220596313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82481956481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73299789428711</t>
+    <t xml:space="preserve">11.1256122589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9725770950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7736320495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7315464019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5211248397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4063501358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1308860778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2800960540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88220500946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82481861114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73299884796143</t>
   </si>
   <si>
     <t xml:space="preserve">9.89368438720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94724559783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0888042449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3948698043823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4866914749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3680906295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6894626617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1562175750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0529203414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7621545791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.903712272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9610996246338</t>
+    <t xml:space="preserve">9.94724464416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0888023376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3948726654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4866933822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3680896759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6894655227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1562185287476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.052921295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7621536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9037103652954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9610986709595</t>
   </si>
   <si>
     <t xml:space="preserve">10.834846496582</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1141328811646</t>
+    <t xml:space="preserve">11.1141338348389</t>
   </si>
   <si>
     <t xml:space="preserve">11.5196743011475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3513383865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2709941864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0108346939087</t>
+    <t xml:space="preserve">11.351336479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2709951400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.010835647583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9151887893677</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0873537063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9496231079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1676950454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5655870437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8577995300293</t>
+    <t xml:space="preserve">11.0873527526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9496202468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1676969528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5655860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8578004837036</t>
   </si>
   <si>
     <t xml:space="preserve">10.4178266525269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4446067810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5823392868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.467565536499</t>
+    <t xml:space="preserve">10.4446086883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5823402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4675626754761</t>
   </si>
   <si>
     <t xml:space="preserve">10.6741600036621</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7124176025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6435537338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1332635879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9113636016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.941969871521</t>
+    <t xml:space="preserve">10.7124166488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1332654953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9113655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9419717788696</t>
   </si>
   <si>
     <t xml:space="preserve">11.2518644332886</t>
@@ -1454,34 +1454,34 @@
     <t xml:space="preserve">11.446985244751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4737663269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3972492218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3857717514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5961923599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.665057182312</t>
+    <t xml:space="preserve">11.4737644195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3972501754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3857707977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.59619140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6650590896606</t>
   </si>
   <si>
     <t xml:space="preserve">11.6994915008545</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8678283691406</t>
+    <t xml:space="preserve">11.8678293228149</t>
   </si>
   <si>
     <t xml:space="preserve">11.9558238983154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6918382644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7377510070801</t>
+    <t xml:space="preserve">11.6918392181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7377481460571</t>
   </si>
   <si>
     <t xml:space="preserve">11.6382780075073</t>
@@ -1490,46 +1490,46 @@
     <t xml:space="preserve">11.9137401580811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3307590484619</t>
+    <t xml:space="preserve">12.3307571411133</t>
   </si>
   <si>
     <t xml:space="preserve">12.319281578064</t>
   </si>
   <si>
-    <t xml:space="preserve">12.346061706543</t>
+    <t xml:space="preserve">12.3460645675659</t>
   </si>
   <si>
     <t xml:space="preserve">12.617696762085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3422346115112</t>
+    <t xml:space="preserve">12.3422365188599</t>
   </si>
   <si>
     <t xml:space="preserve">12.5450077056885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4493608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4914436340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4302320480347</t>
+    <t xml:space="preserve">12.4493618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4914445877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4302310943604</t>
   </si>
   <si>
     <t xml:space="preserve">12.4876184463501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7171716690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1341915130615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0806303024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2284317016602</t>
+    <t xml:space="preserve">12.717170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1341905593872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0806264877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2284336090088</t>
   </si>
   <si>
     <t xml:space="preserve">13.2362117767334</t>
@@ -1538,19 +1538,19 @@
     <t xml:space="preserve">12.9328241348267</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6488847732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3377208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2093629837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.275486946106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.341609954834</t>
+    <t xml:space="preserve">12.6488857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3377199172974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2093639373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2754859924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3416090011597</t>
   </si>
   <si>
     <t xml:space="preserve">11.9409847259521</t>
@@ -1559,40 +1559,40 @@
     <t xml:space="preserve">12.0887870788574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8359670639038</t>
+    <t xml:space="preserve">11.8359642028809</t>
   </si>
   <si>
     <t xml:space="preserve">11.7970685958862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1393508911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1043472290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1860256195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2132539749146</t>
+    <t xml:space="preserve">12.1393518447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1043462753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1860265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2132520675659</t>
   </si>
   <si>
     <t xml:space="preserve">12.0654487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.267707824707</t>
+    <t xml:space="preserve">12.2677068710327</t>
   </si>
   <si>
     <t xml:space="preserve">11.6998300552368</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7192783355713</t>
+    <t xml:space="preserve">11.7192792892456</t>
   </si>
   <si>
     <t xml:space="preserve">11.5987024307251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6375980377197</t>
+    <t xml:space="preserve">11.6375970840454</t>
   </si>
   <si>
     <t xml:space="preserve">12.2015838623047</t>
@@ -1601,19 +1601,19 @@
     <t xml:space="preserve">11.6803817749023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7270574569702</t>
+    <t xml:space="preserve">11.7270565032959</t>
   </si>
   <si>
     <t xml:space="preserve">12.3260507583618</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2560415267944</t>
+    <t xml:space="preserve">12.2560386657715</t>
   </si>
   <si>
     <t xml:space="preserve">12.2249221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1665802001953</t>
+    <t xml:space="preserve">12.166579246521</t>
   </si>
   <si>
     <t xml:space="preserve">12.3610582351685</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">12.3921747207642</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4544076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7733526229858</t>
+    <t xml:space="preserve">12.4544086456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7733516693115</t>
   </si>
   <si>
     <t xml:space="preserve">12.8316955566406</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">12.4621858596802</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5205297470093</t>
+    <t xml:space="preserve">12.520528793335</t>
   </si>
   <si>
     <t xml:space="preserve">12.3882856369019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3338308334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3454999923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2443695068359</t>
+    <t xml:space="preserve">12.3338289260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3454990386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2443704605103</t>
   </si>
   <si>
     <t xml:space="preserve">12.2482595443726</t>
@@ -1658,43 +1658,43 @@
     <t xml:space="preserve">12.0421123504639</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1121253967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1588001251221</t>
+    <t xml:space="preserve">12.1121263504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1587991714478</t>
   </si>
   <si>
     <t xml:space="preserve">11.4003324508667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5636940002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5714750289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7737331390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7309474945068</t>
+    <t xml:space="preserve">11.5636949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5714731216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7737312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7309484481812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8242959976196</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6220369338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3381004333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2486400604248</t>
+    <t xml:space="preserve">11.6220397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3380994796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2486391067505</t>
   </si>
   <si>
     <t xml:space="preserve">11.3225421905518</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4197835922241</t>
+    <t xml:space="preserve">11.4197788238525</t>
   </si>
   <si>
     <t xml:space="preserve">11.3964443206787</t>
@@ -1703,31 +1703,31 @@
     <t xml:space="preserve">11.5170202255249</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8826398849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6881618499756</t>
+    <t xml:space="preserve">11.8826389312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.688159942627</t>
   </si>
   <si>
     <t xml:space="preserve">11.6920509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0386009216309</t>
+    <t xml:space="preserve">11.0386028289795</t>
   </si>
   <si>
     <t xml:space="preserve">11.2408599853516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2136344909668</t>
+    <t xml:space="preserve">11.2136335372925</t>
   </si>
   <si>
     <t xml:space="preserve">11.1397314071655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8091192245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7196578979492</t>
+    <t xml:space="preserve">10.809121131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7196588516235</t>
   </si>
   <si>
     <t xml:space="preserve">10.5446271896362</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">10.7585535049438</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7468852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7507762908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8130083084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569225311279</t>
+    <t xml:space="preserve">10.7468843460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7507743835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8130073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569215774536</t>
   </si>
   <si>
     <t xml:space="preserve">10.9647006988525</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">10.8985786437988</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8207883834839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9296951293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5325765609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4431190490723</t>
+    <t xml:space="preserve">10.8207874298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9296960830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5325794219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4431171417236</t>
   </si>
   <si>
     <t xml:space="preserve">11.3886642456055</t>
@@ -1778,40 +1778,40 @@
     <t xml:space="preserve">11.225302696228</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5286884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5831432342529</t>
+    <t xml:space="preserve">11.5286893844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5831413269043</t>
   </si>
   <si>
     <t xml:space="preserve">11.746506690979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4314489364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3769960403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7581739425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4275617599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9452543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9530324935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9997091293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1202850341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.050271987915</t>
+    <t xml:space="preserve">11.4314479827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3769969940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7581729888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4275608062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9452533721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.953031539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9997081756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1202831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0502710342407</t>
   </si>
   <si>
     <t xml:space="preserve">10.9063577651978</t>
@@ -1820,10 +1820,10 @@
     <t xml:space="preserve">10.8946895599365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6496458053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2295713424683</t>
+    <t xml:space="preserve">10.6496448516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2295703887939</t>
   </si>
   <si>
     <t xml:space="preserve">10.1245536804199</t>
@@ -1841,85 +1841,85 @@
     <t xml:space="preserve">9.92229557037354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.217903137207</t>
+    <t xml:space="preserve">10.2179012298584</t>
   </si>
   <si>
     <t xml:space="preserve">10.3851556777954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4473886489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4512777328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4396085739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3423709869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3073635101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0701007843018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98841953277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68503284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59168243408203</t>
+    <t xml:space="preserve">10.4473876953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4512805938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4396095275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3423690795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3073644638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0700998306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98841762542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68503189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59168148040771</t>
   </si>
   <si>
     <t xml:space="preserve">9.70836925506592</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61501884460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51674556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24944400787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42633628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29268455505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13937759399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3988208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22192764282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5693941116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51436519622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35319423675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6401538848877</t>
+    <t xml:space="preserve">9.61501979827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51674652099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24944305419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42633533477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29268360137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13937950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39881896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22192859649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56939601898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51436328887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.353196144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64015293121338</t>
   </si>
   <si>
     <t xml:space="preserve">8.52615642547607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36498928070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08982563018799</t>
+    <t xml:space="preserve">8.36498737335205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08982467651367</t>
   </si>
   <si>
     <t xml:space="preserve">8.10947799682617</t>
@@ -1928,115 +1928,115 @@
     <t xml:space="preserve">7.86183071136475</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97189569473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06230735778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04265403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75805616378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58195066452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58352279663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25647068023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2690486907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2187328338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42156887054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48289108276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47031211853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75176525115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87755632400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92079448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15665149688721</t>
+    <t xml:space="preserve">7.97189807891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0623083114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04265308380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75805521011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58195018768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5835223197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25646877288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26904916763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21873426437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42156982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48289155960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47031307220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75176477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87755489349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92079639434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15665054321289</t>
   </si>
   <si>
     <t xml:space="preserve">8.17630386352539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10161781311035</t>
+    <t xml:space="preserve">8.10161685943604</t>
   </si>
   <si>
     <t xml:space="preserve">8.03086090087891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08589267730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37678241729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30995559692383</t>
+    <t xml:space="preserve">8.08589458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37677955627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30995655059814</t>
   </si>
   <si>
     <t xml:space="preserve">8.18023586273193</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25492286682129</t>
+    <t xml:space="preserve">8.25492191314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.38857460021973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67553043365479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44360637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55367183685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62049865722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60870552062988</t>
+    <t xml:space="preserve">8.6755313873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44360542297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55367374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62049770355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60870456695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.78166675567627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83669853210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61656761169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42001914978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59691429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80131912231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05289936065674</t>
+    <t xml:space="preserve">8.83669757843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61656665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42002201080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59691333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80132102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05290031433105</t>
   </si>
   <si>
     <t xml:space="preserve">9.0646915435791</t>
@@ -2048,34 +2048,34 @@
     <t xml:space="preserve">9.33199405670166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39095592498779</t>
+    <t xml:space="preserve">9.39095878601074</t>
   </si>
   <si>
     <t xml:space="preserve">9.43419742584229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59143543243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46957588195801</t>
+    <t xml:space="preserve">9.59143352508545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46957492828369</t>
   </si>
   <si>
     <t xml:space="preserve">9.4538516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35557842254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35164833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17475605010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23372077941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20620727539062</t>
+    <t xml:space="preserve">9.3555793762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35165023803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17475700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23372173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20620441436768</t>
   </si>
   <si>
     <t xml:space="preserve">9.32413196563721</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">9.09613800048828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95855617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26123714447021</t>
+    <t xml:space="preserve">8.95855808258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26123809814453</t>
   </si>
   <si>
     <t xml:space="preserve">9.6779146194458</t>
@@ -2096,31 +2096,31 @@
     <t xml:space="preserve">9.72901725769043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68184661865234</t>
+    <t xml:space="preserve">9.68184471130371</t>
   </si>
   <si>
     <t xml:space="preserve">9.70149993896484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81549549102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86659908294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1338996887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0316963195801</t>
+    <t xml:space="preserve">9.81549739837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86659812927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.133900642395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0316972732544</t>
   </si>
   <si>
     <t xml:space="preserve">9.89804649353027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66219043731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83908176422119</t>
+    <t xml:space="preserve">9.66219139099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83908271789551</t>
   </si>
   <si>
     <t xml:space="preserve">10.1024551391602</t>
@@ -2132,49 +2132,49 @@
     <t xml:space="preserve">9.97273254394531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78797912597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0827970504761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1456928253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87446117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76832485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83515167236328</t>
+    <t xml:space="preserve">9.78798007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0827989578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1456937789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87446022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76832580566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83515071868896</t>
   </si>
   <si>
     <t xml:space="preserve">9.88625240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2203807830811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3501005172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2518291473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6095418930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3815479278564</t>
+    <t xml:space="preserve">10.2203798294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3501024246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2518281936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6095428466797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3815488815308</t>
   </si>
   <si>
     <t xml:space="preserve">10.161416053772</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76046180725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73294925689697</t>
+    <t xml:space="preserve">9.76046371459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73294734954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.57571029663086</t>
@@ -2183,55 +2183,55 @@
     <t xml:space="preserve">9.44205951690674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28089237213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44599151611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25337600708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18262004852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13544750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37916469573975</t>
+    <t xml:space="preserve">9.28089332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44599056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25337409973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18261909484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13544845581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37916564941406</t>
   </si>
   <si>
     <t xml:space="preserve">9.44992160797119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79584121704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84694385528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85498428344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0037546157837</t>
+    <t xml:space="preserve">9.79584217071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84694290161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8549861907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0037536621094</t>
   </si>
   <si>
     <t xml:space="preserve">9.69013404846191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28001308441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16742897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00659656524658</t>
+    <t xml:space="preserve">9.28001117706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1674280166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00659847259521</t>
   </si>
   <si>
     <t xml:space="preserve">8.99855422973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86184787750244</t>
+    <t xml:space="preserve">8.86184883117676</t>
   </si>
   <si>
     <t xml:space="preserve">8.83370208740234</t>
@@ -2240,25 +2240,25 @@
     <t xml:space="preserve">8.4838924407959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72514057159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93422222137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64070224761963</t>
+    <t xml:space="preserve">8.72514152526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9342212677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64070415496826</t>
   </si>
   <si>
     <t xml:space="preserve">8.64874458312988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63266181945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91009712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04278469085693</t>
+    <t xml:space="preserve">8.63265991210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91009616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04278373718262</t>
   </si>
   <si>
     <t xml:space="preserve">8.79349422454834</t>
@@ -2267,19 +2267,19 @@
     <t xml:space="preserve">8.68493175506592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72916030883789</t>
+    <t xml:space="preserve">8.72916126251221</t>
   </si>
   <si>
     <t xml:space="preserve">8.89803504943848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13928127288818</t>
+    <t xml:space="preserve">9.13928318023682</t>
   </si>
   <si>
     <t xml:space="preserve">9.2357816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09505558013916</t>
+    <t xml:space="preserve">9.09505367279053</t>
   </si>
   <si>
     <t xml:space="preserve">8.99453449249268</t>
@@ -2291,25 +2291,25 @@
     <t xml:space="preserve">9.22371959686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25588607788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48909282684326</t>
+    <t xml:space="preserve">9.25588703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48909187316895</t>
   </si>
   <si>
     <t xml:space="preserve">9.26794815063477</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28805160522461</t>
+    <t xml:space="preserve">9.28805255889893</t>
   </si>
   <si>
     <t xml:space="preserve">9.38455200195312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38053226470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58961296081543</t>
+    <t xml:space="preserve">9.38053131103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5896110534668</t>
   </si>
   <si>
     <t xml:space="preserve">9.4971342086792</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">9.64188385009766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81879806518555</t>
+    <t xml:space="preserve">9.81879901885986</t>
   </si>
   <si>
     <t xml:space="preserve">9.77456855773926</t>
@@ -2327,100 +2327,100 @@
     <t xml:space="preserve">9.66600799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66198635101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29207229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13123989105225</t>
+    <t xml:space="preserve">9.6619873046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29207420349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13124179840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.96638870239258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08701229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15536499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4287805557251</t>
+    <t xml:space="preserve">9.08701133728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15536594390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42878150939941</t>
   </si>
   <si>
     <t xml:space="preserve">9.34836483001709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11113739013672</t>
+    <t xml:space="preserve">9.11113834381104</t>
   </si>
   <si>
     <t xml:space="preserve">8.78143119812012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56832981109619</t>
+    <t xml:space="preserve">8.56832790374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.41956043243408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22254085540771</t>
+    <t xml:space="preserve">8.2225399017334</t>
   </si>
   <si>
     <t xml:space="preserve">8.15418720245361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30295562744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13810348510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87434005737305</t>
+    <t xml:space="preserve">8.30295467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13810253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87433815002441</t>
   </si>
   <si>
     <t xml:space="preserve">8.00461387634277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58805799484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62665700912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91615533828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75532341003418</t>
+    <t xml:space="preserve">7.58805894851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62665843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91615438461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75532245635986</t>
   </si>
   <si>
     <t xml:space="preserve">7.8486065864563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9515380859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82930660247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93384695053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98692083358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07779026031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02552032470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97244596481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92902135848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72798109054565</t>
+    <t xml:space="preserve">7.95153856277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82930612564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93384504318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98692035675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07779121398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02552127838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97244453430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92902040481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7279806137085</t>
   </si>
   <si>
     <t xml:space="preserve">7.86951351165771</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">8.07377052307129</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03356266021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27078819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36728763580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29491329193115</t>
+    <t xml:space="preserve">8.0335636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27079010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36728858947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29491424560547</t>
   </si>
   <si>
     <t xml:space="preserve">8.17428970336914</t>
@@ -2447,16 +2447,16 @@
     <t xml:space="preserve">8.23058223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4597692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29893398284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17831039428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08181095123291</t>
+    <t xml:space="preserve">8.45976734161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29893493652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17831134796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08181285858154</t>
   </si>
   <si>
     <t xml:space="preserve">8.06170749664307</t>
@@ -2465,94 +2465,94 @@
     <t xml:space="preserve">7.83734703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72476577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7199387550354</t>
+    <t xml:space="preserve">7.72476530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71994161605835</t>
   </si>
   <si>
     <t xml:space="preserve">7.59931612014771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87273025512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82769727706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68133926391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36128425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43526792526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42079162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50764226913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38219165802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41596746444702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48673391342163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74728202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54302501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64274215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61218214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51889991760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47869253158569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53337478637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55267524719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57197427749634</t>
+    <t xml:space="preserve">7.87272930145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82769584655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68134117126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3612847328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43526697158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4207911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50764131546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38219308853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41596698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48673343658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74728107452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54302549362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64273977279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61218070983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51889944076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47869300842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53337335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55267572402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57197332382202</t>
   </si>
   <si>
     <t xml:space="preserve">7.48995065689087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56232500076294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67812347412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75210762023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52854919433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28086709976196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90168046951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03838634490967</t>
+    <t xml:space="preserve">7.56232452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67812442779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75210571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52854824066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28086805343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90168142318726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0383882522583</t>
   </si>
   <si>
     <t xml:space="preserve">8.18233203887939</t>
@@ -2561,73 +2561,73 @@
     <t xml:space="preserve">8.04562473297119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05769062042236</t>
+    <t xml:space="preserve">8.0576868057251</t>
   </si>
   <si>
     <t xml:space="preserve">8.0978946685791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96762132644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96601390838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96279573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89434814453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82426977157593</t>
+    <t xml:space="preserve">7.96762084960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96601343154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96279621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89434719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82427024841309</t>
   </si>
   <si>
     <t xml:space="preserve">7.95301866531372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90575504302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03124523162842</t>
+    <t xml:space="preserve">7.90575551986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03124332427979</t>
   </si>
   <si>
     <t xml:space="preserve">8.0133171081543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01820755004883</t>
+    <t xml:space="preserve">8.0182056427002</t>
   </si>
   <si>
     <t xml:space="preserve">7.94975852966309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86501407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72322654724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66944742202759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8324179649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90412521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07361698150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10458183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12902736663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15673446655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38896656036377</t>
+    <t xml:space="preserve">7.86501502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72322511672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66944694519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83241939544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90412616729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07361793518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10458087921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12902641296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15673160552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38896751403809</t>
   </si>
   <si>
     <t xml:space="preserve">8.29933261871338</t>
@@ -2645,19 +2645,19 @@
     <t xml:space="preserve">8.2382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28710842132568</t>
+    <t xml:space="preserve">8.287109375</t>
   </si>
   <si>
     <t xml:space="preserve">8.35229873657227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22192096710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18932628631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23007106781006</t>
+    <t xml:space="preserve">8.22192192077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18932723999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23007202148438</t>
   </si>
   <si>
     <t xml:space="preserve">8.34007549285889</t>
@@ -2666,25 +2666,25 @@
     <t xml:space="preserve">8.56416130065918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55193901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53564167022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46230506896973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45823097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30747985839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25858879089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31155490875244</t>
+    <t xml:space="preserve">8.55193710327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53564262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46230411529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45823001861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30748081207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25859069824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31155586242676</t>
   </si>
   <si>
     <t xml:space="preserve">8.3848934173584</t>
@@ -2696,22 +2696,22 @@
     <t xml:space="preserve">8.32785320281982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27488708496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23414421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92205286026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04917144775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14695453643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74767398834229</t>
+    <t xml:space="preserve">8.27488613128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2341423034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92205381393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04917049407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14695358276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7476749420166</t>
   </si>
   <si>
     <t xml:space="preserve">7.600998878479</t>
@@ -2720,100 +2720,100 @@
     <t xml:space="preserve">7.51299476623535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67107677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77537727355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79819488525391</t>
+    <t xml:space="preserve">7.67107534408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77537870407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79819440841675</t>
   </si>
   <si>
     <t xml:space="preserve">7.656409740448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70367193222046</t>
+    <t xml:space="preserve">7.7036714553833</t>
   </si>
   <si>
     <t xml:space="preserve">7.76722860336304</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87153053283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84708690643311</t>
+    <t xml:space="preserve">7.87153244018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84708595275879</t>
   </si>
   <si>
     <t xml:space="preserve">7.67270660400391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70856046676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99376010894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63848114013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25223875045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15445566177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17075347900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85784816741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65576362609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6052417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63620615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46508693695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34611701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98106145858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70173358917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57950448989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48498153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81353735923767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91050505638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6570839881897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78583145141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872624397278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08895921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25356101989746</t>
+    <t xml:space="preserve">7.70856189727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99376201629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63848400115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25223827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15445756912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17075395584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85784864425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65576410293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60524129867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63620662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46508646011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34611654281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98106050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70173311233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57950305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48498010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81353688240051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91050553321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65708470344543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78583168983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787260055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08896017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2535605430603</t>
   </si>
   <si>
     <t xml:space="preserve">4.19163179397583</t>
@@ -2822,16 +2822,16 @@
     <t xml:space="preserve">4.35949230194092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38556718826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62839555740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53713130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51268529891968</t>
+    <t xml:space="preserve">4.3855676651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62839603424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53713178634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51268625259399</t>
   </si>
   <si>
     <t xml:space="preserve">4.54691076278687</t>
@@ -2840,31 +2840,31 @@
     <t xml:space="preserve">4.46868324279785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67402744293213</t>
+    <t xml:space="preserve">4.6740288734436</t>
   </si>
   <si>
     <t xml:space="preserve">4.70662212371826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82396173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04560375213623</t>
+    <t xml:space="preserve">4.82396221160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04560232162476</t>
   </si>
   <si>
     <t xml:space="preserve">4.92989301681519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89403963088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82885122299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61209869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69684267044067</t>
+    <t xml:space="preserve">4.89403867721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82884979248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61209917068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69684410095215</t>
   </si>
   <si>
     <t xml:space="preserve">4.72617864608765</t>
@@ -2873,73 +2873,73 @@
     <t xml:space="preserve">4.69847345352173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46379375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60231876373291</t>
+    <t xml:space="preserve">4.46379423141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60231971740723</t>
   </si>
   <si>
     <t xml:space="preserve">4.78484869003296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82233142852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81418371200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90707778930664</t>
+    <t xml:space="preserve">4.82233238220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8141827583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90707635879517</t>
   </si>
   <si>
     <t xml:space="preserve">5.19390726089478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21020460128784</t>
+    <t xml:space="preserve">5.210205078125</t>
   </si>
   <si>
     <t xml:space="preserve">4.92174482345581</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15805339813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95922803878784</t>
+    <t xml:space="preserve">5.15805292129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95922756195068</t>
   </si>
   <si>
     <t xml:space="preserve">5.03419494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07656812667847</t>
+    <t xml:space="preserve">5.07656717300415</t>
   </si>
   <si>
     <t xml:space="preserve">4.98530340194702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89729928970337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68380641937256</t>
+    <t xml:space="preserve">4.89729881286621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6838059425354</t>
   </si>
   <si>
     <t xml:space="preserve">4.71314096450806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07167863845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62024641036987</t>
+    <t xml:space="preserve">5.07167816162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62024784088135</t>
   </si>
   <si>
     <t xml:space="preserve">4.76855134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53387117385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52083396911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56320667266846</t>
+    <t xml:space="preserve">4.5338716506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52083349227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56320714950562</t>
   </si>
   <si>
     <t xml:space="preserve">4.63491439819336</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">4.64143323898315</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7555136680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55668830871582</t>
+    <t xml:space="preserve">4.75551319122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5566873550415</t>
   </si>
   <si>
     <t xml:space="preserve">4.7620325088501</t>
@@ -2963,28 +2963,28 @@
     <t xml:space="preserve">5.20857524871826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26235580444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5377779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61926317214966</t>
+    <t xml:space="preserve">5.26235485076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53777837753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61926460266113</t>
   </si>
   <si>
     <t xml:space="preserve">5.519850730896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4416241645813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09612512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10101366043091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09449481964111</t>
+    <t xml:space="preserve">5.44162464141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09612464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10101270675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09449434280396</t>
   </si>
   <si>
     <t xml:space="preserve">5.04397344589233</t>
@@ -2996,106 +2996,106 @@
     <t xml:space="preserve">4.95596885681152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05538129806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74247646331787</t>
+    <t xml:space="preserve">5.05538082122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74247550964355</t>
   </si>
   <si>
     <t xml:space="preserve">4.80440521240234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68054723739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73269748687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62676572799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77018117904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68217658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84677791595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76366233825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68706560134888</t>
+    <t xml:space="preserve">4.68054628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7326979637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62676620483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77018070220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68217611312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84677743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76366186141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68706512451172</t>
   </si>
   <si>
     <t xml:space="preserve">4.51920509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54364967346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59906101226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67728757858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68543529510498</t>
+    <t xml:space="preserve">4.54365062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59906053543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67728710174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68543672561646</t>
   </si>
   <si>
     <t xml:space="preserve">4.81092405319214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70336294174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62350606918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58928203582764</t>
+    <t xml:space="preserve">4.70336198806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62350654602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58928298950195</t>
   </si>
   <si>
     <t xml:space="preserve">4.50290727615356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41490268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19977951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12155342102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01888132095337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20955896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22096681594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4100136756897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14274024963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21770715713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3611216545105</t>
+    <t xml:space="preserve">4.41490316390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19978046417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12155389785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01888179779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22096633911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41001415252686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14273977279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21770763397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36112260818481</t>
   </si>
   <si>
     <t xml:space="preserve">4.33993577957153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24867153167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2046685218811</t>
+    <t xml:space="preserve">4.24867105484009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20466899871826</t>
   </si>
   <si>
     <t xml:space="preserve">4.16718530654907</t>
@@ -3104,151 +3104,151 @@
     <t xml:space="preserve">4.12644338607788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03517818450928</t>
+    <t xml:space="preserve">4.03517866134644</t>
   </si>
   <si>
     <t xml:space="preserve">4.01725149154663</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15251874923706</t>
+    <t xml:space="preserve">4.15251922607422</t>
   </si>
   <si>
     <t xml:space="preserve">4.10525703430176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06369876861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98954725265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01399230957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00910377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93250703811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89502286911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92191362380981</t>
+    <t xml:space="preserve">4.06369829177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98954629898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01399278640747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0091028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93250751495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89502215385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92191338539124</t>
   </si>
   <si>
     <t xml:space="preserve">3.93332171440125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90887570381165</t>
+    <t xml:space="preserve">3.90887594223022</t>
   </si>
   <si>
     <t xml:space="preserve">3.7744243144989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77931308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76138544082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71575450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68397450447083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73694038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89257836341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89583802223206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78827667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53974485397339</t>
+    <t xml:space="preserve">3.77931356430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76138710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71575403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68397426605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73694086074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89257860183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89583849906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78827691078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53974437713623</t>
   </si>
   <si>
     <t xml:space="preserve">3.50063157081604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47129702568054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40040373802185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34010481834412</t>
+    <t xml:space="preserve">3.47129654884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40040397644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34010434150696</t>
   </si>
   <si>
     <t xml:space="preserve">3.47781562805176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36617994308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47211217880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38329195976257</t>
+    <t xml:space="preserve">3.36617946624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47211146354675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38329172134399</t>
   </si>
   <si>
     <t xml:space="preserve">3.46151852607727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49574208259583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59189558029175</t>
+    <t xml:space="preserve">3.49574184417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59189534187317</t>
   </si>
   <si>
     <t xml:space="preserve">3.520188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6277494430542</t>
+    <t xml:space="preserve">3.62774991989136</t>
   </si>
   <si>
     <t xml:space="preserve">3.60248875617981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54218983650208</t>
+    <t xml:space="preserve">3.5421895980835</t>
   </si>
   <si>
     <t xml:space="preserve">3.45418453216553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54626369476318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36943912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49085307121277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5650053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64812135696411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55767178535461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57641363143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60900783538818</t>
+    <t xml:space="preserve">3.54626393318176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36943960189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49085330963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56500506401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64812040328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55767154693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57641339302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60900735855103</t>
   </si>
   <si>
     <t xml:space="preserve">3.51366901397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41588640213013</t>
+    <t xml:space="preserve">3.41588616371155</t>
   </si>
   <si>
     <t xml:space="preserve">3.31321406364441</t>
@@ -3257,25 +3257,25 @@
     <t xml:space="preserve">3.11927795410156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31810307502747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49166798591614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5739688873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1231837272644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10199785232544</t>
+    <t xml:space="preserve">3.31810331344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49166750907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57396912574768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12318325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10199737548828</t>
   </si>
   <si>
     <t xml:space="preserve">4.49312973022461</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5583176612854</t>
+    <t xml:space="preserve">4.55831813812256</t>
   </si>
   <si>
     <t xml:space="preserve">4.56809568405151</t>
@@ -3284,52 +3284,52 @@
     <t xml:space="preserve">4.59743118286133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66587924957275</t>
+    <t xml:space="preserve">4.6658787727356</t>
   </si>
   <si>
     <t xml:space="preserve">5.02767610549927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12382936477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1841287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10590219497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09286499023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30218267440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63676309585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58237361907959</t>
+    <t xml:space="preserve">5.12382984161377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18412923812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10590267181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09286451339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30218315124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63676357269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58237266540527</t>
   </si>
   <si>
     <t xml:space="preserve">5.50655698776245</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52468729019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34503602981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42744493484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45381593704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48677921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71093130111694</t>
+    <t xml:space="preserve">5.52468681335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34503650665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42744541168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45381546020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4867787361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71093082427979</t>
   </si>
   <si>
     <t xml:space="preserve">5.60709571838379</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">5.61533689498901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61863279342651</t>
+    <t xml:space="preserve">5.61863327026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.70433807373047</t>
@@ -3347,34 +3347,34 @@
     <t xml:space="preserve">5.60379981994629</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53127956390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59885549545288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57083606719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62522554397583</t>
+    <t xml:space="preserve">5.53127908706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59885501861572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57083559036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62522649765015</t>
   </si>
   <si>
     <t xml:space="preserve">5.54281711578369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39777755737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38294410705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53292751312256</t>
+    <t xml:space="preserve">5.39777851104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38294363021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53292942047119</t>
   </si>
   <si>
     <t xml:space="preserve">5.49337196350098</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41920375823975</t>
+    <t xml:space="preserve">5.41920471191406</t>
   </si>
   <si>
     <t xml:space="preserve">5.45876026153564</t>
@@ -3395,28 +3395,28 @@
     <t xml:space="preserve">5.83619165420532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73070955276489</t>
+    <t xml:space="preserve">5.73070907592773</t>
   </si>
   <si>
     <t xml:space="preserve">5.89552688598633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81311750411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86421203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56259489059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54776239395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36975860595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18351411819458</t>
+    <t xml:space="preserve">5.81311845779419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86421155929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5625958442688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54776191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36975812911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18351459503174</t>
   </si>
   <si>
     <t xml:space="preserve">5.09121704101562</t>
@@ -3425,22 +3425,22 @@
     <t xml:space="preserve">5.15879201889038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24779319763184</t>
+    <t xml:space="preserve">5.24779367446899</t>
   </si>
   <si>
     <t xml:space="preserve">5.40766668319702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29888677597046</t>
+    <t xml:space="preserve">5.29888725280762</t>
   </si>
   <si>
     <t xml:space="preserve">5.29064607620239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50985383987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59720706939697</t>
+    <t xml:space="preserve">5.50985336303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59720659255981</t>
   </si>
   <si>
     <t xml:space="preserve">5.70928287506104</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">5.82960033416748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72576475143433</t>
+    <t xml:space="preserve">5.72576427459717</t>
   </si>
   <si>
     <t xml:space="preserve">5.79498815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80158138275146</t>
+    <t xml:space="preserve">5.80158042907715</t>
   </si>
   <si>
     <t xml:space="preserve">5.85926723480225</t>
@@ -3464,13 +3464,13 @@
     <t xml:space="preserve">6.20538425445557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21527242660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07517862319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93343496322632</t>
+    <t xml:space="preserve">6.21527290344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0751781463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">5.96310186386108</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">6.18725395202637</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12297439575195</t>
+    <t xml:space="preserve">6.12297487258911</t>
   </si>
   <si>
     <t xml:space="preserve">6.33558988571167</t>
@@ -3491,25 +3491,25 @@
     <t xml:space="preserve">7.12506628036499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28988456726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4085521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39207172393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65413093566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89146900177002</t>
+    <t xml:space="preserve">7.28988361358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40855264663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39206981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6541314125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89146947860718</t>
   </si>
   <si>
     <t xml:space="preserve">8.00683975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87004327774048</t>
+    <t xml:space="preserve">7.87004137039185</t>
   </si>
   <si>
     <t xml:space="preserve">7.973876953125</t>
@@ -3518,124 +3518,124 @@
     <t xml:space="preserve">8.16671371459961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17165946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96893215179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99200677871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96069049835205</t>
+    <t xml:space="preserve">8.17166042327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96893262863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99200773239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96069192886353</t>
   </si>
   <si>
     <t xml:space="preserve">7.86180067062378</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68379735946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61951923370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4909610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76950359344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56183242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83708000183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87993097305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95904445648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92113494873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96398735046387</t>
+    <t xml:space="preserve">7.68379926681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6195182800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49096202850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76950311660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56183195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83707857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87993049621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95904493331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92113590240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96398782730103</t>
   </si>
   <si>
     <t xml:space="preserve">7.97222900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84696674346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64588975906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56513023376465</t>
+    <t xml:space="preserve">7.84696769714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64589071273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56512975692749</t>
   </si>
   <si>
     <t xml:space="preserve">7.51073980331421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50085115432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86344909667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5766658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55359363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60798120498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27010488510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34427404403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33768081665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31790399551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5700740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41184949874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66072273254395</t>
+    <t xml:space="preserve">7.50085163116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86344861984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57666635513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55359411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60798311233521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27010583877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34427452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33768177032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3179030418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57007360458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4118480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66072368621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.14154815673828</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38218021392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44810819625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50909233093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8453197479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98871088027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06947135925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87828397750854</t>
+    <t xml:space="preserve">7.38218259811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44810914993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50909042358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84532070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98871231079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06947040557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87828254699707</t>
   </si>
   <si>
     <t xml:space="preserve">8.14363956451416</t>
@@ -3656,49 +3656,49 @@
     <t xml:space="preserve">7.72335338592529</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79587364196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82431507110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67040395736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69382619857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90963315963745</t>
+    <t xml:space="preserve">7.79587411880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8243145942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67040348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69382524490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90963411331177</t>
   </si>
   <si>
     <t xml:space="preserve">7.82598733901978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80423879623413</t>
+    <t xml:space="preserve">7.80424070358276</t>
   </si>
   <si>
     <t xml:space="preserve">8.01502799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10703945159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17563056945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05350589752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06354522705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03343200683594</t>
+    <t xml:space="preserve">8.1070384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17563247680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05350685119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06354331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03343105316162</t>
   </si>
   <si>
     <t xml:space="preserve">7.97655200958252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98826313018799</t>
+    <t xml:space="preserve">7.9882607460022</t>
   </si>
   <si>
     <t xml:space="preserve">8.15053749084473</t>
@@ -3707,13 +3707,13 @@
     <t xml:space="preserve">8.00331783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99327945709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81427764892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68378782272339</t>
+    <t xml:space="preserve">7.99327993392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81427574157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68378734588623</t>
   </si>
   <si>
     <t xml:space="preserve">7.71222829818726</t>
@@ -3722,46 +3722,46 @@
     <t xml:space="preserve">7.78918361663818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84104251861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88955879211426</t>
+    <t xml:space="preserve">7.84104347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8895583152771</t>
   </si>
   <si>
     <t xml:space="preserve">7.93472814559937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67207765579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6737494468689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68880701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83602476119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83100605010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8862133026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51482105255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40273475646973</t>
+    <t xml:space="preserve">7.67207813262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67374897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68880653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83602523803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83100652694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88621282577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51482248306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40273571014404</t>
   </si>
   <si>
     <t xml:space="preserve">7.30068588256836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52987718582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50311183929443</t>
+    <t xml:space="preserve">7.52987813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5031099319458</t>
   </si>
   <si>
     <t xml:space="preserve">7.34250926971436</t>
@@ -3773,163 +3773,163 @@
     <t xml:space="preserve">7.3391637802124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13171863555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88412523269653</t>
+    <t xml:space="preserve">7.13171911239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88412475585938</t>
   </si>
   <si>
     <t xml:space="preserve">7.00290298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1400842666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05978202819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14175748825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34752750396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28228378295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34418106079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34083700180054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17354393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23376846313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28061008453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18525362014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16015863418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35589265823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31574296951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35923862457275</t>
+    <t xml:space="preserve">7.14008378982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05978441238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14175701141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3475284576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28228235244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34418249130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34083557128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17354297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23376941680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28061103820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18525266647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16015958786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35589218139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31574249267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35923957824707</t>
   </si>
   <si>
     <t xml:space="preserve">7.36927604675293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17856168746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2103476524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87576055526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82055425643921</t>
+    <t xml:space="preserve">7.17856073379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21034717559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87576103210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82055330276489</t>
   </si>
   <si>
     <t xml:space="preserve">6.95104312896729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97279071807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03468942642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09993410110474</t>
+    <t xml:space="preserve">6.97279119491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03468894958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09993362426758</t>
   </si>
   <si>
     <t xml:space="preserve">7.2136926651001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13506412506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21871137619019</t>
+    <t xml:space="preserve">7.13506603240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21871280670166</t>
   </si>
   <si>
     <t xml:space="preserve">7.10327863693237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08989524841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02632474899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97446393966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9443507194519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18358087539673</t>
+    <t xml:space="preserve">7.0898962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02632427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97446441650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94435024261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18358039855957</t>
   </si>
   <si>
     <t xml:space="preserve">7.13339233398438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25217056274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01963329315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75865459442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75698184967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10829782485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16517925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20198202133179</t>
+    <t xml:space="preserve">7.2521710395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0196328163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75865507125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75698232650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10829830169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1651782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2019829750061</t>
   </si>
   <si>
     <t xml:space="preserve">7.44455814361572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.40942668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46965217590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60515832901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59512329101562</t>
+    <t xml:space="preserve">7.40942621231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46965312957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60515975952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59512281417847</t>
   </si>
   <si>
     <t xml:space="preserve">7.80591201782227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54827928543091</t>
+    <t xml:space="preserve">7.54828023910522</t>
   </si>
   <si>
     <t xml:space="preserve">7.66705989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01837539672852</t>
+    <t xml:space="preserve">8.0183744430542</t>
   </si>
   <si>
     <t xml:space="preserve">8.20909023284912</t>
@@ -3938,19 +3938,19 @@
     <t xml:space="preserve">8.07190799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96651268005371</t>
+    <t xml:space="preserve">7.96651411056519</t>
   </si>
   <si>
     <t xml:space="preserve">8.01001071929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26095104217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21243476867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31615829467773</t>
+    <t xml:space="preserve">8.26095199584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21243381500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31615734100342</t>
   </si>
   <si>
     <t xml:space="preserve">8.46086597442627</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">8.41904258728027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41067886352539</t>
+    <t xml:space="preserve">8.41067790985107</t>
   </si>
   <si>
     <t xml:space="preserve">8.28102588653564</t>
@@ -3974,73 +3974,73 @@
     <t xml:space="preserve">8.051833152771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05517959594727</t>
+    <t xml:space="preserve">8.05517864227295</t>
   </si>
   <si>
     <t xml:space="preserve">8.27266120910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24087429046631</t>
+    <t xml:space="preserve">8.24087524414062</t>
   </si>
   <si>
     <t xml:space="preserve">8.13547992706299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64488887786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88328075408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12167453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07566928863525</t>
+    <t xml:space="preserve">8.64488792419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88328266143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12167549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07567024230957</t>
   </si>
   <si>
     <t xml:space="preserve">8.77453994750977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68253040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58633518218994</t>
+    <t xml:space="preserve">8.68252944946289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58633613586426</t>
   </si>
   <si>
     <t xml:space="preserve">8.56542491912842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38558292388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1488618850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93974685668945</t>
+    <t xml:space="preserve">8.38558197021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14886283874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93974733352661</t>
   </si>
   <si>
     <t xml:space="preserve">8.12971687316895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07713603973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17212104797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07035064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49874401092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56659030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34608936309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64970254898071</t>
+    <t xml:space="preserve">8.07713508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17212009429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07035160064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49874448776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56659078598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34608793258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64970350265503</t>
   </si>
   <si>
     <t xml:space="preserve">7.57676792144775</t>
@@ -4049,58 +4049,58 @@
     <t xml:space="preserve">7.59881782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71076345443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88207674026489</t>
+    <t xml:space="preserve">7.71076393127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88207721710205</t>
   </si>
   <si>
     <t xml:space="preserve">7.78539514541626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62934875488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56319856643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49535036087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74638366699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50722503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72263813018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65648651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48517513275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73111867904663</t>
+    <t xml:space="preserve">7.62934923171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56319808959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49535131454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74638319015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50722599029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72263717651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65648698806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48517417907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73111963272095</t>
   </si>
   <si>
     <t xml:space="preserve">7.72942209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74299144744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82610416412354</t>
+    <t xml:space="preserve">7.74299097061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82610321044922</t>
   </si>
   <si>
     <t xml:space="preserve">7.88886213302612</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87529230117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81083822250366</t>
+    <t xml:space="preserve">7.87529325485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81083726882935</t>
   </si>
   <si>
     <t xml:space="preserve">8.11953926086426</t>
@@ -4109,22 +4109,22 @@
     <t xml:space="preserve">8.23148727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29424571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29594230651855</t>
+    <t xml:space="preserve">8.29424476623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29594039916992</t>
   </si>
   <si>
     <t xml:space="preserve">8.30951023101807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26710510253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43672275543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51050567626953</t>
+    <t xml:space="preserve">8.2671070098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43672180175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51050472259521</t>
   </si>
   <si>
     <t xml:space="preserve">8.53170871734619</t>
@@ -4139,22 +4139,22 @@
     <t xml:space="preserve">9.09568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12960624694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7861328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73948860168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39251136779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21865463256836</t>
+    <t xml:space="preserve">9.12960720062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78613185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35361003875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73948764801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39251041412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21865558624268</t>
   </si>
   <si>
     <t xml:space="preserve">9.67237854003906</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">9.68509960174561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69358158111572</t>
+    <t xml:space="preserve">9.69358062744141</t>
   </si>
   <si>
     <t xml:space="preserve">9.60877227783203</t>
@@ -4184,31 +4184,31 @@
     <t xml:space="preserve">9.9098424911499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75718688964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82927513122559</t>
+    <t xml:space="preserve">9.75718784332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82927322387695</t>
   </si>
   <si>
     <t xml:space="preserve">10.0540161132812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76990699768066</t>
+    <t xml:space="preserve">9.76990795135498</t>
   </si>
   <si>
     <t xml:space="preserve">9.587571144104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28650093078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36282730102539</t>
+    <t xml:space="preserve">9.28650188446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36282825469971</t>
   </si>
   <si>
     <t xml:space="preserve">9.26529979705811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16353034973145</t>
+    <t xml:space="preserve">9.16352939605713</t>
   </si>
   <si>
     <t xml:space="preserve">9.44763660430908</t>
@@ -4217,43 +4217,43 @@
     <t xml:space="preserve">9.78687000274658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70206069946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.181227684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9734468460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79535007476807</t>
+    <t xml:space="preserve">9.70206165313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1812286376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97344779968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79535102844238</t>
   </si>
   <si>
     <t xml:space="preserve">11.0717144012451</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4279098510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7960872650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9657049179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.961464881897</t>
+    <t xml:space="preserve">11.4279088973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7960863113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9657039642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9614639282227</t>
   </si>
   <si>
     <t xml:space="preserve">10.6900768280029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3338832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5543832778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7240018844604</t>
+    <t xml:space="preserve">10.3338842391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5543842315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7239999771118</t>
   </si>
   <si>
     <t xml:space="preserve">11.3770236968994</t>
@@ -4262,10 +4262,10 @@
     <t xml:space="preserve">11.4406309127808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7586622238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7925834655762</t>
+    <t xml:space="preserve">11.758659362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7925844192505</t>
   </si>
   <si>
     <t xml:space="preserve">12.0851726531982</t>
@@ -4274,13 +4274,13 @@
     <t xml:space="preserve">11.8095464706421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4872760772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.682333946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6653718948364</t>
+    <t xml:space="preserve">11.4872741699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6823320388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6653728485107</t>
   </si>
   <si>
     <t xml:space="preserve">11.7798633575439</t>
@@ -4289,31 +4289,31 @@
     <t xml:space="preserve">11.7713823318481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8689126968384</t>
+    <t xml:space="preserve">11.8689136505127</t>
   </si>
   <si>
     <t xml:space="preserve">11.7374591827393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7883424758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.318395614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2039051055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5982608795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7042722702026</t>
+    <t xml:space="preserve">11.7883434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3183965682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2039031982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5982637405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.704273223877</t>
   </si>
   <si>
     <t xml:space="preserve">12.7721195220947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7424373626709</t>
+    <t xml:space="preserve">12.7424364089966</t>
   </si>
   <si>
     <t xml:space="preserve">12.7127532958984</t>
@@ -4322,46 +4322,46 @@
     <t xml:space="preserve">12.3692808151245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5254364013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9325170516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8773937225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5600996017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0766916275024</t>
+    <t xml:space="preserve">11.5254383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9325189590454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8773918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5601005554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0766925811768</t>
   </si>
   <si>
     <t xml:space="preserve">12.6279468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4837713241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4244060516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3268756866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8561897277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9749212265015</t>
+    <t xml:space="preserve">12.483772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4244050979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3268775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8561906814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9749231338501</t>
   </si>
   <si>
     <t xml:space="preserve">12.3862419128418</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0597314834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5134553909302</t>
+    <t xml:space="preserve">12.0597305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5134544372559</t>
   </si>
   <si>
     <t xml:space="preserve">13.0477466583252</t>
@@ -4373,34 +4373,34 @@
     <t xml:space="preserve">13.1410350799561</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8018026351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9714183807373</t>
+    <t xml:space="preserve">12.8018016815186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9714193344116</t>
   </si>
   <si>
     <t xml:space="preserve">13.2608242034912</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0794048309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3169775009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6798152923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8482751846313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0124139785767</t>
+    <t xml:space="preserve">13.0794057846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3169765472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6798143386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.848274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0124130249023</t>
   </si>
   <si>
     <t xml:space="preserve">13.4983959197998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6020622253418</t>
+    <t xml:space="preserve">13.6020641326904</t>
   </si>
   <si>
     <t xml:space="preserve">13.6322994232178</t>
@@ -4409,61 +4409,61 @@
     <t xml:space="preserve">13.5891036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7273302078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8266763687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7878017425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1830730438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7856798171997</t>
+    <t xml:space="preserve">13.7273292541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8266754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.787802696228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1830739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.785680770874</t>
   </si>
   <si>
     <t xml:space="preserve">12.5869846343994</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4789962768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1075201034546</t>
+    <t xml:space="preserve">12.4789972305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1075210571289</t>
   </si>
   <si>
     <t xml:space="preserve">11.3688888549805</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2004270553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4120845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4768753051758</t>
+    <t xml:space="preserve">11.2004289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4120836257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4768762588501</t>
   </si>
   <si>
     <t xml:space="preserve">10.885106086731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5568246841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7555227279663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7728004455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0406074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8764677047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6000204086304</t>
+    <t xml:space="preserve">10.5568256378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.755521774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7727994918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0406064987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8764667510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6000213623047</t>
   </si>
   <si>
     <t xml:space="preserve">10.4013233184814</t>
@@ -4472,40 +4472,40 @@
     <t xml:space="preserve">10.7814388275146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89162540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.593581199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5654640197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9542179107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0190114974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9239835739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7987174987793</t>
+    <t xml:space="preserve">9.89162349700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59358024597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5654649734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9542188644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0190095901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9239816665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7987155914307</t>
   </si>
   <si>
     <t xml:space="preserve">10.3624486923218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5309085845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9585380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9930944442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.880786895752</t>
+    <t xml:space="preserve">10.5309076309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9585371017456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9930934906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8807859420776</t>
   </si>
   <si>
     <t xml:space="preserve">10.669132232666</t>
@@ -4517,34 +4517,34 @@
     <t xml:space="preserve">10.9067039489746</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2479429244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3904876708984</t>
+    <t xml:space="preserve">11.2479448318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3904867172241</t>
   </si>
   <si>
     <t xml:space="preserve">11.7533226013184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4380016326904</t>
+    <t xml:space="preserve">11.4379997253418</t>
   </si>
   <si>
     <t xml:space="preserve">11.4639177322388</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3343324661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9023847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1097202301025</t>
+    <t xml:space="preserve">11.3343334197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9023838043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1097192764282</t>
   </si>
   <si>
     <t xml:space="preserve">11.2220258712769</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1010808944702</t>
+    <t xml:space="preserve">11.1010828018188</t>
   </si>
   <si>
     <t xml:space="preserve">11.3732080459595</t>
@@ -4559,40 +4559,40 @@
     <t xml:space="preserve">11.4855155944824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0924406051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0729665756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9649782180786</t>
+    <t xml:space="preserve">11.0924415588379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0729656219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9649791717529</t>
   </si>
   <si>
     <t xml:space="preserve">12.1852722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0124921798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8872270584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8785886764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8267555236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2284660339355</t>
+    <t xml:space="preserve">12.0124912261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8872289657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8785877227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8267545700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2284669876099</t>
   </si>
   <si>
     <t xml:space="preserve">12.3407735824585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9174633026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5416688919067</t>
+    <t xml:space="preserve">11.917462348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5416669845581</t>
   </si>
   <si>
     <t xml:space="preserve">11.5459871292114</t>
@@ -4601,31 +4601,31 @@
     <t xml:space="preserve">12.1204795837402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3666896820068</t>
+    <t xml:space="preserve">12.3666906356812</t>
   </si>
   <si>
     <t xml:space="preserve">12.3105363845825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3062181472778</t>
+    <t xml:space="preserve">12.3062171936035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0340900421143</t>
   </si>
   <si>
-    <t xml:space="preserve">11.72740650177</t>
+    <t xml:space="preserve">11.7274074554443</t>
   </si>
   <si>
     <t xml:space="preserve">11.7014904022217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5891819000244</t>
+    <t xml:space="preserve">11.5891828536987</t>
   </si>
   <si>
     <t xml:space="preserve">11.9217834472656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7771186828613</t>
+    <t xml:space="preserve">10.7771196365356</t>
   </si>
   <si>
     <t xml:space="preserve">11.0103712081909</t>
@@ -4637,13 +4637,13 @@
     <t xml:space="preserve">11.6755723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4595985412598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2500638961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5351505279541</t>
+    <t xml:space="preserve">11.4595975875854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2500648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5351514816284</t>
   </si>
   <si>
     <t xml:space="preserve">12.7943201065063</t>
@@ -4655,13 +4655,13 @@
     <t xml:space="preserve">12.5178718566895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9304227828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0384101867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5999412536621</t>
+    <t xml:space="preserve">11.9304218292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0384092330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5999431610107</t>
   </si>
   <si>
     <t xml:space="preserve">12.3494129180908</t>
@@ -4673,40 +4673,40 @@
     <t xml:space="preserve">12.9886960983276</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9368629455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0966835021973</t>
+    <t xml:space="preserve">12.936863899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0966844558716</t>
   </si>
   <si>
     <t xml:space="preserve">12.99733543396</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2910614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6582164764404</t>
+    <t xml:space="preserve">13.2910594940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6582183837891</t>
   </si>
   <si>
     <t xml:space="preserve">13.2262687683105</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5675077438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9173860549927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7618837356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9562616348267</t>
+    <t xml:space="preserve">13.5675067901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9173851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7618846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.956262588501</t>
   </si>
   <si>
     <t xml:space="preserve">14.3795728683472</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5048360824585</t>
+    <t xml:space="preserve">14.5048379898071</t>
   </si>
   <si>
     <t xml:space="preserve">14.2111120223999</t>
@@ -4718,85 +4718,85 @@
     <t xml:space="preserve">13.5329513549805</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8180370330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7575654983521</t>
+    <t xml:space="preserve">13.8180379867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7575645446777</t>
   </si>
   <si>
     <t xml:space="preserve">14.4098072052002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4789190292358</t>
+    <t xml:space="preserve">14.4789199829102</t>
   </si>
   <si>
     <t xml:space="preserve">14.068567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1808767318726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5523586273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4427547454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1154050827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2026987075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2812633514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8928060531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2987203598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5911550521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2507095336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0150165557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8011465072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6789350509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3821353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5479936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4301490783691</t>
+    <t xml:space="preserve">14.1808757781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5523595809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4427556991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1154041290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2026996612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2812623977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8928050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2987194061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5911560058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.25071144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0150175094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8011484146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6789360046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.382137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5479946136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4301471710205</t>
   </si>
   <si>
     <t xml:space="preserve">13.2992067337036</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7531366348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7793226242065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5130758285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4170541763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7138519287109</t>
+    <t xml:space="preserve">13.753134727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7793235778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5130777359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4170532226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7138538360596</t>
   </si>
   <si>
     <t xml:space="preserve">13.9015350341797</t>
@@ -4805,37 +4805,37 @@
     <t xml:space="preserve">14.220157623291</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4733095169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5300512313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4209318161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.46457862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2157917022705</t>
+    <t xml:space="preserve">14.4733104705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.53005027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4209337234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4645795822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2157907485962</t>
   </si>
   <si>
     <t xml:space="preserve">14.6828145980835</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1765098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1769971847534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.561089515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7705936431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8229703903198</t>
+    <t xml:space="preserve">14.1765108108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1769952774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5610885620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7705926895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8229694366455</t>
   </si>
   <si>
     <t xml:space="preserve">13.8316993713379</t>
@@ -4847,85 +4847,85 @@
     <t xml:space="preserve">14.1983337402344</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1023092269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9888286590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4122037887573</t>
+    <t xml:space="preserve">14.1023111343384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9888277053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.412202835083</t>
   </si>
   <si>
     <t xml:space="preserve">15.0101652145386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2725324630737</t>
+    <t xml:space="preserve">14.272533416748</t>
   </si>
   <si>
     <t xml:space="preserve">14.4471197128296</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1808757781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0019245147705</t>
+    <t xml:space="preserve">14.1808748245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0019235610962</t>
   </si>
   <si>
     <t xml:space="preserve">14.0281105041504</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542993545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3729219436646</t>
+    <t xml:space="preserve">14.0542984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3729209899902</t>
   </si>
   <si>
     <t xml:space="preserve">14.1546859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1852378845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.879711151123</t>
+    <t xml:space="preserve">14.1852416992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8797121047974</t>
   </si>
   <si>
     <t xml:space="preserve">13.3995952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3210306167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3123006820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6527481079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8840751647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8447923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.137228012085</t>
+    <t xml:space="preserve">13.3210315704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2119131088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3123016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6527462005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8840761184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8447933197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1372270584106</t>
   </si>
   <si>
     <t xml:space="preserve">15.1411056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4165678024292</t>
+    <t xml:space="preserve">14.4165668487549</t>
   </si>
   <si>
     <t xml:space="preserve">14.1939687728882</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7356748580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9844636917114</t>
+    <t xml:space="preserve">13.7356758117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9844627380371</t>
   </si>
   <si>
     <t xml:space="preserve">13.6876640319824</t>
@@ -4937,85 +4937,85 @@
     <t xml:space="preserve">14.0848512649536</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1284980773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2288846969604</t>
+    <t xml:space="preserve">14.1284971237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2288856506348</t>
   </si>
   <si>
     <t xml:space="preserve">14.3030862808228</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7662296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4825248718262</t>
+    <t xml:space="preserve">13.7662305831909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4825239181519</t>
   </si>
   <si>
     <t xml:space="preserve">12.69251537323</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8758335113525</t>
+    <t xml:space="preserve">12.8758316040039</t>
   </si>
   <si>
     <t xml:space="preserve">11.7235546112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7541084289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5402374267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5707893371582</t>
+    <t xml:space="preserve">11.7541065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5402383804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5707912445068</t>
   </si>
   <si>
     <t xml:space="preserve">11.9592475891113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8326721191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.566424369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1954259872437</t>
+    <t xml:space="preserve">11.8326711654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5664253234863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.195426940918</t>
   </si>
   <si>
     <t xml:space="preserve">11.3001804351807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6362600326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.575156211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4136600494385</t>
+    <t xml:space="preserve">11.6362609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5751552581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4136610031128</t>
   </si>
   <si>
     <t xml:space="preserve">11.4354858398438</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7802953720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4878606796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3438272476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3132743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.618803024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7715663909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7322826385498</t>
+    <t xml:space="preserve">11.7802963256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4878616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.343825340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3132734298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6188020706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7715673446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7322835922241</t>
   </si>
   <si>
     <t xml:space="preserve">11.6406259536743</t>
@@ -5024,10 +5024,10 @@
     <t xml:space="preserve">11.5838851928711</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4573087692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4398498535156</t>
+    <t xml:space="preserve">11.4573078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4398508071899</t>
   </si>
   <si>
     <t xml:space="preserve">11.3918371200562</t>
@@ -5039,7 +5039,7 @@
     <t xml:space="preserve">11.0775804519653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7807817459106</t>
+    <t xml:space="preserve">10.780782699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.7109470367432</t>
@@ -5054,28 +5054,28 @@
     <t xml:space="preserve">10.929181098938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9117231369019</t>
+    <t xml:space="preserve">10.9117212295532</t>
   </si>
   <si>
     <t xml:space="preserve">10.6934881210327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5712776184082</t>
+    <t xml:space="preserve">10.5712766647339</t>
   </si>
   <si>
     <t xml:space="preserve">10.6978521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">10.662935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5887365341187</t>
+    <t xml:space="preserve">10.6629362106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5887355804443</t>
   </si>
   <si>
     <t xml:space="preserve">10.7327709197998</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7676887512207</t>
+    <t xml:space="preserve">10.7676877975464</t>
   </si>
   <si>
     <t xml:space="preserve">10.8843870162964</t>
@@ -5087,64 +5087,64 @@
     <t xml:space="preserve">11.0684108734131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.659966468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7542219161987</t>
+    <t xml:space="preserve">10.6599655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7542238235474</t>
   </si>
   <si>
     <t xml:space="preserve">10.9606895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">10.664454460144</t>
+    <t xml:space="preserve">10.6644554138184</t>
   </si>
   <si>
     <t xml:space="preserve">10.47594165802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6958742141724</t>
+    <t xml:space="preserve">10.695873260498</t>
   </si>
   <si>
     <t xml:space="preserve">11.0818767547607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1536903381348</t>
+    <t xml:space="preserve">11.1536912918091</t>
   </si>
   <si>
     <t xml:space="preserve">11.4095306396484</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4992990493774</t>
+    <t xml:space="preserve">11.4992980957031</t>
   </si>
   <si>
     <t xml:space="preserve">11.5576477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5127630233765</t>
+    <t xml:space="preserve">11.5127639770508</t>
   </si>
   <si>
     <t xml:space="preserve">11.4454374313354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7192306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6070213317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6922998428345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2344818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5980443954468</t>
+    <t xml:space="preserve">11.7192296981812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6070203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6923007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2344827651978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5980424880981</t>
   </si>
   <si>
     <t xml:space="preserve">11.4409484863281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4948110580444</t>
+    <t xml:space="preserve">11.4948101043701</t>
   </si>
   <si>
     <t xml:space="preserve">11.6294622421265</t>
@@ -5153,16 +5153,16 @@
     <t xml:space="preserve">11.6339511871338</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6653680801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9795589447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3117008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3072118759155</t>
+    <t xml:space="preserve">11.6653690338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9795579910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3116998672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3072109222412</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745374679565</t>
@@ -5174,28 +5174,28 @@
     <t xml:space="preserve">11.9256963729858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2398862838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2129554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5540733337402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7829818725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7964487075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7380981445312</t>
+    <t xml:space="preserve">12.2398853302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2129545211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5540742874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7829828262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7964477539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7380971908569</t>
   </si>
   <si>
     <t xml:space="preserve">12.7470750808716</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9355869293213</t>
+    <t xml:space="preserve">12.9355888366699</t>
   </si>
   <si>
     <t xml:space="preserve">12.9445657730103</t>
@@ -5204,31 +5204,31 @@
     <t xml:space="preserve">13.2901735305786</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3260803222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5011281967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4248247146606</t>
+    <t xml:space="preserve">13.3260812759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.501127243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.424825668335</t>
   </si>
   <si>
     <t xml:space="preserve">13.3844289779663</t>
   </si>
   <si>
-    <t xml:space="preserve">13.469708442688</t>
+    <t xml:space="preserve">13.4697093963623</t>
   </si>
   <si>
     <t xml:space="preserve">13.465220451355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5819187164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5370349884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.415846824646</t>
+    <t xml:space="preserve">13.581919670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5370359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4158477783203</t>
   </si>
   <si>
     <t xml:space="preserve">13.1375665664673</t>
@@ -5237,34 +5237,34 @@
     <t xml:space="preserve">13.429313659668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3530111312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4068717956543</t>
+    <t xml:space="preserve">13.3530101776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.40687084198</t>
   </si>
   <si>
     <t xml:space="preserve">13.833270072937</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8467350006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.806339263916</t>
+    <t xml:space="preserve">13.846734046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8063402175903</t>
   </si>
   <si>
     <t xml:space="preserve">13.8108282089233</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7883853912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7300367355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7120819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6896409988403</t>
+    <t xml:space="preserve">13.788384437561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7300357818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.712082862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.689640045166</t>
   </si>
   <si>
     <t xml:space="preserve">13.554988861084</t>
@@ -5276,16 +5276,16 @@
     <t xml:space="preserve">13.4427785873413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6043605804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7255477905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6941299438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2497777938843</t>
+    <t xml:space="preserve">13.6043615341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7255487442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.694130897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2497758865356</t>
   </si>
   <si>
     <t xml:space="preserve">13.3799409866333</t>
@@ -5306,19 +5306,19 @@
     <t xml:space="preserve">13.613338470459</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5101051330566</t>
+    <t xml:space="preserve">13.5101041793823</t>
   </si>
   <si>
     <t xml:space="preserve">13.855712890625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.851224899292</t>
+    <t xml:space="preserve">13.8512239456177</t>
   </si>
   <si>
     <t xml:space="preserve">13.6088495254517</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5460119247437</t>
+    <t xml:space="preserve">13.546012878418</t>
   </si>
   <si>
     <t xml:space="preserve">13.1689853668213</t>
@@ -5327,7 +5327,7 @@
     <t xml:space="preserve">13.160008430481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2048931121826</t>
+    <t xml:space="preserve">13.2048940658569</t>
   </si>
   <si>
     <t xml:space="preserve">13.2093811035156</t>
@@ -5336,10 +5336,10 @@
     <t xml:space="preserve">13.5415239334106</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4517555236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9894495010376</t>
+    <t xml:space="preserve">13.4517545700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9894504547119</t>
   </si>
   <si>
     <t xml:space="preserve">13.0837049484253</t>
@@ -5348,7 +5348,7 @@
     <t xml:space="preserve">12.7919597625732</t>
   </si>
   <si>
-    <t xml:space="preserve">13.13307762146</t>
+    <t xml:space="preserve">13.1330785751343</t>
   </si>
   <si>
     <t xml:space="preserve">13.649245262146</t>
@@ -5357,13 +5357,13 @@
     <t xml:space="preserve">13.770432472229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7210597991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.79736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1519479751587</t>
+    <t xml:space="preserve">13.72105884552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7973613739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1519470214844</t>
   </si>
   <si>
     <t xml:space="preserve">14.053201675415</t>
@@ -5372,16 +5372,16 @@
     <t xml:space="preserve">14.2506914138794</t>
   </si>
   <si>
-    <t xml:space="preserve">14.259669303894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.026270866394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.698618888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8198041915894</t>
+    <t xml:space="preserve">14.2596683502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0262718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6986179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8198051452637</t>
   </si>
   <si>
     <t xml:space="preserve">13.860200881958</t>
@@ -5393,34 +5393,34 @@
     <t xml:space="preserve">14.6860685348511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6483659744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9966659545898</t>
+    <t xml:space="preserve">14.648365020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9966640472412</t>
   </si>
   <si>
     <t xml:space="preserve">14.5334615707397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0810308456421</t>
+    <t xml:space="preserve">14.0810298919678</t>
   </si>
   <si>
     <t xml:space="preserve">14.3395624160767</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4436941146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6546487808228</t>
+    <t xml:space="preserve">14.4436931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6546506881714</t>
   </si>
   <si>
     <t xml:space="preserve">14.4526710510254</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4706258773804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.891619682312</t>
+    <t xml:space="preserve">14.4706239700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8916187286377</t>
   </si>
   <si>
     <t xml:space="preserve">14.0621786117554</t>
@@ -5429,52 +5429,52 @@
     <t xml:space="preserve">14.3031406402588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1303749084473</t>
+    <t xml:space="preserve">14.1303758621216</t>
   </si>
   <si>
     <t xml:space="preserve">13.9394245147705</t>
   </si>
   <si>
-    <t xml:space="preserve">14.02126121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1531076431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0576324462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9439716339111</t>
+    <t xml:space="preserve">14.0212602615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1531066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0576314926147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9439706802368</t>
   </si>
   <si>
     <t xml:space="preserve">14.3213262557983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.625937461853</t>
+    <t xml:space="preserve">14.6259384155273</t>
   </si>
   <si>
     <t xml:space="preserve">14.5395555496216</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4440813064575</t>
+    <t xml:space="preserve">14.4440803527832</t>
   </si>
   <si>
     <t xml:space="preserve">14.1894788742065</t>
   </si>
   <si>
-    <t xml:space="preserve">14.316780090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1030960083008</t>
+    <t xml:space="preserve">14.3167791366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1030969619751</t>
   </si>
   <si>
     <t xml:space="preserve">13.8712272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9621572494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.221305847168</t>
+    <t xml:space="preserve">13.9621553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2213039398193</t>
   </si>
   <si>
     <t xml:space="preserve">14.3804302215576</t>
@@ -5489,43 +5489,43 @@
     <t xml:space="preserve">14.5213708877563</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5895662307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5122766494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4531745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3667917251587</t>
+    <t xml:space="preserve">14.5895681381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5122785568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4531736373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3667907714844</t>
   </si>
   <si>
     <t xml:space="preserve">14.1940250396729</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1440162658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8484954833984</t>
+    <t xml:space="preserve">14.1440143585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8484945297241</t>
   </si>
   <si>
     <t xml:space="preserve">13.6393585205078</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4302215576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3711185455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3893032073975</t>
+    <t xml:space="preserve">13.4302225112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3711175918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3893041610718</t>
   </si>
   <si>
     <t xml:space="preserve">13.2438163757324</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1756210327148</t>
+    <t xml:space="preserve">13.1756200790405</t>
   </si>
   <si>
     <t xml:space="preserve">13.1801662445068</t>
@@ -5537,28 +5537,28 @@
     <t xml:space="preserve">13.1210632324219</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4484081268311</t>
+    <t xml:space="preserve">13.4484071731567</t>
   </si>
   <si>
     <t xml:space="preserve">13.6211729049683</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6166257858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6939163208008</t>
+    <t xml:space="preserve">13.6166276931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6939172744751</t>
   </si>
   <si>
     <t xml:space="preserve">13.6257190704346</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3529329299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3802099227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.657546043396</t>
+    <t xml:space="preserve">13.3529319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3802108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6575450897217</t>
   </si>
   <si>
     <t xml:space="preserve">13.2119922637939</t>
@@ -5567,25 +5567,25 @@
     <t xml:space="preserve">13.4575004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2483644485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.407488822937</t>
+    <t xml:space="preserve">13.248363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4074897766113</t>
   </si>
   <si>
     <t xml:space="preserve">13.5575227737427</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4756870269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.402943611145</t>
+    <t xml:space="preserve">13.4756860733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4029426574707</t>
   </si>
   <si>
     <t xml:space="preserve">13.6029872894287</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7166481018066</t>
+    <t xml:space="preserve">13.716649055481</t>
   </si>
   <si>
     <t xml:space="preserve">13.5711622238159</t>
@@ -5597,22 +5597,22 @@
     <t xml:space="preserve">14.6577653884888</t>
   </si>
   <si>
-    <t xml:space="preserve">14.930552482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0714921951294</t>
+    <t xml:space="preserve">14.9305515289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0714931488037</t>
   </si>
   <si>
     <t xml:space="preserve">15.1715126037598</t>
   </si>
   <si>
-    <t xml:space="preserve">15.080584526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9805631637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9169120788574</t>
+    <t xml:space="preserve">15.0805826187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.980562210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9169139862061</t>
   </si>
   <si>
     <t xml:space="preserve">15.4488458633423</t>
@@ -5624,13 +5624,13 @@
     <t xml:space="preserve">15.6943559646606</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7398176193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7307271957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9535036087036</t>
+    <t xml:space="preserve">15.7398204803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7307262420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9535026550293</t>
   </si>
   <si>
     <t xml:space="preserve">16.103536605835</t>
@@ -5639,7 +5639,7 @@
     <t xml:space="preserve">16.2490234375</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1308155059814</t>
+    <t xml:space="preserve">16.1308135986328</t>
   </si>
   <si>
     <t xml:space="preserve">16.0762577056885</t>
@@ -5657,7 +5657,7 @@
     <t xml:space="preserve">16.603645324707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6263790130615</t>
+    <t xml:space="preserve">16.6263771057129</t>
   </si>
   <si>
     <t xml:space="preserve">16.6491107940674</t>
@@ -5666,7 +5666,7 @@
     <t xml:space="preserve">16.7309474945068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6536560058594</t>
+    <t xml:space="preserve">16.653657913208</t>
   </si>
   <si>
     <t xml:space="preserve">16.912805557251</t>
@@ -5678,70 +5678,70 @@
     <t xml:space="preserve">16.7718639373779</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8991622924805</t>
+    <t xml:space="preserve">16.8991641998291</t>
   </si>
   <si>
     <t xml:space="preserve">16.6627502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8218765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6900253295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7536773681641</t>
+    <t xml:space="preserve">16.8218746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6900272369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7536792755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.2308368682861</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3172187805176</t>
+    <t xml:space="preserve">16.3172168731689</t>
   </si>
   <si>
     <t xml:space="preserve">16.0944442749023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0626182556152</t>
+    <t xml:space="preserve">16.0626201629639</t>
   </si>
   <si>
     <t xml:space="preserve">15.944411277771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8671216964722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7761917114258</t>
+    <t xml:space="preserve">15.8671207427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7761926651001</t>
   </si>
   <si>
     <t xml:space="preserve">14.530463218689</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4486284255981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2531290054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1622009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1803865432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4304418563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4213485717773</t>
+    <t xml:space="preserve">14.4486265182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2531299591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1621990203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1803874969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.43044090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.421347618103</t>
   </si>
   <si>
     <t xml:space="preserve">14.2440366744995</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5668354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6941347122192</t>
+    <t xml:space="preserve">14.5668344497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6941356658936</t>
   </si>
   <si>
     <t xml:space="preserve">14.6804962158203</t>
@@ -5783,16 +5783,16 @@
     <t xml:space="preserve">14.0752191543579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9306888580322</t>
+    <t xml:space="preserve">13.9306898117065</t>
   </si>
   <si>
     <t xml:space="preserve">13.8467712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">13.739538192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8187971115112</t>
+    <t xml:space="preserve">13.7395391464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8187961578369</t>
   </si>
   <si>
     <t xml:space="preserve">13.8980541229248</t>
@@ -5813,7 +5813,7 @@
     <t xml:space="preserve">13.3479137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4271697998047</t>
+    <t xml:space="preserve">13.427170753479</t>
   </si>
   <si>
     <t xml:space="preserve">13.627646446228</t>
@@ -5822,7 +5822,7 @@
     <t xml:space="preserve">13.3898725509644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5297393798828</t>
+    <t xml:space="preserve">13.5297403335571</t>
   </si>
   <si>
     <t xml:space="preserve">13.3712244033813</t>
@@ -5831,16 +5831,16 @@
     <t xml:space="preserve">13.5204153060913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4318323135376</t>
+    <t xml:space="preserve">13.4318332672119</t>
   </si>
   <si>
     <t xml:space="preserve">13.133451461792</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0728445053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3805494308472</t>
+    <t xml:space="preserve">13.0728435516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3805484771729</t>
   </si>
   <si>
     <t xml:space="preserve">13.282642364502</t>
@@ -5849,10 +5849,10 @@
     <t xml:space="preserve">13.4131841659546</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4971046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3246030807495</t>
+    <t xml:space="preserve">13.4971036911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3246021270752</t>
   </si>
   <si>
     <t xml:space="preserve">13.1707496643066</t>
@@ -5861,13 +5861,13 @@
     <t xml:space="preserve">13.189398765564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2919664382935</t>
+    <t xml:space="preserve">13.2919673919678</t>
   </si>
   <si>
     <t xml:space="preserve">13.5717010498047</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5623750686646</t>
+    <t xml:space="preserve">13.5623760223389</t>
   </si>
   <si>
     <t xml:space="preserve">13.501766204834</t>
@@ -5876,13 +5876,13 @@
     <t xml:space="preserve">13.7115659713745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4038600921631</t>
+    <t xml:space="preserve">13.4038610458374</t>
   </si>
   <si>
     <t xml:space="preserve">13.4364948272705</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4551458358765</t>
+    <t xml:space="preserve">13.4551448822021</t>
   </si>
   <si>
     <t xml:space="preserve">13.5950107574463</t>
@@ -5891,7 +5891,7 @@
     <t xml:space="preserve">13.6509580612183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4620933532715</t>
+    <t xml:space="preserve">12.4620923995972</t>
   </si>
   <si>
     <t xml:space="preserve">12.084454536438</t>
@@ -5900,19 +5900,19 @@
     <t xml:space="preserve">11.8513431549072</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8280334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9585742950439</t>
+    <t xml:space="preserve">11.8280324935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9585733413696</t>
   </si>
   <si>
     <t xml:space="preserve">11.8793163299561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9632368087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8979654312134</t>
+    <t xml:space="preserve">11.9632358551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8979663848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.8373565673828</t>
@@ -5930,16 +5930,16 @@
     <t xml:space="preserve">11.753436088562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7814102172852</t>
+    <t xml:space="preserve">11.7814111709595</t>
   </si>
   <si>
     <t xml:space="preserve">11.9772243499756</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6415433883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2802667617798</t>
+    <t xml:space="preserve">11.641544342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2802677154541</t>
   </si>
   <si>
     <t xml:space="preserve">12.2849292755127</t>
@@ -5948,16 +5948,16 @@
     <t xml:space="preserve">12.3548622131348</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3735113143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1823606491089</t>
+    <t xml:space="preserve">12.3735122680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1823596954346</t>
   </si>
   <si>
     <t xml:space="preserve">12.0145206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1217517852783</t>
+    <t xml:space="preserve">12.1217527389526</t>
   </si>
   <si>
     <t xml:space="preserve">11.865330696106</t>
@@ -5975,22 +5975,22 @@
     <t xml:space="preserve">12.3175649642944</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3082408905029</t>
+    <t xml:space="preserve">12.3082399368286</t>
   </si>
   <si>
     <t xml:space="preserve">12.471417427063</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3268899917603</t>
+    <t xml:space="preserve">12.3268890380859</t>
   </si>
   <si>
     <t xml:space="preserve">12.3362131118774</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8723678588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8956785202026</t>
+    <t xml:space="preserve">12.872368812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.895679473877</t>
   </si>
   <si>
     <t xml:space="preserve">12.8164215087891</t>
@@ -5999,7 +5999,7 @@
     <t xml:space="preserve">13.2080478668213</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1800737380981</t>
+    <t xml:space="preserve">13.1800746917725</t>
   </si>
   <si>
     <t xml:space="preserve">13.553050994873</t>
@@ -6008,10 +6008,10 @@
     <t xml:space="preserve">13.6975793838501</t>
   </si>
   <si>
-    <t xml:space="preserve">13.702241897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8747434616089</t>
+    <t xml:space="preserve">13.7022409439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8747444152832</t>
   </si>
   <si>
     <t xml:space="preserve">13.4598073959351</t>
@@ -6038,19 +6038,19 @@
     <t xml:space="preserve">13.8421087265015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7255535125732</t>
+    <t xml:space="preserve">13.7255525588989</t>
   </si>
   <si>
     <t xml:space="preserve">13.5577125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">13.814133644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0798816680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.99596118927</t>
+    <t xml:space="preserve">13.8141345977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0798807144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9959602355957</t>
   </si>
   <si>
     <t xml:space="preserve">14.1218404769897</t>
@@ -6065,7 +6065,7 @@
     <t xml:space="preserve">14.4202222824097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3946256637573</t>
+    <t xml:space="preserve">15.394624710083</t>
   </si>
   <si>
     <t xml:space="preserve">16.1405792236328</t>
@@ -6077,13 +6077,13 @@
     <t xml:space="preserve">16.3643646240234</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1359176635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2291603088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2757816314697</t>
+    <t xml:space="preserve">16.1359157562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2291622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2757835388184</t>
   </si>
   <si>
     <t xml:space="preserve">16.4016628265381</t>
@@ -6092,7 +6092,7 @@
     <t xml:space="preserve">16.5484447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4679508209229</t>
+    <t xml:space="preserve">16.4679489135742</t>
   </si>
   <si>
     <t xml:space="preserve">16.5531787872314</t>
@@ -6104,7 +6104,7 @@
     <t xml:space="preserve">16.9225006103516</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9556465148926</t>
+    <t xml:space="preserve">16.9556446075439</t>
   </si>
   <si>
     <t xml:space="preserve">17.0124626159668</t>
@@ -6113,7 +6113,7 @@
     <t xml:space="preserve">16.9698505401611</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1687145233154</t>
+    <t xml:space="preserve">17.1687126159668</t>
   </si>
   <si>
     <t xml:space="preserve">17.1971244812012</t>
@@ -6128,16 +6128,16 @@
     <t xml:space="preserve">17.3675804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6137943267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0929546356201</t>
+    <t xml:space="preserve">17.6137962341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0929565429688</t>
   </si>
   <si>
     <t xml:space="preserve">17.4764823913574</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5143642425537</t>
+    <t xml:space="preserve">17.5143623352051</t>
   </si>
   <si>
     <t xml:space="preserve">17.5427703857422</t>
@@ -6158,10 +6158,10 @@
     <t xml:space="preserve">17.2113285064697</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0503425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9982604980469</t>
+    <t xml:space="preserve">17.0503406524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9982585906982</t>
   </si>
   <si>
     <t xml:space="preserve">17.1118965148926</t>
@@ -6173,13 +6173,13 @@
     <t xml:space="preserve">17.253942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">17.490686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.594856262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9168262481689</t>
+    <t xml:space="preserve">17.4906883239746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5948543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9168281555176</t>
   </si>
   <si>
     <t xml:space="preserve">17.9310321807861</t>
@@ -6191,13 +6191,13 @@
     <t xml:space="preserve">18.058874130249</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9120941162109</t>
+    <t xml:space="preserve">17.9120922088623</t>
   </si>
   <si>
     <t xml:space="preserve">18.0115261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9641761779785</t>
+    <t xml:space="preserve">17.9641742706299</t>
   </si>
   <si>
     <t xml:space="preserve">17.9831161499023</t>
@@ -6212,13 +6212,13 @@
     <t xml:space="preserve">17.4717483520508</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6516723632812</t>
+    <t xml:space="preserve">17.6516742706299</t>
   </si>
   <si>
     <t xml:space="preserve">17.2207984924316</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3486404418945</t>
+    <t xml:space="preserve">17.3486385345459</t>
   </si>
   <si>
     <t xml:space="preserve">17.6043243408203</t>
@@ -6236,13 +6236,13 @@
     <t xml:space="preserve">17.9262962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7653121948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7605743408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6990242004395</t>
+    <t xml:space="preserve">17.7653102874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7605762481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6990222930908</t>
   </si>
   <si>
     <t xml:space="preserve">17.3107624053955</t>
@@ -6251,7 +6251,7 @@
     <t xml:space="preserve">16.7141647338867</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8420066833496</t>
+    <t xml:space="preserve">16.8420085906982</t>
   </si>
   <si>
     <t xml:space="preserve">17.1355686187744</t>
@@ -6263,16 +6263,16 @@
     <t xml:space="preserve">16.032341003418</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9518480300903</t>
+    <t xml:space="preserve">15.951847076416</t>
   </si>
   <si>
     <t xml:space="preserve">16.4300708770752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3590488433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8997640609741</t>
+    <t xml:space="preserve">16.3590469360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8997650146484</t>
   </si>
   <si>
     <t xml:space="preserve">15.8287410736084</t>
@@ -6281,13 +6281,13 @@
     <t xml:space="preserve">16.1791210174561</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1933269500732</t>
+    <t xml:space="preserve">16.1933288574219</t>
   </si>
   <si>
     <t xml:space="preserve">16.647876739502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8609466552734</t>
+    <t xml:space="preserve">16.8609485626221</t>
   </si>
   <si>
     <t xml:space="preserve">17.3154964447021</t>
@@ -6311,10 +6311,10 @@
     <t xml:space="preserve">17.145040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1024265289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4783582687378</t>
+    <t xml:space="preserve">17.102424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4783573150635</t>
   </si>
   <si>
     <t xml:space="preserve">14.6497535705566</t>
@@ -6338,7 +6338,7 @@
     <t xml:space="preserve">13.4139461517334</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5796670913696</t>
+    <t xml:space="preserve">13.5796680450439</t>
   </si>
   <si>
     <t xml:space="preserve">13.7737979888916</t>
@@ -6350,7 +6350,7 @@
     <t xml:space="preserve">13.7832679748535</t>
   </si>
   <si>
-    <t xml:space="preserve">13.920578956604</t>
+    <t xml:space="preserve">13.9205799102783</t>
   </si>
   <si>
     <t xml:space="preserve">13.9963369369507</t>
@@ -6359,13 +6359,13 @@
     <t xml:space="preserve">14.0200128555298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9679288864136</t>
+    <t xml:space="preserve">13.9679279327393</t>
   </si>
   <si>
     <t xml:space="preserve">13.9063749313354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9584579467773</t>
+    <t xml:space="preserve">13.9584589004517</t>
   </si>
   <si>
     <t xml:space="preserve">14.1052408218384</t>
@@ -6377,13 +6377,13 @@
     <t xml:space="preserve">14.1715288162231</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2899007797241</t>
+    <t xml:space="preserve">14.2899017333984</t>
   </si>
   <si>
     <t xml:space="preserve">14.7633905410767</t>
   </si>
   <si>
-    <t xml:space="preserve">14.796534538269</t>
+    <t xml:space="preserve">14.7965335845947</t>
   </si>
   <si>
     <t xml:space="preserve">14.7775945663452</t>
@@ -6747,6 +6747,9 @@
   </si>
   <si>
     <t xml:space="preserve">17.2049999237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1450004577637</t>
   </si>
 </sst>
 </file>
@@ -72579,7 +72582,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6912962963</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>1968507</v>
@@ -72600,6 +72603,32 @@
         <v>2244</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6911226852</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>1189178</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>17.3649997711182</v>
+      </c>
+      <c r="D2521" t="n">